--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -48603,6 +48603,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2098">
+      <c r="A2098" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2098" t="n">
+        <v>113794</v>
+      </c>
+      <c r="C2098" t="n">
+        <v>26.8999996185303</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>25.0499992370605</v>
+      </c>
+      <c r="E2098" t="n">
+        <v>26.8500003814697</v>
+      </c>
+      <c r="F2098" t="n">
+        <v>25.0499992370605</v>
+      </c>
+      <c r="G2098" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -48626,6 +48626,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2099">
+      <c r="A2099" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2099" t="n">
+        <v>63916</v>
+      </c>
+      <c r="C2099" t="n">
+        <v>25.3999996185303</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>25</v>
+      </c>
+      <c r="E2099" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="F2099" t="n">
+        <v>25.1000003814697</v>
+      </c>
+      <c r="G2099" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -48649,6 +48649,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2100">
+      <c r="A2100" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2100" t="n">
+        <v>133440</v>
+      </c>
+      <c r="C2100" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>24.9500007629395</v>
+      </c>
+      <c r="E2100" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>25.7000007629395</v>
+      </c>
+      <c r="G2100" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -48672,6 +48672,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2101">
+      <c r="A2101" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2101" t="n">
+        <v>71542</v>
+      </c>
+      <c r="C2101" t="n">
+        <v>26.7999992370605</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>25.7000007629395</v>
+      </c>
+      <c r="E2101" t="n">
+        <v>26.7999992370605</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>26.1000003814697</v>
+      </c>
+      <c r="G2101" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -48513,22 +48513,22 @@
     </row>
     <row r="2094">
       <c r="A2094" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2094" t="n">
-        <v>56268</v>
+        <v>75773</v>
       </c>
       <c r="C2094" t="n">
+        <v>28</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>27.6000003814697</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>27.7000007629395</v>
+      </c>
+      <c r="F2094" t="n">
         <v>27.9500007629395</v>
-      </c>
-      <c r="D2094" t="n">
-        <v>27.1000003814697</v>
-      </c>
-      <c r="E2094" t="n">
-        <v>27.8999996185303</v>
-      </c>
-      <c r="F2094" t="n">
-        <v>27.3999996185303</v>
       </c>
       <c r="G2094" t="s">
         <v>7</v>
@@ -48536,22 +48536,22 @@
     </row>
     <row r="2095">
       <c r="A2095" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2095" t="n">
-        <v>63196</v>
+        <v>56268</v>
       </c>
       <c r="C2095" t="n">
+        <v>27.9500007629395</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>27.1000003814697</v>
+      </c>
+      <c r="E2095" t="n">
+        <v>27.8999996185303</v>
+      </c>
+      <c r="F2095" t="n">
         <v>27.3999996185303</v>
-      </c>
-      <c r="D2095" t="n">
-        <v>26.75</v>
-      </c>
-      <c r="E2095" t="n">
-        <v>27.25</v>
-      </c>
-      <c r="F2095" t="n">
-        <v>27</v>
       </c>
       <c r="G2095" t="s">
         <v>7</v>
@@ -48559,22 +48559,22 @@
     </row>
     <row r="2096">
       <c r="A2096" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2096" t="n">
-        <v>43828</v>
+        <v>63196</v>
       </c>
       <c r="C2096" t="n">
-        <v>27.5499992370605</v>
+        <v>27.3999996185303</v>
       </c>
       <c r="D2096" t="n">
-        <v>26.8999996185303</v>
+        <v>26.75</v>
       </c>
       <c r="E2096" t="n">
-        <v>27.3999996185303</v>
+        <v>27.25</v>
       </c>
       <c r="F2096" t="n">
-        <v>27.25</v>
+        <v>27</v>
       </c>
       <c r="G2096" t="s">
         <v>7</v>
@@ -48582,22 +48582,22 @@
     </row>
     <row r="2097">
       <c r="A2097" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2097" t="n">
-        <v>45298</v>
+        <v>43828</v>
       </c>
       <c r="C2097" t="n">
-        <v>27.3500003814697</v>
+        <v>27.5499992370605</v>
       </c>
       <c r="D2097" t="n">
-        <v>26.8500003814697</v>
+        <v>26.8999996185303</v>
       </c>
       <c r="E2097" t="n">
-        <v>27.0499992370605</v>
+        <v>27.3999996185303</v>
       </c>
       <c r="F2097" t="n">
-        <v>26.9500007629395</v>
+        <v>27.25</v>
       </c>
       <c r="G2097" t="s">
         <v>7</v>
@@ -48605,22 +48605,22 @@
     </row>
     <row r="2098">
       <c r="A2098" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2098" t="n">
-        <v>113794</v>
+        <v>45298</v>
       </c>
       <c r="C2098" t="n">
-        <v>26.8999996185303</v>
+        <v>27.3500003814697</v>
       </c>
       <c r="D2098" t="n">
-        <v>25.0499992370605</v>
+        <v>26.8500003814697</v>
       </c>
       <c r="E2098" t="n">
-        <v>26.8500003814697</v>
+        <v>27.0499992370605</v>
       </c>
       <c r="F2098" t="n">
-        <v>25.0499992370605</v>
+        <v>26.9500007629395</v>
       </c>
       <c r="G2098" t="s">
         <v>7</v>
@@ -48628,22 +48628,22 @@
     </row>
     <row r="2099">
       <c r="A2099" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2099" t="n">
-        <v>63916</v>
+        <v>113794</v>
       </c>
       <c r="C2099" t="n">
-        <v>25.3999996185303</v>
+        <v>26.8999996185303</v>
       </c>
       <c r="D2099" t="n">
-        <v>25</v>
+        <v>25.0499992370605</v>
       </c>
       <c r="E2099" t="n">
-        <v>25.25</v>
+        <v>26.8500003814697</v>
       </c>
       <c r="F2099" t="n">
-        <v>25.1000003814697</v>
+        <v>25.0499992370605</v>
       </c>
       <c r="G2099" t="s">
         <v>7</v>
@@ -48651,22 +48651,22 @@
     </row>
     <row r="2100">
       <c r="A2100" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2100" t="n">
-        <v>133440</v>
+        <v>63916</v>
       </c>
       <c r="C2100" t="n">
-        <v>25.75</v>
+        <v>25.3999996185303</v>
       </c>
       <c r="D2100" t="n">
-        <v>24.9500007629395</v>
+        <v>25</v>
       </c>
       <c r="E2100" t="n">
-        <v>25</v>
+        <v>25.25</v>
       </c>
       <c r="F2100" t="n">
-        <v>25.7000007629395</v>
+        <v>25.1000003814697</v>
       </c>
       <c r="G2100" t="s">
         <v>7</v>
@@ -48674,24 +48674,47 @@
     </row>
     <row r="2101">
       <c r="A2101" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2101" t="n">
-        <v>71542</v>
+        <v>133440</v>
       </c>
       <c r="C2101" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>24.9500007629395</v>
+      </c>
+      <c r="E2101" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>25.7000007629395</v>
+      </c>
+      <c r="G2101" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2102" t="n">
+        <v>440017</v>
+      </c>
+      <c r="C2102" t="n">
         <v>26.7999992370605</v>
       </c>
-      <c r="D2101" t="n">
-        <v>25.7000007629395</v>
-      </c>
-      <c r="E2101" t="n">
+      <c r="D2102" t="n">
+        <v>26.2000007629395</v>
+      </c>
+      <c r="E2102" t="n">
         <v>26.7999992370605</v>
       </c>
-      <c r="F2101" t="n">
-        <v>26.1000003814697</v>
-      </c>
-      <c r="G2101" t="s">
+      <c r="F2102" t="n">
+        <v>26.6000003814697</v>
+      </c>
+      <c r="G2102" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G2" t="n">
-        <v>7.53173160552979</v>
+        <v>7.5317325592041</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G4" t="n">
-        <v>7.75996541976929</v>
+        <v>7.75996685028076</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G5" t="n">
-        <v>7.75996541976929</v>
+        <v>7.75996685028076</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G6" t="n">
-        <v>7.66867399215698</v>
+        <v>7.66867351531982</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.31955623626709</v>
       </c>
       <c r="G8" t="n">
-        <v>7.82204580307007</v>
+        <v>7.82204627990723</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.41859817504883</v>
       </c>
       <c r="G9" t="n">
-        <v>7.91516447067261</v>
+        <v>7.91516542434692</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.10884761810303</v>
       </c>
       <c r="G10" t="n">
-        <v>7.62393808364868</v>
+        <v>7.62393760681152</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>8.42830753326416</v>
       </c>
       <c r="G11" t="n">
-        <v>7.92429399490356</v>
+        <v>7.92429494857788</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G12" t="n">
-        <v>7.53173160552979</v>
+        <v>7.5317325592041</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G13" t="n">
-        <v>7.53173160552979</v>
+        <v>7.5317325592041</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>7.71656322479248</v>
       </c>
       <c r="G15" t="n">
-        <v>7.25511264801025</v>
+        <v>7.25511312484741</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.95154619216919</v>
       </c>
       <c r="G16" t="n">
-        <v>7.47604322433472</v>
+        <v>7.47604417800903</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.00106716156006</v>
       </c>
       <c r="G18" t="n">
-        <v>7.52260303497314</v>
+        <v>7.52260255813599</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>7.8651270866394</v>
       </c>
       <c r="G19" t="n">
-        <v>7.39479207992554</v>
+        <v>7.3947925567627</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>7.95251703262329</v>
       </c>
       <c r="G20" t="n">
-        <v>7.47695589065552</v>
+        <v>7.47695636749268</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>7.97193717956543</v>
       </c>
       <c r="G21" t="n">
-        <v>7.49521493911743</v>
+        <v>7.49521541595459</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>8.24381828308105</v>
       </c>
       <c r="G23" t="n">
-        <v>7.7508373260498</v>
+        <v>7.75083780288696</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G24" t="n">
-        <v>7.66867399215698</v>
+        <v>7.66867351531982</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G25" t="n">
-        <v>7.80561399459839</v>
+        <v>7.80561304092407</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>8.37101936340332</v>
       </c>
       <c r="G26" t="n">
-        <v>7.87043285369873</v>
+        <v>7.87043190002441</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G27" t="n">
-        <v>7.80561399459839</v>
+        <v>7.80561304092407</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.45743942260742</v>
       </c>
       <c r="G28" t="n">
-        <v>7.95168399810791</v>
+        <v>7.95168590545654</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>8.31178760528564</v>
       </c>
       <c r="G29" t="n">
-        <v>7.81474304199219</v>
+        <v>7.81474256515503</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.47394561767578</v>
       </c>
       <c r="G30" t="n">
-        <v>7.96720361709595</v>
+        <v>7.96720218658447</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.20497798919678</v>
       </c>
       <c r="G33" t="n">
-        <v>7.71431875228882</v>
+        <v>7.71432018280029</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G34" t="n">
-        <v>7.80561399459839</v>
+        <v>7.80561304092407</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G35" t="n">
-        <v>7.66867399215698</v>
+        <v>7.66867351531982</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G36" t="n">
-        <v>7.66867399215698</v>
+        <v>7.66867351531982</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>8.31178760528564</v>
       </c>
       <c r="G37" t="n">
-        <v>7.81474304199219</v>
+        <v>7.81474256515503</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G38" t="n">
-        <v>7.80561399459839</v>
+        <v>7.80561304092407</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.29625225067139</v>
       </c>
       <c r="G40" t="n">
-        <v>7.80013513565063</v>
+        <v>7.80013704299927</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>8.12923908233643</v>
       </c>
       <c r="G41" t="n">
-        <v>7.64310932159424</v>
+        <v>7.6431097984314</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>8.1855583190918</v>
       </c>
       <c r="G43" t="n">
-        <v>7.69606161117554</v>
+        <v>7.69606113433838</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G44" t="n">
-        <v>7.66867399215698</v>
+        <v>7.66867351531982</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.99232816696167</v>
       </c>
       <c r="G47" t="n">
-        <v>7.5143871307373</v>
+        <v>7.51438617706299</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>8.22634029388428</v>
       </c>
       <c r="G49" t="n">
-        <v>7.73440456390381</v>
+        <v>7.73440504074097</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>8.1875</v>
       </c>
       <c r="G50" t="n">
-        <v>7.69788694381714</v>
+        <v>7.6978874206543</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>8.51667022705078</v>
       </c>
       <c r="G52" t="n">
-        <v>8.00737190246582</v>
+        <v>8.00737285614014</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>8.96721458435059</v>
       </c>
       <c r="G56" t="n">
-        <v>8.43097400665283</v>
+        <v>8.43097591400146</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.24977684020996</v>
       </c>
       <c r="G57" t="n">
-        <v>8.69663906097412</v>
+        <v>8.69664001464844</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.46728229522705</v>
       </c>
       <c r="G58" t="n">
-        <v>8.90113925933838</v>
+        <v>8.90113830566406</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.08859062194824</v>
       </c>
       <c r="G59" t="n">
-        <v>8.54509353637695</v>
+        <v>8.54509162902832</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.75844955444336</v>
       </c>
       <c r="G60" t="n">
-        <v>8.23469257354736</v>
+        <v>8.234694480896</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.94973659515381</v>
       </c>
       <c r="G62" t="n">
-        <v>8.41454315185547</v>
+        <v>8.41454219818115</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G63" t="n">
-        <v>8.3077278137207</v>
+        <v>8.30772876739502</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G64" t="n">
-        <v>8.39902114868164</v>
+        <v>8.39902210235596</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.20511054992676</v>
       </c>
       <c r="G65" t="n">
-        <v>8.65464305877686</v>
+        <v>8.65464496612549</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.24395084381104</v>
       </c>
       <c r="G66" t="n">
-        <v>8.69116020202637</v>
+        <v>8.69116306304932</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.10412693023682</v>
       </c>
       <c r="G67" t="n">
-        <v>8.55970001220703</v>
+        <v>8.55970096588135</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.29250144958496</v>
       </c>
       <c r="G69" t="n">
-        <v>8.73680973052979</v>
+        <v>8.73680877685547</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.37115287780762</v>
       </c>
       <c r="G72" t="n">
-        <v>8.81075668334961</v>
+        <v>8.81075763702393</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.66148281097412</v>
       </c>
       <c r="G74" t="n">
-        <v>9.08372497558594</v>
+        <v>9.08372688293457</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G75" t="n">
-        <v>9.27544212341309</v>
+        <v>9.27544116973877</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.63332366943359</v>
       </c>
       <c r="G77" t="n">
-        <v>9.05724906921387</v>
+        <v>9.0572509765625</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.70614910125732</v>
       </c>
       <c r="G79" t="n">
-        <v>9.12572193145752</v>
+        <v>9.1257209777832</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.57506275177002</v>
       </c>
       <c r="G80" t="n">
-        <v>9.00247383117676</v>
+        <v>9.00247478485107</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.26239967346191</v>
       </c>
       <c r="G82" t="n">
-        <v>8.70850849151611</v>
+        <v>8.7085075378418</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.50320911407471</v>
       </c>
       <c r="G83" t="n">
-        <v>8.93491554260254</v>
+        <v>8.93491744995117</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.55467224121094</v>
       </c>
       <c r="G84" t="n">
-        <v>8.98330307006836</v>
+        <v>8.98330211639404</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.40610885620117</v>
       </c>
       <c r="G85" t="n">
-        <v>8.84362411499023</v>
+        <v>8.84362316131592</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.16238689422607</v>
       </c>
       <c r="G86" t="n">
-        <v>8.61447620391846</v>
+        <v>8.61447525024414</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.98954772949219</v>
       </c>
       <c r="G87" t="n">
-        <v>8.4519739151001</v>
+        <v>8.45197296142578</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G88" t="n">
-        <v>8.3077278137207</v>
+        <v>8.30772876739502</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>8.43413352966309</v>
       </c>
       <c r="G89" t="n">
-        <v>7.92977237701416</v>
+        <v>7.929771900177</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>8.88467979431152</v>
       </c>
       <c r="G91" t="n">
-        <v>8.3533763885498</v>
+        <v>8.35337543487549</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.03033065795898</v>
       </c>
       <c r="G92" t="n">
-        <v>8.49031543731689</v>
+        <v>8.49031734466553</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.07888126373291</v>
       </c>
       <c r="G93" t="n">
-        <v>8.535964012146</v>
+        <v>8.53596305847168</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.07888126373291</v>
       </c>
       <c r="G95" t="n">
-        <v>8.535964012146</v>
+        <v>8.53596305847168</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.30706596374512</v>
       </c>
       <c r="G96" t="n">
-        <v>8.75050354003906</v>
+        <v>8.75050258636475</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G97" t="n">
-        <v>8.3077278137207</v>
+        <v>8.30772876739502</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G98" t="n">
-        <v>7.80561399459839</v>
+        <v>7.80561304092407</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>8.48462677001953</v>
       </c>
       <c r="G99" t="n">
-        <v>7.97724533081055</v>
+        <v>7.97724628448486</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.97193717956543</v>
       </c>
       <c r="G100" t="n">
-        <v>7.49521493911743</v>
+        <v>7.49521541595459</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G101" t="n">
-        <v>7.75996541976929</v>
+        <v>7.75996685028076</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>8.19041347503662</v>
       </c>
       <c r="G102" t="n">
-        <v>7.70062637329102</v>
+        <v>7.70062732696533</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>8.3700475692749</v>
       </c>
       <c r="G103" t="n">
-        <v>7.86951732635498</v>
+        <v>7.8695182800293</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>8.3700475692749</v>
       </c>
       <c r="G104" t="n">
-        <v>7.86951732635498</v>
+        <v>7.8695182800293</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.81476783752441</v>
       </c>
       <c r="G105" t="n">
-        <v>8.2876443862915</v>
+        <v>8.28764533996582</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.27210998535156</v>
       </c>
       <c r="G106" t="n">
-        <v>8.71763801574707</v>
+        <v>8.71763706207275</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.25074768066406</v>
       </c>
       <c r="G108" t="n">
-        <v>8.69755172729492</v>
+        <v>8.69755268096924</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.98760604858398</v>
       </c>
       <c r="G109" t="n">
-        <v>8.45014667510986</v>
+        <v>8.45014762878418</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.08664894104004</v>
       </c>
       <c r="G110" t="n">
-        <v>8.54326725006104</v>
+        <v>8.54326629638672</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.19443035125732</v>
       </c>
       <c r="G111" t="n">
-        <v>8.64460277557373</v>
+        <v>8.64460372924805</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.06334495544434</v>
       </c>
       <c r="G112" t="n">
-        <v>8.52135753631592</v>
+        <v>8.5213565826416</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.81379699707031</v>
       </c>
       <c r="G114" t="n">
-        <v>8.28673267364502</v>
+        <v>8.2867317199707</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>9.04586696624756</v>
       </c>
       <c r="G115" t="n">
-        <v>8.50492286682129</v>
+        <v>8.50492382049561</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.2138500213623</v>
       </c>
       <c r="G116" t="n">
-        <v>8.66286277770996</v>
+        <v>8.66286087036133</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.51084423065186</v>
       </c>
       <c r="G117" t="n">
-        <v>8.00189590454102</v>
+        <v>8.0018949508667</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.49724960327148</v>
       </c>
       <c r="G118" t="n">
-        <v>7.98911333084106</v>
+        <v>7.98911380767822</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>8.54482936859131</v>
       </c>
       <c r="G119" t="n">
-        <v>8.03384876251221</v>
+        <v>8.03384685516357</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.03324413299561</v>
       </c>
       <c r="G121" t="n">
-        <v>8.49305725097656</v>
+        <v>8.49305534362793</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>8.80700016021729</v>
       </c>
       <c r="G122" t="n">
-        <v>8.28034210205078</v>
+        <v>8.28034019470215</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G123" t="n">
-        <v>8.39902114868164</v>
+        <v>8.39902210235596</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>8.99149036407471</v>
       </c>
       <c r="G124" t="n">
-        <v>8.45379829406738</v>
+        <v>8.4537992477417</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G125" t="n">
-        <v>8.39902114868164</v>
+        <v>8.39902210235596</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.42650032043457</v>
       </c>
       <c r="G126" t="n">
-        <v>8.86279582977295</v>
+        <v>8.86279487609863</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.52748394012451</v>
       </c>
       <c r="G129" t="n">
-        <v>8.95773983001709</v>
+        <v>8.95774173736572</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.5935115814209</v>
       </c>
       <c r="G134" t="n">
-        <v>9.01981735229492</v>
+        <v>9.01981830596924</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G136" t="n">
-        <v>8.3077278137207</v>
+        <v>8.30772876739502</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>8.70018863677979</v>
       </c>
       <c r="G138" t="n">
-        <v>8.17991733551025</v>
+        <v>8.17991828918457</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G139" t="n">
-        <v>8.21643447875977</v>
+        <v>8.2164363861084</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>8.7429141998291</v>
       </c>
       <c r="G144" t="n">
-        <v>8.2200870513916</v>
+        <v>8.22008800506592</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>8.76815986633301</v>
       </c>
       <c r="G145" t="n">
-        <v>8.24382400512695</v>
+        <v>8.24382305145264</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G146" t="n">
-        <v>8.3077278137207</v>
+        <v>8.30772876739502</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>8.98178005218506</v>
       </c>
       <c r="G148" t="n">
-        <v>8.44466876983643</v>
+        <v>8.44466781616211</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>8.91380977630615</v>
       </c>
       <c r="G150" t="n">
-        <v>8.38076210021973</v>
+        <v>8.38076496124268</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>8.69047927856445</v>
       </c>
       <c r="G151" t="n">
-        <v>8.17078876495361</v>
+        <v>8.1707878112793</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G152" t="n">
-        <v>8.21643447875977</v>
+        <v>8.2164363861084</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>8.61474132537842</v>
       </c>
       <c r="G156" t="n">
-        <v>8.09958076477051</v>
+        <v>8.09957885742188</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G157" t="n">
-        <v>8.21643447875977</v>
+        <v>8.2164363861084</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>8.87497043609619</v>
       </c>
       <c r="G158" t="n">
-        <v>8.34424781799316</v>
+        <v>8.34424686431885</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.20316886901855</v>
       </c>
       <c r="G161" t="n">
-        <v>8.65281963348389</v>
+        <v>8.65281867980957</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>9.20316886901855</v>
       </c>
       <c r="G162" t="n">
-        <v>8.65281963348389</v>
+        <v>8.65281867980957</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.26822566986084</v>
       </c>
       <c r="G163" t="n">
-        <v>8.71398639678955</v>
+        <v>8.71398544311523</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.21482086181641</v>
       </c>
       <c r="G164" t="n">
-        <v>8.66377449035645</v>
+        <v>8.66377353668213</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.61584568023682</v>
       </c>
       <c r="G165" t="n">
-        <v>9.04081726074219</v>
+        <v>9.04081630706787</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.33522605895996</v>
       </c>
       <c r="G169" t="n">
-        <v>8.77697944641113</v>
+        <v>8.77697849273682</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G171" t="n">
-        <v>8.992431640625</v>
+        <v>8.99243068695068</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.75858306884766</v>
       </c>
       <c r="G172" t="n">
-        <v>9.17501926422119</v>
+        <v>9.17502117156982</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.89258098602295</v>
       </c>
       <c r="G174" t="n">
-        <v>9.30100345611572</v>
+        <v>9.30100440979004</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.92753791809082</v>
       </c>
       <c r="G175" t="n">
-        <v>9.33386898040771</v>
+        <v>9.33386993408203</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>10.1547517776489</v>
       </c>
       <c r="G176" t="n">
-        <v>9.54749870300293</v>
+        <v>9.5474967956543</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>10.2440853118896</v>
       </c>
       <c r="G180" t="n">
-        <v>9.63148975372314</v>
+        <v>9.63148880004883</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.1897087097168</v>
       </c>
       <c r="G183" t="n">
-        <v>9.58036422729492</v>
+        <v>9.58036327362061</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.84791469573975</v>
       </c>
       <c r="G184" t="n">
-        <v>9.25900840759277</v>
+        <v>9.25900936126709</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>10.1625204086304</v>
       </c>
       <c r="G186" t="n">
-        <v>9.55480098724365</v>
+        <v>9.55480003356934</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>10.0304641723633</v>
       </c>
       <c r="G187" t="n">
-        <v>9.43064308166504</v>
+        <v>9.43064117431641</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>10.0498838424683</v>
       </c>
       <c r="G189" t="n">
-        <v>9.44890117645264</v>
+        <v>9.44890022277832</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>9.81101703643799</v>
       </c>
       <c r="G190" t="n">
-        <v>9.2243185043335</v>
+        <v>9.22431755065918</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>9.99939155578613</v>
       </c>
       <c r="G191" t="n">
-        <v>9.40142726898193</v>
+        <v>9.40142631530762</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G194" t="n">
-        <v>8.992431640625</v>
+        <v>8.99243068695068</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.78771305084229</v>
       </c>
       <c r="G195" t="n">
-        <v>9.20240688323975</v>
+        <v>9.20240783691406</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.66148281097412</v>
       </c>
       <c r="G196" t="n">
-        <v>9.08372497558594</v>
+        <v>9.08372688293457</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.66536712646484</v>
       </c>
       <c r="G197" t="n">
-        <v>9.08737850189209</v>
+        <v>9.08737754821777</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.44786167144775</v>
       </c>
       <c r="G199" t="n">
-        <v>8.88287925720215</v>
+        <v>8.88287830352783</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.03033065795898</v>
       </c>
       <c r="G200" t="n">
-        <v>8.49031543731689</v>
+        <v>8.49031734466553</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>8.87497043609619</v>
       </c>
       <c r="G201" t="n">
-        <v>8.34424781799316</v>
+        <v>8.34424686431885</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.5935115814209</v>
       </c>
       <c r="G204" t="n">
-        <v>9.01981735229492</v>
+        <v>9.01981830596924</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>9.51680278778076</v>
       </c>
       <c r="G205" t="n">
-        <v>8.94769668579102</v>
+        <v>8.94769763946533</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>9.47699165344238</v>
       </c>
       <c r="G209" t="n">
-        <v>8.9102668762207</v>
+        <v>8.91026782989502</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>9.47699165344238</v>
       </c>
       <c r="G210" t="n">
-        <v>8.9102668762207</v>
+        <v>8.91026782989502</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.62264347076416</v>
       </c>
       <c r="G211" t="n">
-        <v>9.04720878601074</v>
+        <v>9.04720783233643</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.66148281097412</v>
       </c>
       <c r="G212" t="n">
-        <v>9.08372497558594</v>
+        <v>9.08372688293457</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.78771305084229</v>
       </c>
       <c r="G213" t="n">
-        <v>9.20240688323975</v>
+        <v>9.20240783691406</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G216" t="n">
-        <v>9.6771354675293</v>
+        <v>9.67713451385498</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>10.0013341903687</v>
       </c>
       <c r="G217" t="n">
-        <v>9.40325450897217</v>
+        <v>9.40325355529785</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.3120546340942</v>
       </c>
       <c r="G219" t="n">
-        <v>9.69539356231689</v>
+        <v>9.69539260864258</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G221" t="n">
-        <v>9.84146308898926</v>
+        <v>9.84146213531494</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>10.3120546340942</v>
       </c>
       <c r="G222" t="n">
-        <v>9.69539356231689</v>
+        <v>9.69539260864258</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G223" t="n">
-        <v>9.93275737762451</v>
+        <v>9.9327564239502</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G224" t="n">
-        <v>9.98753452301025</v>
+        <v>9.98753261566162</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G225" t="n">
-        <v>9.73191070556641</v>
+        <v>9.73190975189209</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G226" t="n">
-        <v>9.98753452301025</v>
+        <v>9.98753261566162</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G228" t="n">
-        <v>9.73191070556641</v>
+        <v>9.73190975189209</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G229" t="n">
-        <v>9.75016975402832</v>
+        <v>9.750168800354</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G230" t="n">
-        <v>9.73191070556641</v>
+        <v>9.73190975189209</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G231" t="n">
-        <v>9.73191070556641</v>
+        <v>9.73190975189209</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G234" t="n">
-        <v>10.042308807373</v>
+        <v>10.0423097610474</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.214955329895</v>
       </c>
       <c r="G235" t="n">
-        <v>9.60410022735596</v>
+        <v>9.60410118103027</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G236" t="n">
-        <v>9.71365165710449</v>
+        <v>9.71365261077881</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G237" t="n">
-        <v>9.76842880249023</v>
+        <v>9.76842784881592</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G239" t="n">
-        <v>10.0788278579712</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G240" t="n">
-        <v>10.042308807373</v>
+        <v>10.0423097610474</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G241" t="n">
-        <v>10.042308807373</v>
+        <v>10.0423097610474</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G242" t="n">
-        <v>10.0970869064331</v>
+        <v>10.0970849990845</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G244" t="n">
-        <v>10.2431564331055</v>
+        <v>10.2431573867798</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G248" t="n">
-        <v>9.93275737762451</v>
+        <v>9.9327564239502</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>11.1082782745361</v>
       </c>
       <c r="G251" t="n">
-        <v>10.4440031051636</v>
+        <v>10.4440011978149</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>11.3413181304932</v>
       </c>
       <c r="G254" t="n">
-        <v>10.6631059646606</v>
+        <v>10.6631088256836</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>11.0111770629883</v>
       </c>
       <c r="G255" t="n">
-        <v>10.352707862854</v>
+        <v>10.3527069091797</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>11.0694379806519</v>
       </c>
       <c r="G256" t="n">
-        <v>10.4074859619141</v>
+        <v>10.4074831008911</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>11.0305967330933</v>
       </c>
       <c r="G257" t="n">
-        <v>10.3709669113159</v>
+        <v>10.3709650039673</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G260" t="n">
-        <v>9.91450023651123</v>
+        <v>9.91449928283691</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G261" t="n">
-        <v>9.78668785095215</v>
+        <v>9.78668594360352</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G262" t="n">
-        <v>10.0788278579712</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G264" t="n">
-        <v>9.876145362854</v>
+        <v>9.87614440917969</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G266" t="n">
-        <v>9.85771942138672</v>
+        <v>9.8577184677124</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G267" t="n">
-        <v>9.85771942138672</v>
+        <v>9.8577184677124</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G269" t="n">
-        <v>10.0788278579712</v>
+        <v>10.0788259506226</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G276" t="n">
-        <v>9.83929347991943</v>
+        <v>9.83929252624512</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G282" t="n">
-        <v>9.67346382141113</v>
+        <v>9.67346286773682</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G283" t="n">
-        <v>9.876145362854</v>
+        <v>9.87614440917969</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G285" t="n">
-        <v>9.80244159698486</v>
+        <v>9.80244255065918</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.0500173568726</v>
       </c>
       <c r="G287" t="n">
-        <v>10.4841909408569</v>
+        <v>10.4841899871826</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>10.8558168411255</v>
       </c>
       <c r="G292" t="n">
-        <v>10.299934387207</v>
+        <v>10.2999334335327</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G294" t="n">
-        <v>9.76559162139893</v>
+        <v>9.76558971405029</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G299" t="n">
-        <v>9.80244159698486</v>
+        <v>9.80244255065918</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G300" t="n">
-        <v>9.67346382141113</v>
+        <v>9.67346286773682</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.2732152938843</v>
       </c>
       <c r="G301" t="n">
-        <v>9.74716663360596</v>
+        <v>9.74716567993164</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G302" t="n">
-        <v>9.83929347991943</v>
+        <v>9.83929252624512</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G303" t="n">
-        <v>10.0051259994507</v>
+        <v>10.0051250457764</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G310" t="n">
-        <v>10.1893815994263</v>
+        <v>10.1893787384033</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G311" t="n">
-        <v>10.1893815994263</v>
+        <v>10.1893787384033</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>11.0500173568726</v>
       </c>
       <c r="G313" t="n">
-        <v>10.4841909408569</v>
+        <v>10.4841899871826</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G314" t="n">
-        <v>10.7790012359619</v>
+        <v>10.7790021896362</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G315" t="n">
-        <v>10.4104881286621</v>
+        <v>10.4104871749878</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>11.6908798217773</v>
       </c>
       <c r="G318" t="n">
-        <v>11.0922365188599</v>
+        <v>11.0922374725342</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>12.15696144104</v>
       </c>
       <c r="G319" t="n">
-        <v>11.5344524383545</v>
+        <v>11.5344533920288</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>12.176381111145</v>
       </c>
       <c r="G323" t="n">
-        <v>11.5528783798218</v>
+        <v>11.5528793334961</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>12.0598611831665</v>
       </c>
       <c r="G324" t="n">
-        <v>11.442325592041</v>
+        <v>11.4423246383667</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>12.15696144104</v>
       </c>
       <c r="G325" t="n">
-        <v>11.5344524383545</v>
+        <v>11.5344533920288</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>12.176381111145</v>
       </c>
       <c r="G326" t="n">
-        <v>11.5528783798218</v>
+        <v>11.5528793334961</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G327" t="n">
-        <v>11.8845386505127</v>
+        <v>11.8845405578613</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G330" t="n">
-        <v>12.1609258651733</v>
+        <v>12.160924911499</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>13.0308637619019</v>
       </c>
       <c r="G331" t="n">
-        <v>12.3636064529419</v>
+        <v>12.3636054992676</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G333" t="n">
-        <v>12.1056480407715</v>
+        <v>12.1056470870972</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>12.0210208892822</v>
       </c>
       <c r="G339" t="n">
-        <v>11.4054737091064</v>
+        <v>11.4054727554321</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>12.4871015548706</v>
       </c>
       <c r="G344" t="n">
-        <v>11.8476886749268</v>
+        <v>11.8476877212524</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G346" t="n">
-        <v>11.8845386505127</v>
+        <v>11.8845405578613</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G347" t="n">
-        <v>12.0872211456299</v>
+        <v>12.0872220993042</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G348" t="n">
-        <v>12.1609258651733</v>
+        <v>12.160924911499</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>12.7978229522705</v>
       </c>
       <c r="G350" t="n">
-        <v>12.1424980163574</v>
+        <v>12.1424989700317</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>13.2833251953125</v>
       </c>
       <c r="G352" t="n">
-        <v>12.603138923645</v>
+        <v>12.6031398773193</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>13.5940456390381</v>
       </c>
       <c r="G353" t="n">
-        <v>12.8979511260986</v>
+        <v>12.89794921875</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>13.9824476242065</v>
       </c>
       <c r="G355" t="n">
-        <v>13.2664642333984</v>
+        <v>13.2664613723755</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>14.0989675521851</v>
       </c>
       <c r="G359" t="n">
-        <v>13.3770160675049</v>
+        <v>13.3770170211792</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.8270874023438</v>
       </c>
       <c r="G360" t="n">
-        <v>13.1190586090088</v>
+        <v>13.1190567016602</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G361" t="n">
-        <v>13.0269298553467</v>
+        <v>13.0269317626953</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G362" t="n">
-        <v>13.0269298553467</v>
+        <v>13.0269317626953</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G365" t="n">
-        <v>12.2162017822266</v>
+        <v>12.2162008285522</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>12.9920244216919</v>
       </c>
       <c r="G366" t="n">
-        <v>12.3267555236816</v>
+        <v>12.326756477356</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G367" t="n">
-        <v>12.1609258651733</v>
+        <v>12.160924911499</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G368" t="n">
-        <v>12.0872211456299</v>
+        <v>12.0872220993042</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G369" t="n">
-        <v>12.1056480407715</v>
+        <v>12.1056470870972</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.8560838699341</v>
       </c>
       <c r="G371" t="n">
-        <v>12.1977767944336</v>
+        <v>12.1977777481079</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>15.2835922241211</v>
       </c>
       <c r="G373" t="n">
-        <v>14.5009803771973</v>
+        <v>14.5009813308716</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>14.5650501251221</v>
       </c>
       <c r="G374" t="n">
-        <v>13.8192338943481</v>
+        <v>13.8192329406738</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>14.0407075881958</v>
       </c>
       <c r="G375" t="n">
-        <v>13.321741104126</v>
+        <v>13.3217391967773</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G377" t="n">
-        <v>12.768970489502</v>
+        <v>12.7689714431763</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>13.3027448654175</v>
       </c>
       <c r="G378" t="n">
-        <v>12.6215648651123</v>
+        <v>12.6215658187866</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G380" t="n">
-        <v>12.4741611480713</v>
+        <v>12.4741592407227</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G381" t="n">
-        <v>12.2899045944214</v>
+        <v>12.2899036407471</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G382" t="n">
-        <v>12.2899045944214</v>
+        <v>12.2899036407471</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G384" t="n">
-        <v>12.2162017822266</v>
+        <v>12.2162008285522</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>13.380425453186</v>
       </c>
       <c r="G385" t="n">
-        <v>12.6952695846558</v>
+        <v>12.6952667236328</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>13.4192657470703</v>
       </c>
       <c r="G386" t="n">
-        <v>12.7321195602417</v>
+        <v>12.732120513916</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>13.7105674743652</v>
       </c>
       <c r="G388" t="n">
-        <v>13.008505821228</v>
+        <v>13.0085048675537</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>13.6911468505859</v>
       </c>
       <c r="G390" t="n">
-        <v>12.9900798797607</v>
+        <v>12.9900789260864</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>13.9630270004272</v>
       </c>
       <c r="G391" t="n">
-        <v>13.2480363845825</v>
+        <v>13.2480373382568</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>13.9630270004272</v>
       </c>
       <c r="G392" t="n">
-        <v>13.2480363845825</v>
+        <v>13.2480373382568</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G394" t="n">
-        <v>12.768970489502</v>
+        <v>12.7689714431763</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>13.2444849014282</v>
       </c>
       <c r="G397" t="n">
-        <v>12.5662899017334</v>
+        <v>12.5662879943848</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>12.8949241638184</v>
       </c>
       <c r="G398" t="n">
-        <v>12.2346277236938</v>
+        <v>12.2346286773682</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G399" t="n">
-        <v>12.1056480407715</v>
+        <v>12.1056470870972</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>13.0502843856812</v>
       </c>
       <c r="G400" t="n">
-        <v>12.3820323944092</v>
+        <v>12.3820333480835</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G401" t="n">
-        <v>12.3451805114746</v>
+        <v>12.3451814651489</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G402" t="n">
-        <v>12.3451805114746</v>
+        <v>12.3451814651489</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G404" t="n">
-        <v>12.3451805114746</v>
+        <v>12.3451814651489</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G405" t="n">
-        <v>12.1609258651733</v>
+        <v>12.160924911499</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G407" t="n">
-        <v>12.0872211456299</v>
+        <v>12.0872220993042</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G408" t="n">
-        <v>11.8845386505127</v>
+        <v>11.8845405578613</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>12.4871015548706</v>
       </c>
       <c r="G409" t="n">
-        <v>11.8476886749268</v>
+        <v>11.8476877212524</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>12.4094219207764</v>
       </c>
       <c r="G410" t="n">
-        <v>11.7739868164062</v>
+        <v>11.7739858627319</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G411" t="n">
-        <v>11.7002840042114</v>
+        <v>11.7002849578857</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G413" t="n">
-        <v>10.9448308944702</v>
+        <v>10.9448318481445</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>11.6131992340088</v>
       </c>
       <c r="G414" t="n">
-        <v>11.0185346603394</v>
+        <v>11.0185356140137</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G415" t="n">
-        <v>10.9632568359375</v>
+        <v>10.9632587432861</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G416" t="n">
-        <v>10.7790012359619</v>
+        <v>10.7790021896362</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G417" t="n">
-        <v>10.9632568359375</v>
+        <v>10.9632587432861</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G419" t="n">
-        <v>10.9448308944702</v>
+        <v>10.9448318481445</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G420" t="n">
-        <v>11.2396440505981</v>
+        <v>11.2396421432495</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G421" t="n">
-        <v>11.2396440505981</v>
+        <v>11.2396421432495</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G422" t="n">
-        <v>11.0553865432739</v>
+        <v>11.0553874969482</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G425" t="n">
-        <v>11.2396440505981</v>
+        <v>11.2396421432495</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G426" t="n">
-        <v>11.2396440505981</v>
+        <v>11.2396421432495</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G427" t="n">
-        <v>11.2396440505981</v>
+        <v>11.2396421432495</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G432" t="n">
-        <v>10.0788278579712</v>
+        <v>10.0788259506226</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G433" t="n">
-        <v>10.4104881286621</v>
+        <v>10.4104871749878</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G434" t="n">
-        <v>10.7790012359619</v>
+        <v>10.7790021896362</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G441" t="n">
-        <v>10.0788278579712</v>
+        <v>10.0788259506226</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G442" t="n">
-        <v>9.67346382141113</v>
+        <v>9.67346286773682</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G443" t="n">
-        <v>9.36022663116455</v>
+        <v>9.36022472381592</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.84597301483154</v>
       </c>
       <c r="G444" t="n">
-        <v>9.34180164337158</v>
+        <v>9.34180068969727</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>10.0013341903687</v>
       </c>
       <c r="G446" t="n">
-        <v>9.48920726776123</v>
+        <v>9.48920631408691</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.12743091583252</v>
       </c>
       <c r="G447" t="n">
-        <v>8.66005325317383</v>
+        <v>8.66005229949951</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G448" t="n">
-        <v>9.85771942138672</v>
+        <v>9.8577184677124</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.6322193145752</v>
       </c>
       <c r="G451" t="n">
-        <v>8.19019985198975</v>
+        <v>8.1901969909668</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>8.58366870880127</v>
       </c>
       <c r="G452" t="n">
-        <v>8.14413261413574</v>
+        <v>8.14413452148438</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G453" t="n">
-        <v>8.47579479217529</v>
+        <v>8.47579669952393</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G454" t="n">
-        <v>8.3836669921875</v>
+        <v>8.38366794586182</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>10.0984344482422</v>
       </c>
       <c r="G455" t="n">
-        <v>9.58133506774902</v>
+        <v>9.58133602142334</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G456" t="n">
-        <v>11.7002840042114</v>
+        <v>11.7002849578857</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G459" t="n">
-        <v>10.0788278579712</v>
+        <v>10.0788259506226</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>10.234375</v>
       </c>
       <c r="G461" t="n">
-        <v>9.71031475067139</v>
+        <v>9.71031379699707</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>10.7781372070312</v>
       </c>
       <c r="G463" t="n">
-        <v>10.2262315750122</v>
+        <v>10.2262334823608</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G465" t="n">
-        <v>9.76559162139893</v>
+        <v>9.76558971405029</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>10.2732152938843</v>
       </c>
       <c r="G466" t="n">
-        <v>9.74716663360596</v>
+        <v>9.74716567993164</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>11.2053775787354</v>
       </c>
       <c r="G469" t="n">
-        <v>10.6315956115723</v>
+        <v>10.6315965652466</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G470" t="n">
-        <v>11.0553865432739</v>
+        <v>11.0553874969482</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G472" t="n">
-        <v>11.0553865432739</v>
+        <v>11.0553874969482</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G473" t="n">
-        <v>11.7002840042114</v>
+        <v>11.7002849578857</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>12.2346420288086</v>
       </c>
       <c r="G474" t="n">
-        <v>11.6081552505493</v>
+        <v>11.6081571578979</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>13.0697040557861</v>
       </c>
       <c r="G476" t="n">
-        <v>12.4004564285278</v>
+        <v>12.4004583358765</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G477" t="n">
-        <v>12.4741611480713</v>
+        <v>12.4741592407227</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G479" t="n">
-        <v>12.3451805114746</v>
+        <v>12.3451814651489</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>12.3123216629028</v>
       </c>
       <c r="G482" t="n">
-        <v>11.6818571090698</v>
+        <v>11.6818590164185</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G485" t="n">
-        <v>11.7002840042114</v>
+        <v>11.7002849578857</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>14.3708486557007</v>
       </c>
       <c r="G489" t="n">
-        <v>13.6349763870239</v>
+        <v>13.6349754333496</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>14.1183881759644</v>
       </c>
       <c r="G490" t="n">
-        <v>13.3954439163208</v>
+        <v>13.3954420089722</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G491" t="n">
-        <v>13.0269298553467</v>
+        <v>13.0269317626953</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>14.2931690216064</v>
       </c>
       <c r="G492" t="n">
-        <v>13.5612735748291</v>
+        <v>13.5612745285034</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>15.7496738433838</v>
       </c>
       <c r="G494" t="n">
-        <v>14.9431962966919</v>
+        <v>14.9431972503662</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>15.633152961731</v>
       </c>
       <c r="G495" t="n">
-        <v>14.8326425552368</v>
+        <v>14.8326435089111</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G497" t="n">
-        <v>15.1827306747437</v>
+        <v>15.1827297210693</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G498" t="n">
-        <v>15.6433715820312</v>
+        <v>15.6433725357056</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>16.7206764221191</v>
       </c>
       <c r="G499" t="n">
-        <v>15.8644790649414</v>
+        <v>15.8644781112671</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>15.6525726318359</v>
       </c>
       <c r="G501" t="n">
-        <v>14.8510675430298</v>
+        <v>14.8510684967041</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>15.3030118942261</v>
       </c>
       <c r="G502" t="n">
-        <v>14.5194082260132</v>
+        <v>14.5194072723389</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>15.1476516723633</v>
       </c>
       <c r="G503" t="n">
-        <v>14.3720006942749</v>
+        <v>14.3720026016235</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G504" t="n">
-        <v>13.9482116699219</v>
+        <v>13.9482126235962</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G505" t="n">
-        <v>13.9482116699219</v>
+        <v>13.9482126235962</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>14.4485292434692</v>
       </c>
       <c r="G507" t="n">
-        <v>13.7086791992188</v>
+        <v>13.7086801528931</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>14.4679489135742</v>
       </c>
       <c r="G508" t="n">
-        <v>13.7271041870117</v>
+        <v>13.727105140686</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>14.3125886917114</v>
       </c>
       <c r="G509" t="n">
-        <v>13.5796976089478</v>
+        <v>13.5796995162964</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>14.7398300170898</v>
       </c>
       <c r="G510" t="n">
-        <v>13.9850635528564</v>
+        <v>13.9850645065308</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>14.9922914505005</v>
       </c>
       <c r="G511" t="n">
-        <v>14.2245979309082</v>
+        <v>14.2245969772339</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>15.4001121520996</v>
       </c>
       <c r="G512" t="n">
-        <v>14.6115341186523</v>
+        <v>14.6115350723267</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>15.6914129257202</v>
       </c>
       <c r="G513" t="n">
-        <v>14.8879194259644</v>
+        <v>14.8879203796387</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>15.128231048584</v>
       </c>
       <c r="G514" t="n">
-        <v>14.4609594345093</v>
+        <v>14.4609603881836</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G515" t="n">
-        <v>14.7022838592529</v>
+        <v>14.7022848129272</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>15.4777927398682</v>
       </c>
       <c r="G516" t="n">
-        <v>14.7951011657715</v>
+        <v>14.7951021194458</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>15.3612718582153</v>
       </c>
       <c r="G517" t="n">
-        <v>14.6837215423584</v>
+        <v>14.6837205886841</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>15.3418521881104</v>
       </c>
       <c r="G518" t="n">
-        <v>14.6651582717896</v>
+        <v>14.6651573181152</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>15.5748929977417</v>
       </c>
       <c r="G519" t="n">
-        <v>14.8879194259644</v>
+        <v>14.8879203796387</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>15.8661937713623</v>
       </c>
       <c r="G520" t="n">
-        <v>15.16637134552</v>
+        <v>15.1663722991943</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G521" t="n">
-        <v>14.7022838592529</v>
+        <v>14.7022848129272</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G522" t="n">
-        <v>15.1292457580566</v>
+        <v>15.129246711731</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>16.0215549468994</v>
       </c>
       <c r="G523" t="n">
-        <v>15.3148794174194</v>
+        <v>15.3148803710938</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>15.9244537353516</v>
       </c>
       <c r="G524" t="n">
-        <v>15.2220621109009</v>
+        <v>15.2220611572266</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G525" t="n">
-        <v>14.9064826965332</v>
+        <v>14.9064836502075</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G527" t="n">
-        <v>14.9064826965332</v>
+        <v>14.9064836502075</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G531" t="n">
-        <v>15.0364284515381</v>
+        <v>15.0364274978638</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G534" t="n">
-        <v>15.1292457580566</v>
+        <v>15.129246711731</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G535" t="n">
-        <v>15.1292457580566</v>
+        <v>15.129246711731</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G536" t="n">
-        <v>14.9064826965332</v>
+        <v>14.9064836502075</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G539" t="n">
-        <v>14.8507928848267</v>
+        <v>14.8507919311523</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>15.0505514144897</v>
       </c>
       <c r="G540" t="n">
-        <v>14.3867053985596</v>
+        <v>14.3867063522339</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>15.0505514144897</v>
       </c>
       <c r="G541" t="n">
-        <v>14.3867053985596</v>
+        <v>14.3867063522339</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>15.3612718582153</v>
       </c>
       <c r="G542" t="n">
-        <v>14.6837215423584</v>
+        <v>14.6837205886841</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G543" t="n">
-        <v>14.8507928848267</v>
+        <v>14.8507919311523</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>16.1769142150879</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4633855819702</v>
+        <v>15.4633874893188</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G546" t="n">
-        <v>16.0574188232422</v>
+        <v>16.0574226379395</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G547" t="n">
-        <v>16.8556499481201</v>
+        <v>16.8556518554688</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G548" t="n">
-        <v>17.5610637664795</v>
+        <v>17.5610618591309</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G549" t="n">
-        <v>17.5610637664795</v>
+        <v>17.5610618591309</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G550" t="n">
-        <v>16.6143264770508</v>
+        <v>16.6143245697021</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>17.536319732666</v>
       </c>
       <c r="G551" t="n">
-        <v>16.7628326416016</v>
+        <v>16.7628345489502</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G554" t="n">
-        <v>17.2826099395752</v>
+        <v>17.2826118469238</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G560" t="n">
-        <v>17.5424995422363</v>
+        <v>17.542501449585</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G563" t="n">
-        <v>18.5634918212891</v>
+        <v>18.5634899139404</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G565" t="n">
-        <v>18.210786819458</v>
+        <v>18.2107849121094</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G566" t="n">
-        <v>18.5634918212891</v>
+        <v>18.5634899139404</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G568" t="n">
-        <v>18.0994052886963</v>
+        <v>18.0994033813477</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G569" t="n">
-        <v>17.9137706756592</v>
+        <v>17.9137687683105</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G570" t="n">
-        <v>17.2640476226807</v>
+        <v>17.264045715332</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G572" t="n">
-        <v>17.3568668365479</v>
+        <v>17.3568649291992</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G573" t="n">
-        <v>17.6910076141357</v>
+        <v>17.6910037994385</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>17.5945796966553</v>
       </c>
       <c r="G574" t="n">
-        <v>16.8185253143311</v>
+        <v>16.8185234069824</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>16.4487953186035</v>
       </c>
       <c r="G576" t="n">
-        <v>15.7232751846313</v>
+        <v>15.72327709198</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G577" t="n">
-        <v>16.354434967041</v>
+        <v>16.3544330596924</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>16.5847358703613</v>
       </c>
       <c r="G578" t="n">
-        <v>15.8532209396362</v>
+        <v>15.8532190322876</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>15.9827136993408</v>
       </c>
       <c r="G579" t="n">
-        <v>15.2777519226074</v>
+        <v>15.2777528762817</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G580" t="n">
-        <v>15.6675844192505</v>
+        <v>15.6675853729248</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G582" t="n">
-        <v>16.4843826293945</v>
+        <v>16.4843807220459</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G584" t="n">
-        <v>16.317310333252</v>
+        <v>16.3173065185547</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G585" t="n">
-        <v>16.1688003540039</v>
+        <v>16.1688041687012</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G587" t="n">
-        <v>16.5957641601562</v>
+        <v>16.5957622528076</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>16.9731388092041</v>
       </c>
       <c r="G588" t="n">
-        <v>16.2244930267334</v>
+        <v>16.2244911193848</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G590" t="n">
-        <v>16.2616214752197</v>
+        <v>16.2616195678711</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G591" t="n">
-        <v>16.2616214752197</v>
+        <v>16.2616195678711</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G592" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G593" t="n">
-        <v>16.5957641601562</v>
+        <v>16.5957622528076</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G595" t="n">
-        <v>16.5771999359131</v>
+        <v>16.5771961212158</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G596" t="n">
-        <v>16.521505355835</v>
+        <v>16.5215072631836</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G597" t="n">
-        <v>16.5029449462891</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G599" t="n">
-        <v>16.7071437835693</v>
+        <v>16.7071418762207</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G600" t="n">
-        <v>16.4843826293945</v>
+        <v>16.4843807220459</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>17.4586391448975</v>
       </c>
       <c r="G601" t="n">
-        <v>16.6885776519775</v>
+        <v>16.6885757446289</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G602" t="n">
-        <v>16.6143264770508</v>
+        <v>16.6143245697021</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G603" t="n">
-        <v>15.6861486434937</v>
+        <v>15.6861505508423</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>16.0409755706787</v>
       </c>
       <c r="G604" t="n">
-        <v>15.3334436416626</v>
+        <v>15.3334445953369</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>15.5554733276367</v>
       </c>
       <c r="G605" t="n">
-        <v>14.8693571090698</v>
+        <v>14.8693561553955</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>15.2641716003418</v>
       </c>
       <c r="G606" t="n">
-        <v>14.5909032821655</v>
+        <v>14.5909023284912</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G607" t="n">
-        <v>14.8507928848267</v>
+        <v>14.8507919311523</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G608" t="n">
-        <v>14.8507928848267</v>
+        <v>14.8507919311523</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G609" t="n">
-        <v>15.6861486434937</v>
+        <v>15.6861505508423</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>15.108811378479</v>
       </c>
       <c r="G611" t="n">
-        <v>14.4423961639404</v>
+        <v>14.4423971176147</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G613" t="n">
-        <v>16.4101238250732</v>
+        <v>16.4101276397705</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G614" t="n">
-        <v>16.4101238250732</v>
+        <v>16.4101276397705</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>16.5847358703613</v>
       </c>
       <c r="G615" t="n">
-        <v>15.8532209396362</v>
+        <v>15.8532190322876</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>16.2351741790771</v>
       </c>
       <c r="G616" t="n">
-        <v>15.5190773010254</v>
+        <v>15.519079208374</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G617" t="n">
-        <v>16.1688003540039</v>
+        <v>16.1688041687012</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G618" t="n">
-        <v>15.7789659500122</v>
+        <v>15.7789669036865</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G619" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G621" t="n">
-        <v>16.521505355835</v>
+        <v>16.5215072631836</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G622" t="n">
-        <v>16.4843826293945</v>
+        <v>16.4843807220459</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G623" t="n">
-        <v>16.5957641601562</v>
+        <v>16.5957622528076</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G624" t="n">
-        <v>16.3730010986328</v>
+        <v>16.3729991912842</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G625" t="n">
-        <v>16.8556499481201</v>
+        <v>16.8556518554688</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>17.4974803924561</v>
       </c>
       <c r="G626" t="n">
-        <v>16.7257061004639</v>
+        <v>16.7257041931152</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G627" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G628" t="n">
-        <v>16.5029449462891</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G629" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G630" t="n">
-        <v>16.5029449462891</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G631" t="n">
-        <v>16.317310333252</v>
+        <v>16.3173065185547</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G632" t="n">
-        <v>16.3358726501465</v>
+        <v>16.3358707427979</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>17.4974803924561</v>
       </c>
       <c r="G633" t="n">
-        <v>16.7257061004639</v>
+        <v>16.7257041931152</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G634" t="n">
-        <v>16.8370876312256</v>
+        <v>16.837085723877</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>17.7499408721924</v>
       </c>
       <c r="G635" t="n">
-        <v>16.9670314788818</v>
+        <v>16.9670295715332</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G636" t="n">
-        <v>16.354434967041</v>
+        <v>16.3544330596924</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G639" t="n">
-        <v>16.3730010986328</v>
+        <v>16.3729991912842</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G640" t="n">
-        <v>16.7071437835693</v>
+        <v>16.7071418762207</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>17.5557403564453</v>
       </c>
       <c r="G641" t="n">
-        <v>16.7813968658447</v>
+        <v>16.7813987731934</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G642" t="n">
-        <v>16.354434967041</v>
+        <v>16.3544330596924</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G643" t="n">
-        <v>16.7071437835693</v>
+        <v>16.7071418762207</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G644" t="n">
-        <v>17.2826099395752</v>
+        <v>17.2826118469238</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G649" t="n">
-        <v>17.8023872375488</v>
+        <v>17.8023834228516</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G652" t="n">
-        <v>16.5771999359131</v>
+        <v>16.5771961212158</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G654" t="n">
-        <v>16.3358726501465</v>
+        <v>16.3358707427979</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>17.2255992889404</v>
       </c>
       <c r="G655" t="n">
-        <v>16.4658184051514</v>
+        <v>16.4658164978027</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G657" t="n">
-        <v>16.7071437835693</v>
+        <v>16.7071418762207</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>17.2255992889404</v>
       </c>
       <c r="G658" t="n">
-        <v>16.4658184051514</v>
+        <v>16.4658164978027</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G659" t="n">
-        <v>16.5957641601562</v>
+        <v>16.5957622528076</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G660" t="n">
-        <v>16.5029449462891</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G661" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G663" t="n">
-        <v>16.3730010986328</v>
+        <v>16.3729991912842</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G664" t="n">
-        <v>16.3730010986328</v>
+        <v>16.3729991912842</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>16.9731388092041</v>
       </c>
       <c r="G665" t="n">
-        <v>16.2244930267334</v>
+        <v>16.2244911193848</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G666" t="n">
-        <v>16.521505355835</v>
+        <v>16.5215072631836</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G667" t="n">
-        <v>16.3358726501465</v>
+        <v>16.3358707427979</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G668" t="n">
-        <v>16.1688003540039</v>
+        <v>16.1688041687012</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G669" t="n">
-        <v>15.7789659500122</v>
+        <v>15.7789669036865</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G671" t="n">
-        <v>16.2616214752197</v>
+        <v>16.2616195678711</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G674" t="n">
-        <v>16.317310333252</v>
+        <v>16.3173065185547</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G676" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G677" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G681" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>16.7012577056885</v>
       </c>
       <c r="G682" t="n">
-        <v>15.9646043777466</v>
+        <v>15.9646034240723</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>16.4682159423828</v>
       </c>
       <c r="G683" t="n">
-        <v>15.7418394088745</v>
+        <v>15.7418413162231</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G684" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>16.2157554626465</v>
       </c>
       <c r="G687" t="n">
-        <v>15.5005149841309</v>
+        <v>15.5005159378052</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>16.5264759063721</v>
       </c>
       <c r="G690" t="n">
-        <v>15.7975301742554</v>
+        <v>15.797532081604</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>16.6041564941406</v>
       </c>
       <c r="G691" t="n">
-        <v>15.8717851638794</v>
+        <v>15.8717832565308</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>14.7204103469849</v>
       </c>
       <c r="G695" t="n">
-        <v>14.0711278915405</v>
+        <v>14.0711269378662</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>15.3418521881104</v>
       </c>
       <c r="G696" t="n">
-        <v>14.6651582717896</v>
+        <v>14.6651573181152</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>15.4389533996582</v>
       </c>
       <c r="G698" t="n">
-        <v>14.7579765319824</v>
+        <v>14.7579755783081</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G700" t="n">
-        <v>15.0364284515381</v>
+        <v>15.0364274978638</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G701" t="n">
-        <v>15.4076976776123</v>
+        <v>15.4076986312866</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>16.2934341430664</v>
       </c>
       <c r="G703" t="n">
-        <v>15.5747680664062</v>
+        <v>15.5747690200806</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>16.1380748748779</v>
       </c>
       <c r="G704" t="n">
-        <v>15.4262609481812</v>
+        <v>15.4262599945068</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>16.332275390625</v>
       </c>
       <c r="G705" t="n">
-        <v>15.6118974685669</v>
+        <v>15.6118955612183</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G706" t="n">
-        <v>15.4076976776123</v>
+        <v>15.4076986312866</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>16.0798149108887</v>
       </c>
       <c r="G707" t="n">
-        <v>15.3705711364746</v>
+        <v>15.3705701828003</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>16.0603942871094</v>
       </c>
       <c r="G708" t="n">
-        <v>15.3520059585571</v>
+        <v>15.3520069122314</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G709" t="n">
-        <v>15.6675844192505</v>
+        <v>15.6675853729248</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>16.2740154266357</v>
       </c>
       <c r="G710" t="n">
-        <v>15.556206703186</v>
+        <v>15.5562047958374</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G711" t="n">
-        <v>15.760404586792</v>
+        <v>15.7604055404663</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>16.856616973877</v>
       </c>
       <c r="G712" t="n">
-        <v>16.113109588623</v>
+        <v>16.1131076812744</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G713" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G714" t="n">
-        <v>16.5771999359131</v>
+        <v>16.5771961212158</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>17.8082008361816</v>
       </c>
       <c r="G716" t="n">
-        <v>17.0227241516113</v>
+        <v>17.0227222442627</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G718" t="n">
-        <v>17.5424995422363</v>
+        <v>17.542501449585</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G719" t="n">
-        <v>17.5424995422363</v>
+        <v>17.542501449585</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>18.4684829711914</v>
       </c>
       <c r="G721" t="n">
-        <v>17.6538791656494</v>
+        <v>17.653881072998</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G722" t="n">
-        <v>18.0065841674805</v>
+        <v>18.0065860748291</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G729" t="n">
-        <v>17.2640476226807</v>
+        <v>17.264045715332</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>17.8470401763916</v>
       </c>
       <c r="G730" t="n">
-        <v>17.0598487854004</v>
+        <v>17.0598468780518</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G732" t="n">
-        <v>17.2826099395752</v>
+        <v>17.2826118469238</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G733" t="n">
-        <v>17.4496803283691</v>
+        <v>17.4496784210205</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G737" t="n">
-        <v>19.5844860076904</v>
+        <v>19.5844841003418</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G738" t="n">
-        <v>19.6773014068604</v>
+        <v>19.6772975921631</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G740" t="n">
-        <v>19.3988456726074</v>
+        <v>19.3988494873047</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G743" t="n">
-        <v>20.3270244598389</v>
+        <v>20.3270225524902</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G744" t="n">
-        <v>20.1413879394531</v>
+        <v>20.1413898468018</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G745" t="n">
-        <v>20.002161026001</v>
+        <v>20.0021591186523</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G746" t="n">
-        <v>19.8165245056152</v>
+        <v>19.8165283203125</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G747" t="n">
-        <v>20.1413879394531</v>
+        <v>20.1413898468018</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G749" t="n">
-        <v>20.4662494659424</v>
+        <v>20.466251373291</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G753" t="n">
-        <v>21.8121032714844</v>
+        <v>21.8120994567871</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G754" t="n">
-        <v>21.1623821258545</v>
+        <v>21.1623783111572</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G755" t="n">
-        <v>20.1413879394531</v>
+        <v>20.1413898468018</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G756" t="n">
-        <v>20.4662494659424</v>
+        <v>20.466251373291</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G758" t="n">
-        <v>20.3270244598389</v>
+        <v>20.3270225524902</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G759" t="n">
-        <v>20.6982936859131</v>
+        <v>20.6982917785645</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G761" t="n">
-        <v>19.955753326416</v>
+        <v>19.9557552337646</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G762" t="n">
-        <v>19.8165245056152</v>
+        <v>19.8165283203125</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G765" t="n">
-        <v>19.5844860076904</v>
+        <v>19.5844841003418</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>20.245418548584</v>
       </c>
       <c r="G766" t="n">
-        <v>19.3524398803711</v>
+        <v>19.3524379730225</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G771" t="n">
-        <v>19.3260688781738</v>
+        <v>19.3260650634766</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G774" t="n">
-        <v>19.5594711303711</v>
+        <v>19.5594730377197</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>19.6628170013428</v>
       </c>
       <c r="G775" t="n">
-        <v>18.9059314727783</v>
+        <v>18.9059352874756</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G776" t="n">
-        <v>18.7192077636719</v>
+        <v>18.7192096710205</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G777" t="n">
-        <v>19.0459804534912</v>
+        <v>19.0459785461426</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G779" t="n">
-        <v>18.812572479248</v>
+        <v>18.8125705718994</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G780" t="n">
-        <v>19.512788772583</v>
+        <v>19.5127925872803</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G786" t="n">
-        <v>19.0459804534912</v>
+        <v>19.0459785461426</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G788" t="n">
-        <v>18.2990798950195</v>
+        <v>18.2990779876709</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G789" t="n">
-        <v>18.5044746398926</v>
+        <v>18.5044765472412</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G790" t="n">
-        <v>18.355094909668</v>
+        <v>18.3550968170166</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>19.1287651062012</v>
       </c>
       <c r="G792" t="n">
-        <v>18.3924388885498</v>
+        <v>18.3924407958984</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G797" t="n">
-        <v>18.7192077636719</v>
+        <v>18.7192096710205</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G800" t="n">
-        <v>19.9329223632812</v>
+        <v>19.9329242706299</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G801" t="n">
-        <v>20.259693145752</v>
+        <v>20.2596950531006</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>21.5077228546143</v>
       </c>
       <c r="G803" t="n">
-        <v>20.6798229217529</v>
+        <v>20.6798248291016</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G804" t="n">
-        <v>21.1466369628906</v>
+        <v>21.146635055542</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G805" t="n">
-        <v>21.940221786499</v>
+        <v>21.9402179718018</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G806" t="n">
-        <v>22.3136711120605</v>
+        <v>22.3136692047119</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G808" t="n">
-        <v>23.0605716705322</v>
+        <v>23.0605735778809</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G809" t="n">
-        <v>23.3406620025635</v>
+        <v>23.3406600952148</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G810" t="n">
-        <v>23.0138912200928</v>
+        <v>23.0138931274414</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G811" t="n">
-        <v>22.920524597168</v>
+        <v>22.9205265045166</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G815" t="n">
-        <v>23.574068069458</v>
+        <v>23.5740661621094</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G816" t="n">
-        <v>23.0138912200928</v>
+        <v>23.0138931274414</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G817" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G818" t="n">
-        <v>22.6871242523193</v>
+        <v>22.6871223449707</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G820" t="n">
-        <v>23.0138912200928</v>
+        <v>23.0138931274414</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G822" t="n">
-        <v>23.3406620025635</v>
+        <v>23.3406600952148</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G823" t="n">
-        <v>23.574068069458</v>
+        <v>23.5740661621094</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G824" t="n">
-        <v>23.3873405456543</v>
+        <v>23.3873424530029</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G825" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G826" t="n">
-        <v>22.7804851531982</v>
+        <v>22.780481338501</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G828" t="n">
-        <v>23.0605716705322</v>
+        <v>23.0605735778809</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G829" t="n">
-        <v>23.1072521209717</v>
+        <v>23.107250213623</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G832" t="n">
-        <v>23.2939796447754</v>
+        <v>23.2939777374268</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G833" t="n">
-        <v>22.7804851531982</v>
+        <v>22.780481338501</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G834" t="n">
-        <v>23.1072521209717</v>
+        <v>23.107250213623</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G835" t="n">
-        <v>23.3406620025635</v>
+        <v>23.3406600952148</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G837" t="n">
-        <v>23.7141094207764</v>
+        <v>23.714111328125</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G839" t="n">
-        <v>21.613452911377</v>
+        <v>21.6134510040283</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G840" t="n">
-        <v>21.5667724609375</v>
+        <v>21.5667705535889</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>22.8671283721924</v>
       </c>
       <c r="G841" t="n">
-        <v>21.9869041442871</v>
+        <v>21.9869022369385</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G845" t="n">
-        <v>20.7731876373291</v>
+        <v>20.7731838226318</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G846" t="n">
-        <v>20.8198699951172</v>
+        <v>20.8198680877686</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G848" t="n">
-        <v>20.4464206695557</v>
+        <v>20.4464168548584</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>21.9446754455566</v>
       </c>
       <c r="G849" t="n">
-        <v>21.0999546051025</v>
+        <v>21.0999584197998</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G851" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G852" t="n">
-        <v>24.6477336883545</v>
+        <v>24.6477355957031</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G853" t="n">
-        <v>24.5076904296875</v>
+        <v>24.5076923370361</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G854" t="n">
-        <v>24.8344612121582</v>
+        <v>24.8344631195068</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G855" t="n">
-        <v>24.2742862701416</v>
+        <v>24.274284362793</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G856" t="n">
-        <v>24.5076904296875</v>
+        <v>24.5076923370361</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G862" t="n">
-        <v>23.3406620025635</v>
+        <v>23.3406600952148</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G863" t="n">
-        <v>23.3873405456543</v>
+        <v>23.3873424530029</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G864" t="n">
-        <v>23.9941959381104</v>
+        <v>23.994197845459</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G865" t="n">
-        <v>23.6674289703369</v>
+        <v>23.6674308776855</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G866" t="n">
-        <v>24.1342430114746</v>
+        <v>24.134241104126</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G867" t="n">
-        <v>24.1342430114746</v>
+        <v>24.134241104126</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G868" t="n">
-        <v>23.8074760437012</v>
+        <v>23.8074741363525</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G869" t="n">
-        <v>23.8074760437012</v>
+        <v>23.8074741363525</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G870" t="n">
-        <v>24.2742862701416</v>
+        <v>24.274284362793</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G872" t="n">
-        <v>24.5076904296875</v>
+        <v>24.5076923370361</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>26.2656402587891</v>
       </c>
       <c r="G874" t="n">
-        <v>25.2545928955078</v>
+        <v>25.2545967102051</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>26.5083904266357</v>
       </c>
       <c r="G875" t="n">
-        <v>25.4879989624023</v>
+        <v>25.488000869751</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G882" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G885" t="n">
-        <v>22.9672107696533</v>
+        <v>22.9672088623047</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G888" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G890" t="n">
-        <v>23.6674289703369</v>
+        <v>23.6674308776855</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G891" t="n">
-        <v>24.5543746948242</v>
+        <v>24.5543727874756</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G892" t="n">
-        <v>24.5076904296875</v>
+        <v>24.5076923370361</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G893" t="n">
-        <v>24.3676490783691</v>
+        <v>24.3676509857178</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G895" t="n">
-        <v>24.6010551452637</v>
+        <v>24.6010570526123</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G896" t="n">
-        <v>24.3676490783691</v>
+        <v>24.3676509857178</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G897" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G898" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G899" t="n">
-        <v>23.0605716705322</v>
+        <v>23.0605735778809</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>24.7120342254639</v>
       </c>
       <c r="G900" t="n">
-        <v>23.7607898712158</v>
+        <v>23.7607917785645</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G901" t="n">
-        <v>23.574068069458</v>
+        <v>23.5740661621094</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G902" t="n">
-        <v>23.854154586792</v>
+        <v>23.8541564941406</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G903" t="n">
-        <v>23.8074760437012</v>
+        <v>23.8074741363525</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G904" t="n">
-        <v>24.6944179534912</v>
+        <v>24.6944198608398</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G905" t="n">
-        <v>24.8344612121582</v>
+        <v>24.8344631195068</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G906" t="n">
-        <v>24.461009979248</v>
+        <v>24.4610118865967</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G907" t="n">
-        <v>24.461009979248</v>
+        <v>24.4610118865967</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G908" t="n">
-        <v>23.854154586792</v>
+        <v>23.8541564941406</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G909" t="n">
-        <v>23.8074760437012</v>
+        <v>23.8074741363525</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G910" t="n">
-        <v>23.7141094207764</v>
+        <v>23.714111328125</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G914" t="n">
-        <v>24.9745082855225</v>
+        <v>24.9745063781738</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G918" t="n">
-        <v>23.3406620025635</v>
+        <v>23.3406600952148</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G920" t="n">
-        <v>22.7804851531982</v>
+        <v>22.780481338501</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G923" t="n">
-        <v>21.2866840362549</v>
+        <v>21.2866802215576</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G924" t="n">
-        <v>20.7731876373291</v>
+        <v>20.7731838226318</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G925" t="n">
-        <v>20.3063716888428</v>
+        <v>20.3063735961914</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G927" t="n">
-        <v>21.1466369628906</v>
+        <v>21.146635055542</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G929" t="n">
-        <v>21.1466369628906</v>
+        <v>21.146635055542</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G933" t="n">
-        <v>21.1933212280273</v>
+        <v>21.1933193206787</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G934" t="n">
-        <v>21.4734058380127</v>
+        <v>21.4734077453613</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G936" t="n">
-        <v>21.2399997711182</v>
+        <v>21.2400016784668</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G938" t="n">
-        <v>21.1466369628906</v>
+        <v>21.146635055542</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G941" t="n">
-        <v>20.1196479797363</v>
+        <v>20.1196460723877</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>19.1870250701904</v>
       </c>
       <c r="G944" t="n">
-        <v>18.4484558105469</v>
+        <v>18.4484577178955</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G946" t="n">
-        <v>20.5397815704346</v>
+        <v>20.5397796630859</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G947" t="n">
-        <v>19.3260688781738</v>
+        <v>19.3260650634766</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G949" t="n">
-        <v>18.0936813354492</v>
+        <v>18.0936794281006</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>17.9053001403809</v>
       </c>
       <c r="G950" t="n">
-        <v>17.2160682678223</v>
+        <v>17.2160701751709</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G951" t="n">
-        <v>16.9359836578369</v>
+        <v>16.9359817504883</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>18.9151439666748</v>
       </c>
       <c r="G953" t="n">
-        <v>18.1870441436768</v>
+        <v>18.1870422363281</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G955" t="n">
-        <v>18.5418243408203</v>
+        <v>18.5418186187744</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G956" t="n">
-        <v>19.7928810119629</v>
+        <v>19.7928771972656</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G958" t="n">
-        <v>20.3063716888428</v>
+        <v>20.3063735961914</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G959" t="n">
-        <v>20.3063716888428</v>
+        <v>20.3063735961914</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G960" t="n">
-        <v>20.5397815704346</v>
+        <v>20.5397796630859</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G961" t="n">
-        <v>20.7731876373291</v>
+        <v>20.7731838226318</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>22.7214775085449</v>
       </c>
       <c r="G965" t="n">
-        <v>21.8468570709229</v>
+        <v>21.8468589782715</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G967" t="n">
-        <v>22.1736278533936</v>
+        <v>22.1736259460449</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G968" t="n">
-        <v>23.0138912200928</v>
+        <v>23.0138931274414</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G971" t="n">
-        <v>20.3530521392822</v>
+        <v>20.3530540466309</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G973" t="n">
-        <v>20.259693145752</v>
+        <v>20.2596950531006</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G974" t="n">
-        <v>20.4464206695557</v>
+        <v>20.4464168548584</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G975" t="n">
-        <v>20.259693145752</v>
+        <v>20.2596950531006</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G976" t="n">
-        <v>20.3530521392822</v>
+        <v>20.3530540466309</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G978" t="n">
-        <v>20.3063716888428</v>
+        <v>20.3063735961914</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G979" t="n">
-        <v>20.3530521392822</v>
+        <v>20.3530540466309</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G980" t="n">
-        <v>20.4464206695557</v>
+        <v>20.4464168548584</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G983" t="n">
-        <v>21.5667724609375</v>
+        <v>21.5667705535889</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G985" t="n">
-        <v>21.4734058380127</v>
+        <v>21.4734077453613</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G989" t="n">
-        <v>22.1736278533936</v>
+        <v>22.1736259460449</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G991" t="n">
-        <v>21.5667724609375</v>
+        <v>21.5667705535889</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>22.6243762969971</v>
       </c>
       <c r="G998" t="n">
-        <v>21.7534923553467</v>
+        <v>21.7534961700439</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G999" t="n">
-        <v>20.8198699951172</v>
+        <v>20.8198680877686</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1000" t="n">
-        <v>20.5397815704346</v>
+        <v>20.5397796630859</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1002" t="n">
-        <v>20.3530521392822</v>
+        <v>20.3530540466309</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G1003" t="n">
-        <v>19.512788772583</v>
+        <v>19.5127925872803</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1004" t="n">
-        <v>20.4464206695557</v>
+        <v>20.4464168548584</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1005" t="n">
-        <v>19.9329223632812</v>
+        <v>19.9329242706299</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G1007" t="n">
-        <v>20.259693145752</v>
+        <v>20.2596950531006</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G1009" t="n">
-        <v>21.5667724609375</v>
+        <v>21.5667705535889</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1010" t="n">
-        <v>20.8198699951172</v>
+        <v>20.8198680877686</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1011" t="n">
-        <v>20.8198699951172</v>
+        <v>20.8198680877686</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1012" t="n">
-        <v>20.5397815704346</v>
+        <v>20.5397796630859</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G1013" t="n">
-        <v>20.0729675292969</v>
+        <v>20.0729694366455</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G1014" t="n">
-        <v>20.259693145752</v>
+        <v>20.2596950531006</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1015" t="n">
-        <v>20.5397815704346</v>
+        <v>20.5397796630859</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1016" t="n">
-        <v>20.3997325897217</v>
+        <v>20.3997344970703</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1018" t="n">
-        <v>18.812572479248</v>
+        <v>18.8125705718994</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1019" t="n">
-        <v>18.2057151794434</v>
+        <v>18.2057132720947</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>18.5655822753906</v>
       </c>
       <c r="G1020" t="n">
-        <v>17.8509368896484</v>
+        <v>17.8509349822998</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G1021" t="n">
-        <v>17.7762451171875</v>
+        <v>17.7762470245361</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G1025" t="n">
-        <v>16.8312034606934</v>
+        <v>16.8312015533447</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G1026" t="n">
-        <v>16.7935466766357</v>
+        <v>16.7935485839844</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G1027" t="n">
-        <v>16.2852210998535</v>
+        <v>16.2852230072021</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>16.6624164581299</v>
       </c>
       <c r="G1028" t="n">
-        <v>16.1534366607666</v>
+        <v>16.153434753418</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>18.4102230072021</v>
       </c>
       <c r="G1032" t="n">
-        <v>17.8478488922119</v>
+        <v>17.8478507995605</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G1033" t="n">
-        <v>17.6972351074219</v>
+        <v>17.6972370147705</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1034" t="n">
-        <v>18.1490821838379</v>
+        <v>18.1490802764893</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1035" t="n">
-        <v>18.130256652832</v>
+        <v>18.1302547454834</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G1037" t="n">
-        <v>18.8268489837646</v>
+        <v>18.826847076416</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1041" t="n">
-        <v>18.130256652832</v>
+        <v>18.1302547454834</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>18.8763046264648</v>
       </c>
       <c r="G1043" t="n">
-        <v>18.2996940612793</v>
+        <v>18.2996959686279</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G1047" t="n">
-        <v>19.7211208343506</v>
+        <v>19.7211246490479</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1048" t="n">
-        <v>20.0505924224854</v>
+        <v>20.050594329834</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1049" t="n">
-        <v>20.6153984069824</v>
+        <v>20.6153964996338</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1050" t="n">
-        <v>20.7095317840576</v>
+        <v>20.7095336914062</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1051" t="n">
-        <v>20.8036670684814</v>
+        <v>20.8036651611328</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G1053" t="n">
-        <v>20.897798538208</v>
+        <v>20.8978004455566</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1054" t="n">
-        <v>20.8036670684814</v>
+        <v>20.8036651611328</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1055" t="n">
-        <v>20.0505924224854</v>
+        <v>20.050594329834</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>22.6243762969971</v>
       </c>
       <c r="G1057" t="n">
-        <v>21.9332752227783</v>
+        <v>21.933277130127</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1068" t="n">
-        <v>20.7095317840576</v>
+        <v>20.7095336914062</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1070" t="n">
-        <v>20.8036670684814</v>
+        <v>20.8036651611328</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1071" t="n">
-        <v>20.6624660491943</v>
+        <v>20.6624641418457</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G1072" t="n">
-        <v>20.2859287261963</v>
+        <v>20.285924911499</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1077" t="n">
-        <v>20.0976581573486</v>
+        <v>20.0976600646973</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G1080" t="n">
-        <v>19.1092491149902</v>
+        <v>19.1092510223389</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>20.0512180328369</v>
       </c>
       <c r="G1081" t="n">
-        <v>19.4387187957764</v>
+        <v>19.438720703125</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>20.245418548584</v>
       </c>
       <c r="G1083" t="n">
-        <v>19.626989364624</v>
+        <v>19.6269855499268</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>19.6628170013428</v>
       </c>
       <c r="G1084" t="n">
-        <v>19.0621814727783</v>
+        <v>19.062183380127</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G1085" t="n">
-        <v>18.8739147186279</v>
+        <v>18.8739128112793</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>19.0122451782227</v>
       </c>
       <c r="G1087" t="n">
-        <v>18.4314842224121</v>
+        <v>18.4314823150635</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G1088" t="n">
-        <v>18.2432136535645</v>
+        <v>18.2432155609131</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G1091" t="n">
-        <v>17.6031036376953</v>
+        <v>17.6031017303467</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G1092" t="n">
-        <v>18.2620391845703</v>
+        <v>18.2620410919189</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>18.2354412078857</v>
       </c>
       <c r="G1095" t="n">
-        <v>17.6784076690674</v>
+        <v>17.678409576416</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G1096" t="n">
-        <v>16.8876819610596</v>
+        <v>16.8876800537109</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1098" t="n">
-        <v>18.9680500030518</v>
+        <v>18.9680480957031</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G1099" t="n">
-        <v>19.9564590454102</v>
+        <v>19.9564552307129</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1100" t="n">
-        <v>18.9680500030518</v>
+        <v>18.9680480957031</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G1101" t="n">
-        <v>18.6762313842773</v>
+        <v>18.676233291626</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G1103" t="n">
-        <v>18.1679096221924</v>
+        <v>18.1679077148438</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1106" t="n">
-        <v>18.130256652832</v>
+        <v>18.1302547454834</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G1107" t="n">
-        <v>17.9419860839844</v>
+        <v>17.9419822692871</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1108" t="n">
-        <v>18.1490821838379</v>
+        <v>18.1490802764893</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G1109" t="n">
-        <v>18.2432136535645</v>
+        <v>18.2432155609131</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1110" t="n">
-        <v>18.1490821838379</v>
+        <v>18.1490802764893</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1114" t="n">
-        <v>20.52126121521</v>
+        <v>20.5212631225586</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1116" t="n">
-        <v>20.8036670684814</v>
+        <v>20.8036651611328</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1117" t="n">
-        <v>20.8036670684814</v>
+        <v>20.8036651611328</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1119" t="n">
-        <v>20.3800621032715</v>
+        <v>20.3800640106201</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1120" t="n">
-        <v>20.52126121521</v>
+        <v>20.5212631225586</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1121" t="n">
-        <v>20.0505924224854</v>
+        <v>20.050594329834</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1123" t="n">
-        <v>20.6153984069824</v>
+        <v>20.6153964996338</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1124" t="n">
-        <v>20.7095317840576</v>
+        <v>20.7095336914062</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1125" t="n">
-        <v>20.6153984069824</v>
+        <v>20.6153964996338</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1127" t="n">
-        <v>23.1570243835449</v>
+        <v>23.1570224761963</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1128" t="n">
-        <v>24.0042324066162</v>
+        <v>24.0042304992676</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1130" t="n">
-        <v>23.2040882110596</v>
+        <v>23.2040901184082</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1131" t="n">
-        <v>23.2040882110596</v>
+        <v>23.2040901184082</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1133" t="n">
-        <v>22.7804851531982</v>
+        <v>22.7804832458496</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1136" t="n">
-        <v>23.1570243835449</v>
+        <v>23.1570224761963</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1137" t="n">
-        <v>22.7804851531982</v>
+        <v>22.7804832458496</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1139" t="n">
-        <v>21.9803447723389</v>
+        <v>21.9803428649902</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>23.4497299194336</v>
       </c>
       <c r="G1141" t="n">
-        <v>22.7334175109863</v>
+        <v>22.733419418335</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>23.3526306152344</v>
       </c>
       <c r="G1142" t="n">
-        <v>22.6392860412598</v>
+        <v>22.6392822265625</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1143" t="n">
-        <v>22.8746185302734</v>
+        <v>22.8746204376221</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1144" t="n">
-        <v>21.9803447723389</v>
+        <v>21.9803428649902</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1148" t="n">
-        <v>23.2982234954834</v>
+        <v>23.2982215881348</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1150" t="n">
-        <v>24.0042324066162</v>
+        <v>24.0042304992676</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1151" t="n">
-        <v>23.2982234954834</v>
+        <v>23.2982215881348</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G1152" t="n">
-        <v>23.0158195495605</v>
+        <v>23.0158214569092</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G1154" t="n">
-        <v>21.8391437530518</v>
+        <v>21.8391418457031</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1156" t="n">
-        <v>22.4039478302002</v>
+        <v>22.4039497375488</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1159" t="n">
-        <v>21.9803447723389</v>
+        <v>21.9803428649902</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1163" t="n">
-        <v>21.9803447723389</v>
+        <v>21.9803428649902</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G1169" t="n">
-        <v>21.4155368804932</v>
+        <v>21.4155387878418</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G1170" t="n">
-        <v>21.2272720336914</v>
+        <v>21.2272701263428</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1177" t="n">
-        <v>22.7804851531982</v>
+        <v>22.7804832458496</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1178" t="n">
-        <v>22.8746185302734</v>
+        <v>22.8746204376221</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.9803447723389</v>
+        <v>21.9803428649902</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G1183" t="n">
-        <v>21.3684730529785</v>
+        <v>21.3684711456299</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1185" t="n">
-        <v>23.3452911376953</v>
+        <v>23.3452892303467</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G1187" t="n">
-        <v>24.5219688415527</v>
+        <v>24.5219669342041</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1189" t="n">
-        <v>23.2040882110596</v>
+        <v>23.2040901184082</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1191" t="n">
-        <v>23.9100933074951</v>
+        <v>23.9100971221924</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>25.9257888793945</v>
       </c>
       <c r="G1192" t="n">
-        <v>25.1338443756104</v>
+        <v>25.1338405609131</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.7573070526123</v>
+        <v>24.7573051452637</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1197" t="n">
-        <v>24.0042324066162</v>
+        <v>24.0042304992676</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1199" t="n">
-        <v>24.3337001800537</v>
+        <v>24.3336982727051</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1200" t="n">
-        <v>24.8514366149902</v>
+        <v>24.8514385223389</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1203" t="n">
-        <v>24.8514366149902</v>
+        <v>24.8514385223389</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1204" t="n">
-        <v>24.3337001800537</v>
+        <v>24.3336982727051</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1206" t="n">
-        <v>24.8514366149902</v>
+        <v>24.8514385223389</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>25.9257888793945</v>
       </c>
       <c r="G1207" t="n">
-        <v>25.1338443756104</v>
+        <v>25.1338405609131</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>26.1685390472412</v>
       </c>
       <c r="G1208" t="n">
-        <v>25.3691749572754</v>
+        <v>25.369176864624</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>26.4112892150879</v>
       </c>
       <c r="G1209" t="n">
-        <v>25.6045112609863</v>
+        <v>25.6045093536377</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1211" t="n">
-        <v>23.9100933074951</v>
+        <v>23.9100971221924</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1213" t="n">
-        <v>23.9100933074951</v>
+        <v>23.9100971221924</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1214" t="n">
-        <v>23.2040882110596</v>
+        <v>23.2040901184082</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1215" t="n">
-        <v>23.3923568725586</v>
+        <v>23.3923587799072</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1216" t="n">
-        <v>22.7804851531982</v>
+        <v>22.7804832458496</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1217" t="n">
-        <v>22.9687538146973</v>
+        <v>22.9687519073486</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1220" t="n">
-        <v>23.0628871917725</v>
+        <v>23.0628890991211</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1222" t="n">
-        <v>22.4039478302002</v>
+        <v>22.4039497375488</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1223" t="n">
-        <v>23.3452911376953</v>
+        <v>23.3452892303467</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G1224" t="n">
-        <v>23.4864921569824</v>
+        <v>23.4864940643311</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1226" t="n">
-        <v>23.7218265533447</v>
+        <v>23.7218284606934</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1228" t="n">
-        <v>23.6276931762695</v>
+        <v>23.6276912689209</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1230" t="n">
-        <v>23.2982234954834</v>
+        <v>23.2982215881348</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1231" t="n">
-        <v>23.0628871917725</v>
+        <v>23.0628890991211</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1232" t="n">
-        <v>22.8746185302734</v>
+        <v>22.8746204376221</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1234" t="n">
-        <v>23.6276931762695</v>
+        <v>23.6276912689209</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1235" t="n">
-        <v>23.0628871917725</v>
+        <v>23.0628890991211</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1240" t="n">
-        <v>21.9803447723389</v>
+        <v>21.9803428649902</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1244" t="n">
-        <v>22.4039478302002</v>
+        <v>22.4039497375488</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1245" t="n">
-        <v>22.4039478302002</v>
+        <v>22.4039497375488</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G1251" t="n">
-        <v>23.4864921569824</v>
+        <v>23.4864940643311</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1252" t="n">
-        <v>23.3923568725586</v>
+        <v>23.3923587799072</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1253" t="n">
-        <v>23.6276931762695</v>
+        <v>23.6276912689209</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1254" t="n">
-        <v>22.9687538146973</v>
+        <v>22.9687519073486</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1255" t="n">
-        <v>22.8746185302734</v>
+        <v>22.8746204376221</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1257" t="n">
-        <v>22.9687538146973</v>
+        <v>22.9687519073486</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1258" t="n">
-        <v>23.0628871917725</v>
+        <v>23.0628890991211</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1259" t="n">
-        <v>22.7804851531982</v>
+        <v>22.7804832458496</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1260" t="n">
-        <v>23.1570243835449</v>
+        <v>23.1570224761963</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1263" t="n">
-        <v>23.7218265533447</v>
+        <v>23.7218284606934</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1264" t="n">
-        <v>23.6276931762695</v>
+        <v>23.6276912689209</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1265" t="n">
-        <v>23.2982234954834</v>
+        <v>23.2982215881348</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G1267" t="n">
-        <v>24.8985061645508</v>
+        <v>24.8985080718994</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>27.1395435333252</v>
       </c>
       <c r="G1269" t="n">
-        <v>26.3105220794678</v>
+        <v>26.3105201721191</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>27.0424423217773</v>
       </c>
       <c r="G1270" t="n">
-        <v>26.2163829803467</v>
+        <v>26.2163848876953</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>26.4598407745361</v>
       </c>
       <c r="G1273" t="n">
-        <v>25.6515808105469</v>
+        <v>25.6515789031982</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>27.0424423217773</v>
       </c>
       <c r="G1274" t="n">
-        <v>26.2163829803467</v>
+        <v>26.2163848876953</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>27.1880931854248</v>
       </c>
       <c r="G1275" t="n">
-        <v>26.3575878143311</v>
+        <v>26.3575859069824</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>27.1880931854248</v>
       </c>
       <c r="G1276" t="n">
-        <v>26.3575878143311</v>
+        <v>26.3575859069824</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>27.1880931854248</v>
       </c>
       <c r="G1277" t="n">
-        <v>26.3575878143311</v>
+        <v>26.3575859069824</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>27.3337421417236</v>
       </c>
       <c r="G1278" t="n">
-        <v>26.4987850189209</v>
+        <v>26.4987869262695</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>26.071439743042</v>
       </c>
       <c r="G1284" t="n">
-        <v>25.4377002716064</v>
+        <v>25.4376983642578</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>26.5569400787354</v>
       </c>
       <c r="G1287" t="n">
-        <v>25.9113998413086</v>
+        <v>25.91139793396</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>26.6054916381836</v>
       </c>
       <c r="G1290" t="n">
-        <v>25.9587707519531</v>
+        <v>25.9587688446045</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>26.4112892150879</v>
       </c>
       <c r="G1293" t="n">
-        <v>25.7692890167236</v>
+        <v>25.769287109375</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>25.7315883636475</v>
       </c>
       <c r="G1298" t="n">
-        <v>25.1061096191406</v>
+        <v>25.106107711792</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1300" t="n">
-        <v>24.8218898773193</v>
+        <v>24.8218879699707</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>25.1489868164062</v>
       </c>
       <c r="G1304" t="n">
-        <v>24.537670135498</v>
+        <v>24.5376720428467</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>25.1489868164062</v>
       </c>
       <c r="G1308" t="n">
-        <v>24.537670135498</v>
+        <v>24.5376720428467</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1311" t="n">
-        <v>24.8218898773193</v>
+        <v>24.8218879699707</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1315" t="n">
-        <v>23.7323780059814</v>
+        <v>23.7323799133301</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1317" t="n">
-        <v>24.0639686584473</v>
+        <v>24.0639705657959</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1322" t="n">
-        <v>23.7323780059814</v>
+        <v>23.7323799133301</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1330" t="n">
-        <v>23.7323780059814</v>
+        <v>23.7323799133301</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1331" t="n">
-        <v>24.5850410461426</v>
+        <v>24.5850391387939</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1332" t="n">
-        <v>24.8218898773193</v>
+        <v>24.8218879699707</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1337" t="n">
-        <v>23.4955291748047</v>
+        <v>23.4955272674561</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1339" t="n">
-        <v>23.0691967010498</v>
+        <v>23.0691986083984</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1340" t="n">
-        <v>23.0691967010498</v>
+        <v>23.0691986083984</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1341" t="n">
-        <v>23.0691967010498</v>
+        <v>23.0691986083984</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1353" t="n">
-        <v>20.8428077697754</v>
+        <v>20.842809677124</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1356" t="n">
-        <v>20.7006969451904</v>
+        <v>20.7006950378418</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1357" t="n">
-        <v>20.7480697631836</v>
+        <v>20.748067855835</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1359" t="n">
-        <v>20.7006969451904</v>
+        <v>20.7006950378418</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1362" t="n">
-        <v>20.7480697631836</v>
+        <v>20.748067855835</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G1365" t="n">
-        <v>18.815372467041</v>
+        <v>18.8153705596924</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>18.8763046264648</v>
       </c>
       <c r="G1368" t="n">
-        <v>18.4174613952637</v>
+        <v>18.4174633026123</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>18.8568840026855</v>
       </c>
       <c r="G1369" t="n">
-        <v>18.3985157012939</v>
+        <v>18.3985137939453</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G1371" t="n">
-        <v>17.6405944824219</v>
+        <v>17.6405963897705</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>19.1093444824219</v>
       </c>
       <c r="G1374" t="n">
-        <v>18.6448383331299</v>
+        <v>18.6448364257812</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>19.1870250701904</v>
       </c>
       <c r="G1375" t="n">
-        <v>18.720630645752</v>
+        <v>18.7206287384033</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G1377" t="n">
-        <v>20.0848865509033</v>
+        <v>20.0848846435547</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1378" t="n">
-        <v>19.705924987793</v>
+        <v>19.7059268951416</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1382" t="n">
-        <v>20.7006969451904</v>
+        <v>20.7006950378418</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1383" t="n">
-        <v>20.8428077697754</v>
+        <v>20.842809677124</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G1385" t="n">
-        <v>21.6480979919434</v>
+        <v>21.6480960845947</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1392" t="n">
-        <v>20.4407520294189</v>
+        <v>20.4407501220703</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1396" t="n">
-        <v>22.7336254119873</v>
+        <v>22.7336273193359</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>21.9042892456055</v>
+        <v>21.9042911529541</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1402" t="n">
-        <v>21.6603660583496</v>
+        <v>21.6603679656982</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1410" t="n">
-        <v>24.2459526062012</v>
+        <v>24.2459506988525</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1412" t="n">
-        <v>23.7093200683594</v>
+        <v>23.709321975708</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G1413" t="n">
-        <v>24.5386562347412</v>
+        <v>24.5386581420898</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1417" t="n">
-        <v>22.7336254119873</v>
+        <v>22.7336273193359</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1418" t="n">
-        <v>22.7336254119873</v>
+        <v>22.7336273193359</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>23.25</v>
       </c>
       <c r="G1420" t="n">
-        <v>22.6848449707031</v>
+        <v>22.6848430633545</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1422" t="n">
-        <v>22.3921356201172</v>
+        <v>22.3921375274658</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1428" t="n">
-        <v>22.2945652008057</v>
+        <v>22.2945671081543</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>21.6603660583496</v>
+        <v>21.6603679656982</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1430" t="n">
-        <v>21.5627975463867</v>
+        <v>21.5627956390381</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1432" t="n">
-        <v>22.14821434021</v>
+        <v>22.1482124328613</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1438" t="n">
-        <v>22.2945652008057</v>
+        <v>22.2945671081543</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1441" t="n">
-        <v>21.5627975463867</v>
+        <v>21.5627956390381</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1447" t="n">
-        <v>21.9042892456055</v>
+        <v>21.9042911529541</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1448" t="n">
-        <v>21.9042892456055</v>
+        <v>21.9042911529541</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1449" t="n">
-        <v>22.2945652008057</v>
+        <v>22.2945671081543</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1451" t="n">
-        <v>21.9042892456055</v>
+        <v>21.9042911529541</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1452" t="n">
-        <v>21.6603660583496</v>
+        <v>21.6603679656982</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1453" t="n">
-        <v>21.9042892456055</v>
+        <v>21.9042911529541</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1454" t="n">
-        <v>21.6603660583496</v>
+        <v>21.6603679656982</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>22</v>
       </c>
       <c r="G1456" t="n">
-        <v>21.4652271270752</v>
+        <v>21.4652290344238</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1460" t="n">
-        <v>21.3676605224609</v>
+        <v>21.3676586151123</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1466" t="n">
-        <v>19.201623916626</v>
+        <v>19.2016220092773</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1467" t="n">
-        <v>18.8113441467285</v>
+        <v>18.8113460540771</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>18.8308582305908</v>
+        <v>18.8308601379395</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1470" t="n">
-        <v>19.0650272369385</v>
+        <v>19.0650253295898</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1472" t="n">
-        <v>18.9869689941406</v>
+        <v>18.9869709014893</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1475" t="n">
-        <v>20.0504760742188</v>
+        <v>20.0504722595215</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1480" t="n">
-        <v>20.4407520294189</v>
+        <v>20.4407501220703</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1481" t="n">
-        <v>19.5626258850098</v>
+        <v>19.5626277923584</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1483" t="n">
-        <v>19.5626258850098</v>
+        <v>19.5626277923584</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1486" t="n">
-        <v>19.2406482696533</v>
+        <v>19.240650177002</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1487" t="n">
-        <v>18.8308582305908</v>
+        <v>18.8308601379395</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1498" t="n">
-        <v>18.8113441467285</v>
+        <v>18.8113460540771</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1499" t="n">
-        <v>18.5576667785645</v>
+        <v>18.5576648712158</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1502" t="n">
-        <v>18.5576667785645</v>
+        <v>18.5576648712158</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1503" t="n">
-        <v>18.7528018951416</v>
+        <v>18.7528038024902</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1505" t="n">
-        <v>17.3087787628174</v>
+        <v>17.308780670166</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1506" t="n">
-        <v>18.1673908233643</v>
+        <v>18.1673889160156</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1507" t="n">
-        <v>18.128360748291</v>
+        <v>18.1283626556396</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1508" t="n">
-        <v>16.6453075408936</v>
+        <v>16.6453094482422</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1509" t="n">
-        <v>18.3625259399414</v>
+        <v>18.36252784729</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1512" t="n">
-        <v>18.0112781524658</v>
+        <v>18.0112762451172</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1515" t="n">
-        <v>17.2112083435059</v>
+        <v>17.2112102508545</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1523" t="n">
-        <v>16.9965591430664</v>
+        <v>16.9965572357178</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>18</v>
       </c>
       <c r="G1529" t="n">
-        <v>17.5624599456787</v>
+        <v>17.5624580383301</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1533" t="n">
-        <v>16.8209323883057</v>
+        <v>16.8209342956543</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1534" t="n">
-        <v>16.5087127685547</v>
+        <v>16.5087108612061</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1535" t="n">
-        <v>17.3087787628174</v>
+        <v>17.308780670166</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1542" t="n">
-        <v>16.8280124664307</v>
+        <v>16.8280143737793</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>16.5715465545654</v>
+        <v>16.5715484619141</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1546" t="n">
-        <v>17.3803997039795</v>
+        <v>17.3803977966309</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1547" t="n">
-        <v>17.4987659454346</v>
+        <v>17.4987678527832</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1553" t="n">
-        <v>17.0844783782959</v>
+        <v>17.0844764709473</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1554" t="n">
-        <v>17.5974082946777</v>
+        <v>17.5974063873291</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1557" t="n">
-        <v>17.3212146759033</v>
+        <v>17.3212127685547</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1562" t="n">
-        <v>16.5715465545654</v>
+        <v>16.5715484619141</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1563" t="n">
-        <v>16.6307334899902</v>
+        <v>16.6307315826416</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1564" t="n">
-        <v>16.8280124664307</v>
+        <v>16.8280143737793</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1567" t="n">
-        <v>15.5654191970825</v>
+        <v>15.5654182434082</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="n">
-        <v>15.6837873458862</v>
+        <v>15.6837863922119</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>16.5</v>
       </c>
       <c r="G1570" t="n">
-        <v>16.2756271362305</v>
+        <v>16.2756290435791</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1571" t="n">
-        <v>16.2361698150635</v>
+        <v>16.2361717224121</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1572" t="n">
-        <v>15.920521736145</v>
+        <v>15.9205236434937</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1573" t="n">
-        <v>16.0191650390625</v>
+        <v>16.0191631317139</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>16.374267578125</v>
+        <v>16.3742694854736</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1575" t="n">
-        <v>16.8674697875977</v>
+        <v>16.867467880249</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1578" t="n">
-        <v>17.4593124389648</v>
+        <v>17.4593105316162</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1579" t="n">
-        <v>17.1042060852051</v>
+        <v>17.1042041778564</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1583" t="n">
-        <v>17.5579509735107</v>
+        <v>17.5579490661621</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1588" t="n">
-        <v>16.8674697875977</v>
+        <v>16.867467880249</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1590" t="n">
-        <v>16.7490997314453</v>
+        <v>16.7491016387939</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1594" t="n">
-        <v>16.9858360290527</v>
+        <v>16.9858379364014</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1595" t="n">
-        <v>17.5579509735107</v>
+        <v>17.5579490661621</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1596" t="n">
-        <v>17.8144130706787</v>
+        <v>17.8144149780273</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1605" t="n">
-        <v>19.2545604705811</v>
+        <v>19.2545623779297</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1609" t="n">
-        <v>19.2545604705811</v>
+        <v>19.2545623779297</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1612" t="n">
-        <v>19.136194229126</v>
+        <v>19.1361923217773</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1613" t="n">
-        <v>19.2545604705811</v>
+        <v>19.2545623779297</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1615" t="n">
-        <v>18.7613620758057</v>
+        <v>18.761360168457</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1618" t="n">
-        <v>19.136194229126</v>
+        <v>19.1361923217773</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1621" t="n">
-        <v>19.4518394470215</v>
+        <v>19.4518413543701</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1622" t="n">
-        <v>19.0770092010498</v>
+        <v>19.0770072937012</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1630" t="n">
-        <v>18.564079284668</v>
+        <v>18.5640811920166</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1634" t="n">
-        <v>18.0511493682861</v>
+        <v>18.0511512756348</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1635" t="n">
-        <v>16.9858360290527</v>
+        <v>16.9858379364014</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1636" t="n">
-        <v>17.5974082946777</v>
+        <v>17.5974063873291</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1644" t="n">
-        <v>17.3803997039795</v>
+        <v>17.3803977966309</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1645" t="n">
-        <v>17.9130535125732</v>
+        <v>17.9130554199219</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1652" t="n">
-        <v>18.4457130432129</v>
+        <v>18.4457111358643</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1655" t="n">
-        <v>18.4457130432129</v>
+        <v>18.4457111358643</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1656" t="n">
-        <v>18.8008155822754</v>
+        <v>18.800817489624</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>19.2940158843994</v>
+        <v>19.294017791748</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1659" t="n">
-        <v>19.0770092010498</v>
+        <v>19.0770072937012</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1662" t="n">
-        <v>17.9130535125732</v>
+        <v>17.9130554199219</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1665" t="n">
-        <v>17.9525108337402</v>
+        <v>17.9525127410889</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1677" t="n">
-        <v>17.6171360015869</v>
+        <v>17.6171340942383</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1680" t="n">
-        <v>18.8008155822754</v>
+        <v>18.800817489624</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1681" t="n">
-        <v>18.8600025177002</v>
+        <v>18.8600006103516</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1682" t="n">
-        <v>18.8600025177002</v>
+        <v>18.8600006103516</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1684" t="n">
-        <v>18.8600025177002</v>
+        <v>18.8600006103516</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1685" t="n">
-        <v>19.136194229126</v>
+        <v>19.1361923217773</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1691" t="n">
-        <v>19.1559219360352</v>
+        <v>19.1559200286865</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1692" t="n">
-        <v>19.4912967681885</v>
+        <v>19.4912986755371</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1693" t="n">
-        <v>19.1559219360352</v>
+        <v>19.1559200286865</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1699" t="n">
-        <v>21.0103549957275</v>
+        <v>21.0103569030762</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>21</v>
       </c>
       <c r="G1705" t="n">
-        <v>20.7144374847412</v>
+        <v>20.7144355773926</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>20.75</v>
       </c>
       <c r="G1706" t="n">
-        <v>20.4678363800049</v>
+        <v>20.4678344726562</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1712" t="n">
-        <v>18.8008155822754</v>
+        <v>18.800817489624</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1715" t="n">
-        <v>20.6651172637939</v>
+        <v>20.6651153564453</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1717" t="n">
-        <v>19.3926563262939</v>
+        <v>19.3926582336426</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>20</v>
       </c>
       <c r="G1718" t="n">
-        <v>19.7280330657959</v>
+        <v>19.7280349731445</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1720" t="n">
-        <v>17.8933258056641</v>
+        <v>17.8933277130127</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1724" t="n">
-        <v>18.7613620758057</v>
+        <v>18.761360168457</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1729" t="n">
-        <v>17.3014869689941</v>
+        <v>17.3014850616455</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1731" t="n">
-        <v>16.6307334899902</v>
+        <v>16.6307315826416</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1732" t="n">
-        <v>16.5123634338379</v>
+        <v>16.5123653411865</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>16.5</v>
       </c>
       <c r="G1734" t="n">
-        <v>16.2756271362305</v>
+        <v>16.2756290435791</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>15</v>
       </c>
       <c r="G1736" t="n">
-        <v>14.7960262298584</v>
+        <v>14.7960252761841</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1740" t="n">
-        <v>15.6837873458862</v>
+        <v>15.6837863922119</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1742" t="n">
-        <v>16.6307334899902</v>
+        <v>16.6307315826416</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1743" t="n">
-        <v>16.374267578125</v>
+        <v>16.3742694854736</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1747" t="n">
-        <v>16.9858360290527</v>
+        <v>16.9858379364014</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1748" t="n">
-        <v>17.1042060852051</v>
+        <v>17.1042041778564</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1758" t="n">
-        <v>19.2545604705811</v>
+        <v>19.2545623779297</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1759" t="n">
-        <v>20.1719150543213</v>
+        <v>20.1719169616699</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1761" t="n">
-        <v>19.3926563262939</v>
+        <v>19.3926582336426</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>21</v>
       </c>
       <c r="G1763" t="n">
-        <v>20.7144374847412</v>
+        <v>20.7144355773926</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>20.75</v>
       </c>
       <c r="G1764" t="n">
-        <v>20.4678363800049</v>
+        <v>20.4678344726562</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1766" t="n">
-        <v>20.615795135498</v>
+        <v>20.6157970428467</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1767" t="n">
-        <v>20.1719150543213</v>
+        <v>20.1719169616699</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1768" t="n">
-        <v>20.615795135498</v>
+        <v>20.6157970428467</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1772" t="n">
-        <v>20.4185161590576</v>
+        <v>20.418514251709</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>20.75</v>
       </c>
       <c r="G1773" t="n">
-        <v>20.4678363800049</v>
+        <v>20.4678344726562</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1784" t="n">
-        <v>22.2433586120605</v>
+        <v>22.2433567047119</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1785" t="n">
-        <v>22.3419971466064</v>
+        <v>22.3419990539551</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -55076,6 +55076,32 @@
         <v>27.9500007629395</v>
       </c>
       <c r="H2104" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>156459</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>28.7000007629395</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>27.8500003814697</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>28.1499996185303</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>28.6499996185303</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>28.6499996185303</v>
+      </c>
+      <c r="H2105" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G2" t="n">
-        <v>7.5317325592041</v>
+        <v>7.53173208236694</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G3" t="n">
-        <v>7.85126113891602</v>
+        <v>7.85125970840454</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G4" t="n">
-        <v>7.75996685028076</v>
+        <v>7.75996541976929</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G5" t="n">
-        <v>7.75996685028076</v>
+        <v>7.75996541976929</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.31955623626709</v>
       </c>
       <c r="G8" t="n">
-        <v>7.82204627990723</v>
+        <v>7.82204532623291</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.41859817504883</v>
       </c>
       <c r="G9" t="n">
-        <v>7.91516542434692</v>
+        <v>7.91516494750977</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.10884761810303</v>
       </c>
       <c r="G10" t="n">
-        <v>7.62393760681152</v>
+        <v>7.62393808364868</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>8.42830753326416</v>
       </c>
       <c r="G11" t="n">
-        <v>7.92429494857788</v>
+        <v>7.92429447174072</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G12" t="n">
-        <v>7.5317325592041</v>
+        <v>7.53173208236694</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G13" t="n">
-        <v>7.5317325592041</v>
+        <v>7.53173208236694</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>7.86609792709351</v>
       </c>
       <c r="G14" t="n">
-        <v>7.39570426940918</v>
+        <v>7.39570474624634</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>7.71656322479248</v>
       </c>
       <c r="G15" t="n">
-        <v>7.25511312484741</v>
+        <v>7.2551121711731</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.95154619216919</v>
       </c>
       <c r="G16" t="n">
-        <v>7.47604417800903</v>
+        <v>7.47604370117188</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>7.88940191268921</v>
       </c>
       <c r="G17" t="n">
-        <v>7.41761493682861</v>
+        <v>7.41761445999146</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.00106716156006</v>
       </c>
       <c r="G18" t="n">
-        <v>7.52260255813599</v>
+        <v>7.5226035118103</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>7.8651270866394</v>
       </c>
       <c r="G19" t="n">
-        <v>7.3947925567627</v>
+        <v>7.39479160308838</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>7.95251703262329</v>
       </c>
       <c r="G20" t="n">
-        <v>7.47695636749268</v>
+        <v>7.47695589065552</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>7.97193717956543</v>
       </c>
       <c r="G21" t="n">
-        <v>7.49521541595459</v>
+        <v>7.49521493911743</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>8.08068943023682</v>
       </c>
       <c r="G22" t="n">
-        <v>7.59746313095093</v>
+        <v>7.59746360778809</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>8.24381828308105</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75083780288696</v>
+        <v>7.75083684921265</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>8.37101936340332</v>
       </c>
       <c r="G26" t="n">
-        <v>7.87043190002441</v>
+        <v>7.87043237686157</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.45743942260742</v>
       </c>
       <c r="G28" t="n">
-        <v>7.95168590545654</v>
+        <v>7.95168495178223</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>8.31178760528564</v>
       </c>
       <c r="G29" t="n">
-        <v>7.81474256515503</v>
+        <v>7.81474208831787</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.47394561767578</v>
       </c>
       <c r="G30" t="n">
-        <v>7.96720218658447</v>
+        <v>7.96720314025879</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G31" t="n">
-        <v>7.85126113891602</v>
+        <v>7.85125970840454</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>8.25741195678711</v>
       </c>
       <c r="G32" t="n">
-        <v>7.76361894607544</v>
+        <v>7.76361846923828</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.20497798919678</v>
       </c>
       <c r="G33" t="n">
-        <v>7.71432018280029</v>
+        <v>7.71431970596313</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>8.31178760528564</v>
       </c>
       <c r="G37" t="n">
-        <v>7.81474256515503</v>
+        <v>7.81474208831787</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G39" t="n">
-        <v>7.85126113891602</v>
+        <v>7.85125970840454</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.29625225067139</v>
       </c>
       <c r="G40" t="n">
-        <v>7.80013704299927</v>
+        <v>7.80013656616211</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>8.12923908233643</v>
       </c>
       <c r="G41" t="n">
-        <v>7.6431097984314</v>
+        <v>7.64311027526855</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>8.1855583190918</v>
       </c>
       <c r="G43" t="n">
-        <v>7.69606113433838</v>
+        <v>7.69606161117554</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G45" t="n">
-        <v>7.85126113891602</v>
+        <v>7.85125970840454</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>8.33606338500977</v>
       </c>
       <c r="G46" t="n">
-        <v>7.83756542205811</v>
+        <v>7.83756685256958</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.99232816696167</v>
       </c>
       <c r="G47" t="n">
-        <v>7.51438617706299</v>
+        <v>7.51438665390015</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>8.10787677764893</v>
       </c>
       <c r="G48" t="n">
-        <v>7.62302541732788</v>
+        <v>7.62302684783936</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>8.22634029388428</v>
       </c>
       <c r="G49" t="n">
-        <v>7.73440504074097</v>
+        <v>7.73440551757812</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>8.1875</v>
       </c>
       <c r="G50" t="n">
-        <v>7.6978874206543</v>
+        <v>7.69788789749146</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>8.44772911071777</v>
       </c>
       <c r="G51" t="n">
-        <v>7.94255495071411</v>
+        <v>7.94255447387695</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G54" t="n">
-        <v>8.24930191040039</v>
+        <v>8.24930095672607</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>8.94293975830078</v>
       </c>
       <c r="G55" t="n">
-        <v>8.40815162658691</v>
+        <v>8.4081506729126</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>8.96721458435059</v>
       </c>
       <c r="G56" t="n">
-        <v>8.43097591400146</v>
+        <v>8.43097400665283</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.24977684020996</v>
       </c>
       <c r="G57" t="n">
-        <v>8.69664001464844</v>
+        <v>8.69663906097412</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.71960926055908</v>
       </c>
       <c r="G61" t="n">
-        <v>8.19817638397217</v>
+        <v>8.19817543029785</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G63" t="n">
-        <v>8.30772876739502</v>
+        <v>8.30772972106934</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.24395084381104</v>
       </c>
       <c r="G66" t="n">
-        <v>8.69116306304932</v>
+        <v>8.691162109375</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.10412693023682</v>
       </c>
       <c r="G67" t="n">
-        <v>8.55970096588135</v>
+        <v>8.55970001220703</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>9.15656089782715</v>
       </c>
       <c r="G68" t="n">
-        <v>8.60899829864502</v>
+        <v>8.60899925231934</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.29250144958496</v>
       </c>
       <c r="G69" t="n">
-        <v>8.73680877685547</v>
+        <v>8.73680973052979</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.66148281097412</v>
       </c>
       <c r="G74" t="n">
-        <v>9.08372688293457</v>
+        <v>9.08372497558594</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G75" t="n">
-        <v>9.27544116973877</v>
+        <v>9.27544212341309</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.63332366943359</v>
       </c>
       <c r="G77" t="n">
-        <v>9.0572509765625</v>
+        <v>9.05725193023682</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>9.50029563903809</v>
       </c>
       <c r="G78" t="n">
-        <v>8.93217754364014</v>
+        <v>8.93217849731445</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.57506275177002</v>
       </c>
       <c r="G80" t="n">
-        <v>9.00247478485107</v>
+        <v>9.00247383117676</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.53525161743164</v>
       </c>
       <c r="G81" t="n">
-        <v>8.96504402160645</v>
+        <v>8.96504306793213</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.16238689422607</v>
       </c>
       <c r="G86" t="n">
-        <v>8.61447525024414</v>
+        <v>8.61447715759277</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.98954772949219</v>
       </c>
       <c r="G87" t="n">
-        <v>8.45197296142578</v>
+        <v>8.45197105407715</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G88" t="n">
-        <v>8.30772876739502</v>
+        <v>8.30772972106934</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>8.43413352966309</v>
       </c>
       <c r="G89" t="n">
-        <v>7.929771900177</v>
+        <v>7.92977285385132</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>8.77689933776855</v>
       </c>
       <c r="G90" t="n">
-        <v>8.25203990936279</v>
+        <v>8.25204086303711</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>8.88467979431152</v>
       </c>
       <c r="G91" t="n">
-        <v>8.35337543487549</v>
+        <v>8.3533763885498</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.12743091583252</v>
       </c>
       <c r="G94" t="n">
-        <v>8.58161067962646</v>
+        <v>8.58160972595215</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.30706596374512</v>
       </c>
       <c r="G96" t="n">
-        <v>8.75050258636475</v>
+        <v>8.75050354003906</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G97" t="n">
-        <v>8.30772876739502</v>
+        <v>8.30772972106934</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>8.48462677001953</v>
       </c>
       <c r="G99" t="n">
-        <v>7.97724628448486</v>
+        <v>7.97724676132202</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.97193717956543</v>
       </c>
       <c r="G100" t="n">
-        <v>7.49521541595459</v>
+        <v>7.49521493911743</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G101" t="n">
-        <v>7.75996685028076</v>
+        <v>7.75996541976929</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.81476783752441</v>
       </c>
       <c r="G105" t="n">
-        <v>8.28764533996582</v>
+        <v>8.28764343261719</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.19443035125732</v>
       </c>
       <c r="G111" t="n">
-        <v>8.64460372924805</v>
+        <v>8.64460277557373</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>8.86817264556885</v>
       </c>
       <c r="G113" t="n">
-        <v>8.33785629272461</v>
+        <v>8.33785533905029</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.51084423065186</v>
       </c>
       <c r="G117" t="n">
-        <v>8.0018949508667</v>
+        <v>8.00189590454102</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.49724960327148</v>
       </c>
       <c r="G118" t="n">
-        <v>7.98911380767822</v>
+        <v>7.98911333084106</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>8.54482936859131</v>
       </c>
       <c r="G119" t="n">
-        <v>8.03384685516357</v>
+        <v>8.03384780883789</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.65260982513428</v>
       </c>
       <c r="G120" t="n">
-        <v>8.13518333435059</v>
+        <v>8.1351842880249</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.03324413299561</v>
       </c>
       <c r="G121" t="n">
-        <v>8.49305534362793</v>
+        <v>8.49305629730225</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>8.80700016021729</v>
       </c>
       <c r="G122" t="n">
-        <v>8.28034019470215</v>
+        <v>8.28034210205078</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>8.99149036407471</v>
       </c>
       <c r="G124" t="n">
-        <v>8.4537992477417</v>
+        <v>8.45379829406738</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.42650032043457</v>
       </c>
       <c r="G126" t="n">
-        <v>8.86279487609863</v>
+        <v>8.86279582977295</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.52748394012451</v>
       </c>
       <c r="G129" t="n">
-        <v>8.95774173736572</v>
+        <v>8.95774078369141</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.67119312286377</v>
       </c>
       <c r="G130" t="n">
-        <v>9.09285545349121</v>
+        <v>9.09285449981689</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>9.50029563903809</v>
       </c>
       <c r="G132" t="n">
-        <v>8.93217754364014</v>
+        <v>8.93217849731445</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.53525161743164</v>
       </c>
       <c r="G133" t="n">
-        <v>8.96504402160645</v>
+        <v>8.96504306793213</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.5935115814209</v>
       </c>
       <c r="G134" t="n">
-        <v>9.01981830596924</v>
+        <v>9.01981925964355</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.35755920410156</v>
       </c>
       <c r="G135" t="n">
-        <v>8.79797744750977</v>
+        <v>8.79797840118408</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G136" t="n">
-        <v>8.30772876739502</v>
+        <v>8.30772972106934</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>8.77495670318604</v>
       </c>
       <c r="G137" t="n">
-        <v>8.25021362304688</v>
+        <v>8.25021266937256</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G139" t="n">
-        <v>8.2164363861084</v>
+        <v>8.21643543243408</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>8.80991268157959</v>
       </c>
       <c r="G140" t="n">
-        <v>8.28308010101318</v>
+        <v>8.28307914733887</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8.66523265838623</v>
       </c>
       <c r="G141" t="n">
-        <v>8.14705181121826</v>
+        <v>8.14704990386963</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G142" t="n">
-        <v>8.24930191040039</v>
+        <v>8.24930095672607</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>8.7429141998291</v>
       </c>
       <c r="G144" t="n">
-        <v>8.22008800506592</v>
+        <v>8.2200870513916</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>8.76815986633301</v>
       </c>
       <c r="G145" t="n">
-        <v>8.24382305145264</v>
+        <v>8.24382400512695</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G146" t="n">
-        <v>8.30772876739502</v>
+        <v>8.30772972106934</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G147" t="n">
-        <v>8.24930191040039</v>
+        <v>8.24930095672607</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>8.98178005218506</v>
       </c>
       <c r="G148" t="n">
-        <v>8.44466781616211</v>
+        <v>8.44466876983643</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>8.94293975830078</v>
       </c>
       <c r="G149" t="n">
-        <v>8.40815162658691</v>
+        <v>8.4081506729126</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>8.91380977630615</v>
       </c>
       <c r="G150" t="n">
-        <v>8.38076496124268</v>
+        <v>8.38076400756836</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G152" t="n">
-        <v>8.2164363861084</v>
+        <v>8.21643543243408</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>8.82739067077637</v>
       </c>
       <c r="G153" t="n">
-        <v>8.29951190948486</v>
+        <v>8.29951286315918</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>8.65260982513428</v>
       </c>
       <c r="G154" t="n">
-        <v>8.13518333435059</v>
+        <v>8.1351842880249</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>8.68659496307373</v>
       </c>
       <c r="G155" t="n">
-        <v>8.16713619232178</v>
+        <v>8.16713523864746</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>8.61474132537842</v>
       </c>
       <c r="G156" t="n">
-        <v>8.09957885742188</v>
+        <v>8.09957981109619</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G157" t="n">
-        <v>8.2164363861084</v>
+        <v>8.21643543243408</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>8.87497043609619</v>
       </c>
       <c r="G158" t="n">
-        <v>8.34424686431885</v>
+        <v>8.34424781799316</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>8.96430206298828</v>
       </c>
       <c r="G160" t="n">
-        <v>8.42823696136475</v>
+        <v>8.42823791503906</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.21482086181641</v>
       </c>
       <c r="G164" t="n">
-        <v>8.66377353668213</v>
+        <v>8.66377449035645</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.61584568023682</v>
       </c>
       <c r="G165" t="n">
-        <v>9.04081630706787</v>
+        <v>9.0408182144165</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.57894706726074</v>
       </c>
       <c r="G166" t="n">
-        <v>9.00612545013428</v>
+        <v>9.00612449645996</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.40222454071045</v>
       </c>
       <c r="G167" t="n">
-        <v>8.8399715423584</v>
+        <v>8.83997058868408</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.33522605895996</v>
       </c>
       <c r="G169" t="n">
-        <v>8.77697849273682</v>
+        <v>8.77697944641113</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G171" t="n">
-        <v>8.99243068695068</v>
+        <v>8.99243259429932</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.75858306884766</v>
       </c>
       <c r="G172" t="n">
-        <v>9.17502117156982</v>
+        <v>9.17501831054688</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.72751140594482</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14580631256104</v>
+        <v>9.1458044052124</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.89258098602295</v>
       </c>
       <c r="G174" t="n">
-        <v>9.30100440979004</v>
+        <v>9.30100345611572</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.92753791809082</v>
       </c>
       <c r="G175" t="n">
-        <v>9.33386993408203</v>
+        <v>9.33387088775635</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>10.1547517776489</v>
       </c>
       <c r="G176" t="n">
-        <v>9.5474967956543</v>
+        <v>9.54749774932861</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>10.2440853118896</v>
       </c>
       <c r="G180" t="n">
-        <v>9.63148880004883</v>
+        <v>9.63148784637451</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>10.1372737884521</v>
       </c>
       <c r="G182" t="n">
-        <v>9.5310640335083</v>
+        <v>9.53106594085693</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>10.1625204086304</v>
       </c>
       <c r="G186" t="n">
-        <v>9.55480003356934</v>
+        <v>9.55480098724365</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>10.0304641723633</v>
       </c>
       <c r="G187" t="n">
-        <v>9.43064117431641</v>
+        <v>9.43064212799072</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>9.81101703643799</v>
       </c>
       <c r="G190" t="n">
-        <v>9.22431755065918</v>
+        <v>9.2243185043335</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>9.99939155578613</v>
       </c>
       <c r="G191" t="n">
-        <v>9.40142631530762</v>
+        <v>9.40142726898193</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.64594745635986</v>
       </c>
       <c r="G193" t="n">
-        <v>9.06911945343018</v>
+        <v>9.06911849975586</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G194" t="n">
-        <v>8.99243068695068</v>
+        <v>8.99243259429932</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.78771305084229</v>
       </c>
       <c r="G195" t="n">
-        <v>9.20240783691406</v>
+        <v>9.20240688323975</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.66148281097412</v>
       </c>
       <c r="G196" t="n">
-        <v>9.08372688293457</v>
+        <v>9.08372497558594</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.57409191131592</v>
       </c>
       <c r="G198" t="n">
-        <v>9.00156021118164</v>
+        <v>9.00156116485596</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>8.87497043609619</v>
       </c>
       <c r="G201" t="n">
-        <v>8.34424686431885</v>
+        <v>8.34424781799316</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.25657367706299</v>
       </c>
       <c r="G203" t="n">
-        <v>8.70302963256836</v>
+        <v>8.70302867889404</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.5935115814209</v>
       </c>
       <c r="G204" t="n">
-        <v>9.01981830596924</v>
+        <v>9.01981925964355</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>9.67119312286377</v>
       </c>
       <c r="G207" t="n">
-        <v>9.09285545349121</v>
+        <v>9.09285449981689</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>9.71003341674805</v>
       </c>
       <c r="G208" t="n">
-        <v>9.12937355041504</v>
+        <v>9.12937164306641</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>9.47699165344238</v>
       </c>
       <c r="G209" t="n">
-        <v>8.91026782989502</v>
+        <v>8.9102668762207</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>9.47699165344238</v>
       </c>
       <c r="G210" t="n">
-        <v>8.91026782989502</v>
+        <v>8.9102668762207</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.62264347076416</v>
       </c>
       <c r="G211" t="n">
-        <v>9.04720783233643</v>
+        <v>9.04720878601074</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.66148281097412</v>
       </c>
       <c r="G212" t="n">
-        <v>9.08372688293457</v>
+        <v>9.08372497558594</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.78771305084229</v>
       </c>
       <c r="G213" t="n">
-        <v>9.20240783691406</v>
+        <v>9.20240688323975</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.98191356658936</v>
       </c>
       <c r="G214" t="n">
-        <v>9.38499546051025</v>
+        <v>9.38499450683594</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G216" t="n">
-        <v>9.67713451385498</v>
+        <v>9.6771354675293</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.0790138244629</v>
       </c>
       <c r="G218" t="n">
-        <v>9.47628784179688</v>
+        <v>9.47628974914551</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.3120546340942</v>
       </c>
       <c r="G219" t="n">
-        <v>9.69539260864258</v>
+        <v>9.69539356231689</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G221" t="n">
-        <v>9.84146213531494</v>
+        <v>9.84146308898926</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>10.3120546340942</v>
       </c>
       <c r="G222" t="n">
-        <v>9.69539260864258</v>
+        <v>9.69539356231689</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G224" t="n">
-        <v>9.98753261566162</v>
+        <v>9.98753356933594</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G226" t="n">
-        <v>9.98753261566162</v>
+        <v>9.98753356933594</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G227" t="n">
-        <v>9.85972309112549</v>
+        <v>9.8597240447998</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G232" t="n">
-        <v>9.87798023223877</v>
+        <v>9.87798118591309</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G234" t="n">
-        <v>10.0423097610474</v>
+        <v>10.0423107147217</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.4285745620728</v>
       </c>
       <c r="G238" t="n">
-        <v>9.80494594573975</v>
+        <v>9.80494499206543</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G239" t="n">
-        <v>10.0788269042969</v>
+        <v>10.0788259506226</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G240" t="n">
-        <v>10.0423097610474</v>
+        <v>10.0423107147217</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G241" t="n">
-        <v>10.0423097610474</v>
+        <v>10.0423107147217</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G243" t="n">
-        <v>9.87798023223877</v>
+        <v>9.87798118591309</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G244" t="n">
-        <v>10.2431573867798</v>
+        <v>10.2431554794312</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>10.6033563613892</v>
       </c>
       <c r="G245" t="n">
-        <v>9.96927452087402</v>
+        <v>9.96927547454834</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G246" t="n">
-        <v>9.85972309112549</v>
+        <v>9.8597240447998</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>10.4285745620728</v>
       </c>
       <c r="G247" t="n">
-        <v>9.80494594573975</v>
+        <v>9.80494499206543</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G249" t="n">
-        <v>9.95101547241211</v>
+        <v>9.95101642608643</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>11.1082782745361</v>
       </c>
       <c r="G251" t="n">
-        <v>10.4440011978149</v>
+        <v>10.4440021514893</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>11.2636375427246</v>
       </c>
       <c r="G253" t="n">
-        <v>10.5900716781616</v>
+        <v>10.5900707244873</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>11.3413181304932</v>
       </c>
       <c r="G254" t="n">
-        <v>10.6631088256836</v>
+        <v>10.663106918335</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>11.0111770629883</v>
       </c>
       <c r="G255" t="n">
-        <v>10.3527069091797</v>
+        <v>10.3527088165283</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>11.0694379806519</v>
       </c>
       <c r="G256" t="n">
-        <v>10.4074831008911</v>
+        <v>10.4074850082397</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>11.0305967330933</v>
       </c>
       <c r="G257" t="n">
-        <v>10.3709650039673</v>
+        <v>10.3709678649902</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G259" t="n">
-        <v>9.95101547241211</v>
+        <v>9.95101642608643</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G262" t="n">
-        <v>10.0788269042969</v>
+        <v>10.0788259506226</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>10.6616163253784</v>
       </c>
       <c r="G263" t="n">
-        <v>10.1156787872314</v>
+        <v>10.1156797409058</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>10.6616163253784</v>
       </c>
       <c r="G268" t="n">
-        <v>10.1156787872314</v>
+        <v>10.1156797409058</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G270" t="n">
-        <v>9.93142127990723</v>
+        <v>9.93142032623291</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G271" t="n">
-        <v>10.1341028213501</v>
+        <v>10.1341047286987</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G272" t="n">
-        <v>10.1525287628174</v>
+        <v>10.1525297164917</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G273" t="n">
-        <v>10.1341028213501</v>
+        <v>10.1341047286987</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G274" t="n">
-        <v>10.0235500335693</v>
+        <v>10.023549079895</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G275" t="n">
-        <v>10.0235500335693</v>
+        <v>10.023549079895</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G278" t="n">
-        <v>9.93142127990723</v>
+        <v>9.93142032623291</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G279" t="n">
-        <v>10.1341028213501</v>
+        <v>10.1341047286987</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G280" t="n">
-        <v>10.1525287628174</v>
+        <v>10.1525297164917</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G285" t="n">
-        <v>9.80244255065918</v>
+        <v>9.80244159698486</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>10.6421957015991</v>
       </c>
       <c r="G286" t="n">
-        <v>10.0972528457642</v>
+        <v>10.0972518920898</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.0500173568726</v>
       </c>
       <c r="G287" t="n">
-        <v>10.4841899871826</v>
+        <v>10.4841909408569</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G288" t="n">
-        <v>10.3367862701416</v>
+        <v>10.3367853164673</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3552112579346</v>
+        <v>10.3552122116089</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G291" t="n">
-        <v>10.3367862701416</v>
+        <v>10.3367853164673</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>10.8558168411255</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2999334335327</v>
+        <v>10.2999353408813</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G293" t="n">
-        <v>9.93142127990723</v>
+        <v>9.93142032623291</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G294" t="n">
-        <v>9.76558971405029</v>
+        <v>9.76559162139893</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G295" t="n">
-        <v>10.2446575164795</v>
+        <v>10.2446584701538</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G296" t="n">
-        <v>10.3367862701416</v>
+        <v>10.3367853164673</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G297" t="n">
-        <v>9.96827220916748</v>
+        <v>9.96827411651611</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G298" t="n">
-        <v>9.93142127990723</v>
+        <v>9.93142032623291</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G299" t="n">
-        <v>9.80244255065918</v>
+        <v>9.80244159698486</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.2732152938843</v>
       </c>
       <c r="G301" t="n">
-        <v>9.74716567993164</v>
+        <v>9.74716663360596</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G305" t="n">
-        <v>10.1341028213501</v>
+        <v>10.1341047286987</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10.253794670105</v>
       </c>
       <c r="G306" t="n">
-        <v>9.72873973846436</v>
+        <v>9.72874069213867</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G307" t="n">
-        <v>9.93142127990723</v>
+        <v>9.93142032623291</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G309" t="n">
-        <v>9.93142127990723</v>
+        <v>9.93142032623291</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G310" t="n">
-        <v>10.1893787384033</v>
+        <v>10.189380645752</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G311" t="n">
-        <v>10.1893787384033</v>
+        <v>10.189380645752</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>11.0500173568726</v>
       </c>
       <c r="G313" t="n">
-        <v>10.4841899871826</v>
+        <v>10.4841909408569</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G314" t="n">
-        <v>10.7790021896362</v>
+        <v>10.7790012359619</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G315" t="n">
-        <v>10.4104871749878</v>
+        <v>10.4104881286621</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G316" t="n">
-        <v>10.1525287628174</v>
+        <v>10.1525297164917</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>11.943341255188</v>
       </c>
       <c r="G320" t="n">
-        <v>11.3317718505859</v>
+        <v>11.3317699432373</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>11.943341255188</v>
       </c>
       <c r="G321" t="n">
-        <v>11.3317718505859</v>
+        <v>11.3317699432373</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>12.176381111145</v>
       </c>
       <c r="G323" t="n">
-        <v>11.5528793334961</v>
+        <v>11.5528774261475</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>12.0598611831665</v>
       </c>
       <c r="G324" t="n">
-        <v>11.4423246383667</v>
+        <v>11.442325592041</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>12.176381111145</v>
       </c>
       <c r="G326" t="n">
-        <v>11.5528793334961</v>
+        <v>11.5528774261475</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G327" t="n">
-        <v>11.8845405578613</v>
+        <v>11.8845415115356</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G330" t="n">
-        <v>12.160924911499</v>
+        <v>12.1609239578247</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>13.0308637619019</v>
       </c>
       <c r="G331" t="n">
-        <v>12.3636054992676</v>
+        <v>12.3636064529419</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>13.186224937439</v>
       </c>
       <c r="G332" t="n">
-        <v>12.5110120773315</v>
+        <v>12.5110111236572</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>12.0210208892822</v>
       </c>
       <c r="G339" t="n">
-        <v>11.4054727554321</v>
+        <v>11.4054737091064</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>12.681303024292</v>
       </c>
       <c r="G345" t="n">
-        <v>12.031946182251</v>
+        <v>12.0319442749023</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G346" t="n">
-        <v>11.8845405578613</v>
+        <v>11.8845415115356</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G347" t="n">
-        <v>12.0872220993042</v>
+        <v>12.0872211456299</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G348" t="n">
-        <v>12.160924911499</v>
+        <v>12.1609239578247</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>13.2833251953125</v>
       </c>
       <c r="G352" t="n">
-        <v>12.6031398773193</v>
+        <v>12.6031408309937</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>13.5940456390381</v>
       </c>
       <c r="G353" t="n">
-        <v>12.89794921875</v>
+        <v>12.8979501724243</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>13.9824476242065</v>
       </c>
       <c r="G355" t="n">
-        <v>13.2664613723755</v>
+        <v>13.2664642333984</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>14.1378078460693</v>
       </c>
       <c r="G356" t="n">
-        <v>13.4138689041138</v>
+        <v>13.4138679504395</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>14.7204103469849</v>
       </c>
       <c r="G357" t="n">
-        <v>13.9666376113892</v>
+        <v>13.9666366577148</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>14.1378078460693</v>
       </c>
       <c r="G358" t="n">
-        <v>13.4138689041138</v>
+        <v>13.4138679504395</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>14.0989675521851</v>
       </c>
       <c r="G359" t="n">
-        <v>13.3770170211792</v>
+        <v>13.3770160675049</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.8270874023438</v>
       </c>
       <c r="G360" t="n">
-        <v>13.1190567016602</v>
+        <v>13.1190595626831</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G361" t="n">
-        <v>13.0269317626953</v>
+        <v>13.026930809021</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G362" t="n">
-        <v>13.0269317626953</v>
+        <v>13.026930809021</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G365" t="n">
-        <v>12.2162008285522</v>
+        <v>12.2162027359009</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>12.9920244216919</v>
       </c>
       <c r="G366" t="n">
-        <v>12.326756477356</v>
+        <v>12.3267545700073</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G367" t="n">
-        <v>12.160924911499</v>
+        <v>12.1609239578247</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G368" t="n">
-        <v>12.0872220993042</v>
+        <v>12.0872211456299</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G370" t="n">
-        <v>12.1240730285645</v>
+        <v>12.1240739822388</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.8560838699341</v>
       </c>
       <c r="G371" t="n">
-        <v>12.1977777481079</v>
+        <v>12.1977767944336</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>15.2835922241211</v>
       </c>
       <c r="G373" t="n">
-        <v>14.5009813308716</v>
+        <v>14.5009832382202</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>14.0407075881958</v>
       </c>
       <c r="G375" t="n">
-        <v>13.3217391967773</v>
+        <v>13.3217401504517</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G376" t="n">
-        <v>13.0822076797485</v>
+        <v>13.0822086334229</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G377" t="n">
-        <v>12.7689714431763</v>
+        <v>12.7689695358276</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G380" t="n">
-        <v>12.4741592407227</v>
+        <v>12.4741611480713</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G381" t="n">
-        <v>12.2899036407471</v>
+        <v>12.2899045944214</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G382" t="n">
-        <v>12.2899036407471</v>
+        <v>12.2899045944214</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G384" t="n">
-        <v>12.2162008285522</v>
+        <v>12.2162027359009</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>13.380425453186</v>
       </c>
       <c r="G385" t="n">
-        <v>12.6952667236328</v>
+        <v>12.6952686309814</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>13.4969463348389</v>
       </c>
       <c r="G387" t="n">
-        <v>12.8058223724365</v>
+        <v>12.8058233261108</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>13.9630270004272</v>
       </c>
       <c r="G391" t="n">
-        <v>13.2480373382568</v>
+        <v>13.2480363845825</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>13.9630270004272</v>
       </c>
       <c r="G392" t="n">
-        <v>13.2480373382568</v>
+        <v>13.2480363845825</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G393" t="n">
-        <v>13.0822076797485</v>
+        <v>13.0822086334229</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G394" t="n">
-        <v>12.7689714431763</v>
+        <v>12.7689695358276</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>13.6717262268066</v>
       </c>
       <c r="G396" t="n">
-        <v>12.9716529846191</v>
+        <v>12.9716539382935</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>12.8949241638184</v>
       </c>
       <c r="G398" t="n">
-        <v>12.2346286773682</v>
+        <v>12.2346277236938</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>13.0502843856812</v>
       </c>
       <c r="G400" t="n">
-        <v>12.3820333480835</v>
+        <v>12.3820323944092</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G405" t="n">
-        <v>12.160924911499</v>
+        <v>12.1609239578247</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G407" t="n">
-        <v>12.0872220993042</v>
+        <v>12.0872211456299</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G408" t="n">
-        <v>11.8845405578613</v>
+        <v>11.8845415115356</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>12.4094219207764</v>
       </c>
       <c r="G410" t="n">
-        <v>11.7739858627319</v>
+        <v>11.7739877700806</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G411" t="n">
-        <v>11.7002849578857</v>
+        <v>11.7002840042114</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>11.8268203735352</v>
       </c>
       <c r="G412" t="n">
-        <v>11.2212171554565</v>
+        <v>11.2212162017822</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G415" t="n">
-        <v>10.9632587432861</v>
+        <v>10.9632596969604</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G416" t="n">
-        <v>10.7790021896362</v>
+        <v>10.7790012359619</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G417" t="n">
-        <v>10.9632587432861</v>
+        <v>10.9632596969604</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G420" t="n">
-        <v>11.2396421432495</v>
+        <v>11.2396411895752</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G421" t="n">
-        <v>11.2396421432495</v>
+        <v>11.2396411895752</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>11.8073997497559</v>
       </c>
       <c r="G423" t="n">
-        <v>11.2027912139893</v>
+        <v>11.2027902603149</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G424" t="n">
-        <v>11.1475143432617</v>
+        <v>11.1475133895874</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G425" t="n">
-        <v>11.2396421432495</v>
+        <v>11.2396411895752</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G426" t="n">
-        <v>11.2396421432495</v>
+        <v>11.2396411895752</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G427" t="n">
-        <v>11.2396421432495</v>
+        <v>11.2396411895752</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G428" t="n">
-        <v>11.1475143432617</v>
+        <v>11.1475133895874</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>11.8073997497559</v>
       </c>
       <c r="G429" t="n">
-        <v>11.2027912139893</v>
+        <v>11.2027902603149</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>11.9045000076294</v>
       </c>
       <c r="G430" t="n">
-        <v>11.2949180603027</v>
+        <v>11.2949190139771</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G433" t="n">
-        <v>10.4104871749878</v>
+        <v>10.4104881286621</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G434" t="n">
-        <v>10.7790021896362</v>
+        <v>10.7790012359619</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G435" t="n">
-        <v>10.2446575164795</v>
+        <v>10.2446584701538</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G436" t="n">
-        <v>10.2446575164795</v>
+        <v>10.2446584701538</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G438" t="n">
-        <v>10.3552112579346</v>
+        <v>10.3552122116089</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G439" t="n">
-        <v>10.3367862701416</v>
+        <v>10.3367853164673</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G440" t="n">
-        <v>10.0235500335693</v>
+        <v>10.023549079895</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G443" t="n">
-        <v>9.36022472381592</v>
+        <v>9.36022663116455</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>10.0013341903687</v>
       </c>
       <c r="G446" t="n">
-        <v>9.48920631408691</v>
+        <v>9.48920726776123</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.12743091583252</v>
       </c>
       <c r="G447" t="n">
-        <v>8.66005229949951</v>
+        <v>8.66005325317383</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.22453117370605</v>
       </c>
       <c r="G449" t="n">
-        <v>8.75218105316162</v>
+        <v>8.7521800994873</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.6322193145752</v>
       </c>
       <c r="G451" t="n">
-        <v>8.1901969909668</v>
+        <v>8.19019794464111</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G453" t="n">
-        <v>8.47579669952393</v>
+        <v>8.47579574584961</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>10.0984344482422</v>
       </c>
       <c r="G455" t="n">
-        <v>9.58133602142334</v>
+        <v>9.58133506774902</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G456" t="n">
-        <v>11.7002849578857</v>
+        <v>11.7002840042114</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>11.2247982025146</v>
       </c>
       <c r="G458" t="n">
-        <v>10.6500225067139</v>
+        <v>10.6500215530396</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G460" t="n">
-        <v>10.1341028213501</v>
+        <v>10.1341047286987</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>10.234375</v>
       </c>
       <c r="G461" t="n">
-        <v>9.71031379699707</v>
+        <v>9.71031475067139</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G462" t="n">
-        <v>10.1341028213501</v>
+        <v>10.1341047286987</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G464" t="n">
-        <v>10.170955657959</v>
+        <v>10.1709547042847</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G465" t="n">
-        <v>9.76558971405029</v>
+        <v>9.76559162139893</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>10.2732152938843</v>
       </c>
       <c r="G466" t="n">
-        <v>9.74716567993164</v>
+        <v>9.74716663360596</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>10.1761140823364</v>
       </c>
       <c r="G467" t="n">
-        <v>9.65503597259521</v>
+        <v>9.65503692626953</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G468" t="n">
-        <v>9.94984817504883</v>
+        <v>9.94984722137451</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>11.2053775787354</v>
       </c>
       <c r="G469" t="n">
-        <v>10.6315965652466</v>
+        <v>10.6315956115723</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>11.8268203735352</v>
       </c>
       <c r="G471" t="n">
-        <v>11.2212171554565</v>
+        <v>11.2212162017822</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G473" t="n">
-        <v>11.7002849578857</v>
+        <v>11.7002840042114</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>12.2346420288086</v>
       </c>
       <c r="G474" t="n">
-        <v>11.6081571578979</v>
+        <v>11.6081562042236</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G475" t="n">
-        <v>11.7924108505249</v>
+        <v>11.7924127578735</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G477" t="n">
-        <v>12.4741592407227</v>
+        <v>12.4741611480713</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>13.2056446075439</v>
       </c>
       <c r="G478" t="n">
-        <v>12.5294370651245</v>
+        <v>12.5294361114502</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>12.3123216629028</v>
       </c>
       <c r="G482" t="n">
-        <v>11.6818590164185</v>
+        <v>11.6818580627441</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G483" t="n">
-        <v>11.7924108505249</v>
+        <v>11.7924127578735</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G484" t="n">
-        <v>12.1240730285645</v>
+        <v>12.1240739822388</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G485" t="n">
-        <v>11.7002849578857</v>
+        <v>11.7002840042114</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G488" t="n">
-        <v>13.0822076797485</v>
+        <v>13.0822086334229</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>14.1183881759644</v>
       </c>
       <c r="G490" t="n">
-        <v>13.3954420089722</v>
+        <v>13.3954429626465</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G491" t="n">
-        <v>13.0269317626953</v>
+        <v>13.026930809021</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>14.2931690216064</v>
       </c>
       <c r="G492" t="n">
-        <v>13.5612745285034</v>
+        <v>13.5612735748291</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>15.633152961731</v>
       </c>
       <c r="G495" t="n">
-        <v>14.8326435089111</v>
+        <v>14.8326425552368</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G498" t="n">
-        <v>15.6433725357056</v>
+        <v>15.6433706283569</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>16.7206764221191</v>
       </c>
       <c r="G499" t="n">
-        <v>15.8644781112671</v>
+        <v>15.8644800186157</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G500" t="n">
-        <v>15.2932844161987</v>
+        <v>15.2932825088501</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>15.6525726318359</v>
       </c>
       <c r="G501" t="n">
-        <v>14.8510684967041</v>
+        <v>14.8510675430298</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>15.3030118942261</v>
       </c>
       <c r="G502" t="n">
-        <v>14.5194072723389</v>
+        <v>14.5194082260132</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G504" t="n">
-        <v>13.9482126235962</v>
+        <v>13.9482107162476</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G505" t="n">
-        <v>13.9482126235962</v>
+        <v>13.9482107162476</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>14.4485292434692</v>
       </c>
       <c r="G507" t="n">
-        <v>13.7086801528931</v>
+        <v>13.7086782455444</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>14.4679489135742</v>
       </c>
       <c r="G508" t="n">
-        <v>13.727105140686</v>
+        <v>13.7271041870117</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>14.3125886917114</v>
       </c>
       <c r="G509" t="n">
-        <v>13.5796995162964</v>
+        <v>13.5796985626221</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>14.7398300170898</v>
       </c>
       <c r="G510" t="n">
-        <v>13.9850645065308</v>
+        <v>13.9850625991821</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>15.128231048584</v>
       </c>
       <c r="G514" t="n">
-        <v>14.4609603881836</v>
+        <v>14.4609594345093</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G515" t="n">
-        <v>14.7022848129272</v>
+        <v>14.7022829055786</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>15.3612718582153</v>
       </c>
       <c r="G517" t="n">
-        <v>14.6837205886841</v>
+        <v>14.6837196350098</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>15.3418521881104</v>
       </c>
       <c r="G518" t="n">
-        <v>14.6651573181152</v>
+        <v>14.6651582717896</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>15.8661937713623</v>
       </c>
       <c r="G520" t="n">
-        <v>15.1663722991943</v>
+        <v>15.16637134552</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G521" t="n">
-        <v>14.7022848129272</v>
+        <v>14.7022829055786</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G522" t="n">
-        <v>15.129246711731</v>
+        <v>15.1292457580566</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>16.0215549468994</v>
       </c>
       <c r="G523" t="n">
-        <v>15.3148803710938</v>
+        <v>15.3148794174194</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>15.9244537353516</v>
       </c>
       <c r="G524" t="n">
-        <v>15.2220611572266</v>
+        <v>15.2220630645752</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>15.1864919662476</v>
       </c>
       <c r="G526" t="n">
-        <v>14.5166511535645</v>
+        <v>14.5166492462158</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G528" t="n">
-        <v>14.9807367324829</v>
+        <v>14.9807376861572</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G531" t="n">
-        <v>15.0364274978638</v>
+        <v>15.0364294052124</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G534" t="n">
-        <v>15.129246711731</v>
+        <v>15.1292457580566</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G535" t="n">
-        <v>15.129246711731</v>
+        <v>15.1292457580566</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G539" t="n">
-        <v>14.8507919311523</v>
+        <v>14.8507928848267</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>15.3612718582153</v>
       </c>
       <c r="G542" t="n">
-        <v>14.6837205886841</v>
+        <v>14.6837196350098</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G543" t="n">
-        <v>14.8507919311523</v>
+        <v>14.8507928848267</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G546" t="n">
-        <v>16.0574226379395</v>
+        <v>16.0574169158936</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G547" t="n">
-        <v>16.8556518554688</v>
+        <v>16.8556499481201</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G548" t="n">
-        <v>17.5610618591309</v>
+        <v>17.5610637664795</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G549" t="n">
-        <v>17.5610618591309</v>
+        <v>17.5610637664795</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G550" t="n">
-        <v>16.6143245697021</v>
+        <v>16.6143264770508</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>18.1189212799072</v>
       </c>
       <c r="G552" t="n">
-        <v>17.3197383880615</v>
+        <v>17.3197364807129</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>18.0995025634766</v>
       </c>
       <c r="G553" t="n">
-        <v>17.3011741638184</v>
+        <v>17.301176071167</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G554" t="n">
-        <v>17.2826118469238</v>
+        <v>17.2826099395752</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>18.9928245544434</v>
       </c>
       <c r="G558" t="n">
-        <v>18.1550941467285</v>
+        <v>18.1550922393799</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G559" t="n">
-        <v>18.1922225952148</v>
+        <v>18.1922206878662</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G560" t="n">
-        <v>17.542501449585</v>
+        <v>17.5424995422363</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G563" t="n">
-        <v>18.5634899139404</v>
+        <v>18.5634937286377</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G564" t="n">
-        <v>19.0275764465332</v>
+        <v>19.0275783538818</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G566" t="n">
-        <v>18.5634899139404</v>
+        <v>18.5634937286377</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G569" t="n">
-        <v>17.9137687683105</v>
+        <v>17.9137706756592</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G570" t="n">
-        <v>17.264045715332</v>
+        <v>17.2640476226807</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G572" t="n">
-        <v>17.3568649291992</v>
+        <v>17.3568630218506</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G573" t="n">
-        <v>17.6910037994385</v>
+        <v>17.6910057067871</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G575" t="n">
-        <v>16.5586318969727</v>
+        <v>16.5586338043213</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>16.4487953186035</v>
       </c>
       <c r="G576" t="n">
-        <v>15.72327709198</v>
+        <v>15.7232751846313</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G577" t="n">
-        <v>16.3544330596924</v>
+        <v>16.3544368743896</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>16.5847358703613</v>
       </c>
       <c r="G578" t="n">
-        <v>15.8532190322876</v>
+        <v>15.8532209396362</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>15.9827136993408</v>
       </c>
       <c r="G579" t="n">
-        <v>15.2777528762817</v>
+        <v>15.2777519226074</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G580" t="n">
-        <v>15.6675853729248</v>
+        <v>15.6675863265991</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G582" t="n">
-        <v>16.4843807220459</v>
+        <v>16.4843826293945</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>16.9342975616455</v>
       </c>
       <c r="G583" t="n">
-        <v>16.1873626708984</v>
+        <v>16.1873645782471</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G584" t="n">
-        <v>16.3173065185547</v>
+        <v>16.317310333252</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G585" t="n">
-        <v>16.1688041687012</v>
+        <v>16.1688022613525</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G590" t="n">
-        <v>16.2616195678711</v>
+        <v>16.2616176605225</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G591" t="n">
-        <v>16.2616195678711</v>
+        <v>16.2616176605225</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G594" t="n">
-        <v>16.5586318969727</v>
+        <v>16.5586338043213</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G595" t="n">
-        <v>16.5771961212158</v>
+        <v>16.5771999359131</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G596" t="n">
-        <v>16.5215072631836</v>
+        <v>16.5215091705322</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G597" t="n">
-        <v>16.5029430389404</v>
+        <v>16.5029449462891</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G598" t="n">
-        <v>16.6514530181885</v>
+        <v>16.6514549255371</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G600" t="n">
-        <v>16.4843807220459</v>
+        <v>16.4843826293945</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>17.4586391448975</v>
       </c>
       <c r="G601" t="n">
-        <v>16.6885757446289</v>
+        <v>16.6885795593262</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G602" t="n">
-        <v>16.6143245697021</v>
+        <v>16.6143264770508</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G603" t="n">
-        <v>15.6861505508423</v>
+        <v>15.6861486434937</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>16.0409755706787</v>
       </c>
       <c r="G604" t="n">
-        <v>15.3334445953369</v>
+        <v>15.3334436416626</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>15.2641716003418</v>
       </c>
       <c r="G606" t="n">
-        <v>14.5909023284912</v>
+        <v>14.5909042358398</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G607" t="n">
-        <v>14.8507919311523</v>
+        <v>14.8507928848267</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G608" t="n">
-        <v>14.8507919311523</v>
+        <v>14.8507928848267</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G609" t="n">
-        <v>15.6861505508423</v>
+        <v>15.6861486434937</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G610" t="n">
-        <v>14.9807367324829</v>
+        <v>14.9807376861572</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>15.108811378479</v>
       </c>
       <c r="G611" t="n">
-        <v>14.4423971176147</v>
+        <v>14.4423961639404</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>18.0024013519287</v>
       </c>
       <c r="G612" t="n">
-        <v>17.2083568572998</v>
+        <v>17.2083549499512</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G613" t="n">
-        <v>16.4101276397705</v>
+        <v>16.4101257324219</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G614" t="n">
-        <v>16.4101276397705</v>
+        <v>16.4101257324219</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>16.5847358703613</v>
       </c>
       <c r="G615" t="n">
-        <v>15.8532190322876</v>
+        <v>15.8532209396362</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>16.2351741790771</v>
       </c>
       <c r="G616" t="n">
-        <v>15.519079208374</v>
+        <v>15.5190782546997</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G617" t="n">
-        <v>16.1688041687012</v>
+        <v>16.1688022613525</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G618" t="n">
-        <v>15.7789669036865</v>
+        <v>15.7789649963379</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>16.8760375976562</v>
       </c>
       <c r="G620" t="n">
-        <v>16.1316757202148</v>
+        <v>16.1316719055176</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G621" t="n">
-        <v>16.5215072631836</v>
+        <v>16.5215091705322</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G622" t="n">
-        <v>16.4843807220459</v>
+        <v>16.4843826293945</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G624" t="n">
-        <v>16.3729991912842</v>
+        <v>16.3730010986328</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G625" t="n">
-        <v>16.8556518554688</v>
+        <v>16.8556499481201</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>17.4974803924561</v>
       </c>
       <c r="G626" t="n">
-        <v>16.7257041931152</v>
+        <v>16.7257080078125</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G628" t="n">
-        <v>16.5029430389404</v>
+        <v>16.5029449462891</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G630" t="n">
-        <v>16.5029430389404</v>
+        <v>16.5029449462891</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G631" t="n">
-        <v>16.3173065185547</v>
+        <v>16.317310333252</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G632" t="n">
-        <v>16.3358707427979</v>
+        <v>16.3358745574951</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>17.4974803924561</v>
       </c>
       <c r="G633" t="n">
-        <v>16.7257041931152</v>
+        <v>16.7257080078125</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G634" t="n">
-        <v>16.837085723877</v>
+        <v>16.8370876312256</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>17.7499408721924</v>
       </c>
       <c r="G635" t="n">
-        <v>16.9670295715332</v>
+        <v>16.9670314788818</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G636" t="n">
-        <v>16.3544330596924</v>
+        <v>16.3544368743896</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G639" t="n">
-        <v>16.3729991912842</v>
+        <v>16.3730010986328</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G642" t="n">
-        <v>16.3544330596924</v>
+        <v>16.3544368743896</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G644" t="n">
-        <v>17.2826118469238</v>
+        <v>17.2826099395752</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G646" t="n">
-        <v>17.7838230133057</v>
+        <v>17.7838249206543</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>18.7986240386963</v>
       </c>
       <c r="G647" t="n">
-        <v>17.9694595336914</v>
+        <v>17.9694576263428</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G648" t="n">
-        <v>18.4149837493896</v>
+        <v>18.4149856567383</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G649" t="n">
-        <v>17.8023834228516</v>
+        <v>17.8023872375488</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G652" t="n">
-        <v>16.5771961212158</v>
+        <v>16.5771999359131</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G654" t="n">
-        <v>16.3358707427979</v>
+        <v>16.3358745574951</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>17.2255992889404</v>
       </c>
       <c r="G655" t="n">
-        <v>16.4658164978027</v>
+        <v>16.4658184051514</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>17.2255992889404</v>
       </c>
       <c r="G658" t="n">
-        <v>16.4658164978027</v>
+        <v>16.4658184051514</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G660" t="n">
-        <v>16.5029430389404</v>
+        <v>16.5029449462891</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>17.2061786651611</v>
       </c>
       <c r="G662" t="n">
-        <v>16.4472522735596</v>
+        <v>16.4472541809082</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G663" t="n">
-        <v>16.3729991912842</v>
+        <v>16.3730010986328</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G664" t="n">
-        <v>16.3729991912842</v>
+        <v>16.3730010986328</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G666" t="n">
-        <v>16.5215072631836</v>
+        <v>16.5215091705322</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G667" t="n">
-        <v>16.3358707427979</v>
+        <v>16.3358745574951</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G668" t="n">
-        <v>16.1688041687012</v>
+        <v>16.1688022613525</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G669" t="n">
-        <v>15.7789669036865</v>
+        <v>15.7789649963379</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G671" t="n">
-        <v>16.2616195678711</v>
+        <v>16.2616176605225</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G674" t="n">
-        <v>16.3173065185547</v>
+        <v>16.317310333252</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>17.2061786651611</v>
       </c>
       <c r="G679" t="n">
-        <v>16.4472522735596</v>
+        <v>16.4472541809082</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G680" t="n">
-        <v>16.5586318969727</v>
+        <v>16.5586338043213</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>16.7012577056885</v>
       </c>
       <c r="G682" t="n">
-        <v>15.9646034240723</v>
+        <v>15.9646043777466</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>16.4682159423828</v>
       </c>
       <c r="G683" t="n">
-        <v>15.7418413162231</v>
+        <v>15.7418384552002</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>16.8760375976562</v>
       </c>
       <c r="G685" t="n">
-        <v>16.1316757202148</v>
+        <v>16.1316719055176</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>16.2157554626465</v>
       </c>
       <c r="G687" t="n">
-        <v>15.5005159378052</v>
+        <v>15.5005149841309</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>16.9342975616455</v>
       </c>
       <c r="G688" t="n">
-        <v>16.1873626708984</v>
+        <v>16.1873645782471</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>16.6429977416992</v>
       </c>
       <c r="G689" t="n">
-        <v>15.9089136123657</v>
+        <v>15.9089117050171</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>16.5264759063721</v>
       </c>
       <c r="G690" t="n">
-        <v>15.797532081604</v>
+        <v>15.7975301742554</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>16.6041564941406</v>
       </c>
       <c r="G691" t="n">
-        <v>15.8717832565308</v>
+        <v>15.8717851638794</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>15.9632940292358</v>
       </c>
       <c r="G692" t="n">
-        <v>15.2591886520386</v>
+        <v>15.2591896057129</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G694" t="n">
-        <v>14.4238309860229</v>
+        <v>14.4238328933716</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>14.7204103469849</v>
       </c>
       <c r="G695" t="n">
-        <v>14.0711269378662</v>
+        <v>14.0711259841919</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>15.3418521881104</v>
       </c>
       <c r="G696" t="n">
-        <v>14.6651573181152</v>
+        <v>14.6651582717896</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G697" t="n">
-        <v>14.4238309860229</v>
+        <v>14.4238328933716</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>15.4389533996582</v>
       </c>
       <c r="G698" t="n">
-        <v>14.7579755783081</v>
+        <v>14.7579746246338</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G700" t="n">
-        <v>15.0364274978638</v>
+        <v>15.0364294052124</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G701" t="n">
-        <v>15.4076986312866</v>
+        <v>15.4076957702637</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>16.2934341430664</v>
       </c>
       <c r="G703" t="n">
-        <v>15.5747690200806</v>
+        <v>15.5747671127319</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>16.1380748748779</v>
       </c>
       <c r="G704" t="n">
-        <v>15.4262599945068</v>
+        <v>15.4262609481812</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G706" t="n">
-        <v>15.4076986312866</v>
+        <v>15.4076957702637</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>16.0603942871094</v>
       </c>
       <c r="G708" t="n">
-        <v>15.3520069122314</v>
+        <v>15.3520059585571</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G709" t="n">
-        <v>15.6675853729248</v>
+        <v>15.6675863265991</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>16.2740154266357</v>
       </c>
       <c r="G710" t="n">
-        <v>15.5562047958374</v>
+        <v>15.5562057495117</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G711" t="n">
-        <v>15.7604055404663</v>
+        <v>15.7604036331177</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>16.856616973877</v>
       </c>
       <c r="G712" t="n">
-        <v>16.1131076812744</v>
+        <v>16.113109588623</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G714" t="n">
-        <v>16.5771961212158</v>
+        <v>16.5771999359131</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G717" t="n">
-        <v>17.8209533691406</v>
+        <v>17.820951461792</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G718" t="n">
-        <v>17.542501449585</v>
+        <v>17.5424995422363</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G719" t="n">
-        <v>17.542501449585</v>
+        <v>17.5424995422363</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>18.4684829711914</v>
       </c>
       <c r="G721" t="n">
-        <v>17.653881072998</v>
+        <v>17.6538772583008</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G722" t="n">
-        <v>18.0065860748291</v>
+        <v>18.0065841674805</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G723" t="n">
-        <v>17.8209533691406</v>
+        <v>17.820951461792</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>18.3325424194336</v>
       </c>
       <c r="G724" t="n">
-        <v>17.5239372253418</v>
+        <v>17.5239353179932</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G725" t="n">
-        <v>17.8209533691406</v>
+        <v>17.820951461792</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>19.2064456939697</v>
       </c>
       <c r="G726" t="n">
-        <v>18.3592929840088</v>
+        <v>18.3592948913574</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>18.779203414917</v>
       </c>
       <c r="G727" t="n">
-        <v>17.9508934020996</v>
+        <v>17.9508972167969</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G729" t="n">
-        <v>17.264045715332</v>
+        <v>17.2640476226807</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>17.8470401763916</v>
       </c>
       <c r="G730" t="n">
-        <v>17.0598468780518</v>
+        <v>17.0598487854004</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G732" t="n">
-        <v>17.2826118469238</v>
+        <v>17.2826099395752</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G733" t="n">
-        <v>17.4496784210205</v>
+        <v>17.4496822357178</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>18.293701171875</v>
       </c>
       <c r="G734" t="n">
-        <v>17.4868087768555</v>
+        <v>17.4868068695068</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G736" t="n">
-        <v>18.1922225952148</v>
+        <v>18.1922206878662</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G738" t="n">
-        <v>19.6772975921631</v>
+        <v>19.6773014068604</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G739" t="n">
-        <v>19.3060321807861</v>
+        <v>19.3060302734375</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G740" t="n">
-        <v>19.3988494873047</v>
+        <v>19.3988456726074</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G742" t="n">
-        <v>20.4198398590088</v>
+        <v>20.4198417663574</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G743" t="n">
-        <v>20.3270225524902</v>
+        <v>20.3270244598389</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G744" t="n">
-        <v>20.1413898468018</v>
+        <v>20.1413860321045</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G745" t="n">
-        <v>20.0021591186523</v>
+        <v>20.002161026001</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G746" t="n">
-        <v>19.8165283203125</v>
+        <v>19.8165264129639</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G747" t="n">
-        <v>20.1413898468018</v>
+        <v>20.1413860321045</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G748" t="n">
-        <v>20.0949802398682</v>
+        <v>20.0949783325195</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G749" t="n">
-        <v>20.466251373291</v>
+        <v>20.4662494659424</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G751" t="n">
-        <v>21.0695629119873</v>
+        <v>21.0695610046387</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G752" t="n">
-        <v>21.4408340454102</v>
+        <v>21.4408302307129</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G753" t="n">
-        <v>21.8120994567871</v>
+        <v>21.8121013641357</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G754" t="n">
-        <v>21.1623783111572</v>
+        <v>21.1623802185059</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G755" t="n">
-        <v>20.1413898468018</v>
+        <v>20.1413860321045</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G756" t="n">
-        <v>20.466251373291</v>
+        <v>20.4662494659424</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G757" t="n">
-        <v>20.4198398590088</v>
+        <v>20.4198417663574</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G758" t="n">
-        <v>20.3270225524902</v>
+        <v>20.3270244598389</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G759" t="n">
-        <v>20.6982917785645</v>
+        <v>20.6982936859131</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G760" t="n">
-        <v>20.0949802398682</v>
+        <v>20.0949783325195</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G761" t="n">
-        <v>19.9557552337646</v>
+        <v>19.955753326416</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G762" t="n">
-        <v>19.8165283203125</v>
+        <v>19.8165264129639</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G764" t="n">
-        <v>19.6308917999268</v>
+        <v>19.6308898925781</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>20.245418548584</v>
       </c>
       <c r="G766" t="n">
-        <v>19.3524379730225</v>
+        <v>19.3524398803711</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>19.9541187286377</v>
       </c>
       <c r="G767" t="n">
-        <v>19.0739860534668</v>
+        <v>19.0739879608154</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G770" t="n">
-        <v>19.6528339385986</v>
+        <v>19.65283203125</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G772" t="n">
-        <v>19.4194297790527</v>
+        <v>19.4194278717041</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G776" t="n">
-        <v>18.7192096710205</v>
+        <v>18.7192077636719</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G777" t="n">
-        <v>19.0459785461426</v>
+        <v>19.0459804534912</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G778" t="n">
-        <v>18.9526138305664</v>
+        <v>18.952615737915</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G779" t="n">
-        <v>18.8125705718994</v>
+        <v>18.812572479248</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G780" t="n">
-        <v>19.5127925872803</v>
+        <v>19.5127906799316</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G782" t="n">
-        <v>19.6528339385986</v>
+        <v>19.65283203125</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G784" t="n">
-        <v>19.6995182037354</v>
+        <v>19.6995162963867</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G786" t="n">
-        <v>19.0459785461426</v>
+        <v>19.0459804534912</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G787" t="n">
-        <v>18.9526138305664</v>
+        <v>18.952615737915</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G789" t="n">
-        <v>18.5044765472412</v>
+        <v>18.5044784545898</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G790" t="n">
-        <v>18.3550968170166</v>
+        <v>18.355094909668</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>19.4006462097168</v>
       </c>
       <c r="G791" t="n">
-        <v>18.6538562774658</v>
+        <v>18.6538524627686</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G793" t="n">
-        <v>18.6725273132324</v>
+        <v>18.6725292205811</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G794" t="n">
-        <v>18.6725273132324</v>
+        <v>18.6725292205811</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G796" t="n">
-        <v>18.6725273132324</v>
+        <v>18.6725292205811</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G797" t="n">
-        <v>18.7192096710205</v>
+        <v>18.7192077636719</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G798" t="n">
-        <v>18.6725273132324</v>
+        <v>18.6725292205811</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G801" t="n">
-        <v>20.2596950531006</v>
+        <v>20.2596912384033</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G804" t="n">
-        <v>21.146635055542</v>
+        <v>21.1466388702393</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G805" t="n">
-        <v>21.9402179718018</v>
+        <v>21.940221786499</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G806" t="n">
-        <v>22.3136692047119</v>
+        <v>22.3136711120605</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G807" t="n">
-        <v>22.8271656036377</v>
+        <v>22.8271675109863</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G809" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406620025635</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G810" t="n">
-        <v>23.0138931274414</v>
+        <v>23.0138912200928</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G811" t="n">
-        <v>22.9205265045166</v>
+        <v>22.9205284118652</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G812" t="n">
-        <v>23.4340229034424</v>
+        <v>23.4340209960938</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G814" t="n">
-        <v>23.6207466125488</v>
+        <v>23.6207485198975</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G816" t="n">
-        <v>23.0138931274414</v>
+        <v>23.0138912200928</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G817" t="n">
-        <v>22.8738479614258</v>
+        <v>22.8738460540771</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G820" t="n">
-        <v>23.0138931274414</v>
+        <v>23.0138912200928</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G821" t="n">
-        <v>23.6207466125488</v>
+        <v>23.6207485198975</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G822" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406620025635</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G824" t="n">
-        <v>23.3873424530029</v>
+        <v>23.3873405456543</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G825" t="n">
-        <v>22.8738479614258</v>
+        <v>22.8738460540771</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G826" t="n">
-        <v>22.780481338501</v>
+        <v>22.7804832458496</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G827" t="n">
-        <v>22.8271656036377</v>
+        <v>22.8271675109863</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G829" t="n">
-        <v>23.107250213623</v>
+        <v>23.1072521209717</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G830" t="n">
-        <v>22.8271656036377</v>
+        <v>22.8271675109863</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G831" t="n">
-        <v>22.8271656036377</v>
+        <v>22.8271675109863</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G832" t="n">
-        <v>23.2939777374268</v>
+        <v>23.293981552124</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G833" t="n">
-        <v>22.780481338501</v>
+        <v>22.7804832458496</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G834" t="n">
-        <v>23.107250213623</v>
+        <v>23.1072521209717</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G835" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406620025635</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G837" t="n">
-        <v>23.714111328125</v>
+        <v>23.7141094207764</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G838" t="n">
-        <v>22.8271656036377</v>
+        <v>22.8271675109863</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G839" t="n">
-        <v>21.6134510040283</v>
+        <v>21.613452911377</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>22.8671283721924</v>
       </c>
       <c r="G841" t="n">
-        <v>21.9869022369385</v>
+        <v>21.9869003295898</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G842" t="n">
-        <v>21.8001747131348</v>
+        <v>21.8001766204834</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G845" t="n">
-        <v>20.7731838226318</v>
+        <v>20.7731857299805</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G848" t="n">
-        <v>20.4464168548584</v>
+        <v>20.4464206695557</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>21.9446754455566</v>
       </c>
       <c r="G849" t="n">
-        <v>21.0999584197998</v>
+        <v>21.0999565124512</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G850" t="n">
-        <v>21.7068119049072</v>
+        <v>21.7068138122559</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G851" t="n">
-        <v>22.8738479614258</v>
+        <v>22.8738460540771</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G852" t="n">
-        <v>24.6477355957031</v>
+        <v>24.6477375030518</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G853" t="n">
-        <v>24.5076923370361</v>
+        <v>24.5076904296875</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G854" t="n">
-        <v>24.8344631195068</v>
+        <v>24.8344593048096</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G855" t="n">
-        <v>24.274284362793</v>
+        <v>24.2742862701416</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G856" t="n">
-        <v>24.5076923370361</v>
+        <v>24.5076904296875</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G859" t="n">
-        <v>23.4340229034424</v>
+        <v>23.4340209960938</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G860" t="n">
-        <v>23.4807033538818</v>
+        <v>23.4807014465332</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G862" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406620025635</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G863" t="n">
-        <v>23.3873424530029</v>
+        <v>23.3873405456543</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G864" t="n">
-        <v>23.994197845459</v>
+        <v>23.9941959381104</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G865" t="n">
-        <v>23.6674308776855</v>
+        <v>23.6674289703369</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G866" t="n">
-        <v>24.134241104126</v>
+        <v>24.1342430114746</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G867" t="n">
-        <v>24.134241104126</v>
+        <v>24.1342430114746</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G868" t="n">
-        <v>23.8074741363525</v>
+        <v>23.8074722290039</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G869" t="n">
-        <v>23.8074741363525</v>
+        <v>23.8074722290039</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G870" t="n">
-        <v>24.274284362793</v>
+        <v>24.2742862701416</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G872" t="n">
-        <v>24.5076923370361</v>
+        <v>24.5076904296875</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>26.2656402587891</v>
       </c>
       <c r="G874" t="n">
-        <v>25.2545967102051</v>
+        <v>25.2545948028564</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G879" t="n">
-        <v>23.6207466125488</v>
+        <v>23.6207485198975</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G880" t="n">
-        <v>23.4807033538818</v>
+        <v>23.4807014465332</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G881" t="n">
-        <v>23.1539325714111</v>
+        <v>23.1539344787598</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G882" t="n">
-        <v>22.8738479614258</v>
+        <v>22.8738460540771</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>23.3040790557861</v>
       </c>
       <c r="G883" t="n">
-        <v>22.4070339202881</v>
+        <v>22.4070320129395</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G887" t="n">
-        <v>22.8271656036377</v>
+        <v>22.8271675109863</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G888" t="n">
-        <v>22.8738479614258</v>
+        <v>22.8738460540771</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>25.0518856048584</v>
       </c>
       <c r="G889" t="n">
-        <v>24.0875606536865</v>
+        <v>24.0875625610352</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G890" t="n">
-        <v>23.6674308776855</v>
+        <v>23.6674289703369</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G891" t="n">
-        <v>24.5543727874756</v>
+        <v>24.5543746948242</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G892" t="n">
-        <v>24.5076923370361</v>
+        <v>24.5076904296875</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G893" t="n">
-        <v>24.3676509857178</v>
+        <v>24.3676490783691</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G895" t="n">
-        <v>24.6010570526123</v>
+        <v>24.6010551452637</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G896" t="n">
-        <v>24.3676509857178</v>
+        <v>24.3676490783691</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G897" t="n">
-        <v>22.8738479614258</v>
+        <v>22.8738460540771</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G898" t="n">
-        <v>22.8738479614258</v>
+        <v>22.8738460540771</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G902" t="n">
-        <v>23.8541564941406</v>
+        <v>23.854154586792</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G903" t="n">
-        <v>23.8074741363525</v>
+        <v>23.8074722290039</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G905" t="n">
-        <v>24.8344631195068</v>
+        <v>24.8344593048096</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G908" t="n">
-        <v>23.8541564941406</v>
+        <v>23.854154586792</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G909" t="n">
-        <v>23.8074741363525</v>
+        <v>23.8074722290039</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G910" t="n">
-        <v>23.714111328125</v>
+        <v>23.7141094207764</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G911" t="n">
-        <v>23.4807033538818</v>
+        <v>23.4807014465332</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>26.0228881835938</v>
       </c>
       <c r="G913" t="n">
-        <v>25.0211868286133</v>
+        <v>25.0211849212646</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G914" t="n">
-        <v>24.9745063781738</v>
+        <v>24.9745044708252</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>25.0518856048584</v>
       </c>
       <c r="G915" t="n">
-        <v>24.0875606536865</v>
+        <v>24.0875625610352</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G916" t="n">
-        <v>23.4807033538818</v>
+        <v>23.4807014465332</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G918" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406620025635</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G919" t="n">
-        <v>23.4340229034424</v>
+        <v>23.4340209960938</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G920" t="n">
-        <v>22.780481338501</v>
+        <v>22.7804832458496</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G921" t="n">
-        <v>21.3800449371338</v>
+        <v>21.3800430297852</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G923" t="n">
-        <v>21.2866802215576</v>
+        <v>21.2866840362549</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G924" t="n">
-        <v>20.7731838226318</v>
+        <v>20.7731857299805</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G927" t="n">
-        <v>21.146635055542</v>
+        <v>21.1466388702393</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G929" t="n">
-        <v>21.146635055542</v>
+        <v>21.1466388702393</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G931" t="n">
-        <v>20.7265071868896</v>
+        <v>20.726505279541</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G935" t="n">
-        <v>21.3800449371338</v>
+        <v>21.3800430297852</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G936" t="n">
-        <v>21.2400016784668</v>
+        <v>21.2399997711182</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G937" t="n">
-        <v>21.7068119049072</v>
+        <v>21.7068138122559</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G938" t="n">
-        <v>21.146635055542</v>
+        <v>21.1466388702393</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G941" t="n">
-        <v>20.1196460723877</v>
+        <v>20.1196479797363</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>19.1870250701904</v>
       </c>
       <c r="G944" t="n">
-        <v>18.4484577178955</v>
+        <v>18.4484596252441</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G946" t="n">
-        <v>20.5397796630859</v>
+        <v>20.5397815704346</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>20.0026683807373</v>
       </c>
       <c r="G948" t="n">
-        <v>19.2327041625977</v>
+        <v>19.232702255249</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G949" t="n">
-        <v>18.0936794281006</v>
+        <v>18.0936813354492</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>17.9053001403809</v>
       </c>
       <c r="G950" t="n">
-        <v>17.2160701751709</v>
+        <v>17.2160682678223</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G951" t="n">
-        <v>16.9359817504883</v>
+        <v>16.9359836578369</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G952" t="n">
-        <v>16.7119121551514</v>
+        <v>16.7119102478027</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G955" t="n">
-        <v>18.5418186187744</v>
+        <v>18.5418224334717</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G956" t="n">
-        <v>19.7928771972656</v>
+        <v>19.7928791046143</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G957" t="n">
-        <v>19.4194297790527</v>
+        <v>19.4194278717041</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G960" t="n">
-        <v>20.5397796630859</v>
+        <v>20.5397815704346</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G961" t="n">
-        <v>20.7731838226318</v>
+        <v>20.7731857299805</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G963" t="n">
-        <v>21.7068119049072</v>
+        <v>21.7068138122559</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G964" t="n">
-        <v>21.5200862884521</v>
+        <v>21.5200901031494</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>22.7214775085449</v>
       </c>
       <c r="G965" t="n">
-        <v>21.8468589782715</v>
+        <v>21.8468570709229</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G968" t="n">
-        <v>23.0138931274414</v>
+        <v>23.0138912200928</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G969" t="n">
-        <v>21.7068119049072</v>
+        <v>21.7068138122559</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G971" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530521392822</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G972" t="n">
-        <v>20.1663303375244</v>
+        <v>20.166332244873</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G973" t="n">
-        <v>20.2596950531006</v>
+        <v>20.2596912384033</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G974" t="n">
-        <v>20.4464168548584</v>
+        <v>20.4464206695557</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G975" t="n">
-        <v>20.2596950531006</v>
+        <v>20.2596912384033</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G976" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530521392822</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G977" t="n">
-        <v>20.1663303375244</v>
+        <v>20.166332244873</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G979" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530521392822</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G980" t="n">
-        <v>20.4464168548584</v>
+        <v>20.4464206695557</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G984" t="n">
-        <v>21.5200862884521</v>
+        <v>21.5200901031494</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G986" t="n">
-        <v>21.3800449371338</v>
+        <v>21.3800430297852</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G988" t="n">
-        <v>21.5200862884521</v>
+        <v>21.5200901031494</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G990" t="n">
-        <v>21.8001747131348</v>
+        <v>21.8001766204834</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G993" t="n">
-        <v>19.8862438201904</v>
+        <v>19.8862419128418</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>19.3229656219482</v>
       </c>
       <c r="G995" t="n">
-        <v>18.5791645050049</v>
+        <v>18.5791664123535</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G996" t="n">
-        <v>18.9526138305664</v>
+        <v>18.952615737915</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>22.6243762969971</v>
       </c>
       <c r="G998" t="n">
-        <v>21.7534961700439</v>
+        <v>21.7534942626953</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1000" t="n">
-        <v>20.5397796630859</v>
+        <v>20.5397815704346</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1002" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530521392822</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G1003" t="n">
-        <v>19.5127925872803</v>
+        <v>19.5127906799316</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1004" t="n">
-        <v>20.4464168548584</v>
+        <v>20.4464206695557</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G1007" t="n">
-        <v>20.2596950531006</v>
+        <v>20.2596912384033</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1012" t="n">
-        <v>20.5397796630859</v>
+        <v>20.5397815704346</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G1014" t="n">
-        <v>20.2596950531006</v>
+        <v>20.2596912384033</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1015" t="n">
-        <v>20.5397796630859</v>
+        <v>20.5397815704346</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1018" t="n">
-        <v>18.8125705718994</v>
+        <v>18.812572479248</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>18.5655822753906</v>
       </c>
       <c r="G1020" t="n">
-        <v>17.8509349822998</v>
+        <v>17.8509368896484</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.0853652954102</v>
+        <v>17.0853633880615</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G1026" t="n">
-        <v>16.7935485839844</v>
+        <v>16.7935466766357</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>16.6624164581299</v>
       </c>
       <c r="G1028" t="n">
-        <v>16.153434753418</v>
+        <v>16.1534328460693</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G1033" t="n">
-        <v>17.6972370147705</v>
+        <v>17.6972351074219</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1034" t="n">
-        <v>18.1490802764893</v>
+        <v>18.1490821838379</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G1037" t="n">
-        <v>18.826847076416</v>
+        <v>18.8268489837646</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G1040" t="n">
-        <v>18.6574058532715</v>
+        <v>18.6574077606201</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>18.3908023834229</v>
       </c>
       <c r="G1042" t="n">
-        <v>17.8290233612061</v>
+        <v>17.8290252685547</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>18.8763046264648</v>
       </c>
       <c r="G1043" t="n">
-        <v>18.2996959686279</v>
+        <v>18.2996940612793</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G1047" t="n">
-        <v>19.7211246490479</v>
+        <v>19.7211227416992</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1048" t="n">
-        <v>20.050594329834</v>
+        <v>20.0505924224854</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1049" t="n">
-        <v>20.6153964996338</v>
+        <v>20.6153984069824</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1050" t="n">
-        <v>20.7095336914062</v>
+        <v>20.7095317840576</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G1053" t="n">
-        <v>20.8978004455566</v>
+        <v>20.897798538208</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1055" t="n">
-        <v>20.050594329834</v>
+        <v>20.0505924224854</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1056" t="n">
-        <v>20.1447257995605</v>
+        <v>20.1447277069092</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>22.6243762969971</v>
       </c>
       <c r="G1057" t="n">
-        <v>21.933277130127</v>
+        <v>21.9332790374756</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1058" t="n">
-        <v>22.5451507568359</v>
+        <v>22.5451469421387</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1059" t="n">
-        <v>22.5451507568359</v>
+        <v>22.5451469421387</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G1065" t="n">
-        <v>21.321403503418</v>
+        <v>21.3214054107666</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1068" t="n">
-        <v>20.7095336914062</v>
+        <v>20.7095317840576</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1071" t="n">
-        <v>20.6624641418457</v>
+        <v>20.6624660491943</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G1072" t="n">
-        <v>20.285924911499</v>
+        <v>20.2859268188477</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1073" t="n">
-        <v>20.1447257995605</v>
+        <v>20.1447277069092</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1074" t="n">
-        <v>20.1447257995605</v>
+        <v>20.1447277069092</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1075" t="n">
-        <v>20.1447257995605</v>
+        <v>20.1447277069092</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1079" t="n">
-        <v>19.5799217224121</v>
+        <v>19.5799198150635</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G1080" t="n">
-        <v>19.1092510223389</v>
+        <v>19.1092491149902</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>20.245418548584</v>
       </c>
       <c r="G1083" t="n">
-        <v>19.6269855499268</v>
+        <v>19.6269874572754</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G1085" t="n">
-        <v>18.8739128112793</v>
+        <v>18.8739147186279</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1086" t="n">
-        <v>18.9209804534912</v>
+        <v>18.9209823608398</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G1089" t="n">
-        <v>17.8101997375488</v>
+        <v>17.8101978302002</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G1091" t="n">
-        <v>17.6031017303467</v>
+        <v>17.6031036376953</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G1092" t="n">
-        <v>18.2620410919189</v>
+        <v>18.2620391845703</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>18.2354412078857</v>
       </c>
       <c r="G1095" t="n">
-        <v>17.678409576416</v>
+        <v>17.6784076690674</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G1096" t="n">
-        <v>16.8876800537109</v>
+        <v>16.8876819610596</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1098" t="n">
-        <v>18.9680480957031</v>
+        <v>18.9680500030518</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G1099" t="n">
-        <v>19.9564552307129</v>
+        <v>19.9564571380615</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1100" t="n">
-        <v>18.9680480957031</v>
+        <v>18.9680500030518</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G1101" t="n">
-        <v>18.676233291626</v>
+        <v>18.6762313842773</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>18.9734058380127</v>
       </c>
       <c r="G1104" t="n">
-        <v>18.3938312530518</v>
+        <v>18.3938293457031</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G1107" t="n">
-        <v>17.9419822692871</v>
+        <v>17.9419841766357</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1108" t="n">
-        <v>18.1490802764893</v>
+        <v>18.1490821838379</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1110" t="n">
-        <v>18.1490802764893</v>
+        <v>18.1490821838379</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>18.6626834869385</v>
       </c>
       <c r="G1111" t="n">
-        <v>18.0925998687744</v>
+        <v>18.0925979614258</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1113" t="n">
-        <v>18.9209804534912</v>
+        <v>18.9209823608398</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1115" t="n">
-        <v>20.4741954803467</v>
+        <v>20.4741973876953</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1121" t="n">
-        <v>20.050594329834</v>
+        <v>20.0505924224854</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1122" t="n">
-        <v>20.4741954803467</v>
+        <v>20.4741973876953</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1123" t="n">
-        <v>20.6153964996338</v>
+        <v>20.6153984069824</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1124" t="n">
-        <v>20.7095336914062</v>
+        <v>20.7095317840576</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1125" t="n">
-        <v>20.6153964996338</v>
+        <v>20.6153984069824</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1132" t="n">
-        <v>23.2511558532715</v>
+        <v>23.2511577606201</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1134" t="n">
-        <v>23.2511558532715</v>
+        <v>23.2511577606201</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1135" t="n">
-        <v>23.5335597991943</v>
+        <v>23.533561706543</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1138" t="n">
-        <v>22.5451507568359</v>
+        <v>22.5451469421387</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1139" t="n">
-        <v>21.9803428649902</v>
+        <v>21.9803447723389</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>23.4497299194336</v>
       </c>
       <c r="G1141" t="n">
-        <v>22.733419418335</v>
+        <v>22.7334175109863</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>23.3526306152344</v>
       </c>
       <c r="G1142" t="n">
-        <v>22.6392822265625</v>
+        <v>22.6392860412598</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1144" t="n">
-        <v>21.9803428649902</v>
+        <v>21.9803447723389</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>22.7214775085449</v>
       </c>
       <c r="G1145" t="n">
-        <v>22.0274105072021</v>
+        <v>22.0274124145508</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1147" t="n">
-        <v>23.5335597991943</v>
+        <v>23.533561706543</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1148" t="n">
-        <v>23.2982215881348</v>
+        <v>23.2982234954834</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1149" t="n">
-        <v>24.192497253418</v>
+        <v>24.1924991607666</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1151" t="n">
-        <v>23.2982215881348</v>
+        <v>23.2982234954834</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1156" t="n">
-        <v>22.4039497375488</v>
+        <v>22.4039478302002</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1159" t="n">
-        <v>21.9803428649902</v>
+        <v>21.9803447723389</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1163" t="n">
-        <v>21.9803428649902</v>
+        <v>21.9803447723389</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1166" t="n">
-        <v>21.6508731842041</v>
+        <v>21.6508750915527</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G1169" t="n">
-        <v>21.4155387878418</v>
+        <v>21.4155368804932</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G1170" t="n">
-        <v>21.2272701263428</v>
+        <v>21.2272720336914</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1173" t="n">
-        <v>21.6508731842041</v>
+        <v>21.6508750915527</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1175" t="n">
-        <v>21.6508731842041</v>
+        <v>21.6508750915527</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1179" t="n">
-        <v>22.5451507568359</v>
+        <v>22.5451469421387</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.9803428649902</v>
+        <v>21.9803447723389</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1185" t="n">
-        <v>23.3452892303467</v>
+        <v>23.3452911376953</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G1187" t="n">
-        <v>24.5219669342041</v>
+        <v>24.5219688415527</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1190" t="n">
-        <v>24.0983638763428</v>
+        <v>24.0983619689941</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1191" t="n">
-        <v>23.9100971221924</v>
+        <v>23.9100952148438</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>25.9257888793945</v>
       </c>
       <c r="G1192" t="n">
-        <v>25.1338405609131</v>
+        <v>25.1338424682617</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1194" t="n">
-        <v>24.6631679534912</v>
+        <v>24.6631698608398</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1201" t="n">
-        <v>25.557445526123</v>
+        <v>25.5574436187744</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1205" t="n">
-        <v>24.192497253418</v>
+        <v>24.1924991607666</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>25.9257888793945</v>
       </c>
       <c r="G1207" t="n">
-        <v>25.1338405609131</v>
+        <v>25.1338424682617</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>26.1685390472412</v>
       </c>
       <c r="G1208" t="n">
-        <v>25.369176864624</v>
+        <v>25.3691749572754</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>26.4112892150879</v>
       </c>
       <c r="G1209" t="n">
-        <v>25.6045093536377</v>
+        <v>25.6045112609863</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G1210" t="n">
-        <v>25.180908203125</v>
+        <v>25.1809062957764</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1211" t="n">
-        <v>23.9100971221924</v>
+        <v>23.9100952148438</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1213" t="n">
-        <v>23.9100971221924</v>
+        <v>23.9100952148438</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1215" t="n">
-        <v>23.3923587799072</v>
+        <v>23.3923568725586</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1217" t="n">
-        <v>22.9687519073486</v>
+        <v>22.9687538146973</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1218" t="n">
-        <v>23.1099529266357</v>
+        <v>23.1099548339844</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1220" t="n">
-        <v>23.0628890991211</v>
+        <v>23.0628871917725</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1222" t="n">
-        <v>22.4039497375488</v>
+        <v>22.4039478302002</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1223" t="n">
-        <v>23.3452892303467</v>
+        <v>23.3452911376953</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1226" t="n">
-        <v>23.7218284606934</v>
+        <v>23.7218265533447</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1229" t="n">
-        <v>23.1099529266357</v>
+        <v>23.1099548339844</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1230" t="n">
-        <v>23.2982215881348</v>
+        <v>23.2982234954834</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1231" t="n">
-        <v>23.0628890991211</v>
+        <v>23.0628871917725</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1233" t="n">
-        <v>23.1099529266357</v>
+        <v>23.1099548339844</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1235" t="n">
-        <v>23.0628890991211</v>
+        <v>23.0628871917725</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1240" t="n">
-        <v>21.9803428649902</v>
+        <v>21.9803447723389</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G1241" t="n">
-        <v>21.321403503418</v>
+        <v>21.3214054107666</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G1243" t="n">
-        <v>22.498083114624</v>
+        <v>22.4980812072754</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1244" t="n">
-        <v>22.4039497375488</v>
+        <v>22.4039478302002</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1245" t="n">
-        <v>22.4039497375488</v>
+        <v>22.4039478302002</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>22.915678024292</v>
       </c>
       <c r="G1246" t="n">
-        <v>22.2156791687012</v>
+        <v>22.2156772613525</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G1248" t="n">
-        <v>22.498083114624</v>
+        <v>22.4980812072754</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1249" t="n">
-        <v>23.2511558532715</v>
+        <v>23.2511577606201</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1250" t="n">
-        <v>23.5335597991943</v>
+        <v>23.533561706543</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1252" t="n">
-        <v>23.3923587799072</v>
+        <v>23.3923568725586</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1254" t="n">
-        <v>22.9687519073486</v>
+        <v>22.9687538146973</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1257" t="n">
-        <v>22.9687519073486</v>
+        <v>22.9687538146973</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1258" t="n">
-        <v>23.0628890991211</v>
+        <v>23.0628871917725</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1263" t="n">
-        <v>23.7218284606934</v>
+        <v>23.7218265533447</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1265" t="n">
-        <v>23.2982215881348</v>
+        <v>23.2982234954834</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>26.8482418060303</v>
       </c>
       <c r="G1272" t="n">
-        <v>26.0281162261963</v>
+        <v>26.0281181335449</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>27.1880931854248</v>
       </c>
       <c r="G1275" t="n">
-        <v>26.3575859069824</v>
+        <v>26.3575878143311</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>27.1880931854248</v>
       </c>
       <c r="G1276" t="n">
-        <v>26.3575859069824</v>
+        <v>26.3575878143311</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>27.1880931854248</v>
       </c>
       <c r="G1277" t="n">
-        <v>26.3575859069824</v>
+        <v>26.3575878143311</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>27.3337421417236</v>
       </c>
       <c r="G1278" t="n">
-        <v>26.4987869262695</v>
+        <v>26.4987850189209</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>26.071439743042</v>
       </c>
       <c r="G1284" t="n">
-        <v>25.4376983642578</v>
+        <v>25.4377002716064</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>26.5569400787354</v>
       </c>
       <c r="G1287" t="n">
-        <v>25.91139793396</v>
+        <v>25.9113998413086</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>26.6054916381836</v>
       </c>
       <c r="G1290" t="n">
-        <v>25.9587688446045</v>
+        <v>25.9587707519531</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>26.4112892150879</v>
       </c>
       <c r="G1293" t="n">
-        <v>25.769287109375</v>
+        <v>25.7692890167236</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>25.7315883636475</v>
       </c>
       <c r="G1298" t="n">
-        <v>25.106107711792</v>
+        <v>25.1061096191406</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1300" t="n">
-        <v>24.8218879699707</v>
+        <v>24.8218898773193</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>25.1489868164062</v>
       </c>
       <c r="G1304" t="n">
-        <v>24.5376720428467</v>
+        <v>24.537670135498</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>25.1489868164062</v>
       </c>
       <c r="G1308" t="n">
-        <v>24.5376720428467</v>
+        <v>24.537670135498</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1311" t="n">
-        <v>24.8218879699707</v>
+        <v>24.8218898773193</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1315" t="n">
-        <v>23.7323799133301</v>
+        <v>23.7323780059814</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1317" t="n">
-        <v>24.0639705657959</v>
+        <v>24.0639686584473</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1322" t="n">
-        <v>23.7323799133301</v>
+        <v>23.7323780059814</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1330" t="n">
-        <v>23.7323799133301</v>
+        <v>23.7323780059814</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1331" t="n">
-        <v>24.5850391387939</v>
+        <v>24.5850410461426</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1332" t="n">
-        <v>24.8218879699707</v>
+        <v>24.8218898773193</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1337" t="n">
-        <v>23.4955272674561</v>
+        <v>23.4955291748047</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1339" t="n">
-        <v>23.0691986083984</v>
+        <v>23.0691967010498</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1340" t="n">
-        <v>23.0691986083984</v>
+        <v>23.0691967010498</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1341" t="n">
-        <v>23.0691986083984</v>
+        <v>23.0691967010498</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1353" t="n">
-        <v>20.842809677124</v>
+        <v>20.8428077697754</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1356" t="n">
-        <v>20.7006950378418</v>
+        <v>20.7006969451904</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1357" t="n">
-        <v>20.748067855835</v>
+        <v>20.7480697631836</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1359" t="n">
-        <v>20.7006950378418</v>
+        <v>20.7006969451904</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1362" t="n">
-        <v>20.748067855835</v>
+        <v>20.7480697631836</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G1365" t="n">
-        <v>18.8153705596924</v>
+        <v>18.815372467041</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>18.8763046264648</v>
       </c>
       <c r="G1368" t="n">
-        <v>18.4174633026123</v>
+        <v>18.4174613952637</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>18.8568840026855</v>
       </c>
       <c r="G1369" t="n">
-        <v>18.3985137939453</v>
+        <v>18.3985157012939</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G1371" t="n">
-        <v>17.6405963897705</v>
+        <v>17.6405944824219</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>19.1093444824219</v>
       </c>
       <c r="G1374" t="n">
-        <v>18.6448364257812</v>
+        <v>18.6448383331299</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>19.1870250701904</v>
       </c>
       <c r="G1375" t="n">
-        <v>18.7206287384033</v>
+        <v>18.720630645752</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G1377" t="n">
-        <v>20.0848846435547</v>
+        <v>20.0848865509033</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1378" t="n">
-        <v>19.7059268951416</v>
+        <v>19.705924987793</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1382" t="n">
-        <v>20.7006950378418</v>
+        <v>20.7006969451904</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1383" t="n">
-        <v>20.842809677124</v>
+        <v>20.8428077697754</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G1385" t="n">
-        <v>21.6480960845947</v>
+        <v>21.6480979919434</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1392" t="n">
-        <v>20.4407501220703</v>
+        <v>20.4407520294189</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1396" t="n">
-        <v>22.7336273193359</v>
+        <v>22.7336254119873</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1402" t="n">
-        <v>21.6603679656982</v>
+        <v>21.6603660583496</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1410" t="n">
-        <v>24.2459506988525</v>
+        <v>24.2459526062012</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1412" t="n">
-        <v>23.709321975708</v>
+        <v>23.7093200683594</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G1413" t="n">
-        <v>24.5386581420898</v>
+        <v>24.5386562347412</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1417" t="n">
-        <v>22.7336273193359</v>
+        <v>22.7336254119873</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1418" t="n">
-        <v>22.7336273193359</v>
+        <v>22.7336254119873</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>23.25</v>
       </c>
       <c r="G1420" t="n">
-        <v>22.6848430633545</v>
+        <v>22.6848449707031</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1422" t="n">
-        <v>22.3921375274658</v>
+        <v>22.3921356201172</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1428" t="n">
-        <v>22.2945671081543</v>
+        <v>22.2945652008057</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>21.6603679656982</v>
+        <v>21.6603660583496</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1430" t="n">
-        <v>21.5627956390381</v>
+        <v>21.5627975463867</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1432" t="n">
-        <v>22.1482124328613</v>
+        <v>22.14821434021</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1438" t="n">
-        <v>22.2945671081543</v>
+        <v>22.2945652008057</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1441" t="n">
-        <v>21.5627956390381</v>
+        <v>21.5627975463867</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1447" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1448" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1449" t="n">
-        <v>22.2945671081543</v>
+        <v>22.2945652008057</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1451" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1452" t="n">
-        <v>21.6603679656982</v>
+        <v>21.6603660583496</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1453" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1454" t="n">
-        <v>21.6603679656982</v>
+        <v>21.6603660583496</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>22</v>
       </c>
       <c r="G1456" t="n">
-        <v>21.4652290344238</v>
+        <v>21.4652271270752</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1460" t="n">
-        <v>21.3676586151123</v>
+        <v>21.3676605224609</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1466" t="n">
-        <v>19.2016220092773</v>
+        <v>19.201623916626</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1467" t="n">
-        <v>18.8113460540771</v>
+        <v>18.8113441467285</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>18.8308601379395</v>
+        <v>18.8308582305908</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1470" t="n">
-        <v>19.0650253295898</v>
+        <v>19.0650272369385</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1472" t="n">
-        <v>18.9869709014893</v>
+        <v>18.9869689941406</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1475" t="n">
-        <v>20.0504722595215</v>
+        <v>20.0504760742188</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1480" t="n">
-        <v>20.4407501220703</v>
+        <v>20.4407520294189</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1481" t="n">
-        <v>19.5626277923584</v>
+        <v>19.5626258850098</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1483" t="n">
-        <v>19.5626277923584</v>
+        <v>19.5626258850098</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1486" t="n">
-        <v>19.240650177002</v>
+        <v>19.2406482696533</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1487" t="n">
-        <v>18.8308601379395</v>
+        <v>18.8308582305908</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1498" t="n">
-        <v>18.8113460540771</v>
+        <v>18.8113441467285</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1499" t="n">
-        <v>18.5576648712158</v>
+        <v>18.5576667785645</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1502" t="n">
-        <v>18.5576648712158</v>
+        <v>18.5576667785645</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1503" t="n">
-        <v>18.7528038024902</v>
+        <v>18.7528018951416</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1505" t="n">
-        <v>17.308780670166</v>
+        <v>17.3087787628174</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1506" t="n">
-        <v>18.1673889160156</v>
+        <v>18.1673908233643</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1507" t="n">
-        <v>18.1283626556396</v>
+        <v>18.128360748291</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1508" t="n">
-        <v>16.6453094482422</v>
+        <v>16.6453075408936</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1509" t="n">
-        <v>18.36252784729</v>
+        <v>18.3625259399414</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1512" t="n">
-        <v>18.0112762451172</v>
+        <v>18.0112781524658</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1515" t="n">
-        <v>17.2112102508545</v>
+        <v>17.2112083435059</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1523" t="n">
-        <v>16.9965572357178</v>
+        <v>16.9965591430664</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>18</v>
       </c>
       <c r="G1529" t="n">
-        <v>17.5624580383301</v>
+        <v>17.5624599456787</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1533" t="n">
-        <v>16.8209342956543</v>
+        <v>16.8209323883057</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1534" t="n">
-        <v>16.5087108612061</v>
+        <v>16.5087127685547</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1535" t="n">
-        <v>17.308780670166</v>
+        <v>17.3087787628174</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1542" t="n">
-        <v>16.8280143737793</v>
+        <v>16.8280124664307</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>16.5715484619141</v>
+        <v>16.5715465545654</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1546" t="n">
-        <v>17.3803977966309</v>
+        <v>17.3803997039795</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1547" t="n">
-        <v>17.4987678527832</v>
+        <v>17.4987659454346</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1553" t="n">
-        <v>17.0844764709473</v>
+        <v>17.0844783782959</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1554" t="n">
-        <v>17.5974063873291</v>
+        <v>17.5974082946777</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1557" t="n">
-        <v>17.3212127685547</v>
+        <v>17.3212146759033</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1562" t="n">
-        <v>16.5715484619141</v>
+        <v>16.5715465545654</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1563" t="n">
-        <v>16.6307315826416</v>
+        <v>16.6307334899902</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1564" t="n">
-        <v>16.8280143737793</v>
+        <v>16.8280124664307</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1567" t="n">
-        <v>15.5654182434082</v>
+        <v>15.5654191970825</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="n">
-        <v>15.6837863922119</v>
+        <v>15.6837873458862</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>16.5</v>
       </c>
       <c r="G1570" t="n">
-        <v>16.2756290435791</v>
+        <v>16.2756271362305</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1571" t="n">
-        <v>16.2361717224121</v>
+        <v>16.2361698150635</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1572" t="n">
-        <v>15.9205236434937</v>
+        <v>15.920521736145</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1573" t="n">
-        <v>16.0191631317139</v>
+        <v>16.0191650390625</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>16.3742694854736</v>
+        <v>16.374267578125</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1575" t="n">
-        <v>16.867467880249</v>
+        <v>16.8674697875977</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1578" t="n">
-        <v>17.4593105316162</v>
+        <v>17.4593124389648</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1579" t="n">
-        <v>17.1042041778564</v>
+        <v>17.1042060852051</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1583" t="n">
-        <v>17.5579490661621</v>
+        <v>17.5579509735107</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1588" t="n">
-        <v>16.867467880249</v>
+        <v>16.8674697875977</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1590" t="n">
-        <v>16.7491016387939</v>
+        <v>16.7490997314453</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1594" t="n">
-        <v>16.9858379364014</v>
+        <v>16.9858360290527</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1595" t="n">
-        <v>17.5579490661621</v>
+        <v>17.5579509735107</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1596" t="n">
-        <v>17.8144149780273</v>
+        <v>17.8144130706787</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1605" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1609" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1612" t="n">
-        <v>19.1361923217773</v>
+        <v>19.136194229126</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1613" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1615" t="n">
-        <v>18.761360168457</v>
+        <v>18.7613620758057</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1618" t="n">
-        <v>19.1361923217773</v>
+        <v>19.136194229126</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1621" t="n">
-        <v>19.4518413543701</v>
+        <v>19.4518394470215</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1622" t="n">
-        <v>19.0770072937012</v>
+        <v>19.0770092010498</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1630" t="n">
-        <v>18.5640811920166</v>
+        <v>18.564079284668</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1634" t="n">
-        <v>18.0511512756348</v>
+        <v>18.0511493682861</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1635" t="n">
-        <v>16.9858379364014</v>
+        <v>16.9858360290527</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1636" t="n">
-        <v>17.5974063873291</v>
+        <v>17.5974082946777</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1644" t="n">
-        <v>17.3803977966309</v>
+        <v>17.3803997039795</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1645" t="n">
-        <v>17.9130554199219</v>
+        <v>17.9130535125732</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1652" t="n">
-        <v>18.4457111358643</v>
+        <v>18.4457130432129</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1655" t="n">
-        <v>18.4457111358643</v>
+        <v>18.4457130432129</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1656" t="n">
-        <v>18.800817489624</v>
+        <v>18.8008155822754</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>19.294017791748</v>
+        <v>19.2940158843994</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1659" t="n">
-        <v>19.0770072937012</v>
+        <v>19.0770092010498</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1662" t="n">
-        <v>17.9130554199219</v>
+        <v>17.9130535125732</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1665" t="n">
-        <v>17.9525127410889</v>
+        <v>17.9525108337402</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1677" t="n">
-        <v>17.6171340942383</v>
+        <v>17.6171360015869</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1680" t="n">
-        <v>18.800817489624</v>
+        <v>18.8008155822754</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1681" t="n">
-        <v>18.8600006103516</v>
+        <v>18.8600025177002</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1682" t="n">
-        <v>18.8600006103516</v>
+        <v>18.8600025177002</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1684" t="n">
-        <v>18.8600006103516</v>
+        <v>18.8600025177002</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1685" t="n">
-        <v>19.1361923217773</v>
+        <v>19.136194229126</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1691" t="n">
-        <v>19.1559200286865</v>
+        <v>19.1559219360352</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1692" t="n">
-        <v>19.4912986755371</v>
+        <v>19.4912967681885</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1693" t="n">
-        <v>19.1559200286865</v>
+        <v>19.1559219360352</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1699" t="n">
-        <v>21.0103569030762</v>
+        <v>21.0103549957275</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>21</v>
       </c>
       <c r="G1705" t="n">
-        <v>20.7144355773926</v>
+        <v>20.7144374847412</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>20.75</v>
       </c>
       <c r="G1706" t="n">
-        <v>20.4678344726562</v>
+        <v>20.4678363800049</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1712" t="n">
-        <v>18.800817489624</v>
+        <v>18.8008155822754</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1715" t="n">
-        <v>20.6651153564453</v>
+        <v>20.6651172637939</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1717" t="n">
-        <v>19.3926582336426</v>
+        <v>19.3926563262939</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>20</v>
       </c>
       <c r="G1718" t="n">
-        <v>19.7280349731445</v>
+        <v>19.7280330657959</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1720" t="n">
-        <v>17.8933277130127</v>
+        <v>17.8933258056641</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1724" t="n">
-        <v>18.761360168457</v>
+        <v>18.7613620758057</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1729" t="n">
-        <v>17.3014850616455</v>
+        <v>17.3014869689941</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1731" t="n">
-        <v>16.6307315826416</v>
+        <v>16.6307334899902</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1732" t="n">
-        <v>16.5123653411865</v>
+        <v>16.5123634338379</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>16.5</v>
       </c>
       <c r="G1734" t="n">
-        <v>16.2756290435791</v>
+        <v>16.2756271362305</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>15</v>
       </c>
       <c r="G1736" t="n">
-        <v>14.7960252761841</v>
+        <v>14.7960262298584</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1740" t="n">
-        <v>15.6837863922119</v>
+        <v>15.6837873458862</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1742" t="n">
-        <v>16.6307315826416</v>
+        <v>16.6307334899902</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1743" t="n">
-        <v>16.3742694854736</v>
+        <v>16.374267578125</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1747" t="n">
-        <v>16.9858379364014</v>
+        <v>16.9858360290527</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1748" t="n">
-        <v>17.1042041778564</v>
+        <v>17.1042060852051</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1758" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1759" t="n">
-        <v>20.1719169616699</v>
+        <v>20.1719150543213</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1761" t="n">
-        <v>19.3926582336426</v>
+        <v>19.3926563262939</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>21</v>
       </c>
       <c r="G1763" t="n">
-        <v>20.7144355773926</v>
+        <v>20.7144374847412</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>20.75</v>
       </c>
       <c r="G1764" t="n">
-        <v>20.4678344726562</v>
+        <v>20.4678363800049</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1766" t="n">
-        <v>20.6157970428467</v>
+        <v>20.615795135498</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1767" t="n">
-        <v>20.1719169616699</v>
+        <v>20.1719150543213</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1768" t="n">
-        <v>20.6157970428467</v>
+        <v>20.615795135498</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1772" t="n">
-        <v>20.418514251709</v>
+        <v>20.4185161590576</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>20.75</v>
       </c>
       <c r="G1773" t="n">
-        <v>20.4678344726562</v>
+        <v>20.4678363800049</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1784" t="n">
-        <v>22.2433567047119</v>
+        <v>22.2433586120605</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1785" t="n">
-        <v>22.3419990539551</v>
+        <v>22.3419971466064</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -55102,6 +55102,32 @@
         <v>28.6499996185303</v>
       </c>
       <c r="H2105" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2106" t="n">
+        <v>102351</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>29.0499992370605</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>28.2999992370605</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>28.6499996185303</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>28.7999992370605</v>
+      </c>
+      <c r="G2106" t="n">
+        <v>28.7999992370605</v>
+      </c>
+      <c r="H2106" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G2" t="n">
-        <v>7.53173208236694</v>
+        <v>7.5317325592041</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G3" t="n">
-        <v>7.85125970840454</v>
+        <v>7.85125923156738</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G4" t="n">
-        <v>7.75996541976929</v>
+        <v>7.75996589660645</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G5" t="n">
-        <v>7.75996541976929</v>
+        <v>7.75996589660645</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>8.1253547668457</v>
       </c>
       <c r="G7" t="n">
-        <v>7.63945770263672</v>
+        <v>7.63945817947388</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.31955623626709</v>
       </c>
       <c r="G8" t="n">
-        <v>7.82204532623291</v>
+        <v>7.82204580307007</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.41859817504883</v>
       </c>
       <c r="G9" t="n">
-        <v>7.91516494750977</v>
+        <v>7.91516590118408</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>8.42830753326416</v>
       </c>
       <c r="G11" t="n">
-        <v>7.92429447174072</v>
+        <v>7.92429351806641</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G12" t="n">
-        <v>7.53173208236694</v>
+        <v>7.5317325592041</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G13" t="n">
-        <v>7.53173208236694</v>
+        <v>7.5317325592041</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>7.71656322479248</v>
       </c>
       <c r="G15" t="n">
-        <v>7.2551121711731</v>
+        <v>7.25511264801025</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>7.88940191268921</v>
       </c>
       <c r="G17" t="n">
-        <v>7.41761445999146</v>
+        <v>7.41761541366577</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.00106716156006</v>
       </c>
       <c r="G18" t="n">
-        <v>7.5226035118103</v>
+        <v>7.52260303497314</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>7.8651270866394</v>
       </c>
       <c r="G19" t="n">
-        <v>7.39479160308838</v>
+        <v>7.39479303359985</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>7.97193717956543</v>
       </c>
       <c r="G21" t="n">
-        <v>7.49521493911743</v>
+        <v>7.49521446228027</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.45743942260742</v>
       </c>
       <c r="G28" t="n">
-        <v>7.95168495178223</v>
+        <v>7.95168399810791</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>8.31178760528564</v>
       </c>
       <c r="G29" t="n">
-        <v>7.81474208831787</v>
+        <v>7.81474256515503</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.47394561767578</v>
       </c>
       <c r="G30" t="n">
-        <v>7.96720314025879</v>
+        <v>7.96720266342163</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G31" t="n">
-        <v>7.85125970840454</v>
+        <v>7.85125923156738</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.20497798919678</v>
       </c>
       <c r="G33" t="n">
-        <v>7.71431970596313</v>
+        <v>7.71432113647461</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>8.31178760528564</v>
       </c>
       <c r="G37" t="n">
-        <v>7.81474208831787</v>
+        <v>7.81474256515503</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G39" t="n">
-        <v>7.85125970840454</v>
+        <v>7.85125923156738</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.29625225067139</v>
       </c>
       <c r="G40" t="n">
-        <v>7.80013656616211</v>
+        <v>7.80013561248779</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.23410797119141</v>
       </c>
       <c r="G42" t="n">
-        <v>7.74170827865601</v>
+        <v>7.74170732498169</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>8.1855583190918</v>
       </c>
       <c r="G43" t="n">
-        <v>7.69606161117554</v>
+        <v>7.6960620880127</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G45" t="n">
-        <v>7.85125970840454</v>
+        <v>7.85125923156738</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>8.33606338500977</v>
       </c>
       <c r="G46" t="n">
-        <v>7.83756685256958</v>
+        <v>7.83756589889526</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.99232816696167</v>
       </c>
       <c r="G47" t="n">
-        <v>7.51438665390015</v>
+        <v>7.51438617706299</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>8.10787677764893</v>
       </c>
       <c r="G48" t="n">
-        <v>7.62302684783936</v>
+        <v>7.62302541732788</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>8.22634029388428</v>
       </c>
       <c r="G49" t="n">
-        <v>7.73440551757812</v>
+        <v>7.73440504074097</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>8.1875</v>
       </c>
       <c r="G50" t="n">
-        <v>7.69788789749146</v>
+        <v>7.69788837432861</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>8.44772911071777</v>
       </c>
       <c r="G51" t="n">
-        <v>7.94255447387695</v>
+        <v>7.94255399703979</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G54" t="n">
-        <v>8.24930095672607</v>
+        <v>8.24930191040039</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>8.94293975830078</v>
       </c>
       <c r="G55" t="n">
-        <v>8.4081506729126</v>
+        <v>8.40815258026123</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>8.96721458435059</v>
       </c>
       <c r="G56" t="n">
-        <v>8.43097400665283</v>
+        <v>8.43097496032715</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.24977684020996</v>
       </c>
       <c r="G57" t="n">
-        <v>8.69663906097412</v>
+        <v>8.69664001464844</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.46728229522705</v>
       </c>
       <c r="G58" t="n">
-        <v>8.90113830566406</v>
+        <v>8.90113735198975</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.08859062194824</v>
       </c>
       <c r="G59" t="n">
-        <v>8.54509162902832</v>
+        <v>8.54509258270264</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.71960926055908</v>
       </c>
       <c r="G61" t="n">
-        <v>8.19817543029785</v>
+        <v>8.19817733764648</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.94973659515381</v>
       </c>
       <c r="G62" t="n">
-        <v>8.41454219818115</v>
+        <v>8.41454315185547</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G63" t="n">
-        <v>8.30772972106934</v>
+        <v>8.30772876739502</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G64" t="n">
-        <v>8.39902210235596</v>
+        <v>8.39902400970459</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.20511054992676</v>
       </c>
       <c r="G65" t="n">
-        <v>8.65464496612549</v>
+        <v>8.65464401245117</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.29250144958496</v>
       </c>
       <c r="G69" t="n">
-        <v>8.73680973052979</v>
+        <v>8.73680877685547</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.63235282897949</v>
       </c>
       <c r="G73" t="n">
-        <v>9.05633735656738</v>
+        <v>9.0563383102417</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G75" t="n">
-        <v>9.27544212341309</v>
+        <v>9.27544116973877</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.61293315887451</v>
       </c>
       <c r="G76" t="n">
-        <v>9.03807830810547</v>
+        <v>9.03807926177979</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.63332366943359</v>
       </c>
       <c r="G77" t="n">
-        <v>9.05725193023682</v>
+        <v>9.05724906921387</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>9.50029563903809</v>
       </c>
       <c r="G78" t="n">
-        <v>8.93217849731445</v>
+        <v>8.93217754364014</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.70614910125732</v>
       </c>
       <c r="G79" t="n">
-        <v>9.1257209777832</v>
+        <v>9.12572193145752</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.57506275177002</v>
       </c>
       <c r="G80" t="n">
-        <v>9.00247383117676</v>
+        <v>9.00247478485107</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.53525161743164</v>
       </c>
       <c r="G81" t="n">
-        <v>8.96504306793213</v>
+        <v>8.96504402160645</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.26239967346191</v>
       </c>
       <c r="G82" t="n">
-        <v>8.7085075378418</v>
+        <v>8.70850849151611</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.50320911407471</v>
       </c>
       <c r="G83" t="n">
-        <v>8.93491744995117</v>
+        <v>8.93491649627686</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.55467224121094</v>
       </c>
       <c r="G84" t="n">
-        <v>8.98330211639404</v>
+        <v>8.98330307006836</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.16238689422607</v>
       </c>
       <c r="G86" t="n">
-        <v>8.61447715759277</v>
+        <v>8.61447620391846</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.98954772949219</v>
       </c>
       <c r="G87" t="n">
-        <v>8.45197105407715</v>
+        <v>8.45197200775146</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G88" t="n">
-        <v>8.30772972106934</v>
+        <v>8.30772876739502</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>8.43413352966309</v>
       </c>
       <c r="G89" t="n">
-        <v>7.92977285385132</v>
+        <v>7.92977046966553</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.30706596374512</v>
       </c>
       <c r="G96" t="n">
-        <v>8.75050354003906</v>
+        <v>8.75050163269043</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G97" t="n">
-        <v>8.30772972106934</v>
+        <v>8.30772876739502</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>8.48462677001953</v>
       </c>
       <c r="G99" t="n">
-        <v>7.97724676132202</v>
+        <v>7.97724628448486</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.97193717956543</v>
       </c>
       <c r="G100" t="n">
-        <v>7.49521493911743</v>
+        <v>7.49521446228027</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G101" t="n">
-        <v>7.75996541976929</v>
+        <v>7.75996589660645</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>8.19041347503662</v>
       </c>
       <c r="G102" t="n">
-        <v>7.70062732696533</v>
+        <v>7.70062637329102</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.81476783752441</v>
       </c>
       <c r="G105" t="n">
-        <v>8.28764343261719</v>
+        <v>8.28764533996582</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.27210998535156</v>
       </c>
       <c r="G106" t="n">
-        <v>8.71763706207275</v>
+        <v>8.71763610839844</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.27502346038818</v>
       </c>
       <c r="G107" t="n">
-        <v>8.72037696838379</v>
+        <v>8.72037601470947</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.25074768066406</v>
       </c>
       <c r="G108" t="n">
-        <v>8.69755268096924</v>
+        <v>8.69755172729492</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.98760604858398</v>
       </c>
       <c r="G109" t="n">
-        <v>8.45014762878418</v>
+        <v>8.45014667510986</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.08664894104004</v>
       </c>
       <c r="G110" t="n">
-        <v>8.54326629638672</v>
+        <v>8.54326820373535</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.19443035125732</v>
       </c>
       <c r="G111" t="n">
-        <v>8.64460277557373</v>
+        <v>8.64460372924805</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>8.86817264556885</v>
       </c>
       <c r="G113" t="n">
-        <v>8.33785533905029</v>
+        <v>8.33785724639893</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.81379699707031</v>
       </c>
       <c r="G114" t="n">
-        <v>8.2867317199707</v>
+        <v>8.28673076629639</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.2138500213623</v>
       </c>
       <c r="G116" t="n">
-        <v>8.66286087036133</v>
+        <v>8.6628589630127</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.49724960327148</v>
       </c>
       <c r="G118" t="n">
-        <v>7.98911333084106</v>
+        <v>7.98911285400391</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.65260982513428</v>
       </c>
       <c r="G120" t="n">
-        <v>8.1351842880249</v>
+        <v>8.13518238067627</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G123" t="n">
-        <v>8.39902210235596</v>
+        <v>8.39902400970459</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G125" t="n">
-        <v>8.39902210235596</v>
+        <v>8.39902400970459</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.55078792572021</v>
       </c>
       <c r="G127" t="n">
-        <v>8.97965049743652</v>
+        <v>8.97964954376221</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.67119312286377</v>
       </c>
       <c r="G130" t="n">
-        <v>9.09285449981689</v>
+        <v>9.09285545349121</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.35076236724854</v>
       </c>
       <c r="G131" t="n">
-        <v>8.79158687591553</v>
+        <v>8.79158496856689</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>9.50029563903809</v>
       </c>
       <c r="G132" t="n">
-        <v>8.93217849731445</v>
+        <v>8.93217754364014</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.53525161743164</v>
       </c>
       <c r="G133" t="n">
-        <v>8.96504306793213</v>
+        <v>8.96504402160645</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.5935115814209</v>
       </c>
       <c r="G134" t="n">
-        <v>9.01981925964355</v>
+        <v>9.01981830596924</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.35755920410156</v>
       </c>
       <c r="G135" t="n">
-        <v>8.79797840118408</v>
+        <v>8.79797649383545</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G136" t="n">
-        <v>8.30772972106934</v>
+        <v>8.30772876739502</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>8.77495670318604</v>
       </c>
       <c r="G137" t="n">
-        <v>8.25021266937256</v>
+        <v>8.25021457672119</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G139" t="n">
-        <v>8.21643543243408</v>
+        <v>8.21643447875977</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>8.80991268157959</v>
       </c>
       <c r="G140" t="n">
-        <v>8.28307914733887</v>
+        <v>8.2830810546875</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8.66523265838623</v>
       </c>
       <c r="G141" t="n">
-        <v>8.14704990386963</v>
+        <v>8.14705276489258</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G142" t="n">
-        <v>8.24930095672607</v>
+        <v>8.24930191040039</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>8.8798246383667</v>
       </c>
       <c r="G143" t="n">
-        <v>8.34881114959717</v>
+        <v>8.34881019592285</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>8.7429141998291</v>
       </c>
       <c r="G144" t="n">
-        <v>8.2200870513916</v>
+        <v>8.22008800506592</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>8.76815986633301</v>
       </c>
       <c r="G145" t="n">
-        <v>8.24382400512695</v>
+        <v>8.24382495880127</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G146" t="n">
-        <v>8.30772972106934</v>
+        <v>8.30772876739502</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G147" t="n">
-        <v>8.24930095672607</v>
+        <v>8.24930191040039</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>8.94293975830078</v>
       </c>
       <c r="G149" t="n">
-        <v>8.4081506729126</v>
+        <v>8.40815258026123</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>8.91380977630615</v>
       </c>
       <c r="G150" t="n">
-        <v>8.38076400756836</v>
+        <v>8.38076210021973</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G152" t="n">
-        <v>8.21643543243408</v>
+        <v>8.21643447875977</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>8.82739067077637</v>
       </c>
       <c r="G153" t="n">
-        <v>8.29951286315918</v>
+        <v>8.29951190948486</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>8.65260982513428</v>
       </c>
       <c r="G154" t="n">
-        <v>8.1351842880249</v>
+        <v>8.13518238067627</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>8.68659496307373</v>
       </c>
       <c r="G155" t="n">
-        <v>8.16713523864746</v>
+        <v>8.16713619232178</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>8.61474132537842</v>
       </c>
       <c r="G156" t="n">
-        <v>8.09957981109619</v>
+        <v>8.09958076477051</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G157" t="n">
-        <v>8.21643543243408</v>
+        <v>8.21643447875977</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>8.87497043609619</v>
       </c>
       <c r="G158" t="n">
-        <v>8.34424781799316</v>
+        <v>8.34424686431885</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>8.90410041809082</v>
       </c>
       <c r="G159" t="n">
-        <v>8.37163543701172</v>
+        <v>8.3716344833374</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>8.96430206298828</v>
       </c>
       <c r="G160" t="n">
-        <v>8.42823791503906</v>
+        <v>8.42823696136475</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.20316886901855</v>
       </c>
       <c r="G161" t="n">
-        <v>8.65281867980957</v>
+        <v>8.65281963348389</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>9.20316886901855</v>
       </c>
       <c r="G162" t="n">
-        <v>8.65281867980957</v>
+        <v>8.65281963348389</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.57894706726074</v>
       </c>
       <c r="G166" t="n">
-        <v>9.00612449645996</v>
+        <v>9.00612640380859</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.48573112487793</v>
       </c>
       <c r="G170" t="n">
-        <v>8.91848468780518</v>
+        <v>8.91848373413086</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G171" t="n">
-        <v>8.99243259429932</v>
+        <v>8.99243068695068</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.75858306884766</v>
       </c>
       <c r="G172" t="n">
-        <v>9.17501831054688</v>
+        <v>9.17502021789551</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.72751140594482</v>
       </c>
       <c r="G173" t="n">
-        <v>9.1458044052124</v>
+        <v>9.14580631256104</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.92753791809082</v>
       </c>
       <c r="G175" t="n">
-        <v>9.33387088775635</v>
+        <v>9.33386993408203</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G177" t="n">
-        <v>9.58584213256836</v>
+        <v>9.58584022521973</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G178" t="n">
-        <v>9.58584213256836</v>
+        <v>9.58584022521973</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G179" t="n">
-        <v>9.58584213256836</v>
+        <v>9.58584022521973</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G181" t="n">
-        <v>9.58584213256836</v>
+        <v>9.58584022521973</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>10.1372737884521</v>
       </c>
       <c r="G182" t="n">
-        <v>9.53106594085693</v>
+        <v>9.53106498718262</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.1897087097168</v>
       </c>
       <c r="G183" t="n">
-        <v>9.58036327362061</v>
+        <v>9.58036518096924</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.84791469573975</v>
       </c>
       <c r="G184" t="n">
-        <v>9.25900936126709</v>
+        <v>9.25901031494141</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G185" t="n">
-        <v>9.58584213256836</v>
+        <v>9.58584022521973</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>10.1625204086304</v>
       </c>
       <c r="G186" t="n">
-        <v>9.55480098724365</v>
+        <v>9.55480003356934</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G188" t="n">
-        <v>9.58584213256836</v>
+        <v>9.58584022521973</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>10.0498838424683</v>
       </c>
       <c r="G189" t="n">
-        <v>9.44890022277832</v>
+        <v>9.44890117645264</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>9.81101703643799</v>
       </c>
       <c r="G190" t="n">
-        <v>9.2243185043335</v>
+        <v>9.22431755065918</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.8595666885376</v>
       </c>
       <c r="G192" t="n">
-        <v>9.26996421813965</v>
+        <v>9.26996326446533</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G194" t="n">
-        <v>8.99243259429932</v>
+        <v>8.99243068695068</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.57409191131592</v>
       </c>
       <c r="G198" t="n">
-        <v>9.00156116485596</v>
+        <v>9.00156021118164</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.44786167144775</v>
       </c>
       <c r="G199" t="n">
-        <v>8.88287830352783</v>
+        <v>8.88287925720215</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>8.87497043609619</v>
       </c>
       <c r="G201" t="n">
-        <v>8.34424781799316</v>
+        <v>8.34424686431885</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.25657367706299</v>
       </c>
       <c r="G203" t="n">
-        <v>8.70302867889404</v>
+        <v>8.70303153991699</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.5935115814209</v>
       </c>
       <c r="G204" t="n">
-        <v>9.01981925964355</v>
+        <v>9.01981830596924</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>9.51680278778076</v>
       </c>
       <c r="G205" t="n">
-        <v>8.94769763946533</v>
+        <v>8.94769668579102</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>9.61293315887451</v>
       </c>
       <c r="G206" t="n">
-        <v>9.03807830810547</v>
+        <v>9.03807926177979</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>9.67119312286377</v>
       </c>
       <c r="G207" t="n">
-        <v>9.09285449981689</v>
+        <v>9.09285545349121</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>9.71003341674805</v>
       </c>
       <c r="G208" t="n">
-        <v>9.12937164306641</v>
+        <v>9.12937355041504</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>9.47699165344238</v>
       </c>
       <c r="G209" t="n">
-        <v>8.9102668762207</v>
+        <v>8.91026592254639</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>9.47699165344238</v>
       </c>
       <c r="G210" t="n">
-        <v>8.9102668762207</v>
+        <v>8.91026592254639</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.62264347076416</v>
       </c>
       <c r="G211" t="n">
-        <v>9.04720878601074</v>
+        <v>9.04720973968506</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.98191356658936</v>
       </c>
       <c r="G214" t="n">
-        <v>9.38499450683594</v>
+        <v>9.3849925994873</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G216" t="n">
-        <v>9.6771354675293</v>
+        <v>9.67713451385498</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.0790138244629</v>
       </c>
       <c r="G218" t="n">
-        <v>9.47628974914551</v>
+        <v>9.47628784179688</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.3120546340942</v>
       </c>
       <c r="G219" t="n">
-        <v>9.69539356231689</v>
+        <v>9.69539260864258</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.234375</v>
       </c>
       <c r="G220" t="n">
-        <v>9.62235927581787</v>
+        <v>9.62236022949219</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>10.3120546340942</v>
       </c>
       <c r="G222" t="n">
-        <v>9.69539356231689</v>
+        <v>9.69539260864258</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G223" t="n">
-        <v>9.9327564239502</v>
+        <v>9.93275833129883</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G224" t="n">
-        <v>9.98753356933594</v>
+        <v>9.98753452301025</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G225" t="n">
-        <v>9.73190975189209</v>
+        <v>9.73191165924072</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G226" t="n">
-        <v>9.98753356933594</v>
+        <v>9.98753452301025</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G227" t="n">
-        <v>9.8597240447998</v>
+        <v>9.85972213745117</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G228" t="n">
-        <v>9.73190975189209</v>
+        <v>9.73191165924072</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G229" t="n">
-        <v>9.750168800354</v>
+        <v>9.75016975402832</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G230" t="n">
-        <v>9.73190975189209</v>
+        <v>9.73191165924072</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G231" t="n">
-        <v>9.73190975189209</v>
+        <v>9.73191165924072</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G232" t="n">
-        <v>9.87798118591309</v>
+        <v>9.8779821395874</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>10.6421957015991</v>
       </c>
       <c r="G233" t="n">
-        <v>10.0057926177979</v>
+        <v>10.0057916641235</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G234" t="n">
-        <v>10.0423107147217</v>
+        <v>10.0423097610474</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.214955329895</v>
       </c>
       <c r="G235" t="n">
-        <v>9.60410118103027</v>
+        <v>9.60410022735596</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G236" t="n">
-        <v>9.71365261077881</v>
+        <v>9.71365165710449</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G237" t="n">
-        <v>9.76842784881592</v>
+        <v>9.76842975616455</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.4285745620728</v>
       </c>
       <c r="G238" t="n">
-        <v>9.80494499206543</v>
+        <v>9.80494403839111</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G239" t="n">
-        <v>10.0788259506226</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G240" t="n">
-        <v>10.0423107147217</v>
+        <v>10.0423097610474</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G241" t="n">
-        <v>10.0423107147217</v>
+        <v>10.0423097610474</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G243" t="n">
-        <v>9.87798118591309</v>
+        <v>9.8779821395874</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G244" t="n">
-        <v>10.2431554794312</v>
+        <v>10.2431573867798</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G246" t="n">
-        <v>9.8597240447998</v>
+        <v>9.85972213745117</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>10.4285745620728</v>
       </c>
       <c r="G247" t="n">
-        <v>9.80494499206543</v>
+        <v>9.80494403839111</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G248" t="n">
-        <v>9.9327564239502</v>
+        <v>9.93275833129883</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G249" t="n">
-        <v>9.95101642608643</v>
+        <v>9.95101547241211</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>11.1082782745361</v>
       </c>
       <c r="G251" t="n">
-        <v>10.4440021514893</v>
+        <v>10.4440011978149</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>11.2636375427246</v>
       </c>
       <c r="G253" t="n">
-        <v>10.5900707244873</v>
+        <v>10.5900716781616</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>11.0694379806519</v>
       </c>
       <c r="G256" t="n">
-        <v>10.4074850082397</v>
+        <v>10.4074859619141</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>11.0305967330933</v>
       </c>
       <c r="G257" t="n">
-        <v>10.3709678649902</v>
+        <v>10.3709669113159</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G259" t="n">
-        <v>9.95101642608643</v>
+        <v>9.95101547241211</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G260" t="n">
-        <v>9.91449928283691</v>
+        <v>9.91449737548828</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G262" t="n">
-        <v>10.0788259506226</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>10.6616163253784</v>
       </c>
       <c r="G263" t="n">
-        <v>10.1156797409058</v>
+        <v>10.1156778335571</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G264" t="n">
-        <v>9.87614440917969</v>
+        <v>9.87614250183105</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G266" t="n">
-        <v>9.8577184677124</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G267" t="n">
-        <v>9.8577184677124</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>10.6616163253784</v>
       </c>
       <c r="G268" t="n">
-        <v>10.1156797409058</v>
+        <v>10.1156778335571</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G269" t="n">
-        <v>10.0788259506226</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G271" t="n">
-        <v>10.1341047286987</v>
+        <v>10.1341037750244</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G273" t="n">
-        <v>10.1341047286987</v>
+        <v>10.1341037750244</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G277" t="n">
-        <v>9.98669815063477</v>
+        <v>9.98669910430908</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G279" t="n">
-        <v>10.1341047286987</v>
+        <v>10.1341037750244</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G283" t="n">
-        <v>9.87614440917969</v>
+        <v>9.87614250183105</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G285" t="n">
-        <v>9.80244159698486</v>
+        <v>9.80244255065918</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>10.6421957015991</v>
       </c>
       <c r="G286" t="n">
-        <v>10.0972518920898</v>
+        <v>10.0972528457642</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.0500173568726</v>
       </c>
       <c r="G287" t="n">
-        <v>10.4841909408569</v>
+        <v>10.4841899871826</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G288" t="n">
-        <v>10.3367853164673</v>
+        <v>10.3367862701416</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3552122116089</v>
+        <v>10.3552131652832</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G291" t="n">
-        <v>10.3367853164673</v>
+        <v>10.3367862701416</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>10.8558168411255</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2999353408813</v>
+        <v>10.299934387207</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G294" t="n">
-        <v>9.76559162139893</v>
+        <v>9.76559066772461</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G296" t="n">
-        <v>10.3367853164673</v>
+        <v>10.3367862701416</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G297" t="n">
-        <v>9.96827411651611</v>
+        <v>9.96827125549316</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G299" t="n">
-        <v>9.80244159698486</v>
+        <v>9.80244255065918</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.2732152938843</v>
       </c>
       <c r="G301" t="n">
-        <v>9.74716663360596</v>
+        <v>9.74716472625732</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G303" t="n">
-        <v>10.0051250457764</v>
+        <v>10.0051259994507</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G304" t="n">
-        <v>10.0419750213623</v>
+        <v>10.0419759750366</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G305" t="n">
-        <v>10.1341047286987</v>
+        <v>10.1341037750244</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G308" t="n">
-        <v>9.98669815063477</v>
+        <v>9.98669910430908</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>11.0500173568726</v>
       </c>
       <c r="G313" t="n">
-        <v>10.4841909408569</v>
+        <v>10.4841899871826</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G314" t="n">
-        <v>10.7790012359619</v>
+        <v>10.7790021896362</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G315" t="n">
-        <v>10.4104881286621</v>
+        <v>10.4104871749878</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G317" t="n">
-        <v>11.9766683578491</v>
+        <v>11.9766674041748</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>11.6908798217773</v>
       </c>
       <c r="G318" t="n">
-        <v>11.0922374725342</v>
+        <v>11.0922365188599</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>12.15696144104</v>
       </c>
       <c r="G319" t="n">
-        <v>11.5344533920288</v>
+        <v>11.5344524383545</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G322" t="n">
-        <v>11.4607496261597</v>
+        <v>11.460750579834</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>12.176381111145</v>
       </c>
       <c r="G323" t="n">
-        <v>11.5528774261475</v>
+        <v>11.5528783798218</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>12.0598611831665</v>
       </c>
       <c r="G324" t="n">
-        <v>11.442325592041</v>
+        <v>11.4423246383667</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>12.15696144104</v>
       </c>
       <c r="G325" t="n">
-        <v>11.5344533920288</v>
+        <v>11.5344524383545</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>12.176381111145</v>
       </c>
       <c r="G326" t="n">
-        <v>11.5528774261475</v>
+        <v>11.5528783798218</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G327" t="n">
-        <v>11.8845415115356</v>
+        <v>11.884539604187</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G330" t="n">
-        <v>12.1609239578247</v>
+        <v>12.160924911499</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>13.0308637619019</v>
       </c>
       <c r="G331" t="n">
-        <v>12.3636064529419</v>
+        <v>12.3636054992676</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>13.186224937439</v>
       </c>
       <c r="G332" t="n">
-        <v>12.5110111236572</v>
+        <v>12.5110120773315</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G333" t="n">
-        <v>12.1056470870972</v>
+        <v>12.1056480407715</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G335" t="n">
-        <v>11.5160264968872</v>
+        <v>11.5160274505615</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G337" t="n">
-        <v>11.5160264968872</v>
+        <v>11.5160274505615</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G340" t="n">
-        <v>11.5160264968872</v>
+        <v>11.5160274505615</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G341" t="n">
-        <v>11.4607496261597</v>
+        <v>11.460750579834</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G342" t="n">
-        <v>11.5160264968872</v>
+        <v>11.5160274505615</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>12.681303024292</v>
       </c>
       <c r="G345" t="n">
-        <v>12.0319442749023</v>
+        <v>12.0319452285767</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G346" t="n">
-        <v>11.8845415115356</v>
+        <v>11.884539604187</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G348" t="n">
-        <v>12.1609239578247</v>
+        <v>12.160924911499</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G349" t="n">
-        <v>11.9766683578491</v>
+        <v>11.9766674041748</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>12.7978229522705</v>
       </c>
       <c r="G350" t="n">
-        <v>12.1424989700317</v>
+        <v>12.1424999237061</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>13.2833251953125</v>
       </c>
       <c r="G352" t="n">
-        <v>12.6031408309937</v>
+        <v>12.6031398773193</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>13.5940456390381</v>
       </c>
       <c r="G353" t="n">
-        <v>12.8979501724243</v>
+        <v>12.89794921875</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G354" t="n">
-        <v>13.174334526062</v>
+        <v>13.1743364334106</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>14.1378078460693</v>
       </c>
       <c r="G356" t="n">
-        <v>13.4138679504395</v>
+        <v>13.4138689041138</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>14.7204103469849</v>
       </c>
       <c r="G357" t="n">
-        <v>13.9666366577148</v>
+        <v>13.9666376113892</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>14.1378078460693</v>
       </c>
       <c r="G358" t="n">
-        <v>13.4138679504395</v>
+        <v>13.4138689041138</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>14.0989675521851</v>
       </c>
       <c r="G359" t="n">
-        <v>13.3770160675049</v>
+        <v>13.3770170211792</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.8270874023438</v>
       </c>
       <c r="G360" t="n">
-        <v>13.1190595626831</v>
+        <v>13.1190576553345</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>12.9726037979126</v>
       </c>
       <c r="G363" t="n">
-        <v>12.3083305358887</v>
+        <v>12.3083295822144</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G364" t="n">
-        <v>12.2714796066284</v>
+        <v>12.2714776992798</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G365" t="n">
-        <v>12.2162027359009</v>
+        <v>12.2162017822266</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>12.9920244216919</v>
       </c>
       <c r="G366" t="n">
-        <v>12.3267545700073</v>
+        <v>12.326756477356</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G367" t="n">
-        <v>12.1609239578247</v>
+        <v>12.160924911499</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G369" t="n">
-        <v>12.1056470870972</v>
+        <v>12.1056480407715</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G370" t="n">
-        <v>12.1240739822388</v>
+        <v>12.1240730285645</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>15.2835922241211</v>
       </c>
       <c r="G373" t="n">
-        <v>14.5009832382202</v>
+        <v>14.5009803771973</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>14.5650501251221</v>
       </c>
       <c r="G374" t="n">
-        <v>13.8192329406738</v>
+        <v>13.8192319869995</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>14.0407075881958</v>
       </c>
       <c r="G375" t="n">
-        <v>13.3217401504517</v>
+        <v>13.321741104126</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G376" t="n">
-        <v>13.0822086334229</v>
+        <v>13.0822076797485</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G377" t="n">
-        <v>12.7689695358276</v>
+        <v>12.7689723968506</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G380" t="n">
-        <v>12.4741611480713</v>
+        <v>12.4741592407227</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G384" t="n">
-        <v>12.2162027359009</v>
+        <v>12.2162017822266</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>13.380425453186</v>
       </c>
       <c r="G385" t="n">
-        <v>12.6952686309814</v>
+        <v>12.6952676773071</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>13.4192657470703</v>
       </c>
       <c r="G386" t="n">
-        <v>12.732120513916</v>
+        <v>12.7321195602417</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>13.4969463348389</v>
       </c>
       <c r="G387" t="n">
-        <v>12.8058233261108</v>
+        <v>12.8058223724365</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G389" t="n">
-        <v>13.174334526062</v>
+        <v>13.1743364334106</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>13.6911468505859</v>
       </c>
       <c r="G390" t="n">
-        <v>12.9900789260864</v>
+        <v>12.9900779724121</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G393" t="n">
-        <v>13.0822086334229</v>
+        <v>13.0822076797485</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G394" t="n">
-        <v>12.7689695358276</v>
+        <v>12.7689723968506</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G395" t="n">
-        <v>13.174334526062</v>
+        <v>13.1743364334106</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>12.8949241638184</v>
       </c>
       <c r="G398" t="n">
-        <v>12.2346277236938</v>
+        <v>12.2346286773682</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G399" t="n">
-        <v>12.1056470870972</v>
+        <v>12.1056480407715</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G401" t="n">
-        <v>12.3451814651489</v>
+        <v>12.3451824188232</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G402" t="n">
-        <v>12.3451814651489</v>
+        <v>12.3451824188232</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G404" t="n">
-        <v>12.3451814651489</v>
+        <v>12.3451824188232</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G405" t="n">
-        <v>12.1609239578247</v>
+        <v>12.160924911499</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G408" t="n">
-        <v>11.8845415115356</v>
+        <v>11.884539604187</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>12.4094219207764</v>
       </c>
       <c r="G410" t="n">
-        <v>11.7739877700806</v>
+        <v>11.7739849090576</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G411" t="n">
-        <v>11.7002840042114</v>
+        <v>11.7002849578857</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>11.8268203735352</v>
       </c>
       <c r="G412" t="n">
-        <v>11.2212162017822</v>
+        <v>11.2212171554565</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G415" t="n">
-        <v>10.9632596969604</v>
+        <v>10.9632577896118</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G416" t="n">
-        <v>10.7790012359619</v>
+        <v>10.7790021896362</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G417" t="n">
-        <v>10.9632596969604</v>
+        <v>10.9632577896118</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>11.2636375427246</v>
       </c>
       <c r="G418" t="n">
-        <v>10.6868724822998</v>
+        <v>10.6868715286255</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G422" t="n">
-        <v>11.0553874969482</v>
+        <v>11.0553855895996</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>11.8073997497559</v>
       </c>
       <c r="G423" t="n">
-        <v>11.2027902603149</v>
+        <v>11.2027912139893</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G424" t="n">
-        <v>11.1475133895874</v>
+        <v>11.1475124359131</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G428" t="n">
-        <v>11.1475133895874</v>
+        <v>11.1475124359131</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>11.8073997497559</v>
       </c>
       <c r="G429" t="n">
-        <v>11.2027902603149</v>
+        <v>11.2027912139893</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>11.9045000076294</v>
       </c>
       <c r="G430" t="n">
-        <v>11.2949190139771</v>
+        <v>11.2949199676514</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G431" t="n">
-        <v>11.0369606018066</v>
+        <v>11.036961555481</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G432" t="n">
-        <v>10.0788259506226</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G433" t="n">
-        <v>10.4104881286621</v>
+        <v>10.4104871749878</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G434" t="n">
-        <v>10.7790012359619</v>
+        <v>10.7790021896362</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G437" t="n">
-        <v>9.98669815063477</v>
+        <v>9.98669910430908</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G438" t="n">
-        <v>10.3552122116089</v>
+        <v>10.3552131652832</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G439" t="n">
-        <v>10.3367853164673</v>
+        <v>10.3367862701416</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G441" t="n">
-        <v>10.0788259506226</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>10.0013341903687</v>
       </c>
       <c r="G446" t="n">
-        <v>9.48920726776123</v>
+        <v>9.48920631408691</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.12743091583252</v>
       </c>
       <c r="G447" t="n">
-        <v>8.66005325317383</v>
+        <v>8.66005229949951</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G448" t="n">
-        <v>9.8577184677124</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>8.59337902069092</v>
       </c>
       <c r="G450" t="n">
-        <v>8.15334701538086</v>
+        <v>8.15334606170654</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.6322193145752</v>
       </c>
       <c r="G451" t="n">
-        <v>8.19019794464111</v>
+        <v>8.19019889831543</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>10.0984344482422</v>
       </c>
       <c r="G455" t="n">
-        <v>9.58133506774902</v>
+        <v>9.58133411407471</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G456" t="n">
-        <v>11.7002840042114</v>
+        <v>11.7002849578857</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G457" t="n">
-        <v>11.0369606018066</v>
+        <v>11.036961555481</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G459" t="n">
-        <v>10.0788259506226</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G460" t="n">
-        <v>10.1341047286987</v>
+        <v>10.1341037750244</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G462" t="n">
-        <v>10.1341047286987</v>
+        <v>10.1341037750244</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>10.7781372070312</v>
       </c>
       <c r="G463" t="n">
-        <v>10.2262334823608</v>
+        <v>10.2262325286865</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G465" t="n">
-        <v>9.76559162139893</v>
+        <v>9.76559066772461</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>10.2732152938843</v>
       </c>
       <c r="G466" t="n">
-        <v>9.74716663360596</v>
+        <v>9.74716472625732</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G468" t="n">
-        <v>9.94984722137451</v>
+        <v>9.94984912872314</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G470" t="n">
-        <v>11.0553874969482</v>
+        <v>11.0553855895996</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>11.8268203735352</v>
       </c>
       <c r="G471" t="n">
-        <v>11.2212162017822</v>
+        <v>11.2212171554565</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G472" t="n">
-        <v>11.0553874969482</v>
+        <v>11.0553855895996</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G473" t="n">
-        <v>11.7002840042114</v>
+        <v>11.7002849578857</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G475" t="n">
-        <v>11.7924127578735</v>
+        <v>11.7924108505249</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G477" t="n">
-        <v>12.4741611480713</v>
+        <v>12.4741592407227</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>13.2056446075439</v>
       </c>
       <c r="G478" t="n">
-        <v>12.5294361114502</v>
+        <v>12.5294370651245</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G479" t="n">
-        <v>12.3451814651489</v>
+        <v>12.3451824188232</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G480" t="n">
-        <v>12.2714796066284</v>
+        <v>12.2714776992798</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G481" t="n">
-        <v>11.9766683578491</v>
+        <v>11.9766674041748</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G483" t="n">
-        <v>11.7924127578735</v>
+        <v>11.7924108505249</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G484" t="n">
-        <v>12.1240739822388</v>
+        <v>12.1240730285645</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G485" t="n">
-        <v>11.7002840042114</v>
+        <v>11.7002849578857</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G488" t="n">
-        <v>13.0822086334229</v>
+        <v>13.0822076797485</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>14.3708486557007</v>
       </c>
       <c r="G489" t="n">
-        <v>13.6349754333496</v>
+        <v>13.6349763870239</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>14.1183881759644</v>
       </c>
       <c r="G490" t="n">
-        <v>13.3954429626465</v>
+        <v>13.3954420089722</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>14.2931690216064</v>
       </c>
       <c r="G492" t="n">
-        <v>13.5612735748291</v>
+        <v>13.5612745285034</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>14.9146108627319</v>
       </c>
       <c r="G496" t="n">
-        <v>14.1508941650391</v>
+        <v>14.1508951187134</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G498" t="n">
-        <v>15.6433706283569</v>
+        <v>15.6433725357056</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>16.7206764221191</v>
       </c>
       <c r="G499" t="n">
-        <v>15.8644800186157</v>
+        <v>15.8644781112671</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G500" t="n">
-        <v>15.2932825088501</v>
+        <v>15.2932834625244</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>15.6525726318359</v>
       </c>
       <c r="G501" t="n">
-        <v>14.8510675430298</v>
+        <v>14.8510684967041</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>15.3030118942261</v>
       </c>
       <c r="G502" t="n">
-        <v>14.5194082260132</v>
+        <v>14.5194072723389</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>15.1476516723633</v>
       </c>
       <c r="G503" t="n">
-        <v>14.3720026016235</v>
+        <v>14.3720016479492</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G504" t="n">
-        <v>13.9482107162476</v>
+        <v>13.9482116699219</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G505" t="n">
-        <v>13.9482107162476</v>
+        <v>13.9482116699219</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>14.7980899810791</v>
       </c>
       <c r="G506" t="n">
-        <v>14.040340423584</v>
+        <v>14.0403394699097</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>14.3125886917114</v>
       </c>
       <c r="G509" t="n">
-        <v>13.5796985626221</v>
+        <v>13.5796995162964</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>14.7398300170898</v>
       </c>
       <c r="G510" t="n">
-        <v>13.9850625991821</v>
+        <v>13.9850635528564</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>15.6914129257202</v>
       </c>
       <c r="G513" t="n">
-        <v>14.8879203796387</v>
+        <v>14.8879194259644</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G515" t="n">
-        <v>14.7022829055786</v>
+        <v>14.7022838592529</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>15.3612718582153</v>
       </c>
       <c r="G517" t="n">
-        <v>14.6837196350098</v>
+        <v>14.6837205886841</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>15.3418521881104</v>
       </c>
       <c r="G518" t="n">
-        <v>14.6651582717896</v>
+        <v>14.6651573181152</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>15.8661937713623</v>
       </c>
       <c r="G520" t="n">
-        <v>15.16637134552</v>
+        <v>15.1663722991943</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G521" t="n">
-        <v>14.7022829055786</v>
+        <v>14.7022838592529</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G522" t="n">
-        <v>15.1292457580566</v>
+        <v>15.129246711731</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>15.9244537353516</v>
       </c>
       <c r="G524" t="n">
-        <v>15.2220630645752</v>
+        <v>15.2220611572266</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G525" t="n">
-        <v>14.9064836502075</v>
+        <v>14.9064826965332</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>15.1864919662476</v>
       </c>
       <c r="G526" t="n">
-        <v>14.5166492462158</v>
+        <v>14.5166501998901</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G527" t="n">
-        <v>14.9064836502075</v>
+        <v>14.9064826965332</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G529" t="n">
-        <v>14.813666343689</v>
+        <v>14.8136653900146</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>15.2253322601318</v>
       </c>
       <c r="G530" t="n">
-        <v>14.5537767410278</v>
+        <v>14.5537776947021</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G534" t="n">
-        <v>15.1292457580566</v>
+        <v>15.129246711731</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G535" t="n">
-        <v>15.1292457580566</v>
+        <v>15.129246711731</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G536" t="n">
-        <v>14.9064836502075</v>
+        <v>14.9064826965332</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G537" t="n">
-        <v>15.2963161468506</v>
+        <v>15.2963171005249</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G538" t="n">
-        <v>14.813666343689</v>
+        <v>14.8136653900146</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>15.3612718582153</v>
       </c>
       <c r="G542" t="n">
-        <v>14.6837196350098</v>
+        <v>14.6837205886841</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>16.1769142150879</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4633874893188</v>
+        <v>15.4633865356445</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G546" t="n">
-        <v>16.0574169158936</v>
+        <v>16.0574207305908</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G547" t="n">
-        <v>16.8556499481201</v>
+        <v>16.8556518554688</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G550" t="n">
-        <v>16.6143264770508</v>
+        <v>16.6143245697021</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>17.536319732666</v>
       </c>
       <c r="G551" t="n">
-        <v>16.7628345489502</v>
+        <v>16.7628326416016</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>18.1189212799072</v>
       </c>
       <c r="G552" t="n">
-        <v>17.3197364807129</v>
+        <v>17.3197383880615</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G554" t="n">
-        <v>17.2826099395752</v>
+        <v>17.2826080322266</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G555" t="n">
-        <v>17.6724433898926</v>
+        <v>17.6724452972412</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G556" t="n">
-        <v>17.8952045440674</v>
+        <v>17.8952083587646</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>18.9928245544434</v>
       </c>
       <c r="G558" t="n">
-        <v>18.1550922393799</v>
+        <v>18.1550941467285</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G559" t="n">
-        <v>18.1922206878662</v>
+        <v>18.1922225952148</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G560" t="n">
-        <v>17.5424995422363</v>
+        <v>17.542501449585</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G561" t="n">
-        <v>17.4125556945801</v>
+        <v>17.4125537872314</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G562" t="n">
-        <v>17.8766441345215</v>
+        <v>17.8766403198242</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G563" t="n">
-        <v>18.5634937286377</v>
+        <v>18.5634899139404</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G564" t="n">
-        <v>19.0275783538818</v>
+        <v>19.0275764465332</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G566" t="n">
-        <v>18.5634937286377</v>
+        <v>18.5634899139404</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G567" t="n">
-        <v>17.6724433898926</v>
+        <v>17.6724452972412</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G569" t="n">
-        <v>17.9137706756592</v>
+        <v>17.9137687683105</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G570" t="n">
-        <v>17.2640476226807</v>
+        <v>17.264045715332</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>18.6626834869385</v>
       </c>
       <c r="G571" t="n">
-        <v>17.8395156860352</v>
+        <v>17.8395137786865</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G572" t="n">
-        <v>17.3568630218506</v>
+        <v>17.3568649291992</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G577" t="n">
-        <v>16.3544368743896</v>
+        <v>16.3544330596924</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G580" t="n">
-        <v>15.6675863265991</v>
+        <v>15.6675844192505</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G581" t="n">
-        <v>16.4286918640137</v>
+        <v>16.428689956665</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G582" t="n">
-        <v>16.4843826293945</v>
+        <v>16.4843807220459</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G584" t="n">
-        <v>16.317310333252</v>
+        <v>16.3173065185547</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>16.9731388092041</v>
       </c>
       <c r="G588" t="n">
-        <v>16.2244911193848</v>
+        <v>16.2244930267334</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>17.1479187011719</v>
       </c>
       <c r="G589" t="n">
-        <v>16.3915615081787</v>
+        <v>16.391565322876</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G595" t="n">
-        <v>16.5771999359131</v>
+        <v>16.5771980285645</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G597" t="n">
-        <v>16.5029449462891</v>
+        <v>16.5029411315918</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G598" t="n">
-        <v>16.6514549255371</v>
+        <v>16.6514511108398</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G600" t="n">
-        <v>16.4843826293945</v>
+        <v>16.4843807220459</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>17.4586391448975</v>
       </c>
       <c r="G601" t="n">
-        <v>16.6885795593262</v>
+        <v>16.6885776519775</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G602" t="n">
-        <v>16.6143264770508</v>
+        <v>16.6143245697021</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G603" t="n">
-        <v>15.6861486434937</v>
+        <v>15.6861524581909</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>16.0409755706787</v>
       </c>
       <c r="G604" t="n">
-        <v>15.3334436416626</v>
+        <v>15.3334445953369</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>15.5554733276367</v>
       </c>
       <c r="G605" t="n">
-        <v>14.8693561553955</v>
+        <v>14.8693571090698</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>15.2641716003418</v>
       </c>
       <c r="G606" t="n">
-        <v>14.5909042358398</v>
+        <v>14.5909032821655</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G609" t="n">
-        <v>15.6861486434937</v>
+        <v>15.6861524581909</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>18.0024013519287</v>
       </c>
       <c r="G612" t="n">
-        <v>17.2083549499512</v>
+        <v>17.2083568572998</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G618" t="n">
-        <v>15.7789649963379</v>
+        <v>15.7789640426636</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>16.8760375976562</v>
       </c>
       <c r="G620" t="n">
-        <v>16.1316719055176</v>
+        <v>16.1316738128662</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G622" t="n">
-        <v>16.4843826293945</v>
+        <v>16.4843807220459</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G624" t="n">
-        <v>16.3730010986328</v>
+        <v>16.3729972839355</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G625" t="n">
-        <v>16.8556499481201</v>
+        <v>16.8556518554688</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>17.4974803924561</v>
       </c>
       <c r="G626" t="n">
-        <v>16.7257080078125</v>
+        <v>16.7257041931152</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G628" t="n">
-        <v>16.5029449462891</v>
+        <v>16.5029411315918</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G630" t="n">
-        <v>16.5029449462891</v>
+        <v>16.5029411315918</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G631" t="n">
-        <v>16.317310333252</v>
+        <v>16.3173065185547</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>17.4974803924561</v>
       </c>
       <c r="G633" t="n">
-        <v>16.7257080078125</v>
+        <v>16.7257041931152</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G634" t="n">
-        <v>16.8370876312256</v>
+        <v>16.837085723877</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>17.7499408721924</v>
       </c>
       <c r="G635" t="n">
-        <v>16.9670314788818</v>
+        <v>16.9670295715332</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G636" t="n">
-        <v>16.3544368743896</v>
+        <v>16.3544330596924</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G637" t="n">
-        <v>16.5400714874268</v>
+        <v>16.5400695800781</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G639" t="n">
-        <v>16.3730010986328</v>
+        <v>16.3729972839355</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>17.5557403564453</v>
       </c>
       <c r="G641" t="n">
-        <v>16.7813987731934</v>
+        <v>16.7813968658447</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G642" t="n">
-        <v>16.3544368743896</v>
+        <v>16.3544330596924</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G644" t="n">
-        <v>17.2826099395752</v>
+        <v>17.2826080322266</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G645" t="n">
-        <v>17.4125556945801</v>
+        <v>17.4125537872314</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>18.7986240386963</v>
       </c>
       <c r="G647" t="n">
-        <v>17.9694576263428</v>
+        <v>17.9694595336914</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G648" t="n">
-        <v>18.4149856567383</v>
+        <v>18.4149837493896</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G649" t="n">
-        <v>17.8023872375488</v>
+        <v>17.8023853302002</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G652" t="n">
-        <v>16.5771999359131</v>
+        <v>16.5771980285645</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G653" t="n">
-        <v>16.5400714874268</v>
+        <v>16.5400695800781</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>17.2255992889404</v>
       </c>
       <c r="G655" t="n">
-        <v>16.4658184051514</v>
+        <v>16.4658164978027</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>17.2255992889404</v>
       </c>
       <c r="G658" t="n">
-        <v>16.4658184051514</v>
+        <v>16.4658164978027</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G660" t="n">
-        <v>16.5029449462891</v>
+        <v>16.5029411315918</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G663" t="n">
-        <v>16.3730010986328</v>
+        <v>16.3729972839355</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G664" t="n">
-        <v>16.3730010986328</v>
+        <v>16.3729972839355</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>16.9731388092041</v>
       </c>
       <c r="G665" t="n">
-        <v>16.2244911193848</v>
+        <v>16.2244930267334</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G669" t="n">
-        <v>15.7789649963379</v>
+        <v>15.7789640426636</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G674" t="n">
-        <v>16.317310333252</v>
+        <v>16.3173065185547</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G675" t="n">
-        <v>16.4286918640137</v>
+        <v>16.428689956665</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>16.7012577056885</v>
       </c>
       <c r="G682" t="n">
-        <v>15.9646043777466</v>
+        <v>15.964599609375</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>16.8760375976562</v>
       </c>
       <c r="G685" t="n">
-        <v>16.1316719055176</v>
+        <v>16.1316738128662</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>16.6429977416992</v>
       </c>
       <c r="G689" t="n">
-        <v>15.9089117050171</v>
+        <v>15.9089107513428</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>16.5264759063721</v>
       </c>
       <c r="G690" t="n">
-        <v>15.7975301742554</v>
+        <v>15.797532081604</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>16.6041564941406</v>
       </c>
       <c r="G691" t="n">
-        <v>15.8717851638794</v>
+        <v>15.8717861175537</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>15.9632940292358</v>
       </c>
       <c r="G692" t="n">
-        <v>15.2591896057129</v>
+        <v>15.2591886520386</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G694" t="n">
-        <v>14.4238328933716</v>
+        <v>14.4238319396973</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>15.3418521881104</v>
       </c>
       <c r="G696" t="n">
-        <v>14.6651582717896</v>
+        <v>14.6651573181152</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G697" t="n">
-        <v>14.4238328933716</v>
+        <v>14.4238319396973</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>15.4389533996582</v>
       </c>
       <c r="G698" t="n">
-        <v>14.7579746246338</v>
+        <v>14.7579755783081</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G699" t="n">
-        <v>14.813666343689</v>
+        <v>14.8136653900146</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G701" t="n">
-        <v>15.4076957702637</v>
+        <v>15.407696723938</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>16.2934341430664</v>
       </c>
       <c r="G703" t="n">
-        <v>15.5747671127319</v>
+        <v>15.5747690200806</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G706" t="n">
-        <v>15.4076957702637</v>
+        <v>15.407696723938</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G709" t="n">
-        <v>15.6675863265991</v>
+        <v>15.6675844192505</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>16.2740154266357</v>
       </c>
       <c r="G710" t="n">
-        <v>15.5562057495117</v>
+        <v>15.5562038421631</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G711" t="n">
-        <v>15.7604036331177</v>
+        <v>15.760404586792</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G714" t="n">
-        <v>16.5771999359131</v>
+        <v>16.5771980285645</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G717" t="n">
-        <v>17.820951461792</v>
+        <v>17.8209533691406</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G718" t="n">
-        <v>17.5424995422363</v>
+        <v>17.542501449585</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G719" t="n">
-        <v>17.5424995422363</v>
+        <v>17.542501449585</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>18.2742824554443</v>
       </c>
       <c r="G720" t="n">
-        <v>17.4682464599609</v>
+        <v>17.4682445526123</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G722" t="n">
-        <v>18.0065841674805</v>
+        <v>18.0065860748291</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G723" t="n">
-        <v>17.820951461792</v>
+        <v>17.8209533691406</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>18.3325424194336</v>
       </c>
       <c r="G724" t="n">
-        <v>17.5239353179932</v>
+        <v>17.5239372253418</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G725" t="n">
-        <v>17.820951461792</v>
+        <v>17.8209533691406</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G729" t="n">
-        <v>17.2640476226807</v>
+        <v>17.264045715332</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>17.8470401763916</v>
       </c>
       <c r="G730" t="n">
-        <v>17.0598487854004</v>
+        <v>17.0598468780518</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G732" t="n">
-        <v>17.2826099395752</v>
+        <v>17.2826080322266</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G733" t="n">
-        <v>17.4496822357178</v>
+        <v>17.4496803283691</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>18.293701171875</v>
       </c>
       <c r="G734" t="n">
-        <v>17.4868068695068</v>
+        <v>17.4868087768555</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>18.4490623474121</v>
       </c>
       <c r="G735" t="n">
-        <v>17.6353168487549</v>
+        <v>17.6353149414062</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G736" t="n">
-        <v>18.1922206878662</v>
+        <v>18.1922225952148</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G737" t="n">
-        <v>19.5844841003418</v>
+        <v>19.5844860076904</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G738" t="n">
-        <v>19.6773014068604</v>
+        <v>19.6772994995117</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G740" t="n">
-        <v>19.3988456726074</v>
+        <v>19.3988494873047</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G741" t="n">
-        <v>19.8629341125488</v>
+        <v>19.8629360198975</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G742" t="n">
-        <v>20.4198417663574</v>
+        <v>20.4198398590088</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G743" t="n">
-        <v>20.3270244598389</v>
+        <v>20.3270225524902</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G744" t="n">
-        <v>20.1413860321045</v>
+        <v>20.1413879394531</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G747" t="n">
-        <v>20.1413860321045</v>
+        <v>20.1413879394531</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G749" t="n">
-        <v>20.4662494659424</v>
+        <v>20.4662475585938</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G750" t="n">
-        <v>20.5126571655273</v>
+        <v>20.512659072876</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G752" t="n">
-        <v>21.4408302307129</v>
+        <v>21.4408340454102</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G754" t="n">
-        <v>21.1623802185059</v>
+        <v>21.1623783111572</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G755" t="n">
-        <v>20.1413860321045</v>
+        <v>20.1413879394531</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G756" t="n">
-        <v>20.4662494659424</v>
+        <v>20.4662475585938</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G757" t="n">
-        <v>20.4198417663574</v>
+        <v>20.4198398590088</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G758" t="n">
-        <v>20.3270244598389</v>
+        <v>20.3270225524902</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G763" t="n">
-        <v>19.8629341125488</v>
+        <v>19.8629360198975</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G764" t="n">
-        <v>19.6308898925781</v>
+        <v>19.6308917999268</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G765" t="n">
-        <v>19.5844841003418</v>
+        <v>19.5844860076904</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>19.9541187286377</v>
       </c>
       <c r="G767" t="n">
-        <v>19.0739879608154</v>
+        <v>19.0739860534668</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G770" t="n">
-        <v>19.65283203125</v>
+        <v>19.6528339385986</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G772" t="n">
-        <v>19.4194278717041</v>
+        <v>19.4194297790527</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G773" t="n">
-        <v>19.3727474212646</v>
+        <v>19.3727493286133</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G774" t="n">
-        <v>19.5594730377197</v>
+        <v>19.5594749450684</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G778" t="n">
-        <v>18.952615737915</v>
+        <v>18.9526176452637</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>19.6142673492432</v>
       </c>
       <c r="G781" t="n">
-        <v>18.8592529296875</v>
+        <v>18.8592510223389</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G782" t="n">
-        <v>19.65283203125</v>
+        <v>19.6528339385986</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G784" t="n">
-        <v>19.6995162963867</v>
+        <v>19.6995182037354</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G787" t="n">
-        <v>18.952615737915</v>
+        <v>18.9526176452637</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G788" t="n">
-        <v>18.2990779876709</v>
+        <v>18.2990798950195</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G789" t="n">
-        <v>18.5044784545898</v>
+        <v>18.5044765472412</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G790" t="n">
-        <v>18.355094909668</v>
+        <v>18.3550968170166</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>19.4006462097168</v>
       </c>
       <c r="G791" t="n">
-        <v>18.6538524627686</v>
+        <v>18.6538581848145</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>19.1287651062012</v>
       </c>
       <c r="G792" t="n">
-        <v>18.3924407958984</v>
+        <v>18.3924388885498</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G793" t="n">
-        <v>18.6725292205811</v>
+        <v>18.6725273132324</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G794" t="n">
-        <v>18.6725292205811</v>
+        <v>18.6725273132324</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G795" t="n">
-        <v>18.5231475830078</v>
+        <v>18.5231456756592</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G796" t="n">
-        <v>18.6725292205811</v>
+        <v>18.6725273132324</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G798" t="n">
-        <v>18.6725292205811</v>
+        <v>18.6725273132324</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G800" t="n">
-        <v>19.9329242706299</v>
+        <v>19.9329223632812</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G801" t="n">
-        <v>20.2596912384033</v>
+        <v>20.259693145752</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>21.5077228546143</v>
       </c>
       <c r="G803" t="n">
-        <v>20.6798248291016</v>
+        <v>20.6798229217529</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G804" t="n">
-        <v>21.1466388702393</v>
+        <v>21.1466369628906</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G805" t="n">
-        <v>21.940221786499</v>
+        <v>21.9402198791504</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G807" t="n">
-        <v>22.8271675109863</v>
+        <v>22.8271656036377</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G808" t="n">
-        <v>23.0605735778809</v>
+        <v>23.0605716705322</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G809" t="n">
-        <v>23.3406620025635</v>
+        <v>23.3406600952148</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G811" t="n">
-        <v>22.9205284118652</v>
+        <v>22.920524597168</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G812" t="n">
-        <v>23.4340209960938</v>
+        <v>23.4340229034424</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G819" t="n">
-        <v>22.7338027954102</v>
+        <v>22.7338008880615</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G822" t="n">
-        <v>23.3406620025635</v>
+        <v>23.3406600952148</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G827" t="n">
-        <v>22.8271675109863</v>
+        <v>22.8271656036377</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G828" t="n">
-        <v>23.0605735778809</v>
+        <v>23.0605716705322</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G829" t="n">
-        <v>23.1072521209717</v>
+        <v>23.1072540283203</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G830" t="n">
-        <v>22.8271675109863</v>
+        <v>22.8271656036377</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G831" t="n">
-        <v>22.8271675109863</v>
+        <v>22.8271656036377</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G832" t="n">
-        <v>23.293981552124</v>
+        <v>23.2939796447754</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G834" t="n">
-        <v>23.1072521209717</v>
+        <v>23.1072540283203</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G835" t="n">
-        <v>23.3406620025635</v>
+        <v>23.3406600952148</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G837" t="n">
-        <v>23.7141094207764</v>
+        <v>23.714111328125</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G838" t="n">
-        <v>22.8271675109863</v>
+        <v>22.8271656036377</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G839" t="n">
-        <v>21.613452911377</v>
+        <v>21.6134510040283</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>22.8671283721924</v>
       </c>
       <c r="G841" t="n">
-        <v>21.9869003295898</v>
+        <v>21.9868984222412</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G846" t="n">
-        <v>20.8198680877686</v>
+        <v>20.8198661804199</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G848" t="n">
-        <v>20.4464206695557</v>
+        <v>20.446418762207</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G853" t="n">
-        <v>24.5076904296875</v>
+        <v>24.5076942443848</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G854" t="n">
-        <v>24.8344593048096</v>
+        <v>24.8344612121582</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G856" t="n">
-        <v>24.5076904296875</v>
+        <v>24.5076942443848</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G857" t="n">
-        <v>24.2276058197021</v>
+        <v>24.2276039123535</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G859" t="n">
-        <v>23.4340209960938</v>
+        <v>23.4340229034424</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G862" t="n">
-        <v>23.3406620025635</v>
+        <v>23.3406600952148</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G866" t="n">
-        <v>24.1342430114746</v>
+        <v>24.134241104126</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G867" t="n">
-        <v>24.1342430114746</v>
+        <v>24.134241104126</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G872" t="n">
-        <v>24.5076904296875</v>
+        <v>24.5076942443848</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G877" t="n">
-        <v>25.1145496368408</v>
+        <v>25.1145515441895</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G878" t="n">
-        <v>25.1145496368408</v>
+        <v>25.1145515441895</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>23.3040790557861</v>
       </c>
       <c r="G883" t="n">
-        <v>22.4070320129395</v>
+        <v>22.4070339202881</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G887" t="n">
-        <v>22.8271675109863</v>
+        <v>22.8271656036377</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>25.0518856048584</v>
       </c>
       <c r="G889" t="n">
-        <v>24.0875625610352</v>
+        <v>24.0875606536865</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G891" t="n">
-        <v>24.5543746948242</v>
+        <v>24.5543727874756</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G892" t="n">
-        <v>24.5076904296875</v>
+        <v>24.5076942443848</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G893" t="n">
-        <v>24.3676490783691</v>
+        <v>24.3676528930664</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G896" t="n">
-        <v>24.3676490783691</v>
+        <v>24.3676528930664</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G899" t="n">
-        <v>23.0605735778809</v>
+        <v>23.0605716705322</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G905" t="n">
-        <v>24.8344593048096</v>
+        <v>24.8344612121582</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G906" t="n">
-        <v>24.4610118865967</v>
+        <v>24.461009979248</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G907" t="n">
-        <v>24.4610118865967</v>
+        <v>24.461009979248</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G910" t="n">
-        <v>23.7141094207764</v>
+        <v>23.714111328125</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>26.0228881835938</v>
       </c>
       <c r="G913" t="n">
-        <v>25.0211849212646</v>
+        <v>25.0211868286133</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>25.0518856048584</v>
       </c>
       <c r="G915" t="n">
-        <v>24.0875625610352</v>
+        <v>24.0875606536865</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G917" t="n">
-        <v>22.7338027954102</v>
+        <v>22.7338008880615</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G918" t="n">
-        <v>23.3406620025635</v>
+        <v>23.3406600952148</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G919" t="n">
-        <v>23.4340209960938</v>
+        <v>23.4340229034424</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G921" t="n">
-        <v>21.3800430297852</v>
+        <v>21.3800449371338</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G922" t="n">
-        <v>21.0532760620117</v>
+        <v>21.0532779693604</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G923" t="n">
-        <v>21.2866840362549</v>
+        <v>21.2866821289062</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G925" t="n">
-        <v>20.3063735961914</v>
+        <v>20.30637550354</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G927" t="n">
-        <v>21.1466388702393</v>
+        <v>21.1466369628906</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G929" t="n">
-        <v>21.1466388702393</v>
+        <v>21.1466369628906</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G931" t="n">
-        <v>20.726505279541</v>
+        <v>20.7265071868896</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G934" t="n">
-        <v>21.4734077453613</v>
+        <v>21.4734058380127</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G935" t="n">
-        <v>21.3800430297852</v>
+        <v>21.3800449371338</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G938" t="n">
-        <v>21.1466388702393</v>
+        <v>21.1466369628906</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G939" t="n">
-        <v>21.0532760620117</v>
+        <v>21.0532779693604</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>19.1870250701904</v>
       </c>
       <c r="G944" t="n">
-        <v>18.4484596252441</v>
+        <v>18.4484558105469</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G945" t="n">
-        <v>19.7461986541748</v>
+        <v>19.7461967468262</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>20.0026683807373</v>
       </c>
       <c r="G948" t="n">
-        <v>19.232702255249</v>
+        <v>19.2327060699463</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G949" t="n">
-        <v>18.0936813354492</v>
+        <v>18.093677520752</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G951" t="n">
-        <v>16.9359836578369</v>
+        <v>16.9359817504883</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G952" t="n">
-        <v>16.7119102478027</v>
+        <v>16.7119121551514</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G955" t="n">
-        <v>18.5418224334717</v>
+        <v>18.541820526123</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G956" t="n">
-        <v>19.7928791046143</v>
+        <v>19.7928771972656</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G957" t="n">
-        <v>19.4194278717041</v>
+        <v>19.4194297790527</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G958" t="n">
-        <v>20.3063735961914</v>
+        <v>20.30637550354</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G959" t="n">
-        <v>20.3063735961914</v>
+        <v>20.30637550354</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G964" t="n">
-        <v>21.5200901031494</v>
+        <v>21.5200881958008</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G967" t="n">
-        <v>22.1736259460449</v>
+        <v>22.1736278533936</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G971" t="n">
-        <v>20.3530521392822</v>
+        <v>20.3530540466309</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G973" t="n">
-        <v>20.2596912384033</v>
+        <v>20.259693145752</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G974" t="n">
-        <v>20.4464206695557</v>
+        <v>20.446418762207</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G975" t="n">
-        <v>20.2596912384033</v>
+        <v>20.259693145752</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G976" t="n">
-        <v>20.3530521392822</v>
+        <v>20.3530540466309</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G978" t="n">
-        <v>20.3063735961914</v>
+        <v>20.30637550354</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G979" t="n">
-        <v>20.3530521392822</v>
+        <v>20.3530540466309</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G980" t="n">
-        <v>20.4464206695557</v>
+        <v>20.446418762207</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G984" t="n">
-        <v>21.5200901031494</v>
+        <v>21.5200881958008</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G985" t="n">
-        <v>21.4734077453613</v>
+        <v>21.4734058380127</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G986" t="n">
-        <v>21.3800430297852</v>
+        <v>21.3800449371338</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G988" t="n">
-        <v>21.5200901031494</v>
+        <v>21.5200881958008</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G989" t="n">
-        <v>22.1736259460449</v>
+        <v>22.1736278533936</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>19.3229656219482</v>
       </c>
       <c r="G995" t="n">
-        <v>18.5791664123535</v>
+        <v>18.5791645050049</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G996" t="n">
-        <v>18.952615737915</v>
+        <v>18.9526176452637</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G999" t="n">
-        <v>20.8198680877686</v>
+        <v>20.8198661804199</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1002" t="n">
-        <v>20.3530521392822</v>
+        <v>20.3530540466309</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1004" t="n">
-        <v>20.4464206695557</v>
+        <v>20.446418762207</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1005" t="n">
-        <v>19.9329242706299</v>
+        <v>19.9329223632812</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G1006" t="n">
-        <v>19.7461986541748</v>
+        <v>19.7461967468262</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G1007" t="n">
-        <v>20.2596912384033</v>
+        <v>20.259693145752</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1010" t="n">
-        <v>20.8198680877686</v>
+        <v>20.8198661804199</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1011" t="n">
-        <v>20.8198680877686</v>
+        <v>20.8198661804199</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G1013" t="n">
-        <v>20.0729694366455</v>
+        <v>20.0729675292969</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G1014" t="n">
-        <v>20.2596912384033</v>
+        <v>20.259693145752</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1019" t="n">
-        <v>18.2057132720947</v>
+        <v>18.2057151794434</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>18.5655822753906</v>
       </c>
       <c r="G1020" t="n">
-        <v>17.8509368896484</v>
+        <v>17.8509349822998</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>17.7887802124023</v>
       </c>
       <c r="G1022" t="n">
-        <v>17.1040344238281</v>
+        <v>17.1040325164795</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.0853633880615</v>
+        <v>17.0853652954102</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G1025" t="n">
-        <v>16.8312015533447</v>
+        <v>16.8312034606934</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G1026" t="n">
-        <v>16.7935466766357</v>
+        <v>16.7935485839844</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>16.6624164581299</v>
       </c>
       <c r="G1028" t="n">
-        <v>16.1534328460693</v>
+        <v>16.153434753418</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G1029" t="n">
-        <v>16.7182426452637</v>
+        <v>16.718240737915</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1034" t="n">
-        <v>18.1490821838379</v>
+        <v>18.1490802764893</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1035" t="n">
-        <v>18.1302547454834</v>
+        <v>18.1302528381348</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G1037" t="n">
-        <v>18.8268489837646</v>
+        <v>18.826847076416</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G1040" t="n">
-        <v>18.6574077606201</v>
+        <v>18.6574058532715</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1041" t="n">
-        <v>18.1302547454834</v>
+        <v>18.1302528381348</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>18.3908023834229</v>
       </c>
       <c r="G1042" t="n">
-        <v>17.8290252685547</v>
+        <v>17.8290233612061</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>18.8763046264648</v>
       </c>
       <c r="G1043" t="n">
-        <v>18.2996940612793</v>
+        <v>18.2996959686279</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G1045" t="n">
-        <v>18.4691371917725</v>
+        <v>18.4691352844238</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G1047" t="n">
-        <v>19.7211227416992</v>
+        <v>19.7211246490479</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1050" t="n">
-        <v>20.7095317840576</v>
+        <v>20.7095336914062</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G1053" t="n">
-        <v>20.897798538208</v>
+        <v>20.8978023529053</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>22.6243762969971</v>
       </c>
       <c r="G1057" t="n">
-        <v>21.9332790374756</v>
+        <v>21.933277130127</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1058" t="n">
-        <v>22.5451469421387</v>
+        <v>22.5451507568359</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1059" t="n">
-        <v>22.5451469421387</v>
+        <v>22.5451507568359</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G1061" t="n">
-        <v>22.3098125457764</v>
+        <v>22.309814453125</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1062" t="n">
-        <v>22.4510135650635</v>
+        <v>22.4510116577148</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G1064" t="n">
-        <v>21.886209487915</v>
+        <v>21.8862113952637</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1068" t="n">
-        <v>20.7095317840576</v>
+        <v>20.7095336914062</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1071" t="n">
-        <v>20.6624660491943</v>
+        <v>20.6624641418457</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G1072" t="n">
-        <v>20.2859268188477</v>
+        <v>20.285924911499</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G1076" t="n">
-        <v>19.5328540802002</v>
+        <v>19.5328559875488</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1077" t="n">
-        <v>20.0976600646973</v>
+        <v>20.0976581573486</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1079" t="n">
-        <v>19.5799198150635</v>
+        <v>19.5799217224121</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>20.245418548584</v>
       </c>
       <c r="G1083" t="n">
-        <v>19.6269874572754</v>
+        <v>19.6269855499268</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G1085" t="n">
-        <v>18.8739147186279</v>
+        <v>18.8739128112793</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1086" t="n">
-        <v>18.9209823608398</v>
+        <v>18.9209804534912</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G1092" t="n">
-        <v>18.2620391845703</v>
+        <v>18.2620429992676</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>18.2354412078857</v>
       </c>
       <c r="G1095" t="n">
-        <v>17.6784076690674</v>
+        <v>17.678409576416</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G1096" t="n">
-        <v>16.8876819610596</v>
+        <v>16.8876800537109</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G1097" t="n">
-        <v>18.0172920227051</v>
+        <v>18.0172901153564</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G1101" t="n">
-        <v>18.6762313842773</v>
+        <v>18.676233291626</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G1102" t="n">
-        <v>18.0361194610596</v>
+        <v>18.0361213684082</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>18.9734058380127</v>
       </c>
       <c r="G1104" t="n">
-        <v>18.3938293457031</v>
+        <v>18.3938312530518</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1106" t="n">
-        <v>18.1302547454834</v>
+        <v>18.1302528381348</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1108" t="n">
-        <v>18.1490821838379</v>
+        <v>18.1490802764893</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1110" t="n">
-        <v>18.1490821838379</v>
+        <v>18.1490802764893</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>18.6626834869385</v>
       </c>
       <c r="G1111" t="n">
-        <v>18.0925979614258</v>
+        <v>18.0925998687744</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1113" t="n">
-        <v>18.9209823608398</v>
+        <v>18.9209804534912</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1115" t="n">
-        <v>20.4741973876953</v>
+        <v>20.4741954803467</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1119" t="n">
-        <v>20.3800640106201</v>
+        <v>20.3800621032715</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1122" t="n">
-        <v>20.4741973876953</v>
+        <v>20.4741954803467</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1124" t="n">
-        <v>20.7095317840576</v>
+        <v>20.7095336914062</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1126" t="n">
-        <v>22.3568801879883</v>
+        <v>22.3568820953369</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1129" t="n">
-        <v>24.6161022186279</v>
+        <v>24.6161003112793</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1130" t="n">
-        <v>23.2040901184082</v>
+        <v>23.2040882110596</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1131" t="n">
-        <v>23.2040901184082</v>
+        <v>23.2040882110596</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1132" t="n">
-        <v>23.2511577606201</v>
+        <v>23.2511558532715</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1134" t="n">
-        <v>23.2511577606201</v>
+        <v>23.2511558532715</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1135" t="n">
-        <v>23.533561706543</v>
+        <v>23.5335597991943</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1138" t="n">
-        <v>22.5451469421387</v>
+        <v>22.5451507568359</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1139" t="n">
-        <v>21.9803447723389</v>
+        <v>21.9803428649902</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1140" t="n">
-        <v>22.3568801879883</v>
+        <v>22.3568820953369</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>23.3526306152344</v>
       </c>
       <c r="G1142" t="n">
-        <v>22.6392860412598</v>
+        <v>22.6392822265625</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1144" t="n">
-        <v>21.9803447723389</v>
+        <v>21.9803428649902</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>22.7214775085449</v>
       </c>
       <c r="G1145" t="n">
-        <v>22.0274124145508</v>
+        <v>22.0274105072021</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1146" t="n">
-        <v>22.6863498687744</v>
+        <v>22.686351776123</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1147" t="n">
-        <v>23.533561706543</v>
+        <v>23.5335597991943</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1149" t="n">
-        <v>24.1924991607666</v>
+        <v>24.192497253418</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>22.9642276763916</v>
       </c>
       <c r="G1153" t="n">
-        <v>22.2627468109131</v>
+        <v>22.2627449035645</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1155" t="n">
-        <v>22.6863498687744</v>
+        <v>22.686351776123</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1157" t="n">
-        <v>22.3568801879883</v>
+        <v>22.3568820953369</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1158" t="n">
-        <v>22.3568801879883</v>
+        <v>22.3568820953369</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1159" t="n">
-        <v>21.9803447723389</v>
+        <v>21.9803428649902</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1160" t="n">
-        <v>22.3568801879883</v>
+        <v>22.3568820953369</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1163" t="n">
-        <v>21.9803447723389</v>
+        <v>21.9803428649902</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G1165" t="n">
-        <v>21.4626064300537</v>
+        <v>21.4626045227051</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1166" t="n">
-        <v>21.6508750915527</v>
+        <v>21.6508731842041</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G1167" t="n">
-        <v>21.886209487915</v>
+        <v>21.8862113952637</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G1169" t="n">
-        <v>21.4155368804932</v>
+        <v>21.4155387878418</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G1170" t="n">
-        <v>21.2272720336914</v>
+        <v>21.2272701263428</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G1172" t="n">
-        <v>21.7920761108398</v>
+        <v>21.7920742034912</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1173" t="n">
-        <v>21.6508750915527</v>
+        <v>21.6508731842041</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>22.9642276763916</v>
       </c>
       <c r="G1174" t="n">
-        <v>22.2627468109131</v>
+        <v>22.2627449035645</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1175" t="n">
-        <v>21.6508750915527</v>
+        <v>21.6508731842041</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1179" t="n">
-        <v>22.5451469421387</v>
+        <v>22.5451507568359</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1180" t="n">
-        <v>22.3568801879883</v>
+        <v>22.3568820953369</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.9803447723389</v>
+        <v>21.9803428649902</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G1182" t="n">
-        <v>21.7920761108398</v>
+        <v>21.7920742034912</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1184" t="n">
-        <v>22.3568801879883</v>
+        <v>22.3568820953369</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1185" t="n">
-        <v>23.3452911376953</v>
+        <v>23.3452892303467</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1186" t="n">
-        <v>24.6161022186279</v>
+        <v>24.6161003112793</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G1187" t="n">
-        <v>24.5219688415527</v>
+        <v>24.5219669342041</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G1188" t="n">
-        <v>23.8159618377686</v>
+        <v>23.8159599304199</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1189" t="n">
-        <v>23.2040901184082</v>
+        <v>23.2040882110596</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1190" t="n">
-        <v>24.0983619689941</v>
+        <v>24.0983638763428</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1191" t="n">
-        <v>23.9100952148438</v>
+        <v>23.9100971221924</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>25.9257888793945</v>
       </c>
       <c r="G1192" t="n">
-        <v>25.1338424682617</v>
+        <v>25.1338405609131</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.7573051452637</v>
+        <v>24.757303237915</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1196" t="n">
-        <v>24.2395668029785</v>
+        <v>24.2395687103271</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1198" t="n">
-        <v>24.4278354644775</v>
+        <v>24.4278335571289</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1205" t="n">
-        <v>24.1924991607666</v>
+        <v>24.192497253418</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>25.9257888793945</v>
       </c>
       <c r="G1207" t="n">
-        <v>25.1338424682617</v>
+        <v>25.1338405609131</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>26.1685390472412</v>
       </c>
       <c r="G1208" t="n">
-        <v>25.3691749572754</v>
+        <v>25.369176864624</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G1210" t="n">
-        <v>25.1809062957764</v>
+        <v>25.180908203125</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1211" t="n">
-        <v>23.9100952148438</v>
+        <v>23.9100971221924</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G1212" t="n">
-        <v>23.4394245147705</v>
+        <v>23.4394226074219</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1213" t="n">
-        <v>23.9100952148438</v>
+        <v>23.9100971221924</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1214" t="n">
-        <v>23.2040901184082</v>
+        <v>23.2040882110596</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1217" t="n">
-        <v>22.9687538146973</v>
+        <v>22.9687519073486</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1218" t="n">
-        <v>23.1099548339844</v>
+        <v>23.1099529266357</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1220" t="n">
-        <v>23.0628871917725</v>
+        <v>23.0628890991211</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1223" t="n">
-        <v>23.3452911376953</v>
+        <v>23.3452892303467</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1226" t="n">
-        <v>23.7218265533447</v>
+        <v>23.7218284606934</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1227" t="n">
-        <v>24.2395668029785</v>
+        <v>24.2395687103271</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1229" t="n">
-        <v>23.1099548339844</v>
+        <v>23.1099529266357</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1231" t="n">
-        <v>23.0628871917725</v>
+        <v>23.0628890991211</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1233" t="n">
-        <v>23.1099548339844</v>
+        <v>23.1099529266357</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1235" t="n">
-        <v>23.0628871917725</v>
+        <v>23.0628890991211</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1236" t="n">
-        <v>22.4510135650635</v>
+        <v>22.4510116577148</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1237" t="n">
-        <v>22.3568801879883</v>
+        <v>22.3568820953369</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1238" t="n">
-        <v>22.6863498687744</v>
+        <v>22.686351776123</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G1239" t="n">
-        <v>22.3098125457764</v>
+        <v>22.309814453125</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1240" t="n">
-        <v>21.9803447723389</v>
+        <v>21.9803428649902</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G1243" t="n">
-        <v>22.4980812072754</v>
+        <v>22.498083114624</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>22.915678024292</v>
       </c>
       <c r="G1246" t="n">
-        <v>22.2156772613525</v>
+        <v>22.2156791687012</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1247" t="n">
-        <v>22.4510135650635</v>
+        <v>22.4510116577148</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G1248" t="n">
-        <v>22.4980812072754</v>
+        <v>22.498083114624</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1249" t="n">
-        <v>23.2511577606201</v>
+        <v>23.2511558532715</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1250" t="n">
-        <v>23.533561706543</v>
+        <v>23.5335597991943</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1254" t="n">
-        <v>22.9687538146973</v>
+        <v>22.9687519073486</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1257" t="n">
-        <v>22.9687538146973</v>
+        <v>22.9687519073486</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1258" t="n">
-        <v>23.0628871917725</v>
+        <v>23.0628890991211</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1261" t="n">
-        <v>22.4510135650635</v>
+        <v>22.4510116577148</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1262" t="n">
-        <v>22.6863498687744</v>
+        <v>22.686351776123</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1263" t="n">
-        <v>23.7218265533447</v>
+        <v>23.7218284606934</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1266" t="n">
-        <v>24.4278354644775</v>
+        <v>24.4278335571289</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>26.8482418060303</v>
       </c>
       <c r="G1272" t="n">
-        <v>26.0281181335449</v>
+        <v>26.0281162261963</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>26.4598407745361</v>
       </c>
       <c r="G1273" t="n">
-        <v>25.6515789031982</v>
+        <v>25.6515808105469</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>27.1880931854248</v>
       </c>
       <c r="G1275" t="n">
-        <v>26.3575878143311</v>
+        <v>26.3575859069824</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>27.1880931854248</v>
       </c>
       <c r="G1276" t="n">
-        <v>26.3575878143311</v>
+        <v>26.3575859069824</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>27.1880931854248</v>
       </c>
       <c r="G1277" t="n">
-        <v>26.3575878143311</v>
+        <v>26.3575859069824</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>26.7996921539307</v>
       </c>
       <c r="G1279" t="n">
-        <v>26.148250579834</v>
+        <v>26.1482486724854</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1286" t="n">
-        <v>25.7219181060791</v>
+        <v>25.7219200134277</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>26.5569400787354</v>
       </c>
       <c r="G1287" t="n">
-        <v>25.9113998413086</v>
+        <v>25.91139793396</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>26.7996921539307</v>
       </c>
       <c r="G1288" t="n">
-        <v>26.148250579834</v>
+        <v>26.1482486724854</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G1289" t="n">
-        <v>25.3429584503174</v>
+        <v>25.342960357666</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>26.6054916381836</v>
       </c>
       <c r="G1290" t="n">
-        <v>25.9587707519531</v>
+        <v>25.9587688446045</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1291" t="n">
-        <v>25.7219181060791</v>
+        <v>25.7219200134277</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>26.2656402587891</v>
       </c>
       <c r="G1295" t="n">
-        <v>25.6271800994873</v>
+        <v>25.6271781921387</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>25.7315883636475</v>
       </c>
       <c r="G1298" t="n">
-        <v>25.1061096191406</v>
+        <v>25.106107711792</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1302" t="n">
-        <v>24.3955593109131</v>
+        <v>24.3955612182617</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G1309" t="n">
-        <v>24.6797790527344</v>
+        <v>24.6797771453857</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1313" t="n">
-        <v>24.3955593109131</v>
+        <v>24.3955612182617</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1315" t="n">
-        <v>23.7323780059814</v>
+        <v>23.7323799133301</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1317" t="n">
-        <v>24.0639686584473</v>
+        <v>24.0639705657959</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1318" t="n">
-        <v>23.5428981781006</v>
+        <v>23.5429000854492</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1321" t="n">
-        <v>24.1587085723877</v>
+        <v>24.1587104797363</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1322" t="n">
-        <v>23.7323780059814</v>
+        <v>23.7323799133301</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1324" t="n">
-        <v>24.4902973175049</v>
+        <v>24.4902992248535</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1326" t="n">
-        <v>23.5428981781006</v>
+        <v>23.5429000854492</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1327" t="n">
-        <v>23.8744888305664</v>
+        <v>23.874490737915</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1328" t="n">
-        <v>24.2534484863281</v>
+        <v>24.2534465789795</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1329" t="n">
-        <v>24.2534484863281</v>
+        <v>24.2534465789795</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1330" t="n">
-        <v>23.7323780059814</v>
+        <v>23.7323799133301</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1331" t="n">
-        <v>24.5850410461426</v>
+        <v>24.5850391387939</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1336" t="n">
-        <v>23.8744888305664</v>
+        <v>23.874490737915</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1337" t="n">
-        <v>23.4955291748047</v>
+        <v>23.4955272674561</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1339" t="n">
-        <v>23.0691967010498</v>
+        <v>23.0691986083984</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1340" t="n">
-        <v>23.0691967010498</v>
+        <v>23.0691986083984</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1341" t="n">
-        <v>23.0691967010498</v>
+        <v>23.0691986083984</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1345" t="n">
-        <v>21.7902088165283</v>
+        <v>21.7902069091797</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1350" t="n">
-        <v>21.1743965148926</v>
+        <v>21.1743984222412</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1351" t="n">
-        <v>21.1743965148926</v>
+        <v>21.1743984222412</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1357" t="n">
-        <v>20.7480697631836</v>
+        <v>20.748067855835</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1361" t="n">
-        <v>21.1743965148926</v>
+        <v>21.1743984222412</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1362" t="n">
-        <v>20.7480697631836</v>
+        <v>20.748067855835</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1363" t="n">
-        <v>20.5112190246582</v>
+        <v>20.5112171173096</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G1365" t="n">
-        <v>18.815372467041</v>
+        <v>18.8153705596924</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>18.9734058380127</v>
       </c>
       <c r="G1367" t="n">
-        <v>18.5122032165527</v>
+        <v>18.5122051239014</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>18.8763046264648</v>
       </c>
       <c r="G1368" t="n">
-        <v>18.4174613952637</v>
+        <v>18.4174633026123</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>18.0218200683594</v>
       </c>
       <c r="G1372" t="n">
-        <v>17.5837497711182</v>
+        <v>17.5837478637695</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>19.1093444824219</v>
       </c>
       <c r="G1374" t="n">
-        <v>18.6448383331299</v>
+        <v>18.6448364257812</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G1377" t="n">
-        <v>20.0848865509033</v>
+        <v>20.0848846435547</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1378" t="n">
-        <v>19.705924987793</v>
+        <v>19.7059288024902</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1380" t="n">
-        <v>20.6533260345459</v>
+        <v>20.6533279418945</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1384" t="n">
-        <v>21.7902088165283</v>
+        <v>21.7902069091797</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1387" t="n">
-        <v>20.5112190246582</v>
+        <v>20.5112171173096</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1390" t="n">
-        <v>19.8065509796143</v>
+        <v>19.8065528869629</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1393" t="n">
-        <v>20.7822437286377</v>
+        <v>20.7822418212891</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1396" t="n">
-        <v>22.7336254119873</v>
+        <v>22.7336273193359</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>21.9042892456055</v>
+        <v>21.9042911529541</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1402" t="n">
-        <v>21.6603660583496</v>
+        <v>21.6603679656982</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1406" t="n">
-        <v>23.0751190185547</v>
+        <v>23.0751209259033</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1408" t="n">
-        <v>23.0751190185547</v>
+        <v>23.0751209259033</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1409" t="n">
-        <v>23.3678283691406</v>
+        <v>23.367826461792</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>24.3435211181641</v>
+        <v>24.3435192108154</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>24.75</v>
       </c>
       <c r="G1414" t="n">
-        <v>24.1483821868896</v>
+        <v>24.148380279541</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>24.1971645355225</v>
+        <v>24.1971664428711</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1416" t="n">
-        <v>23.3678283691406</v>
+        <v>23.367826461792</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1417" t="n">
-        <v>22.7336254119873</v>
+        <v>22.7336273193359</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1418" t="n">
-        <v>22.7336254119873</v>
+        <v>22.7336273193359</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>23.25</v>
       </c>
       <c r="G1420" t="n">
-        <v>22.6848449707031</v>
+        <v>22.6848430633545</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1422" t="n">
-        <v>22.3921356201172</v>
+        <v>22.3921375274658</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1428" t="n">
-        <v>22.2945652008057</v>
+        <v>22.2945671081543</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>21.6603660583496</v>
+        <v>21.6603679656982</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1430" t="n">
-        <v>21.5627975463867</v>
+        <v>21.5627956390381</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1432" t="n">
-        <v>22.14821434021</v>
+        <v>22.1482124328613</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>22.25</v>
       </c>
       <c r="G1433" t="n">
-        <v>21.7091522216797</v>
+        <v>21.7091503143311</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1438" t="n">
-        <v>22.2945652008057</v>
+        <v>22.2945671081543</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>22.25</v>
       </c>
       <c r="G1440" t="n">
-        <v>21.7091522216797</v>
+        <v>21.7091503143311</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1441" t="n">
-        <v>21.5627975463867</v>
+        <v>21.5627956390381</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>22.25</v>
       </c>
       <c r="G1446" t="n">
-        <v>21.7091522216797</v>
+        <v>21.7091503143311</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1447" t="n">
-        <v>21.9042892456055</v>
+        <v>21.9042911529541</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1448" t="n">
-        <v>21.9042892456055</v>
+        <v>21.9042911529541</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1449" t="n">
-        <v>22.2945652008057</v>
+        <v>22.2945671081543</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1451" t="n">
-        <v>21.9042892456055</v>
+        <v>21.9042911529541</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1452" t="n">
-        <v>21.6603660583496</v>
+        <v>21.6603679656982</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1453" t="n">
-        <v>21.9042892456055</v>
+        <v>21.9042911529541</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1454" t="n">
-        <v>21.6603660583496</v>
+        <v>21.6603679656982</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>22</v>
       </c>
       <c r="G1456" t="n">
-        <v>21.4652271270752</v>
+        <v>21.4652290344238</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1460" t="n">
-        <v>21.3676605224609</v>
+        <v>21.3676586151123</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1462" t="n">
-        <v>21.2700901031494</v>
+        <v>21.2700881958008</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>19.6114120483398</v>
+        <v>19.6114139556885</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1466" t="n">
-        <v>19.201623916626</v>
+        <v>19.2016220092773</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1467" t="n">
-        <v>18.8113441467285</v>
+        <v>18.8113460540771</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>18.8308582305908</v>
+        <v>18.8308601379395</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1469" t="n">
-        <v>19.0845394134521</v>
+        <v>19.0845375061035</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1470" t="n">
-        <v>19.0650272369385</v>
+        <v>19.0650234222412</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1472" t="n">
-        <v>18.9869689941406</v>
+        <v>18.9869709014893</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1475" t="n">
-        <v>20.0504760742188</v>
+        <v>20.0504741668701</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>20.5</v>
       </c>
       <c r="G1476" t="n">
-        <v>20.0016899108887</v>
+        <v>20.0016918182373</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>20.5</v>
       </c>
       <c r="G1479" t="n">
-        <v>20.0016899108887</v>
+        <v>20.0016918182373</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1481" t="n">
-        <v>19.5626258850098</v>
+        <v>19.5626277923584</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1483" t="n">
-        <v>19.5626258850098</v>
+        <v>19.5626277923584</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1486" t="n">
-        <v>19.2406482696533</v>
+        <v>19.240650177002</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1487" t="n">
-        <v>18.8308582305908</v>
+        <v>18.8308601379395</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1489" t="n">
-        <v>18.2844715118408</v>
+        <v>18.2844734191895</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1491" t="n">
-        <v>18.1088466644287</v>
+        <v>18.1088447570801</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1492" t="n">
-        <v>17.9722499847412</v>
+        <v>17.9722480773926</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1494" t="n">
-        <v>18.1088466644287</v>
+        <v>18.1088447570801</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.0307903289795</v>
+        <v>18.0307922363281</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1497" t="n">
-        <v>18.2844715118408</v>
+        <v>18.2844734191895</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1498" t="n">
-        <v>18.8113441467285</v>
+        <v>18.8113460540771</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1499" t="n">
-        <v>18.5576667785645</v>
+        <v>18.5576648712158</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1500" t="n">
-        <v>18.5186386108398</v>
+        <v>18.5186367034912</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1501" t="n">
-        <v>18.3820419311523</v>
+        <v>18.3820400238037</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1502" t="n">
-        <v>18.5576667785645</v>
+        <v>18.5576648712158</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1503" t="n">
-        <v>18.7528018951416</v>
+        <v>18.7528038024902</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1505" t="n">
-        <v>17.3087787628174</v>
+        <v>17.308780670166</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1506" t="n">
-        <v>18.1673908233643</v>
+        <v>18.1673889160156</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1508" t="n">
-        <v>16.6453075408936</v>
+        <v>16.6453094482422</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1509" t="n">
-        <v>18.3625259399414</v>
+        <v>18.36252784729</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1518" t="n">
-        <v>17.5234317779541</v>
+        <v>17.5234298706055</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1520" t="n">
-        <v>17.113639831543</v>
+        <v>17.1136417388916</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1522" t="n">
-        <v>17.347806930542</v>
+        <v>17.3478050231934</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1523" t="n">
-        <v>16.9965591430664</v>
+        <v>16.9965572357178</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1524" t="n">
-        <v>17.1331539154053</v>
+        <v>17.1331558227539</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>18</v>
       </c>
       <c r="G1529" t="n">
-        <v>17.5624599456787</v>
+        <v>17.5624580383301</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1530" t="n">
-        <v>17.0160732269287</v>
+        <v>17.0160713195801</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1535" t="n">
-        <v>17.3087787628174</v>
+        <v>17.308780670166</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>17.5</v>
       </c>
       <c r="G1536" t="n">
-        <v>17.074613571167</v>
+        <v>17.0746116638184</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1542" t="n">
-        <v>16.8280124664307</v>
+        <v>16.8280143737793</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>16.5715465545654</v>
+        <v>16.5715484619141</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1546" t="n">
-        <v>17.3803997039795</v>
+        <v>17.3803977966309</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1547" t="n">
-        <v>17.4987659454346</v>
+        <v>17.4987678527832</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1553" t="n">
-        <v>17.0844783782959</v>
+        <v>17.0844764709473</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1554" t="n">
-        <v>17.5974082946777</v>
+        <v>17.5974063873291</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1557" t="n">
-        <v>17.3212146759033</v>
+        <v>17.3212127685547</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1562" t="n">
-        <v>16.5715465545654</v>
+        <v>16.5715484619141</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1563" t="n">
-        <v>16.6307334899902</v>
+        <v>16.6307315826416</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1564" t="n">
-        <v>16.8280124664307</v>
+        <v>16.8280143737793</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1567" t="n">
-        <v>15.5654191970825</v>
+        <v>15.5654182434082</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="n">
-        <v>15.6837873458862</v>
+        <v>15.6837863922119</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>16.5</v>
       </c>
       <c r="G1570" t="n">
-        <v>16.2756271362305</v>
+        <v>16.2756290435791</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1571" t="n">
-        <v>16.2361698150635</v>
+        <v>16.2361717224121</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1572" t="n">
-        <v>15.920521736145</v>
+        <v>15.9205236434937</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1573" t="n">
-        <v>16.0191650390625</v>
+        <v>16.0191631317139</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>16.374267578125</v>
+        <v>16.3742694854736</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1575" t="n">
-        <v>16.8674697875977</v>
+        <v>16.867467880249</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1578" t="n">
-        <v>17.4593124389648</v>
+        <v>17.4593105316162</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1579" t="n">
-        <v>17.1042060852051</v>
+        <v>17.1042041778564</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1583" t="n">
-        <v>17.5579509735107</v>
+        <v>17.5579490661621</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1588" t="n">
-        <v>16.8674697875977</v>
+        <v>16.867467880249</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1590" t="n">
-        <v>16.7490997314453</v>
+        <v>16.7491016387939</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1594" t="n">
-        <v>16.9858360290527</v>
+        <v>16.9858379364014</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1595" t="n">
-        <v>17.5579509735107</v>
+        <v>17.5579490661621</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1596" t="n">
-        <v>17.8144130706787</v>
+        <v>17.8144149780273</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1605" t="n">
-        <v>19.2545604705811</v>
+        <v>19.2545623779297</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1609" t="n">
-        <v>19.2545604705811</v>
+        <v>19.2545623779297</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1612" t="n">
-        <v>19.136194229126</v>
+        <v>19.1361923217773</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1613" t="n">
-        <v>19.2545604705811</v>
+        <v>19.2545623779297</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1615" t="n">
-        <v>18.7613620758057</v>
+        <v>18.761360168457</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1618" t="n">
-        <v>19.136194229126</v>
+        <v>19.1361923217773</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1621" t="n">
-        <v>19.4518394470215</v>
+        <v>19.4518413543701</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1622" t="n">
-        <v>19.0770092010498</v>
+        <v>19.0770072937012</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1630" t="n">
-        <v>18.564079284668</v>
+        <v>18.5640811920166</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1634" t="n">
-        <v>18.0511493682861</v>
+        <v>18.0511512756348</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1635" t="n">
-        <v>16.9858360290527</v>
+        <v>16.9858379364014</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1636" t="n">
-        <v>17.5974082946777</v>
+        <v>17.5974063873291</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1644" t="n">
-        <v>17.3803997039795</v>
+        <v>17.3803977966309</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1645" t="n">
-        <v>17.9130535125732</v>
+        <v>17.9130554199219</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1652" t="n">
-        <v>18.4457130432129</v>
+        <v>18.4457111358643</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1655" t="n">
-        <v>18.4457130432129</v>
+        <v>18.4457111358643</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1656" t="n">
-        <v>18.8008155822754</v>
+        <v>18.800817489624</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>19.2940158843994</v>
+        <v>19.294017791748</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1659" t="n">
-        <v>19.0770092010498</v>
+        <v>19.0770072937012</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1662" t="n">
-        <v>17.9130535125732</v>
+        <v>17.9130554199219</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1665" t="n">
-        <v>17.9525108337402</v>
+        <v>17.9525127410889</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1677" t="n">
-        <v>17.6171360015869</v>
+        <v>17.6171340942383</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1680" t="n">
-        <v>18.8008155822754</v>
+        <v>18.800817489624</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1681" t="n">
-        <v>18.8600025177002</v>
+        <v>18.8600006103516</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1682" t="n">
-        <v>18.8600025177002</v>
+        <v>18.8600006103516</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1684" t="n">
-        <v>18.8600025177002</v>
+        <v>18.8600006103516</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1685" t="n">
-        <v>19.136194229126</v>
+        <v>19.1361923217773</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1691" t="n">
-        <v>19.1559219360352</v>
+        <v>19.1559200286865</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1692" t="n">
-        <v>19.4912967681885</v>
+        <v>19.4912986755371</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1693" t="n">
-        <v>19.1559219360352</v>
+        <v>19.1559200286865</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1699" t="n">
-        <v>21.0103549957275</v>
+        <v>21.0103569030762</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>21</v>
       </c>
       <c r="G1705" t="n">
-        <v>20.7144374847412</v>
+        <v>20.7144355773926</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>20.75</v>
       </c>
       <c r="G1706" t="n">
-        <v>20.4678363800049</v>
+        <v>20.4678344726562</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1712" t="n">
-        <v>18.8008155822754</v>
+        <v>18.800817489624</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1715" t="n">
-        <v>20.6651172637939</v>
+        <v>20.6651153564453</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1717" t="n">
-        <v>19.3926563262939</v>
+        <v>19.3926582336426</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>20</v>
       </c>
       <c r="G1718" t="n">
-        <v>19.7280330657959</v>
+        <v>19.7280349731445</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1720" t="n">
-        <v>17.8933258056641</v>
+        <v>17.8933277130127</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1724" t="n">
-        <v>18.7613620758057</v>
+        <v>18.761360168457</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1729" t="n">
-        <v>17.3014869689941</v>
+        <v>17.3014850616455</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1731" t="n">
-        <v>16.6307334899902</v>
+        <v>16.6307315826416</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1732" t="n">
-        <v>16.5123634338379</v>
+        <v>16.5123653411865</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>16.5</v>
       </c>
       <c r="G1734" t="n">
-        <v>16.2756271362305</v>
+        <v>16.2756290435791</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>15</v>
       </c>
       <c r="G1736" t="n">
-        <v>14.7960262298584</v>
+        <v>14.7960252761841</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1740" t="n">
-        <v>15.6837873458862</v>
+        <v>15.6837863922119</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1742" t="n">
-        <v>16.6307334899902</v>
+        <v>16.6307315826416</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1743" t="n">
-        <v>16.374267578125</v>
+        <v>16.3742694854736</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1747" t="n">
-        <v>16.9858360290527</v>
+        <v>16.9858379364014</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1748" t="n">
-        <v>17.1042060852051</v>
+        <v>17.1042041778564</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1758" t="n">
-        <v>19.2545604705811</v>
+        <v>19.2545623779297</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1759" t="n">
-        <v>20.1719150543213</v>
+        <v>20.1719169616699</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1761" t="n">
-        <v>19.3926563262939</v>
+        <v>19.3926582336426</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>21</v>
       </c>
       <c r="G1763" t="n">
-        <v>20.7144374847412</v>
+        <v>20.7144355773926</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>20.75</v>
       </c>
       <c r="G1764" t="n">
-        <v>20.4678363800049</v>
+        <v>20.4678344726562</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1766" t="n">
-        <v>20.615795135498</v>
+        <v>20.6157970428467</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1767" t="n">
-        <v>20.1719150543213</v>
+        <v>20.1719169616699</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1768" t="n">
-        <v>20.615795135498</v>
+        <v>20.6157970428467</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1772" t="n">
-        <v>20.4185161590576</v>
+        <v>20.418514251709</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>20.75</v>
       </c>
       <c r="G1773" t="n">
-        <v>20.4678363800049</v>
+        <v>20.4678344726562</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1784" t="n">
-        <v>22.2433586120605</v>
+        <v>22.2433567047119</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1785" t="n">
-        <v>22.3419971466064</v>
+        <v>22.3419990539551</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -55128,6 +55128,32 @@
         <v>28.7999992370605</v>
       </c>
       <c r="H2106" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2107" t="n">
+        <v>72624</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>28.7999992370605</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>28.2999992370605</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>28.4500007629395</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>28.3999996185303</v>
+      </c>
+      <c r="G2107" t="n">
+        <v>28.3999996185303</v>
+      </c>
+      <c r="H2107" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -447,7 +447,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G3" t="n">
-        <v>7.85125923156738</v>
+        <v>7.85125970840454</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G4" t="n">
-        <v>7.75996589660645</v>
+        <v>7.7599663734436</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G5" t="n">
-        <v>7.75996589660645</v>
+        <v>7.7599663734436</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G6" t="n">
-        <v>7.66867351531982</v>
+        <v>7.66867303848267</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>8.1253547668457</v>
       </c>
       <c r="G7" t="n">
-        <v>7.63945817947388</v>
+        <v>7.63945770263672</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.31955623626709</v>
       </c>
       <c r="G8" t="n">
-        <v>7.82204580307007</v>
+        <v>7.82204532623291</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.41859817504883</v>
       </c>
       <c r="G9" t="n">
-        <v>7.91516590118408</v>
+        <v>7.91516542434692</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.10884761810303</v>
       </c>
       <c r="G10" t="n">
-        <v>7.62393808364868</v>
+        <v>7.62393760681152</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>8.42830753326416</v>
       </c>
       <c r="G11" t="n">
-        <v>7.92429351806641</v>
+        <v>7.92429399490356</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.95154619216919</v>
       </c>
       <c r="G16" t="n">
-        <v>7.47604370117188</v>
+        <v>7.47604322433472</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>7.88940191268921</v>
       </c>
       <c r="G17" t="n">
-        <v>7.41761541366577</v>
+        <v>7.41761493682861</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.00106716156006</v>
       </c>
       <c r="G18" t="n">
-        <v>7.52260303497314</v>
+        <v>7.5226035118103</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>7.8651270866394</v>
       </c>
       <c r="G19" t="n">
-        <v>7.39479303359985</v>
+        <v>7.3947925567627</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>7.95251703262329</v>
       </c>
       <c r="G20" t="n">
-        <v>7.47695589065552</v>
+        <v>7.47695636749268</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>7.97193717956543</v>
       </c>
       <c r="G21" t="n">
-        <v>7.49521446228027</v>
+        <v>7.49521541595459</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>8.08068943023682</v>
       </c>
       <c r="G22" t="n">
-        <v>7.59746360778809</v>
+        <v>7.59746313095093</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>8.24381828308105</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75083684921265</v>
+        <v>7.75083780288696</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G24" t="n">
-        <v>7.66867351531982</v>
+        <v>7.66867303848267</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G25" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>8.37101936340332</v>
       </c>
       <c r="G26" t="n">
-        <v>7.87043237686157</v>
+        <v>7.87043142318726</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G27" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.45743942260742</v>
       </c>
       <c r="G28" t="n">
-        <v>7.95168399810791</v>
+        <v>7.95168447494507</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.47394561767578</v>
       </c>
       <c r="G30" t="n">
-        <v>7.96720266342163</v>
+        <v>7.96720361709595</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G31" t="n">
-        <v>7.85125923156738</v>
+        <v>7.85125970840454</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>8.25741195678711</v>
       </c>
       <c r="G32" t="n">
-        <v>7.76361846923828</v>
+        <v>7.76361799240112</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.20497798919678</v>
       </c>
       <c r="G33" t="n">
-        <v>7.71432113647461</v>
+        <v>7.71431970596313</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G34" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G35" t="n">
-        <v>7.66867351531982</v>
+        <v>7.66867303848267</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G36" t="n">
-        <v>7.66867351531982</v>
+        <v>7.66867303848267</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G38" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G39" t="n">
-        <v>7.85125923156738</v>
+        <v>7.85125970840454</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>8.12923908233643</v>
       </c>
       <c r="G41" t="n">
-        <v>7.64311027526855</v>
+        <v>7.6431097984314</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.23410797119141</v>
       </c>
       <c r="G42" t="n">
-        <v>7.74170732498169</v>
+        <v>7.74170827865601</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>8.1855583190918</v>
       </c>
       <c r="G43" t="n">
-        <v>7.6960620880127</v>
+        <v>7.69606113433838</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G44" t="n">
-        <v>7.66867351531982</v>
+        <v>7.66867303848267</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G45" t="n">
-        <v>7.85125923156738</v>
+        <v>7.85125970840454</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>8.33606338500977</v>
       </c>
       <c r="G46" t="n">
-        <v>7.83756589889526</v>
+        <v>7.83756685256958</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.99232816696167</v>
       </c>
       <c r="G47" t="n">
-        <v>7.51438617706299</v>
+        <v>7.51438665390015</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>8.22634029388428</v>
       </c>
       <c r="G49" t="n">
-        <v>7.73440504074097</v>
+        <v>7.73440551757812</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>8.1875</v>
       </c>
       <c r="G50" t="n">
-        <v>7.69788837432861</v>
+        <v>7.6978874206543</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>8.44772911071777</v>
       </c>
       <c r="G51" t="n">
-        <v>7.94255399703979</v>
+        <v>7.94255352020264</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G54" t="n">
-        <v>8.24930191040039</v>
+        <v>8.24930095672607</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>8.94293975830078</v>
       </c>
       <c r="G55" t="n">
-        <v>8.40815258026123</v>
+        <v>8.40815162658691</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.75844955444336</v>
       </c>
       <c r="G60" t="n">
-        <v>8.234694480896</v>
+        <v>8.23469352722168</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.71960926055908</v>
       </c>
       <c r="G61" t="n">
-        <v>8.19817733764648</v>
+        <v>8.19817543029785</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.94973659515381</v>
       </c>
       <c r="G62" t="n">
-        <v>8.41454315185547</v>
+        <v>8.41454124450684</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G64" t="n">
-        <v>8.39902400970459</v>
+        <v>8.39902210235596</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.20511054992676</v>
       </c>
       <c r="G65" t="n">
-        <v>8.65464401245117</v>
+        <v>8.6546459197998</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.24395084381104</v>
       </c>
       <c r="G66" t="n">
-        <v>8.691162109375</v>
+        <v>8.69116306304932</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.37115287780762</v>
       </c>
       <c r="G72" t="n">
-        <v>8.81075763702393</v>
+        <v>8.81075859069824</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G75" t="n">
-        <v>9.27544116973877</v>
+        <v>9.2754430770874</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.63332366943359</v>
       </c>
       <c r="G77" t="n">
-        <v>9.05724906921387</v>
+        <v>9.05725002288818</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.70614910125732</v>
       </c>
       <c r="G79" t="n">
-        <v>9.12572193145752</v>
+        <v>9.1257209777832</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.57506275177002</v>
       </c>
       <c r="G80" t="n">
-        <v>9.00247478485107</v>
+        <v>9.00247383117676</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.53525161743164</v>
       </c>
       <c r="G81" t="n">
-        <v>8.96504402160645</v>
+        <v>8.9650411605835</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.26239967346191</v>
       </c>
       <c r="G82" t="n">
-        <v>8.70850849151611</v>
+        <v>8.7085075378418</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.55467224121094</v>
       </c>
       <c r="G84" t="n">
-        <v>8.98330307006836</v>
+        <v>8.98330211639404</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>8.43413352966309</v>
       </c>
       <c r="G89" t="n">
-        <v>7.92977046966553</v>
+        <v>7.92977237701416</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>8.77689933776855</v>
       </c>
       <c r="G90" t="n">
-        <v>8.25204086303711</v>
+        <v>8.25204181671143</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.07888126373291</v>
       </c>
       <c r="G93" t="n">
-        <v>8.53596305847168</v>
+        <v>8.535964012146</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.12743091583252</v>
       </c>
       <c r="G94" t="n">
-        <v>8.58160972595215</v>
+        <v>8.58161163330078</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.07888126373291</v>
       </c>
       <c r="G95" t="n">
-        <v>8.53596305847168</v>
+        <v>8.535964012146</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.30706596374512</v>
       </c>
       <c r="G96" t="n">
-        <v>8.75050163269043</v>
+        <v>8.75050354003906</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G98" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>8.48462677001953</v>
       </c>
       <c r="G99" t="n">
-        <v>7.97724628448486</v>
+        <v>7.97724437713623</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.97193717956543</v>
       </c>
       <c r="G100" t="n">
-        <v>7.49521446228027</v>
+        <v>7.49521541595459</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G101" t="n">
-        <v>7.75996589660645</v>
+        <v>7.7599663734436</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>8.3700475692749</v>
       </c>
       <c r="G103" t="n">
-        <v>7.8695182800293</v>
+        <v>7.86951923370361</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>8.3700475692749</v>
       </c>
       <c r="G104" t="n">
-        <v>7.8695182800293</v>
+        <v>7.86951923370361</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.27210998535156</v>
       </c>
       <c r="G106" t="n">
-        <v>8.71763610839844</v>
+        <v>8.71763706207275</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.27502346038818</v>
       </c>
       <c r="G107" t="n">
-        <v>8.72037601470947</v>
+        <v>8.72037696838379</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.08664894104004</v>
       </c>
       <c r="G110" t="n">
-        <v>8.54326820373535</v>
+        <v>8.54326438903809</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.19443035125732</v>
       </c>
       <c r="G111" t="n">
-        <v>8.64460372924805</v>
+        <v>8.64460182189941</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.06334495544434</v>
       </c>
       <c r="G112" t="n">
-        <v>8.5213565826416</v>
+        <v>8.52135562896729</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>8.86817264556885</v>
       </c>
       <c r="G113" t="n">
-        <v>8.33785724639893</v>
+        <v>8.33785629272461</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.81379699707031</v>
       </c>
       <c r="G114" t="n">
-        <v>8.28673076629639</v>
+        <v>8.2867317199707</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>9.04586696624756</v>
       </c>
       <c r="G115" t="n">
-        <v>8.50492382049561</v>
+        <v>8.50492286682129</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.2138500213623</v>
       </c>
       <c r="G116" t="n">
-        <v>8.6628589630127</v>
+        <v>8.66285991668701</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.51084423065186</v>
       </c>
       <c r="G117" t="n">
-        <v>8.00189590454102</v>
+        <v>8.00189685821533</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.49724960327148</v>
       </c>
       <c r="G118" t="n">
-        <v>7.98911285400391</v>
+        <v>7.98911476135254</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>8.54482936859131</v>
       </c>
       <c r="G119" t="n">
-        <v>8.03384780883789</v>
+        <v>8.03384685516357</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.03324413299561</v>
       </c>
       <c r="G121" t="n">
-        <v>8.49305629730225</v>
+        <v>8.4930534362793</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>8.80700016021729</v>
       </c>
       <c r="G122" t="n">
-        <v>8.28034210205078</v>
+        <v>8.28034114837646</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G123" t="n">
-        <v>8.39902400970459</v>
+        <v>8.39902210235596</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>8.99149036407471</v>
       </c>
       <c r="G124" t="n">
-        <v>8.45379829406738</v>
+        <v>8.4537992477417</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G125" t="n">
-        <v>8.39902400970459</v>
+        <v>8.39902210235596</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.55078792572021</v>
       </c>
       <c r="G127" t="n">
-        <v>8.97964954376221</v>
+        <v>8.97965049743652</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.52748394012451</v>
       </c>
       <c r="G129" t="n">
-        <v>8.95774078369141</v>
+        <v>8.95773983001709</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.67119312286377</v>
       </c>
       <c r="G130" t="n">
-        <v>9.09285545349121</v>
+        <v>9.09285640716553</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.35076236724854</v>
       </c>
       <c r="G131" t="n">
-        <v>8.79158496856689</v>
+        <v>8.79158592224121</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.53525161743164</v>
       </c>
       <c r="G133" t="n">
-        <v>8.96504402160645</v>
+        <v>8.9650411605835</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>8.77495670318604</v>
       </c>
       <c r="G137" t="n">
-        <v>8.25021457672119</v>
+        <v>8.25021362304688</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>8.70018863677979</v>
       </c>
       <c r="G138" t="n">
-        <v>8.17991828918457</v>
+        <v>8.17991638183594</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G139" t="n">
-        <v>8.21643447875977</v>
+        <v>8.2164363861084</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>8.80991268157959</v>
       </c>
       <c r="G140" t="n">
-        <v>8.2830810546875</v>
+        <v>8.28308010101318</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8.66523265838623</v>
       </c>
       <c r="G141" t="n">
-        <v>8.14705276489258</v>
+        <v>8.14705181121826</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G142" t="n">
-        <v>8.24930191040039</v>
+        <v>8.24930095672607</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>8.8798246383667</v>
       </c>
       <c r="G143" t="n">
-        <v>8.34881019592285</v>
+        <v>8.34881114959717</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>8.76815986633301</v>
       </c>
       <c r="G145" t="n">
-        <v>8.24382495880127</v>
+        <v>8.24382400512695</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G147" t="n">
-        <v>8.24930191040039</v>
+        <v>8.24930095672607</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>8.98178005218506</v>
       </c>
       <c r="G148" t="n">
-        <v>8.44466876983643</v>
+        <v>8.44467067718506</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>8.94293975830078</v>
       </c>
       <c r="G149" t="n">
-        <v>8.40815258026123</v>
+        <v>8.40815162658691</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>8.91380977630615</v>
       </c>
       <c r="G150" t="n">
-        <v>8.38076210021973</v>
+        <v>8.38076305389404</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G152" t="n">
-        <v>8.21643447875977</v>
+        <v>8.2164363861084</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>8.68659496307373</v>
       </c>
       <c r="G155" t="n">
-        <v>8.16713619232178</v>
+        <v>8.16713523864746</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>8.61474132537842</v>
       </c>
       <c r="G156" t="n">
-        <v>8.09958076477051</v>
+        <v>8.09957981109619</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G157" t="n">
-        <v>8.21643447875977</v>
+        <v>8.2164363861084</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>8.90410041809082</v>
       </c>
       <c r="G159" t="n">
-        <v>8.3716344833374</v>
+        <v>8.37163352966309</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>8.96430206298828</v>
       </c>
       <c r="G160" t="n">
-        <v>8.42823696136475</v>
+        <v>8.42823600769043</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.20316886901855</v>
       </c>
       <c r="G161" t="n">
-        <v>8.65281963348389</v>
+        <v>8.65281867980957</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>9.20316886901855</v>
       </c>
       <c r="G162" t="n">
-        <v>8.65281963348389</v>
+        <v>8.65281867980957</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.57894706726074</v>
       </c>
       <c r="G166" t="n">
-        <v>9.00612640380859</v>
+        <v>9.00612545013428</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.40222454071045</v>
       </c>
       <c r="G167" t="n">
-        <v>8.83997058868408</v>
+        <v>8.8399715423584</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G171" t="n">
-        <v>8.99243068695068</v>
+        <v>8.99242973327637</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.92753791809082</v>
       </c>
       <c r="G175" t="n">
-        <v>9.33386993408203</v>
+        <v>9.33387088775635</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>10.1547517776489</v>
       </c>
       <c r="G176" t="n">
-        <v>9.54749774932861</v>
+        <v>9.54749870300293</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G177" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G178" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G179" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>10.2440853118896</v>
       </c>
       <c r="G180" t="n">
-        <v>9.63148784637451</v>
+        <v>9.63149070739746</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G181" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.1897087097168</v>
       </c>
       <c r="G183" t="n">
-        <v>9.58036518096924</v>
+        <v>9.58036327362061</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.84791469573975</v>
       </c>
       <c r="G184" t="n">
-        <v>9.25901031494141</v>
+        <v>9.25900936126709</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G185" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>10.1625204086304</v>
       </c>
       <c r="G186" t="n">
-        <v>9.55480003356934</v>
+        <v>9.55480098724365</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G188" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>10.0498838424683</v>
       </c>
       <c r="G189" t="n">
-        <v>9.44890117645264</v>
+        <v>9.44890022277832</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.64594745635986</v>
       </c>
       <c r="G193" t="n">
-        <v>9.06911849975586</v>
+        <v>9.06911945343018</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G194" t="n">
-        <v>8.99243068695068</v>
+        <v>8.99242973327637</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.78771305084229</v>
       </c>
       <c r="G195" t="n">
-        <v>9.20240688323975</v>
+        <v>9.20240592956543</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.66536712646484</v>
       </c>
       <c r="G197" t="n">
-        <v>9.08737754821777</v>
+        <v>9.08737850189209</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.25657367706299</v>
       </c>
       <c r="G203" t="n">
-        <v>8.70303153991699</v>
+        <v>8.70303058624268</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>9.51680278778076</v>
       </c>
       <c r="G205" t="n">
-        <v>8.94769668579102</v>
+        <v>8.9476957321167</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>9.67119312286377</v>
       </c>
       <c r="G207" t="n">
-        <v>9.09285545349121</v>
+        <v>9.09285640716553</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>9.71003341674805</v>
       </c>
       <c r="G208" t="n">
-        <v>9.12937355041504</v>
+        <v>9.12937259674072</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>9.47699165344238</v>
       </c>
       <c r="G209" t="n">
-        <v>8.91026592254639</v>
+        <v>8.91026782989502</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>9.47699165344238</v>
       </c>
       <c r="G210" t="n">
-        <v>8.91026592254639</v>
+        <v>8.91026782989502</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.78771305084229</v>
       </c>
       <c r="G213" t="n">
-        <v>9.20240688323975</v>
+        <v>9.20240592956543</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.98191356658936</v>
       </c>
       <c r="G214" t="n">
-        <v>9.3849925994873</v>
+        <v>9.38499355316162</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>9.9236536026001</v>
       </c>
       <c r="G215" t="n">
-        <v>9.33021926879883</v>
+        <v>9.33021831512451</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.0790138244629</v>
       </c>
       <c r="G218" t="n">
-        <v>9.47628784179688</v>
+        <v>9.47628879547119</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.234375</v>
       </c>
       <c r="G220" t="n">
-        <v>9.62236022949219</v>
+        <v>9.62235927581787</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G223" t="n">
-        <v>9.93275833129883</v>
+        <v>9.93275737762451</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G224" t="n">
-        <v>9.98753452301025</v>
+        <v>9.98753261566162</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G225" t="n">
-        <v>9.73191165924072</v>
+        <v>9.73191070556641</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G226" t="n">
-        <v>9.98753452301025</v>
+        <v>9.98753261566162</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G227" t="n">
-        <v>9.85972213745117</v>
+        <v>9.85972309112549</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G228" t="n">
-        <v>9.73191165924072</v>
+        <v>9.73191070556641</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G229" t="n">
-        <v>9.75016975402832</v>
+        <v>9.750168800354</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G230" t="n">
-        <v>9.73191165924072</v>
+        <v>9.73191070556641</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G231" t="n">
-        <v>9.73191165924072</v>
+        <v>9.73191070556641</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G232" t="n">
-        <v>9.8779821395874</v>
+        <v>9.87798309326172</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>10.6421957015991</v>
       </c>
       <c r="G233" t="n">
-        <v>10.0057916641235</v>
+        <v>10.0057926177979</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.214955329895</v>
       </c>
       <c r="G235" t="n">
-        <v>9.60410022735596</v>
+        <v>9.60410118103027</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G236" t="n">
-        <v>9.71365165710449</v>
+        <v>9.71365261077881</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G237" t="n">
-        <v>9.76842975616455</v>
+        <v>9.76842880249023</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.4285745620728</v>
       </c>
       <c r="G238" t="n">
-        <v>9.80494403839111</v>
+        <v>9.80494499206543</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G239" t="n">
-        <v>10.0788269042969</v>
+        <v>10.0788278579712</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G242" t="n">
-        <v>10.0970849990845</v>
+        <v>10.0970859527588</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G243" t="n">
-        <v>9.8779821395874</v>
+        <v>9.87798309326172</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G244" t="n">
-        <v>10.2431573867798</v>
+        <v>10.2431564331055</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>10.6033563613892</v>
       </c>
       <c r="G245" t="n">
-        <v>9.96927547454834</v>
+        <v>9.96927452087402</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G246" t="n">
-        <v>9.85972213745117</v>
+        <v>9.85972309112549</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>10.4285745620728</v>
       </c>
       <c r="G247" t="n">
-        <v>9.80494403839111</v>
+        <v>9.80494499206543</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G248" t="n">
-        <v>9.93275833129883</v>
+        <v>9.93275737762451</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G249" t="n">
-        <v>9.95101547241211</v>
+        <v>9.95101642608643</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G250" t="n">
-        <v>10.060567855835</v>
+        <v>10.0605669021606</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>11.1082782745361</v>
       </c>
       <c r="G251" t="n">
-        <v>10.4440011978149</v>
+        <v>10.4440040588379</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>11.2053775787354</v>
       </c>
       <c r="G252" t="n">
-        <v>10.5352954864502</v>
+        <v>10.5352964401245</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>11.2636375427246</v>
       </c>
       <c r="G253" t="n">
-        <v>10.5900716781616</v>
+        <v>10.5900726318359</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>11.3413181304932</v>
       </c>
       <c r="G254" t="n">
-        <v>10.663106918335</v>
+        <v>10.6631059646606</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>11.0694379806519</v>
       </c>
       <c r="G256" t="n">
-        <v>10.4074859619141</v>
+        <v>10.4074850082397</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>11.0305967330933</v>
       </c>
       <c r="G257" t="n">
-        <v>10.3709669113159</v>
+        <v>10.3709659576416</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G258" t="n">
-        <v>10.2614145278931</v>
+        <v>10.2614135742188</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G259" t="n">
-        <v>9.95101547241211</v>
+        <v>9.95101642608643</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G260" t="n">
-        <v>9.91449737548828</v>
+        <v>9.9144983291626</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G262" t="n">
-        <v>10.0788269042969</v>
+        <v>10.0788278579712</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>10.6616163253784</v>
       </c>
       <c r="G263" t="n">
-        <v>10.1156778335571</v>
+        <v>10.1156797409058</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G264" t="n">
-        <v>9.87614250183105</v>
+        <v>9.87614345550537</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G265" t="n">
-        <v>9.82086753845215</v>
+        <v>9.82086849212646</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G266" t="n">
-        <v>9.85771942138672</v>
+        <v>9.8577184677124</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G267" t="n">
-        <v>9.85771942138672</v>
+        <v>9.8577184677124</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>10.6616163253784</v>
       </c>
       <c r="G268" t="n">
-        <v>10.1156778335571</v>
+        <v>10.1156797409058</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G269" t="n">
-        <v>10.0788269042969</v>
+        <v>10.0788259506226</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G270" t="n">
-        <v>9.93142032623291</v>
+        <v>9.93142127990723</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G271" t="n">
-        <v>10.1341037750244</v>
+        <v>10.1341028213501</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G272" t="n">
-        <v>10.1525297164917</v>
+        <v>10.1525287628174</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G273" t="n">
-        <v>10.1341037750244</v>
+        <v>10.1341028213501</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G274" t="n">
-        <v>10.023549079895</v>
+        <v>10.0235500335693</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G275" t="n">
-        <v>10.023549079895</v>
+        <v>10.0235500335693</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G277" t="n">
-        <v>9.98669910430908</v>
+        <v>9.98669815063477</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G278" t="n">
-        <v>9.93142032623291</v>
+        <v>9.93142127990723</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G279" t="n">
-        <v>10.1341037750244</v>
+        <v>10.1341028213501</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G280" t="n">
-        <v>10.1525297164917</v>
+        <v>10.1525287628174</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G281" t="n">
-        <v>9.82086753845215</v>
+        <v>9.82086849212646</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G283" t="n">
-        <v>9.87614250183105</v>
+        <v>9.87614345550537</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G284" t="n">
-        <v>9.82086753845215</v>
+        <v>9.82086849212646</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>10.6421957015991</v>
       </c>
       <c r="G286" t="n">
-        <v>10.0972528457642</v>
+        <v>10.0972518920898</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.0500173568726</v>
       </c>
       <c r="G287" t="n">
-        <v>10.4841899871826</v>
+        <v>10.4841918945312</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3552131652832</v>
+        <v>10.3552112579346</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G293" t="n">
-        <v>9.93142032623291</v>
+        <v>9.93142127990723</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G297" t="n">
-        <v>9.96827125549316</v>
+        <v>9.96827411651611</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G298" t="n">
-        <v>9.93142032623291</v>
+        <v>9.93142127990723</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.2732152938843</v>
       </c>
       <c r="G301" t="n">
-        <v>9.74716472625732</v>
+        <v>9.74716663360596</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G303" t="n">
-        <v>10.0051259994507</v>
+        <v>10.0051250457764</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G305" t="n">
-        <v>10.1341037750244</v>
+        <v>10.1341028213501</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G307" t="n">
-        <v>9.93142032623291</v>
+        <v>9.93142127990723</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G308" t="n">
-        <v>9.98669910430908</v>
+        <v>9.98669815063477</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G309" t="n">
-        <v>9.93142032623291</v>
+        <v>9.93142127990723</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>11.0500173568726</v>
       </c>
       <c r="G313" t="n">
-        <v>10.4841899871826</v>
+        <v>10.4841918945312</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G314" t="n">
-        <v>10.7790021896362</v>
+        <v>10.7790002822876</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G315" t="n">
-        <v>10.4104871749878</v>
+        <v>10.4104881286621</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G316" t="n">
-        <v>10.1525297164917</v>
+        <v>10.1525287628174</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>11.6908798217773</v>
       </c>
       <c r="G318" t="n">
-        <v>11.0922365188599</v>
+        <v>11.0922374725342</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>12.15696144104</v>
       </c>
       <c r="G319" t="n">
-        <v>11.5344524383545</v>
+        <v>11.5344533920288</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>11.943341255188</v>
       </c>
       <c r="G320" t="n">
-        <v>11.3317699432373</v>
+        <v>11.3317718505859</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>11.943341255188</v>
       </c>
       <c r="G321" t="n">
-        <v>11.3317699432373</v>
+        <v>11.3317718505859</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>12.15696144104</v>
       </c>
       <c r="G325" t="n">
-        <v>11.5344524383545</v>
+        <v>11.5344533920288</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G328" t="n">
-        <v>12.0687961578369</v>
+        <v>12.0687980651855</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G329" t="n">
-        <v>12.0687961578369</v>
+        <v>12.0687980651855</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G330" t="n">
-        <v>12.160924911499</v>
+        <v>12.1609239578247</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>13.0308637619019</v>
       </c>
       <c r="G331" t="n">
-        <v>12.3636054992676</v>
+        <v>12.3636064529419</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>13.186224937439</v>
       </c>
       <c r="G332" t="n">
-        <v>12.5110120773315</v>
+        <v>12.5110130310059</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G334" t="n">
-        <v>11.4976024627686</v>
+        <v>11.4976015090942</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G335" t="n">
-        <v>11.5160274505615</v>
+        <v>11.5160264968872</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>12.2929019927979</v>
       </c>
       <c r="G336" t="n">
-        <v>11.6634330749512</v>
+        <v>11.6634321212769</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G337" t="n">
-        <v>11.5160274505615</v>
+        <v>11.5160264968872</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G338" t="n">
-        <v>11.4976024627686</v>
+        <v>11.4976015090942</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G340" t="n">
-        <v>11.5160274505615</v>
+        <v>11.5160264968872</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G342" t="n">
-        <v>11.5160274505615</v>
+        <v>11.5160264968872</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G343" t="n">
-        <v>11.4976024627686</v>
+        <v>11.4976015090942</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>12.681303024292</v>
       </c>
       <c r="G345" t="n">
-        <v>12.0319452285767</v>
+        <v>12.0319442749023</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G348" t="n">
-        <v>12.160924911499</v>
+        <v>12.1609239578247</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>12.7978229522705</v>
       </c>
       <c r="G350" t="n">
-        <v>12.1424999237061</v>
+        <v>12.1424980163574</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>13.2833251953125</v>
       </c>
       <c r="G352" t="n">
-        <v>12.6031398773193</v>
+        <v>12.603138923645</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>13.5940456390381</v>
       </c>
       <c r="G353" t="n">
-        <v>12.89794921875</v>
+        <v>12.8979501724243</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G354" t="n">
-        <v>13.1743364334106</v>
+        <v>13.1743335723877</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>14.1378078460693</v>
       </c>
       <c r="G356" t="n">
-        <v>13.4138689041138</v>
+        <v>13.4138679504395</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>14.1378078460693</v>
       </c>
       <c r="G358" t="n">
-        <v>13.4138689041138</v>
+        <v>13.4138679504395</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.8270874023438</v>
       </c>
       <c r="G360" t="n">
-        <v>13.1190576553345</v>
+        <v>13.1190586090088</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G361" t="n">
-        <v>13.026930809021</v>
+        <v>13.0269298553467</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G362" t="n">
-        <v>13.026930809021</v>
+        <v>13.0269298553467</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>12.9726037979126</v>
       </c>
       <c r="G363" t="n">
-        <v>12.3083295822144</v>
+        <v>12.3083305358887</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G364" t="n">
-        <v>12.2714776992798</v>
+        <v>12.2714805603027</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>12.9920244216919</v>
       </c>
       <c r="G366" t="n">
-        <v>12.326756477356</v>
+        <v>12.3267555236816</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G367" t="n">
-        <v>12.160924911499</v>
+        <v>12.1609239578247</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.8560838699341</v>
       </c>
       <c r="G371" t="n">
-        <v>12.1977767944336</v>
+        <v>12.197774887085</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>15.2835922241211</v>
       </c>
       <c r="G373" t="n">
-        <v>14.5009803771973</v>
+        <v>14.5009813308716</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>14.5650501251221</v>
       </c>
       <c r="G374" t="n">
-        <v>13.8192319869995</v>
+        <v>13.8192348480225</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G377" t="n">
-        <v>12.7689723968506</v>
+        <v>12.768970489502</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G380" t="n">
-        <v>12.4741592407227</v>
+        <v>12.4741611480713</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G381" t="n">
-        <v>12.2899045944214</v>
+        <v>12.2899055480957</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G382" t="n">
-        <v>12.2899045944214</v>
+        <v>12.2899055480957</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>13.380425453186</v>
       </c>
       <c r="G385" t="n">
-        <v>12.6952676773071</v>
+        <v>12.6952686309814</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>13.4192657470703</v>
       </c>
       <c r="G386" t="n">
-        <v>12.7321195602417</v>
+        <v>12.7321214675903</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G389" t="n">
-        <v>13.1743364334106</v>
+        <v>13.1743335723877</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>13.6911468505859</v>
       </c>
       <c r="G390" t="n">
-        <v>12.9900779724121</v>
+        <v>12.9900789260864</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>13.9630270004272</v>
       </c>
       <c r="G391" t="n">
-        <v>13.2480363845825</v>
+        <v>13.2480373382568</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>13.9630270004272</v>
       </c>
       <c r="G392" t="n">
-        <v>13.2480363845825</v>
+        <v>13.2480373382568</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G394" t="n">
-        <v>12.7689723968506</v>
+        <v>12.768970489502</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G395" t="n">
-        <v>13.1743364334106</v>
+        <v>13.1743335723877</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>13.6717262268066</v>
       </c>
       <c r="G396" t="n">
-        <v>12.9716539382935</v>
+        <v>12.9716520309448</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>13.2444849014282</v>
       </c>
       <c r="G397" t="n">
-        <v>12.5662879943848</v>
+        <v>12.5662889480591</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>12.8949241638184</v>
       </c>
       <c r="G398" t="n">
-        <v>12.2346286773682</v>
+        <v>12.2346267700195</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G401" t="n">
-        <v>12.3451824188232</v>
+        <v>12.3451814651489</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G402" t="n">
-        <v>12.3451824188232</v>
+        <v>12.3451814651489</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G404" t="n">
-        <v>12.3451824188232</v>
+        <v>12.3451814651489</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G405" t="n">
-        <v>12.160924911499</v>
+        <v>12.1609239578247</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G406" t="n">
-        <v>12.0687961578369</v>
+        <v>12.0687980651855</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G411" t="n">
-        <v>11.7002849578857</v>
+        <v>11.7002840042114</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G413" t="n">
-        <v>10.9448318481445</v>
+        <v>10.9448308944702</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>11.6131992340088</v>
       </c>
       <c r="G414" t="n">
-        <v>11.0185356140137</v>
+        <v>11.0185346603394</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G416" t="n">
-        <v>10.7790021896362</v>
+        <v>10.7790002822876</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>11.2636375427246</v>
       </c>
       <c r="G418" t="n">
-        <v>10.6868715286255</v>
+        <v>10.6868734359741</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G419" t="n">
-        <v>10.9448318481445</v>
+        <v>10.9448308944702</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G420" t="n">
-        <v>11.2396411895752</v>
+        <v>11.2396421432495</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G421" t="n">
-        <v>11.2396411895752</v>
+        <v>11.2396421432495</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G422" t="n">
-        <v>11.0553855895996</v>
+        <v>11.0553865432739</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G424" t="n">
-        <v>11.1475124359131</v>
+        <v>11.1475133895874</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G425" t="n">
-        <v>11.2396411895752</v>
+        <v>11.2396421432495</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G426" t="n">
-        <v>11.2396411895752</v>
+        <v>11.2396421432495</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G427" t="n">
-        <v>11.2396411895752</v>
+        <v>11.2396421432495</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G428" t="n">
-        <v>11.1475124359131</v>
+        <v>11.1475133895874</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>11.9045000076294</v>
       </c>
       <c r="G430" t="n">
-        <v>11.2949199676514</v>
+        <v>11.2949190139771</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G431" t="n">
-        <v>11.036961555481</v>
+        <v>11.0369596481323</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G432" t="n">
-        <v>10.0788269042969</v>
+        <v>10.0788259506226</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G433" t="n">
-        <v>10.4104871749878</v>
+        <v>10.4104881286621</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G434" t="n">
-        <v>10.7790021896362</v>
+        <v>10.7790002822876</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G437" t="n">
-        <v>9.98669910430908</v>
+        <v>9.98669815063477</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G438" t="n">
-        <v>10.3552131652832</v>
+        <v>10.3552112579346</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G440" t="n">
-        <v>10.023549079895</v>
+        <v>10.0235500335693</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G441" t="n">
-        <v>10.0788269042969</v>
+        <v>10.0788259506226</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G443" t="n">
-        <v>9.36022663116455</v>
+        <v>9.36022567749023</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.84597301483154</v>
       </c>
       <c r="G444" t="n">
-        <v>9.34180068969727</v>
+        <v>9.34180164337158</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.30221080780029</v>
       </c>
       <c r="G445" t="n">
-        <v>8.82588291168213</v>
+        <v>8.82588195800781</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G448" t="n">
-        <v>9.85771942138672</v>
+        <v>9.8577184677124</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.22453117370605</v>
       </c>
       <c r="G449" t="n">
-        <v>8.7521800994873</v>
+        <v>8.75218200683594</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>8.59337902069092</v>
       </c>
       <c r="G450" t="n">
-        <v>8.15334606170654</v>
+        <v>8.15334796905518</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>8.58366870880127</v>
       </c>
       <c r="G452" t="n">
-        <v>8.14413452148438</v>
+        <v>8.14413547515869</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G454" t="n">
-        <v>8.38366794586182</v>
+        <v>8.3836669921875</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>10.0984344482422</v>
       </c>
       <c r="G455" t="n">
-        <v>9.58133411407471</v>
+        <v>9.58133506774902</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G456" t="n">
-        <v>11.7002849578857</v>
+        <v>11.7002840042114</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G457" t="n">
-        <v>11.036961555481</v>
+        <v>11.0369596481323</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>11.2247982025146</v>
       </c>
       <c r="G458" t="n">
-        <v>10.6500215530396</v>
+        <v>10.6500225067139</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G459" t="n">
-        <v>10.0788269042969</v>
+        <v>10.0788259506226</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G460" t="n">
-        <v>10.1341037750244</v>
+        <v>10.1341028213501</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G462" t="n">
-        <v>10.1341037750244</v>
+        <v>10.1341028213501</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G464" t="n">
-        <v>10.1709547042847</v>
+        <v>10.1709566116333</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>10.2732152938843</v>
       </c>
       <c r="G466" t="n">
-        <v>9.74716472625732</v>
+        <v>9.74716663360596</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G468" t="n">
-        <v>9.94984912872314</v>
+        <v>9.94984817504883</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>11.2053775787354</v>
       </c>
       <c r="G469" t="n">
-        <v>10.6315956115723</v>
+        <v>10.6315965652466</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G470" t="n">
-        <v>11.0553855895996</v>
+        <v>11.0553865432739</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G472" t="n">
-        <v>11.0553855895996</v>
+        <v>11.0553865432739</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G473" t="n">
-        <v>11.7002849578857</v>
+        <v>11.7002840042114</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>13.0697040557861</v>
       </c>
       <c r="G476" t="n">
-        <v>12.4004583358765</v>
+        <v>12.4004573822021</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G477" t="n">
-        <v>12.4741592407227</v>
+        <v>12.4741611480713</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>13.2056446075439</v>
       </c>
       <c r="G478" t="n">
-        <v>12.5294370651245</v>
+        <v>12.5294380187988</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G479" t="n">
-        <v>12.3451824188232</v>
+        <v>12.3451814651489</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G480" t="n">
-        <v>12.2714776992798</v>
+        <v>12.2714805603027</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>12.3123216629028</v>
       </c>
       <c r="G482" t="n">
-        <v>11.6818580627441</v>
+        <v>11.6818590164185</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G485" t="n">
-        <v>11.7002849578857</v>
+        <v>11.7002840042114</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>14.3708486557007</v>
       </c>
       <c r="G489" t="n">
-        <v>13.6349763870239</v>
+        <v>13.6349754333496</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G491" t="n">
-        <v>13.026930809021</v>
+        <v>13.0269298553467</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>14.2931690216064</v>
       </c>
       <c r="G492" t="n">
-        <v>13.5612745285034</v>
+        <v>13.5612735748291</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G493" t="n">
-        <v>14.7957906723022</v>
+        <v>14.7957925796509</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>15.633152961731</v>
       </c>
       <c r="G495" t="n">
-        <v>14.8326425552368</v>
+        <v>14.8326435089111</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G497" t="n">
-        <v>15.1827297210693</v>
+        <v>15.182731628418</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>16.7206764221191</v>
       </c>
       <c r="G499" t="n">
-        <v>15.8644781112671</v>
+        <v>15.8644771575928</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G500" t="n">
-        <v>15.2932834625244</v>
+        <v>15.2932844161987</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>15.6525726318359</v>
       </c>
       <c r="G501" t="n">
-        <v>14.8510684967041</v>
+        <v>14.8510675430298</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>15.1476516723633</v>
       </c>
       <c r="G503" t="n">
-        <v>14.3720016479492</v>
+        <v>14.3720026016235</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>14.7980899810791</v>
       </c>
       <c r="G506" t="n">
-        <v>14.0403394699097</v>
+        <v>14.040340423584</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>14.4485292434692</v>
       </c>
       <c r="G507" t="n">
-        <v>13.7086782455444</v>
+        <v>13.7086791992188</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>14.3125886917114</v>
       </c>
       <c r="G509" t="n">
-        <v>13.5796995162964</v>
+        <v>13.5796985626221</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>14.7398300170898</v>
       </c>
       <c r="G510" t="n">
-        <v>13.9850635528564</v>
+        <v>13.9850625991821</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>15.5748929977417</v>
       </c>
       <c r="G519" t="n">
-        <v>14.8879203796387</v>
+        <v>14.8879194259644</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G522" t="n">
-        <v>15.129246711731</v>
+        <v>15.1292457580566</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>16.0215549468994</v>
       </c>
       <c r="G523" t="n">
-        <v>15.3148794174194</v>
+        <v>15.3148813247681</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>15.9244537353516</v>
       </c>
       <c r="G524" t="n">
-        <v>15.2220611572266</v>
+        <v>15.2220621109009</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G525" t="n">
-        <v>14.9064826965332</v>
+        <v>14.9064836502075</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>15.1864919662476</v>
       </c>
       <c r="G526" t="n">
-        <v>14.5166501998901</v>
+        <v>14.5166492462158</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G527" t="n">
-        <v>14.9064826965332</v>
+        <v>14.9064836502075</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>15.2253322601318</v>
       </c>
       <c r="G530" t="n">
-        <v>14.5537776947021</v>
+        <v>14.5537767410278</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G531" t="n">
-        <v>15.0364294052124</v>
+        <v>15.0364284515381</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G534" t="n">
-        <v>15.129246711731</v>
+        <v>15.1292457580566</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G535" t="n">
-        <v>15.129246711731</v>
+        <v>15.1292457580566</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G536" t="n">
-        <v>14.9064826965332</v>
+        <v>14.9064836502075</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>15.0505514144897</v>
       </c>
       <c r="G540" t="n">
-        <v>14.3867063522339</v>
+        <v>14.3867053985596</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>15.0505514144897</v>
       </c>
       <c r="G541" t="n">
-        <v>14.3867063522339</v>
+        <v>14.3867053985596</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>16.1769142150879</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4633865356445</v>
+        <v>15.4633855819702</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>17.536319732666</v>
       </c>
       <c r="G551" t="n">
-        <v>16.7628326416016</v>
+        <v>16.7628307342529</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>18.1189212799072</v>
       </c>
       <c r="G552" t="n">
-        <v>17.3197383880615</v>
+        <v>17.3197364807129</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G554" t="n">
-        <v>17.2826080322266</v>
+        <v>17.2826118469238</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G556" t="n">
-        <v>17.8952083587646</v>
+        <v>17.8952045440674</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G560" t="n">
-        <v>17.542501449585</v>
+        <v>17.5424995422363</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G563" t="n">
-        <v>18.5634899139404</v>
+        <v>18.5634918212891</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G565" t="n">
-        <v>18.2107849121094</v>
+        <v>18.2107830047607</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G566" t="n">
-        <v>18.5634899139404</v>
+        <v>18.5634918212891</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G570" t="n">
-        <v>17.264045715332</v>
+        <v>17.2640476226807</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G573" t="n">
-        <v>17.6910057067871</v>
+        <v>17.6910076141357</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>17.5945796966553</v>
       </c>
       <c r="G574" t="n">
-        <v>16.8185234069824</v>
+        <v>16.8185253143311</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G575" t="n">
-        <v>16.5586338043213</v>
+        <v>16.5586318969727</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>16.4487953186035</v>
       </c>
       <c r="G576" t="n">
-        <v>15.7232751846313</v>
+        <v>15.72327709198</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>16.5847358703613</v>
       </c>
       <c r="G578" t="n">
-        <v>15.8532209396362</v>
+        <v>15.8532228469849</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G580" t="n">
-        <v>15.6675844192505</v>
+        <v>15.6675853729248</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G581" t="n">
-        <v>16.428689956665</v>
+        <v>16.4286918640137</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>16.9342975616455</v>
       </c>
       <c r="G583" t="n">
-        <v>16.1873645782471</v>
+        <v>16.1873626708984</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G584" t="n">
-        <v>16.3173065185547</v>
+        <v>16.3173084259033</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>17.5168991088867</v>
       </c>
       <c r="G586" t="n">
-        <v>16.7442684173584</v>
+        <v>16.7442665100098</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G587" t="n">
-        <v>16.5957622528076</v>
+        <v>16.595760345459</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>16.9731388092041</v>
       </c>
       <c r="G588" t="n">
-        <v>16.2244930267334</v>
+        <v>16.2244911193848</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>17.1479187011719</v>
       </c>
       <c r="G589" t="n">
-        <v>16.391565322876</v>
+        <v>16.3915615081787</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G593" t="n">
-        <v>16.5957622528076</v>
+        <v>16.595760345459</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G594" t="n">
-        <v>16.5586338043213</v>
+        <v>16.5586318969727</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G596" t="n">
-        <v>16.5215091705322</v>
+        <v>16.5215072631836</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G597" t="n">
-        <v>16.5029411315918</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G598" t="n">
-        <v>16.6514511108398</v>
+        <v>16.6514530181885</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G603" t="n">
-        <v>15.6861524581909</v>
+        <v>15.686149597168</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>16.0409755706787</v>
       </c>
       <c r="G604" t="n">
-        <v>15.3334445953369</v>
+        <v>15.3334455490112</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>15.5554733276367</v>
       </c>
       <c r="G605" t="n">
-        <v>14.8693571090698</v>
+        <v>14.8693561553955</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>15.2641716003418</v>
       </c>
       <c r="G606" t="n">
-        <v>14.5909032821655</v>
+        <v>14.5909023284912</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G609" t="n">
-        <v>15.6861524581909</v>
+        <v>15.686149597168</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>15.108811378479</v>
       </c>
       <c r="G611" t="n">
-        <v>14.4423961639404</v>
+        <v>14.4423952102661</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G613" t="n">
-        <v>16.4101257324219</v>
+        <v>16.4101276397705</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G614" t="n">
-        <v>16.4101257324219</v>
+        <v>16.4101276397705</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>16.5847358703613</v>
       </c>
       <c r="G615" t="n">
-        <v>15.8532209396362</v>
+        <v>15.8532228469849</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G618" t="n">
-        <v>15.7789640426636</v>
+        <v>15.7789669036865</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G621" t="n">
-        <v>16.5215091705322</v>
+        <v>16.5215072631836</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G623" t="n">
-        <v>16.5957622528076</v>
+        <v>16.595760345459</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G624" t="n">
-        <v>16.3729972839355</v>
+        <v>16.3729991912842</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G628" t="n">
-        <v>16.5029411315918</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G630" t="n">
-        <v>16.5029411315918</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G631" t="n">
-        <v>16.3173065185547</v>
+        <v>16.3173084259033</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G632" t="n">
-        <v>16.3358745574951</v>
+        <v>16.3358707427979</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>17.7499408721924</v>
       </c>
       <c r="G635" t="n">
-        <v>16.9670295715332</v>
+        <v>16.9670314788818</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G637" t="n">
-        <v>16.5400695800781</v>
+        <v>16.5400714874268</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G639" t="n">
-        <v>16.3729972839355</v>
+        <v>16.3729991912842</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G644" t="n">
-        <v>17.2826080322266</v>
+        <v>17.2826118469238</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G649" t="n">
-        <v>17.8023853302002</v>
+        <v>17.8023872375488</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>18.7597846984863</v>
       </c>
       <c r="G650" t="n">
-        <v>17.9323329925537</v>
+        <v>17.9323310852051</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G653" t="n">
-        <v>16.5400695800781</v>
+        <v>16.5400714874268</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G654" t="n">
-        <v>16.3358745574951</v>
+        <v>16.3358707427979</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>17.2255992889404</v>
       </c>
       <c r="G655" t="n">
-        <v>16.4658164978027</v>
+        <v>16.4658184051514</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>17.4003791809082</v>
       </c>
       <c r="G656" t="n">
-        <v>16.6328887939453</v>
+        <v>16.6328868865967</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>17.2255992889404</v>
       </c>
       <c r="G658" t="n">
-        <v>16.4658164978027</v>
+        <v>16.4658184051514</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G659" t="n">
-        <v>16.5957622528076</v>
+        <v>16.595760345459</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G660" t="n">
-        <v>16.5029411315918</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>17.2061786651611</v>
       </c>
       <c r="G662" t="n">
-        <v>16.4472541809082</v>
+        <v>16.4472522735596</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G663" t="n">
-        <v>16.3729972839355</v>
+        <v>16.3729991912842</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G664" t="n">
-        <v>16.3729972839355</v>
+        <v>16.3729991912842</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>16.9731388092041</v>
       </c>
       <c r="G665" t="n">
-        <v>16.2244930267334</v>
+        <v>16.2244911193848</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G666" t="n">
-        <v>16.5215091705322</v>
+        <v>16.5215072631836</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G667" t="n">
-        <v>16.3358745574951</v>
+        <v>16.3358707427979</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G669" t="n">
-        <v>15.7789640426636</v>
+        <v>15.7789669036865</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>16.9537181854248</v>
       </c>
       <c r="G670" t="n">
-        <v>16.2059288024902</v>
+        <v>16.2059268951416</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G674" t="n">
-        <v>16.3173065185547</v>
+        <v>16.3173084259033</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G675" t="n">
-        <v>16.428689956665</v>
+        <v>16.4286918640137</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>16.9537181854248</v>
       </c>
       <c r="G678" t="n">
-        <v>16.2059288024902</v>
+        <v>16.2059268951416</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>17.2061786651611</v>
       </c>
       <c r="G679" t="n">
-        <v>16.4472541809082</v>
+        <v>16.4472522735596</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G680" t="n">
-        <v>16.5586338043213</v>
+        <v>16.5586318969727</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>16.7012577056885</v>
       </c>
       <c r="G682" t="n">
-        <v>15.964599609375</v>
+        <v>15.9646024703979</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>16.4682159423828</v>
       </c>
       <c r="G683" t="n">
-        <v>15.7418384552002</v>
+        <v>15.7418403625488</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>16.3711166381836</v>
       </c>
       <c r="G686" t="n">
-        <v>15.6490230560303</v>
+        <v>15.649022102356</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>16.2157554626465</v>
       </c>
       <c r="G687" t="n">
-        <v>15.5005149841309</v>
+        <v>15.5005140304565</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>16.9342975616455</v>
       </c>
       <c r="G688" t="n">
-        <v>16.1873645782471</v>
+        <v>16.1873626708984</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>16.6429977416992</v>
       </c>
       <c r="G689" t="n">
-        <v>15.9089107513428</v>
+        <v>15.9089117050171</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>16.6041564941406</v>
       </c>
       <c r="G691" t="n">
-        <v>15.8717861175537</v>
+        <v>15.8717842102051</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>15.9632940292358</v>
       </c>
       <c r="G692" t="n">
-        <v>15.2591886520386</v>
+        <v>15.2591896057129</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G694" t="n">
-        <v>14.4238319396973</v>
+        <v>14.4238328933716</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G697" t="n">
-        <v>14.4238319396973</v>
+        <v>14.4238328933716</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G700" t="n">
-        <v>15.0364294052124</v>
+        <v>15.0364284515381</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G701" t="n">
-        <v>15.407696723938</v>
+        <v>15.4076976776123</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>16.2545948028564</v>
       </c>
       <c r="G702" t="n">
-        <v>15.5376415252686</v>
+        <v>15.5376405715942</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>16.2934341430664</v>
       </c>
       <c r="G703" t="n">
-        <v>15.5747690200806</v>
+        <v>15.5747671127319</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>16.332275390625</v>
       </c>
       <c r="G705" t="n">
-        <v>15.6118955612183</v>
+        <v>15.6118965148926</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G706" t="n">
-        <v>15.407696723938</v>
+        <v>15.4076976776123</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>16.0798149108887</v>
       </c>
       <c r="G707" t="n">
-        <v>15.3705701828003</v>
+        <v>15.3705711364746</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>16.0603942871094</v>
       </c>
       <c r="G708" t="n">
-        <v>15.3520059585571</v>
+        <v>15.3520069122314</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G709" t="n">
-        <v>15.6675844192505</v>
+        <v>15.6675853729248</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>16.2740154266357</v>
       </c>
       <c r="G710" t="n">
-        <v>15.5562038421631</v>
+        <v>15.5562057495117</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G715" t="n">
-        <v>16.9855976104736</v>
+        <v>16.985595703125</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G717" t="n">
-        <v>17.8209533691406</v>
+        <v>17.8209495544434</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G718" t="n">
-        <v>17.542501449585</v>
+        <v>17.5424995422363</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G719" t="n">
-        <v>17.542501449585</v>
+        <v>17.5424995422363</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>18.4684829711914</v>
       </c>
       <c r="G721" t="n">
-        <v>17.6538772583008</v>
+        <v>17.653881072998</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G723" t="n">
-        <v>17.8209533691406</v>
+        <v>17.8209495544434</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>18.3325424194336</v>
       </c>
       <c r="G724" t="n">
-        <v>17.5239372253418</v>
+        <v>17.5239334106445</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G725" t="n">
-        <v>17.8209533691406</v>
+        <v>17.8209495544434</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>18.779203414917</v>
       </c>
       <c r="G727" t="n">
-        <v>17.9508972167969</v>
+        <v>17.9508934020996</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G729" t="n">
-        <v>17.264045715332</v>
+        <v>17.2640476226807</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>17.8470401763916</v>
       </c>
       <c r="G730" t="n">
-        <v>17.0598468780518</v>
+        <v>17.0598487854004</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G731" t="n">
-        <v>16.9855976104736</v>
+        <v>16.985595703125</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G732" t="n">
-        <v>17.2826080322266</v>
+        <v>17.2826118469238</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G733" t="n">
-        <v>17.4496803283691</v>
+        <v>17.4496822357178</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>18.293701171875</v>
       </c>
       <c r="G734" t="n">
-        <v>17.4868087768555</v>
+        <v>17.4868068695068</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>18.4490623474121</v>
       </c>
       <c r="G735" t="n">
-        <v>17.6353149414062</v>
+        <v>17.6353187561035</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G737" t="n">
-        <v>19.5844860076904</v>
+        <v>19.5844879150391</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G739" t="n">
-        <v>19.3060302734375</v>
+        <v>19.3060321807861</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G740" t="n">
-        <v>19.3988494873047</v>
+        <v>19.3988475799561</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G741" t="n">
-        <v>19.8629360198975</v>
+        <v>19.8629341125488</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G742" t="n">
-        <v>20.4198398590088</v>
+        <v>20.4198417663574</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G748" t="n">
-        <v>20.0949783325195</v>
+        <v>20.0949802398682</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G749" t="n">
-        <v>20.4662475585938</v>
+        <v>20.4662494659424</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G750" t="n">
-        <v>20.512659072876</v>
+        <v>20.5126552581787</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G754" t="n">
-        <v>21.1623783111572</v>
+        <v>21.1623802185059</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G756" t="n">
-        <v>20.4662475585938</v>
+        <v>20.4662494659424</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G757" t="n">
-        <v>20.4198398590088</v>
+        <v>20.4198417663574</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G759" t="n">
-        <v>20.6982936859131</v>
+        <v>20.6982917785645</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G760" t="n">
-        <v>20.0949783325195</v>
+        <v>20.0949802398682</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G763" t="n">
-        <v>19.8629360198975</v>
+        <v>19.8629341125488</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G765" t="n">
-        <v>19.5844860076904</v>
+        <v>19.5844879150391</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>19.9541187286377</v>
       </c>
       <c r="G767" t="n">
-        <v>19.0739860534668</v>
+        <v>19.0739898681641</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G769" t="n">
-        <v>19.8395595550537</v>
+        <v>19.8395576477051</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G770" t="n">
-        <v>19.6528339385986</v>
+        <v>19.6528358459473</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G771" t="n">
-        <v>19.3260650634766</v>
+        <v>19.3260669708252</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G772" t="n">
-        <v>19.4194297790527</v>
+        <v>19.4194278717041</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G774" t="n">
-        <v>19.5594749450684</v>
+        <v>19.5594730377197</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>19.6628170013428</v>
       </c>
       <c r="G775" t="n">
-        <v>18.9059352874756</v>
+        <v>18.9059371948242</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G776" t="n">
-        <v>18.7192077636719</v>
+        <v>18.7192096710205</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G777" t="n">
-        <v>19.0459804534912</v>
+        <v>19.0459785461426</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G778" t="n">
-        <v>18.9526176452637</v>
+        <v>18.9526138305664</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>19.6142673492432</v>
       </c>
       <c r="G781" t="n">
-        <v>18.8592510223389</v>
+        <v>18.8592529296875</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G782" t="n">
-        <v>19.6528339385986</v>
+        <v>19.6528358459473</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>20.8280200958252</v>
       </c>
       <c r="G783" t="n">
-        <v>20.0262851715088</v>
+        <v>20.0262832641602</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G784" t="n">
-        <v>19.6995182037354</v>
+        <v>19.699520111084</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G786" t="n">
-        <v>19.0459804534912</v>
+        <v>19.0459785461426</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G787" t="n">
-        <v>18.9526176452637</v>
+        <v>18.9526138305664</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G788" t="n">
-        <v>18.2990798950195</v>
+        <v>18.2990779876709</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G789" t="n">
-        <v>18.5044765472412</v>
+        <v>18.5044746398926</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>19.4006462097168</v>
       </c>
       <c r="G791" t="n">
-        <v>18.6538581848145</v>
+        <v>18.6538562774658</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G793" t="n">
-        <v>18.6725273132324</v>
+        <v>18.6725292205811</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G794" t="n">
-        <v>18.6725273132324</v>
+        <v>18.6725292205811</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G795" t="n">
-        <v>18.5231456756592</v>
+        <v>18.5231475830078</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G796" t="n">
-        <v>18.6725273132324</v>
+        <v>18.6725292205811</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G797" t="n">
-        <v>18.7192077636719</v>
+        <v>18.7192096710205</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G798" t="n">
-        <v>18.6725273132324</v>
+        <v>18.6725292205811</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>20.8280200958252</v>
       </c>
       <c r="G802" t="n">
-        <v>20.0262851715088</v>
+        <v>20.0262832641602</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G804" t="n">
-        <v>21.1466369628906</v>
+        <v>21.146635055542</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G805" t="n">
-        <v>21.9402198791504</v>
+        <v>21.940221786499</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G808" t="n">
-        <v>23.0605716705322</v>
+        <v>23.0605735778809</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G809" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406581878662</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G811" t="n">
-        <v>22.920524597168</v>
+        <v>22.9205284118652</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G815" t="n">
-        <v>23.5740661621094</v>
+        <v>23.574068069458</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G817" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G818" t="n">
-        <v>22.6871223449707</v>
+        <v>22.6871204376221</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G822" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406581878662</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G823" t="n">
-        <v>23.5740661621094</v>
+        <v>23.574068069458</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G825" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G828" t="n">
-        <v>23.0605716705322</v>
+        <v>23.0605735778809</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G829" t="n">
-        <v>23.1072540283203</v>
+        <v>23.1072521209717</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G834" t="n">
-        <v>23.1072540283203</v>
+        <v>23.1072521209717</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G835" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406581878662</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G837" t="n">
-        <v>23.714111328125</v>
+        <v>23.7141132354736</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G839" t="n">
-        <v>21.6134510040283</v>
+        <v>21.613452911377</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>22.8671283721924</v>
       </c>
       <c r="G841" t="n">
-        <v>21.9868984222412</v>
+        <v>21.9869003295898</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G846" t="n">
-        <v>20.8198661804199</v>
+        <v>20.8198680877686</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>21.9446754455566</v>
       </c>
       <c r="G849" t="n">
-        <v>21.0999565124512</v>
+        <v>21.0999584197998</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G850" t="n">
-        <v>21.7068138122559</v>
+        <v>21.7068119049072</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G851" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G852" t="n">
-        <v>24.6477375030518</v>
+        <v>24.6477336883545</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G853" t="n">
-        <v>24.5076942443848</v>
+        <v>24.5076923370361</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G856" t="n">
-        <v>24.5076942443848</v>
+        <v>24.5076923370361</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G857" t="n">
-        <v>24.2276039123535</v>
+        <v>24.2276077270508</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G860" t="n">
-        <v>23.4807014465332</v>
+        <v>23.4807033538818</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G862" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406581878662</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G868" t="n">
-        <v>23.8074722290039</v>
+        <v>23.8074760437012</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G869" t="n">
-        <v>23.8074722290039</v>
+        <v>23.8074760437012</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G872" t="n">
-        <v>24.5076942443848</v>
+        <v>24.5076923370361</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>26.2656402587891</v>
       </c>
       <c r="G874" t="n">
-        <v>25.2545948028564</v>
+        <v>25.2545967102051</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>26.5083904266357</v>
       </c>
       <c r="G875" t="n">
-        <v>25.488000869751</v>
+        <v>25.4879989624023</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G876" t="n">
-        <v>25.2079124450684</v>
+        <v>25.207914352417</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G880" t="n">
-        <v>23.4807014465332</v>
+        <v>23.4807033538818</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G881" t="n">
-        <v>23.1539344787598</v>
+        <v>23.1539363861084</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G882" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>23.3040790557861</v>
       </c>
       <c r="G883" t="n">
-        <v>22.4070339202881</v>
+        <v>22.4070358276367</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G885" t="n">
-        <v>22.9672088623047</v>
+        <v>22.9672107696533</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G888" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G891" t="n">
-        <v>24.5543727874756</v>
+        <v>24.5543746948242</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G892" t="n">
-        <v>24.5076942443848</v>
+        <v>24.5076923370361</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G893" t="n">
-        <v>24.3676528930664</v>
+        <v>24.3676490783691</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G896" t="n">
-        <v>24.3676528930664</v>
+        <v>24.3676490783691</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G897" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G898" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G899" t="n">
-        <v>23.0605716705322</v>
+        <v>23.0605735778809</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G901" t="n">
-        <v>23.5740661621094</v>
+        <v>23.574068069458</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G903" t="n">
-        <v>23.8074722290039</v>
+        <v>23.8074760437012</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G904" t="n">
-        <v>24.6944198608398</v>
+        <v>24.6944179534912</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G906" t="n">
-        <v>24.461009979248</v>
+        <v>24.4610118865967</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G907" t="n">
-        <v>24.461009979248</v>
+        <v>24.4610118865967</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G909" t="n">
-        <v>23.8074722290039</v>
+        <v>23.8074760437012</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G910" t="n">
-        <v>23.714111328125</v>
+        <v>23.7141132354736</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G911" t="n">
-        <v>23.4807014465332</v>
+        <v>23.4807033538818</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>26.0228881835938</v>
       </c>
       <c r="G913" t="n">
-        <v>25.0211868286133</v>
+        <v>25.0211849212646</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G914" t="n">
-        <v>24.9745044708252</v>
+        <v>24.9745063781738</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G916" t="n">
-        <v>23.4807014465332</v>
+        <v>23.4807033538818</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G918" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406581878662</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G921" t="n">
-        <v>21.3800449371338</v>
+        <v>21.3800430297852</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G922" t="n">
-        <v>21.0532779693604</v>
+        <v>21.0532760620117</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G926" t="n">
-        <v>19.8395595550537</v>
+        <v>19.8395576477051</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G927" t="n">
-        <v>21.1466369628906</v>
+        <v>21.146635055542</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G928" t="n">
-        <v>21.6601314544678</v>
+        <v>21.6601333618164</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G929" t="n">
-        <v>21.1466369628906</v>
+        <v>21.146635055542</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G934" t="n">
-        <v>21.4734058380127</v>
+        <v>21.4734077453613</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G935" t="n">
-        <v>21.3800449371338</v>
+        <v>21.3800430297852</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G936" t="n">
-        <v>21.2399997711182</v>
+        <v>21.2399978637695</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G937" t="n">
-        <v>21.7068138122559</v>
+        <v>21.7068119049072</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G938" t="n">
-        <v>21.1466369628906</v>
+        <v>21.146635055542</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G939" t="n">
-        <v>21.0532779693604</v>
+        <v>21.0532760620117</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>19.8570175170898</v>
       </c>
       <c r="G943" t="n">
-        <v>19.0926609039307</v>
+        <v>19.092658996582</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>19.1870250701904</v>
       </c>
       <c r="G944" t="n">
-        <v>18.4484558105469</v>
+        <v>18.4484577178955</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G945" t="n">
-        <v>19.7461967468262</v>
+        <v>19.7461948394775</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G947" t="n">
-        <v>19.3260650634766</v>
+        <v>19.3260669708252</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>20.0026683807373</v>
       </c>
       <c r="G948" t="n">
-        <v>19.2327060699463</v>
+        <v>19.2327041625977</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>17.9053001403809</v>
       </c>
       <c r="G950" t="n">
-        <v>17.2160682678223</v>
+        <v>17.2160701751709</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G951" t="n">
-        <v>16.9359817504883</v>
+        <v>16.9359798431396</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G956" t="n">
-        <v>19.7928771972656</v>
+        <v>19.7928791046143</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G957" t="n">
-        <v>19.4194297790527</v>
+        <v>19.4194278717041</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G962" t="n">
-        <v>21.6601314544678</v>
+        <v>21.6601333618164</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G963" t="n">
-        <v>21.7068138122559</v>
+        <v>21.7068119049072</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G964" t="n">
-        <v>21.5200881958008</v>
+        <v>21.5200862884521</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G966" t="n">
-        <v>21.6601314544678</v>
+        <v>21.6601333618164</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G967" t="n">
-        <v>22.1736278533936</v>
+        <v>22.1736259460449</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G969" t="n">
-        <v>21.7068138122559</v>
+        <v>21.7068119049072</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G971" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530559539795</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G972" t="n">
-        <v>20.166332244873</v>
+        <v>20.1663303375244</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G976" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530559539795</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G977" t="n">
-        <v>20.166332244873</v>
+        <v>20.1663303375244</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G979" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530559539795</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G982" t="n">
-        <v>21.6601314544678</v>
+        <v>21.6601333618164</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G984" t="n">
-        <v>21.5200881958008</v>
+        <v>21.5200862884521</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G985" t="n">
-        <v>21.4734058380127</v>
+        <v>21.4734077453613</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G986" t="n">
-        <v>21.3800449371338</v>
+        <v>21.3800430297852</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G988" t="n">
-        <v>21.5200881958008</v>
+        <v>21.5200862884521</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G989" t="n">
-        <v>22.1736278533936</v>
+        <v>22.1736259460449</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G996" t="n">
-        <v>18.9526176452637</v>
+        <v>18.9526138305664</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>22.6243762969971</v>
       </c>
       <c r="G998" t="n">
-        <v>21.7534942626953</v>
+        <v>21.7534961700439</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G999" t="n">
-        <v>20.8198661804199</v>
+        <v>20.8198680877686</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1002" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530559539795</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G1006" t="n">
-        <v>19.7461967468262</v>
+        <v>19.7461948394775</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1010" t="n">
-        <v>20.8198661804199</v>
+        <v>20.8198680877686</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1011" t="n">
-        <v>20.8198661804199</v>
+        <v>20.8198680877686</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1019" t="n">
-        <v>18.2057151794434</v>
+        <v>18.2057132720947</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>17.7887802124023</v>
       </c>
       <c r="G1022" t="n">
-        <v>17.1040325164795</v>
+        <v>17.1040363311768</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.0853652954102</v>
+        <v>17.0853633880615</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G1025" t="n">
-        <v>16.8312034606934</v>
+        <v>16.8312015533447</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G1026" t="n">
-        <v>16.7935485839844</v>
+        <v>16.7935466766357</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>18.4102230072021</v>
       </c>
       <c r="G1032" t="n">
-        <v>17.8478507995605</v>
+        <v>17.8478527069092</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G1033" t="n">
-        <v>17.6972351074219</v>
+        <v>17.6972370147705</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1035" t="n">
-        <v>18.1302528381348</v>
+        <v>18.1302547454834</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1036" t="n">
-        <v>18.0549449920654</v>
+        <v>18.0549468994141</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1041" t="n">
-        <v>18.1302528381348</v>
+        <v>18.1302547454834</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>18.3908023834229</v>
       </c>
       <c r="G1042" t="n">
-        <v>17.8290233612061</v>
+        <v>17.8290214538574</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>19.225866317749</v>
       </c>
       <c r="G1046" t="n">
-        <v>18.638578414917</v>
+        <v>18.6385803222656</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G1047" t="n">
-        <v>19.7211246490479</v>
+        <v>19.7211227416992</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1048" t="n">
-        <v>20.0505924224854</v>
+        <v>20.0505905151367</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1050" t="n">
-        <v>20.7095336914062</v>
+        <v>20.7095317840576</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1055" t="n">
-        <v>20.0505924224854</v>
+        <v>20.0505905151367</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1056" t="n">
-        <v>20.1447277069092</v>
+        <v>20.1447257995605</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1062" t="n">
-        <v>22.4510116577148</v>
+        <v>22.4510154724121</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G1064" t="n">
-        <v>21.8862113952637</v>
+        <v>21.886209487915</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G1065" t="n">
-        <v>21.3214054107666</v>
+        <v>21.321403503418</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>21.9446754455566</v>
       </c>
       <c r="G1067" t="n">
-        <v>21.2743358612061</v>
+        <v>21.2743377685547</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1068" t="n">
-        <v>20.7095336914062</v>
+        <v>20.7095317840576</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1071" t="n">
-        <v>20.6624641418457</v>
+        <v>20.6624622344971</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G1072" t="n">
-        <v>20.285924911499</v>
+        <v>20.2859268188477</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1073" t="n">
-        <v>20.1447277069092</v>
+        <v>20.1447257995605</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1074" t="n">
-        <v>20.1447277069092</v>
+        <v>20.1447257995605</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1075" t="n">
-        <v>20.1447277069092</v>
+        <v>20.1447257995605</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G1076" t="n">
-        <v>19.5328559875488</v>
+        <v>19.5328540802002</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1077" t="n">
-        <v>20.0976581573486</v>
+        <v>20.0976600646973</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G1078" t="n">
-        <v>19.8152542114258</v>
+        <v>19.8152561187744</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1079" t="n">
-        <v>19.5799217224121</v>
+        <v>19.5799198150635</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>20.0512180328369</v>
       </c>
       <c r="G1081" t="n">
-        <v>19.438720703125</v>
+        <v>19.4387187957764</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G1082" t="n">
-        <v>19.9093914031982</v>
+        <v>19.9093894958496</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>20.245418548584</v>
       </c>
       <c r="G1083" t="n">
-        <v>19.6269855499268</v>
+        <v>19.6269874572754</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G1085" t="n">
-        <v>18.8739128112793</v>
+        <v>18.8739147186279</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1086" t="n">
-        <v>18.9209804534912</v>
+        <v>18.9209823608398</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G1088" t="n">
-        <v>18.2432155609131</v>
+        <v>18.2432136535645</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G1089" t="n">
-        <v>17.8101978302002</v>
+        <v>17.8101997375488</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G1091" t="n">
-        <v>17.6031036376953</v>
+        <v>17.6031017303467</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G1092" t="n">
-        <v>18.2620429992676</v>
+        <v>18.2620410919189</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1093" t="n">
-        <v>18.0549449920654</v>
+        <v>18.0549468994141</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>18.2354412078857</v>
       </c>
       <c r="G1095" t="n">
-        <v>17.678409576416</v>
+        <v>17.6784076690674</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G1096" t="n">
-        <v>16.8876800537109</v>
+        <v>16.8876838684082</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G1097" t="n">
-        <v>18.0172901153564</v>
+        <v>18.0172920227051</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1098" t="n">
-        <v>18.9680500030518</v>
+        <v>18.9680480957031</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1100" t="n">
-        <v>18.9680500030518</v>
+        <v>18.9680480957031</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G1102" t="n">
-        <v>18.0361213684082</v>
+        <v>18.0361175537109</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G1103" t="n">
-        <v>18.1679077148438</v>
+        <v>18.1679096221924</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>18.9734058380127</v>
       </c>
       <c r="G1104" t="n">
-        <v>18.3938312530518</v>
+        <v>18.3938293457031</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1105" t="n">
-        <v>18.0549449920654</v>
+        <v>18.0549468994141</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1106" t="n">
-        <v>18.1302528381348</v>
+        <v>18.1302547454834</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G1109" t="n">
-        <v>18.2432155609131</v>
+        <v>18.2432136535645</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1112" t="n">
-        <v>18.3561763763428</v>
+        <v>18.3561744689941</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1113" t="n">
-        <v>18.9209804534912</v>
+        <v>18.9209823608398</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1115" t="n">
-        <v>20.4741954803467</v>
+        <v>20.4741973876953</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1119" t="n">
-        <v>20.3800621032715</v>
+        <v>20.3800640106201</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1121" t="n">
-        <v>20.0505924224854</v>
+        <v>20.0505905151367</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1122" t="n">
-        <v>20.4741954803467</v>
+        <v>20.4741973876953</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1124" t="n">
-        <v>20.7095336914062</v>
+        <v>20.7095317840576</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1126" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1128" t="n">
-        <v>24.0042304992676</v>
+        <v>24.0042324066162</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1129" t="n">
-        <v>24.6161003112793</v>
+        <v>24.6161022186279</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1130" t="n">
-        <v>23.2040882110596</v>
+        <v>23.2040901184082</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1131" t="n">
-        <v>23.2040882110596</v>
+        <v>23.2040901184082</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1132" t="n">
-        <v>23.2511558532715</v>
+        <v>23.2511577606201</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1134" t="n">
-        <v>23.2511558532715</v>
+        <v>23.2511577606201</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1135" t="n">
-        <v>23.5335597991943</v>
+        <v>23.5335578918457</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1139" t="n">
-        <v>21.9803428649902</v>
+        <v>21.9803447723389</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1140" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>23.3526306152344</v>
       </c>
       <c r="G1142" t="n">
-        <v>22.6392822265625</v>
+        <v>22.6392841339111</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1143" t="n">
-        <v>22.8746204376221</v>
+        <v>22.8746185302734</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1144" t="n">
-        <v>21.9803428649902</v>
+        <v>21.9803447723389</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1146" t="n">
-        <v>22.686351776123</v>
+        <v>22.6863498687744</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1147" t="n">
-        <v>23.5335597991943</v>
+        <v>23.5335578918457</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1149" t="n">
-        <v>24.192497253418</v>
+        <v>24.1924953460693</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1150" t="n">
-        <v>24.0042304992676</v>
+        <v>24.0042324066162</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>22.9642276763916</v>
       </c>
       <c r="G1153" t="n">
-        <v>22.2627449035645</v>
+        <v>22.2627468109131</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G1154" t="n">
-        <v>21.8391418457031</v>
+        <v>21.8391437530518</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1155" t="n">
-        <v>22.686351776123</v>
+        <v>22.6863498687744</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1157" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1158" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1159" t="n">
-        <v>21.9803428649902</v>
+        <v>21.9803447723389</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1160" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1163" t="n">
-        <v>21.9803428649902</v>
+        <v>21.9803447723389</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1166" t="n">
-        <v>21.6508731842041</v>
+        <v>21.6508750915527</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G1167" t="n">
-        <v>21.8862113952637</v>
+        <v>21.886209487915</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G1169" t="n">
-        <v>21.4155387878418</v>
+        <v>21.4155368804932</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G1170" t="n">
-        <v>21.2272701263428</v>
+        <v>21.2272720336914</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G1172" t="n">
-        <v>21.7920742034912</v>
+        <v>21.7920780181885</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1173" t="n">
-        <v>21.6508731842041</v>
+        <v>21.6508750915527</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>22.9642276763916</v>
       </c>
       <c r="G1174" t="n">
-        <v>22.2627449035645</v>
+        <v>22.2627468109131</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1175" t="n">
-        <v>21.6508731842041</v>
+        <v>21.6508750915527</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1178" t="n">
-        <v>22.8746204376221</v>
+        <v>22.8746185302734</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1180" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.9803428649902</v>
+        <v>21.9803447723389</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G1182" t="n">
-        <v>21.7920742034912</v>
+        <v>21.7920780181885</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1184" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1185" t="n">
-        <v>23.3452892303467</v>
+        <v>23.3452911376953</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1186" t="n">
-        <v>24.6161003112793</v>
+        <v>24.6161022186279</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G1187" t="n">
-        <v>24.5219669342041</v>
+        <v>24.5219688415527</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G1188" t="n">
-        <v>23.8159599304199</v>
+        <v>23.8159618377686</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1189" t="n">
-        <v>23.2040882110596</v>
+        <v>23.2040901184082</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.757303237915</v>
+        <v>24.7573051452637</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1196" t="n">
-        <v>24.2395687103271</v>
+        <v>24.2395668029785</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1197" t="n">
-        <v>24.0042304992676</v>
+        <v>24.0042324066162</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1198" t="n">
-        <v>24.4278335571289</v>
+        <v>24.4278354644775</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1200" t="n">
-        <v>24.8514385223389</v>
+        <v>24.8514366149902</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1203" t="n">
-        <v>24.8514385223389</v>
+        <v>24.8514366149902</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1205" t="n">
-        <v>24.192497253418</v>
+        <v>24.1924953460693</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1206" t="n">
-        <v>24.8514385223389</v>
+        <v>24.8514366149902</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>26.1685390472412</v>
       </c>
       <c r="G1208" t="n">
-        <v>25.369176864624</v>
+        <v>25.3691749572754</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G1210" t="n">
-        <v>25.180908203125</v>
+        <v>25.1809101104736</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1214" t="n">
-        <v>23.2040882110596</v>
+        <v>23.2040901184082</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1215" t="n">
-        <v>23.3923568725586</v>
+        <v>23.39235496521</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1218" t="n">
-        <v>23.1099529266357</v>
+        <v>23.1099548339844</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1223" t="n">
-        <v>23.3452892303467</v>
+        <v>23.3452911376953</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1227" t="n">
-        <v>24.2395687103271</v>
+        <v>24.2395668029785</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1228" t="n">
-        <v>23.6276912689209</v>
+        <v>23.6276931762695</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1229" t="n">
-        <v>23.1099529266357</v>
+        <v>23.1099548339844</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1232" t="n">
-        <v>22.8746204376221</v>
+        <v>22.8746185302734</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1233" t="n">
-        <v>23.1099529266357</v>
+        <v>23.1099548339844</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1234" t="n">
-        <v>23.6276912689209</v>
+        <v>23.6276931762695</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1236" t="n">
-        <v>22.4510116577148</v>
+        <v>22.4510154724121</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1237" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1238" t="n">
-        <v>22.686351776123</v>
+        <v>22.6863498687744</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1240" t="n">
-        <v>21.9803428649902</v>
+        <v>21.9803447723389</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G1241" t="n">
-        <v>21.3214054107666</v>
+        <v>21.321403503418</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G1243" t="n">
-        <v>22.498083114624</v>
+        <v>22.4980812072754</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1247" t="n">
-        <v>22.4510116577148</v>
+        <v>22.4510154724121</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G1248" t="n">
-        <v>22.498083114624</v>
+        <v>22.4980812072754</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1249" t="n">
-        <v>23.2511558532715</v>
+        <v>23.2511577606201</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1250" t="n">
-        <v>23.5335597991943</v>
+        <v>23.5335578918457</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1252" t="n">
-        <v>23.3923568725586</v>
+        <v>23.39235496521</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1253" t="n">
-        <v>23.6276912689209</v>
+        <v>23.6276931762695</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1255" t="n">
-        <v>22.8746204376221</v>
+        <v>22.8746185302734</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1261" t="n">
-        <v>22.4510116577148</v>
+        <v>22.4510154724121</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1262" t="n">
-        <v>22.686351776123</v>
+        <v>22.6863498687744</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1264" t="n">
-        <v>23.6276912689209</v>
+        <v>23.6276931762695</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1266" t="n">
-        <v>24.4278335571289</v>
+        <v>24.4278354644775</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G1267" t="n">
-        <v>24.8985080718994</v>
+        <v>24.8985042572021</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>27.1395435333252</v>
       </c>
       <c r="G1269" t="n">
-        <v>26.3105201721191</v>
+        <v>26.3105182647705</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>26.4598407745361</v>
       </c>
       <c r="G1273" t="n">
-        <v>25.6515808105469</v>
+        <v>25.6515789031982</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>27.3337421417236</v>
       </c>
       <c r="G1278" t="n">
-        <v>26.4987850189209</v>
+        <v>26.4987869262695</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>26.7996921539307</v>
       </c>
       <c r="G1279" t="n">
-        <v>26.1482486724854</v>
+        <v>26.148250579834</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1280" t="n">
-        <v>25.5798091888428</v>
+        <v>25.5798110961914</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G1281" t="n">
-        <v>25.4850692749023</v>
+        <v>25.485071182251</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1282" t="n">
-        <v>25.5798091888428</v>
+        <v>25.5798110961914</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>26.3141899108887</v>
       </c>
       <c r="G1283" t="n">
-        <v>25.6745491027832</v>
+        <v>25.6745471954346</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1285" t="n">
-        <v>25.5798091888428</v>
+        <v>25.5798110961914</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1286" t="n">
-        <v>25.7219200134277</v>
+        <v>25.7219181060791</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>26.7996921539307</v>
       </c>
       <c r="G1288" t="n">
-        <v>26.1482486724854</v>
+        <v>26.148250579834</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>26.6054916381836</v>
       </c>
       <c r="G1290" t="n">
-        <v>25.9587688446045</v>
+        <v>25.9587707519531</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1291" t="n">
-        <v>25.7219200134277</v>
+        <v>25.7219181060791</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G1294" t="n">
-        <v>25.4850692749023</v>
+        <v>25.485071182251</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>26.2656402587891</v>
       </c>
       <c r="G1295" t="n">
-        <v>25.6271781921387</v>
+        <v>25.6271820068359</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G1297" t="n">
-        <v>25.0587406158447</v>
+        <v>25.0587387084961</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>25.7315883636475</v>
       </c>
       <c r="G1298" t="n">
-        <v>25.106107711792</v>
+        <v>25.1061096191406</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1301" t="n">
-        <v>25.0113697052002</v>
+        <v>25.0113677978516</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1302" t="n">
-        <v>24.3955612182617</v>
+        <v>24.3955593109131</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1305" t="n">
-        <v>23.7797470092773</v>
+        <v>23.779748916626</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G1309" t="n">
-        <v>24.6797771453857</v>
+        <v>24.6797790527344</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1312" t="n">
-        <v>24.3481884002686</v>
+        <v>24.3481864929199</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1313" t="n">
-        <v>24.3955612182617</v>
+        <v>24.3955593109131</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1314" t="n">
-        <v>23.7797470092773</v>
+        <v>23.779748916626</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1315" t="n">
-        <v>23.7323799133301</v>
+        <v>23.7323780059814</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1316" t="n">
-        <v>23.7797470092773</v>
+        <v>23.779748916626</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1318" t="n">
-        <v>23.5429000854492</v>
+        <v>23.542896270752</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1319" t="n">
-        <v>23.6850090026855</v>
+        <v>23.6850070953369</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1322" t="n">
-        <v>23.7323799133301</v>
+        <v>23.7323780059814</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G1323" t="n">
-        <v>23.9218578338623</v>
+        <v>23.9218597412109</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1324" t="n">
-        <v>24.4902992248535</v>
+        <v>24.4902973175049</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1325" t="n">
-        <v>23.7797470092773</v>
+        <v>23.779748916626</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1326" t="n">
-        <v>23.5429000854492</v>
+        <v>23.542896270752</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1327" t="n">
-        <v>23.874490737915</v>
+        <v>23.8744888305664</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1328" t="n">
-        <v>24.2534465789795</v>
+        <v>24.2534484863281</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1329" t="n">
-        <v>24.2534465789795</v>
+        <v>24.2534484863281</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1330" t="n">
-        <v>23.7323799133301</v>
+        <v>23.7323780059814</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1331" t="n">
-        <v>24.5850391387939</v>
+        <v>24.5850410461426</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1334" t="n">
-        <v>25.5798091888428</v>
+        <v>25.5798110961914</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1336" t="n">
-        <v>23.874490737915</v>
+        <v>23.8744888305664</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1337" t="n">
-        <v>23.4955272674561</v>
+        <v>23.4955291748047</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1339" t="n">
-        <v>23.0691986083984</v>
+        <v>23.0691967010498</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1340" t="n">
-        <v>23.0691986083984</v>
+        <v>23.0691967010498</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1341" t="n">
-        <v>23.0691986083984</v>
+        <v>23.0691967010498</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>23.3040790557861</v>
       </c>
       <c r="G1343" t="n">
-        <v>22.7376079559326</v>
+        <v>22.7376098632812</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1345" t="n">
-        <v>21.7902069091797</v>
+        <v>21.7902088165283</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G1346" t="n">
-        <v>21.0322875976562</v>
+        <v>21.0322895050049</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1348" t="n">
-        <v>20.7954368591309</v>
+        <v>20.7954349517822</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1355" t="n">
-        <v>20.7954368591309</v>
+        <v>20.7954349517822</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G1358" t="n">
-        <v>19.9427757263184</v>
+        <v>19.942777633667</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1363" t="n">
-        <v>20.5112171173096</v>
+        <v>20.5112190246582</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1364" t="n">
-        <v>20.7954368591309</v>
+        <v>20.7954349517822</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>18.9734058380127</v>
       </c>
       <c r="G1367" t="n">
-        <v>18.5122051239014</v>
+        <v>18.5122032165527</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>18.8568840026855</v>
       </c>
       <c r="G1369" t="n">
-        <v>18.3985157012939</v>
+        <v>18.3985137939453</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>18.0218200683594</v>
       </c>
       <c r="G1372" t="n">
-        <v>17.5837478637695</v>
+        <v>17.5837497711182</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>18.1966018676758</v>
       </c>
       <c r="G1373" t="n">
-        <v>17.7542819976807</v>
+        <v>17.7542839050293</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>19.1093444824219</v>
       </c>
       <c r="G1374" t="n">
-        <v>18.6448364257812</v>
+        <v>18.6448383331299</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G1377" t="n">
-        <v>20.0848846435547</v>
+        <v>20.0848865509033</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1378" t="n">
-        <v>19.7059288024902</v>
+        <v>19.7059268951416</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1384" t="n">
-        <v>21.7902069091797</v>
+        <v>21.7902088165283</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1387" t="n">
-        <v>20.5112171173096</v>
+        <v>20.5112190246582</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1390" t="n">
-        <v>19.8065528869629</v>
+        <v>19.8065509796143</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1391" t="n">
-        <v>19.6601963043213</v>
+        <v>19.6601982116699</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1397" t="n">
-        <v>22.636058807373</v>
+        <v>22.6360607147217</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1402" t="n">
-        <v>21.6603679656982</v>
+        <v>21.6603660583496</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1409" t="n">
-        <v>23.367826461792</v>
+        <v>23.3678283691406</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>24.3435192108154</v>
+        <v>24.3435211181641</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>24.75</v>
       </c>
       <c r="G1414" t="n">
-        <v>24.148380279541</v>
+        <v>24.1483821868896</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>24.1971664428711</v>
+        <v>24.1971645355225</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1416" t="n">
-        <v>23.367826461792</v>
+        <v>23.3678283691406</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>22.0506439208984</v>
+        <v>22.0506420135498</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1428" t="n">
-        <v>22.2945671081543</v>
+        <v>22.2945652008057</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>21.6603679656982</v>
+        <v>21.6603660583496</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1430" t="n">
-        <v>21.5627956390381</v>
+        <v>21.5627994537354</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1432" t="n">
-        <v>22.1482124328613</v>
+        <v>22.14821434021</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1438" t="n">
-        <v>22.2945671081543</v>
+        <v>22.2945652008057</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1439" t="n">
-        <v>21.8067207336426</v>
+        <v>21.8067226409912</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1441" t="n">
-        <v>21.5627956390381</v>
+        <v>21.5627994537354</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1447" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1448" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1449" t="n">
-        <v>22.2945671081543</v>
+        <v>22.2945652008057</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1451" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1452" t="n">
-        <v>21.6603679656982</v>
+        <v>21.6603660583496</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1453" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1454" t="n">
-        <v>21.6603679656982</v>
+        <v>21.6603660583496</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>22</v>
       </c>
       <c r="G1456" t="n">
-        <v>21.4652290344238</v>
+        <v>21.4652271270752</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1457" t="n">
-        <v>21.074951171875</v>
+        <v>21.0749530792236</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1458" t="n">
-        <v>20.8798122406006</v>
+        <v>20.879810333252</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1459" t="n">
-        <v>21.3188743591309</v>
+        <v>21.3188762664795</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>21.5</v>
       </c>
       <c r="G1461" t="n">
-        <v>20.9773807525635</v>
+        <v>20.9773826599121</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>19.6114139556885</v>
+        <v>19.6114120483398</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>18.8308601379395</v>
+        <v>18.8308582305908</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1469" t="n">
-        <v>19.0845375061035</v>
+        <v>19.0845394134521</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1470" t="n">
-        <v>19.0650234222412</v>
+        <v>19.0650272369385</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1472" t="n">
-        <v>18.9869709014893</v>
+        <v>18.9869689941406</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1473" t="n">
-        <v>19.6601963043213</v>
+        <v>19.6601982116699</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>20.5</v>
       </c>
       <c r="G1476" t="n">
-        <v>20.0016918182373</v>
+        <v>20.0016899108887</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>20.5</v>
       </c>
       <c r="G1479" t="n">
-        <v>20.0016918182373</v>
+        <v>20.0016899108887</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1486" t="n">
-        <v>19.240650177002</v>
+        <v>19.2406482696533</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1487" t="n">
-        <v>18.8308601379395</v>
+        <v>18.8308582305908</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1488" t="n">
-        <v>18.6162071228027</v>
+        <v>18.6162052154541</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1489" t="n">
-        <v>18.2844734191895</v>
+        <v>18.2844715118408</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>18.5</v>
       </c>
       <c r="G1490" t="n">
-        <v>18.0503063201904</v>
+        <v>18.0503044128418</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1492" t="n">
-        <v>17.9722480773926</v>
+        <v>17.9722499847412</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.0307922363281</v>
+        <v>18.0307903289795</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1496" t="n">
-        <v>17.6014881134033</v>
+        <v>17.6014862060547</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1497" t="n">
-        <v>18.2844734191895</v>
+        <v>18.2844715118408</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1499" t="n">
-        <v>18.5576648712158</v>
+        <v>18.5576667785645</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1500" t="n">
-        <v>18.5186367034912</v>
+        <v>18.5186386108398</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1502" t="n">
-        <v>18.5576648712158</v>
+        <v>18.5576667785645</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1503" t="n">
-        <v>18.7528038024902</v>
+        <v>18.7528018951416</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1504" t="n">
-        <v>18.6162071228027</v>
+        <v>18.6162052154541</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1506" t="n">
-        <v>18.1673889160156</v>
+        <v>18.1673908233643</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1507" t="n">
-        <v>18.128360748291</v>
+        <v>18.1283588409424</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1509" t="n">
-        <v>18.36252784729</v>
+        <v>18.3625259399414</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1512" t="n">
-        <v>18.0112781524658</v>
+        <v>18.0112762451172</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1514" t="n">
-        <v>17.1526679992676</v>
+        <v>17.1526699066162</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1518" t="n">
-        <v>17.5234298706055</v>
+        <v>17.5234317779541</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1520" t="n">
-        <v>17.1136417388916</v>
+        <v>17.113639831543</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1522" t="n">
-        <v>17.3478050231934</v>
+        <v>17.347806930542</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1524" t="n">
-        <v>17.1331558227539</v>
+        <v>17.1331539154053</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1525" t="n">
-        <v>16.6648216247559</v>
+        <v>16.6648235321045</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>18</v>
       </c>
       <c r="G1529" t="n">
-        <v>17.5624580383301</v>
+        <v>17.5624599456787</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1530" t="n">
-        <v>17.0160713195801</v>
+        <v>17.0160732269287</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>17.5</v>
       </c>
       <c r="G1536" t="n">
-        <v>17.0746116638184</v>
+        <v>17.074613571167</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1542" t="n">
-        <v>16.8280143737793</v>
+        <v>16.8280124664307</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>16.5715484619141</v>
+        <v>16.5715465545654</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1546" t="n">
-        <v>17.3803977966309</v>
+        <v>17.3803997039795</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1547" t="n">
-        <v>17.4987678527832</v>
+        <v>17.4987659454346</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1553" t="n">
-        <v>17.0844764709473</v>
+        <v>17.0844783782959</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1554" t="n">
-        <v>17.5974063873291</v>
+        <v>17.5974082946777</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1557" t="n">
-        <v>17.3212127685547</v>
+        <v>17.3212146759033</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1562" t="n">
-        <v>16.5715484619141</v>
+        <v>16.5715465545654</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1563" t="n">
-        <v>16.6307315826416</v>
+        <v>16.6307334899902</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1564" t="n">
-        <v>16.8280143737793</v>
+        <v>16.8280124664307</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1567" t="n">
-        <v>15.5654182434082</v>
+        <v>15.5654191970825</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="n">
-        <v>15.6837863922119</v>
+        <v>15.6837873458862</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>16.5</v>
       </c>
       <c r="G1570" t="n">
-        <v>16.2756290435791</v>
+        <v>16.2756271362305</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1571" t="n">
-        <v>16.2361717224121</v>
+        <v>16.2361698150635</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1572" t="n">
-        <v>15.9205236434937</v>
+        <v>15.920521736145</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1573" t="n">
-        <v>16.0191631317139</v>
+        <v>16.0191650390625</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>16.3742694854736</v>
+        <v>16.374267578125</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1575" t="n">
-        <v>16.867467880249</v>
+        <v>16.8674697875977</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1578" t="n">
-        <v>17.4593105316162</v>
+        <v>17.4593124389648</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1579" t="n">
-        <v>17.1042041778564</v>
+        <v>17.1042060852051</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1583" t="n">
-        <v>17.5579490661621</v>
+        <v>17.5579509735107</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1588" t="n">
-        <v>16.867467880249</v>
+        <v>16.8674697875977</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1590" t="n">
-        <v>16.7491016387939</v>
+        <v>16.7490997314453</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1594" t="n">
-        <v>16.9858379364014</v>
+        <v>16.9858360290527</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1595" t="n">
-        <v>17.5579490661621</v>
+        <v>17.5579509735107</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1596" t="n">
-        <v>17.8144149780273</v>
+        <v>17.8144130706787</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1605" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1609" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1612" t="n">
-        <v>19.1361923217773</v>
+        <v>19.136194229126</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1613" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1615" t="n">
-        <v>18.761360168457</v>
+        <v>18.7613620758057</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1618" t="n">
-        <v>19.1361923217773</v>
+        <v>19.136194229126</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1621" t="n">
-        <v>19.4518413543701</v>
+        <v>19.4518394470215</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1622" t="n">
-        <v>19.0770072937012</v>
+        <v>19.0770092010498</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1630" t="n">
-        <v>18.5640811920166</v>
+        <v>18.564079284668</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1634" t="n">
-        <v>18.0511512756348</v>
+        <v>18.0511493682861</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1635" t="n">
-        <v>16.9858379364014</v>
+        <v>16.9858360290527</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1636" t="n">
-        <v>17.5974063873291</v>
+        <v>17.5974082946777</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1644" t="n">
-        <v>17.3803977966309</v>
+        <v>17.3803997039795</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1645" t="n">
-        <v>17.9130554199219</v>
+        <v>17.9130535125732</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1652" t="n">
-        <v>18.4457111358643</v>
+        <v>18.4457130432129</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1655" t="n">
-        <v>18.4457111358643</v>
+        <v>18.4457130432129</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1656" t="n">
-        <v>18.800817489624</v>
+        <v>18.8008155822754</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>19.294017791748</v>
+        <v>19.2940158843994</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1659" t="n">
-        <v>19.0770072937012</v>
+        <v>19.0770092010498</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1662" t="n">
-        <v>17.9130554199219</v>
+        <v>17.9130535125732</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1665" t="n">
-        <v>17.9525127410889</v>
+        <v>17.9525108337402</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1677" t="n">
-        <v>17.6171340942383</v>
+        <v>17.6171360015869</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1680" t="n">
-        <v>18.800817489624</v>
+        <v>18.8008155822754</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1681" t="n">
-        <v>18.8600006103516</v>
+        <v>18.8600025177002</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1682" t="n">
-        <v>18.8600006103516</v>
+        <v>18.8600025177002</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1684" t="n">
-        <v>18.8600006103516</v>
+        <v>18.8600025177002</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1685" t="n">
-        <v>19.1361923217773</v>
+        <v>19.136194229126</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1691" t="n">
-        <v>19.1559200286865</v>
+        <v>19.1559219360352</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1692" t="n">
-        <v>19.4912986755371</v>
+        <v>19.4912967681885</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1693" t="n">
-        <v>19.1559200286865</v>
+        <v>19.1559219360352</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1699" t="n">
-        <v>21.0103569030762</v>
+        <v>21.0103549957275</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>21</v>
       </c>
       <c r="G1705" t="n">
-        <v>20.7144355773926</v>
+        <v>20.7144374847412</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>20.75</v>
       </c>
       <c r="G1706" t="n">
-        <v>20.4678344726562</v>
+        <v>20.4678363800049</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1712" t="n">
-        <v>18.800817489624</v>
+        <v>18.8008155822754</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1715" t="n">
-        <v>20.6651153564453</v>
+        <v>20.6651172637939</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1717" t="n">
-        <v>19.3926582336426</v>
+        <v>19.3926563262939</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>20</v>
       </c>
       <c r="G1718" t="n">
-        <v>19.7280349731445</v>
+        <v>19.7280330657959</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1720" t="n">
-        <v>17.8933277130127</v>
+        <v>17.8933258056641</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1724" t="n">
-        <v>18.761360168457</v>
+        <v>18.7613620758057</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1729" t="n">
-        <v>17.3014850616455</v>
+        <v>17.3014869689941</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1731" t="n">
-        <v>16.6307315826416</v>
+        <v>16.6307334899902</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1732" t="n">
-        <v>16.5123653411865</v>
+        <v>16.5123634338379</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>16.5</v>
       </c>
       <c r="G1734" t="n">
-        <v>16.2756290435791</v>
+        <v>16.2756271362305</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>15</v>
       </c>
       <c r="G1736" t="n">
-        <v>14.7960252761841</v>
+        <v>14.7960262298584</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1740" t="n">
-        <v>15.6837863922119</v>
+        <v>15.6837873458862</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1742" t="n">
-        <v>16.6307315826416</v>
+        <v>16.6307334899902</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1743" t="n">
-        <v>16.3742694854736</v>
+        <v>16.374267578125</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1747" t="n">
-        <v>16.9858379364014</v>
+        <v>16.9858360290527</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1748" t="n">
-        <v>17.1042041778564</v>
+        <v>17.1042060852051</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1758" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1759" t="n">
-        <v>20.1719169616699</v>
+        <v>20.1719150543213</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1761" t="n">
-        <v>19.3926582336426</v>
+        <v>19.3926563262939</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>21</v>
       </c>
       <c r="G1763" t="n">
-        <v>20.7144355773926</v>
+        <v>20.7144374847412</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>20.75</v>
       </c>
       <c r="G1764" t="n">
-        <v>20.4678344726562</v>
+        <v>20.4678363800049</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1766" t="n">
-        <v>20.6157970428467</v>
+        <v>20.615795135498</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1767" t="n">
-        <v>20.1719169616699</v>
+        <v>20.1719150543213</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1768" t="n">
-        <v>20.6157970428467</v>
+        <v>20.615795135498</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1772" t="n">
-        <v>20.418514251709</v>
+        <v>20.4185161590576</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>20.75</v>
       </c>
       <c r="G1773" t="n">
-        <v>20.4678344726562</v>
+        <v>20.4678363800049</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1784" t="n">
-        <v>22.2433567047119</v>
+        <v>22.2433586120605</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1785" t="n">
-        <v>22.3419990539551</v>
+        <v>22.3419971466064</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -55154,6 +55154,32 @@
         <v>28.3999996185303</v>
       </c>
       <c r="H2107" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2108" t="n">
+        <v>58789</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>29.2000007629395</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>28.2000007629395</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>29.2000007629395</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>28.2000007629395</v>
+      </c>
+      <c r="G2108" t="n">
+        <v>28.2000007629395</v>
+      </c>
+      <c r="H2108" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G2" t="n">
-        <v>7.5317325592041</v>
+        <v>7.53173160552979</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G3" t="n">
-        <v>7.8512601852417</v>
+        <v>7.85125970840454</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G4" t="n">
-        <v>7.7599663734436</v>
+        <v>7.75996589660645</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G5" t="n">
-        <v>7.7599663734436</v>
+        <v>7.75996589660645</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>8.1253547668457</v>
       </c>
       <c r="G7" t="n">
-        <v>7.63945770263672</v>
+        <v>7.63945817947388</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.31955623626709</v>
       </c>
       <c r="G8" t="n">
-        <v>7.82204675674438</v>
+        <v>7.82204627990723</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.41859817504883</v>
       </c>
       <c r="G9" t="n">
-        <v>7.91516447067261</v>
+        <v>7.91516590118408</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.10884761810303</v>
       </c>
       <c r="G10" t="n">
-        <v>7.62393808364868</v>
+        <v>7.62393856048584</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>8.42830753326416</v>
       </c>
       <c r="G11" t="n">
-        <v>7.92429447174072</v>
+        <v>7.92429399490356</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G12" t="n">
-        <v>7.5317325592041</v>
+        <v>7.53173160552979</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G13" t="n">
-        <v>7.5317325592041</v>
+        <v>7.53173160552979</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>7.86609792709351</v>
       </c>
       <c r="G14" t="n">
-        <v>7.3957052230835</v>
+        <v>7.39570379257202</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>7.71656322479248</v>
       </c>
       <c r="G15" t="n">
-        <v>7.2551121711731</v>
+        <v>7.25511264801025</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.95154619216919</v>
       </c>
       <c r="G16" t="n">
-        <v>7.4760422706604</v>
+        <v>7.47604370117188</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>7.88940191268921</v>
       </c>
       <c r="G17" t="n">
-        <v>7.41761541366577</v>
+        <v>7.41761493682861</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>7.95251703262329</v>
       </c>
       <c r="G20" t="n">
-        <v>7.47695541381836</v>
+        <v>7.47695636749268</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>8.08068943023682</v>
       </c>
       <c r="G22" t="n">
-        <v>7.59746360778809</v>
+        <v>7.59746313095093</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>8.24381828308105</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75083780288696</v>
+        <v>7.75083827972412</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G25" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G27" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.45743942260742</v>
       </c>
       <c r="G28" t="n">
-        <v>7.95168590545654</v>
+        <v>7.95168495178223</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>8.31178760528564</v>
       </c>
       <c r="G29" t="n">
-        <v>7.81474113464355</v>
+        <v>7.81474256515503</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.47394561767578</v>
       </c>
       <c r="G30" t="n">
-        <v>7.96720457077026</v>
+        <v>7.96720266342163</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G31" t="n">
-        <v>7.8512601852417</v>
+        <v>7.85125970840454</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.20497798919678</v>
       </c>
       <c r="G33" t="n">
-        <v>7.71431922912598</v>
+        <v>7.71431970596313</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G34" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>8.31178760528564</v>
       </c>
       <c r="G37" t="n">
-        <v>7.81474113464355</v>
+        <v>7.81474256515503</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G38" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G39" t="n">
-        <v>7.8512601852417</v>
+        <v>7.85125970840454</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>8.12923908233643</v>
       </c>
       <c r="G41" t="n">
-        <v>7.6431097984314</v>
+        <v>7.64311027526855</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.23410797119141</v>
       </c>
       <c r="G42" t="n">
-        <v>7.74170684814453</v>
+        <v>7.74170827865601</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>8.1855583190918</v>
       </c>
       <c r="G43" t="n">
-        <v>7.69606161117554</v>
+        <v>7.6960620880127</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G45" t="n">
-        <v>7.8512601852417</v>
+        <v>7.85125970840454</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.99232816696167</v>
       </c>
       <c r="G47" t="n">
-        <v>7.51438665390015</v>
+        <v>7.51438617706299</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>8.10787677764893</v>
       </c>
       <c r="G48" t="n">
-        <v>7.62302589416504</v>
+        <v>7.62302541732788</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>8.22634029388428</v>
       </c>
       <c r="G49" t="n">
-        <v>7.73440551757812</v>
+        <v>7.73440456390381</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>8.44772911071777</v>
       </c>
       <c r="G51" t="n">
-        <v>7.94255399703979</v>
+        <v>7.94255352020264</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>8.51667022705078</v>
       </c>
       <c r="G52" t="n">
-        <v>8.00737380981445</v>
+        <v>8.00737190246582</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>8.57395935058594</v>
       </c>
       <c r="G53" t="n">
-        <v>8.06123638153076</v>
+        <v>8.06123733520508</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>8.94293975830078</v>
       </c>
       <c r="G55" t="n">
-        <v>8.40815258026123</v>
+        <v>8.40815162658691</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.24977684020996</v>
       </c>
       <c r="G57" t="n">
-        <v>8.69664096832275</v>
+        <v>8.69663906097412</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.71960926055908</v>
       </c>
       <c r="G61" t="n">
-        <v>8.19817543029785</v>
+        <v>8.19817638397217</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.94973659515381</v>
       </c>
       <c r="G62" t="n">
-        <v>8.41454219818115</v>
+        <v>8.41454124450684</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G63" t="n">
-        <v>8.30772972106934</v>
+        <v>8.3077278137207</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G64" t="n">
-        <v>8.39902210235596</v>
+        <v>8.39902305603027</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.24395084381104</v>
       </c>
       <c r="G66" t="n">
-        <v>8.69116306304932</v>
+        <v>8.69116401672363</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.10412693023682</v>
       </c>
       <c r="G67" t="n">
-        <v>8.55969905853271</v>
+        <v>8.55970001220703</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>9.15656089782715</v>
       </c>
       <c r="G68" t="n">
-        <v>8.6089973449707</v>
+        <v>8.60899829864502</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.29250144958496</v>
       </c>
       <c r="G69" t="n">
-        <v>8.73680973052979</v>
+        <v>8.73680877685547</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.51583194732666</v>
       </c>
       <c r="G70" t="n">
-        <v>8.94678592681885</v>
+        <v>8.94678401947021</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.51583194732666</v>
       </c>
       <c r="G71" t="n">
-        <v>8.94678592681885</v>
+        <v>8.94678401947021</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.37115287780762</v>
       </c>
       <c r="G72" t="n">
-        <v>8.81075859069824</v>
+        <v>8.81075668334961</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.63235282897949</v>
       </c>
       <c r="G73" t="n">
-        <v>9.0563383102417</v>
+        <v>9.05633735656738</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G75" t="n">
-        <v>9.27544212341309</v>
+        <v>9.2754430770874</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.61293315887451</v>
       </c>
       <c r="G76" t="n">
-        <v>9.03807926177979</v>
+        <v>9.03807830810547</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.70614910125732</v>
       </c>
       <c r="G79" t="n">
-        <v>9.12572288513184</v>
+        <v>9.12572193145752</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.57506275177002</v>
       </c>
       <c r="G80" t="n">
-        <v>9.00247478485107</v>
+        <v>9.00247287750244</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.55467224121094</v>
       </c>
       <c r="G84" t="n">
-        <v>8.98330402374268</v>
+        <v>8.98330307006836</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.40610885620117</v>
       </c>
       <c r="G85" t="n">
-        <v>8.84362316131592</v>
+        <v>8.8436222076416</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.16238689422607</v>
       </c>
       <c r="G86" t="n">
-        <v>8.61447620391846</v>
+        <v>8.61447525024414</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G88" t="n">
-        <v>8.30772972106934</v>
+        <v>8.3077278137207</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>8.43413352966309</v>
       </c>
       <c r="G89" t="n">
-        <v>7.929771900177</v>
+        <v>7.92977237701416</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>8.77689933776855</v>
       </c>
       <c r="G90" t="n">
-        <v>8.25204086303711</v>
+        <v>8.25203895568848</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>8.88467979431152</v>
       </c>
       <c r="G91" t="n">
-        <v>8.35337734222412</v>
+        <v>8.3533763885498</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.07888126373291</v>
       </c>
       <c r="G93" t="n">
-        <v>8.53596305847168</v>
+        <v>8.535964012146</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.12743091583252</v>
       </c>
       <c r="G94" t="n">
-        <v>8.58161163330078</v>
+        <v>8.58161067962646</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.07888126373291</v>
       </c>
       <c r="G95" t="n">
-        <v>8.53596305847168</v>
+        <v>8.535964012146</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.30706596374512</v>
       </c>
       <c r="G96" t="n">
-        <v>8.75050258636475</v>
+        <v>8.75050163269043</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G97" t="n">
-        <v>8.30772972106934</v>
+        <v>8.3077278137207</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G98" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>8.48462677001953</v>
       </c>
       <c r="G99" t="n">
-        <v>7.97724437713623</v>
+        <v>7.97724485397339</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G101" t="n">
-        <v>7.7599663734436</v>
+        <v>7.75996589660645</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>8.19041347503662</v>
       </c>
       <c r="G102" t="n">
-        <v>7.70062637329102</v>
+        <v>7.70062589645386</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>8.3700475692749</v>
       </c>
       <c r="G103" t="n">
-        <v>7.86951780319214</v>
+        <v>7.8695182800293</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>8.3700475692749</v>
       </c>
       <c r="G104" t="n">
-        <v>7.86951780319214</v>
+        <v>7.8695182800293</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.81476783752441</v>
       </c>
       <c r="G105" t="n">
-        <v>8.2876443862915</v>
+        <v>8.28764343261719</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.27210998535156</v>
       </c>
       <c r="G106" t="n">
-        <v>8.71763610839844</v>
+        <v>8.71763706207275</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.27502346038818</v>
       </c>
       <c r="G107" t="n">
-        <v>8.72037506103516</v>
+        <v>8.72037601470947</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.25074768066406</v>
       </c>
       <c r="G108" t="n">
-        <v>8.69755363464355</v>
+        <v>8.69755172729492</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.98760604858398</v>
       </c>
       <c r="G109" t="n">
-        <v>8.45014572143555</v>
+        <v>8.45014762878418</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.08664894104004</v>
       </c>
       <c r="G110" t="n">
-        <v>8.54326820373535</v>
+        <v>8.54326629638672</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.19443035125732</v>
       </c>
       <c r="G111" t="n">
-        <v>8.64460277557373</v>
+        <v>8.64460182189941</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>8.86817264556885</v>
       </c>
       <c r="G113" t="n">
-        <v>8.33785724639893</v>
+        <v>8.33785533905029</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.81379699707031</v>
       </c>
       <c r="G114" t="n">
-        <v>8.28673267364502</v>
+        <v>8.28673076629639</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>9.04586696624756</v>
       </c>
       <c r="G115" t="n">
-        <v>8.50492477416992</v>
+        <v>8.50492382049561</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.2138500213623</v>
       </c>
       <c r="G116" t="n">
-        <v>8.66285991668701</v>
+        <v>8.66286087036133</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.51084423065186</v>
       </c>
       <c r="G117" t="n">
-        <v>8.00189590454102</v>
+        <v>8.0018949508667</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.49724960327148</v>
       </c>
       <c r="G118" t="n">
-        <v>7.98911476135254</v>
+        <v>7.98911428451538</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.65260982513428</v>
       </c>
       <c r="G120" t="n">
-        <v>8.13518524169922</v>
+        <v>8.13518333435059</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.03324413299561</v>
       </c>
       <c r="G121" t="n">
-        <v>8.49305534362793</v>
+        <v>8.49305438995361</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>8.80700016021729</v>
       </c>
       <c r="G122" t="n">
-        <v>8.28034114837646</v>
+        <v>8.28034210205078</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G123" t="n">
-        <v>8.39902210235596</v>
+        <v>8.39902305603027</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>8.99149036407471</v>
       </c>
       <c r="G124" t="n">
-        <v>8.45380020141602</v>
+        <v>8.4537992477417</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G125" t="n">
-        <v>8.39902210235596</v>
+        <v>8.39902305603027</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.55078792572021</v>
       </c>
       <c r="G127" t="n">
-        <v>8.97965049743652</v>
+        <v>8.97964954376221</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.52748394012451</v>
       </c>
       <c r="G129" t="n">
-        <v>8.95774078369141</v>
+        <v>8.95773983001709</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.35076236724854</v>
       </c>
       <c r="G131" t="n">
-        <v>8.79158687591553</v>
+        <v>8.79158592224121</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.5935115814209</v>
       </c>
       <c r="G134" t="n">
-        <v>9.01981830596924</v>
+        <v>9.01981925964355</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G136" t="n">
-        <v>8.30772972106934</v>
+        <v>8.3077278137207</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>8.70018863677979</v>
       </c>
       <c r="G138" t="n">
-        <v>8.17991638183594</v>
+        <v>8.17991828918457</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G139" t="n">
-        <v>8.2164363861084</v>
+        <v>8.21643733978271</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>8.80991268157959</v>
       </c>
       <c r="G140" t="n">
-        <v>8.28307914733887</v>
+        <v>8.28307819366455</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>8.76815986633301</v>
       </c>
       <c r="G145" t="n">
-        <v>8.24382495880127</v>
+        <v>8.24382209777832</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G146" t="n">
-        <v>8.30772972106934</v>
+        <v>8.3077278137207</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>8.98178005218506</v>
       </c>
       <c r="G148" t="n">
-        <v>8.44466876983643</v>
+        <v>8.44466972351074</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>8.94293975830078</v>
       </c>
       <c r="G149" t="n">
-        <v>8.40815258026123</v>
+        <v>8.40815162658691</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>8.91380977630615</v>
       </c>
       <c r="G150" t="n">
-        <v>8.38076305389404</v>
+        <v>8.38076210021973</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G152" t="n">
-        <v>8.2164363861084</v>
+        <v>8.21643733978271</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>8.82739067077637</v>
       </c>
       <c r="G153" t="n">
-        <v>8.2995138168335</v>
+        <v>8.29951286315918</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>8.65260982513428</v>
       </c>
       <c r="G154" t="n">
-        <v>8.13518524169922</v>
+        <v>8.13518333435059</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G157" t="n">
-        <v>8.2164363861084</v>
+        <v>8.21643733978271</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>8.87497043609619</v>
       </c>
       <c r="G158" t="n">
-        <v>8.34424686431885</v>
+        <v>8.34424781799316</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>8.96430206298828</v>
       </c>
       <c r="G160" t="n">
-        <v>8.42823600769043</v>
+        <v>8.42823696136475</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.20316886901855</v>
       </c>
       <c r="G161" t="n">
-        <v>8.65281867980957</v>
+        <v>8.65281677246094</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>9.20316886901855</v>
       </c>
       <c r="G162" t="n">
-        <v>8.65281867980957</v>
+        <v>8.65281677246094</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.57894706726074</v>
       </c>
       <c r="G166" t="n">
-        <v>9.00612545013428</v>
+        <v>9.00612640380859</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.40222454071045</v>
       </c>
       <c r="G167" t="n">
-        <v>8.8399715423584</v>
+        <v>8.83997058868408</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.51583194732666</v>
       </c>
       <c r="G168" t="n">
-        <v>8.94678592681885</v>
+        <v>8.94678401947021</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.33522605895996</v>
       </c>
       <c r="G169" t="n">
-        <v>8.77697849273682</v>
+        <v>8.77697944641113</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.48573112487793</v>
       </c>
       <c r="G170" t="n">
-        <v>8.91848278045654</v>
+        <v>8.91848468780518</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G171" t="n">
-        <v>8.992431640625</v>
+        <v>8.99243259429932</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.75858306884766</v>
       </c>
       <c r="G172" t="n">
-        <v>9.17501926422119</v>
+        <v>9.17501831054688</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.72751140594482</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14580631256104</v>
+        <v>9.14580535888672</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.89258098602295</v>
       </c>
       <c r="G174" t="n">
-        <v>9.30100250244141</v>
+        <v>9.30100345611572</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.92753791809082</v>
       </c>
       <c r="G175" t="n">
-        <v>9.33386993408203</v>
+        <v>9.33387088775635</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G177" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G178" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G179" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G181" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.1897087097168</v>
       </c>
       <c r="G183" t="n">
-        <v>9.58036518096924</v>
+        <v>9.58036422729492</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.84791469573975</v>
       </c>
       <c r="G184" t="n">
-        <v>9.25901031494141</v>
+        <v>9.25900936126709</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G185" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G188" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>10.0498838424683</v>
       </c>
       <c r="G189" t="n">
-        <v>9.44890022277832</v>
+        <v>9.448899269104</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>9.99939155578613</v>
       </c>
       <c r="G191" t="n">
-        <v>9.40142822265625</v>
+        <v>9.40142726898193</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.8595666885376</v>
       </c>
       <c r="G192" t="n">
-        <v>9.26996326446533</v>
+        <v>9.26996421813965</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.64594745635986</v>
       </c>
       <c r="G193" t="n">
-        <v>9.06911945343018</v>
+        <v>9.06911849975586</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G194" t="n">
-        <v>8.992431640625</v>
+        <v>8.99243259429932</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.57409191131592</v>
       </c>
       <c r="G198" t="n">
-        <v>9.00156021118164</v>
+        <v>9.00156116485596</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.44786167144775</v>
       </c>
       <c r="G199" t="n">
-        <v>8.88287830352783</v>
+        <v>8.88287925720215</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>8.87497043609619</v>
       </c>
       <c r="G201" t="n">
-        <v>8.34424686431885</v>
+        <v>8.34424781799316</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>8.85263729095459</v>
       </c>
       <c r="G202" t="n">
-        <v>8.3232479095459</v>
+        <v>8.32324886322021</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.25657367706299</v>
       </c>
       <c r="G203" t="n">
-        <v>8.70302963256836</v>
+        <v>8.70303058624268</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.5935115814209</v>
       </c>
       <c r="G204" t="n">
-        <v>9.01981830596924</v>
+        <v>9.01981925964355</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>9.61293315887451</v>
       </c>
       <c r="G206" t="n">
-        <v>9.03807926177979</v>
+        <v>9.03807830810547</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>9.47699165344238</v>
       </c>
       <c r="G209" t="n">
-        <v>8.9102668762207</v>
+        <v>8.91026782989502</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>9.47699165344238</v>
       </c>
       <c r="G210" t="n">
-        <v>8.9102668762207</v>
+        <v>8.91026782989502</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.62264347076416</v>
       </c>
       <c r="G211" t="n">
-        <v>9.04720973968506</v>
+        <v>9.04720878601074</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.98191356658936</v>
       </c>
       <c r="G214" t="n">
-        <v>9.38499546051025</v>
+        <v>9.38499450683594</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>10.0013341903687</v>
       </c>
       <c r="G217" t="n">
-        <v>9.40325260162354</v>
+        <v>9.40325355529785</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.0790138244629</v>
       </c>
       <c r="G218" t="n">
-        <v>9.47628784179688</v>
+        <v>9.47628879547119</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G221" t="n">
-        <v>9.84146308898926</v>
+        <v>9.84146213531494</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G223" t="n">
-        <v>9.9327564239502</v>
+        <v>9.93275737762451</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G224" t="n">
-        <v>9.98753356933594</v>
+        <v>9.98753261566162</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G226" t="n">
-        <v>9.98753356933594</v>
+        <v>9.98753261566162</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G227" t="n">
-        <v>9.85972213745117</v>
+        <v>9.8597240447998</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G229" t="n">
-        <v>9.75016975402832</v>
+        <v>9.75016784667969</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>10.6421957015991</v>
       </c>
       <c r="G233" t="n">
-        <v>10.0057907104492</v>
+        <v>10.0057916641235</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G234" t="n">
-        <v>10.042308807373</v>
+        <v>10.0423107147217</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G236" t="n">
-        <v>9.71365356445312</v>
+        <v>9.71365451812744</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G237" t="n">
-        <v>9.76842880249023</v>
+        <v>9.76842784881592</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.4285745620728</v>
       </c>
       <c r="G238" t="n">
-        <v>9.80494403839111</v>
+        <v>9.80494689941406</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G239" t="n">
-        <v>10.0788278579712</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G240" t="n">
-        <v>10.042308807373</v>
+        <v>10.0423107147217</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G241" t="n">
-        <v>10.042308807373</v>
+        <v>10.0423107147217</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G244" t="n">
-        <v>10.2431564331055</v>
+        <v>10.2431554794312</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G246" t="n">
-        <v>9.85972213745117</v>
+        <v>9.8597240447998</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>10.4285745620728</v>
       </c>
       <c r="G247" t="n">
-        <v>9.80494403839111</v>
+        <v>9.80494689941406</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G248" t="n">
-        <v>9.9327564239502</v>
+        <v>9.93275737762451</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G249" t="n">
-        <v>9.95101547241211</v>
+        <v>9.95101737976074</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>11.2053775787354</v>
       </c>
       <c r="G252" t="n">
-        <v>10.5352964401245</v>
+        <v>10.5352954864502</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>11.2636375427246</v>
       </c>
       <c r="G253" t="n">
-        <v>10.5900716781616</v>
+        <v>10.5900707244873</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>11.3413181304932</v>
       </c>
       <c r="G254" t="n">
-        <v>10.6631059646606</v>
+        <v>10.6631078720093</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>11.0305967330933</v>
       </c>
       <c r="G257" t="n">
-        <v>10.3709669113159</v>
+        <v>10.3709659576416</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G258" t="n">
-        <v>10.2614135742188</v>
+        <v>10.2614145278931</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G259" t="n">
-        <v>9.95101547241211</v>
+        <v>9.95101737976074</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G260" t="n">
-        <v>9.91449928283691</v>
+        <v>9.9144983291626</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G261" t="n">
-        <v>9.78668689727783</v>
+        <v>9.78668785095215</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G262" t="n">
-        <v>10.0788278579712</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>10.6616163253784</v>
       </c>
       <c r="G263" t="n">
-        <v>10.1156778335571</v>
+        <v>10.1156787872314</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G264" t="n">
-        <v>9.87614440917969</v>
+        <v>9.876145362854</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G266" t="n">
-        <v>9.8577184677124</v>
+        <v>9.85771751403809</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G267" t="n">
-        <v>9.8577184677124</v>
+        <v>9.85771751403809</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>10.6616163253784</v>
       </c>
       <c r="G268" t="n">
-        <v>10.1156778335571</v>
+        <v>10.1156787872314</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G269" t="n">
-        <v>10.0788269042969</v>
+        <v>10.0788259506226</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G270" t="n">
-        <v>9.93142032623291</v>
+        <v>9.93142127990723</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G272" t="n">
-        <v>10.1525287628174</v>
+        <v>10.1525297164917</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G276" t="n">
-        <v>9.83929347991943</v>
+        <v>9.83929252624512</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G277" t="n">
-        <v>9.98669815063477</v>
+        <v>9.98669910430908</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G278" t="n">
-        <v>9.93142032623291</v>
+        <v>9.93142127990723</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G280" t="n">
-        <v>10.1525287628174</v>
+        <v>10.1525297164917</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G283" t="n">
-        <v>9.87614440917969</v>
+        <v>9.876145362854</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G285" t="n">
-        <v>9.8024435043335</v>
+        <v>9.80244445800781</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>10.6421957015991</v>
       </c>
       <c r="G286" t="n">
-        <v>10.0972518920898</v>
+        <v>10.0972528457642</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>10.8558168411255</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2999334335327</v>
+        <v>10.2999353408813</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G293" t="n">
-        <v>9.93142032623291</v>
+        <v>9.93142127990723</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G295" t="n">
-        <v>10.2446584701538</v>
+        <v>10.2446575164795</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G297" t="n">
-        <v>9.96827411651611</v>
+        <v>9.9682731628418</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G298" t="n">
-        <v>9.93142032623291</v>
+        <v>9.93142127990723</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G299" t="n">
-        <v>9.8024435043335</v>
+        <v>9.80244445800781</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G302" t="n">
-        <v>9.83929347991943</v>
+        <v>9.83929252624512</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G303" t="n">
-        <v>10.0051259994507</v>
+        <v>10.0051250457764</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G304" t="n">
-        <v>10.0419759750366</v>
+        <v>10.0419769287109</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G307" t="n">
-        <v>9.93142032623291</v>
+        <v>9.93142127990723</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G308" t="n">
-        <v>9.98669815063477</v>
+        <v>9.98669910430908</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G309" t="n">
-        <v>9.93142032623291</v>
+        <v>9.93142127990723</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G310" t="n">
-        <v>10.189380645752</v>
+        <v>10.1893796920776</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G311" t="n">
-        <v>10.189380645752</v>
+        <v>10.1893796920776</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G315" t="n">
-        <v>10.4104881286621</v>
+        <v>10.4104890823364</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G316" t="n">
-        <v>10.1525287628174</v>
+        <v>10.1525297164917</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>12.15696144104</v>
       </c>
       <c r="G319" t="n">
-        <v>11.5344524383545</v>
+        <v>11.5344533920288</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G322" t="n">
-        <v>11.460750579834</v>
+        <v>11.4607496261597</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>12.176381111145</v>
       </c>
       <c r="G323" t="n">
-        <v>11.5528793334961</v>
+        <v>11.5528783798218</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>12.15696144104</v>
       </c>
       <c r="G325" t="n">
-        <v>11.5344524383545</v>
+        <v>11.5344533920288</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>12.176381111145</v>
       </c>
       <c r="G326" t="n">
-        <v>11.5528793334961</v>
+        <v>11.5528783798218</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>13.0308637619019</v>
       </c>
       <c r="G331" t="n">
-        <v>12.3636054992676</v>
+        <v>12.3636064529419</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>13.186224937439</v>
       </c>
       <c r="G332" t="n">
-        <v>12.5110120773315</v>
+        <v>12.5110130310059</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G333" t="n">
-        <v>12.1056470870972</v>
+        <v>12.1056480407715</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G334" t="n">
-        <v>11.4976015090942</v>
+        <v>11.4976005554199</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G335" t="n">
-        <v>11.5160264968872</v>
+        <v>11.5160274505615</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G337" t="n">
-        <v>11.5160264968872</v>
+        <v>11.5160274505615</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G338" t="n">
-        <v>11.4976015090942</v>
+        <v>11.4976005554199</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G340" t="n">
-        <v>11.5160264968872</v>
+        <v>11.5160274505615</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G341" t="n">
-        <v>11.460750579834</v>
+        <v>11.4607496261597</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G342" t="n">
-        <v>11.5160264968872</v>
+        <v>11.5160274505615</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G343" t="n">
-        <v>11.4976015090942</v>
+        <v>11.4976005554199</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>12.4871015548706</v>
       </c>
       <c r="G344" t="n">
-        <v>11.8476896286011</v>
+        <v>11.8476867675781</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G351" t="n">
-        <v>12.4373111724854</v>
+        <v>12.4373092651367</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>13.5940456390381</v>
       </c>
       <c r="G353" t="n">
-        <v>12.8979511260986</v>
+        <v>12.8979501724243</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G354" t="n">
-        <v>13.174334526062</v>
+        <v>13.1743364334106</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>13.9824476242065</v>
       </c>
       <c r="G355" t="n">
-        <v>13.2664632797241</v>
+        <v>13.2664642333984</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>14.0989675521851</v>
       </c>
       <c r="G359" t="n">
-        <v>13.3770160675049</v>
+        <v>13.3770170211792</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.8270874023438</v>
       </c>
       <c r="G360" t="n">
-        <v>13.1190595626831</v>
+        <v>13.1190576553345</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>12.9726037979126</v>
       </c>
       <c r="G363" t="n">
-        <v>12.30832862854</v>
+        <v>12.3083295822144</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G364" t="n">
-        <v>12.2714786529541</v>
+        <v>12.2714805603027</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G365" t="n">
-        <v>12.2162008285522</v>
+        <v>12.2162017822266</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G369" t="n">
-        <v>12.1056470870972</v>
+        <v>12.1056480407715</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.8560838699341</v>
       </c>
       <c r="G371" t="n">
-        <v>12.1977758407593</v>
+        <v>12.197774887085</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G372" t="n">
-        <v>12.4373111724854</v>
+        <v>12.4373092651367</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>14.5650501251221</v>
       </c>
       <c r="G374" t="n">
-        <v>13.8192329406738</v>
+        <v>13.8192338943481</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>14.0407075881958</v>
       </c>
       <c r="G375" t="n">
-        <v>13.321741104126</v>
+        <v>13.3217401504517</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G376" t="n">
-        <v>13.0822076797485</v>
+        <v>13.0822086334229</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>13.3027448654175</v>
       </c>
       <c r="G378" t="n">
-        <v>12.6215658187866</v>
+        <v>12.6215667724609</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G379" t="n">
-        <v>12.4373111724854</v>
+        <v>12.4373092651367</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G380" t="n">
-        <v>12.474160194397</v>
+        <v>12.4741611480713</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G381" t="n">
-        <v>12.2899045944214</v>
+        <v>12.2899036407471</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G382" t="n">
-        <v>12.2899045944214</v>
+        <v>12.2899036407471</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G383" t="n">
-        <v>12.4373111724854</v>
+        <v>12.4373092651367</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G384" t="n">
-        <v>12.2162008285522</v>
+        <v>12.2162017822266</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>13.4192657470703</v>
       </c>
       <c r="G386" t="n">
-        <v>12.7321195602417</v>
+        <v>12.732120513916</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>13.4969463348389</v>
       </c>
       <c r="G387" t="n">
-        <v>12.8058233261108</v>
+        <v>12.8058223724365</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>13.7105674743652</v>
       </c>
       <c r="G388" t="n">
-        <v>13.0085039138794</v>
+        <v>13.008505821228</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G389" t="n">
-        <v>13.174334526062</v>
+        <v>13.1743364334106</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G393" t="n">
-        <v>13.0822076797485</v>
+        <v>13.0822086334229</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G395" t="n">
-        <v>13.174334526062</v>
+        <v>13.1743364334106</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>13.2444849014282</v>
       </c>
       <c r="G397" t="n">
-        <v>12.5662879943848</v>
+        <v>12.5662889480591</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>12.8949241638184</v>
       </c>
       <c r="G398" t="n">
-        <v>12.2346286773682</v>
+        <v>12.2346267700195</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G399" t="n">
-        <v>12.1056470870972</v>
+        <v>12.1056480407715</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G403" t="n">
-        <v>12.4373111724854</v>
+        <v>12.4373092651367</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>12.4871015548706</v>
       </c>
       <c r="G409" t="n">
-        <v>11.8476896286011</v>
+        <v>11.8476867675781</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>12.4094219207764</v>
       </c>
       <c r="G410" t="n">
-        <v>11.7739849090576</v>
+        <v>11.7739858627319</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G411" t="n">
-        <v>11.7002830505371</v>
+        <v>11.7002840042114</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G413" t="n">
-        <v>10.9448318481445</v>
+        <v>10.9448308944702</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>11.6131992340088</v>
       </c>
       <c r="G414" t="n">
-        <v>11.0185356140137</v>
+        <v>11.0185346603394</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G419" t="n">
-        <v>10.9448318481445</v>
+        <v>10.9448308944702</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G422" t="n">
-        <v>11.0553865432739</v>
+        <v>11.0553855895996</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>11.8073997497559</v>
       </c>
       <c r="G423" t="n">
-        <v>11.2027912139893</v>
+        <v>11.2027902603149</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>11.8073997497559</v>
       </c>
       <c r="G429" t="n">
-        <v>11.2027912139893</v>
+        <v>11.2027902603149</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G432" t="n">
-        <v>10.0788269042969</v>
+        <v>10.0788259506226</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G433" t="n">
-        <v>10.4104881286621</v>
+        <v>10.4104890823364</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G435" t="n">
-        <v>10.2446584701538</v>
+        <v>10.2446575164795</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G436" t="n">
-        <v>10.2446584701538</v>
+        <v>10.2446575164795</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G437" t="n">
-        <v>9.98669815063477</v>
+        <v>9.98669910430908</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G441" t="n">
-        <v>10.0788269042969</v>
+        <v>10.0788259506226</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G443" t="n">
-        <v>9.36022663116455</v>
+        <v>9.36022758483887</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.84597301483154</v>
       </c>
       <c r="G444" t="n">
-        <v>9.34180164337158</v>
+        <v>9.34180068969727</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.12743091583252</v>
       </c>
       <c r="G447" t="n">
-        <v>8.66005325317383</v>
+        <v>8.66005229949951</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G448" t="n">
-        <v>9.8577184677124</v>
+        <v>9.85771751403809</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.22453117370605</v>
       </c>
       <c r="G449" t="n">
-        <v>8.75218105316162</v>
+        <v>8.7521800994873</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.6322193145752</v>
       </c>
       <c r="G451" t="n">
-        <v>8.1901969909668</v>
+        <v>8.19019889831543</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>8.58366870880127</v>
       </c>
       <c r="G452" t="n">
-        <v>8.14413452148438</v>
+        <v>8.14413356781006</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G453" t="n">
-        <v>8.47579574584961</v>
+        <v>8.47579669952393</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G454" t="n">
-        <v>8.38366794586182</v>
+        <v>8.3836669921875</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G456" t="n">
-        <v>11.7002830505371</v>
+        <v>11.7002840042114</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G459" t="n">
-        <v>10.0788269042969</v>
+        <v>10.0788259506226</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G464" t="n">
-        <v>10.170955657959</v>
+        <v>10.1709547042847</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G468" t="n">
-        <v>9.94984722137451</v>
+        <v>9.94984912872314</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>11.2053775787354</v>
       </c>
       <c r="G469" t="n">
-        <v>10.6315956115723</v>
+        <v>10.6315965652466</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G470" t="n">
-        <v>11.0553865432739</v>
+        <v>11.0553855895996</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G472" t="n">
-        <v>11.0553865432739</v>
+        <v>11.0553855895996</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G473" t="n">
-        <v>11.7002830505371</v>
+        <v>11.7002840042114</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G475" t="n">
-        <v>11.7924108505249</v>
+        <v>11.7924118041992</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>13.0697040557861</v>
       </c>
       <c r="G476" t="n">
-        <v>12.4004564285278</v>
+        <v>12.4004573822021</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G477" t="n">
-        <v>12.474160194397</v>
+        <v>12.4741611480713</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>13.2056446075439</v>
       </c>
       <c r="G478" t="n">
-        <v>12.5294380187988</v>
+        <v>12.5294370651245</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G480" t="n">
-        <v>12.2714786529541</v>
+        <v>12.2714805603027</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>12.3123216629028</v>
       </c>
       <c r="G482" t="n">
-        <v>11.6818580627441</v>
+        <v>11.6818571090698</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G483" t="n">
-        <v>11.7924108505249</v>
+        <v>11.7924118041992</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G485" t="n">
-        <v>11.7002830505371</v>
+        <v>11.7002840042114</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G486" t="n">
-        <v>12.4373111724854</v>
+        <v>12.4373092651367</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G487" t="n">
-        <v>12.4373111724854</v>
+        <v>12.4373092651367</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G488" t="n">
-        <v>13.0822076797485</v>
+        <v>13.0822086334229</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>14.3708486557007</v>
       </c>
       <c r="G489" t="n">
-        <v>13.6349754333496</v>
+        <v>13.6349763870239</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>14.1183881759644</v>
       </c>
       <c r="G490" t="n">
-        <v>13.3954429626465</v>
+        <v>13.3954420089722</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>14.2931690216064</v>
       </c>
       <c r="G492" t="n">
-        <v>13.5612745285034</v>
+        <v>13.5612726211548</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>15.7496738433838</v>
       </c>
       <c r="G494" t="n">
-        <v>14.9431982040405</v>
+        <v>14.9431972503662</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>15.633152961731</v>
       </c>
       <c r="G495" t="n">
-        <v>14.8326425552368</v>
+        <v>14.8326435089111</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>14.9146108627319</v>
       </c>
       <c r="G496" t="n">
-        <v>14.1508941650391</v>
+        <v>14.1508932113647</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G497" t="n">
-        <v>15.1827306747437</v>
+        <v>15.1827297210693</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G498" t="n">
-        <v>15.6433725357056</v>
+        <v>15.6433734893799</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G500" t="n">
-        <v>15.2932834625244</v>
+        <v>15.293285369873</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>15.1476516723633</v>
       </c>
       <c r="G503" t="n">
-        <v>14.3720026016235</v>
+        <v>14.3720035552979</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G504" t="n">
-        <v>13.9482107162476</v>
+        <v>13.9482116699219</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G505" t="n">
-        <v>13.9482107162476</v>
+        <v>13.9482116699219</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>14.7980899810791</v>
       </c>
       <c r="G506" t="n">
-        <v>14.0403385162354</v>
+        <v>14.040340423584</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>14.4485292434692</v>
       </c>
       <c r="G507" t="n">
-        <v>13.7086791992188</v>
+        <v>13.7086772918701</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>14.3125886917114</v>
       </c>
       <c r="G509" t="n">
-        <v>13.5796985626221</v>
+        <v>13.5797004699707</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>14.7398300170898</v>
       </c>
       <c r="G510" t="n">
-        <v>13.9850635528564</v>
+        <v>13.9850645065308</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>15.4001121520996</v>
       </c>
       <c r="G512" t="n">
-        <v>14.6115341186523</v>
+        <v>14.6115350723267</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>15.6914129257202</v>
       </c>
       <c r="G513" t="n">
-        <v>14.88791847229</v>
+        <v>14.8879203796387</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>15.128231048584</v>
       </c>
       <c r="G514" t="n">
-        <v>14.4609594345093</v>
+        <v>14.4609603881836</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G515" t="n">
-        <v>14.7022838592529</v>
+        <v>14.7022848129272</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>15.4777927398682</v>
       </c>
       <c r="G516" t="n">
-        <v>14.7951021194458</v>
+        <v>14.7951011657715</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>15.3612718582153</v>
       </c>
       <c r="G517" t="n">
-        <v>14.6837215423584</v>
+        <v>14.6837205886841</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>15.3418521881104</v>
       </c>
       <c r="G518" t="n">
-        <v>14.6651582717896</v>
+        <v>14.6651573181152</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>15.5748929977417</v>
       </c>
       <c r="G519" t="n">
-        <v>14.8879194259644</v>
+        <v>14.8879203796387</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>15.8661937713623</v>
       </c>
       <c r="G520" t="n">
-        <v>15.16637134552</v>
+        <v>15.1663732528687</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G521" t="n">
-        <v>14.7022838592529</v>
+        <v>14.7022848129272</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G522" t="n">
-        <v>15.1292457580566</v>
+        <v>15.129246711731</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>16.0215549468994</v>
       </c>
       <c r="G523" t="n">
-        <v>15.3148803710938</v>
+        <v>15.3148813247681</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>15.9244537353516</v>
       </c>
       <c r="G524" t="n">
-        <v>15.2220621109009</v>
+        <v>15.2220611572266</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G525" t="n">
-        <v>14.9064836502075</v>
+        <v>14.9064826965332</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G527" t="n">
-        <v>14.9064836502075</v>
+        <v>14.9064826965332</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G528" t="n">
-        <v>14.9807367324829</v>
+        <v>14.9807357788086</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>15.2253322601318</v>
       </c>
       <c r="G530" t="n">
-        <v>14.5537767410278</v>
+        <v>14.5537757873535</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G531" t="n">
-        <v>15.0364294052124</v>
+        <v>15.0364284515381</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G532" t="n">
-        <v>14.8322286605835</v>
+        <v>14.8322296142578</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>15.613733291626</v>
       </c>
       <c r="G533" t="n">
-        <v>14.9250459671021</v>
+        <v>14.9250478744507</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G534" t="n">
-        <v>15.1292457580566</v>
+        <v>15.129246711731</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G535" t="n">
-        <v>15.1292457580566</v>
+        <v>15.129246711731</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G536" t="n">
-        <v>14.9064836502075</v>
+        <v>14.9064826965332</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G539" t="n">
-        <v>14.8507928848267</v>
+        <v>14.8507919311523</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>15.3612718582153</v>
       </c>
       <c r="G542" t="n">
-        <v>14.6837215423584</v>
+        <v>14.6837205886841</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G543" t="n">
-        <v>14.8507928848267</v>
+        <v>14.8507919311523</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G544" t="n">
-        <v>14.8322286605835</v>
+        <v>14.8322296142578</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>16.1769142150879</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4633874893188</v>
+        <v>15.4633865356445</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G548" t="n">
-        <v>17.5610618591309</v>
+        <v>17.5610656738281</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G549" t="n">
-        <v>17.5610618591309</v>
+        <v>17.5610656738281</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G550" t="n">
-        <v>16.6143245697021</v>
+        <v>16.6143226623535</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G554" t="n">
-        <v>17.2826080322266</v>
+        <v>17.2826118469238</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G555" t="n">
-        <v>17.6724452972412</v>
+        <v>17.6724472045898</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G556" t="n">
-        <v>17.895206451416</v>
+        <v>17.8952045440674</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G557" t="n">
-        <v>17.7652606964111</v>
+        <v>17.7652626037598</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G559" t="n">
-        <v>18.1922225952148</v>
+        <v>18.1922206878662</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G560" t="n">
-        <v>17.5424995422363</v>
+        <v>17.5425033569336</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G561" t="n">
-        <v>17.4125537872314</v>
+        <v>17.4125556945801</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G563" t="n">
-        <v>18.5634899139404</v>
+        <v>18.5634918212891</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G564" t="n">
-        <v>19.0275764465332</v>
+        <v>19.0275783538818</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G565" t="n">
-        <v>18.210786819458</v>
+        <v>18.2107849121094</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G566" t="n">
-        <v>18.5634899139404</v>
+        <v>18.5634918212891</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G567" t="n">
-        <v>17.6724452972412</v>
+        <v>17.6724472045898</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G572" t="n">
-        <v>17.3568630218506</v>
+        <v>17.3568649291992</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G573" t="n">
-        <v>17.6910076141357</v>
+        <v>17.6910057067871</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>17.5945796966553</v>
       </c>
       <c r="G574" t="n">
-        <v>16.8185234069824</v>
+        <v>16.8185253143311</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G575" t="n">
-        <v>16.5586318969727</v>
+        <v>16.5586338043213</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>16.4487953186035</v>
       </c>
       <c r="G576" t="n">
-        <v>15.7232751846313</v>
+        <v>15.72327709198</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>15.9827136993408</v>
       </c>
       <c r="G579" t="n">
-        <v>15.2777528762817</v>
+        <v>15.2777519226074</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G580" t="n">
-        <v>15.6675863265991</v>
+        <v>15.6675853729248</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G582" t="n">
-        <v>16.4843807220459</v>
+        <v>16.4843788146973</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>17.5168991088867</v>
       </c>
       <c r="G586" t="n">
-        <v>16.7442684173584</v>
+        <v>16.7442665100098</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>17.1479187011719</v>
       </c>
       <c r="G589" t="n">
-        <v>16.391565322876</v>
+        <v>16.3915634155273</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G590" t="n">
-        <v>16.2616195678711</v>
+        <v>16.2616176605225</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G591" t="n">
-        <v>16.2616195678711</v>
+        <v>16.2616176605225</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G592" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430515289307</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G594" t="n">
-        <v>16.5586318969727</v>
+        <v>16.5586338043213</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G595" t="n">
-        <v>16.5771999359131</v>
+        <v>16.5771980285645</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G596" t="n">
-        <v>16.5215091705322</v>
+        <v>16.5215072631836</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G597" t="n">
-        <v>16.5029392242432</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G600" t="n">
-        <v>16.4843807220459</v>
+        <v>16.4843788146973</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>17.4586391448975</v>
       </c>
       <c r="G601" t="n">
-        <v>16.6885757446289</v>
+        <v>16.6885795593262</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G602" t="n">
-        <v>16.6143245697021</v>
+        <v>16.6143226623535</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G603" t="n">
-        <v>15.6861486434937</v>
+        <v>15.6861505508423</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>16.0409755706787</v>
       </c>
       <c r="G604" t="n">
-        <v>15.3334436416626</v>
+        <v>15.3334445953369</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>15.5554733276367</v>
       </c>
       <c r="G605" t="n">
-        <v>14.8693580627441</v>
+        <v>14.8693571090698</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>15.2641716003418</v>
       </c>
       <c r="G606" t="n">
-        <v>14.5909042358398</v>
+        <v>14.5909032821655</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G607" t="n">
-        <v>14.8507928848267</v>
+        <v>14.8507919311523</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G608" t="n">
-        <v>14.8507928848267</v>
+        <v>14.8507919311523</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G609" t="n">
-        <v>15.6861486434937</v>
+        <v>15.6861505508423</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G610" t="n">
-        <v>14.9807367324829</v>
+        <v>14.9807357788086</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>15.108811378479</v>
       </c>
       <c r="G611" t="n">
-        <v>14.4423961639404</v>
+        <v>14.4423971176147</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>18.0024013519287</v>
       </c>
       <c r="G612" t="n">
-        <v>17.2083568572998</v>
+        <v>17.2083549499512</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G618" t="n">
-        <v>15.7789659500122</v>
+        <v>15.7789669036865</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G619" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430515289307</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G621" t="n">
-        <v>16.5215091705322</v>
+        <v>16.5215072631836</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G622" t="n">
-        <v>16.4843807220459</v>
+        <v>16.4843788146973</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G627" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430515289307</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G628" t="n">
-        <v>16.5029392242432</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G629" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430515289307</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G630" t="n">
-        <v>16.5029392242432</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G637" t="n">
-        <v>16.5400695800781</v>
+        <v>16.5400714874268</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>17.5557403564453</v>
       </c>
       <c r="G641" t="n">
-        <v>16.7813987731934</v>
+        <v>16.7813949584961</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G644" t="n">
-        <v>17.2826080322266</v>
+        <v>17.2826118469238</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G645" t="n">
-        <v>17.4125537872314</v>
+        <v>17.4125556945801</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G646" t="n">
-        <v>17.7838230133057</v>
+        <v>17.7838249206543</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>18.7986240386963</v>
       </c>
       <c r="G647" t="n">
-        <v>17.9694576263428</v>
+        <v>17.9694595336914</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>18.7597846984863</v>
       </c>
       <c r="G650" t="n">
-        <v>17.9323329925537</v>
+        <v>17.9323310852051</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G652" t="n">
-        <v>16.5771999359131</v>
+        <v>16.5771980285645</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G653" t="n">
-        <v>16.5400695800781</v>
+        <v>16.5400714874268</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>17.4003791809082</v>
       </c>
       <c r="G656" t="n">
-        <v>16.6328868865967</v>
+        <v>16.6328887939453</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G660" t="n">
-        <v>16.5029392242432</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G661" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430515289307</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>17.2061786651611</v>
       </c>
       <c r="G662" t="n">
-        <v>16.4472541809082</v>
+        <v>16.4472522735596</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G666" t="n">
-        <v>16.5215091705322</v>
+        <v>16.5215072631836</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G669" t="n">
-        <v>15.7789659500122</v>
+        <v>15.7789669036865</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>16.9537181854248</v>
       </c>
       <c r="G670" t="n">
-        <v>16.2059307098389</v>
+        <v>16.2059268951416</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G671" t="n">
-        <v>16.2616195678711</v>
+        <v>16.2616176605225</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G676" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430515289307</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G677" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430515289307</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>16.9537181854248</v>
       </c>
       <c r="G678" t="n">
-        <v>16.2059307098389</v>
+        <v>16.2059268951416</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>17.2061786651611</v>
       </c>
       <c r="G679" t="n">
-        <v>16.4472541809082</v>
+        <v>16.4472522735596</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G680" t="n">
-        <v>16.5586318969727</v>
+        <v>16.5586338043213</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G681" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430515289307</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>16.7012577056885</v>
       </c>
       <c r="G682" t="n">
-        <v>15.9646034240723</v>
+        <v>15.9646043777466</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>16.4682159423828</v>
       </c>
       <c r="G683" t="n">
-        <v>15.7418384552002</v>
+        <v>15.7418422698975</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G684" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430515289307</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>16.3711166381836</v>
       </c>
       <c r="G686" t="n">
-        <v>15.6490230560303</v>
+        <v>15.6490240097046</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>16.2157554626465</v>
       </c>
       <c r="G687" t="n">
-        <v>15.5005168914795</v>
+        <v>15.5005149841309</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>16.5264759063721</v>
       </c>
       <c r="G690" t="n">
-        <v>15.797532081604</v>
+        <v>15.7975301742554</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>16.6041564941406</v>
       </c>
       <c r="G691" t="n">
-        <v>15.8717842102051</v>
+        <v>15.8717861175537</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G693" t="n">
-        <v>14.8322286605835</v>
+        <v>14.8322296142578</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G694" t="n">
-        <v>14.4238309860229</v>
+        <v>14.4238319396973</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>14.7204103469849</v>
       </c>
       <c r="G695" t="n">
-        <v>14.0711269378662</v>
+        <v>14.0711259841919</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>15.3418521881104</v>
       </c>
       <c r="G696" t="n">
-        <v>14.6651582717896</v>
+        <v>14.6651573181152</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G697" t="n">
-        <v>14.4238309860229</v>
+        <v>14.4238319396973</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G700" t="n">
-        <v>15.0364294052124</v>
+        <v>15.0364284515381</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>16.332275390625</v>
       </c>
       <c r="G705" t="n">
-        <v>15.6118936538696</v>
+        <v>15.6118974685669</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>16.0798149108887</v>
       </c>
       <c r="G707" t="n">
-        <v>15.3705701828003</v>
+        <v>15.3705720901489</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>16.0603942871094</v>
       </c>
       <c r="G708" t="n">
-        <v>15.3520059585571</v>
+        <v>15.3520078659058</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G709" t="n">
-        <v>15.6675863265991</v>
+        <v>15.6675853729248</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G711" t="n">
-        <v>15.760404586792</v>
+        <v>15.7604026794434</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>16.856616973877</v>
       </c>
       <c r="G712" t="n">
-        <v>16.113109588623</v>
+        <v>16.1131076812744</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G713" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430515289307</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G714" t="n">
-        <v>16.5771999359131</v>
+        <v>16.5771980285645</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G715" t="n">
-        <v>16.9855976104736</v>
+        <v>16.985595703125</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G717" t="n">
-        <v>17.8209533691406</v>
+        <v>17.8209495544434</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G718" t="n">
-        <v>17.5424995422363</v>
+        <v>17.5425033569336</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G719" t="n">
-        <v>17.5424995422363</v>
+        <v>17.5425033569336</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>18.4684829711914</v>
       </c>
       <c r="G721" t="n">
-        <v>17.6538791656494</v>
+        <v>17.653881072998</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G723" t="n">
-        <v>17.8209533691406</v>
+        <v>17.8209495544434</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G725" t="n">
-        <v>17.8209533691406</v>
+        <v>17.8209495544434</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>19.2064456939697</v>
       </c>
       <c r="G726" t="n">
-        <v>18.3592929840088</v>
+        <v>18.3592910766602</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>18.779203414917</v>
       </c>
       <c r="G727" t="n">
-        <v>17.9508972167969</v>
+        <v>17.9508934020996</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G728" t="n">
-        <v>17.7652606964111</v>
+        <v>17.7652626037598</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>17.8470401763916</v>
       </c>
       <c r="G730" t="n">
-        <v>17.0598468780518</v>
+        <v>17.0598487854004</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G731" t="n">
-        <v>16.9855976104736</v>
+        <v>16.985595703125</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G732" t="n">
-        <v>17.2826080322266</v>
+        <v>17.2826118469238</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>18.293701171875</v>
       </c>
       <c r="G734" t="n">
-        <v>17.4868068695068</v>
+        <v>17.4868087768555</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>18.4490623474121</v>
       </c>
       <c r="G735" t="n">
-        <v>17.6353168487549</v>
+        <v>17.6353149414062</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G736" t="n">
-        <v>18.1922225952148</v>
+        <v>18.1922206878662</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G737" t="n">
-        <v>19.5844860076904</v>
+        <v>19.5844841003418</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G738" t="n">
-        <v>19.6773014068604</v>
+        <v>19.6772994995117</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G743" t="n">
-        <v>20.3270244598389</v>
+        <v>20.3270225524902</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G745" t="n">
-        <v>20.0021629333496</v>
+        <v>20.002161026001</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G746" t="n">
-        <v>19.8165283203125</v>
+        <v>19.8165264129639</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G748" t="n">
-        <v>20.0949783325195</v>
+        <v>20.0949802398682</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G749" t="n">
-        <v>20.4662494659424</v>
+        <v>20.4662475585938</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G750" t="n">
-        <v>20.512659072876</v>
+        <v>20.5126552581787</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G751" t="n">
-        <v>21.0695610046387</v>
+        <v>21.0695629119873</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G754" t="n">
-        <v>21.1623802185059</v>
+        <v>21.1623821258545</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G756" t="n">
-        <v>20.4662494659424</v>
+        <v>20.4662475585938</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G758" t="n">
-        <v>20.3270244598389</v>
+        <v>20.3270225524902</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G759" t="n">
-        <v>20.6982955932617</v>
+        <v>20.6982936859131</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G760" t="n">
-        <v>20.0949783325195</v>
+        <v>20.0949802398682</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G761" t="n">
-        <v>19.9557552337646</v>
+        <v>19.955753326416</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G762" t="n">
-        <v>19.8165283203125</v>
+        <v>19.8165264129639</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G764" t="n">
-        <v>19.6308917999268</v>
+        <v>19.6308937072754</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G765" t="n">
-        <v>19.5844860076904</v>
+        <v>19.5844841003418</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>20.245418548584</v>
       </c>
       <c r="G766" t="n">
-        <v>19.3524398803711</v>
+        <v>19.3524379730225</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G770" t="n">
-        <v>19.6528358459473</v>
+        <v>19.6528339385986</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G772" t="n">
-        <v>19.4194297790527</v>
+        <v>19.4194278717041</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G774" t="n">
-        <v>19.5594730377197</v>
+        <v>19.5594711303711</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>19.6628170013428</v>
       </c>
       <c r="G775" t="n">
-        <v>18.905933380127</v>
+        <v>18.9059352874756</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G776" t="n">
-        <v>18.7192077636719</v>
+        <v>18.7192096710205</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G778" t="n">
-        <v>18.952615737915</v>
+        <v>18.9526176452637</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G779" t="n">
-        <v>18.8125743865967</v>
+        <v>18.812572479248</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G780" t="n">
-        <v>19.5127906799316</v>
+        <v>19.512788772583</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G782" t="n">
-        <v>19.6528358459473</v>
+        <v>19.6528339385986</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>20.8280200958252</v>
       </c>
       <c r="G783" t="n">
-        <v>20.0262851715088</v>
+        <v>20.0262832641602</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G784" t="n">
-        <v>19.6995182037354</v>
+        <v>19.6995162963867</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G787" t="n">
-        <v>18.952615737915</v>
+        <v>18.9526176452637</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G790" t="n">
-        <v>18.3550968170166</v>
+        <v>18.355094909668</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>19.4006462097168</v>
       </c>
       <c r="G791" t="n">
-        <v>18.6538581848145</v>
+        <v>18.6538543701172</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G795" t="n">
-        <v>18.5231456756592</v>
+        <v>18.5231475830078</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G797" t="n">
-        <v>18.7192077636719</v>
+        <v>18.7192096710205</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G800" t="n">
-        <v>19.9329223632812</v>
+        <v>19.9329242706299</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>20.8280200958252</v>
       </c>
       <c r="G802" t="n">
-        <v>20.0262851715088</v>
+        <v>20.0262832641602</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>21.5077228546143</v>
       </c>
       <c r="G803" t="n">
-        <v>20.6798229217529</v>
+        <v>20.6798248291016</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G804" t="n">
-        <v>21.1466369628906</v>
+        <v>21.1466388702393</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G805" t="n">
-        <v>21.9402198791504</v>
+        <v>21.940221786499</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G808" t="n">
-        <v>23.0605716705322</v>
+        <v>23.0605735778809</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G811" t="n">
-        <v>22.920524597168</v>
+        <v>22.9205284118652</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G812" t="n">
-        <v>23.4340229034424</v>
+        <v>23.4340209960938</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G813" t="n">
-        <v>24.0408782958984</v>
+        <v>24.0408802032471</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G819" t="n">
-        <v>22.7337989807129</v>
+        <v>22.7338008880615</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G828" t="n">
-        <v>23.0605716705322</v>
+        <v>23.0605735778809</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G832" t="n">
-        <v>23.2939796447754</v>
+        <v>23.293981552124</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G836" t="n">
-        <v>24.0408782958984</v>
+        <v>24.0408802032471</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G842" t="n">
-        <v>21.800178527832</v>
+        <v>21.8001766204834</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G843" t="n">
-        <v>21.4267272949219</v>
+        <v>21.4267253875732</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G844" t="n">
-        <v>21.0065956115723</v>
+        <v>21.0065937042236</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G846" t="n">
-        <v>20.8198661804199</v>
+        <v>20.8198680877686</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>21.9446754455566</v>
       </c>
       <c r="G849" t="n">
-        <v>21.0999565124512</v>
+        <v>21.0999546051025</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G850" t="n">
-        <v>21.7068119049072</v>
+        <v>21.7068157196045</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G852" t="n">
-        <v>24.6477355957031</v>
+        <v>24.6477375030518</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G853" t="n">
-        <v>24.5076923370361</v>
+        <v>24.5076942443848</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G854" t="n">
-        <v>24.8344593048096</v>
+        <v>24.8344612121582</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G856" t="n">
-        <v>24.5076923370361</v>
+        <v>24.5076942443848</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G859" t="n">
-        <v>23.4340229034424</v>
+        <v>23.4340209960938</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G865" t="n">
-        <v>23.6674289703369</v>
+        <v>23.6674270629883</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G866" t="n">
-        <v>24.1342430114746</v>
+        <v>24.134241104126</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G867" t="n">
-        <v>24.1342430114746</v>
+        <v>24.134241104126</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G868" t="n">
-        <v>23.8074722290039</v>
+        <v>23.8074741363525</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G869" t="n">
-        <v>23.8074722290039</v>
+        <v>23.8074741363525</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G872" t="n">
-        <v>24.5076923370361</v>
+        <v>24.5076942443848</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>26.4112892150879</v>
       </c>
       <c r="G873" t="n">
-        <v>25.3946380615234</v>
+        <v>25.3946361541748</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>26.5083904266357</v>
       </c>
       <c r="G875" t="n">
-        <v>25.4879989624023</v>
+        <v>25.488000869751</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G876" t="n">
-        <v>25.207914352417</v>
+        <v>25.2079105377197</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G877" t="n">
-        <v>25.1145515441895</v>
+        <v>25.1145496368408</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G878" t="n">
-        <v>25.1145515441895</v>
+        <v>25.1145496368408</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>23.3040790557861</v>
       </c>
       <c r="G883" t="n">
-        <v>22.4070339202881</v>
+        <v>22.4070320129395</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>25.0518856048584</v>
       </c>
       <c r="G889" t="n">
-        <v>24.0875606536865</v>
+        <v>24.0875625610352</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G890" t="n">
-        <v>23.6674289703369</v>
+        <v>23.6674270629883</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G891" t="n">
-        <v>24.5543746948242</v>
+        <v>24.5543766021729</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G892" t="n">
-        <v>24.5076923370361</v>
+        <v>24.5076942443848</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G893" t="n">
-        <v>24.3676528930664</v>
+        <v>24.3676490783691</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G895" t="n">
-        <v>24.6010570526123</v>
+        <v>24.6010551452637</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G896" t="n">
-        <v>24.3676528930664</v>
+        <v>24.3676490783691</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G899" t="n">
-        <v>23.0605716705322</v>
+        <v>23.0605735778809</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>24.7120342254639</v>
       </c>
       <c r="G900" t="n">
-        <v>23.7607917785645</v>
+        <v>23.7607898712158</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G903" t="n">
-        <v>23.8074722290039</v>
+        <v>23.8074741363525</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G905" t="n">
-        <v>24.8344593048096</v>
+        <v>24.8344612121582</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G906" t="n">
-        <v>24.461009979248</v>
+        <v>24.4610118865967</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G907" t="n">
-        <v>24.461009979248</v>
+        <v>24.4610118865967</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G909" t="n">
-        <v>23.8074722290039</v>
+        <v>23.8074741363525</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G914" t="n">
-        <v>24.9745044708252</v>
+        <v>24.9745063781738</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>25.0518856048584</v>
       </c>
       <c r="G915" t="n">
-        <v>24.0875606536865</v>
+        <v>24.0875625610352</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G917" t="n">
-        <v>22.7337989807129</v>
+        <v>22.7338008880615</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G919" t="n">
-        <v>23.4340229034424</v>
+        <v>23.4340209960938</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G922" t="n">
-        <v>21.0532779693604</v>
+        <v>21.0532741546631</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G927" t="n">
-        <v>21.1466369628906</v>
+        <v>21.1466388702393</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G928" t="n">
-        <v>21.6601314544678</v>
+        <v>21.6601333618164</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G929" t="n">
-        <v>21.1466369628906</v>
+        <v>21.1466388702393</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G930" t="n">
-        <v>21.0065956115723</v>
+        <v>21.0065937042236</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G931" t="n">
-        <v>20.7265071868896</v>
+        <v>20.726505279541</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G933" t="n">
-        <v>21.1933212280273</v>
+        <v>21.1933193206787</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G934" t="n">
-        <v>21.4734058380127</v>
+        <v>21.4734077453613</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G936" t="n">
-        <v>21.2399978637695</v>
+        <v>21.2399997711182</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G937" t="n">
-        <v>21.7068119049072</v>
+        <v>21.7068157196045</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G938" t="n">
-        <v>21.1466369628906</v>
+        <v>21.1466388702393</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G939" t="n">
-        <v>21.0532779693604</v>
+        <v>21.0532741546631</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G940" t="n">
-        <v>21.0065956115723</v>
+        <v>21.0065937042236</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G941" t="n">
-        <v>20.119649887085</v>
+        <v>20.1196479797363</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>19.8570175170898</v>
       </c>
       <c r="G943" t="n">
-        <v>19.0926609039307</v>
+        <v>19.092658996582</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G945" t="n">
-        <v>19.7461967468262</v>
+        <v>19.7461986541748</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G946" t="n">
-        <v>20.5397815704346</v>
+        <v>20.5397796630859</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>20.0026683807373</v>
       </c>
       <c r="G948" t="n">
-        <v>19.2327060699463</v>
+        <v>19.2327041625977</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G949" t="n">
-        <v>18.093677520752</v>
+        <v>18.0936813354492</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>17.9053001403809</v>
       </c>
       <c r="G950" t="n">
-        <v>17.2160682678223</v>
+        <v>17.2160701751709</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>18.7986240386963</v>
       </c>
       <c r="G954" t="n">
-        <v>18.0750045776367</v>
+        <v>18.0750064849854</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G955" t="n">
-        <v>18.541820526123</v>
+        <v>18.5418224334717</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G957" t="n">
-        <v>19.4194297790527</v>
+        <v>19.4194278717041</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G960" t="n">
-        <v>20.5397815704346</v>
+        <v>20.5397796630859</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G962" t="n">
-        <v>21.6601314544678</v>
+        <v>21.6601333618164</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G963" t="n">
-        <v>21.7068119049072</v>
+        <v>21.7068157196045</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>22.7214775085449</v>
       </c>
       <c r="G965" t="n">
-        <v>21.8468570709229</v>
+        <v>21.8468589782715</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G966" t="n">
-        <v>21.6601314544678</v>
+        <v>21.6601333618164</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G967" t="n">
-        <v>22.1736278533936</v>
+        <v>22.1736259460449</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G969" t="n">
-        <v>21.7068119049072</v>
+        <v>21.7068157196045</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G971" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530559539795</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G976" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530559539795</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G979" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530559539795</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G982" t="n">
-        <v>21.6601314544678</v>
+        <v>21.6601333618164</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G985" t="n">
-        <v>21.4734058380127</v>
+        <v>21.4734077453613</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G987" t="n">
-        <v>21.4267272949219</v>
+        <v>21.4267253875732</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G989" t="n">
-        <v>22.1736278533936</v>
+        <v>22.1736259460449</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G990" t="n">
-        <v>21.800178527832</v>
+        <v>21.8001766204834</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>19.3229656219482</v>
       </c>
       <c r="G995" t="n">
-        <v>18.5791625976562</v>
+        <v>18.5791664123535</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G996" t="n">
-        <v>18.952615737915</v>
+        <v>18.9526176452637</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>22.6243762969971</v>
       </c>
       <c r="G998" t="n">
-        <v>21.7534923553467</v>
+        <v>21.7534942626953</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G999" t="n">
-        <v>20.8198661804199</v>
+        <v>20.8198680877686</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1000" t="n">
-        <v>20.5397815704346</v>
+        <v>20.5397796630859</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1002" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530559539795</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G1003" t="n">
-        <v>19.5127906799316</v>
+        <v>19.512788772583</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1005" t="n">
-        <v>19.9329223632812</v>
+        <v>19.9329242706299</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G1006" t="n">
-        <v>19.7461967468262</v>
+        <v>19.7461986541748</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G1008" t="n">
-        <v>21.0065956115723</v>
+        <v>21.0065937042236</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1010" t="n">
-        <v>20.8198661804199</v>
+        <v>20.8198680877686</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1011" t="n">
-        <v>20.8198661804199</v>
+        <v>20.8198680877686</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1012" t="n">
-        <v>20.5397815704346</v>
+        <v>20.5397796630859</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1015" t="n">
-        <v>20.5397815704346</v>
+        <v>20.5397796630859</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1016" t="n">
-        <v>20.3997344970703</v>
+        <v>20.3997364044189</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1018" t="n">
-        <v>18.8125743865967</v>
+        <v>18.812572479248</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1019" t="n">
-        <v>18.2057151794434</v>
+        <v>18.2057132720947</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>18.5655822753906</v>
       </c>
       <c r="G1020" t="n">
-        <v>17.8509330749512</v>
+        <v>17.8509349822998</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.0853652954102</v>
+        <v>17.0853633880615</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G1024" t="n">
-        <v>16.6617622375488</v>
+        <v>16.6617584228516</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G1033" t="n">
-        <v>17.6972351074219</v>
+        <v>17.6972370147705</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G1037" t="n">
-        <v>18.8268489837646</v>
+        <v>18.826847076416</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G1038" t="n">
-        <v>18.5067920684814</v>
+        <v>18.5067901611328</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G1039" t="n">
-        <v>18.450309753418</v>
+        <v>18.4503116607666</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G1040" t="n">
-        <v>18.6574058532715</v>
+        <v>18.6574077606201</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>18.3908023834229</v>
       </c>
       <c r="G1042" t="n">
-        <v>17.8290214538574</v>
+        <v>17.8290233612061</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>18.8763046264648</v>
       </c>
       <c r="G1043" t="n">
-        <v>18.2996959686279</v>
+        <v>18.2996940612793</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G1044" t="n">
-        <v>18.5067920684814</v>
+        <v>18.5067901611328</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G1045" t="n">
-        <v>18.4691352844238</v>
+        <v>18.4691371917725</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>19.225866317749</v>
       </c>
       <c r="G1046" t="n">
-        <v>18.638578414917</v>
+        <v>18.6385803222656</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G1047" t="n">
-        <v>19.7211227416992</v>
+        <v>19.7211208343506</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1050" t="n">
-        <v>20.7095336914062</v>
+        <v>20.7095317840576</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G1052" t="n">
-        <v>20.7566013336182</v>
+        <v>20.7565975189209</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G1053" t="n">
-        <v>20.8978023529053</v>
+        <v>20.8978004455566</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>22.6243762969971</v>
       </c>
       <c r="G1057" t="n">
-        <v>21.9332752227783</v>
+        <v>21.933277130127</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1058" t="n">
-        <v>22.5451507568359</v>
+        <v>22.5451488494873</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1059" t="n">
-        <v>22.5451507568359</v>
+        <v>22.5451488494873</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1060" t="n">
-        <v>22.121545791626</v>
+        <v>22.1215476989746</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1062" t="n">
-        <v>22.4510135650635</v>
+        <v>22.4510116577148</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1063" t="n">
-        <v>22.121545791626</v>
+        <v>22.1215476989746</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G1064" t="n">
-        <v>21.886209487915</v>
+        <v>21.8862113952637</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1068" t="n">
-        <v>20.7095336914062</v>
+        <v>20.7095317840576</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1077" t="n">
-        <v>20.0976581573486</v>
+        <v>20.0976600646973</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G1078" t="n">
-        <v>19.8152561187744</v>
+        <v>19.8152542114258</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1079" t="n">
-        <v>19.5799217224121</v>
+        <v>19.5799198150635</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G1080" t="n">
-        <v>19.1092472076416</v>
+        <v>19.1092510223389</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>20.0512180328369</v>
       </c>
       <c r="G1081" t="n">
-        <v>19.438720703125</v>
+        <v>19.4387187957764</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>19.6628170013428</v>
       </c>
       <c r="G1084" t="n">
-        <v>19.0621814727783</v>
+        <v>19.062183380127</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G1085" t="n">
-        <v>18.8739128112793</v>
+        <v>18.8739147186279</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1086" t="n">
-        <v>18.9209785461426</v>
+        <v>18.9209823608398</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G1088" t="n">
-        <v>18.2432155609131</v>
+        <v>18.2432174682617</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G1089" t="n">
-        <v>17.8101978302002</v>
+        <v>17.8101997375488</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G1091" t="n">
-        <v>17.6031036376953</v>
+        <v>17.6031017303467</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G1097" t="n">
-        <v>18.0172901153564</v>
+        <v>18.0172939300537</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G1099" t="n">
-        <v>19.9564590454102</v>
+        <v>19.9564571380615</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G1102" t="n">
-        <v>18.0361194610596</v>
+        <v>18.0361175537109</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G1103" t="n">
-        <v>18.1679096221924</v>
+        <v>18.1679077148438</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>18.9734058380127</v>
       </c>
       <c r="G1104" t="n">
-        <v>18.3938312530518</v>
+        <v>18.3938293457031</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G1107" t="n">
-        <v>17.9419860839844</v>
+        <v>17.9419841766357</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G1109" t="n">
-        <v>18.2432155609131</v>
+        <v>18.2432174682617</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1112" t="n">
-        <v>18.3561763763428</v>
+        <v>18.3561744689941</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1113" t="n">
-        <v>18.9209785461426</v>
+        <v>18.9209823608398</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1115" t="n">
-        <v>20.4741954803467</v>
+        <v>20.4741973876953</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G1118" t="n">
-        <v>20.7566013336182</v>
+        <v>20.7565975189209</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1119" t="n">
-        <v>20.3800621032715</v>
+        <v>20.3800640106201</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1122" t="n">
-        <v>20.4741954803467</v>
+        <v>20.4741973876953</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1124" t="n">
-        <v>20.7095336914062</v>
+        <v>20.7095317840576</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1126" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1129" t="n">
-        <v>24.6161003112793</v>
+        <v>24.6161041259766</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1130" t="n">
-        <v>23.2040882110596</v>
+        <v>23.2040901184082</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1131" t="n">
-        <v>23.2040882110596</v>
+        <v>23.2040901184082</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1132" t="n">
-        <v>23.2511558532715</v>
+        <v>23.2511577606201</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1134" t="n">
-        <v>23.2511558532715</v>
+        <v>23.2511577606201</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1138" t="n">
-        <v>22.5451507568359</v>
+        <v>22.5451488494873</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1140" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>22.7214775085449</v>
       </c>
       <c r="G1145" t="n">
-        <v>22.0274105072021</v>
+        <v>22.0274124145508</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>22.9642276763916</v>
       </c>
       <c r="G1153" t="n">
-        <v>22.2627449035645</v>
+        <v>22.2627468109131</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G1154" t="n">
-        <v>21.8391418457031</v>
+        <v>21.8391437530518</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1157" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1158" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1160" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1161" t="n">
-        <v>22.121545791626</v>
+        <v>22.1215476989746</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1162" t="n">
-        <v>22.121545791626</v>
+        <v>22.1215476989746</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G1164" t="n">
-        <v>21.6038093566895</v>
+        <v>21.6038074493408</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G1165" t="n">
-        <v>21.4626045227051</v>
+        <v>21.4626064300537</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1166" t="n">
-        <v>21.6508731842041</v>
+        <v>21.6508750915527</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G1167" t="n">
-        <v>21.886209487915</v>
+        <v>21.8862113952637</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G1169" t="n">
-        <v>21.4155368804932</v>
+        <v>21.4155387878418</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G1171" t="n">
-        <v>21.6038093566895</v>
+        <v>21.6038074493408</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G1172" t="n">
-        <v>21.7920761108398</v>
+        <v>21.7920780181885</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1173" t="n">
-        <v>21.6508731842041</v>
+        <v>21.6508750915527</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>22.9642276763916</v>
       </c>
       <c r="G1174" t="n">
-        <v>22.2627449035645</v>
+        <v>22.2627468109131</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1175" t="n">
-        <v>21.6508731842041</v>
+        <v>21.6508750915527</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1176" t="n">
-        <v>22.121545791626</v>
+        <v>22.1215476989746</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1179" t="n">
-        <v>22.5451507568359</v>
+        <v>22.5451488494873</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1180" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G1182" t="n">
-        <v>21.7920761108398</v>
+        <v>21.7920780181885</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G1183" t="n">
-        <v>21.3684730529785</v>
+        <v>21.3684711456299</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1184" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1185" t="n">
-        <v>23.3452892303467</v>
+        <v>23.3452911376953</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1186" t="n">
-        <v>24.6161003112793</v>
+        <v>24.6161041259766</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G1188" t="n">
-        <v>23.8159599304199</v>
+        <v>23.8159618377686</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1189" t="n">
-        <v>23.2040882110596</v>
+        <v>23.2040901184082</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>25.9257888793945</v>
       </c>
       <c r="G1192" t="n">
-        <v>25.1338424682617</v>
+        <v>25.1338405609131</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.7573051452637</v>
+        <v>24.7573070526123</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1199" t="n">
-        <v>24.3337001800537</v>
+        <v>24.3336982727051</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1200" t="n">
-        <v>24.8514366149902</v>
+        <v>24.8514385223389</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1203" t="n">
-        <v>24.8514366149902</v>
+        <v>24.8514385223389</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1204" t="n">
-        <v>24.3337001800537</v>
+        <v>24.3336982727051</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1206" t="n">
-        <v>24.8514366149902</v>
+        <v>24.8514385223389</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>25.9257888793945</v>
       </c>
       <c r="G1207" t="n">
-        <v>25.1338424682617</v>
+        <v>25.1338405609131</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>26.1685390472412</v>
       </c>
       <c r="G1208" t="n">
-        <v>25.369176864624</v>
+        <v>25.3691749572754</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G1212" t="n">
-        <v>23.4394226074219</v>
+        <v>23.4394245147705</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1214" t="n">
-        <v>23.2040882110596</v>
+        <v>23.2040901184082</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1218" t="n">
-        <v>23.1099529266357</v>
+        <v>23.1099548339844</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1220" t="n">
-        <v>23.0628890991211</v>
+        <v>23.0628871917725</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1223" t="n">
-        <v>23.3452892303467</v>
+        <v>23.3452911376953</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G1225" t="n">
-        <v>23.8630294799805</v>
+        <v>23.8630275726318</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1229" t="n">
-        <v>23.1099529266357</v>
+        <v>23.1099548339844</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1231" t="n">
-        <v>23.0628890991211</v>
+        <v>23.0628871917725</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1233" t="n">
-        <v>23.1099529266357</v>
+        <v>23.1099548339844</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1235" t="n">
-        <v>23.0628890991211</v>
+        <v>23.0628871917725</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1236" t="n">
-        <v>22.4510135650635</v>
+        <v>22.4510116577148</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1237" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G1242" t="n">
-        <v>21.1802043914795</v>
+        <v>21.1802024841309</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>22.915678024292</v>
       </c>
       <c r="G1246" t="n">
-        <v>22.2156791687012</v>
+        <v>22.2156772613525</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1247" t="n">
-        <v>22.4510135650635</v>
+        <v>22.4510116577148</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1249" t="n">
-        <v>23.2511558532715</v>
+        <v>23.2511577606201</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1258" t="n">
-        <v>23.0628890991211</v>
+        <v>23.0628871917725</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1261" t="n">
-        <v>22.4510135650635</v>
+        <v>22.4510116577148</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1268" t="n">
-        <v>25.4162464141846</v>
+        <v>25.4162425994873</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>26.4598407745361</v>
       </c>
       <c r="G1273" t="n">
-        <v>25.6515808105469</v>
+        <v>25.6515789031982</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>26.7996921539307</v>
       </c>
       <c r="G1279" t="n">
-        <v>26.1482486724854</v>
+        <v>26.148250579834</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>26.071439743042</v>
       </c>
       <c r="G1284" t="n">
-        <v>25.4377002716064</v>
+        <v>25.4376983642578</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1286" t="n">
-        <v>25.7219200134277</v>
+        <v>25.7219181060791</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>26.7996921539307</v>
       </c>
       <c r="G1288" t="n">
-        <v>26.1482486724854</v>
+        <v>26.148250579834</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G1289" t="n">
-        <v>25.342960357666</v>
+        <v>25.3429584503174</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1291" t="n">
-        <v>25.7219200134277</v>
+        <v>25.7219181060791</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>26.2656402587891</v>
       </c>
       <c r="G1295" t="n">
-        <v>25.6271781921387</v>
+        <v>25.6271800994873</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>25.7315883636475</v>
       </c>
       <c r="G1298" t="n">
-        <v>25.106107711792</v>
+        <v>25.1061096191406</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1302" t="n">
-        <v>24.3955612182617</v>
+        <v>24.3955593109131</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1307" t="n">
-        <v>24.7745189666748</v>
+        <v>24.7745208740234</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G1309" t="n">
-        <v>24.6797771453857</v>
+        <v>24.6797790527344</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1313" t="n">
-        <v>24.3955612182617</v>
+        <v>24.3955593109131</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1315" t="n">
-        <v>23.7323799133301</v>
+        <v>23.7323780059814</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1317" t="n">
-        <v>24.0639705657959</v>
+        <v>24.0639686584473</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1318" t="n">
-        <v>23.5429000854492</v>
+        <v>23.5428981781006</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1321" t="n">
-        <v>24.1587104797363</v>
+        <v>24.1587085723877</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1322" t="n">
-        <v>23.7323799133301</v>
+        <v>23.7323780059814</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1324" t="n">
-        <v>24.4902992248535</v>
+        <v>24.4902973175049</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1326" t="n">
-        <v>23.5429000854492</v>
+        <v>23.5428981781006</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1327" t="n">
-        <v>23.874490737915</v>
+        <v>23.8744888305664</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1328" t="n">
-        <v>24.2534465789795</v>
+        <v>24.2534484863281</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1329" t="n">
-        <v>24.2534465789795</v>
+        <v>24.2534484863281</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1330" t="n">
-        <v>23.7323799133301</v>
+        <v>23.7323780059814</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1333" t="n">
-        <v>24.7745189666748</v>
+        <v>24.7745208740234</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1336" t="n">
-        <v>23.874490737915</v>
+        <v>23.8744888305664</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1337" t="n">
-        <v>23.4955272674561</v>
+        <v>23.4955291748047</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1339" t="n">
-        <v>23.0691986083984</v>
+        <v>23.0691967010498</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1340" t="n">
-        <v>23.0691986083984</v>
+        <v>23.0691967010498</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1341" t="n">
-        <v>23.0691986083984</v>
+        <v>23.0691967010498</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>23.3040790557861</v>
       </c>
       <c r="G1343" t="n">
-        <v>22.7376079559326</v>
+        <v>22.737606048584</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1345" t="n">
-        <v>21.7902069091797</v>
+        <v>21.7902088165283</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1350" t="n">
-        <v>21.1743984222412</v>
+        <v>21.1743965148926</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1351" t="n">
-        <v>21.1743984222412</v>
+        <v>21.1743965148926</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1361" t="n">
-        <v>21.1743984222412</v>
+        <v>21.1743965148926</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1363" t="n">
-        <v>20.5112171173096</v>
+        <v>20.5112190246582</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G1365" t="n">
-        <v>18.8153705596924</v>
+        <v>18.815372467041</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>19.759916305542</v>
       </c>
       <c r="G1366" t="n">
-        <v>19.2795963287354</v>
+        <v>19.279598236084</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>18.9734058380127</v>
       </c>
       <c r="G1367" t="n">
-        <v>18.5122051239014</v>
+        <v>18.5122032165527</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>18.8763046264648</v>
       </c>
       <c r="G1368" t="n">
-        <v>18.4174633026123</v>
+        <v>18.4174613952637</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>18.0218200683594</v>
       </c>
       <c r="G1372" t="n">
-        <v>17.5837478637695</v>
+        <v>17.5837497711182</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G1376" t="n">
-        <v>19.800666809082</v>
+        <v>19.8006649017334</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G1377" t="n">
-        <v>20.0848846435547</v>
+        <v>20.0848865509033</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1378" t="n">
-        <v>19.7059288024902</v>
+        <v>19.7059268951416</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1384" t="n">
-        <v>21.7902069091797</v>
+        <v>21.7902088165283</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1387" t="n">
-        <v>20.5112171173096</v>
+        <v>20.5112190246582</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1390" t="n">
-        <v>19.8065528869629</v>
+        <v>19.8065509796143</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1396" t="n">
-        <v>22.7336273193359</v>
+        <v>22.7336254119873</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1401" t="n">
-        <v>22.0018577575684</v>
+        <v>22.001859664917</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1406" t="n">
-        <v>23.0751209259033</v>
+        <v>23.0751190185547</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1407" t="n">
-        <v>23.8556747436523</v>
+        <v>23.8556728363037</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1408" t="n">
-        <v>23.0751209259033</v>
+        <v>23.0751190185547</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1409" t="n">
-        <v>23.367826461792</v>
+        <v>23.3678302764893</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1410" t="n">
-        <v>24.2459526062012</v>
+        <v>24.2459506988525</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>24.3435192108154</v>
+        <v>24.3435211181641</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G1413" t="n">
-        <v>24.5386562347412</v>
+        <v>24.5386581420898</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>24.75</v>
       </c>
       <c r="G1414" t="n">
-        <v>24.148380279541</v>
+        <v>24.1483821868896</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>24.1971664428711</v>
+        <v>24.1971645355225</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1416" t="n">
-        <v>23.367826461792</v>
+        <v>23.3678302764893</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1417" t="n">
-        <v>22.7336273193359</v>
+        <v>22.7336254119873</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1418" t="n">
-        <v>22.7336273193359</v>
+        <v>22.7336254119873</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1422" t="n">
-        <v>22.3921375274658</v>
+        <v>22.3921356201172</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>22.0506439208984</v>
+        <v>22.0506458282471</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1425" t="n">
-        <v>22.3433513641357</v>
+        <v>22.3433494567871</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1428" t="n">
-        <v>22.2945671081543</v>
+        <v>22.2945652008057</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1430" t="n">
-        <v>21.5627956390381</v>
+        <v>21.5627975463867</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>22.25</v>
       </c>
       <c r="G1433" t="n">
-        <v>21.7091503143311</v>
+        <v>21.7091522216797</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1434" t="n">
-        <v>22.0994281768799</v>
+        <v>22.0994262695312</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1438" t="n">
-        <v>22.2945671081543</v>
+        <v>22.2945652008057</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1439" t="n">
-        <v>21.8067207336426</v>
+        <v>21.8067226409912</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>22.25</v>
       </c>
       <c r="G1440" t="n">
-        <v>21.7091503143311</v>
+        <v>21.7091522216797</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1441" t="n">
-        <v>21.5627956390381</v>
+        <v>21.5627975463867</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1442" t="n">
-        <v>22.3433513641357</v>
+        <v>22.3433494567871</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1443" t="n">
-        <v>22.0994281768799</v>
+        <v>22.0994262695312</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>22.25</v>
       </c>
       <c r="G1446" t="n">
-        <v>21.7091503143311</v>
+        <v>21.7091522216797</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1449" t="n">
-        <v>22.2945671081543</v>
+        <v>22.2945652008057</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1462" t="n">
-        <v>21.2700881958008</v>
+        <v>21.2700901031494</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>19.6114139556885</v>
+        <v>19.6114120483398</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>20</v>
       </c>
       <c r="G1464" t="n">
-        <v>19.513843536377</v>
+        <v>19.5138416290283</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1470" t="n">
-        <v>19.0650234222412</v>
+        <v>19.0650253295898</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>20.5</v>
       </c>
       <c r="G1476" t="n">
-        <v>20.0016918182373</v>
+        <v>20.0016899108887</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>21</v>
       </c>
       <c r="G1477" t="n">
-        <v>20.4895362854004</v>
+        <v>20.489538192749</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>20.5</v>
       </c>
       <c r="G1479" t="n">
-        <v>20.0016918182373</v>
+        <v>20.0016899108887</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1486" t="n">
-        <v>19.240650177002</v>
+        <v>19.2406482696533</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1489" t="n">
-        <v>18.2844734191895</v>
+        <v>18.2844715118408</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1491" t="n">
-        <v>18.1088447570801</v>
+        <v>18.1088466644287</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1492" t="n">
-        <v>17.9722480773926</v>
+        <v>17.9722499847412</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1494" t="n">
-        <v>18.1088447570801</v>
+        <v>18.1088466644287</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.0307922363281</v>
+        <v>18.0307903289795</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1497" t="n">
-        <v>18.2844734191895</v>
+        <v>18.2844715118408</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1499" t="n">
-        <v>18.5576648712158</v>
+        <v>18.5576667785645</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1500" t="n">
-        <v>18.5186367034912</v>
+        <v>18.5186386108398</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1501" t="n">
-        <v>18.3820400238037</v>
+        <v>18.3820419311523</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1502" t="n">
-        <v>18.5576648712158</v>
+        <v>18.5576667785645</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1505" t="n">
-        <v>17.308780670166</v>
+        <v>17.3087787628174</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1508" t="n">
-        <v>16.6453094482422</v>
+        <v>16.6453075408936</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1509" t="n">
-        <v>18.36252784729</v>
+        <v>18.3625259399414</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1512" t="n">
-        <v>18.0112781524658</v>
+        <v>18.0112762451172</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1513" t="n">
-        <v>17.4063491821289</v>
+        <v>17.4063510894775</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1515" t="n">
-        <v>17.2112083435059</v>
+        <v>17.2112102508545</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1522" t="n">
-        <v>17.3478050231934</v>
+        <v>17.3478088378906</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1523" t="n">
-        <v>16.9965572357178</v>
+        <v>16.9965591430664</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1530" t="n">
-        <v>17.0160713195801</v>
+        <v>17.0160732269287</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1533" t="n">
-        <v>16.8209323883057</v>
+        <v>16.8209342956543</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1534" t="n">
-        <v>16.5087127685547</v>
+        <v>16.5087108612061</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1535" t="n">
-        <v>17.308780670166</v>
+        <v>17.3087787628174</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>17.5</v>
       </c>
       <c r="G1536" t="n">
-        <v>17.0746116638184</v>
+        <v>17.074613571167</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1542" t="n">
-        <v>16.8280143737793</v>
+        <v>16.8280124664307</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>16.5715484619141</v>
+        <v>16.5715465545654</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1546" t="n">
-        <v>17.3803977966309</v>
+        <v>17.3803997039795</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1547" t="n">
-        <v>17.4987678527832</v>
+        <v>17.4987659454346</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1553" t="n">
-        <v>17.0844764709473</v>
+        <v>17.0844783782959</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1554" t="n">
-        <v>17.5974063873291</v>
+        <v>17.5974082946777</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1557" t="n">
-        <v>17.3212127685547</v>
+        <v>17.3212146759033</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1562" t="n">
-        <v>16.5715484619141</v>
+        <v>16.5715465545654</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1563" t="n">
-        <v>16.6307315826416</v>
+        <v>16.6307334899902</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1564" t="n">
-        <v>16.8280143737793</v>
+        <v>16.8280124664307</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1567" t="n">
-        <v>15.5654182434082</v>
+        <v>15.5654191970825</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="n">
-        <v>15.6837863922119</v>
+        <v>15.6837873458862</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>16.5</v>
       </c>
       <c r="G1570" t="n">
-        <v>16.2756290435791</v>
+        <v>16.2756271362305</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1571" t="n">
-        <v>16.2361717224121</v>
+        <v>16.2361698150635</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1572" t="n">
-        <v>15.9205236434937</v>
+        <v>15.920521736145</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1573" t="n">
-        <v>16.0191631317139</v>
+        <v>16.0191650390625</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>16.3742694854736</v>
+        <v>16.374267578125</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1575" t="n">
-        <v>16.867467880249</v>
+        <v>16.8674697875977</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1578" t="n">
-        <v>17.4593105316162</v>
+        <v>17.4593124389648</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1579" t="n">
-        <v>17.1042041778564</v>
+        <v>17.1042060852051</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1583" t="n">
-        <v>17.5579490661621</v>
+        <v>17.5579509735107</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1588" t="n">
-        <v>16.867467880249</v>
+        <v>16.8674697875977</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1590" t="n">
-        <v>16.7491016387939</v>
+        <v>16.7490997314453</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1594" t="n">
-        <v>16.9858379364014</v>
+        <v>16.9858360290527</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1595" t="n">
-        <v>17.5579490661621</v>
+        <v>17.5579509735107</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1596" t="n">
-        <v>17.8144149780273</v>
+        <v>17.8144130706787</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1605" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1609" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1612" t="n">
-        <v>19.1361923217773</v>
+        <v>19.136194229126</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1613" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1615" t="n">
-        <v>18.761360168457</v>
+        <v>18.7613620758057</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1618" t="n">
-        <v>19.1361923217773</v>
+        <v>19.136194229126</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1621" t="n">
-        <v>19.4518413543701</v>
+        <v>19.4518394470215</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1622" t="n">
-        <v>19.0770072937012</v>
+        <v>19.0770092010498</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1630" t="n">
-        <v>18.5640811920166</v>
+        <v>18.564079284668</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1634" t="n">
-        <v>18.0511512756348</v>
+        <v>18.0511493682861</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1635" t="n">
-        <v>16.9858379364014</v>
+        <v>16.9858360290527</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1636" t="n">
-        <v>17.5974063873291</v>
+        <v>17.5974082946777</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1644" t="n">
-        <v>17.3803977966309</v>
+        <v>17.3803997039795</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1645" t="n">
-        <v>17.9130554199219</v>
+        <v>17.9130535125732</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1652" t="n">
-        <v>18.4457111358643</v>
+        <v>18.4457130432129</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1655" t="n">
-        <v>18.4457111358643</v>
+        <v>18.4457130432129</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1656" t="n">
-        <v>18.800817489624</v>
+        <v>18.8008155822754</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>19.294017791748</v>
+        <v>19.2940158843994</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1659" t="n">
-        <v>19.0770072937012</v>
+        <v>19.0770092010498</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1662" t="n">
-        <v>17.9130554199219</v>
+        <v>17.9130535125732</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1665" t="n">
-        <v>17.9525127410889</v>
+        <v>17.9525108337402</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1677" t="n">
-        <v>17.6171340942383</v>
+        <v>17.6171360015869</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1680" t="n">
-        <v>18.800817489624</v>
+        <v>18.8008155822754</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1681" t="n">
-        <v>18.8600006103516</v>
+        <v>18.8600025177002</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1682" t="n">
-        <v>18.8600006103516</v>
+        <v>18.8600025177002</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1684" t="n">
-        <v>18.8600006103516</v>
+        <v>18.8600025177002</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1685" t="n">
-        <v>19.1361923217773</v>
+        <v>19.136194229126</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1691" t="n">
-        <v>19.1559200286865</v>
+        <v>19.1559219360352</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1692" t="n">
-        <v>19.4912986755371</v>
+        <v>19.4912967681885</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1693" t="n">
-        <v>19.1559200286865</v>
+        <v>19.1559219360352</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1699" t="n">
-        <v>21.0103569030762</v>
+        <v>21.0103549957275</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>21</v>
       </c>
       <c r="G1705" t="n">
-        <v>20.7144355773926</v>
+        <v>20.7144374847412</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>20.75</v>
       </c>
       <c r="G1706" t="n">
-        <v>20.4678344726562</v>
+        <v>20.4678363800049</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1712" t="n">
-        <v>18.800817489624</v>
+        <v>18.8008155822754</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1715" t="n">
-        <v>20.6651153564453</v>
+        <v>20.6651172637939</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1717" t="n">
-        <v>19.3926582336426</v>
+        <v>19.3926563262939</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>20</v>
       </c>
       <c r="G1718" t="n">
-        <v>19.7280349731445</v>
+        <v>19.7280330657959</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1720" t="n">
-        <v>17.8933277130127</v>
+        <v>17.8933258056641</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1724" t="n">
-        <v>18.761360168457</v>
+        <v>18.7613620758057</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1729" t="n">
-        <v>17.3014850616455</v>
+        <v>17.3014869689941</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1731" t="n">
-        <v>16.6307315826416</v>
+        <v>16.6307334899902</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1732" t="n">
-        <v>16.5123653411865</v>
+        <v>16.5123634338379</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>16.5</v>
       </c>
       <c r="G1734" t="n">
-        <v>16.2756290435791</v>
+        <v>16.2756271362305</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>15</v>
       </c>
       <c r="G1736" t="n">
-        <v>14.7960252761841</v>
+        <v>14.7960262298584</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1740" t="n">
-        <v>15.6837863922119</v>
+        <v>15.6837873458862</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1742" t="n">
-        <v>16.6307315826416</v>
+        <v>16.6307334899902</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1743" t="n">
-        <v>16.3742694854736</v>
+        <v>16.374267578125</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1747" t="n">
-        <v>16.9858379364014</v>
+        <v>16.9858360290527</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1748" t="n">
-        <v>17.1042041778564</v>
+        <v>17.1042060852051</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1758" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1759" t="n">
-        <v>20.1719169616699</v>
+        <v>20.1719150543213</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1761" t="n">
-        <v>19.3926582336426</v>
+        <v>19.3926563262939</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>21</v>
       </c>
       <c r="G1763" t="n">
-        <v>20.7144355773926</v>
+        <v>20.7144374847412</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>20.75</v>
       </c>
       <c r="G1764" t="n">
-        <v>20.4678344726562</v>
+        <v>20.4678363800049</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1766" t="n">
-        <v>20.6157970428467</v>
+        <v>20.615795135498</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1767" t="n">
-        <v>20.1719169616699</v>
+        <v>20.1719150543213</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1768" t="n">
-        <v>20.6157970428467</v>
+        <v>20.615795135498</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1772" t="n">
-        <v>20.418514251709</v>
+        <v>20.4185161590576</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>20.75</v>
       </c>
       <c r="G1773" t="n">
-        <v>20.4678344726562</v>
+        <v>20.4678363800049</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1784" t="n">
-        <v>22.2433567047119</v>
+        <v>22.2433586120605</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1785" t="n">
-        <v>22.3419990539551</v>
+        <v>22.3419971466064</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -55232,6 +55232,32 @@
         <v>28.5</v>
       </c>
       <c r="H2110" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2111" t="n">
+        <v>85472</v>
+      </c>
+      <c r="C2111" t="n">
+        <v>29.1499996185303</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>27.9500007629395</v>
+      </c>
+      <c r="E2111" t="n">
+        <v>29.1499996185303</v>
+      </c>
+      <c r="F2111" t="n">
+        <v>28.0499992370605</v>
+      </c>
+      <c r="G2111" t="n">
+        <v>28.0499992370605</v>
+      </c>
+      <c r="H2111" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -48987,8 +48987,31 @@
       <c r="E2114" t="n">
         <v>28.3999996185303</v>
       </c>
-      <c r="F2114"/>
+      <c r="F2114" t="n">
+        <v>28.3999996185303</v>
+      </c>
       <c r="G2114" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2115" t="n">
+        <v>178515</v>
+      </c>
+      <c r="C2115" t="n">
+        <v>29.7000007629395</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>28.1499996185303</v>
+      </c>
+      <c r="E2115" t="n">
+        <v>28.7999992370605</v>
+      </c>
+      <c r="F2115"/>
+      <c r="G2115" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -49010,8 +49010,31 @@
       <c r="E2115" t="n">
         <v>28.7999992370605</v>
       </c>
-      <c r="F2115"/>
+      <c r="F2115" t="n">
+        <v>28.8999996185303</v>
+      </c>
       <c r="G2115" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2116" t="n">
+        <v>47056</v>
+      </c>
+      <c r="C2116" t="n">
+        <v>28.5499992370605</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>27.8500003814697</v>
+      </c>
+      <c r="E2116" t="n">
+        <v>28.3999996185303</v>
+      </c>
+      <c r="F2116"/>
+      <c r="G2116" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -49033,8 +49033,31 @@
       <c r="E2116" t="n">
         <v>28.3999996185303</v>
       </c>
-      <c r="F2116"/>
+      <c r="F2116" t="n">
+        <v>28</v>
+      </c>
       <c r="G2116" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2117" t="n">
+        <v>76884</v>
+      </c>
+      <c r="C2117" t="n">
+        <v>28.3999996185303</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>26.6000003814697</v>
+      </c>
+      <c r="E2117" t="n">
+        <v>28.3999996185303</v>
+      </c>
+      <c r="F2117"/>
+      <c r="G2117" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -49056,8 +49056,31 @@
       <c r="E2117" t="n">
         <v>28.3999996185303</v>
       </c>
-      <c r="F2117"/>
+      <c r="F2117" t="n">
+        <v>26.75</v>
+      </c>
       <c r="G2117" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2118" t="n">
+        <v>43014</v>
+      </c>
+      <c r="C2118" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>26.8999996185303</v>
+      </c>
+      <c r="E2118" t="n">
+        <v>26.9500007629395</v>
+      </c>
+      <c r="F2118"/>
+      <c r="G2118" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -49086,6 +49086,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2119">
+      <c r="A2119" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2119" t="n">
+        <v>41838</v>
+      </c>
+      <c r="C2119" t="n">
+        <v>27.6000003814697</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2119" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2119" t="n">
+        <v>27.5499992370605</v>
+      </c>
+      <c r="G2119" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G2" t="n">
-        <v>7.53173208236694</v>
+        <v>7.53173303604126</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G3" t="n">
-        <v>7.85125923156738</v>
+        <v>7.85125875473022</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G4" t="n">
-        <v>7.7599663734436</v>
+        <v>7.75996494293213</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G5" t="n">
-        <v>7.7599663734436</v>
+        <v>7.75996494293213</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G6" t="n">
-        <v>7.66867446899414</v>
+        <v>7.66867351531982</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>8.1253547668457</v>
       </c>
       <c r="G7" t="n">
-        <v>7.63945817947388</v>
+        <v>7.63945770263672</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.10884761810303</v>
       </c>
       <c r="G10" t="n">
-        <v>7.62393808364868</v>
+        <v>7.62393760681152</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>8.42830753326416</v>
       </c>
       <c r="G11" t="n">
-        <v>7.92429494857788</v>
+        <v>7.92429351806641</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G12" t="n">
-        <v>7.53173208236694</v>
+        <v>7.53173303604126</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G13" t="n">
-        <v>7.53173208236694</v>
+        <v>7.53173303604126</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>7.71656322479248</v>
       </c>
       <c r="G15" t="n">
-        <v>7.2551121711731</v>
+        <v>7.25511264801025</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.95154619216919</v>
       </c>
       <c r="G16" t="n">
-        <v>7.47604370117188</v>
+        <v>7.47604322433472</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>7.88940191268921</v>
       </c>
       <c r="G17" t="n">
-        <v>7.41761541366577</v>
+        <v>7.41761493682861</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.00106716156006</v>
       </c>
       <c r="G18" t="n">
-        <v>7.52260303497314</v>
+        <v>7.5226035118103</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>7.8651270866394</v>
       </c>
       <c r="G19" t="n">
-        <v>7.39479207992554</v>
+        <v>7.3947925567627</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>7.95251703262329</v>
       </c>
       <c r="G20" t="n">
-        <v>7.47695589065552</v>
+        <v>7.47695684432983</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>8.08068943023682</v>
       </c>
       <c r="G22" t="n">
-        <v>7.59746265411377</v>
+        <v>7.59746313095093</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>8.24381828308105</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75083684921265</v>
+        <v>7.75083780288696</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G24" t="n">
-        <v>7.66867446899414</v>
+        <v>7.66867351531982</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G25" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561256408691</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>8.37101936340332</v>
       </c>
       <c r="G26" t="n">
-        <v>7.87043285369873</v>
+        <v>7.87043142318726</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G27" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561256408691</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.45743942260742</v>
       </c>
       <c r="G28" t="n">
-        <v>7.95168447494507</v>
+        <v>7.95168399810791</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>8.31178760528564</v>
       </c>
       <c r="G29" t="n">
-        <v>7.81474256515503</v>
+        <v>7.81474208831787</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.47394561767578</v>
       </c>
       <c r="G30" t="n">
-        <v>7.96720361709595</v>
+        <v>7.96720457077026</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G31" t="n">
-        <v>7.85125923156738</v>
+        <v>7.85125875473022</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>8.25741195678711</v>
       </c>
       <c r="G32" t="n">
-        <v>7.76361894607544</v>
+        <v>7.76361846923828</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.20497798919678</v>
       </c>
       <c r="G33" t="n">
-        <v>7.71431970596313</v>
+        <v>7.71432018280029</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G34" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561256408691</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G35" t="n">
-        <v>7.66867446899414</v>
+        <v>7.66867351531982</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G36" t="n">
-        <v>7.66867446899414</v>
+        <v>7.66867351531982</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>8.31178760528564</v>
       </c>
       <c r="G37" t="n">
-        <v>7.81474256515503</v>
+        <v>7.81474208831787</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G38" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561256408691</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G39" t="n">
-        <v>7.85125923156738</v>
+        <v>7.85125875473022</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.29625225067139</v>
       </c>
       <c r="G40" t="n">
-        <v>7.80013608932495</v>
+        <v>7.80013561248779</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.23410797119141</v>
       </c>
       <c r="G42" t="n">
-        <v>7.74170780181885</v>
+        <v>7.74170732498169</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>8.1855583190918</v>
       </c>
       <c r="G43" t="n">
-        <v>7.6960620880127</v>
+        <v>7.69606161117554</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G44" t="n">
-        <v>7.66867446899414</v>
+        <v>7.66867351531982</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G45" t="n">
-        <v>7.85125923156738</v>
+        <v>7.85125875473022</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>8.33606338500977</v>
       </c>
       <c r="G46" t="n">
-        <v>7.83756685256958</v>
+        <v>7.83756732940674</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.99232816696167</v>
       </c>
       <c r="G47" t="n">
-        <v>7.51438665390015</v>
+        <v>7.51438760757446</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>8.10787677764893</v>
       </c>
       <c r="G48" t="n">
-        <v>7.62302541732788</v>
+        <v>7.62302494049072</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>8.1875</v>
       </c>
       <c r="G50" t="n">
-        <v>7.69788789749146</v>
+        <v>7.6978874206543</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>8.44772911071777</v>
       </c>
       <c r="G51" t="n">
-        <v>7.94255447387695</v>
+        <v>7.94255352020264</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>8.51667022705078</v>
       </c>
       <c r="G52" t="n">
-        <v>8.00737190246582</v>
+        <v>8.00737285614014</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>8.57395935058594</v>
       </c>
       <c r="G53" t="n">
-        <v>8.06123638153076</v>
+        <v>8.06123542785645</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G54" t="n">
-        <v>8.24930000305176</v>
+        <v>8.24930095672607</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.24977684020996</v>
       </c>
       <c r="G57" t="n">
-        <v>8.69664001464844</v>
+        <v>8.69663906097412</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.08859062194824</v>
       </c>
       <c r="G59" t="n">
-        <v>8.54509162902832</v>
+        <v>8.545090675354</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>8.75844955444336</v>
       </c>
       <c r="G60" t="n">
-        <v>8.23469543457031</v>
+        <v>8.234694480896</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>8.71960926055908</v>
       </c>
       <c r="G61" t="n">
-        <v>8.19817733764648</v>
+        <v>8.19817638397217</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G64" t="n">
-        <v>8.39902400970459</v>
+        <v>8.39902305603027</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.20511054992676</v>
       </c>
       <c r="G65" t="n">
-        <v>8.65464305877686</v>
+        <v>8.65464401245117</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.10412693023682</v>
       </c>
       <c r="G67" t="n">
-        <v>8.55969905853271</v>
+        <v>8.55970001220703</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.29250144958496</v>
       </c>
       <c r="G69" t="n">
-        <v>8.73680877685547</v>
+        <v>8.73680973052979</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.51583194732666</v>
       </c>
       <c r="G70" t="n">
-        <v>8.94678401947021</v>
+        <v>8.94678497314453</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.51583194732666</v>
       </c>
       <c r="G71" t="n">
-        <v>8.94678401947021</v>
+        <v>8.94678497314453</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.37115287780762</v>
       </c>
       <c r="G72" t="n">
-        <v>8.81075668334961</v>
+        <v>8.81075763702393</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.66148281097412</v>
       </c>
       <c r="G74" t="n">
-        <v>9.08372497558594</v>
+        <v>9.08372688293457</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G75" t="n">
-        <v>9.27544212341309</v>
+        <v>9.27544116973877</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.63332366943359</v>
       </c>
       <c r="G77" t="n">
-        <v>9.05724906921387</v>
+        <v>9.05725002288818</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.70614910125732</v>
       </c>
       <c r="G79" t="n">
-        <v>9.12572193145752</v>
+        <v>9.1257209777832</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.57506275177002</v>
       </c>
       <c r="G80" t="n">
-        <v>9.00247383117676</v>
+        <v>9.00247478485107</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.53525161743164</v>
       </c>
       <c r="G81" t="n">
-        <v>8.96504211425781</v>
+        <v>8.96504306793213</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.26239967346191</v>
       </c>
       <c r="G82" t="n">
-        <v>8.70850658416748</v>
+        <v>8.7085075378418</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.55467224121094</v>
       </c>
       <c r="G84" t="n">
-        <v>8.98330116271973</v>
+        <v>8.98330211639404</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.40610885620117</v>
       </c>
       <c r="G85" t="n">
-        <v>8.84362316131592</v>
+        <v>8.8436222076416</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.98954772949219</v>
       </c>
       <c r="G87" t="n">
-        <v>8.45197105407715</v>
+        <v>8.45197200775146</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>8.43413352966309</v>
       </c>
       <c r="G89" t="n">
-        <v>7.92977142333984</v>
+        <v>7.92977285385132</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>8.77689933776855</v>
       </c>
       <c r="G90" t="n">
-        <v>8.25204277038574</v>
+        <v>8.25203895568848</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.03033065795898</v>
       </c>
       <c r="G92" t="n">
-        <v>8.49031639099121</v>
+        <v>8.49031734466553</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.07888126373291</v>
       </c>
       <c r="G93" t="n">
-        <v>8.535964012146</v>
+        <v>8.53596496582031</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.07888126373291</v>
       </c>
       <c r="G95" t="n">
-        <v>8.535964012146</v>
+        <v>8.53596496582031</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.30706596374512</v>
       </c>
       <c r="G96" t="n">
-        <v>8.75050258636475</v>
+        <v>8.75050163269043</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G98" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561256408691</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>8.48462677001953</v>
       </c>
       <c r="G99" t="n">
-        <v>7.97724533081055</v>
+        <v>7.97724580764771</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G101" t="n">
-        <v>7.7599663734436</v>
+        <v>7.75996494293213</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>8.19041347503662</v>
       </c>
       <c r="G102" t="n">
-        <v>7.70062637329102</v>
+        <v>7.70062589645386</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>8.3700475692749</v>
       </c>
       <c r="G103" t="n">
-        <v>7.86952018737793</v>
+        <v>7.8695182800293</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>8.3700475692749</v>
       </c>
       <c r="G104" t="n">
-        <v>7.86952018737793</v>
+        <v>7.8695182800293</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.81476783752441</v>
       </c>
       <c r="G105" t="n">
-        <v>8.2876443862915</v>
+        <v>8.28764533996582</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.27502346038818</v>
       </c>
       <c r="G107" t="n">
-        <v>8.72037696838379</v>
+        <v>8.72037601470947</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.25074768066406</v>
       </c>
       <c r="G108" t="n">
-        <v>8.69755172729492</v>
+        <v>8.69755268096924</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.98760604858398</v>
       </c>
       <c r="G109" t="n">
-        <v>8.4501485824585</v>
+        <v>8.45014667510986</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.08664894104004</v>
       </c>
       <c r="G110" t="n">
-        <v>8.54326725006104</v>
+        <v>8.54326629638672</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.06334495544434</v>
       </c>
       <c r="G112" t="n">
-        <v>8.52135562896729</v>
+        <v>8.5213565826416</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>8.86817264556885</v>
       </c>
       <c r="G113" t="n">
-        <v>8.33785533905029</v>
+        <v>8.33785629272461</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.81379699707031</v>
       </c>
       <c r="G114" t="n">
-        <v>8.28672981262207</v>
+        <v>8.2867317199707</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>9.04586696624756</v>
       </c>
       <c r="G115" t="n">
-        <v>8.50492382049561</v>
+        <v>8.50492477416992</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.2138500213623</v>
       </c>
       <c r="G116" t="n">
-        <v>8.66286182403564</v>
+        <v>8.66286087036133</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.51084423065186</v>
       </c>
       <c r="G117" t="n">
-        <v>8.00189781188965</v>
+        <v>8.00189590454102</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.49724960327148</v>
       </c>
       <c r="G118" t="n">
-        <v>7.98911476135254</v>
+        <v>7.98911428451538</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.65260982513428</v>
       </c>
       <c r="G120" t="n">
-        <v>8.13518238067627</v>
+        <v>8.1351842880249</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.03324413299561</v>
       </c>
       <c r="G121" t="n">
-        <v>8.49305725097656</v>
+        <v>8.49305438995361</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G123" t="n">
-        <v>8.39902400970459</v>
+        <v>8.39902305603027</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G125" t="n">
-        <v>8.39902400970459</v>
+        <v>8.39902305603027</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.48281764984131</v>
       </c>
       <c r="G128" t="n">
-        <v>8.91574573516846</v>
+        <v>8.91574478149414</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.53525161743164</v>
       </c>
       <c r="G133" t="n">
-        <v>8.96504211425781</v>
+        <v>8.96504306793213</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.5935115814209</v>
       </c>
       <c r="G134" t="n">
-        <v>9.01981735229492</v>
+        <v>9.01982021331787</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.35755920410156</v>
       </c>
       <c r="G135" t="n">
-        <v>8.79797554016113</v>
+        <v>8.79797649383545</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>8.70018863677979</v>
       </c>
       <c r="G138" t="n">
-        <v>8.17991733551025</v>
+        <v>8.17991828918457</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G139" t="n">
-        <v>8.2164363861084</v>
+        <v>8.21643733978271</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>8.80991268157959</v>
       </c>
       <c r="G140" t="n">
-        <v>8.28308010101318</v>
+        <v>8.28307819366455</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G142" t="n">
-        <v>8.24930000305176</v>
+        <v>8.24930095672607</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>8.8798246383667</v>
       </c>
       <c r="G143" t="n">
-        <v>8.34881114959717</v>
+        <v>8.34880924224854</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>8.76815986633301</v>
       </c>
       <c r="G145" t="n">
-        <v>8.24382400512695</v>
+        <v>8.24382209777832</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G147" t="n">
-        <v>8.24930000305176</v>
+        <v>8.24930095672607</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>8.91380977630615</v>
       </c>
       <c r="G150" t="n">
-        <v>8.38076210021973</v>
+        <v>8.38076305389404</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>8.69047927856445</v>
       </c>
       <c r="G151" t="n">
-        <v>8.17078685760498</v>
+        <v>8.17078876495361</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G152" t="n">
-        <v>8.2164363861084</v>
+        <v>8.21643733978271</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>8.82739067077637</v>
       </c>
       <c r="G153" t="n">
-        <v>8.29951190948486</v>
+        <v>8.29951286315918</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>8.65260982513428</v>
       </c>
       <c r="G154" t="n">
-        <v>8.13518238067627</v>
+        <v>8.1351842880249</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>8.61474132537842</v>
       </c>
       <c r="G156" t="n">
-        <v>8.09957885742188</v>
+        <v>8.09957981109619</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G157" t="n">
-        <v>8.2164363861084</v>
+        <v>8.21643733978271</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>8.90410041809082</v>
       </c>
       <c r="G159" t="n">
-        <v>8.37163257598877</v>
+        <v>8.37163543701172</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>8.96430206298828</v>
       </c>
       <c r="G160" t="n">
-        <v>8.42823791503906</v>
+        <v>8.42823600769043</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.26822566986084</v>
       </c>
       <c r="G163" t="n">
-        <v>8.71398544311523</v>
+        <v>8.71398639678955</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.61584568023682</v>
       </c>
       <c r="G165" t="n">
-        <v>9.04081630706787</v>
+        <v>9.04081726074219</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.57894706726074</v>
       </c>
       <c r="G166" t="n">
-        <v>9.00612640380859</v>
+        <v>9.00612545013428</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.40222454071045</v>
       </c>
       <c r="G167" t="n">
-        <v>8.83997058868408</v>
+        <v>8.8399715423584</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.51583194732666</v>
       </c>
       <c r="G168" t="n">
-        <v>8.94678401947021</v>
+        <v>8.94678497314453</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.33522605895996</v>
       </c>
       <c r="G169" t="n">
-        <v>8.77697944641113</v>
+        <v>8.77697849273682</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.48573112487793</v>
       </c>
       <c r="G170" t="n">
-        <v>8.91848278045654</v>
+        <v>8.91848373413086</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G171" t="n">
-        <v>8.99243068695068</v>
+        <v>8.992431640625</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.75858306884766</v>
       </c>
       <c r="G172" t="n">
-        <v>9.17501926422119</v>
+        <v>9.17502021789551</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.92753791809082</v>
       </c>
       <c r="G175" t="n">
-        <v>9.33386993408203</v>
+        <v>9.33387088775635</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G177" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G178" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G179" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>10.2440853118896</v>
       </c>
       <c r="G180" t="n">
-        <v>9.63148880004883</v>
+        <v>9.63149070739746</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G181" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>10.1372737884521</v>
       </c>
       <c r="G182" t="n">
-        <v>9.53106594085693</v>
+        <v>9.5310640335083</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.1897087097168</v>
       </c>
       <c r="G183" t="n">
-        <v>9.58036327362061</v>
+        <v>9.58036422729492</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G185" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>10.1625204086304</v>
       </c>
       <c r="G186" t="n">
-        <v>9.55480003356934</v>
+        <v>9.55480098724365</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>10.0304641723633</v>
       </c>
       <c r="G187" t="n">
-        <v>9.43064022064209</v>
+        <v>9.43064212799072</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G188" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>9.99939155578613</v>
       </c>
       <c r="G191" t="n">
-        <v>9.40142631530762</v>
+        <v>9.40142822265625</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.8595666885376</v>
       </c>
       <c r="G192" t="n">
-        <v>9.26996421813965</v>
+        <v>9.26996517181396</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G194" t="n">
-        <v>8.99243068695068</v>
+        <v>8.992431640625</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.66148281097412</v>
       </c>
       <c r="G196" t="n">
-        <v>9.08372497558594</v>
+        <v>9.08372688293457</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.66536712646484</v>
       </c>
       <c r="G197" t="n">
-        <v>9.08737850189209</v>
+        <v>9.08737754821777</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.44786167144775</v>
       </c>
       <c r="G199" t="n">
-        <v>8.88287925720215</v>
+        <v>8.88287830352783</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.03033065795898</v>
       </c>
       <c r="G200" t="n">
-        <v>8.49031639099121</v>
+        <v>8.49031734466553</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.25657367706299</v>
       </c>
       <c r="G203" t="n">
-        <v>8.70303058624268</v>
+        <v>8.70302963256836</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.5935115814209</v>
       </c>
       <c r="G204" t="n">
-        <v>9.01981735229492</v>
+        <v>9.01982021331787</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>9.51680278778076</v>
       </c>
       <c r="G205" t="n">
-        <v>8.9476957321167</v>
+        <v>8.94769763946533</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>9.71003341674805</v>
       </c>
       <c r="G208" t="n">
-        <v>9.12937259674072</v>
+        <v>9.12937355041504</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.62264347076416</v>
       </c>
       <c r="G211" t="n">
-        <v>9.04721069335938</v>
+        <v>9.04720783233643</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.66148281097412</v>
       </c>
       <c r="G212" t="n">
-        <v>9.08372497558594</v>
+        <v>9.08372688293457</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>9.9236536026001</v>
       </c>
       <c r="G215" t="n">
-        <v>9.33021831512451</v>
+        <v>9.33021926879883</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G216" t="n">
-        <v>9.67713451385498</v>
+        <v>9.67713356018066</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.0790138244629</v>
       </c>
       <c r="G218" t="n">
-        <v>9.47628784179688</v>
+        <v>9.47628879547119</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.3120546340942</v>
       </c>
       <c r="G219" t="n">
-        <v>9.69539260864258</v>
+        <v>9.69539451599121</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.234375</v>
       </c>
       <c r="G220" t="n">
-        <v>9.62236022949219</v>
+        <v>9.62235832214355</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G221" t="n">
-        <v>9.84146308898926</v>
+        <v>9.84146404266357</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>10.3120546340942</v>
       </c>
       <c r="G222" t="n">
-        <v>9.69539260864258</v>
+        <v>9.69539451599121</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G223" t="n">
-        <v>9.93275737762451</v>
+        <v>9.93275833129883</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G224" t="n">
-        <v>9.98753452301025</v>
+        <v>9.98753261566162</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G226" t="n">
-        <v>9.98753452301025</v>
+        <v>9.98753261566162</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G227" t="n">
-        <v>9.85972499847412</v>
+        <v>9.85972309112549</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G229" t="n">
-        <v>9.75016975402832</v>
+        <v>9.75017070770264</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G232" t="n">
-        <v>9.87798309326172</v>
+        <v>9.8779821395874</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G236" t="n">
-        <v>9.71365070343018</v>
+        <v>9.71365451812744</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G237" t="n">
-        <v>9.76842975616455</v>
+        <v>9.76842880249023</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.4285745620728</v>
       </c>
       <c r="G238" t="n">
-        <v>9.80494403839111</v>
+        <v>9.80494594573975</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G242" t="n">
-        <v>10.0970869064331</v>
+        <v>10.0970849990845</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G243" t="n">
-        <v>9.87798309326172</v>
+        <v>9.8779821395874</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G244" t="n">
-        <v>10.2431554794312</v>
+        <v>10.2431573867798</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>10.6033563613892</v>
       </c>
       <c r="G245" t="n">
-        <v>9.96927452087402</v>
+        <v>9.96927547454834</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G246" t="n">
-        <v>9.85972499847412</v>
+        <v>9.85972309112549</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>10.4285745620728</v>
       </c>
       <c r="G247" t="n">
-        <v>9.80494403839111</v>
+        <v>9.80494594573975</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G248" t="n">
-        <v>9.93275737762451</v>
+        <v>9.93275833129883</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G249" t="n">
-        <v>9.95101547241211</v>
+        <v>9.95101642608643</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>11.1082782745361</v>
       </c>
       <c r="G251" t="n">
-        <v>10.4440031051636</v>
+        <v>10.4440021514893</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>11.2053775787354</v>
       </c>
       <c r="G252" t="n">
-        <v>10.5352954864502</v>
+        <v>10.5352964401245</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>11.2636375427246</v>
       </c>
       <c r="G253" t="n">
-        <v>10.5900716781616</v>
+        <v>10.5900726318359</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>11.3413181304932</v>
       </c>
       <c r="G254" t="n">
-        <v>10.6631059646606</v>
+        <v>10.6631078720093</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>11.0111770629883</v>
       </c>
       <c r="G255" t="n">
-        <v>10.3527097702026</v>
+        <v>10.352707862854</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>11.0694379806519</v>
       </c>
       <c r="G256" t="n">
-        <v>10.4074840545654</v>
+        <v>10.4074850082397</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G258" t="n">
-        <v>10.2614145278931</v>
+        <v>10.2614135742188</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G259" t="n">
-        <v>9.95101547241211</v>
+        <v>9.95101642608643</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G260" t="n">
-        <v>9.91449737548828</v>
+        <v>9.9144983291626</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G264" t="n">
-        <v>9.87614345550537</v>
+        <v>9.87614440917969</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G265" t="n">
-        <v>9.82086753845215</v>
+        <v>9.82086944580078</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G271" t="n">
-        <v>10.1341028213501</v>
+        <v>10.1341037750244</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G272" t="n">
-        <v>10.1525297164917</v>
+        <v>10.1525278091431</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G273" t="n">
-        <v>10.1341028213501</v>
+        <v>10.1341037750244</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G274" t="n">
-        <v>10.023549079895</v>
+        <v>10.0235500335693</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G275" t="n">
-        <v>10.023549079895</v>
+        <v>10.0235500335693</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G276" t="n">
-        <v>9.83929252624512</v>
+        <v>9.83929443359375</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G279" t="n">
-        <v>10.1341028213501</v>
+        <v>10.1341037750244</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G280" t="n">
-        <v>10.1525297164917</v>
+        <v>10.1525278091431</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G281" t="n">
-        <v>9.82086753845215</v>
+        <v>9.82086944580078</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G282" t="n">
-        <v>9.67346382141113</v>
+        <v>9.67346286773682</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G283" t="n">
-        <v>9.87614345550537</v>
+        <v>9.87614440917969</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G284" t="n">
-        <v>9.82086753845215</v>
+        <v>9.82086944580078</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G288" t="n">
-        <v>10.3367853164673</v>
+        <v>10.3367862701416</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3552122116089</v>
+        <v>10.3552112579346</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>10.8752374649048</v>
       </c>
       <c r="G290" t="n">
-        <v>10.3183622360229</v>
+        <v>10.3183603286743</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G291" t="n">
-        <v>10.3367853164673</v>
+        <v>10.3367862701416</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>10.8558168411255</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2999353408813</v>
+        <v>10.2999334335327</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G294" t="n">
-        <v>9.76559162139893</v>
+        <v>9.76559066772461</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G296" t="n">
-        <v>10.3367853164673</v>
+        <v>10.3367862701416</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G297" t="n">
-        <v>9.9682731628418</v>
+        <v>9.96827411651611</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G300" t="n">
-        <v>9.67346382141113</v>
+        <v>9.67346286773682</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G302" t="n">
-        <v>9.83929252624512</v>
+        <v>9.83929443359375</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G304" t="n">
-        <v>10.0419759750366</v>
+        <v>10.0419769287109</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G305" t="n">
-        <v>10.1341028213501</v>
+        <v>10.1341037750244</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10.253794670105</v>
       </c>
       <c r="G306" t="n">
-        <v>9.72874069213867</v>
+        <v>9.72873878479004</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G310" t="n">
-        <v>10.189380645752</v>
+        <v>10.1893796920776</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G311" t="n">
-        <v>10.189380645752</v>
+        <v>10.1893796920776</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>10.8752374649048</v>
       </c>
       <c r="G312" t="n">
-        <v>10.3183622360229</v>
+        <v>10.3183603286743</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G314" t="n">
-        <v>10.7790021896362</v>
+        <v>10.7790012359619</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G315" t="n">
-        <v>10.4104871749878</v>
+        <v>10.4104881286621</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G316" t="n">
-        <v>10.1525297164917</v>
+        <v>10.1525278091431</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>11.6908798217773</v>
       </c>
       <c r="G318" t="n">
-        <v>11.0922374725342</v>
+        <v>11.0922365188599</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>11.943341255188</v>
       </c>
       <c r="G320" t="n">
-        <v>11.3317728042603</v>
+        <v>11.3317708969116</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>11.943341255188</v>
       </c>
       <c r="G321" t="n">
-        <v>11.3317728042603</v>
+        <v>11.3317708969116</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G322" t="n">
-        <v>11.4607496261597</v>
+        <v>11.460750579834</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>12.0598611831665</v>
       </c>
       <c r="G324" t="n">
-        <v>11.4423246383667</v>
+        <v>11.4423236846924</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G327" t="n">
-        <v>11.884539604187</v>
+        <v>11.8845405578613</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G328" t="n">
-        <v>12.0687980651855</v>
+        <v>12.0687971115112</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G329" t="n">
-        <v>12.0687980651855</v>
+        <v>12.0687971115112</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>13.186224937439</v>
       </c>
       <c r="G332" t="n">
-        <v>12.5110120773315</v>
+        <v>12.5110130310059</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>12.0210208892822</v>
       </c>
       <c r="G339" t="n">
-        <v>11.4054727554321</v>
+        <v>11.4054737091064</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G341" t="n">
-        <v>11.4607496261597</v>
+        <v>11.460750579834</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>12.4871015548706</v>
       </c>
       <c r="G344" t="n">
-        <v>11.8476886749268</v>
+        <v>11.8476877212524</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>12.681303024292</v>
       </c>
       <c r="G345" t="n">
-        <v>12.0319452285767</v>
+        <v>12.031946182251</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G346" t="n">
-        <v>11.884539604187</v>
+        <v>11.8845405578613</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G351" t="n">
-        <v>12.4373092651367</v>
+        <v>12.4373111724854</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>13.2833251953125</v>
       </c>
       <c r="G352" t="n">
-        <v>12.6031398773193</v>
+        <v>12.6031408309937</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>13.5940456390381</v>
       </c>
       <c r="G353" t="n">
-        <v>12.8979511260986</v>
+        <v>12.89794921875</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G354" t="n">
-        <v>13.1743335723877</v>
+        <v>13.1743354797363</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>13.9824476242065</v>
       </c>
       <c r="G355" t="n">
-        <v>13.2664632797241</v>
+        <v>13.2664642333984</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>14.7204103469849</v>
       </c>
       <c r="G357" t="n">
-        <v>13.9666376113892</v>
+        <v>13.9666395187378</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>14.0989675521851</v>
       </c>
       <c r="G359" t="n">
-        <v>13.3770170211792</v>
+        <v>13.3770160675049</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.8270874023438</v>
       </c>
       <c r="G360" t="n">
-        <v>13.1190576553345</v>
+        <v>13.1190595626831</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G361" t="n">
-        <v>13.026930809021</v>
+        <v>13.0269298553467</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G362" t="n">
-        <v>13.026930809021</v>
+        <v>13.0269298553467</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>12.9726037979126</v>
       </c>
       <c r="G363" t="n">
-        <v>12.30832862854</v>
+        <v>12.3083295822144</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G364" t="n">
-        <v>12.2714796066284</v>
+        <v>12.2714776992798</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>12.9920244216919</v>
       </c>
       <c r="G366" t="n">
-        <v>12.326756477356</v>
+        <v>12.3267555236816</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G370" t="n">
-        <v>12.1240739822388</v>
+        <v>12.1240720748901</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G372" t="n">
-        <v>12.4373092651367</v>
+        <v>12.4373111724854</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>15.2835922241211</v>
       </c>
       <c r="G373" t="n">
-        <v>14.5009813308716</v>
+        <v>14.5009822845459</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>14.5650501251221</v>
       </c>
       <c r="G374" t="n">
-        <v>13.8192338943481</v>
+        <v>13.8192329406738</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G376" t="n">
-        <v>13.0822076797485</v>
+        <v>13.0822067260742</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G377" t="n">
-        <v>12.7689714431763</v>
+        <v>12.768970489502</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>13.3027448654175</v>
       </c>
       <c r="G378" t="n">
-        <v>12.6215658187866</v>
+        <v>12.6215648651123</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G379" t="n">
-        <v>12.4373092651367</v>
+        <v>12.4373111724854</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G380" t="n">
-        <v>12.4741592407227</v>
+        <v>12.4741611480713</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G381" t="n">
-        <v>12.2899045944214</v>
+        <v>12.2899055480957</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G382" t="n">
-        <v>12.2899045944214</v>
+        <v>12.2899055480957</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G383" t="n">
-        <v>12.4373092651367</v>
+        <v>12.4373111724854</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>13.4969463348389</v>
       </c>
       <c r="G387" t="n">
-        <v>12.8058233261108</v>
+        <v>12.8058214187622</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>13.7105674743652</v>
       </c>
       <c r="G388" t="n">
-        <v>13.0085048675537</v>
+        <v>13.008505821228</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G389" t="n">
-        <v>13.1743335723877</v>
+        <v>13.1743354797363</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>13.6911468505859</v>
       </c>
       <c r="G390" t="n">
-        <v>12.9900789260864</v>
+        <v>12.9900779724121</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G393" t="n">
-        <v>13.0822076797485</v>
+        <v>13.0822067260742</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G394" t="n">
-        <v>12.7689714431763</v>
+        <v>12.768970489502</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G395" t="n">
-        <v>13.1743335723877</v>
+        <v>13.1743354797363</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>13.6717262268066</v>
       </c>
       <c r="G396" t="n">
-        <v>12.9716529846191</v>
+        <v>12.9716520309448</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>13.2444849014282</v>
       </c>
       <c r="G397" t="n">
-        <v>12.5662889480591</v>
+        <v>12.5662899017334</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>12.8949241638184</v>
       </c>
       <c r="G398" t="n">
-        <v>12.2346277236938</v>
+        <v>12.2346267700195</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G401" t="n">
-        <v>12.3451824188232</v>
+        <v>12.3451814651489</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G402" t="n">
-        <v>12.3451824188232</v>
+        <v>12.3451814651489</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G403" t="n">
-        <v>12.4373092651367</v>
+        <v>12.4373111724854</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G404" t="n">
-        <v>12.3451824188232</v>
+        <v>12.3451814651489</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G406" t="n">
-        <v>12.0687980651855</v>
+        <v>12.0687971115112</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G408" t="n">
-        <v>11.884539604187</v>
+        <v>11.8845405578613</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>12.4871015548706</v>
       </c>
       <c r="G409" t="n">
-        <v>11.8476886749268</v>
+        <v>11.8476877212524</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>12.4094219207764</v>
       </c>
       <c r="G410" t="n">
-        <v>11.7739849090576</v>
+        <v>11.7739858627319</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G413" t="n">
-        <v>10.9448328018188</v>
+        <v>10.9448318481445</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>11.6131992340088</v>
       </c>
       <c r="G414" t="n">
-        <v>11.0185346603394</v>
+        <v>11.0185356140137</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G416" t="n">
-        <v>10.7790021896362</v>
+        <v>10.7790012359619</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>11.2636375427246</v>
       </c>
       <c r="G418" t="n">
-        <v>10.6868715286255</v>
+        <v>10.6868724822998</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G419" t="n">
-        <v>10.9448328018188</v>
+        <v>10.9448318481445</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G420" t="n">
-        <v>11.2396421432495</v>
+        <v>11.2396430969238</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G421" t="n">
-        <v>11.2396421432495</v>
+        <v>11.2396430969238</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G424" t="n">
-        <v>11.1475143432617</v>
+        <v>11.1475133895874</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G425" t="n">
-        <v>11.2396421432495</v>
+        <v>11.2396430969238</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G426" t="n">
-        <v>11.2396421432495</v>
+        <v>11.2396430969238</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G427" t="n">
-        <v>11.2396421432495</v>
+        <v>11.2396430969238</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G428" t="n">
-        <v>11.1475143432617</v>
+        <v>11.1475133895874</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>11.9045000076294</v>
       </c>
       <c r="G430" t="n">
-        <v>11.2949199676514</v>
+        <v>11.2949190139771</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G433" t="n">
-        <v>10.4104871749878</v>
+        <v>10.4104881286621</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G434" t="n">
-        <v>10.7790021896362</v>
+        <v>10.7790012359619</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G438" t="n">
-        <v>10.3552122116089</v>
+        <v>10.3552112579346</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G439" t="n">
-        <v>10.3367853164673</v>
+        <v>10.3367862701416</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G440" t="n">
-        <v>10.023549079895</v>
+        <v>10.0235500335693</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G442" t="n">
-        <v>9.67346382141113</v>
+        <v>9.67346286773682</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.30221080780029</v>
       </c>
       <c r="G445" t="n">
-        <v>8.82588195800781</v>
+        <v>8.8258810043335</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.22453117370605</v>
       </c>
       <c r="G449" t="n">
-        <v>8.75218200683594</v>
+        <v>8.7521800994873</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>8.58366870880127</v>
       </c>
       <c r="G452" t="n">
-        <v>8.14413452148438</v>
+        <v>8.14413547515869</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G453" t="n">
-        <v>8.47579479217529</v>
+        <v>8.47579574584961</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>10.0984344482422</v>
       </c>
       <c r="G455" t="n">
-        <v>9.58133602142334</v>
+        <v>9.58133411407471</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>11.2247982025146</v>
       </c>
       <c r="G458" t="n">
-        <v>10.6500215530396</v>
+        <v>10.6500225067139</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G460" t="n">
-        <v>10.1341028213501</v>
+        <v>10.1341037750244</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G462" t="n">
-        <v>10.1341028213501</v>
+        <v>10.1341037750244</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>10.7781372070312</v>
       </c>
       <c r="G463" t="n">
-        <v>10.2262315750122</v>
+        <v>10.2262334823608</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G465" t="n">
-        <v>9.76559162139893</v>
+        <v>9.76559066772461</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G468" t="n">
-        <v>9.94984817504883</v>
+        <v>9.94984912872314</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>11.2053775787354</v>
       </c>
       <c r="G469" t="n">
-        <v>10.6315956115723</v>
+        <v>10.6315965652466</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>13.0697040557861</v>
       </c>
       <c r="G476" t="n">
-        <v>12.4004583358765</v>
+        <v>12.4004573822021</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G477" t="n">
-        <v>12.4741592407227</v>
+        <v>12.4741611480713</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G479" t="n">
-        <v>12.3451824188232</v>
+        <v>12.3451814651489</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G480" t="n">
-        <v>12.2714796066284</v>
+        <v>12.2714776992798</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G484" t="n">
-        <v>12.1240739822388</v>
+        <v>12.1240720748901</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G486" t="n">
-        <v>12.4373092651367</v>
+        <v>12.4373111724854</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G487" t="n">
-        <v>12.4373092651367</v>
+        <v>12.4373111724854</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G488" t="n">
-        <v>13.0822076797485</v>
+        <v>13.0822067260742</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G491" t="n">
-        <v>13.026930809021</v>
+        <v>13.0269298553467</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G493" t="n">
-        <v>14.7957916259766</v>
+        <v>14.7957906723022</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>15.633152961731</v>
       </c>
       <c r="G495" t="n">
-        <v>14.8326435089111</v>
+        <v>14.8326425552368</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>16.7206764221191</v>
       </c>
       <c r="G499" t="n">
-        <v>15.8644790649414</v>
+        <v>15.8644781112671</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G500" t="n">
-        <v>15.293285369873</v>
+        <v>15.2932834625244</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>15.3030118942261</v>
       </c>
       <c r="G502" t="n">
-        <v>14.5194072723389</v>
+        <v>14.5194063186646</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>15.1476516723633</v>
       </c>
       <c r="G503" t="n">
-        <v>14.3720026016235</v>
+        <v>14.3720035552979</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G504" t="n">
-        <v>13.9482107162476</v>
+        <v>13.9482116699219</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G505" t="n">
-        <v>13.9482107162476</v>
+        <v>13.9482116699219</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>14.4485292434692</v>
       </c>
       <c r="G507" t="n">
-        <v>13.7086801528931</v>
+        <v>13.7086791992188</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>14.4679489135742</v>
       </c>
       <c r="G508" t="n">
-        <v>13.727105140686</v>
+        <v>13.7271041870117</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>14.3125886917114</v>
       </c>
       <c r="G509" t="n">
-        <v>13.5797004699707</v>
+        <v>13.5796995162964</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>14.7398300170898</v>
       </c>
       <c r="G510" t="n">
-        <v>13.9850635528564</v>
+        <v>13.9850625991821</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>15.128231048584</v>
       </c>
       <c r="G514" t="n">
-        <v>14.4609594345093</v>
+        <v>14.460958480835</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>15.4777927398682</v>
       </c>
       <c r="G516" t="n">
-        <v>14.7951011657715</v>
+        <v>14.7951021194458</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>15.3418521881104</v>
       </c>
       <c r="G518" t="n">
-        <v>14.6651563644409</v>
+        <v>14.6651582717896</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>15.5748929977417</v>
       </c>
       <c r="G519" t="n">
-        <v>14.8879194259644</v>
+        <v>14.8879203796387</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G522" t="n">
-        <v>15.129246711731</v>
+        <v>15.1292448043823</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>16.0215549468994</v>
       </c>
       <c r="G523" t="n">
-        <v>15.3148803710938</v>
+        <v>15.3148822784424</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>15.1864919662476</v>
       </c>
       <c r="G526" t="n">
-        <v>14.5166511535645</v>
+        <v>14.5166501998901</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G528" t="n">
-        <v>14.9807376861572</v>
+        <v>14.9807367324829</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G529" t="n">
-        <v>14.813666343689</v>
+        <v>14.8136653900146</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>15.2253322601318</v>
       </c>
       <c r="G530" t="n">
-        <v>14.5537776947021</v>
+        <v>14.5537757873535</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G532" t="n">
-        <v>14.8322286605835</v>
+        <v>14.8322296142578</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G534" t="n">
-        <v>15.129246711731</v>
+        <v>15.1292448043823</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G535" t="n">
-        <v>15.129246711731</v>
+        <v>15.1292448043823</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G537" t="n">
-        <v>15.2963161468506</v>
+        <v>15.2963171005249</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G538" t="n">
-        <v>14.813666343689</v>
+        <v>14.8136653900146</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G539" t="n">
-        <v>14.8507928848267</v>
+        <v>14.8507919311523</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>15.0505514144897</v>
       </c>
       <c r="G540" t="n">
-        <v>14.3867053985596</v>
+        <v>14.3867063522339</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>15.0505514144897</v>
       </c>
       <c r="G541" t="n">
-        <v>14.3867053985596</v>
+        <v>14.3867063522339</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G543" t="n">
-        <v>14.8507928848267</v>
+        <v>14.8507919311523</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G544" t="n">
-        <v>14.8322286605835</v>
+        <v>14.8322296142578</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G546" t="n">
-        <v>16.0574207305908</v>
+        <v>16.0574169158936</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G547" t="n">
-        <v>16.8556499481201</v>
+        <v>16.8556518554688</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>17.536319732666</v>
       </c>
       <c r="G551" t="n">
-        <v>16.7628288269043</v>
+        <v>16.7628307342529</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>18.1189212799072</v>
       </c>
       <c r="G552" t="n">
-        <v>17.3197364807129</v>
+        <v>17.3197345733643</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>18.0995025634766</v>
       </c>
       <c r="G553" t="n">
-        <v>17.3011741638184</v>
+        <v>17.301176071167</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G554" t="n">
-        <v>17.2826118469238</v>
+        <v>17.2826099395752</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G555" t="n">
-        <v>17.6724433898926</v>
+        <v>17.6724452972412</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G556" t="n">
-        <v>17.895206451416</v>
+        <v>17.8952026367188</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>18.9928245544434</v>
       </c>
       <c r="G558" t="n">
-        <v>18.1550960540771</v>
+        <v>18.1550941467285</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G560" t="n">
-        <v>17.542501449585</v>
+        <v>17.5424995422363</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G562" t="n">
-        <v>17.8766403198242</v>
+        <v>17.8766422271729</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G563" t="n">
-        <v>18.5634899139404</v>
+        <v>18.5634937286377</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G564" t="n">
-        <v>19.0275764465332</v>
+        <v>19.0275802612305</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G565" t="n">
-        <v>18.2107810974121</v>
+        <v>18.2107849121094</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G566" t="n">
-        <v>18.5634899139404</v>
+        <v>18.5634937286377</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G567" t="n">
-        <v>17.6724433898926</v>
+        <v>17.6724452972412</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G568" t="n">
-        <v>18.0994033813477</v>
+        <v>18.0994052886963</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G569" t="n">
-        <v>17.9137687683105</v>
+        <v>17.9137706756592</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G570" t="n">
-        <v>17.264045715332</v>
+        <v>17.2640476226807</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>18.6626834869385</v>
       </c>
       <c r="G571" t="n">
-        <v>17.8395156860352</v>
+        <v>17.8395137786865</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G572" t="n">
-        <v>17.3568649291992</v>
+        <v>17.3568668365479</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>16.4487953186035</v>
       </c>
       <c r="G576" t="n">
-        <v>15.7232761383057</v>
+        <v>15.7232780456543</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G577" t="n">
-        <v>16.354434967041</v>
+        <v>16.3544330596924</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G582" t="n">
-        <v>16.4843826293945</v>
+        <v>16.4843788146973</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>16.9342975616455</v>
       </c>
       <c r="G583" t="n">
-        <v>16.1873645782471</v>
+        <v>16.1873626708984</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G585" t="n">
-        <v>16.1688041687012</v>
+        <v>16.1688003540039</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>17.5168991088867</v>
       </c>
       <c r="G586" t="n">
-        <v>16.7442665100098</v>
+        <v>16.7442684173584</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>17.1479187011719</v>
       </c>
       <c r="G589" t="n">
-        <v>16.3915615081787</v>
+        <v>16.3915634155273</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G590" t="n">
-        <v>16.2616214752197</v>
+        <v>16.2616195678711</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G591" t="n">
-        <v>16.2616214752197</v>
+        <v>16.2616195678711</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G595" t="n">
-        <v>16.5771999359131</v>
+        <v>16.5771980285645</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G597" t="n">
-        <v>16.5029430389404</v>
+        <v>16.5029449462891</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G598" t="n">
-        <v>16.6514492034912</v>
+        <v>16.6514530181885</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G599" t="n">
-        <v>16.7071418762207</v>
+        <v>16.7071437835693</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G600" t="n">
-        <v>16.4843826293945</v>
+        <v>16.4843788146973</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>17.4586391448975</v>
       </c>
       <c r="G601" t="n">
-        <v>16.6885776519775</v>
+        <v>16.6885795593262</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G607" t="n">
-        <v>14.8507928848267</v>
+        <v>14.8507919311523</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G608" t="n">
-        <v>14.8507928848267</v>
+        <v>14.8507919311523</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G610" t="n">
-        <v>14.9807376861572</v>
+        <v>14.9807367324829</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>15.108811378479</v>
       </c>
       <c r="G611" t="n">
-        <v>14.4423952102661</v>
+        <v>14.4423961639404</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>18.0024013519287</v>
       </c>
       <c r="G612" t="n">
-        <v>17.2083568572998</v>
+        <v>17.2083549499512</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G613" t="n">
-        <v>16.4101257324219</v>
+        <v>16.4101276397705</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G614" t="n">
-        <v>16.4101257324219</v>
+        <v>16.4101276397705</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G617" t="n">
-        <v>16.1688041687012</v>
+        <v>16.1688003540039</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G618" t="n">
-        <v>15.7789659500122</v>
+        <v>15.7789640426636</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G622" t="n">
-        <v>16.4843826293945</v>
+        <v>16.4843788146973</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G625" t="n">
-        <v>16.8556499481201</v>
+        <v>16.8556518554688</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G628" t="n">
-        <v>16.5029430389404</v>
+        <v>16.5029449462891</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G630" t="n">
-        <v>16.5029430389404</v>
+        <v>16.5029449462891</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G634" t="n">
-        <v>16.837085723877</v>
+        <v>16.8370876312256</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>17.7499408721924</v>
       </c>
       <c r="G635" t="n">
-        <v>16.9670295715332</v>
+        <v>16.9670314788818</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G636" t="n">
-        <v>16.354434967041</v>
+        <v>16.3544330596924</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G637" t="n">
-        <v>16.5400714874268</v>
+        <v>16.5400733947754</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G638" t="n">
-        <v>16.7999572753906</v>
+        <v>16.7999591827393</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G640" t="n">
-        <v>16.7071418762207</v>
+        <v>16.7071437835693</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G642" t="n">
-        <v>16.354434967041</v>
+        <v>16.3544330596924</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G643" t="n">
-        <v>16.7071418762207</v>
+        <v>16.7071437835693</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G644" t="n">
-        <v>17.2826118469238</v>
+        <v>17.2826099395752</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G646" t="n">
-        <v>17.7838249206543</v>
+        <v>17.7838230133057</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>18.7986240386963</v>
       </c>
       <c r="G647" t="n">
-        <v>17.96946144104</v>
+        <v>17.9694595336914</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G648" t="n">
-        <v>18.414981842041</v>
+        <v>18.4149837493896</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G649" t="n">
-        <v>17.8023853302002</v>
+        <v>17.8023872375488</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>18.7597846984863</v>
       </c>
       <c r="G650" t="n">
-        <v>17.932336807251</v>
+        <v>17.9323310852051</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G651" t="n">
-        <v>16.7999572753906</v>
+        <v>16.7999591827393</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G652" t="n">
-        <v>16.5771999359131</v>
+        <v>16.5771980285645</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G653" t="n">
-        <v>16.5400714874268</v>
+        <v>16.5400733947754</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>17.4003791809082</v>
       </c>
       <c r="G656" t="n">
-        <v>16.6328868865967</v>
+        <v>16.6328887939453</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G657" t="n">
-        <v>16.7071418762207</v>
+        <v>16.7071437835693</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G660" t="n">
-        <v>16.5029430389404</v>
+        <v>16.5029449462891</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>17.2061786651611</v>
       </c>
       <c r="G662" t="n">
-        <v>16.4472522735596</v>
+        <v>16.4472541809082</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G668" t="n">
-        <v>16.1688041687012</v>
+        <v>16.1688003540039</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G669" t="n">
-        <v>15.7789659500122</v>
+        <v>15.7789640426636</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>16.9537181854248</v>
       </c>
       <c r="G670" t="n">
-        <v>16.2059288024902</v>
+        <v>16.2059268951416</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G671" t="n">
-        <v>16.2616214752197</v>
+        <v>16.2616195678711</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G672" t="n">
-        <v>16.7999572753906</v>
+        <v>16.7999591827393</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>16.9537181854248</v>
       </c>
       <c r="G678" t="n">
-        <v>16.2059288024902</v>
+        <v>16.2059268951416</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>17.2061786651611</v>
       </c>
       <c r="G679" t="n">
-        <v>16.4472522735596</v>
+        <v>16.4472541809082</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>16.4682159423828</v>
       </c>
       <c r="G683" t="n">
-        <v>15.7418403625488</v>
+        <v>15.7418384552002</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>16.3711166381836</v>
       </c>
       <c r="G686" t="n">
-        <v>15.6490240097046</v>
+        <v>15.6490230560303</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>16.9342975616455</v>
       </c>
       <c r="G688" t="n">
-        <v>16.1873645782471</v>
+        <v>16.1873626708984</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>16.6429977416992</v>
       </c>
       <c r="G689" t="n">
-        <v>15.9089136123657</v>
+        <v>15.9089107513428</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>16.5264759063721</v>
       </c>
       <c r="G690" t="n">
-        <v>15.7975292205811</v>
+        <v>15.7975301742554</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>16.6041564941406</v>
       </c>
       <c r="G691" t="n">
-        <v>15.8717861175537</v>
+        <v>15.8717823028564</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>15.9632940292358</v>
       </c>
       <c r="G692" t="n">
-        <v>15.2591896057129</v>
+        <v>15.2591886520386</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G693" t="n">
-        <v>14.8322286605835</v>
+        <v>14.8322296142578</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G694" t="n">
-        <v>14.4238328933716</v>
+        <v>14.4238319396973</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>14.7204103469849</v>
       </c>
       <c r="G695" t="n">
-        <v>14.0711259841919</v>
+        <v>14.0711269378662</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>15.3418521881104</v>
       </c>
       <c r="G696" t="n">
-        <v>14.6651563644409</v>
+        <v>14.6651582717896</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G697" t="n">
-        <v>14.4238328933716</v>
+        <v>14.4238319396973</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>15.4389533996582</v>
       </c>
       <c r="G698" t="n">
-        <v>14.7579755783081</v>
+        <v>14.7579765319824</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G699" t="n">
-        <v>14.813666343689</v>
+        <v>14.8136653900146</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G701" t="n">
-        <v>15.4076986312866</v>
+        <v>15.407696723938</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G706" t="n">
-        <v>15.4076986312866</v>
+        <v>15.407696723938</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>16.0798149108887</v>
       </c>
       <c r="G707" t="n">
-        <v>15.3705711364746</v>
+        <v>15.3705701828003</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G711" t="n">
-        <v>15.760404586792</v>
+        <v>15.7604055404663</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>16.856616973877</v>
       </c>
       <c r="G712" t="n">
-        <v>16.113109588623</v>
+        <v>16.1131076812744</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G714" t="n">
-        <v>16.5771999359131</v>
+        <v>16.5771980285645</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G715" t="n">
-        <v>16.985595703125</v>
+        <v>16.9855976104736</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G717" t="n">
-        <v>17.8209533691406</v>
+        <v>17.820951461792</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G718" t="n">
-        <v>17.542501449585</v>
+        <v>17.5424995422363</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G719" t="n">
-        <v>17.542501449585</v>
+        <v>17.5424995422363</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G722" t="n">
-        <v>18.0065860748291</v>
+        <v>18.0065879821777</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G723" t="n">
-        <v>17.8209533691406</v>
+        <v>17.820951461792</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G725" t="n">
-        <v>17.8209533691406</v>
+        <v>17.820951461792</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>18.779203414917</v>
       </c>
       <c r="G727" t="n">
-        <v>17.9508972167969</v>
+        <v>17.9508934020996</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G729" t="n">
-        <v>17.264045715332</v>
+        <v>17.2640476226807</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>17.8470401763916</v>
       </c>
       <c r="G730" t="n">
-        <v>17.0598468780518</v>
+        <v>17.0598487854004</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G731" t="n">
-        <v>16.985595703125</v>
+        <v>16.9855976104736</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G732" t="n">
-        <v>17.2826118469238</v>
+        <v>17.2826099395752</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>18.293701171875</v>
       </c>
       <c r="G734" t="n">
-        <v>17.4868068695068</v>
+        <v>17.4868087768555</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>18.4490623474121</v>
       </c>
       <c r="G735" t="n">
-        <v>17.6353187561035</v>
+        <v>17.6353149414062</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G737" t="n">
-        <v>19.5844821929932</v>
+        <v>19.5844860076904</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G738" t="n">
-        <v>19.6773014068604</v>
+        <v>19.6772994995117</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G739" t="n">
-        <v>19.3060340881348</v>
+        <v>19.3060302734375</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G743" t="n">
-        <v>20.3270244598389</v>
+        <v>20.3270225524902</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G744" t="n">
-        <v>20.1413879394531</v>
+        <v>20.1413898468018</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G747" t="n">
-        <v>20.1413879394531</v>
+        <v>20.1413898468018</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G748" t="n">
-        <v>20.0949802398682</v>
+        <v>20.0949821472168</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G749" t="n">
-        <v>20.466251373291</v>
+        <v>20.4662494659424</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G750" t="n">
-        <v>20.5126552581787</v>
+        <v>20.5126571655273</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G755" t="n">
-        <v>20.1413879394531</v>
+        <v>20.1413898468018</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G756" t="n">
-        <v>20.466251373291</v>
+        <v>20.4662494659424</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G758" t="n">
-        <v>20.3270244598389</v>
+        <v>20.3270225524902</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G760" t="n">
-        <v>20.0949802398682</v>
+        <v>20.0949821472168</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G761" t="n">
-        <v>19.9557514190674</v>
+        <v>19.9557552337646</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G764" t="n">
-        <v>19.630895614624</v>
+        <v>19.6308917999268</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G765" t="n">
-        <v>19.5844821929932</v>
+        <v>19.5844860076904</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G769" t="n">
-        <v>19.8395595550537</v>
+        <v>19.8395576477051</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G770" t="n">
-        <v>19.6528339385986</v>
+        <v>19.6528358459473</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G771" t="n">
-        <v>19.3260669708252</v>
+        <v>19.3260650634766</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G774" t="n">
-        <v>19.5594730377197</v>
+        <v>19.5594749450684</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G777" t="n">
-        <v>19.0459785461426</v>
+        <v>19.0459804534912</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G780" t="n">
-        <v>19.5127906799316</v>
+        <v>19.512788772583</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>19.6142673492432</v>
       </c>
       <c r="G781" t="n">
-        <v>18.8592510223389</v>
+        <v>18.8592529296875</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G782" t="n">
-        <v>19.6528339385986</v>
+        <v>19.6528358459473</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>20.8280200958252</v>
       </c>
       <c r="G783" t="n">
-        <v>20.0262832641602</v>
+        <v>20.0262851715088</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G785" t="n">
-        <v>19.1393394470215</v>
+        <v>19.1393413543701</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G786" t="n">
-        <v>19.0459785461426</v>
+        <v>19.0459804534912</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G789" t="n">
-        <v>18.5044746398926</v>
+        <v>18.5044727325439</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>19.1287651062012</v>
       </c>
       <c r="G792" t="n">
-        <v>18.3924388885498</v>
+        <v>18.3924427032471</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G793" t="n">
-        <v>18.6725273132324</v>
+        <v>18.6725292205811</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G794" t="n">
-        <v>18.6725273132324</v>
+        <v>18.6725292205811</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G795" t="n">
-        <v>18.5231456756592</v>
+        <v>18.5231475830078</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G796" t="n">
-        <v>18.6725273132324</v>
+        <v>18.6725292205811</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G798" t="n">
-        <v>18.6725273132324</v>
+        <v>18.6725292205811</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G800" t="n">
-        <v>19.9329223632812</v>
+        <v>19.9329242706299</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>20.8280200958252</v>
       </c>
       <c r="G802" t="n">
-        <v>20.0262832641602</v>
+        <v>20.0262851715088</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>21.5077228546143</v>
       </c>
       <c r="G803" t="n">
-        <v>20.6798229217529</v>
+        <v>20.6798248291016</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G807" t="n">
-        <v>22.8271656036377</v>
+        <v>22.8271636962891</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G809" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406581878662</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G810" t="n">
-        <v>23.0138912200928</v>
+        <v>23.0138893127441</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G811" t="n">
-        <v>22.9205265045166</v>
+        <v>22.9205284118652</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G812" t="n">
-        <v>23.4340209960938</v>
+        <v>23.4340229034424</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G813" t="n">
-        <v>24.0408821105957</v>
+        <v>24.0408802032471</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G814" t="n">
-        <v>23.6207485198975</v>
+        <v>23.6207466125488</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G815" t="n">
-        <v>23.5740642547607</v>
+        <v>23.5740661621094</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G816" t="n">
-        <v>23.0138912200928</v>
+        <v>23.0138893127441</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G817" t="n">
-        <v>22.8738498687744</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G818" t="n">
-        <v>22.6871223449707</v>
+        <v>22.6871204376221</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G820" t="n">
-        <v>23.0138912200928</v>
+        <v>23.0138893127441</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G821" t="n">
-        <v>23.6207485198975</v>
+        <v>23.6207466125488</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G822" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406581878662</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G823" t="n">
-        <v>23.5740642547607</v>
+        <v>23.5740661621094</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G824" t="n">
-        <v>23.3873424530029</v>
+        <v>23.3873405456543</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G825" t="n">
-        <v>22.8738498687744</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G826" t="n">
-        <v>22.7804851531982</v>
+        <v>22.7804832458496</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G827" t="n">
-        <v>22.8271656036377</v>
+        <v>22.8271636962891</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G829" t="n">
-        <v>23.107250213623</v>
+        <v>23.1072540283203</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G830" t="n">
-        <v>22.8271656036377</v>
+        <v>22.8271636962891</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G831" t="n">
-        <v>22.8271656036377</v>
+        <v>22.8271636962891</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G832" t="n">
-        <v>23.2939796447754</v>
+        <v>23.293981552124</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G833" t="n">
-        <v>22.7804851531982</v>
+        <v>22.7804832458496</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G834" t="n">
-        <v>23.107250213623</v>
+        <v>23.1072540283203</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G835" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406581878662</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G836" t="n">
-        <v>24.0408821105957</v>
+        <v>24.0408802032471</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G837" t="n">
-        <v>23.7141132354736</v>
+        <v>23.714111328125</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G838" t="n">
-        <v>22.8271656036377</v>
+        <v>22.8271636962891</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>22.8671283721924</v>
       </c>
       <c r="G841" t="n">
-        <v>21.9869003295898</v>
+        <v>21.9869022369385</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G845" t="n">
-        <v>20.7731857299805</v>
+        <v>20.7731876373291</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G851" t="n">
-        <v>22.8738498687744</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G854" t="n">
-        <v>24.8344593048096</v>
+        <v>24.8344631195068</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G857" t="n">
-        <v>24.2276058197021</v>
+        <v>24.2276039123535</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G859" t="n">
-        <v>23.4340209960938</v>
+        <v>23.4340229034424</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G862" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406581878662</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G863" t="n">
-        <v>23.3873424530029</v>
+        <v>23.3873405456543</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G864" t="n">
-        <v>23.994197845459</v>
+        <v>23.9941959381104</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G866" t="n">
-        <v>24.1342430114746</v>
+        <v>24.134241104126</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G867" t="n">
-        <v>24.1342430114746</v>
+        <v>24.134241104126</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G868" t="n">
-        <v>23.8074760437012</v>
+        <v>23.8074741363525</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G869" t="n">
-        <v>23.8074760437012</v>
+        <v>23.8074741363525</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>26.2656402587891</v>
       </c>
       <c r="G874" t="n">
-        <v>25.2545928955078</v>
+        <v>25.2545948028564</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G879" t="n">
-        <v>23.6207485198975</v>
+        <v>23.6207466125488</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G882" t="n">
-        <v>22.8738498687744</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G884" t="n">
-        <v>22.1269474029541</v>
+        <v>22.1269454956055</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G885" t="n">
-        <v>22.967212677002</v>
+        <v>22.9672088623047</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G886" t="n">
-        <v>22.1269474029541</v>
+        <v>22.1269454956055</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G887" t="n">
-        <v>22.8271656036377</v>
+        <v>22.8271636962891</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G888" t="n">
-        <v>22.8738498687744</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>25.0518856048584</v>
       </c>
       <c r="G889" t="n">
-        <v>24.0875606536865</v>
+        <v>24.0875625610352</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G891" t="n">
-        <v>24.5543746948242</v>
+        <v>24.5543727874756</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G893" t="n">
-        <v>24.3676509857178</v>
+        <v>24.3676471710205</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G896" t="n">
-        <v>24.3676509857178</v>
+        <v>24.3676471710205</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G897" t="n">
-        <v>22.8738498687744</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G898" t="n">
-        <v>22.8738498687744</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>24.7120342254639</v>
       </c>
       <c r="G900" t="n">
-        <v>23.7607898712158</v>
+        <v>23.7607917785645</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G901" t="n">
-        <v>23.5740642547607</v>
+        <v>23.5740661621094</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G903" t="n">
-        <v>23.8074760437012</v>
+        <v>23.8074741363525</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G904" t="n">
-        <v>24.6944198608398</v>
+        <v>24.6944179534912</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G905" t="n">
-        <v>24.8344593048096</v>
+        <v>24.8344631195068</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G909" t="n">
-        <v>23.8074760437012</v>
+        <v>23.8074741363525</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G910" t="n">
-        <v>23.7141132354736</v>
+        <v>23.714111328125</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>26.0228881835938</v>
       </c>
       <c r="G913" t="n">
-        <v>25.0211849212646</v>
+        <v>25.0211868286133</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G914" t="n">
-        <v>24.9745063781738</v>
+        <v>24.9745044708252</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>25.0518856048584</v>
       </c>
       <c r="G915" t="n">
-        <v>24.0875606536865</v>
+        <v>24.0875625610352</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G918" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406581878662</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G919" t="n">
-        <v>23.4340209960938</v>
+        <v>23.4340229034424</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G920" t="n">
-        <v>22.7804851531982</v>
+        <v>22.7804832458496</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G922" t="n">
-        <v>21.0532760620117</v>
+        <v>21.0532741546631</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G923" t="n">
-        <v>21.2866840362549</v>
+        <v>21.2866802215576</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G924" t="n">
-        <v>20.7731857299805</v>
+        <v>20.7731876373291</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G925" t="n">
-        <v>20.3063716888428</v>
+        <v>20.3063735961914</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G926" t="n">
-        <v>19.8395595550537</v>
+        <v>19.8395576477051</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G934" t="n">
-        <v>21.4734077453613</v>
+        <v>21.4734058380127</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G939" t="n">
-        <v>21.0532760620117</v>
+        <v>21.0532741546631</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G941" t="n">
-        <v>20.1196460723877</v>
+        <v>20.1196479797363</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G942" t="n">
-        <v>20.2130107879639</v>
+        <v>20.2130126953125</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>19.8570175170898</v>
       </c>
       <c r="G943" t="n">
-        <v>19.0926609039307</v>
+        <v>19.092658996582</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G945" t="n">
-        <v>19.7461986541748</v>
+        <v>19.7461967468262</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G947" t="n">
-        <v>19.3260669708252</v>
+        <v>19.3260650634766</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>17.9053001403809</v>
       </c>
       <c r="G950" t="n">
-        <v>17.2160682678223</v>
+        <v>17.2160701751709</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G951" t="n">
-        <v>16.9359817504883</v>
+        <v>16.9359836578369</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G952" t="n">
-        <v>16.7119102478027</v>
+        <v>16.7119140625</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>18.7986240386963</v>
       </c>
       <c r="G954" t="n">
-        <v>18.075008392334</v>
+        <v>18.0750045776367</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G955" t="n">
-        <v>18.5418186187744</v>
+        <v>18.541820526123</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G956" t="n">
-        <v>19.7928791046143</v>
+        <v>19.7928810119629</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G958" t="n">
-        <v>20.3063716888428</v>
+        <v>20.3063735961914</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G959" t="n">
-        <v>20.3063716888428</v>
+        <v>20.3063735961914</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G961" t="n">
-        <v>20.7731857299805</v>
+        <v>20.7731876373291</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G964" t="n">
-        <v>21.5200862884521</v>
+        <v>21.5200881958008</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G968" t="n">
-        <v>23.0138912200928</v>
+        <v>23.0138893127441</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G970" t="n">
-        <v>21.3333625793457</v>
+        <v>21.3333644866943</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G971" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530578613281</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G972" t="n">
-        <v>20.1663303375244</v>
+        <v>20.166332244873</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G976" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530578613281</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G977" t="n">
-        <v>20.1663303375244</v>
+        <v>20.166332244873</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G978" t="n">
-        <v>20.3063716888428</v>
+        <v>20.3063735961914</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G979" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530578613281</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G984" t="n">
-        <v>21.5200862884521</v>
+        <v>21.5200881958008</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G985" t="n">
-        <v>21.4734077453613</v>
+        <v>21.4734058380127</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G988" t="n">
-        <v>21.5200862884521</v>
+        <v>21.5200881958008</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G992" t="n">
-        <v>21.3333625793457</v>
+        <v>21.3333644866943</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G997" t="n">
-        <v>19.1393394470215</v>
+        <v>19.1393413543701</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1002" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530578613281</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G1003" t="n">
-        <v>19.5127906799316</v>
+        <v>19.512788772583</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1005" t="n">
-        <v>19.9329223632812</v>
+        <v>19.9329242706299</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G1006" t="n">
-        <v>19.7461986541748</v>
+        <v>19.7461967468262</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>18.5655822753906</v>
       </c>
       <c r="G1020" t="n">
-        <v>17.8509368896484</v>
+        <v>17.8509330749512</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G1021" t="n">
-        <v>17.7762470245361</v>
+        <v>17.7762489318848</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>17.7887802124023</v>
       </c>
       <c r="G1022" t="n">
-        <v>17.1040344238281</v>
+        <v>17.1040325164795</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.0853633880615</v>
+        <v>17.0853652954102</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G1024" t="n">
-        <v>16.6617584228516</v>
+        <v>16.6617603302002</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G1025" t="n">
-        <v>16.8312034606934</v>
+        <v>16.8312015533447</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G1027" t="n">
-        <v>16.2852230072021</v>
+        <v>16.2852210998535</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G1029" t="n">
-        <v>16.7182426452637</v>
+        <v>16.718240737915</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1034" t="n">
-        <v>18.1490802764893</v>
+        <v>18.1490783691406</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1036" t="n">
-        <v>18.0549430847168</v>
+        <v>18.0549449920654</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G1037" t="n">
-        <v>18.826847076416</v>
+        <v>18.8268489837646</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G1038" t="n">
-        <v>18.5067920684814</v>
+        <v>18.5067901611328</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G1040" t="n">
-        <v>18.6574058532715</v>
+        <v>18.6574039459229</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G1044" t="n">
-        <v>18.5067920684814</v>
+        <v>18.5067901611328</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G1047" t="n">
-        <v>19.7211227416992</v>
+        <v>19.7211246490479</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1050" t="n">
-        <v>20.7095317840576</v>
+        <v>20.7095336914062</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G1052" t="n">
-        <v>20.7565994262695</v>
+        <v>20.7566013336182</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G1053" t="n">
-        <v>20.8978004455566</v>
+        <v>20.8978023529053</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1058" t="n">
-        <v>22.5451507568359</v>
+        <v>22.5451488494873</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1059" t="n">
-        <v>22.5451507568359</v>
+        <v>22.5451488494873</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G1061" t="n">
-        <v>22.3098163604736</v>
+        <v>22.309814453125</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G1064" t="n">
-        <v>21.8862113952637</v>
+        <v>21.886209487915</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G1066" t="n">
-        <v>21.509672164917</v>
+        <v>21.5096740722656</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>21.9446754455566</v>
       </c>
       <c r="G1067" t="n">
-        <v>21.2743358612061</v>
+        <v>21.2743377685547</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1068" t="n">
-        <v>20.7095317840576</v>
+        <v>20.7095336914062</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1071" t="n">
-        <v>20.6624641418457</v>
+        <v>20.6624622344971</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G1072" t="n">
-        <v>20.285924911499</v>
+        <v>20.2859268188477</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G1076" t="n">
-        <v>19.5328521728516</v>
+        <v>19.5328559875488</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1077" t="n">
-        <v>20.0976619720459</v>
+        <v>20.0976600646973</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G1078" t="n">
-        <v>19.8152542114258</v>
+        <v>19.8152561187744</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G1080" t="n">
-        <v>19.1092510223389</v>
+        <v>19.1092491149902</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>20.0512180328369</v>
       </c>
       <c r="G1081" t="n">
-        <v>19.4387187957764</v>
+        <v>19.438720703125</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G1082" t="n">
-        <v>19.9093914031982</v>
+        <v>19.9093894958496</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>19.6628170013428</v>
       </c>
       <c r="G1084" t="n">
-        <v>19.0621814727783</v>
+        <v>19.062183380127</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1086" t="n">
-        <v>18.9209823608398</v>
+        <v>18.9209804534912</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>19.0122451782227</v>
       </c>
       <c r="G1087" t="n">
-        <v>18.4314823150635</v>
+        <v>18.4314842224121</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G1089" t="n">
-        <v>17.8101997375488</v>
+        <v>17.8101978302002</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G1091" t="n">
-        <v>17.6031017303467</v>
+        <v>17.6031036376953</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1093" t="n">
-        <v>18.0549430847168</v>
+        <v>18.0549449920654</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G1094" t="n">
-        <v>17.6595840454102</v>
+        <v>17.6595821380615</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G1096" t="n">
-        <v>16.8876800537109</v>
+        <v>16.8876819610596</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1098" t="n">
-        <v>18.9680480957031</v>
+        <v>18.9680500030518</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G1099" t="n">
-        <v>19.9564552307129</v>
+        <v>19.9564590454102</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1100" t="n">
-        <v>18.9680480957031</v>
+        <v>18.9680500030518</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G1101" t="n">
-        <v>18.6762313842773</v>
+        <v>18.676233291626</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G1103" t="n">
-        <v>18.1679077148438</v>
+        <v>18.1679096221924</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1105" t="n">
-        <v>18.0549430847168</v>
+        <v>18.0549449920654</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G1107" t="n">
-        <v>17.9419822692871</v>
+        <v>17.9419841766357</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1108" t="n">
-        <v>18.1490802764893</v>
+        <v>18.1490783691406</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1110" t="n">
-        <v>18.1490802764893</v>
+        <v>18.1490783691406</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1112" t="n">
-        <v>18.3561744689941</v>
+        <v>18.3561763763428</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1113" t="n">
-        <v>18.9209823608398</v>
+        <v>18.9209804534912</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1114" t="n">
-        <v>20.5212631225586</v>
+        <v>20.5212650299072</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G1118" t="n">
-        <v>20.7565994262695</v>
+        <v>20.7566013336182</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1119" t="n">
-        <v>20.3800621032715</v>
+        <v>20.3800640106201</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1120" t="n">
-        <v>20.5212631225586</v>
+        <v>20.5212650299072</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1124" t="n">
-        <v>20.7095317840576</v>
+        <v>20.7095336914062</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1126" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1128" t="n">
-        <v>24.0042324066162</v>
+        <v>24.0042304992676</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1132" t="n">
-        <v>23.2511577606201</v>
+        <v>23.2511558532715</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1133" t="n">
-        <v>22.7804851531982</v>
+        <v>22.7804832458496</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1134" t="n">
-        <v>23.2511577606201</v>
+        <v>23.2511558532715</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1135" t="n">
-        <v>23.5335597991943</v>
+        <v>23.5335578918457</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1137" t="n">
-        <v>22.7804851531982</v>
+        <v>22.7804832458496</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1138" t="n">
-        <v>22.5451507568359</v>
+        <v>22.5451488494873</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1140" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>23.4497299194336</v>
       </c>
       <c r="G1141" t="n">
-        <v>22.7334175109863</v>
+        <v>22.733419418335</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1143" t="n">
-        <v>22.8746204376221</v>
+        <v>22.8746185302734</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>22.7214775085449</v>
       </c>
       <c r="G1145" t="n">
-        <v>22.0274124145508</v>
+        <v>22.0274105072021</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1146" t="n">
-        <v>22.6863498687744</v>
+        <v>22.686351776123</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1147" t="n">
-        <v>23.5335597991943</v>
+        <v>23.5335578918457</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1149" t="n">
-        <v>24.192497253418</v>
+        <v>24.1924953460693</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1150" t="n">
-        <v>24.0042324066162</v>
+        <v>24.0042304992676</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G1152" t="n">
-        <v>23.0158214569092</v>
+        <v>23.0158195495605</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>22.9642276763916</v>
       </c>
       <c r="G1153" t="n">
-        <v>22.2627468109131</v>
+        <v>22.2627449035645</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1155" t="n">
-        <v>22.6863498687744</v>
+        <v>22.686351776123</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1157" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1158" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1160" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G1165" t="n">
-        <v>21.4626064300537</v>
+        <v>21.4626045227051</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G1167" t="n">
-        <v>21.8862113952637</v>
+        <v>21.886209487915</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>22.9642276763916</v>
       </c>
       <c r="G1174" t="n">
-        <v>22.2627468109131</v>
+        <v>22.2627449035645</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1177" t="n">
-        <v>22.7804851531982</v>
+        <v>22.7804832458496</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1178" t="n">
-        <v>22.8746204376221</v>
+        <v>22.8746185302734</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1179" t="n">
-        <v>22.5451507568359</v>
+        <v>22.5451488494873</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1180" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1184" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G1188" t="n">
-        <v>23.8159618377686</v>
+        <v>23.8159599304199</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1190" t="n">
-        <v>24.0983619689941</v>
+        <v>24.0983638763428</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.7573051452637</v>
+        <v>24.757303237915</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G1195" t="n">
-        <v>24.5690364837646</v>
+        <v>24.569034576416</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1196" t="n">
-        <v>24.2395687103271</v>
+        <v>24.2395668029785</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1197" t="n">
-        <v>24.0042324066162</v>
+        <v>24.0042304992676</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1199" t="n">
-        <v>24.3337001800537</v>
+        <v>24.3336982727051</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1200" t="n">
-        <v>24.8514385223389</v>
+        <v>24.8514366149902</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1201" t="n">
-        <v>25.557445526123</v>
+        <v>25.5574436187744</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1203" t="n">
-        <v>24.8514385223389</v>
+        <v>24.8514366149902</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1204" t="n">
-        <v>24.3337001800537</v>
+        <v>24.3336982727051</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1205" t="n">
-        <v>24.192497253418</v>
+        <v>24.1924953460693</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1206" t="n">
-        <v>24.8514385223389</v>
+        <v>24.8514366149902</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G1210" t="n">
-        <v>25.1809101104736</v>
+        <v>25.1809062957764</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1215" t="n">
-        <v>23.3923587799072</v>
+        <v>23.3923568725586</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1216" t="n">
-        <v>22.7804851531982</v>
+        <v>22.7804832458496</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1217" t="n">
-        <v>22.9687519073486</v>
+        <v>22.9687538146973</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1218" t="n">
-        <v>23.1099529266357</v>
+        <v>23.1099548339844</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1226" t="n">
-        <v>23.721830368042</v>
+        <v>23.7218284606934</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1227" t="n">
-        <v>24.2395687103271</v>
+        <v>24.2395668029785</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1228" t="n">
-        <v>23.6276912689209</v>
+        <v>23.6276931762695</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1229" t="n">
-        <v>23.1099529266357</v>
+        <v>23.1099548339844</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1232" t="n">
-        <v>22.8746204376221</v>
+        <v>22.8746185302734</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1233" t="n">
-        <v>23.1099529266357</v>
+        <v>23.1099548339844</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1234" t="n">
-        <v>23.6276912689209</v>
+        <v>23.6276931762695</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1237" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1238" t="n">
-        <v>22.6863498687744</v>
+        <v>22.686351776123</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G1239" t="n">
-        <v>22.3098163604736</v>
+        <v>22.309814453125</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G1243" t="n">
-        <v>22.4980812072754</v>
+        <v>22.498083114624</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G1248" t="n">
-        <v>22.4980812072754</v>
+        <v>22.498083114624</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1249" t="n">
-        <v>23.2511577606201</v>
+        <v>23.2511558532715</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1250" t="n">
-        <v>23.5335597991943</v>
+        <v>23.5335578918457</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1252" t="n">
-        <v>23.3923587799072</v>
+        <v>23.3923568725586</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1253" t="n">
-        <v>23.6276912689209</v>
+        <v>23.6276931762695</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1254" t="n">
-        <v>22.9687519073486</v>
+        <v>22.9687538146973</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1255" t="n">
-        <v>22.8746204376221</v>
+        <v>22.8746185302734</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1257" t="n">
-        <v>22.9687519073486</v>
+        <v>22.9687538146973</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1259" t="n">
-        <v>22.7804851531982</v>
+        <v>22.7804832458496</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1262" t="n">
-        <v>22.6863498687744</v>
+        <v>22.686351776123</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1263" t="n">
-        <v>23.721830368042</v>
+        <v>23.7218284606934</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1264" t="n">
-        <v>23.6276912689209</v>
+        <v>23.6276931762695</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1268" t="n">
-        <v>25.4162425994873</v>
+        <v>25.4162445068359</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>27.285192489624</v>
       </c>
       <c r="G1271" t="n">
-        <v>26.4517211914062</v>
+        <v>26.4517192840576</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>26.8482418060303</v>
       </c>
       <c r="G1272" t="n">
-        <v>26.0281181335449</v>
+        <v>26.0281162261963</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>27.3337421417236</v>
       </c>
       <c r="G1278" t="n">
-        <v>26.4987869262695</v>
+        <v>26.4987850189209</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>26.7996921539307</v>
       </c>
       <c r="G1279" t="n">
-        <v>26.1482486724854</v>
+        <v>26.148250579834</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>26.3141899108887</v>
       </c>
       <c r="G1283" t="n">
-        <v>25.6745491027832</v>
+        <v>25.6745471954346</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>26.7996921539307</v>
       </c>
       <c r="G1288" t="n">
-        <v>26.1482486724854</v>
+        <v>26.148250579834</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>26.6054916381836</v>
       </c>
       <c r="G1290" t="n">
-        <v>25.9587688446045</v>
+        <v>25.9587707519531</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>26.2656402587891</v>
       </c>
       <c r="G1295" t="n">
-        <v>25.6271781921387</v>
+        <v>25.6271800994873</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G1296" t="n">
-        <v>24.9639987945557</v>
+        <v>24.9640007019043</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>25.7315883636475</v>
       </c>
       <c r="G1298" t="n">
-        <v>25.106107711792</v>
+        <v>25.1061096191406</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1301" t="n">
-        <v>25.0113697052002</v>
+        <v>25.0113677978516</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1302" t="n">
-        <v>24.3955612182617</v>
+        <v>24.3955593109131</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G1303" t="n">
-        <v>24.2060794830322</v>
+        <v>24.2060775756836</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1305" t="n">
-        <v>23.7797470092773</v>
+        <v>23.779748916626</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G1306" t="n">
-        <v>24.2060794830322</v>
+        <v>24.2060775756836</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1307" t="n">
-        <v>24.7745189666748</v>
+        <v>24.7745208740234</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1313" t="n">
-        <v>24.3955612182617</v>
+        <v>24.3955593109131</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1314" t="n">
-        <v>23.7797470092773</v>
+        <v>23.779748916626</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1315" t="n">
-        <v>23.7323799133301</v>
+        <v>23.7323780059814</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1316" t="n">
-        <v>23.7797470092773</v>
+        <v>23.779748916626</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1318" t="n">
-        <v>23.5429000854492</v>
+        <v>23.5428981781006</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G1320" t="n">
-        <v>24.2060794830322</v>
+        <v>24.2060775756836</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1322" t="n">
-        <v>23.7323799133301</v>
+        <v>23.7323780059814</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G1323" t="n">
-        <v>23.9218578338623</v>
+        <v>23.9218597412109</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1324" t="n">
-        <v>24.4902992248535</v>
+        <v>24.4902973175049</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1325" t="n">
-        <v>23.7797470092773</v>
+        <v>23.779748916626</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1326" t="n">
-        <v>23.5429000854492</v>
+        <v>23.5428981781006</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1328" t="n">
-        <v>24.2534465789795</v>
+        <v>24.2534484863281</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1329" t="n">
-        <v>24.2534465789795</v>
+        <v>24.2534484863281</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1330" t="n">
-        <v>23.7323799133301</v>
+        <v>23.7323780059814</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1333" t="n">
-        <v>24.7745189666748</v>
+        <v>24.7745208740234</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G1335" t="n">
-        <v>24.9639987945557</v>
+        <v>24.9640007019043</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1338" t="n">
-        <v>23.3060493469238</v>
+        <v>23.3060474395752</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1345" t="n">
-        <v>21.7902069091797</v>
+        <v>21.7902088165283</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1363" t="n">
-        <v>20.5112171173096</v>
+        <v>20.5112190246582</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>18.8568840026855</v>
       </c>
       <c r="G1369" t="n">
-        <v>18.3985157012939</v>
+        <v>18.3985137939453</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G1377" t="n">
-        <v>20.0848846435547</v>
+        <v>20.0848865509033</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1384" t="n">
-        <v>21.7902069091797</v>
+        <v>21.7902088165283</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1387" t="n">
-        <v>20.5112171173096</v>
+        <v>20.5112190246582</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1390" t="n">
-        <v>19.8065528869629</v>
+        <v>19.8065509796143</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1391" t="n">
-        <v>19.6601963043213</v>
+        <v>19.6601982116699</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1409" t="n">
-        <v>23.367826461792</v>
+        <v>23.3678283691406</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>24.3435192108154</v>
+        <v>24.3435211181641</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>24.75</v>
       </c>
       <c r="G1414" t="n">
-        <v>24.148380279541</v>
+        <v>24.1483821868896</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>24.1971664428711</v>
+        <v>24.1971645355225</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1416" t="n">
-        <v>23.367826461792</v>
+        <v>23.3678283691406</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>23.25</v>
       </c>
       <c r="G1420" t="n">
-        <v>22.6848430633545</v>
+        <v>22.6848411560059</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>22.0506439208984</v>
+        <v>22.0506420135498</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1428" t="n">
-        <v>22.2945671081543</v>
+        <v>22.2945652008057</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1430" t="n">
-        <v>21.5627956390381</v>
+        <v>21.5627975463867</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1432" t="n">
-        <v>22.1482124328613</v>
+        <v>22.14821434021</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1438" t="n">
-        <v>22.2945671081543</v>
+        <v>22.2945652008057</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1441" t="n">
-        <v>21.5627956390381</v>
+        <v>21.5627975463867</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1449" t="n">
-        <v>22.2945671081543</v>
+        <v>22.2945652008057</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>21.5</v>
       </c>
       <c r="G1461" t="n">
-        <v>20.9773807525635</v>
+        <v>20.9773826599121</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>18.8308601379395</v>
+        <v>18.8308582305908</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1470" t="n">
-        <v>19.0650234222412</v>
+        <v>19.0650253295898</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>19.5</v>
       </c>
       <c r="G1471" t="n">
-        <v>19.0259971618652</v>
+        <v>19.0259990692139</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1472" t="n">
-        <v>18.9869709014893</v>
+        <v>18.9869689941406</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1473" t="n">
-        <v>19.6601963043213</v>
+        <v>19.6601982116699</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>20.5</v>
       </c>
       <c r="G1476" t="n">
-        <v>20.0016918182373</v>
+        <v>20.0016899108887</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>20.5</v>
       </c>
       <c r="G1479" t="n">
-        <v>20.0016918182373</v>
+        <v>20.0016899108887</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1482" t="n">
-        <v>19.45530128479</v>
+        <v>19.4553031921387</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1486" t="n">
-        <v>19.240650177002</v>
+        <v>19.2406482696533</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1487" t="n">
-        <v>18.8308601379395</v>
+        <v>18.8308582305908</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1489" t="n">
-        <v>18.2844734191895</v>
+        <v>18.2844715118408</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>18.5</v>
       </c>
       <c r="G1490" t="n">
-        <v>18.0503063201904</v>
+        <v>18.0503044128418</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1493" t="n">
-        <v>17.4844036102295</v>
+        <v>17.4844017028809</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1497" t="n">
-        <v>18.2844734191895</v>
+        <v>18.2844715118408</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1499" t="n">
-        <v>18.5576648712158</v>
+        <v>18.5576667785645</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1502" t="n">
-        <v>18.5576648712158</v>
+        <v>18.5576667785645</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1503" t="n">
-        <v>18.7528038024902</v>
+        <v>18.7528018951416</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1505" t="n">
-        <v>17.308780670166</v>
+        <v>17.3087787628174</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1506" t="n">
-        <v>18.1673889160156</v>
+        <v>18.1673908233643</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1507" t="n">
-        <v>18.128360748291</v>
+        <v>18.1283588409424</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1509" t="n">
-        <v>18.36252784729</v>
+        <v>18.3625259399414</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1512" t="n">
-        <v>18.0112781524658</v>
+        <v>18.0112762451172</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1518" t="n">
-        <v>17.5234298706055</v>
+        <v>17.5234317779541</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1522" t="n">
-        <v>17.3478050231934</v>
+        <v>17.347806930542</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1530" t="n">
-        <v>17.0160713195801</v>
+        <v>17.0160732269287</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1535" t="n">
-        <v>17.308780670166</v>
+        <v>17.3087787628174</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -55506,7 +55506,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="D2121" t="n">
-        <v>28</v>
+        <v>27.75</v>
       </c>
       <c r="E2121" t="n">
         <v>28.6499996185303</v>
@@ -55518,6 +55518,32 @@
         <v>27.75</v>
       </c>
       <c r="H2121" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2122" t="n">
+        <v>346215</v>
+      </c>
+      <c r="C2122" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="E2122" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="F2122" t="n">
+        <v>25.7000007629395</v>
+      </c>
+      <c r="G2122" t="n">
+        <v>25.7000007629395</v>
+      </c>
+      <c r="H2122" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -447,7 +447,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G3" t="n">
-        <v>7.85125875473022</v>
+        <v>7.85125970840454</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G4" t="n">
-        <v>7.75996494293213</v>
+        <v>7.75996589660645</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G5" t="n">
-        <v>7.75996494293213</v>
+        <v>7.75996589660645</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>8.1253547668457</v>
       </c>
       <c r="G7" t="n">
-        <v>7.63945770263672</v>
+        <v>7.63945817947388</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>8.31955623626709</v>
       </c>
       <c r="G8" t="n">
-        <v>7.82204627990723</v>
+        <v>7.82204675674438</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.10884761810303</v>
       </c>
       <c r="G10" t="n">
-        <v>7.62393760681152</v>
+        <v>7.62393808364868</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>7.86609792709351</v>
       </c>
       <c r="G14" t="n">
-        <v>7.3957052230835</v>
+        <v>7.39570474624634</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>7.71656322479248</v>
       </c>
       <c r="G15" t="n">
-        <v>7.25511264801025</v>
+        <v>7.25511312484741</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>7.88940191268921</v>
       </c>
       <c r="G17" t="n">
-        <v>7.41761493682861</v>
+        <v>7.41761541366577</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>7.8651270866394</v>
       </c>
       <c r="G19" t="n">
-        <v>7.3947925567627</v>
+        <v>7.39479207992554</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>7.95251703262329</v>
       </c>
       <c r="G20" t="n">
-        <v>7.47695684432983</v>
+        <v>7.47695636749268</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>8.08068943023682</v>
       </c>
       <c r="G22" t="n">
-        <v>7.59746313095093</v>
+        <v>7.59746408462524</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>8.24381828308105</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75083780288696</v>
+        <v>7.75083684921265</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G25" t="n">
-        <v>7.80561256408691</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G27" t="n">
-        <v>7.80561256408691</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.45743942260742</v>
       </c>
       <c r="G28" t="n">
-        <v>7.95168399810791</v>
+        <v>7.95168352127075</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.47394561767578</v>
       </c>
       <c r="G30" t="n">
-        <v>7.96720457077026</v>
+        <v>7.96720266342163</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G31" t="n">
-        <v>7.85125875473022</v>
+        <v>7.85125970840454</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.20497798919678</v>
       </c>
       <c r="G33" t="n">
-        <v>7.71432018280029</v>
+        <v>7.71431970596313</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G34" t="n">
-        <v>7.80561256408691</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G38" t="n">
-        <v>7.80561256408691</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G39" t="n">
-        <v>7.85125875473022</v>
+        <v>7.85125970840454</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>8.12923908233643</v>
       </c>
       <c r="G41" t="n">
-        <v>7.6431097984314</v>
+        <v>7.64311122894287</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.23410797119141</v>
       </c>
       <c r="G42" t="n">
-        <v>7.74170732498169</v>
+        <v>7.74170780181885</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G45" t="n">
-        <v>7.85125875473022</v>
+        <v>7.85125970840454</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>8.33606338500977</v>
       </c>
       <c r="G46" t="n">
-        <v>7.83756732940674</v>
+        <v>7.83756685256958</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.99232816696167</v>
       </c>
       <c r="G47" t="n">
-        <v>7.51438760757446</v>
+        <v>7.5143871307373</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>8.22634029388428</v>
       </c>
       <c r="G49" t="n">
-        <v>7.73440504074097</v>
+        <v>7.73440456390381</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>8.1875</v>
       </c>
       <c r="G50" t="n">
-        <v>7.6978874206543</v>
+        <v>7.69788694381714</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>8.44772911071777</v>
       </c>
       <c r="G51" t="n">
-        <v>7.94255352020264</v>
+        <v>7.94255399703979</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>8.51667022705078</v>
       </c>
       <c r="G52" t="n">
-        <v>8.00737285614014</v>
+        <v>8.00737380981445</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>8.94293975830078</v>
       </c>
       <c r="G55" t="n">
-        <v>8.40815258026123</v>
+        <v>8.4081506729126</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.46728229522705</v>
       </c>
       <c r="G58" t="n">
-        <v>8.90113830566406</v>
+        <v>8.90113735198975</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.08859062194824</v>
       </c>
       <c r="G59" t="n">
-        <v>8.545090675354</v>
+        <v>8.54509162902832</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G64" t="n">
-        <v>8.39902305603027</v>
+        <v>8.39902210235596</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.20511054992676</v>
       </c>
       <c r="G65" t="n">
-        <v>8.65464401245117</v>
+        <v>8.6546459197998</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.10412693023682</v>
       </c>
       <c r="G67" t="n">
-        <v>8.55970001220703</v>
+        <v>8.55969905853271</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.29250144958496</v>
       </c>
       <c r="G69" t="n">
-        <v>8.73680973052979</v>
+        <v>8.7368106842041</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.63235282897949</v>
       </c>
       <c r="G73" t="n">
-        <v>9.0563383102417</v>
+        <v>9.05633735656738</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.66148281097412</v>
       </c>
       <c r="G74" t="n">
-        <v>9.08372688293457</v>
+        <v>9.08372497558594</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G75" t="n">
-        <v>9.27544116973877</v>
+        <v>9.2754430770874</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.61293315887451</v>
       </c>
       <c r="G76" t="n">
-        <v>9.0380802154541</v>
+        <v>9.03807735443115</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.70614910125732</v>
       </c>
       <c r="G79" t="n">
-        <v>9.1257209777832</v>
+        <v>9.12572002410889</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.57506275177002</v>
       </c>
       <c r="G80" t="n">
-        <v>9.00247478485107</v>
+        <v>9.00247383117676</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.53525161743164</v>
       </c>
       <c r="G81" t="n">
-        <v>8.96504306793213</v>
+        <v>8.96504402160645</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.50320911407471</v>
       </c>
       <c r="G83" t="n">
-        <v>8.93491554260254</v>
+        <v>8.93491744995117</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.40610885620117</v>
       </c>
       <c r="G85" t="n">
-        <v>8.8436222076416</v>
+        <v>8.84362316131592</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.16238689422607</v>
       </c>
       <c r="G86" t="n">
-        <v>8.61447525024414</v>
+        <v>8.61447620391846</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.98954772949219</v>
       </c>
       <c r="G87" t="n">
-        <v>8.45197200775146</v>
+        <v>8.45197105407715</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>8.43413352966309</v>
       </c>
       <c r="G89" t="n">
-        <v>7.92977285385132</v>
+        <v>7.92977142333984</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>8.77689933776855</v>
       </c>
       <c r="G90" t="n">
-        <v>8.25203895568848</v>
+        <v>8.25204086303711</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>8.88467979431152</v>
       </c>
       <c r="G91" t="n">
-        <v>8.3533763885498</v>
+        <v>8.35337543487549</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.03033065795898</v>
       </c>
       <c r="G92" t="n">
-        <v>8.49031734466553</v>
+        <v>8.49031543731689</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.30706596374512</v>
       </c>
       <c r="G96" t="n">
-        <v>8.75050163269043</v>
+        <v>8.75050354003906</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G98" t="n">
-        <v>7.80561256408691</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>8.48462677001953</v>
       </c>
       <c r="G99" t="n">
-        <v>7.97724580764771</v>
+        <v>7.97724723815918</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G101" t="n">
-        <v>7.75996494293213</v>
+        <v>7.75996589660645</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>8.19041347503662</v>
       </c>
       <c r="G102" t="n">
-        <v>7.70062589645386</v>
+        <v>7.70062685012817</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>8.3700475692749</v>
       </c>
       <c r="G103" t="n">
-        <v>7.8695182800293</v>
+        <v>7.86951732635498</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>8.3700475692749</v>
       </c>
       <c r="G104" t="n">
-        <v>7.8695182800293</v>
+        <v>7.86951732635498</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.27210998535156</v>
       </c>
       <c r="G106" t="n">
-        <v>8.71763801574707</v>
+        <v>8.71763896942139</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.27502346038818</v>
       </c>
       <c r="G107" t="n">
-        <v>8.72037601470947</v>
+        <v>8.72037696838379</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.08664894104004</v>
       </c>
       <c r="G110" t="n">
-        <v>8.54326629638672</v>
+        <v>8.54326725006104</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.19443035125732</v>
       </c>
       <c r="G111" t="n">
-        <v>8.64460182189941</v>
+        <v>8.64460277557373</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.81379699707031</v>
       </c>
       <c r="G114" t="n">
-        <v>8.2867317199707</v>
+        <v>8.28673076629639</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>9.04586696624756</v>
       </c>
       <c r="G115" t="n">
-        <v>8.50492477416992</v>
+        <v>8.50492286682129</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.2138500213623</v>
       </c>
       <c r="G116" t="n">
-        <v>8.66286087036133</v>
+        <v>8.66286277770996</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.51084423065186</v>
       </c>
       <c r="G117" t="n">
-        <v>8.00189590454102</v>
+        <v>8.00189781188965</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.49724960327148</v>
       </c>
       <c r="G118" t="n">
-        <v>7.98911428451538</v>
+        <v>7.98911380767822</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>8.54482936859131</v>
       </c>
       <c r="G119" t="n">
-        <v>8.03384780883789</v>
+        <v>8.03384876251221</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.65260982513428</v>
       </c>
       <c r="G120" t="n">
-        <v>8.1351842880249</v>
+        <v>8.13518238067627</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.03324413299561</v>
       </c>
       <c r="G121" t="n">
-        <v>8.49305438995361</v>
+        <v>8.49305629730225</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G123" t="n">
-        <v>8.39902305603027</v>
+        <v>8.39902210235596</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G125" t="n">
-        <v>8.39902305603027</v>
+        <v>8.39902210235596</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.42650032043457</v>
       </c>
       <c r="G126" t="n">
-        <v>8.86279487609863</v>
+        <v>8.86279392242432</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.55078792572021</v>
       </c>
       <c r="G127" t="n">
-        <v>8.97965049743652</v>
+        <v>8.97965145111084</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.48281764984131</v>
       </c>
       <c r="G128" t="n">
-        <v>8.91574478149414</v>
+        <v>8.91574573516846</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.67119312286377</v>
       </c>
       <c r="G130" t="n">
-        <v>9.09285545349121</v>
+        <v>9.09285640716553</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.35076236724854</v>
       </c>
       <c r="G131" t="n">
-        <v>8.79158592224121</v>
+        <v>8.79158782958984</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.53525161743164</v>
       </c>
       <c r="G133" t="n">
-        <v>8.96504306793213</v>
+        <v>8.96504402160645</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.5935115814209</v>
       </c>
       <c r="G134" t="n">
-        <v>9.01982021331787</v>
+        <v>9.01981925964355</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.35755920410156</v>
       </c>
       <c r="G135" t="n">
-        <v>8.79797649383545</v>
+        <v>8.79797554016113</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>8.70018863677979</v>
       </c>
       <c r="G138" t="n">
-        <v>8.17991828918457</v>
+        <v>8.17991638183594</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G139" t="n">
-        <v>8.21643733978271</v>
+        <v>8.21643543243408</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8.66523265838623</v>
       </c>
       <c r="G141" t="n">
-        <v>8.14705181121826</v>
+        <v>8.14705085754395</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>8.8798246383667</v>
       </c>
       <c r="G143" t="n">
-        <v>8.34880924224854</v>
+        <v>8.34881019592285</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>8.7429141998291</v>
       </c>
       <c r="G144" t="n">
-        <v>8.22008800506592</v>
+        <v>8.2200870513916</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>8.76815986633301</v>
       </c>
       <c r="G145" t="n">
-        <v>8.24382209777832</v>
+        <v>8.24382400512695</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>8.98178005218506</v>
       </c>
       <c r="G148" t="n">
-        <v>8.44466972351074</v>
+        <v>8.44466876983643</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>8.94293975830078</v>
       </c>
       <c r="G149" t="n">
-        <v>8.40815258026123</v>
+        <v>8.4081506729126</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>8.91380977630615</v>
       </c>
       <c r="G150" t="n">
-        <v>8.38076305389404</v>
+        <v>8.38076400756836</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G152" t="n">
-        <v>8.21643733978271</v>
+        <v>8.21643543243408</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>8.82739067077637</v>
       </c>
       <c r="G153" t="n">
-        <v>8.29951286315918</v>
+        <v>8.29951190948486</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>8.65260982513428</v>
       </c>
       <c r="G154" t="n">
-        <v>8.1351842880249</v>
+        <v>8.13518238067627</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>8.68659496307373</v>
       </c>
       <c r="G155" t="n">
-        <v>8.16713619232178</v>
+        <v>8.16713523864746</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.73902988433838</v>
       </c>
       <c r="G157" t="n">
-        <v>8.21643733978271</v>
+        <v>8.21643543243408</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>8.87497043609619</v>
       </c>
       <c r="G158" t="n">
-        <v>8.34424686431885</v>
+        <v>8.34424591064453</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.26822566986084</v>
       </c>
       <c r="G163" t="n">
-        <v>8.71398639678955</v>
+        <v>8.71398448944092</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.21482086181641</v>
       </c>
       <c r="G164" t="n">
-        <v>8.66377449035645</v>
+        <v>8.66377353668213</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.61584568023682</v>
       </c>
       <c r="G165" t="n">
-        <v>9.04081726074219</v>
+        <v>9.0408182144165</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.57894706726074</v>
       </c>
       <c r="G166" t="n">
-        <v>9.00612545013428</v>
+        <v>9.00612640380859</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.40222454071045</v>
       </c>
       <c r="G167" t="n">
-        <v>8.8399715423584</v>
+        <v>8.83997058868408</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.75858306884766</v>
       </c>
       <c r="G172" t="n">
-        <v>9.17502021789551</v>
+        <v>9.17501926422119</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.72751140594482</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14580631256104</v>
+        <v>9.1458044052124</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.89258098602295</v>
       </c>
       <c r="G174" t="n">
-        <v>9.30100440979004</v>
+        <v>9.30100345611572</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.92753791809082</v>
       </c>
       <c r="G175" t="n">
-        <v>9.33387088775635</v>
+        <v>9.33386898040771</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>10.1547517776489</v>
       </c>
       <c r="G176" t="n">
-        <v>9.5474967956543</v>
+        <v>9.54749774932861</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G177" t="n">
-        <v>9.58584117889404</v>
+        <v>9.58584213256836</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G178" t="n">
-        <v>9.58584117889404</v>
+        <v>9.58584213256836</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G179" t="n">
-        <v>9.58584117889404</v>
+        <v>9.58584213256836</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>10.2440853118896</v>
       </c>
       <c r="G180" t="n">
-        <v>9.63149070739746</v>
+        <v>9.63148880004883</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G181" t="n">
-        <v>9.58584117889404</v>
+        <v>9.58584213256836</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>10.1372737884521</v>
       </c>
       <c r="G182" t="n">
-        <v>9.5310640335083</v>
+        <v>9.53106594085693</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.84791469573975</v>
       </c>
       <c r="G184" t="n">
-        <v>9.25900936126709</v>
+        <v>9.25900840759277</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G185" t="n">
-        <v>9.58584117889404</v>
+        <v>9.58584213256836</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>10.1625204086304</v>
       </c>
       <c r="G186" t="n">
-        <v>9.55480098724365</v>
+        <v>9.55480194091797</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>10.0304641723633</v>
       </c>
       <c r="G187" t="n">
-        <v>9.43064212799072</v>
+        <v>9.43064308166504</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G188" t="n">
-        <v>9.58584117889404</v>
+        <v>9.58584213256836</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>10.0498838424683</v>
       </c>
       <c r="G189" t="n">
-        <v>9.44890022277832</v>
+        <v>9.44890117645264</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>9.99939155578613</v>
       </c>
       <c r="G191" t="n">
-        <v>9.40142822265625</v>
+        <v>9.40142726898193</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.8595666885376</v>
       </c>
       <c r="G192" t="n">
-        <v>9.26996517181396</v>
+        <v>9.26996421813965</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.78771305084229</v>
       </c>
       <c r="G195" t="n">
-        <v>9.20240688323975</v>
+        <v>9.20240783691406</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.66148281097412</v>
       </c>
       <c r="G196" t="n">
-        <v>9.08372688293457</v>
+        <v>9.08372497558594</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.66536712646484</v>
       </c>
       <c r="G197" t="n">
-        <v>9.08737754821777</v>
+        <v>9.08737850189209</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.03033065795898</v>
       </c>
       <c r="G200" t="n">
-        <v>8.49031734466553</v>
+        <v>8.49031543731689</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>8.87497043609619</v>
       </c>
       <c r="G201" t="n">
-        <v>8.34424686431885</v>
+        <v>8.34424591064453</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.5935115814209</v>
       </c>
       <c r="G204" t="n">
-        <v>9.01982021331787</v>
+        <v>9.01981925964355</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>9.51680278778076</v>
       </c>
       <c r="G205" t="n">
-        <v>8.94769763946533</v>
+        <v>8.94769668579102</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>9.61293315887451</v>
       </c>
       <c r="G206" t="n">
-        <v>9.0380802154541</v>
+        <v>9.03807735443115</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>9.67119312286377</v>
       </c>
       <c r="G207" t="n">
-        <v>9.09285545349121</v>
+        <v>9.09285640716553</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>9.71003341674805</v>
       </c>
       <c r="G208" t="n">
-        <v>9.12937355041504</v>
+        <v>9.12937164306641</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.62264347076416</v>
       </c>
       <c r="G211" t="n">
-        <v>9.04720783233643</v>
+        <v>9.04720973968506</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.66148281097412</v>
       </c>
       <c r="G212" t="n">
-        <v>9.08372688293457</v>
+        <v>9.08372497558594</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.78771305084229</v>
       </c>
       <c r="G213" t="n">
-        <v>9.20240688323975</v>
+        <v>9.20240783691406</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.98191356658936</v>
       </c>
       <c r="G214" t="n">
-        <v>9.38499450683594</v>
+        <v>9.38499546051025</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>9.9236536026001</v>
       </c>
       <c r="G215" t="n">
-        <v>9.33021926879883</v>
+        <v>9.33021831512451</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.234375</v>
       </c>
       <c r="G220" t="n">
-        <v>9.62235832214355</v>
+        <v>9.62235736846924</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G223" t="n">
-        <v>9.93275833129883</v>
+        <v>9.93275737762451</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G225" t="n">
-        <v>9.73191165924072</v>
+        <v>9.73191070556641</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G227" t="n">
-        <v>9.85972309112549</v>
+        <v>9.85972213745117</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G228" t="n">
-        <v>9.73191165924072</v>
+        <v>9.73191070556641</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G229" t="n">
-        <v>9.75017070770264</v>
+        <v>9.75016975402832</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G230" t="n">
-        <v>9.73191165924072</v>
+        <v>9.73191070556641</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G231" t="n">
-        <v>9.73191165924072</v>
+        <v>9.73191070556641</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G234" t="n">
-        <v>10.0423097610474</v>
+        <v>10.0423078536987</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.214955329895</v>
       </c>
       <c r="G235" t="n">
-        <v>9.60409927368164</v>
+        <v>9.60410022735596</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G236" t="n">
-        <v>9.71365451812744</v>
+        <v>9.71365261077881</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.4285745620728</v>
       </c>
       <c r="G238" t="n">
-        <v>9.80494594573975</v>
+        <v>9.80494403839111</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G239" t="n">
-        <v>10.0788259506226</v>
+        <v>10.0788278579712</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G240" t="n">
-        <v>10.0423097610474</v>
+        <v>10.0423078536987</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G241" t="n">
-        <v>10.0423097610474</v>
+        <v>10.0423078536987</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G242" t="n">
-        <v>10.0970849990845</v>
+        <v>10.0970859527588</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G244" t="n">
-        <v>10.2431573867798</v>
+        <v>10.2431545257568</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>10.6033563613892</v>
       </c>
       <c r="G245" t="n">
-        <v>9.96927547454834</v>
+        <v>9.96927452087402</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G246" t="n">
-        <v>9.85972309112549</v>
+        <v>9.85972213745117</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>10.4285745620728</v>
       </c>
       <c r="G247" t="n">
-        <v>9.80494594573975</v>
+        <v>9.80494403839111</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G248" t="n">
-        <v>9.93275833129883</v>
+        <v>9.93275737762451</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G249" t="n">
-        <v>9.95101642608643</v>
+        <v>9.95101547241211</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>11.1082782745361</v>
       </c>
       <c r="G251" t="n">
-        <v>10.4440021514893</v>
+        <v>10.4440031051636</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>11.2053775787354</v>
       </c>
       <c r="G252" t="n">
-        <v>10.5352964401245</v>
+        <v>10.5352945327759</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>11.2636375427246</v>
       </c>
       <c r="G253" t="n">
-        <v>10.5900726318359</v>
+        <v>10.5900707244873</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>11.3413181304932</v>
       </c>
       <c r="G254" t="n">
-        <v>10.6631078720093</v>
+        <v>10.663106918335</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>11.0111770629883</v>
       </c>
       <c r="G255" t="n">
-        <v>10.352707862854</v>
+        <v>10.3527088165283</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>11.0305967330933</v>
       </c>
       <c r="G257" t="n">
-        <v>10.3709669113159</v>
+        <v>10.3709678649902</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G258" t="n">
-        <v>10.2614135742188</v>
+        <v>10.2614145278931</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G259" t="n">
-        <v>9.95101642608643</v>
+        <v>9.95101547241211</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G260" t="n">
-        <v>9.9144983291626</v>
+        <v>9.91449928283691</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G261" t="n">
-        <v>9.78668689727783</v>
+        <v>9.78668785095215</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G262" t="n">
-        <v>10.0788259506226</v>
+        <v>10.0788278579712</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G265" t="n">
-        <v>9.82086944580078</v>
+        <v>9.82086849212646</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G269" t="n">
-        <v>10.0788259506226</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G271" t="n">
-        <v>10.1341037750244</v>
+        <v>10.1341018676758</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G272" t="n">
-        <v>10.1525278091431</v>
+        <v>10.1525287628174</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G273" t="n">
-        <v>10.1341037750244</v>
+        <v>10.1341018676758</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G276" t="n">
-        <v>9.83929443359375</v>
+        <v>9.83929347991943</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G277" t="n">
-        <v>9.98669910430908</v>
+        <v>9.98669815063477</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G279" t="n">
-        <v>10.1341037750244</v>
+        <v>10.1341018676758</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G280" t="n">
-        <v>10.1525278091431</v>
+        <v>10.1525287628174</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G281" t="n">
-        <v>9.82086944580078</v>
+        <v>9.82086849212646</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G282" t="n">
-        <v>9.67346286773682</v>
+        <v>9.67346382141113</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G284" t="n">
-        <v>9.82086944580078</v>
+        <v>9.82086849212646</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>10.6421957015991</v>
       </c>
       <c r="G286" t="n">
-        <v>10.0972528457642</v>
+        <v>10.0972518920898</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.0500173568726</v>
       </c>
       <c r="G287" t="n">
-        <v>10.4841909408569</v>
+        <v>10.4841918945312</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G288" t="n">
-        <v>10.3367862701416</v>
+        <v>10.3367853164673</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>10.8752374649048</v>
       </c>
       <c r="G290" t="n">
-        <v>10.3183603286743</v>
+        <v>10.3183612823486</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G291" t="n">
-        <v>10.3367862701416</v>
+        <v>10.3367853164673</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>10.8558168411255</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2999334335327</v>
+        <v>10.2999353408813</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G296" t="n">
-        <v>10.3367862701416</v>
+        <v>10.3367853164673</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G297" t="n">
-        <v>9.96827411651611</v>
+        <v>9.9682731628418</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G300" t="n">
-        <v>9.67346286773682</v>
+        <v>9.67346382141113</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.2732152938843</v>
       </c>
       <c r="G301" t="n">
-        <v>9.74716567993164</v>
+        <v>9.74716472625732</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G302" t="n">
-        <v>9.83929443359375</v>
+        <v>9.83929347991943</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G303" t="n">
-        <v>10.0051250457764</v>
+        <v>10.0051259994507</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G304" t="n">
-        <v>10.0419769287109</v>
+        <v>10.0419750213623</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G305" t="n">
-        <v>10.1341037750244</v>
+        <v>10.1341018676758</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>10.253794670105</v>
       </c>
       <c r="G306" t="n">
-        <v>9.72873878479004</v>
+        <v>9.72873973846436</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G308" t="n">
-        <v>9.98669910430908</v>
+        <v>9.98669815063477</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G310" t="n">
-        <v>10.1893796920776</v>
+        <v>10.189380645752</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G311" t="n">
-        <v>10.1893796920776</v>
+        <v>10.189380645752</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>10.8752374649048</v>
       </c>
       <c r="G312" t="n">
-        <v>10.3183603286743</v>
+        <v>10.3183612823486</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>11.0500173568726</v>
       </c>
       <c r="G313" t="n">
-        <v>10.4841909408569</v>
+        <v>10.4841918945312</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G314" t="n">
-        <v>10.7790012359619</v>
+        <v>10.7790002822876</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G315" t="n">
-        <v>10.4104881286621</v>
+        <v>10.4104871749878</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G316" t="n">
-        <v>10.1525278091431</v>
+        <v>10.1525287628174</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G317" t="n">
-        <v>11.9766674041748</v>
+        <v>11.9766683578491</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>11.6908798217773</v>
       </c>
       <c r="G318" t="n">
-        <v>11.0922365188599</v>
+        <v>11.0922384262085</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>12.15696144104</v>
       </c>
       <c r="G319" t="n">
-        <v>11.5344524383545</v>
+        <v>11.5344543457031</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G322" t="n">
-        <v>11.460750579834</v>
+        <v>11.4607496261597</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>12.0598611831665</v>
       </c>
       <c r="G324" t="n">
-        <v>11.4423236846924</v>
+        <v>11.4423246383667</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>12.15696144104</v>
       </c>
       <c r="G325" t="n">
-        <v>11.5344524383545</v>
+        <v>11.5344543457031</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G327" t="n">
-        <v>11.8845405578613</v>
+        <v>11.884539604187</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>13.0308637619019</v>
       </c>
       <c r="G331" t="n">
-        <v>12.3636054992676</v>
+        <v>12.3636074066162</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>13.186224937439</v>
       </c>
       <c r="G332" t="n">
-        <v>12.5110130310059</v>
+        <v>12.5110120773315</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G334" t="n">
-        <v>11.4976015090942</v>
+        <v>11.4976005554199</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G335" t="n">
-        <v>11.5160264968872</v>
+        <v>11.5160274505615</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G337" t="n">
-        <v>11.5160264968872</v>
+        <v>11.5160274505615</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G338" t="n">
-        <v>11.4976015090942</v>
+        <v>11.4976005554199</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>12.0210208892822</v>
       </c>
       <c r="G339" t="n">
-        <v>11.4054737091064</v>
+        <v>11.4054727554321</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G340" t="n">
-        <v>11.5160264968872</v>
+        <v>11.5160274505615</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G341" t="n">
-        <v>11.460750579834</v>
+        <v>11.4607496261597</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G342" t="n">
-        <v>11.5160264968872</v>
+        <v>11.5160274505615</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G343" t="n">
-        <v>11.4976015090942</v>
+        <v>11.4976005554199</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>12.4871015548706</v>
       </c>
       <c r="G344" t="n">
-        <v>11.8476877212524</v>
+        <v>11.8476886749268</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>12.681303024292</v>
       </c>
       <c r="G345" t="n">
-        <v>12.031946182251</v>
+        <v>12.0319442749023</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G346" t="n">
-        <v>11.8845405578613</v>
+        <v>11.884539604187</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G349" t="n">
-        <v>11.9766674041748</v>
+        <v>11.9766683578491</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G351" t="n">
-        <v>12.4373111724854</v>
+        <v>12.437310218811</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>13.5940456390381</v>
       </c>
       <c r="G353" t="n">
-        <v>12.89794921875</v>
+        <v>12.8979501724243</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G354" t="n">
-        <v>13.1743354797363</v>
+        <v>13.174334526062</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>13.9824476242065</v>
       </c>
       <c r="G355" t="n">
-        <v>13.2664642333984</v>
+        <v>13.2664632797241</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>14.1378078460693</v>
       </c>
       <c r="G356" t="n">
-        <v>13.4138689041138</v>
+        <v>13.4138679504395</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>14.7204103469849</v>
       </c>
       <c r="G357" t="n">
-        <v>13.9666395187378</v>
+        <v>13.9666385650635</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>14.1378078460693</v>
       </c>
       <c r="G358" t="n">
-        <v>13.4138689041138</v>
+        <v>13.4138679504395</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>14.0989675521851</v>
       </c>
       <c r="G359" t="n">
-        <v>13.3770160675049</v>
+        <v>13.3770170211792</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.8270874023438</v>
       </c>
       <c r="G360" t="n">
-        <v>13.1190595626831</v>
+        <v>13.1190576553345</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G361" t="n">
-        <v>13.0269298553467</v>
+        <v>13.0269317626953</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G362" t="n">
-        <v>13.0269298553467</v>
+        <v>13.0269317626953</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G364" t="n">
-        <v>12.2714776992798</v>
+        <v>12.2714796066284</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G370" t="n">
-        <v>12.1240720748901</v>
+        <v>12.1240739822388</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>12.8560838699341</v>
       </c>
       <c r="G371" t="n">
-        <v>12.197774887085</v>
+        <v>12.1977758407593</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G372" t="n">
-        <v>12.4373111724854</v>
+        <v>12.437310218811</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>14.5650501251221</v>
       </c>
       <c r="G374" t="n">
-        <v>13.8192329406738</v>
+        <v>13.8192338943481</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>14.0407075881958</v>
       </c>
       <c r="G375" t="n">
-        <v>13.3217401504517</v>
+        <v>13.321741104126</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G376" t="n">
-        <v>13.0822067260742</v>
+        <v>13.0822076797485</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G377" t="n">
-        <v>12.768970489502</v>
+        <v>12.7689714431763</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>13.3027448654175</v>
       </c>
       <c r="G378" t="n">
-        <v>12.6215648651123</v>
+        <v>12.6215658187866</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G379" t="n">
-        <v>12.4373111724854</v>
+        <v>12.437310218811</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G380" t="n">
-        <v>12.4741611480713</v>
+        <v>12.474160194397</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G381" t="n">
-        <v>12.2899055480957</v>
+        <v>12.2899045944214</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G382" t="n">
-        <v>12.2899055480957</v>
+        <v>12.2899045944214</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G383" t="n">
-        <v>12.4373111724854</v>
+        <v>12.437310218811</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>13.380425453186</v>
       </c>
       <c r="G385" t="n">
-        <v>12.6952686309814</v>
+        <v>12.6952676773071</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>13.4192657470703</v>
       </c>
       <c r="G386" t="n">
-        <v>12.7321214675903</v>
+        <v>12.732120513916</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>13.4969463348389</v>
       </c>
       <c r="G387" t="n">
-        <v>12.8058214187622</v>
+        <v>12.8058223724365</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G389" t="n">
-        <v>13.1743354797363</v>
+        <v>13.174334526062</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>13.6911468505859</v>
       </c>
       <c r="G390" t="n">
-        <v>12.9900779724121</v>
+        <v>12.9900789260864</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G393" t="n">
-        <v>13.0822067260742</v>
+        <v>13.0822076797485</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G394" t="n">
-        <v>12.768970489502</v>
+        <v>12.7689714431763</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G395" t="n">
-        <v>13.1743354797363</v>
+        <v>13.174334526062</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>13.2444849014282</v>
       </c>
       <c r="G397" t="n">
-        <v>12.5662899017334</v>
+        <v>12.5662889480591</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G403" t="n">
-        <v>12.4373111724854</v>
+        <v>12.437310218811</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G408" t="n">
-        <v>11.8845405578613</v>
+        <v>11.884539604187</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>12.4871015548706</v>
       </c>
       <c r="G409" t="n">
-        <v>11.8476877212524</v>
+        <v>11.8476886749268</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G411" t="n">
-        <v>11.7002840042114</v>
+        <v>11.7002830505371</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>11.8268203735352</v>
       </c>
       <c r="G412" t="n">
-        <v>11.2212171554565</v>
+        <v>11.2212162017822</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G413" t="n">
-        <v>10.9448318481445</v>
+        <v>10.9448308944702</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>11.6131992340088</v>
       </c>
       <c r="G414" t="n">
-        <v>11.0185356140137</v>
+        <v>11.0185346603394</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G415" t="n">
-        <v>10.9632577896118</v>
+        <v>10.9632568359375</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G416" t="n">
-        <v>10.7790012359619</v>
+        <v>10.7790002822876</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G417" t="n">
-        <v>10.9632577896118</v>
+        <v>10.9632568359375</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>11.2636375427246</v>
       </c>
       <c r="G418" t="n">
-        <v>10.6868724822998</v>
+        <v>10.6868715286255</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G419" t="n">
-        <v>10.9448318481445</v>
+        <v>10.9448308944702</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G420" t="n">
-        <v>11.2396430969238</v>
+        <v>11.2396421432495</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G421" t="n">
-        <v>11.2396430969238</v>
+        <v>11.2396421432495</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G422" t="n">
-        <v>11.0553865432739</v>
+        <v>11.0553846359253</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G424" t="n">
-        <v>11.1475133895874</v>
+        <v>11.147515296936</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G425" t="n">
-        <v>11.2396430969238</v>
+        <v>11.2396421432495</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G426" t="n">
-        <v>11.2396430969238</v>
+        <v>11.2396421432495</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G427" t="n">
-        <v>11.2396430969238</v>
+        <v>11.2396421432495</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G428" t="n">
-        <v>11.1475133895874</v>
+        <v>11.147515296936</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>11.9045000076294</v>
       </c>
       <c r="G430" t="n">
-        <v>11.2949190139771</v>
+        <v>11.2949199676514</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G431" t="n">
-        <v>11.0369606018066</v>
+        <v>11.0369596481323</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G432" t="n">
-        <v>10.0788259506226</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G433" t="n">
-        <v>10.4104881286621</v>
+        <v>10.4104871749878</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G434" t="n">
-        <v>10.7790012359619</v>
+        <v>10.7790002822876</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G437" t="n">
-        <v>9.98669910430908</v>
+        <v>9.98669815063477</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G439" t="n">
-        <v>10.3367862701416</v>
+        <v>10.3367853164673</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G441" t="n">
-        <v>10.0788259506226</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G442" t="n">
-        <v>9.67346286773682</v>
+        <v>9.67346382141113</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.30221080780029</v>
       </c>
       <c r="G445" t="n">
-        <v>8.8258810043335</v>
+        <v>8.82588291168213</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.22453117370605</v>
       </c>
       <c r="G449" t="n">
-        <v>8.7521800994873</v>
+        <v>8.75218200683594</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>8.59337902069092</v>
       </c>
       <c r="G450" t="n">
-        <v>8.15334701538086</v>
+        <v>8.15334796905518</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.6322193145752</v>
       </c>
       <c r="G451" t="n">
-        <v>8.19019889831543</v>
+        <v>8.19019985198975</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>8.58366870880127</v>
       </c>
       <c r="G452" t="n">
-        <v>8.14413547515869</v>
+        <v>8.14413452148438</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G453" t="n">
-        <v>8.47579574584961</v>
+        <v>8.47579479217529</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G454" t="n">
-        <v>8.38366794586182</v>
+        <v>8.3836669921875</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>10.0984344482422</v>
       </c>
       <c r="G455" t="n">
-        <v>9.58133411407471</v>
+        <v>9.58133506774902</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G456" t="n">
-        <v>11.7002840042114</v>
+        <v>11.7002830505371</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G457" t="n">
-        <v>11.0369606018066</v>
+        <v>11.0369596481323</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G459" t="n">
-        <v>10.0788259506226</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G460" t="n">
-        <v>10.1341037750244</v>
+        <v>10.1341018676758</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G462" t="n">
-        <v>10.1341037750244</v>
+        <v>10.1341018676758</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>10.7781372070312</v>
       </c>
       <c r="G463" t="n">
-        <v>10.2262334823608</v>
+        <v>10.2262325286865</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G464" t="n">
-        <v>10.170955657959</v>
+        <v>10.1709566116333</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>10.2732152938843</v>
       </c>
       <c r="G466" t="n">
-        <v>9.74716567993164</v>
+        <v>9.74716472625732</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>10.1761140823364</v>
       </c>
       <c r="G467" t="n">
-        <v>9.65503692626953</v>
+        <v>9.65503787994385</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G468" t="n">
-        <v>9.94984912872314</v>
+        <v>9.94984817504883</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>11.2053775787354</v>
       </c>
       <c r="G469" t="n">
-        <v>10.6315965652466</v>
+        <v>10.6315946578979</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G470" t="n">
-        <v>11.0553865432739</v>
+        <v>11.0553846359253</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>11.8268203735352</v>
       </c>
       <c r="G471" t="n">
-        <v>11.2212171554565</v>
+        <v>11.2212162017822</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G472" t="n">
-        <v>11.0553865432739</v>
+        <v>11.0553846359253</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G473" t="n">
-        <v>11.7002840042114</v>
+        <v>11.7002830505371</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>12.2346420288086</v>
       </c>
       <c r="G474" t="n">
-        <v>11.6081562042236</v>
+        <v>11.6081552505493</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G475" t="n">
-        <v>11.7924108505249</v>
+        <v>11.7924118041992</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>13.0697040557861</v>
       </c>
       <c r="G476" t="n">
-        <v>12.4004573822021</v>
+        <v>12.4004592895508</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G477" t="n">
-        <v>12.4741611480713</v>
+        <v>12.474160194397</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>13.2056446075439</v>
       </c>
       <c r="G478" t="n">
-        <v>12.5294370651245</v>
+        <v>12.5294361114502</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G480" t="n">
-        <v>12.2714776992798</v>
+        <v>12.2714796066284</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G481" t="n">
-        <v>11.9766674041748</v>
+        <v>11.9766683578491</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G483" t="n">
-        <v>11.7924108505249</v>
+        <v>11.7924118041992</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G484" t="n">
-        <v>12.1240720748901</v>
+        <v>12.1240739822388</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G485" t="n">
-        <v>11.7002840042114</v>
+        <v>11.7002830505371</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G486" t="n">
-        <v>12.4373111724854</v>
+        <v>12.437310218811</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G487" t="n">
-        <v>12.4373111724854</v>
+        <v>12.437310218811</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G488" t="n">
-        <v>13.0822067260742</v>
+        <v>13.0822076797485</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>14.3708486557007</v>
       </c>
       <c r="G489" t="n">
-        <v>13.6349763870239</v>
+        <v>13.6349754333496</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>14.1183881759644</v>
       </c>
       <c r="G490" t="n">
-        <v>13.3954429626465</v>
+        <v>13.3954420089722</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G491" t="n">
-        <v>13.0269298553467</v>
+        <v>13.0269317626953</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>14.2931690216064</v>
       </c>
       <c r="G492" t="n">
-        <v>13.5612745285034</v>
+        <v>13.5612735748291</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G493" t="n">
-        <v>14.7957906723022</v>
+        <v>14.7957916259766</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>15.7496738433838</v>
       </c>
       <c r="G494" t="n">
-        <v>14.9431982040405</v>
+        <v>14.9431972503662</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>14.9146108627319</v>
       </c>
       <c r="G496" t="n">
-        <v>14.1508951187134</v>
+        <v>14.1508941650391</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G497" t="n">
-        <v>15.1827306747437</v>
+        <v>15.182731628418</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G498" t="n">
-        <v>15.6433725357056</v>
+        <v>15.6433706283569</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>16.7206764221191</v>
       </c>
       <c r="G499" t="n">
-        <v>15.8644781112671</v>
+        <v>15.8644762039185</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G500" t="n">
-        <v>15.2932834625244</v>
+        <v>15.2932844161987</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>15.6525726318359</v>
       </c>
       <c r="G501" t="n">
-        <v>14.8510675430298</v>
+        <v>14.8510684967041</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>15.3030118942261</v>
       </c>
       <c r="G502" t="n">
-        <v>14.5194063186646</v>
+        <v>14.5194082260132</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>15.1476516723633</v>
       </c>
       <c r="G503" t="n">
-        <v>14.3720035552979</v>
+        <v>14.3720026016235</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G504" t="n">
-        <v>13.9482116699219</v>
+        <v>13.9482126235962</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G505" t="n">
-        <v>13.9482116699219</v>
+        <v>13.9482126235962</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>14.7980899810791</v>
       </c>
       <c r="G506" t="n">
-        <v>14.040340423584</v>
+        <v>14.0403394699097</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>14.7398300170898</v>
       </c>
       <c r="G510" t="n">
-        <v>13.9850625991821</v>
+        <v>13.9850635528564</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>14.9922914505005</v>
       </c>
       <c r="G511" t="n">
-        <v>14.2245969772339</v>
+        <v>14.2245979309082</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>15.4001121520996</v>
       </c>
       <c r="G512" t="n">
-        <v>14.6115341186523</v>
+        <v>14.6115350723267</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G515" t="n">
-        <v>14.7022838592529</v>
+        <v>14.7022848129272</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>15.3612718582153</v>
       </c>
       <c r="G517" t="n">
-        <v>14.6837205886841</v>
+        <v>14.6837215423584</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>15.3418521881104</v>
       </c>
       <c r="G518" t="n">
-        <v>14.6651582717896</v>
+        <v>14.6651573181152</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G521" t="n">
-        <v>14.7022838592529</v>
+        <v>14.7022848129272</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G522" t="n">
-        <v>15.1292448043823</v>
+        <v>15.1292457580566</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>16.0215549468994</v>
       </c>
       <c r="G523" t="n">
-        <v>15.3148822784424</v>
+        <v>15.3148813247681</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G525" t="n">
-        <v>14.9064826965332</v>
+        <v>14.9064836502075</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>15.1864919662476</v>
       </c>
       <c r="G526" t="n">
-        <v>14.5166501998901</v>
+        <v>14.5166492462158</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G527" t="n">
-        <v>14.9064826965332</v>
+        <v>14.9064836502075</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>15.2253322601318</v>
       </c>
       <c r="G530" t="n">
-        <v>14.5537757873535</v>
+        <v>14.5537767410278</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G531" t="n">
-        <v>15.0364294052124</v>
+        <v>15.0364274978638</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G534" t="n">
-        <v>15.1292448043823</v>
+        <v>15.1292457580566</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G535" t="n">
-        <v>15.1292448043823</v>
+        <v>15.1292457580566</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G536" t="n">
-        <v>14.9064826965332</v>
+        <v>14.9064836502075</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G537" t="n">
-        <v>15.2963171005249</v>
+        <v>15.2963161468506</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G539" t="n">
-        <v>14.8507919311523</v>
+        <v>14.850793838501</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>15.0505514144897</v>
       </c>
       <c r="G540" t="n">
-        <v>14.3867063522339</v>
+        <v>14.3867053985596</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>15.0505514144897</v>
       </c>
       <c r="G541" t="n">
-        <v>14.3867063522339</v>
+        <v>14.3867053985596</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>15.3612718582153</v>
       </c>
       <c r="G542" t="n">
-        <v>14.6837205886841</v>
+        <v>14.6837215423584</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G543" t="n">
-        <v>14.8507919311523</v>
+        <v>14.850793838501</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>16.1769142150879</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4633865356445</v>
+        <v>15.4633874893188</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G546" t="n">
-        <v>16.0574169158936</v>
+        <v>16.0574207305908</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G547" t="n">
-        <v>16.8556518554688</v>
+        <v>16.8556499481201</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G550" t="n">
-        <v>16.6143245697021</v>
+        <v>16.6143264770508</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>17.536319732666</v>
       </c>
       <c r="G551" t="n">
-        <v>16.7628307342529</v>
+        <v>16.7628326416016</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>18.1189212799072</v>
       </c>
       <c r="G552" t="n">
-        <v>17.3197345733643</v>
+        <v>17.3197383880615</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>18.0995025634766</v>
       </c>
       <c r="G553" t="n">
-        <v>17.301176071167</v>
+        <v>17.3011741638184</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G556" t="n">
-        <v>17.8952026367188</v>
+        <v>17.8952045440674</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G557" t="n">
-        <v>17.7652587890625</v>
+        <v>17.7652626037598</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G561" t="n">
-        <v>17.4125537872314</v>
+        <v>17.4125556945801</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G563" t="n">
-        <v>18.5634937286377</v>
+        <v>18.5634918212891</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G564" t="n">
-        <v>19.0275802612305</v>
+        <v>19.0275764465332</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G565" t="n">
-        <v>18.2107849121094</v>
+        <v>18.210786819458</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G566" t="n">
-        <v>18.5634937286377</v>
+        <v>18.5634918212891</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G568" t="n">
-        <v>18.0994052886963</v>
+        <v>18.0994033813477</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G569" t="n">
-        <v>17.9137706756592</v>
+        <v>17.9137687683105</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>18.6626834869385</v>
       </c>
       <c r="G571" t="n">
-        <v>17.8395137786865</v>
+        <v>17.8395156860352</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>17.5945796966553</v>
       </c>
       <c r="G574" t="n">
-        <v>16.8185234069824</v>
+        <v>16.8185253143311</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G575" t="n">
-        <v>16.5586338043213</v>
+        <v>16.5586318969727</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>16.4487953186035</v>
       </c>
       <c r="G576" t="n">
-        <v>15.7232780456543</v>
+        <v>15.72327709198</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G582" t="n">
-        <v>16.4843788146973</v>
+        <v>16.4843826293945</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>16.9342975616455</v>
       </c>
       <c r="G583" t="n">
-        <v>16.1873626708984</v>
+        <v>16.1873645782471</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G584" t="n">
-        <v>16.3173084259033</v>
+        <v>16.317310333252</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G585" t="n">
-        <v>16.1688003540039</v>
+        <v>16.1688041687012</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>17.1479187011719</v>
       </c>
       <c r="G589" t="n">
-        <v>16.3915634155273</v>
+        <v>16.3915615081787</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G594" t="n">
-        <v>16.5586338043213</v>
+        <v>16.5586318969727</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G595" t="n">
-        <v>16.5771980285645</v>
+        <v>16.5771999359131</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G598" t="n">
-        <v>16.6514530181885</v>
+        <v>16.6514511108398</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G599" t="n">
-        <v>16.7071437835693</v>
+        <v>16.7071418762207</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G600" t="n">
-        <v>16.4843788146973</v>
+        <v>16.4843826293945</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G602" t="n">
-        <v>16.6143245697021</v>
+        <v>16.6143264770508</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G603" t="n">
-        <v>15.686149597168</v>
+        <v>15.6861505508423</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>16.0409755706787</v>
       </c>
       <c r="G604" t="n">
-        <v>15.3334455490112</v>
+        <v>15.3334445953369</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G607" t="n">
-        <v>14.8507919311523</v>
+        <v>14.850793838501</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G608" t="n">
-        <v>14.8507919311523</v>
+        <v>14.850793838501</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G609" t="n">
-        <v>15.686149597168</v>
+        <v>15.6861505508423</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>15.108811378479</v>
       </c>
       <c r="G611" t="n">
-        <v>14.4423961639404</v>
+        <v>14.4423952102661</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>18.0024013519287</v>
       </c>
       <c r="G612" t="n">
-        <v>17.2083549499512</v>
+        <v>17.2083568572998</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G613" t="n">
-        <v>16.4101276397705</v>
+        <v>16.4101257324219</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G614" t="n">
-        <v>16.4101276397705</v>
+        <v>16.4101257324219</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>16.2351741790771</v>
       </c>
       <c r="G616" t="n">
-        <v>15.5190773010254</v>
+        <v>15.5190782546997</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G617" t="n">
-        <v>16.1688003540039</v>
+        <v>16.1688041687012</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G618" t="n">
-        <v>15.7789640426636</v>
+        <v>15.7789649963379</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>16.8760375976562</v>
       </c>
       <c r="G620" t="n">
-        <v>16.1316738128662</v>
+        <v>16.1316757202148</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G622" t="n">
-        <v>16.4843788146973</v>
+        <v>16.4843826293945</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G624" t="n">
-        <v>16.3730010986328</v>
+        <v>16.3729991912842</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G625" t="n">
-        <v>16.8556518554688</v>
+        <v>16.8556499481201</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>17.4974803924561</v>
       </c>
       <c r="G626" t="n">
-        <v>16.7257061004639</v>
+        <v>16.7257080078125</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G631" t="n">
-        <v>16.3173084259033</v>
+        <v>16.317310333252</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>17.4974803924561</v>
       </c>
       <c r="G633" t="n">
-        <v>16.7257061004639</v>
+        <v>16.7257080078125</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G634" t="n">
-        <v>16.8370876312256</v>
+        <v>16.837085723877</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G638" t="n">
-        <v>16.7999591827393</v>
+        <v>16.7999572753906</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G639" t="n">
-        <v>16.3730010986328</v>
+        <v>16.3729991912842</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G640" t="n">
-        <v>16.7071437835693</v>
+        <v>16.7071418762207</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G643" t="n">
-        <v>16.7071437835693</v>
+        <v>16.7071418762207</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G645" t="n">
-        <v>17.4125537872314</v>
+        <v>17.4125556945801</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G646" t="n">
-        <v>17.7838230133057</v>
+        <v>17.7838249206543</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G649" t="n">
-        <v>17.8023872375488</v>
+        <v>17.8023891448975</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>18.7597846984863</v>
       </c>
       <c r="G650" t="n">
-        <v>17.9323310852051</v>
+        <v>17.9323329925537</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G651" t="n">
-        <v>16.7999591827393</v>
+        <v>16.7999572753906</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G652" t="n">
-        <v>16.5771980285645</v>
+        <v>16.5771999359131</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>17.2255992889404</v>
       </c>
       <c r="G655" t="n">
-        <v>16.4658184051514</v>
+        <v>16.4658203125</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G657" t="n">
-        <v>16.7071437835693</v>
+        <v>16.7071418762207</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>17.2255992889404</v>
       </c>
       <c r="G658" t="n">
-        <v>16.4658184051514</v>
+        <v>16.4658203125</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G663" t="n">
-        <v>16.3730010986328</v>
+        <v>16.3729991912842</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G664" t="n">
-        <v>16.3730010986328</v>
+        <v>16.3729991912842</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G668" t="n">
-        <v>16.1688003540039</v>
+        <v>16.1688041687012</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G669" t="n">
-        <v>15.7789640426636</v>
+        <v>15.7789649963379</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G672" t="n">
-        <v>16.7999591827393</v>
+        <v>16.7999572753906</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>17.6916809082031</v>
       </c>
       <c r="G673" t="n">
-        <v>16.911340713501</v>
+        <v>16.9113426208496</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G674" t="n">
-        <v>16.3173084259033</v>
+        <v>16.317310333252</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G680" t="n">
-        <v>16.5586338043213</v>
+        <v>16.5586318969727</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>16.4682159423828</v>
       </c>
       <c r="G683" t="n">
-        <v>15.7418384552002</v>
+        <v>15.7418403625488</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>16.8760375976562</v>
       </c>
       <c r="G685" t="n">
-        <v>16.1316738128662</v>
+        <v>16.1316757202148</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>16.3711166381836</v>
       </c>
       <c r="G686" t="n">
-        <v>15.6490230560303</v>
+        <v>15.6490240097046</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>16.2157554626465</v>
       </c>
       <c r="G687" t="n">
-        <v>15.5005149841309</v>
+        <v>15.5005140304565</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>16.9342975616455</v>
       </c>
       <c r="G688" t="n">
-        <v>16.1873626708984</v>
+        <v>16.1873645782471</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>16.6429977416992</v>
       </c>
       <c r="G689" t="n">
-        <v>15.9089107513428</v>
+        <v>15.9089136123657</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>16.6041564941406</v>
       </c>
       <c r="G691" t="n">
-        <v>15.8717823028564</v>
+        <v>15.871787071228</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G694" t="n">
-        <v>14.4238319396973</v>
+        <v>14.4238328933716</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>15.3418521881104</v>
       </c>
       <c r="G696" t="n">
-        <v>14.6651582717896</v>
+        <v>14.6651573181152</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G697" t="n">
-        <v>14.4238319396973</v>
+        <v>14.4238328933716</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>15.4389533996582</v>
       </c>
       <c r="G698" t="n">
-        <v>14.7579765319824</v>
+        <v>14.7579755783081</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G700" t="n">
-        <v>15.0364294052124</v>
+        <v>15.0364274978638</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>16.2545948028564</v>
       </c>
       <c r="G702" t="n">
-        <v>15.5376405715942</v>
+        <v>15.5376415252686</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>16.2934341430664</v>
       </c>
       <c r="G703" t="n">
-        <v>15.5747671127319</v>
+        <v>15.5747661590576</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>16.1380748748779</v>
       </c>
       <c r="G704" t="n">
-        <v>15.4262599945068</v>
+        <v>15.4262609481812</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>16.332275390625</v>
       </c>
       <c r="G705" t="n">
-        <v>15.6118955612183</v>
+        <v>15.6118974685669</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G711" t="n">
-        <v>15.7604055404663</v>
+        <v>15.760404586792</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>16.856616973877</v>
       </c>
       <c r="G712" t="n">
-        <v>16.1131076812744</v>
+        <v>16.113109588623</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G714" t="n">
-        <v>16.5771980285645</v>
+        <v>16.5771999359131</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G715" t="n">
-        <v>16.9855976104736</v>
+        <v>16.985595703125</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>17.8082008361816</v>
       </c>
       <c r="G716" t="n">
-        <v>17.0227222442627</v>
+        <v>17.0227241516113</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>18.4684829711914</v>
       </c>
       <c r="G721" t="n">
-        <v>17.6538791656494</v>
+        <v>17.653881072998</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G722" t="n">
-        <v>18.0065879821777</v>
+        <v>18.0065860748291</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>18.3325424194336</v>
       </c>
       <c r="G724" t="n">
-        <v>17.5239353179932</v>
+        <v>17.5239334106445</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>19.2064456939697</v>
       </c>
       <c r="G726" t="n">
-        <v>18.3592929840088</v>
+        <v>18.3592948913574</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>18.779203414917</v>
       </c>
       <c r="G727" t="n">
-        <v>17.9508934020996</v>
+        <v>17.9508972167969</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G728" t="n">
-        <v>17.7652587890625</v>
+        <v>17.7652626037598</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G731" t="n">
-        <v>16.9855976104736</v>
+        <v>16.985595703125</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>18.293701171875</v>
       </c>
       <c r="G734" t="n">
-        <v>17.4868087768555</v>
+        <v>17.4868068695068</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>18.4490623474121</v>
       </c>
       <c r="G735" t="n">
-        <v>17.6353149414062</v>
+        <v>17.6353187561035</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G739" t="n">
-        <v>19.3060302734375</v>
+        <v>19.3060321807861</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G742" t="n">
-        <v>20.4198417663574</v>
+        <v>20.4198398590088</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G744" t="n">
-        <v>20.1413898468018</v>
+        <v>20.1413879394531</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G747" t="n">
-        <v>20.1413898468018</v>
+        <v>20.1413879394531</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G748" t="n">
-        <v>20.0949821472168</v>
+        <v>20.0949802398682</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G749" t="n">
-        <v>20.4662494659424</v>
+        <v>20.466251373291</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G755" t="n">
-        <v>20.1413898468018</v>
+        <v>20.1413879394531</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G756" t="n">
-        <v>20.4662494659424</v>
+        <v>20.466251373291</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G757" t="n">
-        <v>20.4198417663574</v>
+        <v>20.4198398590088</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G759" t="n">
-        <v>20.6982936859131</v>
+        <v>20.6982917785645</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G760" t="n">
-        <v>20.0949821472168</v>
+        <v>20.0949802398682</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G761" t="n">
-        <v>19.9557552337646</v>
+        <v>19.955753326416</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G764" t="n">
-        <v>19.6308917999268</v>
+        <v>19.6308937072754</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>20.3910694122314</v>
       </c>
       <c r="G768" t="n">
-        <v>19.6061553955078</v>
+        <v>19.6061534881592</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G769" t="n">
-        <v>19.8395576477051</v>
+        <v>19.8395595550537</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G770" t="n">
-        <v>19.6528358459473</v>
+        <v>19.6528339385986</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G771" t="n">
-        <v>19.3260650634766</v>
+        <v>19.3260669708252</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G773" t="n">
-        <v>19.3727493286133</v>
+        <v>19.3727474212646</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G774" t="n">
-        <v>19.5594749450684</v>
+        <v>19.5594730377197</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G776" t="n">
-        <v>18.7192096710205</v>
+        <v>18.7192115783691</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G777" t="n">
-        <v>19.0459804534912</v>
+        <v>19.0459785461426</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G782" t="n">
-        <v>19.6528358459473</v>
+        <v>19.6528339385986</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G785" t="n">
-        <v>19.1393413543701</v>
+        <v>19.1393394470215</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G786" t="n">
-        <v>19.0459804534912</v>
+        <v>19.0459785461426</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G789" t="n">
-        <v>18.5044727325439</v>
+        <v>18.5044746398926</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>19.1287651062012</v>
       </c>
       <c r="G792" t="n">
-        <v>18.3924427032471</v>
+        <v>18.3924407958984</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G797" t="n">
-        <v>18.7192096710205</v>
+        <v>18.7192115783691</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>20.3910694122314</v>
       </c>
       <c r="G799" t="n">
-        <v>19.6061553955078</v>
+        <v>19.6061534881592</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>21.5077228546143</v>
       </c>
       <c r="G803" t="n">
-        <v>20.6798248291016</v>
+        <v>20.6798229217529</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G805" t="n">
-        <v>21.9402198791504</v>
+        <v>21.940221786499</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G807" t="n">
-        <v>22.8271636962891</v>
+        <v>22.8271656036377</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G808" t="n">
-        <v>23.0605716705322</v>
+        <v>23.0605735778809</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G809" t="n">
-        <v>23.3406581878662</v>
+        <v>23.3406620025635</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G810" t="n">
-        <v>23.0138893127441</v>
+        <v>23.0138912200928</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G811" t="n">
-        <v>22.9205284118652</v>
+        <v>22.9205265045166</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G814" t="n">
-        <v>23.6207466125488</v>
+        <v>23.6207485198975</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G816" t="n">
-        <v>23.0138893127441</v>
+        <v>23.0138912200928</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G817" t="n">
-        <v>22.8738479614258</v>
+        <v>22.8738460540771</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G818" t="n">
-        <v>22.6871204376221</v>
+        <v>22.6871223449707</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G819" t="n">
-        <v>22.7338027954102</v>
+        <v>22.7338008880615</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G820" t="n">
-        <v>23.0138893127441</v>
+        <v>23.0138912200928</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G821" t="n">
-        <v>23.6207466125488</v>
+        <v>23.6207485198975</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G822" t="n">
-        <v>23.3406581878662</v>
+        <v>23.3406620025635</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G824" t="n">
-        <v>23.3873405456543</v>
+        <v>23.3873424530029</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G825" t="n">
-        <v>22.8738479614258</v>
+        <v>22.8738460540771</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G826" t="n">
-        <v>22.7804832458496</v>
+        <v>22.780481338501</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G827" t="n">
-        <v>22.8271636962891</v>
+        <v>22.8271656036377</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G828" t="n">
-        <v>23.0605716705322</v>
+        <v>23.0605735778809</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G830" t="n">
-        <v>22.8271636962891</v>
+        <v>22.8271656036377</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G831" t="n">
-        <v>22.8271636962891</v>
+        <v>22.8271656036377</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G832" t="n">
-        <v>23.293981552124</v>
+        <v>23.2939796447754</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G833" t="n">
-        <v>22.7804832458496</v>
+        <v>22.780481338501</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G835" t="n">
-        <v>23.3406581878662</v>
+        <v>23.3406620025635</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G837" t="n">
-        <v>23.714111328125</v>
+        <v>23.7141094207764</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G838" t="n">
-        <v>22.8271636962891</v>
+        <v>22.8271656036377</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G840" t="n">
-        <v>21.5667705535889</v>
+        <v>21.5667724609375</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G842" t="n">
-        <v>21.8001747131348</v>
+        <v>21.8001766204834</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G843" t="n">
-        <v>21.4267253875732</v>
+        <v>21.4267272949219</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G845" t="n">
-        <v>20.7731876373291</v>
+        <v>20.7731857299805</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G847" t="n">
-        <v>20.6331424713135</v>
+        <v>20.6331443786621</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G848" t="n">
-        <v>20.446418762207</v>
+        <v>20.4464168548584</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G850" t="n">
-        <v>21.7068138122559</v>
+        <v>21.7068119049072</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G851" t="n">
-        <v>22.8738479614258</v>
+        <v>22.8738460540771</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G854" t="n">
-        <v>24.8344631195068</v>
+        <v>24.8344612121582</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G858" t="n">
-        <v>23.2472953796387</v>
+        <v>23.2472972869873</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G860" t="n">
-        <v>23.4807014465332</v>
+        <v>23.4807033538818</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G861" t="n">
-        <v>23.2472953796387</v>
+        <v>23.2472972869873</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G862" t="n">
-        <v>23.3406581878662</v>
+        <v>23.3406620025635</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G863" t="n">
-        <v>23.3873405456543</v>
+        <v>23.3873424530029</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G864" t="n">
-        <v>23.9941959381104</v>
+        <v>23.9941997528076</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G877" t="n">
-        <v>25.1145496368408</v>
+        <v>25.1145477294922</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G878" t="n">
-        <v>25.1145496368408</v>
+        <v>25.1145477294922</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G879" t="n">
-        <v>23.6207466125488</v>
+        <v>23.6207485198975</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G880" t="n">
-        <v>23.4807014465332</v>
+        <v>23.4807033538818</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G881" t="n">
-        <v>23.1539325714111</v>
+        <v>23.1539344787598</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G882" t="n">
-        <v>22.8738479614258</v>
+        <v>22.8738460540771</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>23.3040790557861</v>
       </c>
       <c r="G883" t="n">
-        <v>22.4070339202881</v>
+        <v>22.4070320129395</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G884" t="n">
-        <v>22.1269454956055</v>
+        <v>22.1269474029541</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G885" t="n">
-        <v>22.9672088623047</v>
+        <v>22.9672107696533</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G886" t="n">
-        <v>22.1269454956055</v>
+        <v>22.1269474029541</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G887" t="n">
-        <v>22.8271636962891</v>
+        <v>22.8271656036377</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G888" t="n">
-        <v>22.8738479614258</v>
+        <v>22.8738460540771</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G891" t="n">
-        <v>24.5543727874756</v>
+        <v>24.5543746948242</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G897" t="n">
-        <v>22.8738479614258</v>
+        <v>22.8738460540771</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G898" t="n">
-        <v>22.8738479614258</v>
+        <v>22.8738460540771</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G899" t="n">
-        <v>23.0605716705322</v>
+        <v>23.0605735778809</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G902" t="n">
-        <v>23.854154586792</v>
+        <v>23.8541564941406</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G904" t="n">
-        <v>24.6944179534912</v>
+        <v>24.6944198608398</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G905" t="n">
-        <v>24.8344631195068</v>
+        <v>24.8344612121582</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G906" t="n">
-        <v>24.4610118865967</v>
+        <v>24.461009979248</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G907" t="n">
-        <v>24.4610118865967</v>
+        <v>24.461009979248</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G908" t="n">
-        <v>23.854154586792</v>
+        <v>23.8541564941406</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G910" t="n">
-        <v>23.714111328125</v>
+        <v>23.7141094207764</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G911" t="n">
-        <v>23.4807014465332</v>
+        <v>23.4807033538818</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G914" t="n">
-        <v>24.9745044708252</v>
+        <v>24.9745063781738</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G916" t="n">
-        <v>23.4807014465332</v>
+        <v>23.4807033538818</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G917" t="n">
-        <v>22.7338027954102</v>
+        <v>22.7338008880615</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G918" t="n">
-        <v>23.3406581878662</v>
+        <v>23.3406620025635</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G920" t="n">
-        <v>22.7804832458496</v>
+        <v>22.780481338501</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G921" t="n">
-        <v>21.3800449371338</v>
+        <v>21.3800430297852</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G922" t="n">
-        <v>21.0532741546631</v>
+        <v>21.0532760620117</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G923" t="n">
-        <v>21.2866802215576</v>
+        <v>21.2866821289062</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G924" t="n">
-        <v>20.7731876373291</v>
+        <v>20.7731857299805</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G925" t="n">
-        <v>20.3063735961914</v>
+        <v>20.3063716888428</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G926" t="n">
-        <v>19.8395576477051</v>
+        <v>19.8395595550537</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G928" t="n">
-        <v>21.6601314544678</v>
+        <v>21.6601333618164</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G932" t="n">
-        <v>20.6331424713135</v>
+        <v>20.6331443786621</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G933" t="n">
-        <v>21.1933193206787</v>
+        <v>21.1933174133301</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G934" t="n">
-        <v>21.4734058380127</v>
+        <v>21.4734077453613</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G935" t="n">
-        <v>21.3800449371338</v>
+        <v>21.3800430297852</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G936" t="n">
-        <v>21.2399997711182</v>
+        <v>21.2399978637695</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G937" t="n">
-        <v>21.7068138122559</v>
+        <v>21.7068119049072</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G939" t="n">
-        <v>21.0532741546631</v>
+        <v>21.0532760620117</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G941" t="n">
-        <v>20.1196479797363</v>
+        <v>20.119649887085</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G942" t="n">
-        <v>20.2130126953125</v>
+        <v>20.2130107879639</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>19.8570175170898</v>
       </c>
       <c r="G943" t="n">
-        <v>19.092658996582</v>
+        <v>19.0926609039307</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G945" t="n">
-        <v>19.7461967468262</v>
+        <v>19.7461948394775</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G947" t="n">
-        <v>19.3260650634766</v>
+        <v>19.3260669708252</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>20.0026683807373</v>
       </c>
       <c r="G948" t="n">
-        <v>19.2327041625977</v>
+        <v>19.232702255249</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G949" t="n">
-        <v>18.0936794281006</v>
+        <v>18.093677520752</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>17.9053001403809</v>
       </c>
       <c r="G950" t="n">
-        <v>17.2160701751709</v>
+        <v>17.2160682678223</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G951" t="n">
-        <v>16.9359836578369</v>
+        <v>16.9359817504883</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G952" t="n">
-        <v>16.7119140625</v>
+        <v>16.7119121551514</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>18.9151439666748</v>
       </c>
       <c r="G953" t="n">
-        <v>18.1870422363281</v>
+        <v>18.1870403289795</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>18.7986240386963</v>
       </c>
       <c r="G954" t="n">
-        <v>18.0750045776367</v>
+        <v>18.0750064849854</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G955" t="n">
-        <v>18.541820526123</v>
+        <v>18.5418186187744</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G956" t="n">
-        <v>19.7928810119629</v>
+        <v>19.7928771972656</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G958" t="n">
-        <v>20.3063735961914</v>
+        <v>20.3063716888428</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G959" t="n">
-        <v>20.3063735961914</v>
+        <v>20.3063716888428</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G961" t="n">
-        <v>20.7731876373291</v>
+        <v>20.7731857299805</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G962" t="n">
-        <v>21.6601314544678</v>
+        <v>21.6601333618164</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G963" t="n">
-        <v>21.7068138122559</v>
+        <v>21.7068119049072</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G964" t="n">
-        <v>21.5200881958008</v>
+        <v>21.5200901031494</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G966" t="n">
-        <v>21.6601314544678</v>
+        <v>21.6601333618164</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G968" t="n">
-        <v>23.0138893127441</v>
+        <v>23.0138912200928</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G969" t="n">
-        <v>21.7068138122559</v>
+        <v>21.7068119049072</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G970" t="n">
-        <v>21.3333644866943</v>
+        <v>21.3333606719971</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G971" t="n">
-        <v>20.3530578613281</v>
+        <v>20.3530559539795</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G974" t="n">
-        <v>20.446418762207</v>
+        <v>20.4464168548584</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G976" t="n">
-        <v>20.3530578613281</v>
+        <v>20.3530559539795</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G978" t="n">
-        <v>20.3063735961914</v>
+        <v>20.3063716888428</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G979" t="n">
-        <v>20.3530578613281</v>
+        <v>20.3530559539795</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G980" t="n">
-        <v>20.446418762207</v>
+        <v>20.4464168548584</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G981" t="n">
-        <v>20.6331424713135</v>
+        <v>20.6331443786621</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G982" t="n">
-        <v>21.6601314544678</v>
+        <v>21.6601333618164</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G983" t="n">
-        <v>21.5667705535889</v>
+        <v>21.5667724609375</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G984" t="n">
-        <v>21.5200881958008</v>
+        <v>21.5200901031494</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G985" t="n">
-        <v>21.4734058380127</v>
+        <v>21.4734077453613</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G986" t="n">
-        <v>21.3800449371338</v>
+        <v>21.3800430297852</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G987" t="n">
-        <v>21.4267253875732</v>
+        <v>21.4267272949219</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G988" t="n">
-        <v>21.5200881958008</v>
+        <v>21.5200901031494</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G990" t="n">
-        <v>21.8001747131348</v>
+        <v>21.8001766204834</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G991" t="n">
-        <v>21.5667705535889</v>
+        <v>21.5667724609375</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G992" t="n">
-        <v>21.3333644866943</v>
+        <v>21.3333606719971</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G993" t="n">
-        <v>19.8862419128418</v>
+        <v>19.8862438201904</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G997" t="n">
-        <v>19.1393413543701</v>
+        <v>19.1393394470215</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1001" t="n">
-        <v>20.6331424713135</v>
+        <v>20.6331443786621</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1002" t="n">
-        <v>20.3530578613281</v>
+        <v>20.3530559539795</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1004" t="n">
-        <v>20.446418762207</v>
+        <v>20.4464168548584</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G1006" t="n">
-        <v>19.7461967468262</v>
+        <v>19.7461948394775</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G1009" t="n">
-        <v>21.5667705535889</v>
+        <v>21.5667724609375</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G1013" t="n">
-        <v>20.0729675292969</v>
+        <v>20.0729694366455</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>20.3910694122314</v>
       </c>
       <c r="G1017" t="n">
-        <v>19.6061553955078</v>
+        <v>19.6061534881592</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1019" t="n">
-        <v>18.2057151794434</v>
+        <v>18.2057132720947</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>18.5655822753906</v>
       </c>
       <c r="G1020" t="n">
-        <v>17.8509330749512</v>
+        <v>17.8509349822998</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G1021" t="n">
-        <v>17.7762489318848</v>
+        <v>17.7762470245361</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G1027" t="n">
-        <v>16.2852210998535</v>
+        <v>16.2852230072021</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>18.4102230072021</v>
       </c>
       <c r="G1032" t="n">
-        <v>17.8478507995605</v>
+        <v>17.8478527069092</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G1033" t="n">
-        <v>17.6972351074219</v>
+        <v>17.6972370147705</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1034" t="n">
-        <v>18.1490783691406</v>
+        <v>18.1490802764893</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1036" t="n">
-        <v>18.0549449920654</v>
+        <v>18.0549468994141</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G1037" t="n">
-        <v>18.8268489837646</v>
+        <v>18.826847076416</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G1038" t="n">
-        <v>18.5067901611328</v>
+        <v>18.5067920684814</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G1040" t="n">
-        <v>18.6574039459229</v>
+        <v>18.6574058532715</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>18.3908023834229</v>
       </c>
       <c r="G1042" t="n">
-        <v>17.8290233612061</v>
+        <v>17.8290214538574</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G1044" t="n">
-        <v>18.5067901611328</v>
+        <v>18.5067920684814</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G1047" t="n">
-        <v>19.7211246490479</v>
+        <v>19.7211227416992</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1048" t="n">
-        <v>20.0505924224854</v>
+        <v>20.0505905151367</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1050" t="n">
-        <v>20.7095336914062</v>
+        <v>20.7095317840576</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G1052" t="n">
-        <v>20.7566013336182</v>
+        <v>20.7565994262695</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1055" t="n">
-        <v>20.0505924224854</v>
+        <v>20.0505905151367</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1058" t="n">
-        <v>22.5451488494873</v>
+        <v>22.5451507568359</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1059" t="n">
-        <v>22.5451488494873</v>
+        <v>22.5451507568359</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1062" t="n">
-        <v>22.4510135650635</v>
+        <v>22.4510154724121</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G1066" t="n">
-        <v>21.5096740722656</v>
+        <v>21.509672164917</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1068" t="n">
-        <v>20.7095336914062</v>
+        <v>20.7095317840576</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G1076" t="n">
-        <v>19.5328559875488</v>
+        <v>19.5328540802002</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1079" t="n">
-        <v>19.5799217224121</v>
+        <v>19.5799198150635</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>20.0512180328369</v>
       </c>
       <c r="G1081" t="n">
-        <v>19.438720703125</v>
+        <v>19.4387187957764</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1086" t="n">
-        <v>18.9209804534912</v>
+        <v>18.9209823608398</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>19.0122451782227</v>
       </c>
       <c r="G1087" t="n">
-        <v>18.4314842224121</v>
+        <v>18.4314823150635</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G1088" t="n">
-        <v>18.2432155609131</v>
+        <v>18.2432136535645</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G1089" t="n">
-        <v>17.8101978302002</v>
+        <v>17.8101997375488</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G1091" t="n">
-        <v>17.6031036376953</v>
+        <v>17.6031017303467</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1093" t="n">
-        <v>18.0549449920654</v>
+        <v>18.0549468994141</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>18.2354412078857</v>
       </c>
       <c r="G1095" t="n">
-        <v>17.678409576416</v>
+        <v>17.6784076690674</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G1096" t="n">
-        <v>16.8876819610596</v>
+        <v>16.8876838684082</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1098" t="n">
-        <v>18.9680500030518</v>
+        <v>18.9680480957031</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G1099" t="n">
-        <v>19.9564590454102</v>
+        <v>19.9564571380615</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1100" t="n">
-        <v>18.9680500030518</v>
+        <v>18.9680480957031</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G1102" t="n">
-        <v>18.0361194610596</v>
+        <v>18.0361175537109</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>18.9734058380127</v>
       </c>
       <c r="G1104" t="n">
-        <v>18.3938312530518</v>
+        <v>18.3938293457031</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1105" t="n">
-        <v>18.0549449920654</v>
+        <v>18.0549468994141</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1108" t="n">
-        <v>18.1490783691406</v>
+        <v>18.1490802764893</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G1109" t="n">
-        <v>18.2432155609131</v>
+        <v>18.2432136535645</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1110" t="n">
-        <v>18.1490783691406</v>
+        <v>18.1490802764893</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1112" t="n">
-        <v>18.3561763763428</v>
+        <v>18.3561744689941</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1113" t="n">
-        <v>18.9209804534912</v>
+        <v>18.9209823608398</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1114" t="n">
-        <v>20.5212650299072</v>
+        <v>20.5212631225586</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1115" t="n">
-        <v>20.4741954803467</v>
+        <v>20.4741973876953</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G1118" t="n">
-        <v>20.7566013336182</v>
+        <v>20.7565994262695</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1120" t="n">
-        <v>20.5212650299072</v>
+        <v>20.5212631225586</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1121" t="n">
-        <v>20.0505924224854</v>
+        <v>20.0505905151367</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1122" t="n">
-        <v>20.4741954803467</v>
+        <v>20.4741973876953</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1124" t="n">
-        <v>20.7095336914062</v>
+        <v>20.7095317840576</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1128" t="n">
-        <v>24.0042304992676</v>
+        <v>24.0042324066162</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1130" t="n">
-        <v>23.2040882110596</v>
+        <v>23.2040901184082</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1131" t="n">
-        <v>23.2040882110596</v>
+        <v>23.2040901184082</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1132" t="n">
-        <v>23.2511558532715</v>
+        <v>23.2511577606201</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1134" t="n">
-        <v>23.2511558532715</v>
+        <v>23.2511577606201</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1138" t="n">
-        <v>22.5451488494873</v>
+        <v>22.5451507568359</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1139" t="n">
-        <v>21.9803428649902</v>
+        <v>21.9803447723389</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>23.4497299194336</v>
       </c>
       <c r="G1141" t="n">
-        <v>22.733419418335</v>
+        <v>22.7334175109863</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1144" t="n">
-        <v>21.9803428649902</v>
+        <v>21.9803447723389</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1146" t="n">
-        <v>22.686351776123</v>
+        <v>22.6863498687744</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1150" t="n">
-        <v>24.0042304992676</v>
+        <v>24.0042324066162</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G1152" t="n">
-        <v>23.0158195495605</v>
+        <v>23.0158214569092</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>22.9642276763916</v>
       </c>
       <c r="G1153" t="n">
-        <v>22.2627449035645</v>
+        <v>22.2627468109131</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G1154" t="n">
-        <v>21.8391418457031</v>
+        <v>21.8391437530518</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1155" t="n">
-        <v>22.686351776123</v>
+        <v>22.6863498687744</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1159" t="n">
-        <v>21.9803428649902</v>
+        <v>21.9803447723389</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1163" t="n">
-        <v>21.9803428649902</v>
+        <v>21.9803447723389</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1166" t="n">
-        <v>21.6508731842041</v>
+        <v>21.6508750915527</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G1169" t="n">
-        <v>21.4155387878418</v>
+        <v>21.4155368804932</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G1170" t="n">
-        <v>21.2272701263428</v>
+        <v>21.2272720336914</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G1172" t="n">
-        <v>21.7920761108398</v>
+        <v>21.7920780181885</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1173" t="n">
-        <v>21.6508731842041</v>
+        <v>21.6508750915527</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>22.9642276763916</v>
       </c>
       <c r="G1174" t="n">
-        <v>22.2627449035645</v>
+        <v>22.2627468109131</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1175" t="n">
-        <v>21.6508731842041</v>
+        <v>21.6508750915527</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1179" t="n">
-        <v>22.5451488494873</v>
+        <v>22.5451507568359</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.9803428649902</v>
+        <v>21.9803447723389</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G1182" t="n">
-        <v>21.7920761108398</v>
+        <v>21.7920780181885</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1185" t="n">
-        <v>23.3452892303467</v>
+        <v>23.3452911376953</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G1187" t="n">
-        <v>24.5219669342041</v>
+        <v>24.5219688415527</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G1188" t="n">
-        <v>23.8159599304199</v>
+        <v>23.8159618377686</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1189" t="n">
-        <v>23.2040882110596</v>
+        <v>23.2040901184082</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.757303237915</v>
+        <v>24.7573051452637</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G1195" t="n">
-        <v>24.569034576416</v>
+        <v>24.5690364837646</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1197" t="n">
-        <v>24.0042304992676</v>
+        <v>24.0042324066162</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1198" t="n">
-        <v>24.4278335571289</v>
+        <v>24.4278354644775</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G1210" t="n">
-        <v>25.1809062957764</v>
+        <v>25.1809101104736</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1214" t="n">
-        <v>23.2040882110596</v>
+        <v>23.2040901184082</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1215" t="n">
-        <v>23.3923568725586</v>
+        <v>23.39235496521</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1217" t="n">
-        <v>22.9687538146973</v>
+        <v>22.9687519073486</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1223" t="n">
-        <v>23.3452892303467</v>
+        <v>23.3452911376953</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1236" t="n">
-        <v>22.4510135650635</v>
+        <v>22.4510154724121</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1238" t="n">
-        <v>22.686351776123</v>
+        <v>22.6863498687744</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1240" t="n">
-        <v>21.9803428649902</v>
+        <v>21.9803447723389</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G1243" t="n">
-        <v>22.498083114624</v>
+        <v>22.4980812072754</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1247" t="n">
-        <v>22.4510135650635</v>
+        <v>22.4510154724121</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G1248" t="n">
-        <v>22.498083114624</v>
+        <v>22.4980812072754</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1249" t="n">
-        <v>23.2511558532715</v>
+        <v>23.2511577606201</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1252" t="n">
-        <v>23.3923568725586</v>
+        <v>23.39235496521</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1254" t="n">
-        <v>22.9687538146973</v>
+        <v>22.9687519073486</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1257" t="n">
-        <v>22.9687538146973</v>
+        <v>22.9687519073486</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1261" t="n">
-        <v>22.4510135650635</v>
+        <v>22.4510154724121</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1262" t="n">
-        <v>22.686351776123</v>
+        <v>22.6863498687744</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1266" t="n">
-        <v>24.4278335571289</v>
+        <v>24.4278354644775</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G1267" t="n">
-        <v>24.8985061645508</v>
+        <v>24.8985042572021</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>27.3337421417236</v>
       </c>
       <c r="G1278" t="n">
-        <v>26.4987850189209</v>
+        <v>26.4987869262695</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1280" t="n">
-        <v>25.5798091888428</v>
+        <v>25.5798110961914</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G1281" t="n">
-        <v>25.4850692749023</v>
+        <v>25.485071182251</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1282" t="n">
-        <v>25.5798091888428</v>
+        <v>25.5798110961914</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1285" t="n">
-        <v>25.5798091888428</v>
+        <v>25.5798110961914</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1286" t="n">
-        <v>25.7219200134277</v>
+        <v>25.7219181060791</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1291" t="n">
-        <v>25.7219200134277</v>
+        <v>25.7219181060791</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G1294" t="n">
-        <v>25.4850692749023</v>
+        <v>25.485071182251</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>26.2656402587891</v>
       </c>
       <c r="G1295" t="n">
-        <v>25.6271800994873</v>
+        <v>25.6271820068359</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G1296" t="n">
-        <v>24.9640007019043</v>
+        <v>24.9639987945557</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G1297" t="n">
-        <v>25.0587406158447</v>
+        <v>25.0587387084961</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G1303" t="n">
-        <v>24.2060775756836</v>
+        <v>24.2060794830322</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G1306" t="n">
-        <v>24.2060775756836</v>
+        <v>24.2060794830322</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1307" t="n">
-        <v>24.7745208740234</v>
+        <v>24.7745189666748</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G1309" t="n">
-        <v>24.6797771453857</v>
+        <v>24.6797790527344</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1312" t="n">
-        <v>24.3481884002686</v>
+        <v>24.3481864929199</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1318" t="n">
-        <v>23.5428981781006</v>
+        <v>23.542896270752</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1319" t="n">
-        <v>23.6850090026855</v>
+        <v>23.6850070953369</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G1320" t="n">
-        <v>24.2060775756836</v>
+        <v>24.2060794830322</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1326" t="n">
-        <v>23.5428981781006</v>
+        <v>23.542896270752</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1327" t="n">
-        <v>23.874490737915</v>
+        <v>23.8744888305664</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1331" t="n">
-        <v>24.5850391387939</v>
+        <v>24.5850410461426</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1333" t="n">
-        <v>24.7745208740234</v>
+        <v>24.7745189666748</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1334" t="n">
-        <v>25.5798091888428</v>
+        <v>25.5798110961914</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G1335" t="n">
-        <v>24.9640007019043</v>
+        <v>24.9639987945557</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1336" t="n">
-        <v>23.874490737915</v>
+        <v>23.8744888305664</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1337" t="n">
-        <v>23.4955272674561</v>
+        <v>23.4955291748047</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1338" t="n">
-        <v>23.3060474395752</v>
+        <v>23.3060493469238</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1339" t="n">
-        <v>23.0691986083984</v>
+        <v>23.0691967010498</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1340" t="n">
-        <v>23.0691986083984</v>
+        <v>23.0691967010498</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1341" t="n">
-        <v>23.0691986083984</v>
+        <v>23.0691967010498</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>23.3040790557861</v>
       </c>
       <c r="G1343" t="n">
-        <v>22.7376079559326</v>
+        <v>22.7376098632812</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G1346" t="n">
-        <v>21.0322875976562</v>
+        <v>21.0322895050049</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1348" t="n">
-        <v>20.7954368591309</v>
+        <v>20.7954349517822</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1355" t="n">
-        <v>20.7954368591309</v>
+        <v>20.7954349517822</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G1358" t="n">
-        <v>19.9427757263184</v>
+        <v>19.942777633667</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1364" t="n">
-        <v>20.7954368591309</v>
+        <v>20.7954349517822</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>18.9734058380127</v>
       </c>
       <c r="G1367" t="n">
-        <v>18.5122051239014</v>
+        <v>18.5122032165527</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>18.0218200683594</v>
       </c>
       <c r="G1372" t="n">
-        <v>17.5837478637695</v>
+        <v>17.5837497711182</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>18.1966018676758</v>
       </c>
       <c r="G1373" t="n">
-        <v>17.7542819976807</v>
+        <v>17.7542839050293</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>19.1093444824219</v>
       </c>
       <c r="G1374" t="n">
-        <v>18.6448364257812</v>
+        <v>18.6448383331299</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1378" t="n">
-        <v>19.7059288024902</v>
+        <v>19.7059268951416</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1397" t="n">
-        <v>22.636058807373</v>
+        <v>22.6360607147217</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1402" t="n">
-        <v>21.6603679656982</v>
+        <v>21.6603660583496</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>23.25</v>
       </c>
       <c r="G1420" t="n">
-        <v>22.6848411560059</v>
+        <v>22.6848430633545</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>21.6603679656982</v>
+        <v>21.6603660583496</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1430" t="n">
-        <v>21.5627975463867</v>
+        <v>21.5627994537354</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1439" t="n">
-        <v>21.8067207336426</v>
+        <v>21.8067226409912</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1441" t="n">
-        <v>21.5627975463867</v>
+        <v>21.5627994537354</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1447" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1448" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1451" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1452" t="n">
-        <v>21.6603679656982</v>
+        <v>21.6603660583496</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1453" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1454" t="n">
-        <v>21.6603679656982</v>
+        <v>21.6603660583496</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>22</v>
       </c>
       <c r="G1456" t="n">
-        <v>21.4652290344238</v>
+        <v>21.4652271270752</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1457" t="n">
-        <v>21.074951171875</v>
+        <v>21.0749530792236</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1458" t="n">
-        <v>20.8798122406006</v>
+        <v>20.879810333252</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1459" t="n">
-        <v>21.3188743591309</v>
+        <v>21.3188762664795</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>19.6114139556885</v>
+        <v>19.6114120483398</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1469" t="n">
-        <v>19.0845375061035</v>
+        <v>19.0845394134521</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1470" t="n">
-        <v>19.0650253295898</v>
+        <v>19.0650272369385</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>19.5</v>
       </c>
       <c r="G1471" t="n">
-        <v>19.0259990692139</v>
+        <v>19.0259971618652</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1482" t="n">
-        <v>19.4553031921387</v>
+        <v>19.45530128479</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1488" t="n">
-        <v>18.6162071228027</v>
+        <v>18.6162052154541</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1492" t="n">
-        <v>17.9722480773926</v>
+        <v>17.9722499847412</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1493" t="n">
-        <v>17.4844017028809</v>
+        <v>17.4844036102295</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.0307922363281</v>
+        <v>18.0307903289795</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1496" t="n">
-        <v>17.6014881134033</v>
+        <v>17.6014862060547</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1500" t="n">
-        <v>18.5186367034912</v>
+        <v>18.5186386108398</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1504" t="n">
-        <v>18.6162071228027</v>
+        <v>18.6162052154541</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1505" t="n">
-        <v>17.3087787628174</v>
+        <v>17.308780670166</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1514" t="n">
-        <v>17.1526679992676</v>
+        <v>17.1526699066162</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1520" t="n">
-        <v>17.1136417388916</v>
+        <v>17.113639831543</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1524" t="n">
-        <v>17.1331558227539</v>
+        <v>17.1331539154053</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1525" t="n">
-        <v>16.6648216247559</v>
+        <v>16.6648235321045</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>18</v>
       </c>
       <c r="G1529" t="n">
-        <v>17.5624580383301</v>
+        <v>17.5624599456787</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1535" t="n">
-        <v>17.3087787628174</v>
+        <v>17.308780670166</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>17.5</v>
       </c>
       <c r="G1536" t="n">
-        <v>17.0746116638184</v>
+        <v>17.074613571167</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1542" t="n">
-        <v>16.8280143737793</v>
+        <v>16.8280124664307</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>16.5715484619141</v>
+        <v>16.5715465545654</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1546" t="n">
-        <v>17.3803977966309</v>
+        <v>17.3803997039795</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1547" t="n">
-        <v>17.4987678527832</v>
+        <v>17.4987659454346</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1553" t="n">
-        <v>17.0844764709473</v>
+        <v>17.0844783782959</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1554" t="n">
-        <v>17.5974063873291</v>
+        <v>17.5974082946777</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1557" t="n">
-        <v>17.3212127685547</v>
+        <v>17.3212146759033</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1562" t="n">
-        <v>16.5715484619141</v>
+        <v>16.5715465545654</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1563" t="n">
-        <v>16.6307315826416</v>
+        <v>16.6307334899902</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1564" t="n">
-        <v>16.8280143737793</v>
+        <v>16.8280124664307</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1567" t="n">
-        <v>15.5654182434082</v>
+        <v>15.5654191970825</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="n">
-        <v>15.6837863922119</v>
+        <v>15.6837873458862</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>16.5</v>
       </c>
       <c r="G1570" t="n">
-        <v>16.2756290435791</v>
+        <v>16.2756271362305</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1571" t="n">
-        <v>16.2361717224121</v>
+        <v>16.2361698150635</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1572" t="n">
-        <v>15.9205236434937</v>
+        <v>15.920521736145</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1573" t="n">
-        <v>16.0191631317139</v>
+        <v>16.0191650390625</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>16.3742694854736</v>
+        <v>16.374267578125</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1575" t="n">
-        <v>16.867467880249</v>
+        <v>16.8674697875977</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1578" t="n">
-        <v>17.4593105316162</v>
+        <v>17.4593124389648</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1579" t="n">
-        <v>17.1042041778564</v>
+        <v>17.1042060852051</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1583" t="n">
-        <v>17.5579490661621</v>
+        <v>17.5579509735107</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1588" t="n">
-        <v>16.867467880249</v>
+        <v>16.8674697875977</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1590" t="n">
-        <v>16.7491016387939</v>
+        <v>16.7490997314453</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1594" t="n">
-        <v>16.9858379364014</v>
+        <v>16.9858360290527</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1595" t="n">
-        <v>17.5579490661621</v>
+        <v>17.5579509735107</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1596" t="n">
-        <v>17.8144149780273</v>
+        <v>17.8144130706787</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1605" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1609" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1612" t="n">
-        <v>19.1361923217773</v>
+        <v>19.136194229126</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1613" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1615" t="n">
-        <v>18.761360168457</v>
+        <v>18.7613620758057</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1618" t="n">
-        <v>19.1361923217773</v>
+        <v>19.136194229126</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1621" t="n">
-        <v>19.4518413543701</v>
+        <v>19.4518394470215</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1622" t="n">
-        <v>19.0770072937012</v>
+        <v>19.0770092010498</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1630" t="n">
-        <v>18.5640811920166</v>
+        <v>18.564079284668</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1634" t="n">
-        <v>18.0511512756348</v>
+        <v>18.0511493682861</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1635" t="n">
-        <v>16.9858379364014</v>
+        <v>16.9858360290527</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1636" t="n">
-        <v>17.5974063873291</v>
+        <v>17.5974082946777</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1644" t="n">
-        <v>17.3803977966309</v>
+        <v>17.3803997039795</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1645" t="n">
-        <v>17.9130554199219</v>
+        <v>17.9130535125732</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1652" t="n">
-        <v>18.4457111358643</v>
+        <v>18.4457130432129</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1655" t="n">
-        <v>18.4457111358643</v>
+        <v>18.4457130432129</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1656" t="n">
-        <v>18.800817489624</v>
+        <v>18.8008155822754</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>19.294017791748</v>
+        <v>19.2940158843994</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1659" t="n">
-        <v>19.0770072937012</v>
+        <v>19.0770092010498</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1662" t="n">
-        <v>17.9130554199219</v>
+        <v>17.9130535125732</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1665" t="n">
-        <v>17.9525127410889</v>
+        <v>17.9525108337402</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1677" t="n">
-        <v>17.6171340942383</v>
+        <v>17.6171360015869</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1680" t="n">
-        <v>18.800817489624</v>
+        <v>18.8008155822754</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1681" t="n">
-        <v>18.8600006103516</v>
+        <v>18.8600025177002</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1682" t="n">
-        <v>18.8600006103516</v>
+        <v>18.8600025177002</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1684" t="n">
-        <v>18.8600006103516</v>
+        <v>18.8600025177002</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1685" t="n">
-        <v>19.1361923217773</v>
+        <v>19.136194229126</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1691" t="n">
-        <v>19.1559200286865</v>
+        <v>19.1559219360352</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1692" t="n">
-        <v>19.4912986755371</v>
+        <v>19.4912967681885</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1693" t="n">
-        <v>19.1559200286865</v>
+        <v>19.1559219360352</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1699" t="n">
-        <v>21.0103569030762</v>
+        <v>21.0103549957275</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>21</v>
       </c>
       <c r="G1705" t="n">
-        <v>20.7144355773926</v>
+        <v>20.7144374847412</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>20.75</v>
       </c>
       <c r="G1706" t="n">
-        <v>20.4678344726562</v>
+        <v>20.4678363800049</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1712" t="n">
-        <v>18.800817489624</v>
+        <v>18.8008155822754</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1715" t="n">
-        <v>20.6651153564453</v>
+        <v>20.6651172637939</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1717" t="n">
-        <v>19.3926582336426</v>
+        <v>19.3926563262939</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>20</v>
       </c>
       <c r="G1718" t="n">
-        <v>19.7280349731445</v>
+        <v>19.7280330657959</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1720" t="n">
-        <v>17.8933277130127</v>
+        <v>17.8933258056641</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1724" t="n">
-        <v>18.761360168457</v>
+        <v>18.7613620758057</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1729" t="n">
-        <v>17.3014850616455</v>
+        <v>17.3014869689941</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1731" t="n">
-        <v>16.6307315826416</v>
+        <v>16.6307334899902</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1732" t="n">
-        <v>16.5123653411865</v>
+        <v>16.5123634338379</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>16.5</v>
       </c>
       <c r="G1734" t="n">
-        <v>16.2756290435791</v>
+        <v>16.2756271362305</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>15</v>
       </c>
       <c r="G1736" t="n">
-        <v>14.7960252761841</v>
+        <v>14.7960262298584</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1740" t="n">
-        <v>15.6837863922119</v>
+        <v>15.6837873458862</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1742" t="n">
-        <v>16.6307315826416</v>
+        <v>16.6307334899902</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1743" t="n">
-        <v>16.3742694854736</v>
+        <v>16.374267578125</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1747" t="n">
-        <v>16.9858379364014</v>
+        <v>16.9858360290527</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1748" t="n">
-        <v>17.1042041778564</v>
+        <v>17.1042060852051</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1758" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1759" t="n">
-        <v>20.1719169616699</v>
+        <v>20.1719150543213</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1761" t="n">
-        <v>19.3926582336426</v>
+        <v>19.3926563262939</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>21</v>
       </c>
       <c r="G1763" t="n">
-        <v>20.7144355773926</v>
+        <v>20.7144374847412</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>20.75</v>
       </c>
       <c r="G1764" t="n">
-        <v>20.4678344726562</v>
+        <v>20.4678363800049</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1766" t="n">
-        <v>20.6157970428467</v>
+        <v>20.615795135498</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1767" t="n">
-        <v>20.1719169616699</v>
+        <v>20.1719150543213</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1768" t="n">
-        <v>20.6157970428467</v>
+        <v>20.615795135498</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1772" t="n">
-        <v>20.418514251709</v>
+        <v>20.4185161590576</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>20.75</v>
       </c>
       <c r="G1773" t="n">
-        <v>20.4678344726562</v>
+        <v>20.4678363800049</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1784" t="n">
-        <v>22.2433567047119</v>
+        <v>22.2433586120605</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1785" t="n">
-        <v>22.3419990539551</v>
+        <v>22.3419971466064</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -55532,7 +55532,7 @@
         <v>27.75</v>
       </c>
       <c r="D2122" t="n">
-        <v>25.75</v>
+        <v>25.7000007629395</v>
       </c>
       <c r="E2122" t="n">
         <v>27.75</v>
@@ -55544,6 +55544,32 @@
         <v>25.7000007629395</v>
       </c>
       <c r="H2122" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2123" t="n">
+        <v>89328</v>
+      </c>
+      <c r="C2123" t="n">
+        <v>27</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>26.0499992370605</v>
+      </c>
+      <c r="E2123" t="n">
+        <v>26.0499992370605</v>
+      </c>
+      <c r="F2123" t="n">
+        <v>26.6000003814697</v>
+      </c>
+      <c r="G2123" t="n">
+        <v>26.6000003814697</v>
+      </c>
+      <c r="H2123" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G2" t="n">
-        <v>7.53173303604126</v>
+        <v>7.53173208236694</v>
       </c>
       <c r="H2" t="n">
         <v>3452297</v>
@@ -456,7 +456,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G3" t="n">
-        <v>7.85126066207886</v>
+        <v>7.8512601852417</v>
       </c>
       <c r="H3" t="n">
         <v>1125391</v>
@@ -485,7 +485,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G4" t="n">
-        <v>7.7599663734436</v>
+        <v>7.75996541976929</v>
       </c>
       <c r="H4" t="n">
         <v>686773</v>
@@ -514,7 +514,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G5" t="n">
-        <v>7.7599663734436</v>
+        <v>7.75996541976929</v>
       </c>
       <c r="H5" t="n">
         <v>360346</v>
@@ -543,7 +543,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G6" t="n">
-        <v>7.66867351531982</v>
+        <v>7.66867399215698</v>
       </c>
       <c r="H6" t="n">
         <v>211023</v>
@@ -572,7 +572,7 @@
         <v>8.1253547668457</v>
       </c>
       <c r="G7" t="n">
-        <v>7.63945817947388</v>
+        <v>7.63945770263672</v>
       </c>
       <c r="H7" t="n">
         <v>72296</v>
@@ -601,7 +601,7 @@
         <v>8.31955623626709</v>
       </c>
       <c r="G8" t="n">
-        <v>7.82204580307007</v>
+        <v>7.82204675674438</v>
       </c>
       <c r="H8" t="n">
         <v>85887</v>
@@ -630,7 +630,7 @@
         <v>8.41859817504883</v>
       </c>
       <c r="G9" t="n">
-        <v>7.91516637802124</v>
+        <v>7.91516494750977</v>
       </c>
       <c r="H9" t="n">
         <v>85323</v>
@@ -688,7 +688,7 @@
         <v>8.42830753326416</v>
       </c>
       <c r="G11" t="n">
-        <v>7.92429447174072</v>
+        <v>7.92429351806641</v>
       </c>
       <c r="H11" t="n">
         <v>19928</v>
@@ -717,7 +717,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G12" t="n">
-        <v>7.53173303604126</v>
+        <v>7.53173208236694</v>
       </c>
       <c r="H12" t="n">
         <v>75575</v>
@@ -746,7 +746,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G13" t="n">
-        <v>7.53173303604126</v>
+        <v>7.53173208236694</v>
       </c>
       <c r="H13" t="n">
         <v>73138</v>
@@ -804,7 +804,7 @@
         <v>7.71656322479248</v>
       </c>
       <c r="G15" t="n">
-        <v>7.25511264801025</v>
+        <v>7.2551121711731</v>
       </c>
       <c r="H15" t="n">
         <v>329290</v>
@@ -862,7 +862,7 @@
         <v>7.88940191268921</v>
       </c>
       <c r="G17" t="n">
-        <v>7.41761445999146</v>
+        <v>7.41761493682861</v>
       </c>
       <c r="H17" t="n">
         <v>18836</v>
@@ -891,7 +891,7 @@
         <v>8.00106716156006</v>
       </c>
       <c r="G18" t="n">
-        <v>7.52260303497314</v>
+        <v>7.5226035118103</v>
       </c>
       <c r="H18" t="n">
         <v>83534</v>
@@ -978,7 +978,7 @@
         <v>7.97193717956543</v>
       </c>
       <c r="G21" t="n">
-        <v>7.49521541595459</v>
+        <v>7.49521446228027</v>
       </c>
       <c r="H21" t="n">
         <v>14400</v>
@@ -1007,7 +1007,7 @@
         <v>8.08068943023682</v>
       </c>
       <c r="G22" t="n">
-        <v>7.59746360778809</v>
+        <v>7.59746313095093</v>
       </c>
       <c r="H22" t="n">
         <v>16520</v>
@@ -1065,7 +1065,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G24" t="n">
-        <v>7.66867351531982</v>
+        <v>7.66867399215698</v>
       </c>
       <c r="H24" t="n">
         <v>80661</v>
@@ -1094,7 +1094,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G25" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561399459839</v>
       </c>
       <c r="H25" t="n">
         <v>57598</v>
@@ -1123,7 +1123,7 @@
         <v>8.37101936340332</v>
       </c>
       <c r="G26" t="n">
-        <v>7.87043237686157</v>
+        <v>7.87043142318726</v>
       </c>
       <c r="H26" t="n">
         <v>12597</v>
@@ -1152,7 +1152,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G27" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561399459839</v>
       </c>
       <c r="H27" t="n">
         <v>7454</v>
@@ -1181,7 +1181,7 @@
         <v>8.45743942260742</v>
       </c>
       <c r="G28" t="n">
-        <v>7.95168447494507</v>
+        <v>7.95168399810791</v>
       </c>
       <c r="H28" t="n">
         <v>134473</v>
@@ -1210,7 +1210,7 @@
         <v>8.31178760528564</v>
       </c>
       <c r="G29" t="n">
-        <v>7.81474208831787</v>
+        <v>7.81474256515503</v>
       </c>
       <c r="H29" t="n">
         <v>129981</v>
@@ -1239,7 +1239,7 @@
         <v>8.47394561767578</v>
       </c>
       <c r="G30" t="n">
-        <v>7.96720409393311</v>
+        <v>7.96720361709595</v>
       </c>
       <c r="H30" t="n">
         <v>238620</v>
@@ -1268,7 +1268,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G31" t="n">
-        <v>7.85126066207886</v>
+        <v>7.8512601852417</v>
       </c>
       <c r="H31" t="n">
         <v>21511</v>
@@ -1297,7 +1297,7 @@
         <v>8.25741195678711</v>
       </c>
       <c r="G32" t="n">
-        <v>7.7636194229126</v>
+        <v>7.76361989974976</v>
       </c>
       <c r="H32" t="n">
         <v>19336</v>
@@ -1326,7 +1326,7 @@
         <v>8.20497798919678</v>
       </c>
       <c r="G33" t="n">
-        <v>7.71431970596313</v>
+        <v>7.71431922912598</v>
       </c>
       <c r="H33" t="n">
         <v>19958</v>
@@ -1355,7 +1355,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G34" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561399459839</v>
       </c>
       <c r="H34" t="n">
         <v>33613</v>
@@ -1384,7 +1384,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G35" t="n">
-        <v>7.66867351531982</v>
+        <v>7.66867399215698</v>
       </c>
       <c r="H35" t="n">
         <v>126429</v>
@@ -1413,7 +1413,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G36" t="n">
-        <v>7.66867351531982</v>
+        <v>7.66867399215698</v>
       </c>
       <c r="H36" t="n">
         <v>13515</v>
@@ -1442,7 +1442,7 @@
         <v>8.31178760528564</v>
       </c>
       <c r="G37" t="n">
-        <v>7.81474208831787</v>
+        <v>7.81474256515503</v>
       </c>
       <c r="H37" t="n">
         <v>10519</v>
@@ -1471,7 +1471,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G38" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561399459839</v>
       </c>
       <c r="H38" t="n">
         <v>50515</v>
@@ -1500,7 +1500,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G39" t="n">
-        <v>7.85126066207886</v>
+        <v>7.8512601852417</v>
       </c>
       <c r="H39" t="n">
         <v>3319</v>
@@ -1558,7 +1558,7 @@
         <v>8.12923908233643</v>
       </c>
       <c r="G41" t="n">
-        <v>7.64311122894287</v>
+        <v>7.6431097984314</v>
       </c>
       <c r="H41" t="n">
         <v>69304</v>
@@ -1587,7 +1587,7 @@
         <v>8.23410797119141</v>
       </c>
       <c r="G42" t="n">
-        <v>7.74170827865601</v>
+        <v>7.74170732498169</v>
       </c>
       <c r="H42" t="n">
         <v>27604</v>
@@ -1616,7 +1616,7 @@
         <v>8.1855583190918</v>
       </c>
       <c r="G43" t="n">
-        <v>7.69606065750122</v>
+        <v>7.69606161117554</v>
       </c>
       <c r="H43" t="n">
         <v>12672</v>
@@ -1645,7 +1645,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G44" t="n">
-        <v>7.66867351531982</v>
+        <v>7.66867399215698</v>
       </c>
       <c r="H44" t="n">
         <v>23162</v>
@@ -1674,7 +1674,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G45" t="n">
-        <v>7.85126066207886</v>
+        <v>7.8512601852417</v>
       </c>
       <c r="H45" t="n">
         <v>15675</v>
@@ -1732,7 +1732,7 @@
         <v>7.99232816696167</v>
       </c>
       <c r="G47" t="n">
-        <v>7.5143871307373</v>
+        <v>7.51438665390015</v>
       </c>
       <c r="H47" t="n">
         <v>96901</v>
@@ -1790,7 +1790,7 @@
         <v>8.22634029388428</v>
       </c>
       <c r="G49" t="n">
-        <v>7.73440647125244</v>
+        <v>7.73440456390381</v>
       </c>
       <c r="H49" t="n">
         <v>27912</v>
@@ -1819,7 +1819,7 @@
         <v>8.1875</v>
       </c>
       <c r="G50" t="n">
-        <v>7.69788789749146</v>
+        <v>7.6978874206543</v>
       </c>
       <c r="H50" t="n">
         <v>28126</v>
@@ -1848,7 +1848,7 @@
         <v>8.44772911071777</v>
       </c>
       <c r="G51" t="n">
-        <v>7.94255447387695</v>
+        <v>7.94255542755127</v>
       </c>
       <c r="H51" t="n">
         <v>78995</v>
@@ -1964,7 +1964,7 @@
         <v>8.94293975830078</v>
       </c>
       <c r="G55" t="n">
-        <v>8.40815258026123</v>
+        <v>8.40815162658691</v>
       </c>
       <c r="H55" t="n">
         <v>93447</v>
@@ -1993,7 +1993,7 @@
         <v>8.96721458435059</v>
       </c>
       <c r="G56" t="n">
-        <v>8.43097496032715</v>
+        <v>8.43097400665283</v>
       </c>
       <c r="H56" t="n">
         <v>37346</v>
@@ -2022,7 +2022,7 @@
         <v>9.24977684020996</v>
       </c>
       <c r="G57" t="n">
-        <v>8.69664096832275</v>
+        <v>8.69663906097412</v>
       </c>
       <c r="H57" t="n">
         <v>80805</v>
@@ -2080,7 +2080,7 @@
         <v>9.08859062194824</v>
       </c>
       <c r="G59" t="n">
-        <v>8.54509258270264</v>
+        <v>8.54509353637695</v>
       </c>
       <c r="H59" t="n">
         <v>57537</v>
@@ -2138,7 +2138,7 @@
         <v>8.71960926055908</v>
       </c>
       <c r="G61" t="n">
-        <v>8.19817543029785</v>
+        <v>8.19817638397217</v>
       </c>
       <c r="H61" t="n">
         <v>19712</v>
@@ -2225,7 +2225,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G64" t="n">
-        <v>8.39902210235596</v>
+        <v>8.39902114868164</v>
       </c>
       <c r="H64" t="n">
         <v>50571</v>
@@ -2283,7 +2283,7 @@
         <v>9.24395084381104</v>
       </c>
       <c r="G66" t="n">
-        <v>8.691162109375</v>
+        <v>8.69116115570068</v>
       </c>
       <c r="H66" t="n">
         <v>43076</v>
@@ -2341,7 +2341,7 @@
         <v>9.15656089782715</v>
       </c>
       <c r="G68" t="n">
-        <v>8.60899829864502</v>
+        <v>8.60899925231934</v>
       </c>
       <c r="H68" t="n">
         <v>39006</v>
@@ -2399,7 +2399,7 @@
         <v>9.51583194732666</v>
       </c>
       <c r="G70" t="n">
-        <v>8.94678401947021</v>
+        <v>8.94678592681885</v>
       </c>
       <c r="H70" t="n">
         <v>51034</v>
@@ -2428,7 +2428,7 @@
         <v>9.51583194732666</v>
       </c>
       <c r="G71" t="n">
-        <v>8.94678401947021</v>
+        <v>8.94678592681885</v>
       </c>
       <c r="H71" t="n">
         <v>33820</v>
@@ -2457,7 +2457,7 @@
         <v>9.37115287780762</v>
       </c>
       <c r="G72" t="n">
-        <v>8.81075572967529</v>
+        <v>8.81075763702393</v>
       </c>
       <c r="H72" t="n">
         <v>39116</v>
@@ -2544,7 +2544,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G75" t="n">
-        <v>9.27544116973877</v>
+        <v>9.27544212341309</v>
       </c>
       <c r="H75" t="n">
         <v>612811</v>
@@ -2631,7 +2631,7 @@
         <v>9.50029563903809</v>
       </c>
       <c r="G78" t="n">
-        <v>8.93217849731445</v>
+        <v>8.93217754364014</v>
       </c>
       <c r="H78" t="n">
         <v>26567</v>
@@ -2660,7 +2660,7 @@
         <v>9.70614910125732</v>
       </c>
       <c r="G79" t="n">
-        <v>9.12572193145752</v>
+        <v>9.1257209777832</v>
       </c>
       <c r="H79" t="n">
         <v>25765</v>
@@ -2689,7 +2689,7 @@
         <v>9.57506275177002</v>
       </c>
       <c r="G80" t="n">
-        <v>9.00247383117676</v>
+        <v>9.00247478485107</v>
       </c>
       <c r="H80" t="n">
         <v>21310</v>
@@ -2776,7 +2776,7 @@
         <v>9.50320911407471</v>
       </c>
       <c r="G83" t="n">
-        <v>8.93491744995117</v>
+        <v>8.93491649627686</v>
       </c>
       <c r="H83" t="n">
         <v>21357</v>
@@ -2805,7 +2805,7 @@
         <v>9.55467224121094</v>
       </c>
       <c r="G84" t="n">
-        <v>8.98330211639404</v>
+        <v>8.98330307006836</v>
       </c>
       <c r="H84" t="n">
         <v>24808</v>
@@ -2892,7 +2892,7 @@
         <v>8.98954772949219</v>
       </c>
       <c r="G87" t="n">
-        <v>8.45197200775146</v>
+        <v>8.45197486877441</v>
       </c>
       <c r="H87" t="n">
         <v>53966</v>
@@ -2950,7 +2950,7 @@
         <v>8.43413352966309</v>
       </c>
       <c r="G89" t="n">
-        <v>7.92977094650269</v>
+        <v>7.92977142333984</v>
       </c>
       <c r="H89" t="n">
         <v>72833</v>
@@ -2979,7 +2979,7 @@
         <v>8.77689933776855</v>
       </c>
       <c r="G90" t="n">
-        <v>8.25203800201416</v>
+        <v>8.25203895568848</v>
       </c>
       <c r="H90" t="n">
         <v>32211</v>
@@ -3008,7 +3008,7 @@
         <v>8.88467979431152</v>
       </c>
       <c r="G91" t="n">
-        <v>8.35337448120117</v>
+        <v>8.3533763885498</v>
       </c>
       <c r="H91" t="n">
         <v>47197</v>
@@ -3066,7 +3066,7 @@
         <v>9.07888126373291</v>
       </c>
       <c r="G93" t="n">
-        <v>8.53596305847168</v>
+        <v>8.53596496582031</v>
       </c>
       <c r="H93" t="n">
         <v>63873</v>
@@ -3095,7 +3095,7 @@
         <v>9.12743091583252</v>
       </c>
       <c r="G94" t="n">
-        <v>8.58160877227783</v>
+        <v>8.58161067962646</v>
       </c>
       <c r="H94" t="n">
         <v>29067</v>
@@ -3124,7 +3124,7 @@
         <v>9.07888126373291</v>
       </c>
       <c r="G95" t="n">
-        <v>8.53596305847168</v>
+        <v>8.53596496582031</v>
       </c>
       <c r="H95" t="n">
         <v>54068</v>
@@ -3153,7 +3153,7 @@
         <v>9.30706596374512</v>
       </c>
       <c r="G96" t="n">
-        <v>8.75050258636475</v>
+        <v>8.75050449371338</v>
       </c>
       <c r="H96" t="n">
         <v>28672</v>
@@ -3211,7 +3211,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G98" t="n">
-        <v>7.80561304092407</v>
+        <v>7.80561399459839</v>
       </c>
       <c r="H98" t="n">
         <v>31873</v>
@@ -3240,7 +3240,7 @@
         <v>8.48462677001953</v>
       </c>
       <c r="G99" t="n">
-        <v>7.97724628448486</v>
+        <v>7.97724580764771</v>
       </c>
       <c r="H99" t="n">
         <v>22913</v>
@@ -3269,7 +3269,7 @@
         <v>7.97193717956543</v>
       </c>
       <c r="G100" t="n">
-        <v>7.49521541595459</v>
+        <v>7.49521446228027</v>
       </c>
       <c r="H100" t="n">
         <v>32370</v>
@@ -3298,7 +3298,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G101" t="n">
-        <v>7.7599663734436</v>
+        <v>7.75996541976929</v>
       </c>
       <c r="H101" t="n">
         <v>13973</v>
@@ -3327,7 +3327,7 @@
         <v>8.19041347503662</v>
       </c>
       <c r="G102" t="n">
-        <v>7.70062589645386</v>
+        <v>7.70062637329102</v>
       </c>
       <c r="H102" t="n">
         <v>33890</v>
@@ -3356,7 +3356,7 @@
         <v>8.3700475692749</v>
       </c>
       <c r="G103" t="n">
-        <v>7.8695182800293</v>
+        <v>7.86951732635498</v>
       </c>
       <c r="H103" t="n">
         <v>25306</v>
@@ -3385,7 +3385,7 @@
         <v>8.3700475692749</v>
       </c>
       <c r="G104" t="n">
-        <v>7.8695182800293</v>
+        <v>7.86951732635498</v>
       </c>
       <c r="H104" t="n">
         <v>30512</v>
@@ -3443,7 +3443,7 @@
         <v>9.27210998535156</v>
       </c>
       <c r="G106" t="n">
-        <v>8.71763801574707</v>
+        <v>8.71763706207275</v>
       </c>
       <c r="H106" t="n">
         <v>46620</v>
@@ -3472,7 +3472,7 @@
         <v>9.27502346038818</v>
       </c>
       <c r="G107" t="n">
-        <v>8.72037696838379</v>
+        <v>8.72037792205811</v>
       </c>
       <c r="H107" t="n">
         <v>77271</v>
@@ -3530,7 +3530,7 @@
         <v>8.98760604858398</v>
       </c>
       <c r="G109" t="n">
-        <v>8.45014572143555</v>
+        <v>8.45014762878418</v>
       </c>
       <c r="H109" t="n">
         <v>17509</v>
@@ -3588,7 +3588,7 @@
         <v>9.19443035125732</v>
       </c>
       <c r="G111" t="n">
-        <v>8.64460372924805</v>
+        <v>8.64460277557373</v>
       </c>
       <c r="H111" t="n">
         <v>53266</v>
@@ -3617,7 +3617,7 @@
         <v>9.06334495544434</v>
       </c>
       <c r="G112" t="n">
-        <v>8.52135562896729</v>
+        <v>8.5213565826416</v>
       </c>
       <c r="H112" t="n">
         <v>56861</v>
@@ -3646,7 +3646,7 @@
         <v>8.86817264556885</v>
       </c>
       <c r="G113" t="n">
-        <v>8.33785629272461</v>
+        <v>8.33785533905029</v>
       </c>
       <c r="H113" t="n">
         <v>94989</v>
@@ -3675,7 +3675,7 @@
         <v>8.81379699707031</v>
       </c>
       <c r="G114" t="n">
-        <v>8.28673076629639</v>
+        <v>8.28673267364502</v>
       </c>
       <c r="H114" t="n">
         <v>33903</v>
@@ -3704,7 +3704,7 @@
         <v>9.04586696624756</v>
       </c>
       <c r="G115" t="n">
-        <v>8.50492382049561</v>
+        <v>8.50492286682129</v>
       </c>
       <c r="H115" t="n">
         <v>61099</v>
@@ -3733,7 +3733,7 @@
         <v>9.2138500213623</v>
       </c>
       <c r="G116" t="n">
-        <v>8.66286182403564</v>
+        <v>8.66286373138428</v>
       </c>
       <c r="H116" t="n">
         <v>60391</v>
@@ -3762,7 +3762,7 @@
         <v>8.51084423065186</v>
       </c>
       <c r="G117" t="n">
-        <v>8.00189590454102</v>
+        <v>8.0018949508667</v>
       </c>
       <c r="H117" t="n">
         <v>101226</v>
@@ -3791,7 +3791,7 @@
         <v>8.49724960327148</v>
       </c>
       <c r="G118" t="n">
-        <v>7.98911476135254</v>
+        <v>7.98911285400391</v>
       </c>
       <c r="H118" t="n">
         <v>42084</v>
@@ -3907,7 +3907,7 @@
         <v>8.80700016021729</v>
       </c>
       <c r="G122" t="n">
-        <v>8.28034114837646</v>
+        <v>8.28034019470215</v>
       </c>
       <c r="H122" t="n">
         <v>51549</v>
@@ -3936,7 +3936,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G123" t="n">
-        <v>8.39902210235596</v>
+        <v>8.39902114868164</v>
       </c>
       <c r="H123" t="n">
         <v>89881</v>
@@ -3994,7 +3994,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G125" t="n">
-        <v>8.39902210235596</v>
+        <v>8.39902114868164</v>
       </c>
       <c r="H125" t="n">
         <v>508178</v>
@@ -4023,7 +4023,7 @@
         <v>9.42650032043457</v>
       </c>
       <c r="G126" t="n">
-        <v>8.86279487609863</v>
+        <v>8.86279582977295</v>
       </c>
       <c r="H126" t="n">
         <v>163957</v>
@@ -4052,7 +4052,7 @@
         <v>9.55078792572021</v>
       </c>
       <c r="G127" t="n">
-        <v>8.97964954376221</v>
+        <v>8.97965049743652</v>
       </c>
       <c r="H127" t="n">
         <v>112485</v>
@@ -4110,7 +4110,7 @@
         <v>9.52748394012451</v>
       </c>
       <c r="G129" t="n">
-        <v>8.95773887634277</v>
+        <v>8.95773983001709</v>
       </c>
       <c r="H129" t="n">
         <v>150488</v>
@@ -4139,7 +4139,7 @@
         <v>9.67119312286377</v>
       </c>
       <c r="G130" t="n">
-        <v>9.09285545349121</v>
+        <v>9.09285640716553</v>
       </c>
       <c r="H130" t="n">
         <v>32320</v>
@@ -4168,7 +4168,7 @@
         <v>9.35076236724854</v>
       </c>
       <c r="G131" t="n">
-        <v>8.79158782958984</v>
+        <v>8.79158592224121</v>
       </c>
       <c r="H131" t="n">
         <v>43129</v>
@@ -4197,7 +4197,7 @@
         <v>9.50029563903809</v>
       </c>
       <c r="G132" t="n">
-        <v>8.93217849731445</v>
+        <v>8.93217754364014</v>
       </c>
       <c r="H132" t="n">
         <v>25729</v>
@@ -4342,7 +4342,7 @@
         <v>8.77495670318604</v>
       </c>
       <c r="G137" t="n">
-        <v>8.25021362304688</v>
+        <v>8.25021266937256</v>
       </c>
       <c r="H137" t="n">
         <v>49854</v>
@@ -4371,7 +4371,7 @@
         <v>8.70018863677979</v>
       </c>
       <c r="G138" t="n">
-        <v>8.17991638183594</v>
+        <v>8.17991733551025</v>
       </c>
       <c r="H138" t="n">
         <v>33830</v>
@@ -4429,7 +4429,7 @@
         <v>8.80991268157959</v>
       </c>
       <c r="G140" t="n">
-        <v>8.28307914733887</v>
+        <v>8.28308010101318</v>
       </c>
       <c r="H140" t="n">
         <v>1874557</v>
@@ -4458,7 +4458,7 @@
         <v>8.66523265838623</v>
       </c>
       <c r="G141" t="n">
-        <v>8.14705085754395</v>
+        <v>8.14705181121826</v>
       </c>
       <c r="H141" t="n">
         <v>15104</v>
@@ -4516,7 +4516,7 @@
         <v>8.8798246383667</v>
       </c>
       <c r="G143" t="n">
-        <v>8.34881019592285</v>
+        <v>8.34881114959717</v>
       </c>
       <c r="H143" t="n">
         <v>25023</v>
@@ -4545,7 +4545,7 @@
         <v>8.7429141998291</v>
       </c>
       <c r="G144" t="n">
-        <v>8.22008609771729</v>
+        <v>8.2200870513916</v>
       </c>
       <c r="H144" t="n">
         <v>52218</v>
@@ -4574,7 +4574,7 @@
         <v>8.76815986633301</v>
       </c>
       <c r="G145" t="n">
-        <v>8.24382495880127</v>
+        <v>8.24382400512695</v>
       </c>
       <c r="H145" t="n">
         <v>27159</v>
@@ -4661,7 +4661,7 @@
         <v>8.98178005218506</v>
       </c>
       <c r="G148" t="n">
-        <v>8.44467067718506</v>
+        <v>8.44466972351074</v>
       </c>
       <c r="H148" t="n">
         <v>99143</v>
@@ -4690,7 +4690,7 @@
         <v>8.94293975830078</v>
       </c>
       <c r="G149" t="n">
-        <v>8.40815258026123</v>
+        <v>8.40815162658691</v>
       </c>
       <c r="H149" t="n">
         <v>78033</v>
@@ -4719,7 +4719,7 @@
         <v>8.91380977630615</v>
       </c>
       <c r="G150" t="n">
-        <v>8.38076400756836</v>
+        <v>8.38076210021973</v>
       </c>
       <c r="H150" t="n">
         <v>37840</v>
@@ -4748,7 +4748,7 @@
         <v>8.69047927856445</v>
       </c>
       <c r="G151" t="n">
-        <v>8.1707878112793</v>
+        <v>8.17078876495361</v>
       </c>
       <c r="H151" t="n">
         <v>15730</v>
@@ -4806,7 +4806,7 @@
         <v>8.82739067077637</v>
       </c>
       <c r="G153" t="n">
-        <v>8.29951190948486</v>
+        <v>8.29951286315918</v>
       </c>
       <c r="H153" t="n">
         <v>35901</v>
@@ -4893,7 +4893,7 @@
         <v>8.61474132537842</v>
       </c>
       <c r="G156" t="n">
-        <v>8.09957885742188</v>
+        <v>8.09958076477051</v>
       </c>
       <c r="H156" t="n">
         <v>15804</v>
@@ -4980,7 +4980,7 @@
         <v>8.90410041809082</v>
       </c>
       <c r="G159" t="n">
-        <v>8.37163352966309</v>
+        <v>8.3716344833374</v>
       </c>
       <c r="H159" t="n">
         <v>31397</v>
@@ -5009,7 +5009,7 @@
         <v>8.96430206298828</v>
       </c>
       <c r="G160" t="n">
-        <v>8.42823505401611</v>
+        <v>8.42823600769043</v>
       </c>
       <c r="H160" t="n">
         <v>66416</v>
@@ -5096,7 +5096,7 @@
         <v>9.26822566986084</v>
       </c>
       <c r="G163" t="n">
-        <v>8.71398448944092</v>
+        <v>8.71398544311523</v>
       </c>
       <c r="H163" t="n">
         <v>14598</v>
@@ -5154,7 +5154,7 @@
         <v>9.61584568023682</v>
       </c>
       <c r="G165" t="n">
-        <v>9.0408182144165</v>
+        <v>9.04081726074219</v>
       </c>
       <c r="H165" t="n">
         <v>44742</v>
@@ -5183,7 +5183,7 @@
         <v>9.57894706726074</v>
       </c>
       <c r="G166" t="n">
-        <v>9.00612735748291</v>
+        <v>9.00612545013428</v>
       </c>
       <c r="H166" t="n">
         <v>21729</v>
@@ -5212,7 +5212,7 @@
         <v>9.40222454071045</v>
       </c>
       <c r="G167" t="n">
-        <v>8.83997058868408</v>
+        <v>8.83997249603271</v>
       </c>
       <c r="H167" t="n">
         <v>18153</v>
@@ -5241,7 +5241,7 @@
         <v>9.51583194732666</v>
       </c>
       <c r="G168" t="n">
-        <v>8.94678401947021</v>
+        <v>8.94678592681885</v>
       </c>
       <c r="H168" t="n">
         <v>11146</v>
@@ -5270,7 +5270,7 @@
         <v>9.33522605895996</v>
       </c>
       <c r="G169" t="n">
-        <v>8.77697849273682</v>
+        <v>8.77697944641113</v>
       </c>
       <c r="H169" t="n">
         <v>11871</v>
@@ -5299,7 +5299,7 @@
         <v>9.48573112487793</v>
       </c>
       <c r="G170" t="n">
-        <v>8.91848278045654</v>
+        <v>8.91848468780518</v>
       </c>
       <c r="H170" t="n">
         <v>9464</v>
@@ -5328,7 +5328,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G171" t="n">
-        <v>8.99243068695068</v>
+        <v>8.99242973327637</v>
       </c>
       <c r="H171" t="n">
         <v>18448</v>
@@ -5357,7 +5357,7 @@
         <v>9.75858306884766</v>
       </c>
       <c r="G172" t="n">
-        <v>9.17502021789551</v>
+        <v>9.17501926422119</v>
       </c>
       <c r="H172" t="n">
         <v>58649</v>
@@ -5386,7 +5386,7 @@
         <v>9.72751140594482</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14580631256104</v>
+        <v>9.14580535888672</v>
       </c>
       <c r="H173" t="n">
         <v>31014</v>
@@ -5415,7 +5415,7 @@
         <v>9.89258098602295</v>
       </c>
       <c r="G174" t="n">
-        <v>9.30100440979004</v>
+        <v>9.30100345611572</v>
       </c>
       <c r="H174" t="n">
         <v>22663</v>
@@ -5473,7 +5473,7 @@
         <v>10.1547517776489</v>
       </c>
       <c r="G176" t="n">
-        <v>9.5474967956543</v>
+        <v>9.54749774932861</v>
       </c>
       <c r="H176" t="n">
         <v>24722</v>
@@ -5502,7 +5502,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G177" t="n">
-        <v>9.58584117889404</v>
+        <v>9.58584213256836</v>
       </c>
       <c r="H177" t="n">
         <v>18160</v>
@@ -5531,7 +5531,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G178" t="n">
-        <v>9.58584117889404</v>
+        <v>9.58584213256836</v>
       </c>
       <c r="H178" t="n">
         <v>16440</v>
@@ -5560,7 +5560,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G179" t="n">
-        <v>9.58584117889404</v>
+        <v>9.58584213256836</v>
       </c>
       <c r="H179" t="n">
         <v>13022</v>
@@ -5618,7 +5618,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G181" t="n">
-        <v>9.58584117889404</v>
+        <v>9.58584213256836</v>
       </c>
       <c r="H181" t="n">
         <v>12625</v>
@@ -5647,7 +5647,7 @@
         <v>10.1372737884521</v>
       </c>
       <c r="G182" t="n">
-        <v>9.53106498718262</v>
+        <v>9.5310640335083</v>
       </c>
       <c r="H182" t="n">
         <v>36436</v>
@@ -5676,7 +5676,7 @@
         <v>10.1897087097168</v>
       </c>
       <c r="G183" t="n">
-        <v>9.58036327362061</v>
+        <v>9.58036518096924</v>
       </c>
       <c r="H183" t="n">
         <v>13620</v>
@@ -5734,7 +5734,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G185" t="n">
-        <v>9.58584117889404</v>
+        <v>9.58584213256836</v>
       </c>
       <c r="H185" t="n">
         <v>8445</v>
@@ -5792,7 +5792,7 @@
         <v>10.0304641723633</v>
       </c>
       <c r="G187" t="n">
-        <v>9.43064308166504</v>
+        <v>9.43064212799072</v>
       </c>
       <c r="H187" t="n">
         <v>7232</v>
@@ -5821,7 +5821,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G188" t="n">
-        <v>9.58584117889404</v>
+        <v>9.58584213256836</v>
       </c>
       <c r="H188" t="n">
         <v>23356</v>
@@ -5850,7 +5850,7 @@
         <v>10.0498838424683</v>
       </c>
       <c r="G189" t="n">
-        <v>9.44890213012695</v>
+        <v>9.44890117645264</v>
       </c>
       <c r="H189" t="n">
         <v>32652</v>
@@ -5966,7 +5966,7 @@
         <v>9.64594745635986</v>
       </c>
       <c r="G193" t="n">
-        <v>9.06911849975586</v>
+        <v>9.06911945343018</v>
       </c>
       <c r="H193" t="n">
         <v>13422</v>
@@ -5995,7 +5995,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G194" t="n">
-        <v>8.99243068695068</v>
+        <v>8.99242973327637</v>
       </c>
       <c r="H194" t="n">
         <v>37882</v>
@@ -6082,7 +6082,7 @@
         <v>9.66536712646484</v>
       </c>
       <c r="G197" t="n">
-        <v>9.08737754821777</v>
+        <v>9.08737659454346</v>
       </c>
       <c r="H197" t="n">
         <v>16116</v>
@@ -6111,7 +6111,7 @@
         <v>9.57409191131592</v>
       </c>
       <c r="G198" t="n">
-        <v>9.00156211853027</v>
+        <v>9.00156021118164</v>
       </c>
       <c r="H198" t="n">
         <v>26236</v>
@@ -6227,7 +6227,7 @@
         <v>8.85263729095459</v>
       </c>
       <c r="G202" t="n">
-        <v>8.3232479095459</v>
+        <v>8.32324886322021</v>
       </c>
       <c r="H202" t="n">
         <v>36498</v>
@@ -6256,7 +6256,7 @@
         <v>9.25657367706299</v>
       </c>
       <c r="G203" t="n">
-        <v>8.70303058624268</v>
+        <v>8.70302867889404</v>
       </c>
       <c r="H203" t="n">
         <v>45319</v>
@@ -6314,7 +6314,7 @@
         <v>9.51680278778076</v>
       </c>
       <c r="G205" t="n">
-        <v>8.94769763946533</v>
+        <v>8.94769668579102</v>
       </c>
       <c r="H205" t="n">
         <v>19012</v>
@@ -6372,7 +6372,7 @@
         <v>9.67119312286377</v>
       </c>
       <c r="G207" t="n">
-        <v>9.09285545349121</v>
+        <v>9.09285640716553</v>
       </c>
       <c r="H207" t="n">
         <v>36508</v>
@@ -6430,7 +6430,7 @@
         <v>9.47699165344238</v>
       </c>
       <c r="G209" t="n">
-        <v>8.9102668762207</v>
+        <v>8.91026592254639</v>
       </c>
       <c r="H209" t="n">
         <v>16863</v>
@@ -6459,7 +6459,7 @@
         <v>9.47699165344238</v>
       </c>
       <c r="G210" t="n">
-        <v>8.9102668762207</v>
+        <v>8.91026592254639</v>
       </c>
       <c r="H210" t="n">
         <v>24429</v>
@@ -6488,7 +6488,7 @@
         <v>9.62264347076416</v>
       </c>
       <c r="G211" t="n">
-        <v>9.04720783233643</v>
+        <v>9.04720878601074</v>
       </c>
       <c r="H211" t="n">
         <v>14681</v>
@@ -6633,7 +6633,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G216" t="n">
-        <v>9.67713356018066</v>
+        <v>9.6771354675293</v>
       </c>
       <c r="H216" t="n">
         <v>41846</v>
@@ -6691,7 +6691,7 @@
         <v>10.0790138244629</v>
       </c>
       <c r="G218" t="n">
-        <v>9.47628688812256</v>
+        <v>9.47628879547119</v>
       </c>
       <c r="H218" t="n">
         <v>27030</v>
@@ -6720,7 +6720,7 @@
         <v>10.3120546340942</v>
       </c>
       <c r="G219" t="n">
-        <v>9.69539451599121</v>
+        <v>9.69539356231689</v>
       </c>
       <c r="H219" t="n">
         <v>30483</v>
@@ -6749,7 +6749,7 @@
         <v>10.234375</v>
       </c>
       <c r="G220" t="n">
-        <v>9.62236022949219</v>
+        <v>9.62235832214355</v>
       </c>
       <c r="H220" t="n">
         <v>76922</v>
@@ -6778,7 +6778,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G221" t="n">
-        <v>9.84146213531494</v>
+        <v>9.84146308898926</v>
       </c>
       <c r="H221" t="n">
         <v>36359</v>
@@ -6807,7 +6807,7 @@
         <v>10.3120546340942</v>
       </c>
       <c r="G222" t="n">
-        <v>9.69539451599121</v>
+        <v>9.69539356231689</v>
       </c>
       <c r="H222" t="n">
         <v>14768</v>
@@ -6865,7 +6865,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G224" t="n">
-        <v>9.98753356933594</v>
+        <v>9.98753452301025</v>
       </c>
       <c r="H224" t="n">
         <v>8445</v>
@@ -6894,7 +6894,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G225" t="n">
-        <v>9.73191165924072</v>
+        <v>9.73190975189209</v>
       </c>
       <c r="H225" t="n">
         <v>32595</v>
@@ -6923,7 +6923,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G226" t="n">
-        <v>9.98753356933594</v>
+        <v>9.98753452301025</v>
       </c>
       <c r="H226" t="n">
         <v>36732</v>
@@ -6952,7 +6952,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G227" t="n">
-        <v>9.85972309112549</v>
+        <v>9.85972213745117</v>
       </c>
       <c r="H227" t="n">
         <v>13733</v>
@@ -6981,7 +6981,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G228" t="n">
-        <v>9.73191165924072</v>
+        <v>9.73190975189209</v>
       </c>
       <c r="H228" t="n">
         <v>19355</v>
@@ -7010,7 +7010,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G229" t="n">
-        <v>9.75016975402832</v>
+        <v>9.750168800354</v>
       </c>
       <c r="H229" t="n">
         <v>11125</v>
@@ -7039,7 +7039,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G230" t="n">
-        <v>9.73191165924072</v>
+        <v>9.73190975189209</v>
       </c>
       <c r="H230" t="n">
         <v>20369</v>
@@ -7068,7 +7068,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G231" t="n">
-        <v>9.73191165924072</v>
+        <v>9.73190975189209</v>
       </c>
       <c r="H231" t="n">
         <v>21922</v>
@@ -7097,7 +7097,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G232" t="n">
-        <v>9.87798118591309</v>
+        <v>9.87798023223877</v>
       </c>
       <c r="H232" t="n">
         <v>15426</v>
@@ -7126,7 +7126,7 @@
         <v>10.6421957015991</v>
       </c>
       <c r="G233" t="n">
-        <v>10.0057907104492</v>
+        <v>10.0057935714722</v>
       </c>
       <c r="H233" t="n">
         <v>21115</v>
@@ -7155,7 +7155,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G234" t="n">
-        <v>10.0423078536987</v>
+        <v>10.0423097610474</v>
       </c>
       <c r="H234" t="n">
         <v>13286</v>
@@ -7184,7 +7184,7 @@
         <v>10.214955329895</v>
       </c>
       <c r="G235" t="n">
-        <v>9.60410118103027</v>
+        <v>9.60410022735596</v>
       </c>
       <c r="H235" t="n">
         <v>164121</v>
@@ -7213,7 +7213,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G236" t="n">
-        <v>9.71365261077881</v>
+        <v>9.71365165710449</v>
       </c>
       <c r="H236" t="n">
         <v>14595</v>
@@ -7242,7 +7242,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G237" t="n">
-        <v>9.76842975616455</v>
+        <v>9.76842784881592</v>
       </c>
       <c r="H237" t="n">
         <v>21826</v>
@@ -7271,7 +7271,7 @@
         <v>10.4285745620728</v>
       </c>
       <c r="G238" t="n">
-        <v>9.80494403839111</v>
+        <v>9.80494594573975</v>
       </c>
       <c r="H238" t="n">
         <v>22184</v>
@@ -7329,7 +7329,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G240" t="n">
-        <v>10.0423078536987</v>
+        <v>10.0423097610474</v>
       </c>
       <c r="H240" t="n">
         <v>30544</v>
@@ -7358,7 +7358,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G241" t="n">
-        <v>10.0423078536987</v>
+        <v>10.0423097610474</v>
       </c>
       <c r="H241" t="n">
         <v>35869</v>
@@ -7416,7 +7416,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G243" t="n">
-        <v>9.87798118591309</v>
+        <v>9.87798023223877</v>
       </c>
       <c r="H243" t="n">
         <v>23214</v>
@@ -7445,7 +7445,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G244" t="n">
-        <v>10.2431564331055</v>
+        <v>10.2431554794312</v>
       </c>
       <c r="H244" t="n">
         <v>47303</v>
@@ -7503,7 +7503,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G246" t="n">
-        <v>9.85972309112549</v>
+        <v>9.85972213745117</v>
       </c>
       <c r="H246" t="n">
         <v>19835</v>
@@ -7532,7 +7532,7 @@
         <v>10.4285745620728</v>
       </c>
       <c r="G247" t="n">
-        <v>9.80494403839111</v>
+        <v>9.80494594573975</v>
       </c>
       <c r="H247" t="n">
         <v>20516</v>
@@ -7590,7 +7590,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G249" t="n">
-        <v>9.95101547241211</v>
+        <v>9.95101642608643</v>
       </c>
       <c r="H249" t="n">
         <v>9574</v>
@@ -7619,7 +7619,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G250" t="n">
-        <v>10.060567855835</v>
+        <v>10.0605688095093</v>
       </c>
       <c r="H250" t="n">
         <v>11182</v>
@@ -7648,7 +7648,7 @@
         <v>11.1082782745361</v>
       </c>
       <c r="G251" t="n">
-        <v>10.4440031051636</v>
+        <v>10.4440021514893</v>
       </c>
       <c r="H251" t="n">
         <v>24083</v>
@@ -7677,7 +7677,7 @@
         <v>11.2053775787354</v>
       </c>
       <c r="G252" t="n">
-        <v>10.5352954864502</v>
+        <v>10.5352964401245</v>
       </c>
       <c r="H252" t="n">
         <v>17671</v>
@@ -7793,7 +7793,7 @@
         <v>11.0694379806519</v>
       </c>
       <c r="G256" t="n">
-        <v>10.4074859619141</v>
+        <v>10.4074850082397</v>
       </c>
       <c r="H256" t="n">
         <v>16489</v>
@@ -7822,7 +7822,7 @@
         <v>11.0305967330933</v>
       </c>
       <c r="G257" t="n">
-        <v>10.3709659576416</v>
+        <v>10.3709669113159</v>
       </c>
       <c r="H257" t="n">
         <v>11495</v>
@@ -7880,7 +7880,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G259" t="n">
-        <v>9.95101547241211</v>
+        <v>9.95101642608643</v>
       </c>
       <c r="H259" t="n">
         <v>25241</v>
@@ -7938,7 +7938,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G261" t="n">
-        <v>9.7866849899292</v>
+        <v>9.78668689727783</v>
       </c>
       <c r="H261" t="n">
         <v>10557</v>
@@ -7996,7 +7996,7 @@
         <v>10.6616163253784</v>
       </c>
       <c r="G263" t="n">
-        <v>10.1156797409058</v>
+        <v>10.1156778335571</v>
       </c>
       <c r="H263" t="n">
         <v>15915</v>
@@ -8025,7 +8025,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G264" t="n">
-        <v>9.876145362854</v>
+        <v>9.87614440917969</v>
       </c>
       <c r="H264" t="n">
         <v>9400</v>
@@ -8054,7 +8054,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G265" t="n">
-        <v>9.82086849212646</v>
+        <v>9.82086753845215</v>
       </c>
       <c r="H265" t="n">
         <v>11247</v>
@@ -8141,7 +8141,7 @@
         <v>10.6616163253784</v>
       </c>
       <c r="G268" t="n">
-        <v>10.1156797409058</v>
+        <v>10.1156778335571</v>
       </c>
       <c r="H268" t="n">
         <v>15044</v>
@@ -8228,7 +8228,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G271" t="n">
-        <v>10.1341018676758</v>
+        <v>10.1341028213501</v>
       </c>
       <c r="H271" t="n">
         <v>105178</v>
@@ -8286,7 +8286,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G273" t="n">
-        <v>10.1341018676758</v>
+        <v>10.1341028213501</v>
       </c>
       <c r="H273" t="n">
         <v>6761</v>
@@ -8315,7 +8315,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G274" t="n">
-        <v>10.023549079895</v>
+        <v>10.0235500335693</v>
       </c>
       <c r="H274" t="n">
         <v>20755</v>
@@ -8344,7 +8344,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G275" t="n">
-        <v>10.023549079895</v>
+        <v>10.0235500335693</v>
       </c>
       <c r="H275" t="n">
         <v>26662</v>
@@ -8373,7 +8373,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G276" t="n">
-        <v>9.83929347991943</v>
+        <v>9.83929252624512</v>
       </c>
       <c r="H276" t="n">
         <v>16684</v>
@@ -8402,7 +8402,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G277" t="n">
-        <v>9.98669910430908</v>
+        <v>9.9867000579834</v>
       </c>
       <c r="H277" t="n">
         <v>28143</v>
@@ -8460,7 +8460,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G279" t="n">
-        <v>10.1341018676758</v>
+        <v>10.1341028213501</v>
       </c>
       <c r="H279" t="n">
         <v>63120</v>
@@ -8518,7 +8518,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G281" t="n">
-        <v>9.82086849212646</v>
+        <v>9.82086753845215</v>
       </c>
       <c r="H281" t="n">
         <v>29284</v>
@@ -8547,7 +8547,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G282" t="n">
-        <v>9.67346286773682</v>
+        <v>9.67346382141113</v>
       </c>
       <c r="H282" t="n">
         <v>19151</v>
@@ -8576,7 +8576,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G283" t="n">
-        <v>9.876145362854</v>
+        <v>9.87614440917969</v>
       </c>
       <c r="H283" t="n">
         <v>74802</v>
@@ -8605,7 +8605,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G284" t="n">
-        <v>9.82086849212646</v>
+        <v>9.82086753845215</v>
       </c>
       <c r="H284" t="n">
         <v>38163</v>
@@ -8663,7 +8663,7 @@
         <v>10.6421957015991</v>
       </c>
       <c r="G286" t="n">
-        <v>10.0972528457642</v>
+        <v>10.0972518920898</v>
       </c>
       <c r="H286" t="n">
         <v>15436</v>
@@ -8721,7 +8721,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G288" t="n">
-        <v>10.3367862701416</v>
+        <v>10.3367872238159</v>
       </c>
       <c r="H288" t="n">
         <v>11081</v>
@@ -8808,7 +8808,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G291" t="n">
-        <v>10.3367862701416</v>
+        <v>10.3367872238159</v>
       </c>
       <c r="H291" t="n">
         <v>11184</v>
@@ -8895,7 +8895,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G294" t="n">
-        <v>9.76559066772461</v>
+        <v>9.76559162139893</v>
       </c>
       <c r="H294" t="n">
         <v>19630</v>
@@ -8953,7 +8953,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G296" t="n">
-        <v>10.3367862701416</v>
+        <v>10.3367872238159</v>
       </c>
       <c r="H296" t="n">
         <v>17062</v>
@@ -9069,7 +9069,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G300" t="n">
-        <v>9.67346286773682</v>
+        <v>9.67346382141113</v>
       </c>
       <c r="H300" t="n">
         <v>46224</v>
@@ -9127,7 +9127,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G302" t="n">
-        <v>9.83929347991943</v>
+        <v>9.83929252624512</v>
       </c>
       <c r="H302" t="n">
         <v>1056</v>
@@ -9156,7 +9156,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G303" t="n">
-        <v>10.0051240921021</v>
+        <v>10.0051259994507</v>
       </c>
       <c r="H303" t="n">
         <v>22348</v>
@@ -9214,7 +9214,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G305" t="n">
-        <v>10.1341018676758</v>
+        <v>10.1341028213501</v>
       </c>
       <c r="H305" t="n">
         <v>4341</v>
@@ -9301,7 +9301,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G308" t="n">
-        <v>9.98669910430908</v>
+        <v>9.9867000579834</v>
       </c>
       <c r="H308" t="n">
         <v>5380</v>
@@ -9504,7 +9504,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G315" t="n">
-        <v>10.4104871749878</v>
+        <v>10.4104881286621</v>
       </c>
       <c r="H315" t="n">
         <v>51796</v>
@@ -9562,7 +9562,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G317" t="n">
-        <v>11.9766674041748</v>
+        <v>11.9766693115234</v>
       </c>
       <c r="H317" t="n">
         <v>40875</v>
@@ -9591,7 +9591,7 @@
         <v>11.6908798217773</v>
       </c>
       <c r="G318" t="n">
-        <v>11.0922365188599</v>
+        <v>11.0922374725342</v>
       </c>
       <c r="H318" t="n">
         <v>45226</v>
@@ -9620,7 +9620,7 @@
         <v>12.15696144104</v>
       </c>
       <c r="G319" t="n">
-        <v>11.5344533920288</v>
+        <v>11.5344524383545</v>
       </c>
       <c r="H319" t="n">
         <v>33133</v>
@@ -9649,7 +9649,7 @@
         <v>11.943341255188</v>
       </c>
       <c r="G320" t="n">
-        <v>11.3317728042603</v>
+        <v>11.3317718505859</v>
       </c>
       <c r="H320" t="n">
         <v>26477</v>
@@ -9678,7 +9678,7 @@
         <v>11.943341255188</v>
       </c>
       <c r="G321" t="n">
-        <v>11.3317728042603</v>
+        <v>11.3317718505859</v>
       </c>
       <c r="H321" t="n">
         <v>65085</v>
@@ -9707,7 +9707,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G322" t="n">
-        <v>11.4607496261597</v>
+        <v>11.4607486724854</v>
       </c>
       <c r="H322" t="n">
         <v>18075</v>
@@ -9765,7 +9765,7 @@
         <v>12.0598611831665</v>
       </c>
       <c r="G324" t="n">
-        <v>11.442325592041</v>
+        <v>11.4423246383667</v>
       </c>
       <c r="H324" t="n">
         <v>55912</v>
@@ -9794,7 +9794,7 @@
         <v>12.15696144104</v>
       </c>
       <c r="G325" t="n">
-        <v>11.5344533920288</v>
+        <v>11.5344524383545</v>
       </c>
       <c r="H325" t="n">
         <v>13334</v>
@@ -9852,7 +9852,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G327" t="n">
-        <v>11.8845405578613</v>
+        <v>11.884539604187</v>
       </c>
       <c r="H327" t="n">
         <v>38628</v>
@@ -9881,7 +9881,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G328" t="n">
-        <v>12.0687952041626</v>
+        <v>12.0687971115112</v>
       </c>
       <c r="H328" t="n">
         <v>34385</v>
@@ -9910,7 +9910,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G329" t="n">
-        <v>12.0687952041626</v>
+        <v>12.0687971115112</v>
       </c>
       <c r="H329" t="n">
         <v>28558</v>
@@ -9939,7 +9939,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G330" t="n">
-        <v>12.160924911499</v>
+        <v>12.1609258651733</v>
       </c>
       <c r="H330" t="n">
         <v>146039</v>
@@ -9968,7 +9968,7 @@
         <v>13.0308637619019</v>
       </c>
       <c r="G331" t="n">
-        <v>12.3636054992676</v>
+        <v>12.3636064529419</v>
       </c>
       <c r="H331" t="n">
         <v>18642</v>
@@ -10026,7 +10026,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G333" t="n">
-        <v>12.1056470870972</v>
+        <v>12.1056480407715</v>
       </c>
       <c r="H333" t="n">
         <v>24851</v>
@@ -10200,7 +10200,7 @@
         <v>12.0210208892822</v>
       </c>
       <c r="G339" t="n">
-        <v>11.4054746627808</v>
+        <v>11.4054737091064</v>
       </c>
       <c r="H339" t="n">
         <v>16302</v>
@@ -10258,7 +10258,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G341" t="n">
-        <v>11.4607496261597</v>
+        <v>11.4607486724854</v>
       </c>
       <c r="H341" t="n">
         <v>96017</v>
@@ -10345,7 +10345,7 @@
         <v>12.4871015548706</v>
       </c>
       <c r="G344" t="n">
-        <v>11.8476877212524</v>
+        <v>11.8476886749268</v>
       </c>
       <c r="H344" t="n">
         <v>22299</v>
@@ -10374,7 +10374,7 @@
         <v>12.681303024292</v>
       </c>
       <c r="G345" t="n">
-        <v>12.0319452285767</v>
+        <v>12.031946182251</v>
       </c>
       <c r="H345" t="n">
         <v>33851</v>
@@ -10403,7 +10403,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G346" t="n">
-        <v>11.8845405578613</v>
+        <v>11.884539604187</v>
       </c>
       <c r="H346" t="n">
         <v>25063</v>
@@ -10432,7 +10432,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G347" t="n">
-        <v>12.0872211456299</v>
+        <v>12.0872201919556</v>
       </c>
       <c r="H347" t="n">
         <v>17512</v>
@@ -10461,7 +10461,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G348" t="n">
-        <v>12.160924911499</v>
+        <v>12.1609258651733</v>
       </c>
       <c r="H348" t="n">
         <v>164571</v>
@@ -10490,7 +10490,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G349" t="n">
-        <v>11.9766674041748</v>
+        <v>11.9766693115234</v>
       </c>
       <c r="H349" t="n">
         <v>13283</v>
@@ -10548,7 +10548,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G351" t="n">
-        <v>12.437310218811</v>
+        <v>12.4373092651367</v>
       </c>
       <c r="H351" t="n">
         <v>76761</v>
@@ -10577,7 +10577,7 @@
         <v>13.2833251953125</v>
       </c>
       <c r="G352" t="n">
-        <v>12.6031408309937</v>
+        <v>12.6031398773193</v>
       </c>
       <c r="H352" t="n">
         <v>22421</v>
@@ -10693,7 +10693,7 @@
         <v>14.1378078460693</v>
       </c>
       <c r="G356" t="n">
-        <v>13.4138669967651</v>
+        <v>13.4138689041138</v>
       </c>
       <c r="H356" t="n">
         <v>31972</v>
@@ -10722,7 +10722,7 @@
         <v>14.7204103469849</v>
       </c>
       <c r="G357" t="n">
-        <v>13.9666385650635</v>
+        <v>13.9666395187378</v>
       </c>
       <c r="H357" t="n">
         <v>51342</v>
@@ -10751,7 +10751,7 @@
         <v>14.1378078460693</v>
       </c>
       <c r="G358" t="n">
-        <v>13.4138669967651</v>
+        <v>13.4138689041138</v>
       </c>
       <c r="H358" t="n">
         <v>70279</v>
@@ -10780,7 +10780,7 @@
         <v>14.0989675521851</v>
       </c>
       <c r="G359" t="n">
-        <v>13.3770170211792</v>
+        <v>13.3770160675049</v>
       </c>
       <c r="H359" t="n">
         <v>62383</v>
@@ -10809,7 +10809,7 @@
         <v>13.8270874023438</v>
       </c>
       <c r="G360" t="n">
-        <v>13.1190586090088</v>
+        <v>13.1190576553345</v>
       </c>
       <c r="H360" t="n">
         <v>43385</v>
@@ -10838,7 +10838,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G361" t="n">
-        <v>13.026930809021</v>
+        <v>13.0269289016724</v>
       </c>
       <c r="H361" t="n">
         <v>48913</v>
@@ -10867,7 +10867,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G362" t="n">
-        <v>13.026930809021</v>
+        <v>13.0269289016724</v>
       </c>
       <c r="H362" t="n">
         <v>29032</v>
@@ -10896,7 +10896,7 @@
         <v>12.9726037979126</v>
       </c>
       <c r="G363" t="n">
-        <v>12.3083295822144</v>
+        <v>12.3083305358887</v>
       </c>
       <c r="H363" t="n">
         <v>328227</v>
@@ -10925,7 +10925,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G364" t="n">
-        <v>12.2714805603027</v>
+        <v>12.2714786529541</v>
       </c>
       <c r="H364" t="n">
         <v>81687</v>
@@ -10954,7 +10954,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G365" t="n">
-        <v>12.2162017822266</v>
+        <v>12.2162008285522</v>
       </c>
       <c r="H365" t="n">
         <v>190840</v>
@@ -10983,7 +10983,7 @@
         <v>12.9920244216919</v>
       </c>
       <c r="G366" t="n">
-        <v>12.3267545700073</v>
+        <v>12.326756477356</v>
       </c>
       <c r="H366" t="n">
         <v>73862</v>
@@ -11012,7 +11012,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G367" t="n">
-        <v>12.160924911499</v>
+        <v>12.1609258651733</v>
       </c>
       <c r="H367" t="n">
         <v>62783</v>
@@ -11041,7 +11041,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G368" t="n">
-        <v>12.0872211456299</v>
+        <v>12.0872201919556</v>
       </c>
       <c r="H368" t="n">
         <v>34922</v>
@@ -11070,7 +11070,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G369" t="n">
-        <v>12.1056470870972</v>
+        <v>12.1056480407715</v>
       </c>
       <c r="H369" t="n">
         <v>42419</v>
@@ -11099,7 +11099,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G370" t="n">
-        <v>12.1240730285645</v>
+        <v>12.1240739822388</v>
       </c>
       <c r="H370" t="n">
         <v>23953</v>
@@ -11128,7 +11128,7 @@
         <v>12.8560838699341</v>
       </c>
       <c r="G371" t="n">
-        <v>12.197774887085</v>
+        <v>12.1977758407593</v>
       </c>
       <c r="H371" t="n">
         <v>17051</v>
@@ -11157,7 +11157,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G372" t="n">
-        <v>12.437310218811</v>
+        <v>12.4373092651367</v>
       </c>
       <c r="H372" t="n">
         <v>84706</v>
@@ -11215,7 +11215,7 @@
         <v>14.5650501251221</v>
       </c>
       <c r="G374" t="n">
-        <v>13.8192319869995</v>
+        <v>13.8192338943481</v>
       </c>
       <c r="H374" t="n">
         <v>120229</v>
@@ -11244,7 +11244,7 @@
         <v>14.0407075881958</v>
       </c>
       <c r="G375" t="n">
-        <v>13.321741104126</v>
+        <v>13.3217401504517</v>
       </c>
       <c r="H375" t="n">
         <v>115548</v>
@@ -11302,7 +11302,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G377" t="n">
-        <v>12.7689714431763</v>
+        <v>12.768970489502</v>
       </c>
       <c r="H377" t="n">
         <v>105631</v>
@@ -11331,7 +11331,7 @@
         <v>13.3027448654175</v>
       </c>
       <c r="G378" t="n">
-        <v>12.6215658187866</v>
+        <v>12.6215648651123</v>
       </c>
       <c r="H378" t="n">
         <v>479797</v>
@@ -11360,7 +11360,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G379" t="n">
-        <v>12.437310218811</v>
+        <v>12.4373092651367</v>
       </c>
       <c r="H379" t="n">
         <v>16597</v>
@@ -11418,7 +11418,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G381" t="n">
-        <v>12.2899055480957</v>
+        <v>12.2899036407471</v>
       </c>
       <c r="H381" t="n">
         <v>22165</v>
@@ -11447,7 +11447,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G382" t="n">
-        <v>12.2899055480957</v>
+        <v>12.2899036407471</v>
       </c>
       <c r="H382" t="n">
         <v>16881</v>
@@ -11476,7 +11476,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G383" t="n">
-        <v>12.437310218811</v>
+        <v>12.4373092651367</v>
       </c>
       <c r="H383" t="n">
         <v>19371</v>
@@ -11505,7 +11505,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G384" t="n">
-        <v>12.2162017822266</v>
+        <v>12.2162008285522</v>
       </c>
       <c r="H384" t="n">
         <v>8234</v>
@@ -11534,7 +11534,7 @@
         <v>13.380425453186</v>
       </c>
       <c r="G385" t="n">
-        <v>12.6952676773071</v>
+        <v>12.6952695846558</v>
       </c>
       <c r="H385" t="n">
         <v>15276</v>
@@ -11592,7 +11592,7 @@
         <v>13.4969463348389</v>
       </c>
       <c r="G387" t="n">
-        <v>12.8058214187622</v>
+        <v>12.8058233261108</v>
       </c>
       <c r="H387" t="n">
         <v>42243</v>
@@ -11708,7 +11708,7 @@
         <v>13.9630270004272</v>
       </c>
       <c r="G391" t="n">
-        <v>13.2480373382568</v>
+        <v>13.2480363845825</v>
       </c>
       <c r="H391" t="n">
         <v>49918</v>
@@ -11737,7 +11737,7 @@
         <v>13.9630270004272</v>
       </c>
       <c r="G392" t="n">
-        <v>13.2480373382568</v>
+        <v>13.2480363845825</v>
       </c>
       <c r="H392" t="n">
         <v>26496</v>
@@ -11795,7 +11795,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G394" t="n">
-        <v>12.7689714431763</v>
+        <v>12.768970489502</v>
       </c>
       <c r="H394" t="n">
         <v>27023</v>
@@ -11940,7 +11940,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G399" t="n">
-        <v>12.1056470870972</v>
+        <v>12.1056480407715</v>
       </c>
       <c r="H399" t="n">
         <v>155352</v>
@@ -12056,7 +12056,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G403" t="n">
-        <v>12.437310218811</v>
+        <v>12.4373092651367</v>
       </c>
       <c r="H403" t="n">
         <v>10747</v>
@@ -12114,7 +12114,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G405" t="n">
-        <v>12.160924911499</v>
+        <v>12.1609258651733</v>
       </c>
       <c r="H405" t="n">
         <v>14366</v>
@@ -12143,7 +12143,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G406" t="n">
-        <v>12.0687952041626</v>
+        <v>12.0687971115112</v>
       </c>
       <c r="H406" t="n">
         <v>34716</v>
@@ -12172,7 +12172,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G407" t="n">
-        <v>12.0872211456299</v>
+        <v>12.0872201919556</v>
       </c>
       <c r="H407" t="n">
         <v>16935</v>
@@ -12201,7 +12201,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G408" t="n">
-        <v>11.8845405578613</v>
+        <v>11.884539604187</v>
       </c>
       <c r="H408" t="n">
         <v>21960</v>
@@ -12230,7 +12230,7 @@
         <v>12.4871015548706</v>
       </c>
       <c r="G409" t="n">
-        <v>11.8476877212524</v>
+        <v>11.8476886749268</v>
       </c>
       <c r="H409" t="n">
         <v>154715</v>
@@ -12317,7 +12317,7 @@
         <v>11.8268203735352</v>
       </c>
       <c r="G412" t="n">
-        <v>11.2212162017822</v>
+        <v>11.2212181091309</v>
       </c>
       <c r="H412" t="n">
         <v>26248</v>
@@ -12346,7 +12346,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G413" t="n">
-        <v>10.9448318481445</v>
+        <v>10.9448308944702</v>
       </c>
       <c r="H413" t="n">
         <v>163465</v>
@@ -12375,7 +12375,7 @@
         <v>11.6131992340088</v>
       </c>
       <c r="G414" t="n">
-        <v>11.0185346603394</v>
+        <v>11.0185356140137</v>
       </c>
       <c r="H414" t="n">
         <v>45535</v>
@@ -12404,7 +12404,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G415" t="n">
-        <v>10.9632587432861</v>
+        <v>10.9632568359375</v>
       </c>
       <c r="H415" t="n">
         <v>19309</v>
@@ -12462,7 +12462,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G417" t="n">
-        <v>10.9632587432861</v>
+        <v>10.9632568359375</v>
       </c>
       <c r="H417" t="n">
         <v>37373</v>
@@ -12491,7 +12491,7 @@
         <v>11.2636375427246</v>
       </c>
       <c r="G418" t="n">
-        <v>10.6868734359741</v>
+        <v>10.6868724822998</v>
       </c>
       <c r="H418" t="n">
         <v>40820</v>
@@ -12520,7 +12520,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G419" t="n">
-        <v>10.9448318481445</v>
+        <v>10.9448308944702</v>
       </c>
       <c r="H419" t="n">
         <v>37390</v>
@@ -12549,7 +12549,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G420" t="n">
-        <v>11.2396411895752</v>
+        <v>11.2396430969238</v>
       </c>
       <c r="H420" t="n">
         <v>84619</v>
@@ -12578,7 +12578,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G421" t="n">
-        <v>11.2396411895752</v>
+        <v>11.2396430969238</v>
       </c>
       <c r="H421" t="n">
         <v>94440</v>
@@ -12607,7 +12607,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G422" t="n">
-        <v>11.0553865432739</v>
+        <v>11.0553855895996</v>
       </c>
       <c r="H422" t="n">
         <v>13462</v>
@@ -12636,7 +12636,7 @@
         <v>11.8073997497559</v>
       </c>
       <c r="G423" t="n">
-        <v>11.2027921676636</v>
+        <v>11.2027912139893</v>
       </c>
       <c r="H423" t="n">
         <v>14119</v>
@@ -12665,7 +12665,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G424" t="n">
-        <v>11.147515296936</v>
+        <v>11.1475143432617</v>
       </c>
       <c r="H424" t="n">
         <v>53206</v>
@@ -12694,7 +12694,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G425" t="n">
-        <v>11.2396411895752</v>
+        <v>11.2396430969238</v>
       </c>
       <c r="H425" t="n">
         <v>21806</v>
@@ -12723,7 +12723,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G426" t="n">
-        <v>11.2396411895752</v>
+        <v>11.2396430969238</v>
       </c>
       <c r="H426" t="n">
         <v>44690</v>
@@ -12752,7 +12752,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G427" t="n">
-        <v>11.2396411895752</v>
+        <v>11.2396430969238</v>
       </c>
       <c r="H427" t="n">
         <v>35187</v>
@@ -12781,7 +12781,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G428" t="n">
-        <v>11.147515296936</v>
+        <v>11.1475143432617</v>
       </c>
       <c r="H428" t="n">
         <v>6846</v>
@@ -12810,7 +12810,7 @@
         <v>11.8073997497559</v>
       </c>
       <c r="G429" t="n">
-        <v>11.2027921676636</v>
+        <v>11.2027912139893</v>
       </c>
       <c r="H429" t="n">
         <v>10547</v>
@@ -12868,7 +12868,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G431" t="n">
-        <v>11.0369596481323</v>
+        <v>11.0369606018066</v>
       </c>
       <c r="H431" t="n">
         <v>33933</v>
@@ -12926,7 +12926,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G433" t="n">
-        <v>10.4104871749878</v>
+        <v>10.4104881286621</v>
       </c>
       <c r="H433" t="n">
         <v>46588</v>
@@ -13042,7 +13042,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G437" t="n">
-        <v>9.98669910430908</v>
+        <v>9.9867000579834</v>
       </c>
       <c r="H437" t="n">
         <v>35216</v>
@@ -13100,7 +13100,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G439" t="n">
-        <v>10.3367862701416</v>
+        <v>10.3367872238159</v>
       </c>
       <c r="H439" t="n">
         <v>50080</v>
@@ -13129,7 +13129,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G440" t="n">
-        <v>10.023549079895</v>
+        <v>10.0235500335693</v>
       </c>
       <c r="H440" t="n">
         <v>45035</v>
@@ -13187,7 +13187,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G442" t="n">
-        <v>9.67346286773682</v>
+        <v>9.67346382141113</v>
       </c>
       <c r="H442" t="n">
         <v>61109</v>
@@ -13216,7 +13216,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G443" t="n">
-        <v>9.36022758483887</v>
+        <v>9.36022567749023</v>
       </c>
       <c r="H443" t="n">
         <v>58787</v>
@@ -13303,7 +13303,7 @@
         <v>10.0013341903687</v>
       </c>
       <c r="G446" t="n">
-        <v>9.48920822143555</v>
+        <v>9.48920726776123</v>
       </c>
       <c r="H446" t="n">
         <v>50177</v>
@@ -13390,7 +13390,7 @@
         <v>9.22453117370605</v>
       </c>
       <c r="G449" t="n">
-        <v>8.75218200683594</v>
+        <v>8.75218105316162</v>
       </c>
       <c r="H449" t="n">
         <v>29663</v>
@@ -13448,7 +13448,7 @@
         <v>8.6322193145752</v>
       </c>
       <c r="G451" t="n">
-        <v>8.19019889831543</v>
+        <v>8.19019985198975</v>
       </c>
       <c r="H451" t="n">
         <v>140854</v>
@@ -13477,7 +13477,7 @@
         <v>8.58366870880127</v>
       </c>
       <c r="G452" t="n">
-        <v>8.14413452148438</v>
+        <v>8.14413261413574</v>
       </c>
       <c r="H452" t="n">
         <v>27504</v>
@@ -13535,7 +13535,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G454" t="n">
-        <v>8.38366794586182</v>
+        <v>8.3836669921875</v>
       </c>
       <c r="H454" t="n">
         <v>58292</v>
@@ -13564,7 +13564,7 @@
         <v>10.0984344482422</v>
       </c>
       <c r="G455" t="n">
-        <v>9.58133506774902</v>
+        <v>9.58133602142334</v>
       </c>
       <c r="H455" t="n">
         <v>36655</v>
@@ -13622,7 +13622,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G457" t="n">
-        <v>11.0369596481323</v>
+        <v>11.0369606018066</v>
       </c>
       <c r="H457" t="n">
         <v>57173</v>
@@ -13651,7 +13651,7 @@
         <v>11.2247982025146</v>
       </c>
       <c r="G458" t="n">
-        <v>10.6500205993652</v>
+        <v>10.6500215530396</v>
       </c>
       <c r="H458" t="n">
         <v>48513</v>
@@ -13709,7 +13709,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G460" t="n">
-        <v>10.1341018676758</v>
+        <v>10.1341028213501</v>
       </c>
       <c r="H460" t="n">
         <v>72969</v>
@@ -13738,7 +13738,7 @@
         <v>10.234375</v>
       </c>
       <c r="G461" t="n">
-        <v>9.71031475067139</v>
+        <v>9.71031379699707</v>
       </c>
       <c r="H461" t="n">
         <v>36815</v>
@@ -13767,7 +13767,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G462" t="n">
-        <v>10.1341018676758</v>
+        <v>10.1341028213501</v>
       </c>
       <c r="H462" t="n">
         <v>20192</v>
@@ -13796,7 +13796,7 @@
         <v>10.7781372070312</v>
       </c>
       <c r="G463" t="n">
-        <v>10.2262325286865</v>
+        <v>10.2262315750122</v>
       </c>
       <c r="H463" t="n">
         <v>35295</v>
@@ -13825,7 +13825,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G464" t="n">
-        <v>10.1709547042847</v>
+        <v>10.170955657959</v>
       </c>
       <c r="H464" t="n">
         <v>21536</v>
@@ -13854,7 +13854,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G465" t="n">
-        <v>9.76559066772461</v>
+        <v>9.76559162139893</v>
       </c>
       <c r="H465" t="n">
         <v>19814</v>
@@ -13941,7 +13941,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G468" t="n">
-        <v>9.94984912872314</v>
+        <v>9.94984817504883</v>
       </c>
       <c r="H468" t="n">
         <v>26515</v>
@@ -13970,7 +13970,7 @@
         <v>11.2053775787354</v>
       </c>
       <c r="G469" t="n">
-        <v>10.6315946578979</v>
+        <v>10.6315956115723</v>
       </c>
       <c r="H469" t="n">
         <v>65451</v>
@@ -13999,7 +13999,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G470" t="n">
-        <v>11.0553865432739</v>
+        <v>11.0553855895996</v>
       </c>
       <c r="H470" t="n">
         <v>18460</v>
@@ -14028,7 +14028,7 @@
         <v>11.8268203735352</v>
       </c>
       <c r="G471" t="n">
-        <v>11.2212162017822</v>
+        <v>11.2212181091309</v>
       </c>
       <c r="H471" t="n">
         <v>49981</v>
@@ -14057,7 +14057,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G472" t="n">
-        <v>11.0553865432739</v>
+        <v>11.0553855895996</v>
       </c>
       <c r="H472" t="n">
         <v>82131</v>
@@ -14231,7 +14231,7 @@
         <v>13.2056446075439</v>
       </c>
       <c r="G478" t="n">
-        <v>12.5294370651245</v>
+        <v>12.5294380187988</v>
       </c>
       <c r="H478" t="n">
         <v>22130</v>
@@ -14289,7 +14289,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G480" t="n">
-        <v>12.2714805603027</v>
+        <v>12.2714786529541</v>
       </c>
       <c r="H480" t="n">
         <v>20669</v>
@@ -14318,7 +14318,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G481" t="n">
-        <v>11.9766674041748</v>
+        <v>11.9766693115234</v>
       </c>
       <c r="H481" t="n">
         <v>21030</v>
@@ -14405,7 +14405,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G484" t="n">
-        <v>12.1240730285645</v>
+        <v>12.1240739822388</v>
       </c>
       <c r="H484" t="n">
         <v>26687</v>
@@ -14463,7 +14463,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G486" t="n">
-        <v>12.437310218811</v>
+        <v>12.4373092651367</v>
       </c>
       <c r="H486" t="n">
         <v>34820</v>
@@ -14492,7 +14492,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G487" t="n">
-        <v>12.437310218811</v>
+        <v>12.4373092651367</v>
       </c>
       <c r="H487" t="n">
         <v>22322</v>
@@ -14579,7 +14579,7 @@
         <v>14.1183881759644</v>
       </c>
       <c r="G490" t="n">
-        <v>13.3954420089722</v>
+        <v>13.3954439163208</v>
       </c>
       <c r="H490" t="n">
         <v>42920</v>
@@ -14608,7 +14608,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G491" t="n">
-        <v>13.026930809021</v>
+        <v>13.0269289016724</v>
       </c>
       <c r="H491" t="n">
         <v>30641</v>
@@ -14666,7 +14666,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G493" t="n">
-        <v>14.7957925796509</v>
+        <v>14.7957906723022</v>
       </c>
       <c r="H493" t="n">
         <v>75829</v>
@@ -14695,7 +14695,7 @@
         <v>15.7496738433838</v>
       </c>
       <c r="G494" t="n">
-        <v>14.9431972503662</v>
+        <v>14.9431962966919</v>
       </c>
       <c r="H494" t="n">
         <v>32674</v>
@@ -14724,7 +14724,7 @@
         <v>15.633152961731</v>
       </c>
       <c r="G495" t="n">
-        <v>14.8326444625854</v>
+        <v>14.8326425552368</v>
       </c>
       <c r="H495" t="n">
         <v>23740</v>
@@ -14753,7 +14753,7 @@
         <v>14.9146108627319</v>
       </c>
       <c r="G496" t="n">
-        <v>14.1508941650391</v>
+        <v>14.1508951187134</v>
       </c>
       <c r="H496" t="n">
         <v>48940</v>
@@ -14782,7 +14782,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G497" t="n">
-        <v>15.1827306747437</v>
+        <v>15.182731628418</v>
       </c>
       <c r="H497" t="n">
         <v>39377</v>
@@ -14811,7 +14811,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G498" t="n">
-        <v>15.6433725357056</v>
+        <v>15.6433715820312</v>
       </c>
       <c r="H498" t="n">
         <v>302386</v>
@@ -14869,7 +14869,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G500" t="n">
-        <v>15.2932844161987</v>
+        <v>15.293285369873</v>
       </c>
       <c r="H500" t="n">
         <v>75736</v>
@@ -14898,7 +14898,7 @@
         <v>15.6525726318359</v>
       </c>
       <c r="G501" t="n">
-        <v>14.8510665893555</v>
+        <v>14.8510675430298</v>
       </c>
       <c r="H501" t="n">
         <v>39762</v>
@@ -14927,7 +14927,7 @@
         <v>15.3030118942261</v>
       </c>
       <c r="G502" t="n">
-        <v>14.5194072723389</v>
+        <v>14.5194082260132</v>
       </c>
       <c r="H502" t="n">
         <v>62720</v>
@@ -15188,7 +15188,7 @@
         <v>14.9922914505005</v>
       </c>
       <c r="G511" t="n">
-        <v>14.2245979309082</v>
+        <v>14.2245988845825</v>
       </c>
       <c r="H511" t="n">
         <v>23708</v>
@@ -15246,7 +15246,7 @@
         <v>15.6914129257202</v>
       </c>
       <c r="G513" t="n">
-        <v>14.8879203796387</v>
+        <v>14.8879194259644</v>
       </c>
       <c r="H513" t="n">
         <v>54549</v>
@@ -15333,7 +15333,7 @@
         <v>15.4777927398682</v>
       </c>
       <c r="G516" t="n">
-        <v>14.7951021194458</v>
+        <v>14.7951011657715</v>
       </c>
       <c r="H516" t="n">
         <v>13193</v>
@@ -15420,7 +15420,7 @@
         <v>15.5748929977417</v>
       </c>
       <c r="G519" t="n">
-        <v>14.8879203796387</v>
+        <v>14.8879194259644</v>
       </c>
       <c r="H519" t="n">
         <v>10780</v>
@@ -15449,7 +15449,7 @@
         <v>15.8661937713623</v>
       </c>
       <c r="G520" t="n">
-        <v>15.1663722991943</v>
+        <v>15.16637134552</v>
       </c>
       <c r="H520" t="n">
         <v>26150</v>
@@ -15594,7 +15594,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G525" t="n">
-        <v>14.9064836502075</v>
+        <v>14.9064826965332</v>
       </c>
       <c r="H525" t="n">
         <v>16186</v>
@@ -15623,7 +15623,7 @@
         <v>15.1864919662476</v>
       </c>
       <c r="G526" t="n">
-        <v>14.5166511535645</v>
+        <v>14.5166501998901</v>
       </c>
       <c r="H526" t="n">
         <v>47887</v>
@@ -15652,7 +15652,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G527" t="n">
-        <v>14.9064836502075</v>
+        <v>14.9064826965332</v>
       </c>
       <c r="H527" t="n">
         <v>40650</v>
@@ -15681,7 +15681,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G528" t="n">
-        <v>14.9807367324829</v>
+        <v>14.9807357788086</v>
       </c>
       <c r="H528" t="n">
         <v>11405</v>
@@ -15913,7 +15913,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G536" t="n">
-        <v>14.9064836502075</v>
+        <v>14.9064826965332</v>
       </c>
       <c r="H536" t="n">
         <v>7951</v>
@@ -15942,7 +15942,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G537" t="n">
-        <v>15.2963171005249</v>
+        <v>15.2963161468506</v>
       </c>
       <c r="H537" t="n">
         <v>21472</v>
@@ -16000,7 +16000,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G539" t="n">
-        <v>14.8507919311523</v>
+        <v>14.8507928848267</v>
       </c>
       <c r="H539" t="n">
         <v>10098</v>
@@ -16029,7 +16029,7 @@
         <v>15.0505514144897</v>
       </c>
       <c r="G540" t="n">
-        <v>14.3867063522339</v>
+        <v>14.3867053985596</v>
       </c>
       <c r="H540" t="n">
         <v>8606</v>
@@ -16058,7 +16058,7 @@
         <v>15.0505514144897</v>
       </c>
       <c r="G541" t="n">
-        <v>14.3867063522339</v>
+        <v>14.3867053985596</v>
       </c>
       <c r="H541" t="n">
         <v>11476</v>
@@ -16116,7 +16116,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G543" t="n">
-        <v>14.8507919311523</v>
+        <v>14.8507928848267</v>
       </c>
       <c r="H543" t="n">
         <v>15067</v>
@@ -16203,7 +16203,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G546" t="n">
-        <v>16.0574207305908</v>
+        <v>16.0574169158936</v>
       </c>
       <c r="H546" t="n">
         <v>61019</v>
@@ -16319,7 +16319,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G550" t="n">
-        <v>16.6143226623535</v>
+        <v>16.6143245697021</v>
       </c>
       <c r="H550" t="n">
         <v>37074</v>
@@ -16377,7 +16377,7 @@
         <v>18.1189212799072</v>
       </c>
       <c r="G552" t="n">
-        <v>17.3197364807129</v>
+        <v>17.3197383880615</v>
       </c>
       <c r="H552" t="n">
         <v>10320</v>
@@ -16464,7 +16464,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G555" t="n">
-        <v>17.6724452972412</v>
+        <v>17.6724414825439</v>
       </c>
       <c r="H555" t="n">
         <v>24199</v>
@@ -16493,7 +16493,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G556" t="n">
-        <v>17.895206451416</v>
+        <v>17.8952045440674</v>
       </c>
       <c r="H556" t="n">
         <v>21308</v>
@@ -16609,7 +16609,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G560" t="n">
-        <v>17.5424995422363</v>
+        <v>17.542501449585</v>
       </c>
       <c r="H560" t="n">
         <v>23181</v>
@@ -16638,7 +16638,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G561" t="n">
-        <v>17.4125556945801</v>
+        <v>17.4125537872314</v>
       </c>
       <c r="H561" t="n">
         <v>39089</v>
@@ -16696,7 +16696,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G563" t="n">
-        <v>18.5634937286377</v>
+        <v>18.5634918212891</v>
       </c>
       <c r="H563" t="n">
         <v>83303</v>
@@ -16754,7 +16754,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G565" t="n">
-        <v>18.210786819458</v>
+        <v>18.2107849121094</v>
       </c>
       <c r="H565" t="n">
         <v>31275</v>
@@ -16783,7 +16783,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G566" t="n">
-        <v>18.5634937286377</v>
+        <v>18.5634918212891</v>
       </c>
       <c r="H566" t="n">
         <v>84063</v>
@@ -16812,7 +16812,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G567" t="n">
-        <v>17.6724452972412</v>
+        <v>17.6724414825439</v>
       </c>
       <c r="H567" t="n">
         <v>19901</v>
@@ -16870,7 +16870,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G569" t="n">
-        <v>17.9137687683105</v>
+        <v>17.9137706756592</v>
       </c>
       <c r="H569" t="n">
         <v>127033</v>
@@ -16899,7 +16899,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G570" t="n">
-        <v>17.2640438079834</v>
+        <v>17.2640476226807</v>
       </c>
       <c r="H570" t="n">
         <v>45194</v>
@@ -16957,7 +16957,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G572" t="n">
-        <v>17.3568649291992</v>
+        <v>17.3568668365479</v>
       </c>
       <c r="H572" t="n">
         <v>123917</v>
@@ -16986,7 +16986,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G573" t="n">
-        <v>17.6910076141357</v>
+        <v>17.6910057067871</v>
       </c>
       <c r="H573" t="n">
         <v>109043</v>
@@ -17015,7 +17015,7 @@
         <v>17.5945796966553</v>
       </c>
       <c r="G574" t="n">
-        <v>16.8185214996338</v>
+        <v>16.8185234069824</v>
       </c>
       <c r="H574" t="n">
         <v>68018</v>
@@ -17160,7 +17160,7 @@
         <v>15.9827136993408</v>
       </c>
       <c r="G579" t="n">
-        <v>15.2777528762817</v>
+        <v>15.2777519226074</v>
       </c>
       <c r="H579" t="n">
         <v>42599</v>
@@ -17189,7 +17189,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G580" t="n">
-        <v>15.6675863265991</v>
+        <v>15.6675853729248</v>
       </c>
       <c r="H580" t="n">
         <v>70564</v>
@@ -17218,7 +17218,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G581" t="n">
-        <v>16.428689956665</v>
+        <v>16.4286918640137</v>
       </c>
       <c r="H581" t="n">
         <v>58962</v>
@@ -17276,7 +17276,7 @@
         <v>16.9342975616455</v>
       </c>
       <c r="G583" t="n">
-        <v>16.1873664855957</v>
+        <v>16.1873645782471</v>
       </c>
       <c r="H583" t="n">
         <v>21179</v>
@@ -17305,7 +17305,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G584" t="n">
-        <v>16.3173084259033</v>
+        <v>16.317310333252</v>
       </c>
       <c r="H584" t="n">
         <v>20341</v>
@@ -17334,7 +17334,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G585" t="n">
-        <v>16.1688022613525</v>
+        <v>16.1687984466553</v>
       </c>
       <c r="H585" t="n">
         <v>23602</v>
@@ -17392,7 +17392,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G587" t="n">
-        <v>16.595760345459</v>
+        <v>16.5957622528076</v>
       </c>
       <c r="H587" t="n">
         <v>34827</v>
@@ -17450,7 +17450,7 @@
         <v>17.1479187011719</v>
       </c>
       <c r="G589" t="n">
-        <v>16.3915634155273</v>
+        <v>16.3915615081787</v>
       </c>
       <c r="H589" t="n">
         <v>20367</v>
@@ -17537,7 +17537,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G592" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H592" t="n">
         <v>9975</v>
@@ -17566,7 +17566,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G593" t="n">
-        <v>16.595760345459</v>
+        <v>16.5957622528076</v>
       </c>
       <c r="H593" t="n">
         <v>14891</v>
@@ -17624,7 +17624,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G595" t="n">
-        <v>16.5771961212158</v>
+        <v>16.5771980285645</v>
       </c>
       <c r="H595" t="n">
         <v>9170</v>
@@ -17653,7 +17653,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G596" t="n">
-        <v>16.5215072631836</v>
+        <v>16.521505355835</v>
       </c>
       <c r="H596" t="n">
         <v>20661</v>
@@ -17682,7 +17682,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G597" t="n">
-        <v>16.5029449462891</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H597" t="n">
         <v>81026</v>
@@ -17711,7 +17711,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G598" t="n">
-        <v>16.6514530181885</v>
+        <v>16.6514549255371</v>
       </c>
       <c r="H598" t="n">
         <v>15409</v>
@@ -17740,7 +17740,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G599" t="n">
-        <v>16.7071399688721</v>
+        <v>16.7071418762207</v>
       </c>
       <c r="H599" t="n">
         <v>91536</v>
@@ -17798,7 +17798,7 @@
         <v>17.4586391448975</v>
       </c>
       <c r="G601" t="n">
-        <v>16.6885757446289</v>
+        <v>16.6885776519775</v>
       </c>
       <c r="H601" t="n">
         <v>261860</v>
@@ -17827,7 +17827,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G602" t="n">
-        <v>16.6143226623535</v>
+        <v>16.6143245697021</v>
       </c>
       <c r="H602" t="n">
         <v>70209</v>
@@ -17856,7 +17856,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G603" t="n">
-        <v>15.6861515045166</v>
+        <v>15.686149597168</v>
       </c>
       <c r="H603" t="n">
         <v>79485</v>
@@ -17943,7 +17943,7 @@
         <v>15.2641716003418</v>
       </c>
       <c r="G606" t="n">
-        <v>14.5909042358398</v>
+        <v>14.5909032821655</v>
       </c>
       <c r="H606" t="n">
         <v>36919</v>
@@ -17972,7 +17972,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G607" t="n">
-        <v>14.8507919311523</v>
+        <v>14.8507928848267</v>
       </c>
       <c r="H607" t="n">
         <v>35678</v>
@@ -18001,7 +18001,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G608" t="n">
-        <v>14.8507919311523</v>
+        <v>14.8507928848267</v>
       </c>
       <c r="H608" t="n">
         <v>24874</v>
@@ -18030,7 +18030,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G609" t="n">
-        <v>15.6861515045166</v>
+        <v>15.686149597168</v>
       </c>
       <c r="H609" t="n">
         <v>29121</v>
@@ -18059,7 +18059,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G610" t="n">
-        <v>14.9807367324829</v>
+        <v>14.9807357788086</v>
       </c>
       <c r="H610" t="n">
         <v>37926</v>
@@ -18088,7 +18088,7 @@
         <v>15.108811378479</v>
       </c>
       <c r="G611" t="n">
-        <v>14.4423961639404</v>
+        <v>14.4423971176147</v>
       </c>
       <c r="H611" t="n">
         <v>103659</v>
@@ -18262,7 +18262,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G617" t="n">
-        <v>16.1688022613525</v>
+        <v>16.1687984466553</v>
       </c>
       <c r="H617" t="n">
         <v>47046</v>
@@ -18291,7 +18291,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G618" t="n">
-        <v>15.7789659500122</v>
+        <v>15.7789669036865</v>
       </c>
       <c r="H618" t="n">
         <v>15816</v>
@@ -18320,7 +18320,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G619" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H619" t="n">
         <v>56147</v>
@@ -18349,7 +18349,7 @@
         <v>16.8760375976562</v>
       </c>
       <c r="G620" t="n">
-        <v>16.1316719055176</v>
+        <v>16.1316738128662</v>
       </c>
       <c r="H620" t="n">
         <v>12213</v>
@@ -18378,7 +18378,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G621" t="n">
-        <v>16.5215072631836</v>
+        <v>16.521505355835</v>
       </c>
       <c r="H621" t="n">
         <v>36994</v>
@@ -18436,7 +18436,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G623" t="n">
-        <v>16.595760345459</v>
+        <v>16.5957622528076</v>
       </c>
       <c r="H623" t="n">
         <v>26365</v>
@@ -18465,7 +18465,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G624" t="n">
-        <v>16.3729953765869</v>
+        <v>16.3729991912842</v>
       </c>
       <c r="H624" t="n">
         <v>31241</v>
@@ -18552,7 +18552,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G627" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H627" t="n">
         <v>49894</v>
@@ -18581,7 +18581,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G628" t="n">
-        <v>16.5029449462891</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H628" t="n">
         <v>23660</v>
@@ -18610,7 +18610,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G629" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H629" t="n">
         <v>38483</v>
@@ -18639,7 +18639,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G630" t="n">
-        <v>16.5029449462891</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H630" t="n">
         <v>20106</v>
@@ -18668,7 +18668,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G631" t="n">
-        <v>16.3173084259033</v>
+        <v>16.317310333252</v>
       </c>
       <c r="H631" t="n">
         <v>40982</v>
@@ -18871,7 +18871,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G638" t="n">
-        <v>16.7999591827393</v>
+        <v>16.7999572753906</v>
       </c>
       <c r="H638" t="n">
         <v>34698</v>
@@ -18900,7 +18900,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G639" t="n">
-        <v>16.3729953765869</v>
+        <v>16.3729991912842</v>
       </c>
       <c r="H639" t="n">
         <v>73109</v>
@@ -18929,7 +18929,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G640" t="n">
-        <v>16.7071399688721</v>
+        <v>16.7071418762207</v>
       </c>
       <c r="H640" t="n">
         <v>38853</v>
@@ -18958,7 +18958,7 @@
         <v>17.5557403564453</v>
       </c>
       <c r="G641" t="n">
-        <v>16.7813968658447</v>
+        <v>16.7813949584961</v>
       </c>
       <c r="H641" t="n">
         <v>22369</v>
@@ -19016,7 +19016,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G643" t="n">
-        <v>16.7071399688721</v>
+        <v>16.7071418762207</v>
       </c>
       <c r="H643" t="n">
         <v>69682</v>
@@ -19074,7 +19074,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G645" t="n">
-        <v>17.4125556945801</v>
+        <v>17.4125537872314</v>
       </c>
       <c r="H645" t="n">
         <v>65148</v>
@@ -19132,7 +19132,7 @@
         <v>18.7986240386963</v>
       </c>
       <c r="G647" t="n">
-        <v>17.9694595336914</v>
+        <v>17.9694576263428</v>
       </c>
       <c r="H647" t="n">
         <v>7183</v>
@@ -19161,7 +19161,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G648" t="n">
-        <v>18.4149856567383</v>
+        <v>18.414981842041</v>
       </c>
       <c r="H648" t="n">
         <v>15115</v>
@@ -19190,7 +19190,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G649" t="n">
-        <v>17.8023853302002</v>
+        <v>17.8023872375488</v>
       </c>
       <c r="H649" t="n">
         <v>20632</v>
@@ -19248,7 +19248,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G651" t="n">
-        <v>16.7999591827393</v>
+        <v>16.7999572753906</v>
       </c>
       <c r="H651" t="n">
         <v>3928533</v>
@@ -19277,7 +19277,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G652" t="n">
-        <v>16.5771961212158</v>
+        <v>16.5771980285645</v>
       </c>
       <c r="H652" t="n">
         <v>146523</v>
@@ -19393,7 +19393,7 @@
         <v>17.4003791809082</v>
       </c>
       <c r="G656" t="n">
-        <v>16.6328887939453</v>
+        <v>16.6328907012939</v>
       </c>
       <c r="H656" t="n">
         <v>33953</v>
@@ -19422,7 +19422,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G657" t="n">
-        <v>16.7071399688721</v>
+        <v>16.7071418762207</v>
       </c>
       <c r="H657" t="n">
         <v>18230</v>
@@ -19480,7 +19480,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G659" t="n">
-        <v>16.595760345459</v>
+        <v>16.5957622528076</v>
       </c>
       <c r="H659" t="n">
         <v>86369</v>
@@ -19509,7 +19509,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G660" t="n">
-        <v>16.5029449462891</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H660" t="n">
         <v>15595</v>
@@ -19538,7 +19538,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G661" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H661" t="n">
         <v>79956</v>
@@ -19596,7 +19596,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G663" t="n">
-        <v>16.3729953765869</v>
+        <v>16.3729991912842</v>
       </c>
       <c r="H663" t="n">
         <v>19638</v>
@@ -19625,7 +19625,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G664" t="n">
-        <v>16.3729953765869</v>
+        <v>16.3729991912842</v>
       </c>
       <c r="H664" t="n">
         <v>18813</v>
@@ -19683,7 +19683,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G666" t="n">
-        <v>16.5215072631836</v>
+        <v>16.521505355835</v>
       </c>
       <c r="H666" t="n">
         <v>47042</v>
@@ -19741,7 +19741,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G668" t="n">
-        <v>16.1688022613525</v>
+        <v>16.1687984466553</v>
       </c>
       <c r="H668" t="n">
         <v>98048</v>
@@ -19770,7 +19770,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G669" t="n">
-        <v>15.7789659500122</v>
+        <v>15.7789669036865</v>
       </c>
       <c r="H669" t="n">
         <v>79199</v>
@@ -19799,7 +19799,7 @@
         <v>16.9537181854248</v>
       </c>
       <c r="G670" t="n">
-        <v>16.2059288024902</v>
+        <v>16.2059307098389</v>
       </c>
       <c r="H670" t="n">
         <v>39708</v>
@@ -19857,7 +19857,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G672" t="n">
-        <v>16.7999591827393</v>
+        <v>16.7999572753906</v>
       </c>
       <c r="H672" t="n">
         <v>35437</v>
@@ -19915,7 +19915,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G674" t="n">
-        <v>16.3173084259033</v>
+        <v>16.317310333252</v>
       </c>
       <c r="H674" t="n">
         <v>71685</v>
@@ -19944,7 +19944,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G675" t="n">
-        <v>16.428689956665</v>
+        <v>16.4286918640137</v>
       </c>
       <c r="H675" t="n">
         <v>29643</v>
@@ -19973,7 +19973,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G676" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H676" t="n">
         <v>54594</v>
@@ -20002,7 +20002,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G677" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H677" t="n">
         <v>29454</v>
@@ -20031,7 +20031,7 @@
         <v>16.9537181854248</v>
       </c>
       <c r="G678" t="n">
-        <v>16.2059288024902</v>
+        <v>16.2059307098389</v>
       </c>
       <c r="H678" t="n">
         <v>12610</v>
@@ -20118,7 +20118,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G681" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H681" t="n">
         <v>28477</v>
@@ -20147,7 +20147,7 @@
         <v>16.7012577056885</v>
       </c>
       <c r="G682" t="n">
-        <v>15.9646053314209</v>
+        <v>15.9646043777466</v>
       </c>
       <c r="H682" t="n">
         <v>13217</v>
@@ -20205,7 +20205,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G684" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H684" t="n">
         <v>45521</v>
@@ -20234,7 +20234,7 @@
         <v>16.8760375976562</v>
       </c>
       <c r="G685" t="n">
-        <v>16.1316719055176</v>
+        <v>16.1316738128662</v>
       </c>
       <c r="H685" t="n">
         <v>33702</v>
@@ -20263,7 +20263,7 @@
         <v>16.3711166381836</v>
       </c>
       <c r="G686" t="n">
-        <v>15.6490240097046</v>
+        <v>15.6490230560303</v>
       </c>
       <c r="H686" t="n">
         <v>56048</v>
@@ -20321,7 +20321,7 @@
         <v>16.9342975616455</v>
       </c>
       <c r="G688" t="n">
-        <v>16.1873664855957</v>
+        <v>16.1873645782471</v>
       </c>
       <c r="H688" t="n">
         <v>61499</v>
@@ -20350,7 +20350,7 @@
         <v>16.6429977416992</v>
       </c>
       <c r="G689" t="n">
-        <v>15.9089126586914</v>
+        <v>15.90891456604</v>
       </c>
       <c r="H689" t="n">
         <v>39172</v>
@@ -20408,7 +20408,7 @@
         <v>16.6041564941406</v>
       </c>
       <c r="G691" t="n">
-        <v>15.8717842102051</v>
+        <v>15.8717851638794</v>
       </c>
       <c r="H691" t="n">
         <v>35414</v>
@@ -20756,7 +20756,7 @@
         <v>16.2934341430664</v>
       </c>
       <c r="G703" t="n">
-        <v>15.5747671127319</v>
+        <v>15.5747690200806</v>
       </c>
       <c r="H703" t="n">
         <v>77089</v>
@@ -20785,7 +20785,7 @@
         <v>16.1380748748779</v>
       </c>
       <c r="G704" t="n">
-        <v>15.4262619018555</v>
+        <v>15.4262609481812</v>
       </c>
       <c r="H704" t="n">
         <v>145218</v>
@@ -20814,7 +20814,7 @@
         <v>16.332275390625</v>
       </c>
       <c r="G705" t="n">
-        <v>15.6118946075439</v>
+        <v>15.6118974685669</v>
       </c>
       <c r="H705" t="n">
         <v>37102</v>
@@ -20930,7 +20930,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G709" t="n">
-        <v>15.6675863265991</v>
+        <v>15.6675853729248</v>
       </c>
       <c r="H709" t="n">
         <v>47583</v>
@@ -20988,7 +20988,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G711" t="n">
-        <v>15.760404586792</v>
+        <v>15.7604055404663</v>
       </c>
       <c r="H711" t="n">
         <v>25713</v>
@@ -21017,7 +21017,7 @@
         <v>16.856616973877</v>
       </c>
       <c r="G712" t="n">
-        <v>16.1131076812744</v>
+        <v>16.113109588623</v>
       </c>
       <c r="H712" t="n">
         <v>96484</v>
@@ -21046,7 +21046,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G713" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H713" t="n">
         <v>26553</v>
@@ -21075,7 +21075,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G714" t="n">
-        <v>16.5771961212158</v>
+        <v>16.5771980285645</v>
       </c>
       <c r="H714" t="n">
         <v>51273</v>
@@ -21133,7 +21133,7 @@
         <v>17.8082008361816</v>
       </c>
       <c r="G716" t="n">
-        <v>17.0227203369141</v>
+        <v>17.0227222442627</v>
       </c>
       <c r="H716" t="n">
         <v>35076</v>
@@ -21162,7 +21162,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G717" t="n">
-        <v>17.820951461792</v>
+        <v>17.8209552764893</v>
       </c>
       <c r="H717" t="n">
         <v>158059</v>
@@ -21191,7 +21191,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G718" t="n">
-        <v>17.5424995422363</v>
+        <v>17.542501449585</v>
       </c>
       <c r="H718" t="n">
         <v>38062</v>
@@ -21220,7 +21220,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G719" t="n">
-        <v>17.5424995422363</v>
+        <v>17.542501449585</v>
       </c>
       <c r="H719" t="n">
         <v>75597</v>
@@ -21278,7 +21278,7 @@
         <v>18.4684829711914</v>
       </c>
       <c r="G721" t="n">
-        <v>17.653881072998</v>
+        <v>17.6538791656494</v>
       </c>
       <c r="H721" t="n">
         <v>36426</v>
@@ -21336,7 +21336,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G723" t="n">
-        <v>17.820951461792</v>
+        <v>17.8209552764893</v>
       </c>
       <c r="H723" t="n">
         <v>65985</v>
@@ -21394,7 +21394,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G725" t="n">
-        <v>17.820951461792</v>
+        <v>17.8209552764893</v>
       </c>
       <c r="H725" t="n">
         <v>27519</v>
@@ -21452,7 +21452,7 @@
         <v>18.779203414917</v>
       </c>
       <c r="G727" t="n">
-        <v>17.9508972167969</v>
+        <v>17.9508934020996</v>
       </c>
       <c r="H727" t="n">
         <v>22119</v>
@@ -21510,7 +21510,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G729" t="n">
-        <v>17.2640438079834</v>
+        <v>17.2640476226807</v>
       </c>
       <c r="H729" t="n">
         <v>33955</v>
@@ -21539,7 +21539,7 @@
         <v>17.8470401763916</v>
       </c>
       <c r="G730" t="n">
-        <v>17.0598487854004</v>
+        <v>17.0598468780518</v>
       </c>
       <c r="H730" t="n">
         <v>46352</v>
@@ -21626,7 +21626,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G733" t="n">
-        <v>17.4496822357178</v>
+        <v>17.4496803283691</v>
       </c>
       <c r="H733" t="n">
         <v>16597</v>
@@ -21655,7 +21655,7 @@
         <v>18.293701171875</v>
       </c>
       <c r="G734" t="n">
-        <v>17.4868049621582</v>
+        <v>17.4868087768555</v>
       </c>
       <c r="H734" t="n">
         <v>66103</v>
@@ -21684,7 +21684,7 @@
         <v>18.4490623474121</v>
       </c>
       <c r="G735" t="n">
-        <v>17.6353187561035</v>
+        <v>17.6353168487549</v>
       </c>
       <c r="H735" t="n">
         <v>39308</v>
@@ -21771,7 +21771,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G738" t="n">
-        <v>19.6772994995117</v>
+        <v>19.6773014068604</v>
       </c>
       <c r="H738" t="n">
         <v>55073</v>
@@ -21800,7 +21800,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G739" t="n">
-        <v>19.3060321807861</v>
+        <v>19.3060302734375</v>
       </c>
       <c r="H739" t="n">
         <v>45305</v>
@@ -21829,7 +21829,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G740" t="n">
-        <v>19.3988475799561</v>
+        <v>19.3988456726074</v>
       </c>
       <c r="H740" t="n">
         <v>63358</v>
@@ -21887,7 +21887,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G742" t="n">
-        <v>20.4198379516602</v>
+        <v>20.4198417663574</v>
       </c>
       <c r="H742" t="n">
         <v>47386</v>
@@ -21916,7 +21916,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G743" t="n">
-        <v>20.3270244598389</v>
+        <v>20.3270263671875</v>
       </c>
       <c r="H743" t="n">
         <v>30114</v>
@@ -22003,7 +22003,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G746" t="n">
-        <v>19.8165264129639</v>
+        <v>19.8165283203125</v>
       </c>
       <c r="H746" t="n">
         <v>36026</v>
@@ -22061,7 +22061,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G748" t="n">
-        <v>20.0949783325195</v>
+        <v>20.0949802398682</v>
       </c>
       <c r="H748" t="n">
         <v>43044</v>
@@ -22090,7 +22090,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G749" t="n">
-        <v>20.4662494659424</v>
+        <v>20.466251373291</v>
       </c>
       <c r="H749" t="n">
         <v>34125</v>
@@ -22148,7 +22148,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G751" t="n">
-        <v>21.0695610046387</v>
+        <v>21.0695648193359</v>
       </c>
       <c r="H751" t="n">
         <v>190456</v>
@@ -22177,7 +22177,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G752" t="n">
-        <v>21.4408340454102</v>
+        <v>21.4408359527588</v>
       </c>
       <c r="H752" t="n">
         <v>38481</v>
@@ -22235,7 +22235,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G754" t="n">
-        <v>21.1623783111572</v>
+        <v>21.1623821258545</v>
       </c>
       <c r="H754" t="n">
         <v>35943</v>
@@ -22293,7 +22293,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G756" t="n">
-        <v>20.4662494659424</v>
+        <v>20.466251373291</v>
       </c>
       <c r="H756" t="n">
         <v>70825</v>
@@ -22322,7 +22322,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G757" t="n">
-        <v>20.4198379516602</v>
+        <v>20.4198417663574</v>
       </c>
       <c r="H757" t="n">
         <v>20797</v>
@@ -22351,7 +22351,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G758" t="n">
-        <v>20.3270244598389</v>
+        <v>20.3270263671875</v>
       </c>
       <c r="H758" t="n">
         <v>23340</v>
@@ -22409,7 +22409,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G760" t="n">
-        <v>20.0949783325195</v>
+        <v>20.0949802398682</v>
       </c>
       <c r="H760" t="n">
         <v>18398</v>
@@ -22467,7 +22467,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G762" t="n">
-        <v>19.8165264129639</v>
+        <v>19.8165283203125</v>
       </c>
       <c r="H762" t="n">
         <v>62037</v>
@@ -22525,7 +22525,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G764" t="n">
-        <v>19.6308898925781</v>
+        <v>19.6308917999268</v>
       </c>
       <c r="H764" t="n">
         <v>34886</v>
@@ -22583,7 +22583,7 @@
         <v>20.245418548584</v>
       </c>
       <c r="G766" t="n">
-        <v>19.3524379730225</v>
+        <v>19.3524398803711</v>
       </c>
       <c r="H766" t="n">
         <v>22875</v>
@@ -22670,7 +22670,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G769" t="n">
-        <v>19.8395614624023</v>
+        <v>19.8395595550537</v>
       </c>
       <c r="H769" t="n">
         <v>15945</v>
@@ -22699,7 +22699,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G770" t="n">
-        <v>19.6528339385986</v>
+        <v>19.6528358459473</v>
       </c>
       <c r="H770" t="n">
         <v>12394</v>
@@ -22728,7 +22728,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G771" t="n">
-        <v>19.3260669708252</v>
+        <v>19.3260688781738</v>
       </c>
       <c r="H771" t="n">
         <v>16954</v>
@@ -22757,7 +22757,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G772" t="n">
-        <v>19.4194316864014</v>
+        <v>19.4194297790527</v>
       </c>
       <c r="H772" t="n">
         <v>23520</v>
@@ -22786,7 +22786,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G773" t="n">
-        <v>19.3727493286133</v>
+        <v>19.3727474212646</v>
       </c>
       <c r="H773" t="n">
         <v>12388</v>
@@ -22815,7 +22815,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G774" t="n">
-        <v>19.5594730377197</v>
+        <v>19.5594711303711</v>
       </c>
       <c r="H774" t="n">
         <v>14470</v>
@@ -22844,7 +22844,7 @@
         <v>19.6628170013428</v>
       </c>
       <c r="G775" t="n">
-        <v>18.9059352874756</v>
+        <v>18.905933380127</v>
       </c>
       <c r="H775" t="n">
         <v>26959</v>
@@ -22902,7 +22902,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G777" t="n">
-        <v>19.0459785461426</v>
+        <v>19.0459804534912</v>
       </c>
       <c r="H777" t="n">
         <v>45204</v>
@@ -22931,7 +22931,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G778" t="n">
-        <v>18.952615737915</v>
+        <v>18.9526138305664</v>
       </c>
       <c r="H778" t="n">
         <v>17562</v>
@@ -22960,7 +22960,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G779" t="n">
-        <v>18.8125762939453</v>
+        <v>18.812572479248</v>
       </c>
       <c r="H779" t="n">
         <v>10927</v>
@@ -23047,7 +23047,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G782" t="n">
-        <v>19.6528339385986</v>
+        <v>19.6528358459473</v>
       </c>
       <c r="H782" t="n">
         <v>29187</v>
@@ -23134,7 +23134,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G785" t="n">
-        <v>19.1393375396729</v>
+        <v>19.1393394470215</v>
       </c>
       <c r="H785" t="n">
         <v>17581</v>
@@ -23163,7 +23163,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G786" t="n">
-        <v>19.0459785461426</v>
+        <v>19.0459804534912</v>
       </c>
       <c r="H786" t="n">
         <v>21706</v>
@@ -23192,7 +23192,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G787" t="n">
-        <v>18.952615737915</v>
+        <v>18.9526138305664</v>
       </c>
       <c r="H787" t="n">
         <v>20741</v>
@@ -23250,7 +23250,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G789" t="n">
-        <v>18.5044765472412</v>
+        <v>18.5044746398926</v>
       </c>
       <c r="H789" t="n">
         <v>32253</v>
@@ -23337,7 +23337,7 @@
         <v>19.1287651062012</v>
       </c>
       <c r="G792" t="n">
-        <v>18.3924369812012</v>
+        <v>18.3924388885498</v>
       </c>
       <c r="H792" t="n">
         <v>27508</v>
@@ -23366,7 +23366,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G793" t="n">
-        <v>18.6725292205811</v>
+        <v>18.6725273132324</v>
       </c>
       <c r="H793" t="n">
         <v>38165</v>
@@ -23395,7 +23395,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G794" t="n">
-        <v>18.6725292205811</v>
+        <v>18.6725273132324</v>
       </c>
       <c r="H794" t="n">
         <v>26327</v>
@@ -23453,7 +23453,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G796" t="n">
-        <v>18.6725292205811</v>
+        <v>18.6725273132324</v>
       </c>
       <c r="H796" t="n">
         <v>16839</v>
@@ -23511,7 +23511,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G798" t="n">
-        <v>18.6725292205811</v>
+        <v>18.6725273132324</v>
       </c>
       <c r="H798" t="n">
         <v>43372</v>
@@ -23569,7 +23569,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G800" t="n">
-        <v>19.9329223632812</v>
+        <v>19.9329242706299</v>
       </c>
       <c r="H800" t="n">
         <v>31271</v>
@@ -23685,7 +23685,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G804" t="n">
-        <v>21.1466369628906</v>
+        <v>21.146635055542</v>
       </c>
       <c r="H804" t="n">
         <v>37567</v>
@@ -23714,7 +23714,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G805" t="n">
-        <v>21.940221786499</v>
+        <v>21.9402198791504</v>
       </c>
       <c r="H805" t="n">
         <v>86390</v>
@@ -23743,7 +23743,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G806" t="n">
-        <v>22.3136692047119</v>
+        <v>22.3136711120605</v>
       </c>
       <c r="H806" t="n">
         <v>51200</v>
@@ -23801,7 +23801,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G808" t="n">
-        <v>23.0605716705322</v>
+        <v>23.0605735778809</v>
       </c>
       <c r="H808" t="n">
         <v>33989</v>
@@ -23859,7 +23859,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G810" t="n">
-        <v>23.0138931274414</v>
+        <v>23.0138912200928</v>
       </c>
       <c r="H810" t="n">
         <v>13899</v>
@@ -23888,7 +23888,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G811" t="n">
-        <v>22.920524597168</v>
+        <v>22.9205265045166</v>
       </c>
       <c r="H811" t="n">
         <v>38908</v>
@@ -23946,7 +23946,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G813" t="n">
-        <v>24.0408802032471</v>
+        <v>24.0408782958984</v>
       </c>
       <c r="H813" t="n">
         <v>26369</v>
@@ -23975,7 +23975,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G814" t="n">
-        <v>23.6207485198975</v>
+        <v>23.6207466125488</v>
       </c>
       <c r="H814" t="n">
         <v>58204</v>
@@ -24033,7 +24033,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G816" t="n">
-        <v>23.0138931274414</v>
+        <v>23.0138912200928</v>
       </c>
       <c r="H816" t="n">
         <v>22302</v>
@@ -24062,7 +24062,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G817" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738441467285</v>
       </c>
       <c r="H817" t="n">
         <v>16282</v>
@@ -24091,7 +24091,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G818" t="n">
-        <v>22.6871204376221</v>
+        <v>22.6871223449707</v>
       </c>
       <c r="H818" t="n">
         <v>14320</v>
@@ -24149,7 +24149,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G820" t="n">
-        <v>23.0138931274414</v>
+        <v>23.0138912200928</v>
       </c>
       <c r="H820" t="n">
         <v>8262</v>
@@ -24178,7 +24178,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G821" t="n">
-        <v>23.6207485198975</v>
+        <v>23.6207466125488</v>
       </c>
       <c r="H821" t="n">
         <v>21213</v>
@@ -24294,7 +24294,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G825" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738441467285</v>
       </c>
       <c r="H825" t="n">
         <v>6260</v>
@@ -24323,7 +24323,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G826" t="n">
-        <v>22.780481338501</v>
+        <v>22.7804851531982</v>
       </c>
       <c r="H826" t="n">
         <v>13768</v>
@@ -24381,7 +24381,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G828" t="n">
-        <v>23.0605716705322</v>
+        <v>23.0605735778809</v>
       </c>
       <c r="H828" t="n">
         <v>15395</v>
@@ -24526,7 +24526,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G833" t="n">
-        <v>22.780481338501</v>
+        <v>22.7804851531982</v>
       </c>
       <c r="H833" t="n">
         <v>16579</v>
@@ -24613,7 +24613,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G836" t="n">
-        <v>24.0408802032471</v>
+        <v>24.0408782958984</v>
       </c>
       <c r="H836" t="n">
         <v>28089</v>
@@ -24700,7 +24700,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G839" t="n">
-        <v>21.6134510040283</v>
+        <v>21.613452911377</v>
       </c>
       <c r="H839" t="n">
         <v>26813</v>
@@ -24729,7 +24729,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G840" t="n">
-        <v>21.5667705535889</v>
+        <v>21.5667724609375</v>
       </c>
       <c r="H840" t="n">
         <v>38817</v>
@@ -24758,7 +24758,7 @@
         <v>22.8671283721924</v>
       </c>
       <c r="G841" t="n">
-        <v>21.9869022369385</v>
+        <v>21.9869041442871</v>
       </c>
       <c r="H841" t="n">
         <v>23080</v>
@@ -24787,7 +24787,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G842" t="n">
-        <v>21.800178527832</v>
+        <v>21.8001747131348</v>
       </c>
       <c r="H842" t="n">
         <v>13062</v>
@@ -24845,7 +24845,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G844" t="n">
-        <v>21.0065956115723</v>
+        <v>21.0065937042236</v>
       </c>
       <c r="H844" t="n">
         <v>14580</v>
@@ -24903,7 +24903,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G846" t="n">
-        <v>20.8198680877686</v>
+        <v>20.8198699951172</v>
       </c>
       <c r="H846" t="n">
         <v>17246</v>
@@ -24990,7 +24990,7 @@
         <v>21.9446754455566</v>
       </c>
       <c r="G849" t="n">
-        <v>21.0999546051025</v>
+        <v>21.0999565124512</v>
       </c>
       <c r="H849" t="n">
         <v>19081</v>
@@ -25019,7 +25019,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G850" t="n">
-        <v>21.7068099975586</v>
+        <v>21.7068119049072</v>
       </c>
       <c r="H850" t="n">
         <v>13745</v>
@@ -25048,7 +25048,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G851" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738441467285</v>
       </c>
       <c r="H851" t="n">
         <v>26308</v>
@@ -25077,7 +25077,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G852" t="n">
-        <v>24.6477375030518</v>
+        <v>24.6477355957031</v>
       </c>
       <c r="H852" t="n">
         <v>77188</v>
@@ -25106,7 +25106,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G853" t="n">
-        <v>24.5076923370361</v>
+        <v>24.5076904296875</v>
       </c>
       <c r="H853" t="n">
         <v>25642</v>
@@ -25135,7 +25135,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G854" t="n">
-        <v>24.8344593048096</v>
+        <v>24.8344612121582</v>
       </c>
       <c r="H854" t="n">
         <v>21104</v>
@@ -25193,7 +25193,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G856" t="n">
-        <v>24.5076923370361</v>
+        <v>24.5076904296875</v>
       </c>
       <c r="H856" t="n">
         <v>9746</v>
@@ -25251,7 +25251,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G858" t="n">
-        <v>23.2472953796387</v>
+        <v>23.2472972869873</v>
       </c>
       <c r="H858" t="n">
         <v>50612</v>
@@ -25338,7 +25338,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G861" t="n">
-        <v>23.2472953796387</v>
+        <v>23.2472972869873</v>
       </c>
       <c r="H861" t="n">
         <v>15469</v>
@@ -25483,7 +25483,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G866" t="n">
-        <v>24.1342430114746</v>
+        <v>24.134241104126</v>
       </c>
       <c r="H866" t="n">
         <v>117339</v>
@@ -25512,7 +25512,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G867" t="n">
-        <v>24.1342430114746</v>
+        <v>24.134241104126</v>
       </c>
       <c r="H867" t="n">
         <v>37673</v>
@@ -25541,7 +25541,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G868" t="n">
-        <v>23.8074741363525</v>
+        <v>23.8074760437012</v>
       </c>
       <c r="H868" t="n">
         <v>43603</v>
@@ -25570,7 +25570,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G869" t="n">
-        <v>23.8074741363525</v>
+        <v>23.8074760437012</v>
       </c>
       <c r="H869" t="n">
         <v>33654</v>
@@ -25628,7 +25628,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G871" t="n">
-        <v>24.3209667205811</v>
+        <v>24.3209686279297</v>
       </c>
       <c r="H871" t="n">
         <v>5605</v>
@@ -25657,7 +25657,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G872" t="n">
-        <v>24.5076923370361</v>
+        <v>24.5076904296875</v>
       </c>
       <c r="H872" t="n">
         <v>6996</v>
@@ -25773,7 +25773,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G876" t="n">
-        <v>25.207914352417</v>
+        <v>25.2079105377197</v>
       </c>
       <c r="H876" t="n">
         <v>118395</v>
@@ -25860,7 +25860,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G879" t="n">
-        <v>23.6207485198975</v>
+        <v>23.6207466125488</v>
       </c>
       <c r="H879" t="n">
         <v>27220</v>
@@ -25918,7 +25918,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G881" t="n">
-        <v>23.1539363861084</v>
+        <v>23.1539344787598</v>
       </c>
       <c r="H881" t="n">
         <v>12809</v>
@@ -25947,7 +25947,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G882" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738441467285</v>
       </c>
       <c r="H882" t="n">
         <v>33759</v>
@@ -26005,7 +26005,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G884" t="n">
-        <v>22.1269435882568</v>
+        <v>22.1269474029541</v>
       </c>
       <c r="H884" t="n">
         <v>44427</v>
@@ -26063,7 +26063,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G886" t="n">
-        <v>22.1269435882568</v>
+        <v>22.1269474029541</v>
       </c>
       <c r="H886" t="n">
         <v>27142</v>
@@ -26121,7 +26121,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G888" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738441467285</v>
       </c>
       <c r="H888" t="n">
         <v>19991</v>
@@ -26237,7 +26237,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G892" t="n">
-        <v>24.5076923370361</v>
+        <v>24.5076904296875</v>
       </c>
       <c r="H892" t="n">
         <v>14791</v>
@@ -26266,7 +26266,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G893" t="n">
-        <v>24.3676509857178</v>
+        <v>24.3676490783691</v>
       </c>
       <c r="H893" t="n">
         <v>9165</v>
@@ -26295,7 +26295,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G894" t="n">
-        <v>24.3209667205811</v>
+        <v>24.3209686279297</v>
       </c>
       <c r="H894" t="n">
         <v>89124</v>
@@ -26353,7 +26353,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G896" t="n">
-        <v>24.3676509857178</v>
+        <v>24.3676490783691</v>
       </c>
       <c r="H896" t="n">
         <v>15752</v>
@@ -26382,7 +26382,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G897" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738441467285</v>
       </c>
       <c r="H897" t="n">
         <v>55336</v>
@@ -26411,7 +26411,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G898" t="n">
-        <v>22.8738460540771</v>
+        <v>22.8738441467285</v>
       </c>
       <c r="H898" t="n">
         <v>40638</v>
@@ -26440,7 +26440,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G899" t="n">
-        <v>23.0605716705322</v>
+        <v>23.0605735778809</v>
       </c>
       <c r="H899" t="n">
         <v>20497</v>
@@ -26469,7 +26469,7 @@
         <v>24.7120342254639</v>
       </c>
       <c r="G900" t="n">
-        <v>23.7607917785645</v>
+        <v>23.7607898712158</v>
       </c>
       <c r="H900" t="n">
         <v>11109</v>
@@ -26527,7 +26527,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G902" t="n">
-        <v>23.854154586792</v>
+        <v>23.8541564941406</v>
       </c>
       <c r="H902" t="n">
         <v>4095</v>
@@ -26556,7 +26556,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G903" t="n">
-        <v>23.8074741363525</v>
+        <v>23.8074760437012</v>
       </c>
       <c r="H903" t="n">
         <v>3761</v>
@@ -26585,7 +26585,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G904" t="n">
-        <v>24.6944179534912</v>
+        <v>24.6944198608398</v>
       </c>
       <c r="H904" t="n">
         <v>9853</v>
@@ -26614,7 +26614,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G905" t="n">
-        <v>24.8344593048096</v>
+        <v>24.8344612121582</v>
       </c>
       <c r="H905" t="n">
         <v>15263</v>
@@ -26643,7 +26643,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G906" t="n">
-        <v>24.461009979248</v>
+        <v>24.4610118865967</v>
       </c>
       <c r="H906" t="n">
         <v>20215</v>
@@ -26672,7 +26672,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G907" t="n">
-        <v>24.461009979248</v>
+        <v>24.4610118865967</v>
       </c>
       <c r="H907" t="n">
         <v>22995</v>
@@ -26701,7 +26701,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G908" t="n">
-        <v>23.854154586792</v>
+        <v>23.8541564941406</v>
       </c>
       <c r="H908" t="n">
         <v>22990</v>
@@ -26730,7 +26730,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G909" t="n">
-        <v>23.8074741363525</v>
+        <v>23.8074760437012</v>
       </c>
       <c r="H909" t="n">
         <v>30538</v>
@@ -26817,7 +26817,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G912" t="n">
-        <v>24.3209667205811</v>
+        <v>24.3209686279297</v>
       </c>
       <c r="H912" t="n">
         <v>54129</v>
@@ -26875,7 +26875,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G914" t="n">
-        <v>24.9745044708252</v>
+        <v>24.9745082855225</v>
       </c>
       <c r="H914" t="n">
         <v>27980</v>
@@ -27049,7 +27049,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G920" t="n">
-        <v>22.780481338501</v>
+        <v>22.7804851531982</v>
       </c>
       <c r="H920" t="n">
         <v>16018</v>
@@ -27136,7 +27136,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G923" t="n">
-        <v>21.2866802215576</v>
+        <v>21.2866821289062</v>
       </c>
       <c r="H923" t="n">
         <v>17634</v>
@@ -27194,7 +27194,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G925" t="n">
-        <v>20.30637550354</v>
+        <v>20.3063735961914</v>
       </c>
       <c r="H925" t="n">
         <v>25585</v>
@@ -27223,7 +27223,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G926" t="n">
-        <v>19.8395614624023</v>
+        <v>19.8395595550537</v>
       </c>
       <c r="H926" t="n">
         <v>42284</v>
@@ -27252,7 +27252,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G927" t="n">
-        <v>21.1466369628906</v>
+        <v>21.146635055542</v>
       </c>
       <c r="H927" t="n">
         <v>93245</v>
@@ -27310,7 +27310,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G929" t="n">
-        <v>21.1466369628906</v>
+        <v>21.146635055542</v>
       </c>
       <c r="H929" t="n">
         <v>29524</v>
@@ -27339,7 +27339,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G930" t="n">
-        <v>21.0065956115723</v>
+        <v>21.0065937042236</v>
       </c>
       <c r="H930" t="n">
         <v>21059</v>
@@ -27455,7 +27455,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G934" t="n">
-        <v>21.4734077453613</v>
+        <v>21.4734058380127</v>
       </c>
       <c r="H934" t="n">
         <v>71464</v>
@@ -27542,7 +27542,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G937" t="n">
-        <v>21.7068099975586</v>
+        <v>21.7068119049072</v>
       </c>
       <c r="H937" t="n">
         <v>45513</v>
@@ -27571,7 +27571,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G938" t="n">
-        <v>21.1466369628906</v>
+        <v>21.146635055542</v>
       </c>
       <c r="H938" t="n">
         <v>20938</v>
@@ -27629,7 +27629,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G940" t="n">
-        <v>21.0065956115723</v>
+        <v>21.0065937042236</v>
       </c>
       <c r="H940" t="n">
         <v>14225</v>
@@ -27687,7 +27687,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G942" t="n">
-        <v>20.2130107879639</v>
+        <v>20.2130126953125</v>
       </c>
       <c r="H942" t="n">
         <v>25603</v>
@@ -27716,7 +27716,7 @@
         <v>19.8570175170898</v>
       </c>
       <c r="G943" t="n">
-        <v>19.0926609039307</v>
+        <v>19.092658996582</v>
       </c>
       <c r="H943" t="n">
         <v>28032</v>
@@ -27745,7 +27745,7 @@
         <v>19.1870250701904</v>
       </c>
       <c r="G944" t="n">
-        <v>18.4484577178955</v>
+        <v>18.4484558105469</v>
       </c>
       <c r="H944" t="n">
         <v>106164</v>
@@ -27832,7 +27832,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G947" t="n">
-        <v>19.3260669708252</v>
+        <v>19.3260688781738</v>
       </c>
       <c r="H947" t="n">
         <v>31704</v>
@@ -27861,7 +27861,7 @@
         <v>20.0026683807373</v>
       </c>
       <c r="G948" t="n">
-        <v>19.2327060699463</v>
+        <v>19.232702255249</v>
       </c>
       <c r="H948" t="n">
         <v>67870</v>
@@ -27948,7 +27948,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G951" t="n">
-        <v>16.9359836578369</v>
+        <v>16.9359817504883</v>
       </c>
       <c r="H951" t="n">
         <v>122448</v>
@@ -28064,7 +28064,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G955" t="n">
-        <v>18.541820526123</v>
+        <v>18.5418224334717</v>
       </c>
       <c r="H955" t="n">
         <v>25102</v>
@@ -28093,7 +28093,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G956" t="n">
-        <v>19.7928791046143</v>
+        <v>19.7928810119629</v>
       </c>
       <c r="H956" t="n">
         <v>33741</v>
@@ -28122,7 +28122,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G957" t="n">
-        <v>19.4194316864014</v>
+        <v>19.4194297790527</v>
       </c>
       <c r="H957" t="n">
         <v>74285</v>
@@ -28151,7 +28151,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G958" t="n">
-        <v>20.30637550354</v>
+        <v>20.3063735961914</v>
       </c>
       <c r="H958" t="n">
         <v>43792</v>
@@ -28180,7 +28180,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G959" t="n">
-        <v>20.30637550354</v>
+        <v>20.3063735961914</v>
       </c>
       <c r="H959" t="n">
         <v>29781</v>
@@ -28296,7 +28296,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G963" t="n">
-        <v>21.7068099975586</v>
+        <v>21.7068119049072</v>
       </c>
       <c r="H963" t="n">
         <v>33438</v>
@@ -28325,7 +28325,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G964" t="n">
-        <v>21.5200901031494</v>
+        <v>21.5200862884521</v>
       </c>
       <c r="H964" t="n">
         <v>39656</v>
@@ -28354,7 +28354,7 @@
         <v>22.7214775085449</v>
       </c>
       <c r="G965" t="n">
-        <v>21.8468570709229</v>
+        <v>21.8468589782715</v>
       </c>
       <c r="H965" t="n">
         <v>94239</v>
@@ -28412,7 +28412,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G967" t="n">
-        <v>22.1736259460449</v>
+        <v>22.1736278533936</v>
       </c>
       <c r="H967" t="n">
         <v>17485</v>
@@ -28441,7 +28441,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G968" t="n">
-        <v>23.0138931274414</v>
+        <v>23.0138912200928</v>
       </c>
       <c r="H968" t="n">
         <v>48550</v>
@@ -28470,7 +28470,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G969" t="n">
-        <v>21.7068099975586</v>
+        <v>21.7068119049072</v>
       </c>
       <c r="H969" t="n">
         <v>56367</v>
@@ -28731,7 +28731,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G978" t="n">
-        <v>20.30637550354</v>
+        <v>20.3063735961914</v>
       </c>
       <c r="H978" t="n">
         <v>23820</v>
@@ -28876,7 +28876,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G983" t="n">
-        <v>21.5667705535889</v>
+        <v>21.5667724609375</v>
       </c>
       <c r="H983" t="n">
         <v>57275</v>
@@ -28905,7 +28905,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G984" t="n">
-        <v>21.5200901031494</v>
+        <v>21.5200862884521</v>
       </c>
       <c r="H984" t="n">
         <v>105068</v>
@@ -28934,7 +28934,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G985" t="n">
-        <v>21.4734077453613</v>
+        <v>21.4734058380127</v>
       </c>
       <c r="H985" t="n">
         <v>81020</v>
@@ -29021,7 +29021,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G988" t="n">
-        <v>21.5200901031494</v>
+        <v>21.5200862884521</v>
       </c>
       <c r="H988" t="n">
         <v>14264</v>
@@ -29050,7 +29050,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G989" t="n">
-        <v>22.1736259460449</v>
+        <v>22.1736278533936</v>
       </c>
       <c r="H989" t="n">
         <v>51340</v>
@@ -29079,7 +29079,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G990" t="n">
-        <v>21.800178527832</v>
+        <v>21.8001747131348</v>
       </c>
       <c r="H990" t="n">
         <v>24793</v>
@@ -29108,7 +29108,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G991" t="n">
-        <v>21.5667705535889</v>
+        <v>21.5667724609375</v>
       </c>
       <c r="H991" t="n">
         <v>11542</v>
@@ -29224,7 +29224,7 @@
         <v>19.3229656219482</v>
       </c>
       <c r="G995" t="n">
-        <v>18.5791625976562</v>
+        <v>18.5791645050049</v>
       </c>
       <c r="H995" t="n">
         <v>21414</v>
@@ -29253,7 +29253,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G996" t="n">
-        <v>18.952615737915</v>
+        <v>18.9526138305664</v>
       </c>
       <c r="H996" t="n">
         <v>34614</v>
@@ -29282,7 +29282,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G997" t="n">
-        <v>19.1393375396729</v>
+        <v>19.1393394470215</v>
       </c>
       <c r="H997" t="n">
         <v>23859</v>
@@ -29340,7 +29340,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G999" t="n">
-        <v>20.8198680877686</v>
+        <v>20.8198699951172</v>
       </c>
       <c r="H999" t="n">
         <v>26674</v>
@@ -29514,7 +29514,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1005" t="n">
-        <v>19.9329223632812</v>
+        <v>19.9329242706299</v>
       </c>
       <c r="H1005" t="n">
         <v>21452</v>
@@ -29601,7 +29601,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G1008" t="n">
-        <v>21.0065956115723</v>
+        <v>21.0065937042236</v>
       </c>
       <c r="H1008" t="n">
         <v>36921</v>
@@ -29630,7 +29630,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G1009" t="n">
-        <v>21.5667705535889</v>
+        <v>21.5667724609375</v>
       </c>
       <c r="H1009" t="n">
         <v>42728</v>
@@ -29659,7 +29659,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1010" t="n">
-        <v>20.8198680877686</v>
+        <v>20.8198699951172</v>
       </c>
       <c r="H1010" t="n">
         <v>174076</v>
@@ -29688,7 +29688,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1011" t="n">
-        <v>20.8198680877686</v>
+        <v>20.8198699951172</v>
       </c>
       <c r="H1011" t="n">
         <v>37844</v>
@@ -29746,7 +29746,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G1013" t="n">
-        <v>20.0729656219482</v>
+        <v>20.0729675292969</v>
       </c>
       <c r="H1013" t="n">
         <v>29118</v>
@@ -29833,7 +29833,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1016" t="n">
-        <v>20.3997364044189</v>
+        <v>20.3997344970703</v>
       </c>
       <c r="H1016" t="n">
         <v>34914</v>
@@ -29891,7 +29891,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1018" t="n">
-        <v>18.8125762939453</v>
+        <v>18.812572479248</v>
       </c>
       <c r="H1018" t="n">
         <v>17176</v>
@@ -29920,7 +29920,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1019" t="n">
-        <v>18.2057151794434</v>
+        <v>18.2057132720947</v>
       </c>
       <c r="H1019" t="n">
         <v>43373</v>
@@ -29978,7 +29978,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G1021" t="n">
-        <v>17.7762470245361</v>
+        <v>17.7762451171875</v>
       </c>
       <c r="H1021" t="n">
         <v>16938</v>
@@ -30036,7 +30036,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.0853633880615</v>
+        <v>17.0853652954102</v>
       </c>
       <c r="H1023" t="n">
         <v>23884</v>
@@ -30123,7 +30123,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G1026" t="n">
-        <v>16.7935466766357</v>
+        <v>16.7935447692871</v>
       </c>
       <c r="H1026" t="n">
         <v>20196</v>
@@ -30326,7 +30326,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G1033" t="n">
-        <v>17.6972351074219</v>
+        <v>17.6972370147705</v>
       </c>
       <c r="H1033" t="n">
         <v>21958</v>
@@ -30442,7 +30442,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G1037" t="n">
-        <v>18.826847076416</v>
+        <v>18.8268489837646</v>
       </c>
       <c r="H1037" t="n">
         <v>15503</v>
@@ -30587,7 +30587,7 @@
         <v>18.3908023834229</v>
       </c>
       <c r="G1042" t="n">
-        <v>17.8290233612061</v>
+        <v>17.8290214538574</v>
       </c>
       <c r="H1042" t="n">
         <v>14439</v>
@@ -30674,7 +30674,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G1045" t="n">
-        <v>18.4691352844238</v>
+        <v>18.4691371917725</v>
       </c>
       <c r="H1045" t="n">
         <v>12329</v>
@@ -30703,7 +30703,7 @@
         <v>19.225866317749</v>
       </c>
       <c r="G1046" t="n">
-        <v>18.6385803222656</v>
+        <v>18.638578414917</v>
       </c>
       <c r="H1046" t="n">
         <v>13909</v>
@@ -30848,7 +30848,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1051" t="n">
-        <v>20.8036651611328</v>
+        <v>20.8036670684814</v>
       </c>
       <c r="H1051" t="n">
         <v>13490</v>
@@ -30935,7 +30935,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1054" t="n">
-        <v>20.8036651611328</v>
+        <v>20.8036670684814</v>
       </c>
       <c r="H1054" t="n">
         <v>30458</v>
@@ -30993,7 +30993,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1056" t="n">
-        <v>20.1447257995605</v>
+        <v>20.1447238922119</v>
       </c>
       <c r="H1056" t="n">
         <v>20364</v>
@@ -31051,7 +31051,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1058" t="n">
-        <v>22.5451488494873</v>
+        <v>22.5451507568359</v>
       </c>
       <c r="H1058" t="n">
         <v>114287</v>
@@ -31080,7 +31080,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1059" t="n">
-        <v>22.5451488494873</v>
+        <v>22.5451507568359</v>
       </c>
       <c r="H1059" t="n">
         <v>13110</v>
@@ -31138,7 +31138,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G1061" t="n">
-        <v>22.309814453125</v>
+        <v>22.3098125457764</v>
       </c>
       <c r="H1061" t="n">
         <v>27117</v>
@@ -31254,7 +31254,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G1065" t="n">
-        <v>21.321403503418</v>
+        <v>21.3214015960693</v>
       </c>
       <c r="H1065" t="n">
         <v>16460</v>
@@ -31283,7 +31283,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G1066" t="n">
-        <v>21.5096740722656</v>
+        <v>21.509672164917</v>
       </c>
       <c r="H1066" t="n">
         <v>8057</v>
@@ -31399,7 +31399,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1070" t="n">
-        <v>20.8036651611328</v>
+        <v>20.8036670684814</v>
       </c>
       <c r="H1070" t="n">
         <v>24078</v>
@@ -31428,7 +31428,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1071" t="n">
-        <v>20.6624622344971</v>
+        <v>20.6624641418457</v>
       </c>
       <c r="H1071" t="n">
         <v>5224</v>
@@ -31486,7 +31486,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1073" t="n">
-        <v>20.1447257995605</v>
+        <v>20.1447238922119</v>
       </c>
       <c r="H1073" t="n">
         <v>6725</v>
@@ -31515,7 +31515,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1074" t="n">
-        <v>20.1447257995605</v>
+        <v>20.1447238922119</v>
       </c>
       <c r="H1074" t="n">
         <v>6921</v>
@@ -31544,7 +31544,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1075" t="n">
-        <v>20.1447257995605</v>
+        <v>20.1447238922119</v>
       </c>
       <c r="H1075" t="n">
         <v>16126</v>
@@ -31718,7 +31718,7 @@
         <v>20.0512180328369</v>
       </c>
       <c r="G1081" t="n">
-        <v>19.438720703125</v>
+        <v>19.4387187957764</v>
       </c>
       <c r="H1081" t="n">
         <v>37815</v>
@@ -31747,7 +31747,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G1082" t="n">
-        <v>19.9093894958496</v>
+        <v>19.9093914031982</v>
       </c>
       <c r="H1082" t="n">
         <v>38523</v>
@@ -31863,7 +31863,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1086" t="n">
-        <v>18.9209785461426</v>
+        <v>18.9209804534912</v>
       </c>
       <c r="H1086" t="n">
         <v>15251</v>
@@ -32037,7 +32037,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G1092" t="n">
-        <v>18.2620410919189</v>
+        <v>18.2620391845703</v>
       </c>
       <c r="H1092" t="n">
         <v>39880</v>
@@ -32182,7 +32182,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G1097" t="n">
-        <v>18.0172901153564</v>
+        <v>18.0172920227051</v>
       </c>
       <c r="H1097" t="n">
         <v>18857</v>
@@ -32211,7 +32211,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1098" t="n">
-        <v>18.9680519104004</v>
+        <v>18.9680480957031</v>
       </c>
       <c r="H1098" t="n">
         <v>57714</v>
@@ -32269,7 +32269,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1100" t="n">
-        <v>18.9680519104004</v>
+        <v>18.9680480957031</v>
       </c>
       <c r="H1100" t="n">
         <v>38979</v>
@@ -32327,7 +32327,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G1102" t="n">
-        <v>18.0361213684082</v>
+        <v>18.0361194610596</v>
       </c>
       <c r="H1102" t="n">
         <v>10913</v>
@@ -32356,7 +32356,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G1103" t="n">
-        <v>18.1679096221924</v>
+        <v>18.1679077148438</v>
       </c>
       <c r="H1103" t="n">
         <v>14703</v>
@@ -32617,7 +32617,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1112" t="n">
-        <v>18.3561744689941</v>
+        <v>18.3561763763428</v>
       </c>
       <c r="H1112" t="n">
         <v>9961</v>
@@ -32646,7 +32646,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1113" t="n">
-        <v>18.9209785461426</v>
+        <v>18.9209804534912</v>
       </c>
       <c r="H1113" t="n">
         <v>34948</v>
@@ -32675,7 +32675,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1114" t="n">
-        <v>20.5212631225586</v>
+        <v>20.52126121521</v>
       </c>
       <c r="H1114" t="n">
         <v>25708</v>
@@ -32733,7 +32733,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1116" t="n">
-        <v>20.8036651611328</v>
+        <v>20.8036670684814</v>
       </c>
       <c r="H1116" t="n">
         <v>39044</v>
@@ -32762,7 +32762,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1117" t="n">
-        <v>20.8036651611328</v>
+        <v>20.8036670684814</v>
       </c>
       <c r="H1117" t="n">
         <v>9756</v>
@@ -32849,7 +32849,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1120" t="n">
-        <v>20.5212631225586</v>
+        <v>20.52126121521</v>
       </c>
       <c r="H1120" t="n">
         <v>13548</v>
@@ -33023,7 +33023,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1126" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1126" t="n">
         <v>38618</v>
@@ -33052,7 +33052,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1127" t="n">
-        <v>23.1570243835449</v>
+        <v>23.1570224761963</v>
       </c>
       <c r="H1127" t="n">
         <v>91749</v>
@@ -33081,7 +33081,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1128" t="n">
-        <v>24.0042304992676</v>
+        <v>24.0042324066162</v>
       </c>
       <c r="H1128" t="n">
         <v>31010</v>
@@ -33226,7 +33226,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1133" t="n">
-        <v>22.7804832458496</v>
+        <v>22.7804851531982</v>
       </c>
       <c r="H1133" t="n">
         <v>16253</v>
@@ -33313,7 +33313,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1136" t="n">
-        <v>23.1570243835449</v>
+        <v>23.1570224761963</v>
       </c>
       <c r="H1136" t="n">
         <v>28758</v>
@@ -33342,7 +33342,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1137" t="n">
-        <v>22.7804832458496</v>
+        <v>22.7804851531982</v>
       </c>
       <c r="H1137" t="n">
         <v>26211</v>
@@ -33371,7 +33371,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1138" t="n">
-        <v>22.5451488494873</v>
+        <v>22.5451507568359</v>
       </c>
       <c r="H1138" t="n">
         <v>20349</v>
@@ -33429,7 +33429,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1140" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1140" t="n">
         <v>41434</v>
@@ -33516,7 +33516,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1143" t="n">
-        <v>22.8746185302734</v>
+        <v>22.8746204376221</v>
       </c>
       <c r="H1143" t="n">
         <v>19066</v>
@@ -33603,7 +33603,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1146" t="n">
-        <v>22.686351776123</v>
+        <v>22.6863498687744</v>
       </c>
       <c r="H1146" t="n">
         <v>172883</v>
@@ -33661,7 +33661,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1148" t="n">
-        <v>23.2982234954834</v>
+        <v>23.2982215881348</v>
       </c>
       <c r="H1148" t="n">
         <v>45019</v>
@@ -33719,7 +33719,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1150" t="n">
-        <v>24.0042304992676</v>
+        <v>24.0042324066162</v>
       </c>
       <c r="H1150" t="n">
         <v>22170</v>
@@ -33748,7 +33748,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1151" t="n">
-        <v>23.2982234954834</v>
+        <v>23.2982215881348</v>
       </c>
       <c r="H1151" t="n">
         <v>28673</v>
@@ -33835,7 +33835,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G1154" t="n">
-        <v>21.8391418457031</v>
+        <v>21.8391437530518</v>
       </c>
       <c r="H1154" t="n">
         <v>31463</v>
@@ -33864,7 +33864,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1155" t="n">
-        <v>22.686351776123</v>
+        <v>22.6863498687744</v>
       </c>
       <c r="H1155" t="n">
         <v>14975</v>
@@ -33922,7 +33922,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1157" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1157" t="n">
         <v>6702</v>
@@ -33951,7 +33951,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1158" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1158" t="n">
         <v>11254</v>
@@ -34009,7 +34009,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1160" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1160" t="n">
         <v>4782</v>
@@ -34154,7 +34154,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G1165" t="n">
-        <v>21.4626045227051</v>
+        <v>21.4626064300537</v>
       </c>
       <c r="H1165" t="n">
         <v>13718</v>
@@ -34357,7 +34357,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G1172" t="n">
-        <v>21.7920761108398</v>
+        <v>21.7920780181885</v>
       </c>
       <c r="H1172" t="n">
         <v>51171</v>
@@ -34502,7 +34502,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1177" t="n">
-        <v>22.7804832458496</v>
+        <v>22.7804851531982</v>
       </c>
       <c r="H1177" t="n">
         <v>35798</v>
@@ -34531,7 +34531,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1178" t="n">
-        <v>22.8746185302734</v>
+        <v>22.8746204376221</v>
       </c>
       <c r="H1178" t="n">
         <v>20291</v>
@@ -34560,7 +34560,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1179" t="n">
-        <v>22.5451488494873</v>
+        <v>22.5451507568359</v>
       </c>
       <c r="H1179" t="n">
         <v>10229</v>
@@ -34589,7 +34589,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1180" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1180" t="n">
         <v>9877</v>
@@ -34647,7 +34647,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G1182" t="n">
-        <v>21.7920761108398</v>
+        <v>21.7920780181885</v>
       </c>
       <c r="H1182" t="n">
         <v>17354</v>
@@ -34676,7 +34676,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G1183" t="n">
-        <v>21.3684711456299</v>
+        <v>21.3684730529785</v>
       </c>
       <c r="H1183" t="n">
         <v>24503</v>
@@ -34705,7 +34705,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1184" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1184" t="n">
         <v>21995</v>
@@ -34792,7 +34792,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G1187" t="n">
-        <v>24.5219669342041</v>
+        <v>24.5219688415527</v>
       </c>
       <c r="H1187" t="n">
         <v>20612</v>
@@ -34821,7 +34821,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G1188" t="n">
-        <v>23.8159599304199</v>
+        <v>23.8159618377686</v>
       </c>
       <c r="H1188" t="n">
         <v>26776</v>
@@ -34966,7 +34966,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.7573051452637</v>
+        <v>24.7573070526123</v>
       </c>
       <c r="H1193" t="n">
         <v>10170</v>
@@ -34995,7 +34995,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1194" t="n">
-        <v>24.6631698608398</v>
+        <v>24.6631679534912</v>
       </c>
       <c r="H1194" t="n">
         <v>10597</v>
@@ -35053,7 +35053,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1196" t="n">
-        <v>24.2395668029785</v>
+        <v>24.2395648956299</v>
       </c>
       <c r="H1196" t="n">
         <v>7570</v>
@@ -35082,7 +35082,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1197" t="n">
-        <v>24.0042304992676</v>
+        <v>24.0042324066162</v>
       </c>
       <c r="H1197" t="n">
         <v>14597</v>
@@ -35111,7 +35111,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1198" t="n">
-        <v>24.4278335571289</v>
+        <v>24.4278354644775</v>
       </c>
       <c r="H1198" t="n">
         <v>14289</v>
@@ -35140,7 +35140,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1199" t="n">
-        <v>24.3337001800537</v>
+        <v>24.3336982727051</v>
       </c>
       <c r="H1199" t="n">
         <v>31535</v>
@@ -35169,7 +35169,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1200" t="n">
-        <v>24.8514366149902</v>
+        <v>24.8514385223389</v>
       </c>
       <c r="H1200" t="n">
         <v>15649</v>
@@ -35198,7 +35198,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1201" t="n">
-        <v>25.5574436187744</v>
+        <v>25.557445526123</v>
       </c>
       <c r="H1201" t="n">
         <v>47925</v>
@@ -35256,7 +35256,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1203" t="n">
-        <v>24.8514366149902</v>
+        <v>24.8514385223389</v>
       </c>
       <c r="H1203" t="n">
         <v>47889</v>
@@ -35285,7 +35285,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1204" t="n">
-        <v>24.3337001800537</v>
+        <v>24.3336982727051</v>
       </c>
       <c r="H1204" t="n">
         <v>35811</v>
@@ -35343,7 +35343,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1206" t="n">
-        <v>24.8514366149902</v>
+        <v>24.8514385223389</v>
       </c>
       <c r="H1206" t="n">
         <v>51167</v>
@@ -35401,7 +35401,7 @@
         <v>26.1685390472412</v>
       </c>
       <c r="G1208" t="n">
-        <v>25.369176864624</v>
+        <v>25.3691749572754</v>
       </c>
       <c r="H1208" t="n">
         <v>93294</v>
@@ -35459,7 +35459,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G1210" t="n">
-        <v>25.1809062957764</v>
+        <v>25.180908203125</v>
       </c>
       <c r="H1210" t="n">
         <v>75039</v>
@@ -35517,7 +35517,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G1212" t="n">
-        <v>23.4394226074219</v>
+        <v>23.4394245147705</v>
       </c>
       <c r="H1212" t="n">
         <v>48719</v>
@@ -35633,7 +35633,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1216" t="n">
-        <v>22.7804832458496</v>
+        <v>22.7804851531982</v>
       </c>
       <c r="H1216" t="n">
         <v>48261</v>
@@ -35749,7 +35749,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1220" t="n">
-        <v>23.0628890991211</v>
+        <v>23.0628871917725</v>
       </c>
       <c r="H1220" t="n">
         <v>51035</v>
@@ -35865,7 +35865,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G1224" t="n">
-        <v>23.4864940643311</v>
+        <v>23.4864921569824</v>
       </c>
       <c r="H1224" t="n">
         <v>14439</v>
@@ -35952,7 +35952,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1227" t="n">
-        <v>24.2395668029785</v>
+        <v>24.2395648956299</v>
       </c>
       <c r="H1227" t="n">
         <v>14100</v>
@@ -36039,7 +36039,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1230" t="n">
-        <v>23.2982234954834</v>
+        <v>23.2982215881348</v>
       </c>
       <c r="H1230" t="n">
         <v>12741</v>
@@ -36068,7 +36068,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1231" t="n">
-        <v>23.0628890991211</v>
+        <v>23.0628871917725</v>
       </c>
       <c r="H1231" t="n">
         <v>14915</v>
@@ -36097,7 +36097,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1232" t="n">
-        <v>22.8746185302734</v>
+        <v>22.8746204376221</v>
       </c>
       <c r="H1232" t="n">
         <v>16581</v>
@@ -36184,7 +36184,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1235" t="n">
-        <v>23.0628890991211</v>
+        <v>23.0628871917725</v>
       </c>
       <c r="H1235" t="n">
         <v>42713</v>
@@ -36242,7 +36242,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1237" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1237" t="n">
         <v>15807</v>
@@ -36271,7 +36271,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1238" t="n">
-        <v>22.686351776123</v>
+        <v>22.6863498687744</v>
       </c>
       <c r="H1238" t="n">
         <v>47167</v>
@@ -36300,7 +36300,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G1239" t="n">
-        <v>22.309814453125</v>
+        <v>22.3098125457764</v>
       </c>
       <c r="H1239" t="n">
         <v>22787</v>
@@ -36358,7 +36358,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G1241" t="n">
-        <v>21.321403503418</v>
+        <v>21.3214015960693</v>
       </c>
       <c r="H1241" t="n">
         <v>24454</v>
@@ -36387,7 +36387,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G1242" t="n">
-        <v>21.1802043914795</v>
+        <v>21.1802024841309</v>
       </c>
       <c r="H1242" t="n">
         <v>13607</v>
@@ -36648,7 +36648,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G1251" t="n">
-        <v>23.4864940643311</v>
+        <v>23.4864921569824</v>
       </c>
       <c r="H1251" t="n">
         <v>65266</v>
@@ -36764,7 +36764,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1255" t="n">
-        <v>22.8746185302734</v>
+        <v>22.8746204376221</v>
       </c>
       <c r="H1255" t="n">
         <v>9052</v>
@@ -36851,7 +36851,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1258" t="n">
-        <v>23.0628890991211</v>
+        <v>23.0628871917725</v>
       </c>
       <c r="H1258" t="n">
         <v>22629</v>
@@ -36880,7 +36880,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1259" t="n">
-        <v>22.7804832458496</v>
+        <v>22.7804851531982</v>
       </c>
       <c r="H1259" t="n">
         <v>53304</v>
@@ -36909,7 +36909,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1260" t="n">
-        <v>23.1570243835449</v>
+        <v>23.1570224761963</v>
       </c>
       <c r="H1260" t="n">
         <v>25058</v>
@@ -36967,7 +36967,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1262" t="n">
-        <v>22.686351776123</v>
+        <v>22.6863498687744</v>
       </c>
       <c r="H1262" t="n">
         <v>8522</v>
@@ -37054,7 +37054,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1265" t="n">
-        <v>23.2982234954834</v>
+        <v>23.2982215881348</v>
       </c>
       <c r="H1265" t="n">
         <v>20866</v>
@@ -37083,7 +37083,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1266" t="n">
-        <v>24.4278335571289</v>
+        <v>24.4278354644775</v>
       </c>
       <c r="H1266" t="n">
         <v>88068</v>
@@ -37199,7 +37199,7 @@
         <v>27.0424423217773</v>
       </c>
       <c r="G1270" t="n">
-        <v>26.2163848876953</v>
+        <v>26.2163829803467</v>
       </c>
       <c r="H1270" t="n">
         <v>53560</v>
@@ -37315,7 +37315,7 @@
         <v>27.0424423217773</v>
       </c>
       <c r="G1274" t="n">
-        <v>26.2163848876953</v>
+        <v>26.2163829803467</v>
       </c>
       <c r="H1274" t="n">
         <v>51070</v>
@@ -37576,7 +37576,7 @@
         <v>26.3141899108887</v>
       </c>
       <c r="G1283" t="n">
-        <v>25.6745471954346</v>
+        <v>25.6745491027832</v>
       </c>
       <c r="H1283" t="n">
         <v>4950</v>
@@ -37605,7 +37605,7 @@
         <v>26.071439743042</v>
       </c>
       <c r="G1284" t="n">
-        <v>25.4377002716064</v>
+        <v>25.4376983642578</v>
       </c>
       <c r="H1284" t="n">
         <v>30025</v>
@@ -37663,7 +37663,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1286" t="n">
-        <v>25.7219200134277</v>
+        <v>25.7219181060791</v>
       </c>
       <c r="H1286" t="n">
         <v>19782</v>
@@ -37750,7 +37750,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G1289" t="n">
-        <v>25.342960357666</v>
+        <v>25.3429584503174</v>
       </c>
       <c r="H1289" t="n">
         <v>23089</v>
@@ -37779,7 +37779,7 @@
         <v>26.6054916381836</v>
       </c>
       <c r="G1290" t="n">
-        <v>25.9587707519531</v>
+        <v>25.9587688446045</v>
       </c>
       <c r="H1290" t="n">
         <v>20344</v>
@@ -37808,7 +37808,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1291" t="n">
-        <v>25.7219200134277</v>
+        <v>25.7219181060791</v>
       </c>
       <c r="H1291" t="n">
         <v>17122</v>
@@ -37953,7 +37953,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G1296" t="n">
-        <v>24.9640007019043</v>
+        <v>24.9639987945557</v>
       </c>
       <c r="H1296" t="n">
         <v>41623</v>
@@ -38098,7 +38098,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1301" t="n">
-        <v>25.0113677978516</v>
+        <v>25.0113697052002</v>
       </c>
       <c r="H1301" t="n">
         <v>13511</v>
@@ -38156,7 +38156,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G1303" t="n">
-        <v>24.2060775756836</v>
+        <v>24.2060794830322</v>
       </c>
       <c r="H1303" t="n">
         <v>13414</v>
@@ -38214,7 +38214,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1305" t="n">
-        <v>23.779748916626</v>
+        <v>23.7797470092773</v>
       </c>
       <c r="H1305" t="n">
         <v>297008</v>
@@ -38243,7 +38243,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G1306" t="n">
-        <v>24.2060775756836</v>
+        <v>24.2060794830322</v>
       </c>
       <c r="H1306" t="n">
         <v>105419</v>
@@ -38330,7 +38330,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G1309" t="n">
-        <v>24.6797771453857</v>
+        <v>24.6797790527344</v>
       </c>
       <c r="H1309" t="n">
         <v>19879</v>
@@ -38475,7 +38475,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1314" t="n">
-        <v>23.779748916626</v>
+        <v>23.7797470092773</v>
       </c>
       <c r="H1314" t="n">
         <v>19054</v>
@@ -38533,7 +38533,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1316" t="n">
-        <v>23.779748916626</v>
+        <v>23.7797470092773</v>
       </c>
       <c r="H1316" t="n">
         <v>27645</v>
@@ -38562,7 +38562,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1317" t="n">
-        <v>24.0639705657959</v>
+        <v>24.0639686584473</v>
       </c>
       <c r="H1317" t="n">
         <v>18064</v>
@@ -38649,7 +38649,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G1320" t="n">
-        <v>24.2060775756836</v>
+        <v>24.2060794830322</v>
       </c>
       <c r="H1320" t="n">
         <v>28124</v>
@@ -38678,7 +38678,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1321" t="n">
-        <v>24.1587104797363</v>
+        <v>24.1587085723877</v>
       </c>
       <c r="H1321" t="n">
         <v>52546</v>
@@ -38736,7 +38736,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G1323" t="n">
-        <v>23.9218597412109</v>
+        <v>23.9218578338623</v>
       </c>
       <c r="H1323" t="n">
         <v>29989</v>
@@ -38794,7 +38794,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1325" t="n">
-        <v>23.779748916626</v>
+        <v>23.7797470092773</v>
       </c>
       <c r="H1325" t="n">
         <v>49423</v>
@@ -38852,7 +38852,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1327" t="n">
-        <v>23.874490737915</v>
+        <v>23.8744888305664</v>
       </c>
       <c r="H1327" t="n">
         <v>7352</v>
@@ -39084,7 +39084,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G1335" t="n">
-        <v>24.9640007019043</v>
+        <v>24.9639987945557</v>
       </c>
       <c r="H1335" t="n">
         <v>64616</v>
@@ -39113,7 +39113,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1336" t="n">
-        <v>23.874490737915</v>
+        <v>23.8744888305664</v>
       </c>
       <c r="H1336" t="n">
         <v>40184</v>
@@ -39142,7 +39142,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1337" t="n">
-        <v>23.4955272674561</v>
+        <v>23.4955291748047</v>
       </c>
       <c r="H1337" t="n">
         <v>19801</v>
@@ -39171,7 +39171,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1338" t="n">
-        <v>23.3060474395752</v>
+        <v>23.3060493469238</v>
       </c>
       <c r="H1338" t="n">
         <v>32985</v>
@@ -39200,7 +39200,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1339" t="n">
-        <v>23.0691986083984</v>
+        <v>23.0691967010498</v>
       </c>
       <c r="H1339" t="n">
         <v>24983</v>
@@ -39229,7 +39229,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1340" t="n">
-        <v>23.0691986083984</v>
+        <v>23.0691967010498</v>
       </c>
       <c r="H1340" t="n">
         <v>26222</v>
@@ -39258,7 +39258,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1341" t="n">
-        <v>23.0691986083984</v>
+        <v>23.0691967010498</v>
       </c>
       <c r="H1341" t="n">
         <v>11790</v>
@@ -39316,7 +39316,7 @@
         <v>23.3040790557861</v>
       </c>
       <c r="G1343" t="n">
-        <v>22.7376079559326</v>
+        <v>22.737606048584</v>
       </c>
       <c r="H1343" t="n">
         <v>17057</v>
@@ -39519,7 +39519,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1350" t="n">
-        <v>21.1743984222412</v>
+        <v>21.1743965148926</v>
       </c>
       <c r="H1350" t="n">
         <v>34561</v>
@@ -39548,7 +39548,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1351" t="n">
-        <v>21.1743984222412</v>
+        <v>21.1743965148926</v>
       </c>
       <c r="H1351" t="n">
         <v>18138</v>
@@ -39838,7 +39838,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1361" t="n">
-        <v>21.1743984222412</v>
+        <v>21.1743965148926</v>
       </c>
       <c r="H1361" t="n">
         <v>15624</v>
@@ -39954,7 +39954,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G1365" t="n">
-        <v>18.8153705596924</v>
+        <v>18.815372467041</v>
       </c>
       <c r="H1365" t="n">
         <v>116416</v>
@@ -39983,7 +39983,7 @@
         <v>19.759916305542</v>
       </c>
       <c r="G1366" t="n">
-        <v>19.2795963287354</v>
+        <v>19.279598236084</v>
       </c>
       <c r="H1366" t="n">
         <v>65681</v>
@@ -40012,7 +40012,7 @@
         <v>18.9734058380127</v>
       </c>
       <c r="G1367" t="n">
-        <v>18.5122051239014</v>
+        <v>18.5122032165527</v>
       </c>
       <c r="H1367" t="n">
         <v>34261</v>
@@ -40041,7 +40041,7 @@
         <v>18.8763046264648</v>
       </c>
       <c r="G1368" t="n">
-        <v>18.4174633026123</v>
+        <v>18.4174613952637</v>
       </c>
       <c r="H1368" t="n">
         <v>26162</v>
@@ -40070,7 +40070,7 @@
         <v>18.8568840026855</v>
       </c>
       <c r="G1369" t="n">
-        <v>18.3985137939453</v>
+        <v>18.3985157012939</v>
       </c>
       <c r="H1369" t="n">
         <v>19594</v>
@@ -40157,7 +40157,7 @@
         <v>18.0218200683594</v>
       </c>
       <c r="G1372" t="n">
-        <v>17.5837478637695</v>
+        <v>17.5837497711182</v>
       </c>
       <c r="H1372" t="n">
         <v>14059</v>
@@ -40273,7 +40273,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G1376" t="n">
-        <v>19.800666809082</v>
+        <v>19.8006649017334</v>
       </c>
       <c r="H1376" t="n">
         <v>91478</v>
@@ -40331,7 +40331,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1378" t="n">
-        <v>19.7059288024902</v>
+        <v>19.7059268951416</v>
       </c>
       <c r="H1378" t="n">
         <v>35540</v>
@@ -40708,7 +40708,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1391" t="n">
-        <v>19.6601982116699</v>
+        <v>19.6601963043213</v>
       </c>
       <c r="H1391" t="n">
         <v>113261</v>
@@ -40853,7 +40853,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1396" t="n">
-        <v>22.7336273193359</v>
+        <v>22.7336254119873</v>
       </c>
       <c r="H1396" t="n">
         <v>118906</v>
@@ -40998,7 +40998,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1401" t="n">
-        <v>22.0018577575684</v>
+        <v>22.001859664917</v>
       </c>
       <c r="H1401" t="n">
         <v>65659</v>
@@ -41143,7 +41143,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1406" t="n">
-        <v>23.0751209259033</v>
+        <v>23.0751190185547</v>
       </c>
       <c r="H1406" t="n">
         <v>96786</v>
@@ -41172,7 +41172,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1407" t="n">
-        <v>23.8556747436523</v>
+        <v>23.8556728363037</v>
       </c>
       <c r="H1407" t="n">
         <v>98631</v>
@@ -41201,7 +41201,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1408" t="n">
-        <v>23.0751209259033</v>
+        <v>23.0751190185547</v>
       </c>
       <c r="H1408" t="n">
         <v>52454</v>
@@ -41230,7 +41230,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1409" t="n">
-        <v>23.3678283691406</v>
+        <v>23.3678302764893</v>
       </c>
       <c r="H1409" t="n">
         <v>55523</v>
@@ -41259,7 +41259,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1410" t="n">
-        <v>24.2459526062012</v>
+        <v>24.2459506988525</v>
       </c>
       <c r="H1410" t="n">
         <v>44095</v>
@@ -41346,7 +41346,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G1413" t="n">
-        <v>24.5386562347412</v>
+        <v>24.5386581420898</v>
       </c>
       <c r="H1413" t="n">
         <v>60428</v>
@@ -41433,7 +41433,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1416" t="n">
-        <v>23.3678283691406</v>
+        <v>23.3678302764893</v>
       </c>
       <c r="H1416" t="n">
         <v>48294</v>
@@ -41462,7 +41462,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1417" t="n">
-        <v>22.7336273193359</v>
+        <v>22.7336254119873</v>
       </c>
       <c r="H1417" t="n">
         <v>78463</v>
@@ -41491,7 +41491,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1418" t="n">
-        <v>22.7336273193359</v>
+        <v>22.7336254119873</v>
       </c>
       <c r="H1418" t="n">
         <v>37481</v>
@@ -41549,7 +41549,7 @@
         <v>23.25</v>
       </c>
       <c r="G1420" t="n">
-        <v>22.6848411560059</v>
+        <v>22.6848430633545</v>
       </c>
       <c r="H1420" t="n">
         <v>32386</v>
@@ -41607,7 +41607,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1422" t="n">
-        <v>22.3921375274658</v>
+        <v>22.3921356201172</v>
       </c>
       <c r="H1422" t="n">
         <v>18812</v>
@@ -41636,7 +41636,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>22.0506420135498</v>
+        <v>22.0506458282471</v>
       </c>
       <c r="H1423" t="n">
         <v>55220</v>
@@ -41694,7 +41694,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1425" t="n">
-        <v>22.3433513641357</v>
+        <v>22.3433494567871</v>
       </c>
       <c r="H1425" t="n">
         <v>23340</v>
@@ -41897,7 +41897,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1432" t="n">
-        <v>22.14821434021</v>
+        <v>22.1482124328613</v>
       </c>
       <c r="H1432" t="n">
         <v>49306</v>
@@ -41926,7 +41926,7 @@
         <v>22.25</v>
       </c>
       <c r="G1433" t="n">
-        <v>21.7091503143311</v>
+        <v>21.7091522216797</v>
       </c>
       <c r="H1433" t="n">
         <v>48514</v>
@@ -41955,7 +41955,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1434" t="n">
-        <v>22.0994281768799</v>
+        <v>22.0994262695312</v>
       </c>
       <c r="H1434" t="n">
         <v>38190</v>
@@ -42100,7 +42100,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1439" t="n">
-        <v>21.8067207336426</v>
+        <v>21.8067226409912</v>
       </c>
       <c r="H1439" t="n">
         <v>36944</v>
@@ -42129,7 +42129,7 @@
         <v>22.25</v>
       </c>
       <c r="G1440" t="n">
-        <v>21.7091503143311</v>
+        <v>21.7091522216797</v>
       </c>
       <c r="H1440" t="n">
         <v>34966</v>
@@ -42187,7 +42187,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1442" t="n">
-        <v>22.3433513641357</v>
+        <v>22.3433494567871</v>
       </c>
       <c r="H1442" t="n">
         <v>67943</v>
@@ -42216,7 +42216,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1443" t="n">
-        <v>22.0994281768799</v>
+        <v>22.0994262695312</v>
       </c>
       <c r="H1443" t="n">
         <v>31822</v>
@@ -42303,7 +42303,7 @@
         <v>22.25</v>
       </c>
       <c r="G1446" t="n">
-        <v>21.7091503143311</v>
+        <v>21.7091522216797</v>
       </c>
       <c r="H1446" t="n">
         <v>34680</v>
@@ -42738,7 +42738,7 @@
         <v>21.5</v>
       </c>
       <c r="G1461" t="n">
-        <v>20.9773826599121</v>
+        <v>20.9773807525635</v>
       </c>
       <c r="H1461" t="n">
         <v>42275</v>
@@ -42767,7 +42767,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1462" t="n">
-        <v>21.2700881958008</v>
+        <v>21.2700901031494</v>
       </c>
       <c r="H1462" t="n">
         <v>52249</v>
@@ -42796,7 +42796,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>19.6114139556885</v>
+        <v>19.6114120483398</v>
       </c>
       <c r="H1463" t="n">
         <v>301159</v>
@@ -42825,7 +42825,7 @@
         <v>20</v>
       </c>
       <c r="G1464" t="n">
-        <v>19.513843536377</v>
+        <v>19.5138416290283</v>
       </c>
       <c r="H1464" t="n">
         <v>140532</v>
@@ -42941,7 +42941,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>18.8308582305908</v>
+        <v>18.8308601379395</v>
       </c>
       <c r="H1468" t="n">
         <v>119630</v>
@@ -43028,7 +43028,7 @@
         <v>19.5</v>
       </c>
       <c r="G1471" t="n">
-        <v>19.0259990692139</v>
+        <v>19.0259971618652</v>
       </c>
       <c r="H1471" t="n">
         <v>45259</v>
@@ -43057,7 +43057,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1472" t="n">
-        <v>18.9869689941406</v>
+        <v>18.9869709014893</v>
       </c>
       <c r="H1472" t="n">
         <v>57045</v>
@@ -43086,7 +43086,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1473" t="n">
-        <v>19.6601982116699</v>
+        <v>19.6601963043213</v>
       </c>
       <c r="H1473" t="n">
         <v>74930</v>
@@ -43202,7 +43202,7 @@
         <v>21</v>
       </c>
       <c r="G1477" t="n">
-        <v>20.4895362854004</v>
+        <v>20.489538192749</v>
       </c>
       <c r="H1477" t="n">
         <v>53759</v>
@@ -43347,7 +43347,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1482" t="n">
-        <v>19.4553031921387</v>
+        <v>19.45530128479</v>
       </c>
       <c r="H1482" t="n">
         <v>37455</v>
@@ -43492,7 +43492,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1487" t="n">
-        <v>18.8308582305908</v>
+        <v>18.8308601379395</v>
       </c>
       <c r="H1487" t="n">
         <v>43098</v>
@@ -43579,7 +43579,7 @@
         <v>18.5</v>
       </c>
       <c r="G1490" t="n">
-        <v>18.0503044128418</v>
+        <v>18.0503063201904</v>
       </c>
       <c r="H1490" t="n">
         <v>82372</v>
@@ -43608,7 +43608,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1491" t="n">
-        <v>18.1088447570801</v>
+        <v>18.1088466644287</v>
       </c>
       <c r="H1491" t="n">
         <v>98046</v>
@@ -43637,7 +43637,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1492" t="n">
-        <v>17.9722480773926</v>
+        <v>17.9722499847412</v>
       </c>
       <c r="H1492" t="n">
         <v>99632</v>
@@ -43666,7 +43666,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1493" t="n">
-        <v>17.4844017028809</v>
+        <v>17.4844036102295</v>
       </c>
       <c r="H1493" t="n">
         <v>61819</v>
@@ -43695,7 +43695,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1494" t="n">
-        <v>18.1088447570801</v>
+        <v>18.1088466644287</v>
       </c>
       <c r="H1494" t="n">
         <v>122278</v>
@@ -43724,7 +43724,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.0307922363281</v>
+        <v>18.0307903289795</v>
       </c>
       <c r="H1495" t="n">
         <v>59859</v>
@@ -43869,7 +43869,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1500" t="n">
-        <v>18.5186367034912</v>
+        <v>18.5186386108398</v>
       </c>
       <c r="H1500" t="n">
         <v>69648</v>
@@ -43898,7 +43898,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1501" t="n">
-        <v>18.3820400238037</v>
+        <v>18.3820419311523</v>
       </c>
       <c r="H1501" t="n">
         <v>36525</v>
@@ -43956,7 +43956,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1503" t="n">
-        <v>18.7528018951416</v>
+        <v>18.7528038024902</v>
       </c>
       <c r="H1503" t="n">
         <v>48675</v>
@@ -44043,7 +44043,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1506" t="n">
-        <v>18.1673908233643</v>
+        <v>18.1673889160156</v>
       </c>
       <c r="H1506" t="n">
         <v>142776</v>
@@ -44072,7 +44072,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1507" t="n">
-        <v>18.1283588409424</v>
+        <v>18.128360748291</v>
       </c>
       <c r="H1507" t="n">
         <v>63388</v>
@@ -44101,7 +44101,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1508" t="n">
-        <v>16.6453094482422</v>
+        <v>16.6453075408936</v>
       </c>
       <c r="H1508" t="n">
         <v>280958</v>
@@ -44246,7 +44246,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1513" t="n">
-        <v>17.4063491821289</v>
+        <v>17.4063510894775</v>
       </c>
       <c r="H1513" t="n">
         <v>54000</v>
@@ -44304,7 +44304,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1515" t="n">
-        <v>17.2112083435059</v>
+        <v>17.2112102508545</v>
       </c>
       <c r="H1515" t="n">
         <v>56490</v>
@@ -44391,7 +44391,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1518" t="n">
-        <v>17.5234317779541</v>
+        <v>17.5234298706055</v>
       </c>
       <c r="H1518" t="n">
         <v>61417</v>
@@ -44507,7 +44507,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1522" t="n">
-        <v>17.347806930542</v>
+        <v>17.3478088378906</v>
       </c>
       <c r="H1522" t="n">
         <v>58345</v>
@@ -44536,7 +44536,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1523" t="n">
-        <v>16.9965572357178</v>
+        <v>16.9965591430664</v>
       </c>
       <c r="H1523" t="n">
         <v>137407</v>
@@ -44826,7 +44826,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1533" t="n">
-        <v>16.8209323883057</v>
+        <v>16.8209342956543</v>
       </c>
       <c r="H1533" t="n">
         <v>22910</v>
@@ -44855,7 +44855,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1534" t="n">
-        <v>16.5087127685547</v>
+        <v>16.5087108612061</v>
       </c>
       <c r="H1534" t="n">
         <v>104928</v>
@@ -44913,7 +44913,7 @@
         <v>17.5</v>
       </c>
       <c r="G1536" t="n">
-        <v>17.0746116638184</v>
+        <v>17.074613571167</v>
       </c>
       <c r="H1536" t="n">
         <v>68998</v>
@@ -45087,7 +45087,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1542" t="n">
-        <v>16.8280143737793</v>
+        <v>16.8280124664307</v>
       </c>
       <c r="H1542" t="n">
         <v>51202</v>
@@ -45116,7 +45116,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>16.5715484619141</v>
+        <v>16.5715465545654</v>
       </c>
       <c r="H1543" t="n">
         <v>78476</v>
@@ -45203,7 +45203,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1546" t="n">
-        <v>17.3803977966309</v>
+        <v>17.3803997039795</v>
       </c>
       <c r="H1546" t="n">
         <v>57453</v>
@@ -45232,7 +45232,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1547" t="n">
-        <v>17.4987678527832</v>
+        <v>17.4987659454346</v>
       </c>
       <c r="H1547" t="n">
         <v>68099</v>
@@ -45406,7 +45406,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1553" t="n">
-        <v>17.0844764709473</v>
+        <v>17.0844783782959</v>
       </c>
       <c r="H1553" t="n">
         <v>48296</v>
@@ -45435,7 +45435,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1554" t="n">
-        <v>17.5974063873291</v>
+        <v>17.5974082946777</v>
       </c>
       <c r="H1554" t="n">
         <v>62204</v>
@@ -45522,7 +45522,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1557" t="n">
-        <v>17.3212127685547</v>
+        <v>17.3212146759033</v>
       </c>
       <c r="H1557" t="n">
         <v>138777</v>
@@ -45667,7 +45667,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1562" t="n">
-        <v>16.5715484619141</v>
+        <v>16.5715465545654</v>
       </c>
       <c r="H1562" t="n">
         <v>20856</v>
@@ -45696,7 +45696,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1563" t="n">
-        <v>16.6307315826416</v>
+        <v>16.6307334899902</v>
       </c>
       <c r="H1563" t="n">
         <v>40403</v>
@@ -45725,7 +45725,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1564" t="n">
-        <v>16.8280143737793</v>
+        <v>16.8280124664307</v>
       </c>
       <c r="H1564" t="n">
         <v>67466</v>
@@ -45812,7 +45812,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1567" t="n">
-        <v>15.5654182434082</v>
+        <v>15.5654191970825</v>
       </c>
       <c r="H1567" t="n">
         <v>155412</v>
@@ -45841,7 +45841,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="n">
-        <v>15.6837863922119</v>
+        <v>15.6837873458862</v>
       </c>
       <c r="H1568" t="n">
         <v>56230</v>
@@ -45899,7 +45899,7 @@
         <v>16.5</v>
       </c>
       <c r="G1570" t="n">
-        <v>16.2756290435791</v>
+        <v>16.2756271362305</v>
       </c>
       <c r="H1570" t="n">
         <v>50805</v>
@@ -45928,7 +45928,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1571" t="n">
-        <v>16.2361717224121</v>
+        <v>16.2361698150635</v>
       </c>
       <c r="H1571" t="n">
         <v>18817</v>
@@ -45957,7 +45957,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1572" t="n">
-        <v>15.9205236434937</v>
+        <v>15.920521736145</v>
       </c>
       <c r="H1572" t="n">
         <v>21247</v>
@@ -45986,7 +45986,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1573" t="n">
-        <v>16.0191631317139</v>
+        <v>16.0191650390625</v>
       </c>
       <c r="H1573" t="n">
         <v>28898</v>
@@ -46015,7 +46015,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>16.3742694854736</v>
+        <v>16.374267578125</v>
       </c>
       <c r="H1574" t="n">
         <v>21475</v>
@@ -46044,7 +46044,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1575" t="n">
-        <v>16.867467880249</v>
+        <v>16.8674697875977</v>
       </c>
       <c r="H1575" t="n">
         <v>59935</v>
@@ -46131,7 +46131,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1578" t="n">
-        <v>17.4593105316162</v>
+        <v>17.4593124389648</v>
       </c>
       <c r="H1578" t="n">
         <v>37638</v>
@@ -46160,7 +46160,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1579" t="n">
-        <v>17.1042041778564</v>
+        <v>17.1042060852051</v>
       </c>
       <c r="H1579" t="n">
         <v>71825</v>
@@ -46276,7 +46276,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1583" t="n">
-        <v>17.5579490661621</v>
+        <v>17.5579509735107</v>
       </c>
       <c r="H1583" t="n">
         <v>20852</v>
@@ -46421,7 +46421,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1588" t="n">
-        <v>16.867467880249</v>
+        <v>16.8674697875977</v>
       </c>
       <c r="H1588" t="n">
         <v>71033</v>
@@ -46479,7 +46479,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1590" t="n">
-        <v>16.7491016387939</v>
+        <v>16.7490997314453</v>
       </c>
       <c r="H1590" t="n">
         <v>35436</v>
@@ -46595,7 +46595,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1594" t="n">
-        <v>16.9858379364014</v>
+        <v>16.9858360290527</v>
       </c>
       <c r="H1594" t="n">
         <v>12728</v>
@@ -46624,7 +46624,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1595" t="n">
-        <v>17.5579490661621</v>
+        <v>17.5579509735107</v>
       </c>
       <c r="H1595" t="n">
         <v>46948</v>
@@ -46653,7 +46653,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1596" t="n">
-        <v>17.8144149780273</v>
+        <v>17.8144130706787</v>
       </c>
       <c r="H1596" t="n">
         <v>94431</v>
@@ -46914,7 +46914,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1605" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1605" t="n">
         <v>47377</v>
@@ -47030,7 +47030,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1609" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1609" t="n">
         <v>62656</v>
@@ -47117,7 +47117,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1612" t="n">
-        <v>19.1361923217773</v>
+        <v>19.136194229126</v>
       </c>
       <c r="H1612" t="n">
         <v>32062</v>
@@ -47146,7 +47146,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1613" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1613" t="n">
         <v>23064</v>
@@ -47204,7 +47204,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1615" t="n">
-        <v>18.761360168457</v>
+        <v>18.7613620758057</v>
       </c>
       <c r="H1615" t="n">
         <v>52337</v>
@@ -47291,7 +47291,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1618" t="n">
-        <v>19.1361923217773</v>
+        <v>19.136194229126</v>
       </c>
       <c r="H1618" t="n">
         <v>46997</v>
@@ -47378,7 +47378,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1621" t="n">
-        <v>19.4518413543701</v>
+        <v>19.4518394470215</v>
       </c>
       <c r="H1621" t="n">
         <v>112411</v>
@@ -47407,7 +47407,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1622" t="n">
-        <v>19.0770072937012</v>
+        <v>19.0770092010498</v>
       </c>
       <c r="H1622" t="n">
         <v>36175</v>
@@ -47639,7 +47639,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1630" t="n">
-        <v>18.5640811920166</v>
+        <v>18.564079284668</v>
       </c>
       <c r="H1630" t="n">
         <v>29655</v>
@@ -47755,7 +47755,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1634" t="n">
-        <v>18.0511512756348</v>
+        <v>18.0511493682861</v>
       </c>
       <c r="H1634" t="n">
         <v>471530</v>
@@ -47784,7 +47784,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1635" t="n">
-        <v>16.9858379364014</v>
+        <v>16.9858360290527</v>
       </c>
       <c r="H1635" t="n">
         <v>197325</v>
@@ -47813,7 +47813,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1636" t="n">
-        <v>17.5974063873291</v>
+        <v>17.5974082946777</v>
       </c>
       <c r="H1636" t="n">
         <v>206009</v>
@@ -48045,7 +48045,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1644" t="n">
-        <v>17.3803977966309</v>
+        <v>17.3803997039795</v>
       </c>
       <c r="H1644" t="n">
         <v>59188</v>
@@ -48074,7 +48074,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1645" t="n">
-        <v>17.9130554199219</v>
+        <v>17.9130535125732</v>
       </c>
       <c r="H1645" t="n">
         <v>71263</v>
@@ -48277,7 +48277,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1652" t="n">
-        <v>18.4457111358643</v>
+        <v>18.4457130432129</v>
       </c>
       <c r="H1652" t="n">
         <v>57060</v>
@@ -48364,7 +48364,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1655" t="n">
-        <v>18.4457111358643</v>
+        <v>18.4457130432129</v>
       </c>
       <c r="H1655" t="n">
         <v>68702</v>
@@ -48393,7 +48393,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1656" t="n">
-        <v>18.800817489624</v>
+        <v>18.8008155822754</v>
       </c>
       <c r="H1656" t="n">
         <v>36830</v>
@@ -48451,7 +48451,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>19.294017791748</v>
+        <v>19.2940158843994</v>
       </c>
       <c r="H1658" t="n">
         <v>44283</v>
@@ -48480,7 +48480,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1659" t="n">
-        <v>19.0770072937012</v>
+        <v>19.0770092010498</v>
       </c>
       <c r="H1659" t="n">
         <v>37958</v>
@@ -48567,7 +48567,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1662" t="n">
-        <v>17.9130554199219</v>
+        <v>17.9130535125732</v>
       </c>
       <c r="H1662" t="n">
         <v>53737</v>
@@ -48654,7 +48654,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1665" t="n">
-        <v>17.9525127410889</v>
+        <v>17.9525108337402</v>
       </c>
       <c r="H1665" t="n">
         <v>176564</v>
@@ -49002,7 +49002,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1677" t="n">
-        <v>17.6171340942383</v>
+        <v>17.6171360015869</v>
       </c>
       <c r="H1677" t="n">
         <v>33588</v>
@@ -49089,7 +49089,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1680" t="n">
-        <v>18.800817489624</v>
+        <v>18.8008155822754</v>
       </c>
       <c r="H1680" t="n">
         <v>55654</v>
@@ -49118,7 +49118,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1681" t="n">
-        <v>18.8600006103516</v>
+        <v>18.8600025177002</v>
       </c>
       <c r="H1681" t="n">
         <v>40384</v>
@@ -49147,7 +49147,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1682" t="n">
-        <v>18.8600006103516</v>
+        <v>18.8600025177002</v>
       </c>
       <c r="H1682" t="n">
         <v>37754</v>
@@ -49205,7 +49205,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1684" t="n">
-        <v>18.8600006103516</v>
+        <v>18.8600025177002</v>
       </c>
       <c r="H1684" t="n">
         <v>39958</v>
@@ -49234,7 +49234,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1685" t="n">
-        <v>19.1361923217773</v>
+        <v>19.136194229126</v>
       </c>
       <c r="H1685" t="n">
         <v>41369</v>
@@ -49408,7 +49408,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1691" t="n">
-        <v>19.1559200286865</v>
+        <v>19.1559219360352</v>
       </c>
       <c r="H1691" t="n">
         <v>73900</v>
@@ -49437,7 +49437,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1692" t="n">
-        <v>19.4912986755371</v>
+        <v>19.4912967681885</v>
       </c>
       <c r="H1692" t="n">
         <v>31015</v>
@@ -49466,7 +49466,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1693" t="n">
-        <v>19.1559200286865</v>
+        <v>19.1559219360352</v>
       </c>
       <c r="H1693" t="n">
         <v>26022</v>
@@ -49640,7 +49640,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1699" t="n">
-        <v>21.0103569030762</v>
+        <v>21.0103549957275</v>
       </c>
       <c r="H1699" t="n">
         <v>48753</v>
@@ -49814,7 +49814,7 @@
         <v>21</v>
       </c>
       <c r="G1705" t="n">
-        <v>20.7144355773926</v>
+        <v>20.7144374847412</v>
       </c>
       <c r="H1705" t="n">
         <v>36673</v>
@@ -49843,7 +49843,7 @@
         <v>20.75</v>
       </c>
       <c r="G1706" t="n">
-        <v>20.4678344726562</v>
+        <v>20.4678363800049</v>
       </c>
       <c r="H1706" t="n">
         <v>20784</v>
@@ -50017,7 +50017,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1712" t="n">
-        <v>18.800817489624</v>
+        <v>18.8008155822754</v>
       </c>
       <c r="H1712" t="n">
         <v>98030</v>
@@ -50104,7 +50104,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1715" t="n">
-        <v>20.6651153564453</v>
+        <v>20.6651172637939</v>
       </c>
       <c r="H1715" t="n">
         <v>82485</v>
@@ -50162,7 +50162,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1717" t="n">
-        <v>19.3926582336426</v>
+        <v>19.3926563262939</v>
       </c>
       <c r="H1717" t="n">
         <v>47375</v>
@@ -50191,7 +50191,7 @@
         <v>20</v>
       </c>
       <c r="G1718" t="n">
-        <v>19.7280349731445</v>
+        <v>19.7280330657959</v>
       </c>
       <c r="H1718" t="n">
         <v>48100</v>
@@ -50249,7 +50249,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1720" t="n">
-        <v>17.8933277130127</v>
+        <v>17.8933258056641</v>
       </c>
       <c r="H1720" t="n">
         <v>417782</v>
@@ -50365,7 +50365,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1724" t="n">
-        <v>18.761360168457</v>
+        <v>18.7613620758057</v>
       </c>
       <c r="H1724" t="n">
         <v>44758</v>
@@ -50510,7 +50510,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1729" t="n">
-        <v>17.3014850616455</v>
+        <v>17.3014869689941</v>
       </c>
       <c r="H1729" t="n">
         <v>129668</v>
@@ -50568,7 +50568,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1731" t="n">
-        <v>16.6307315826416</v>
+        <v>16.6307334899902</v>
       </c>
       <c r="H1731" t="n">
         <v>70574</v>
@@ -50597,7 +50597,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1732" t="n">
-        <v>16.5123653411865</v>
+        <v>16.5123634338379</v>
       </c>
       <c r="H1732" t="n">
         <v>59262</v>
@@ -50655,7 +50655,7 @@
         <v>16.5</v>
       </c>
       <c r="G1734" t="n">
-        <v>16.2756290435791</v>
+        <v>16.2756271362305</v>
       </c>
       <c r="H1734" t="n">
         <v>50047</v>
@@ -50713,7 +50713,7 @@
         <v>15</v>
       </c>
       <c r="G1736" t="n">
-        <v>14.7960252761841</v>
+        <v>14.7960262298584</v>
       </c>
       <c r="H1736" t="n">
         <v>121333</v>
@@ -50829,7 +50829,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1740" t="n">
-        <v>15.6837863922119</v>
+        <v>15.6837873458862</v>
       </c>
       <c r="H1740" t="n">
         <v>250868</v>
@@ -50887,7 +50887,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1742" t="n">
-        <v>16.6307315826416</v>
+        <v>16.6307334899902</v>
       </c>
       <c r="H1742" t="n">
         <v>43113</v>
@@ -50916,7 +50916,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1743" t="n">
-        <v>16.3742694854736</v>
+        <v>16.374267578125</v>
       </c>
       <c r="H1743" t="n">
         <v>38877</v>
@@ -51032,7 +51032,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1747" t="n">
-        <v>16.9858379364014</v>
+        <v>16.9858360290527</v>
       </c>
       <c r="H1747" t="n">
         <v>23480</v>
@@ -51061,7 +51061,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1748" t="n">
-        <v>17.1042041778564</v>
+        <v>17.1042060852051</v>
       </c>
       <c r="H1748" t="n">
         <v>27699</v>
@@ -51351,7 +51351,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1758" t="n">
-        <v>19.2545623779297</v>
+        <v>19.2545604705811</v>
       </c>
       <c r="H1758" t="n">
         <v>72515</v>
@@ -51380,7 +51380,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1759" t="n">
-        <v>20.1719169616699</v>
+        <v>20.1719150543213</v>
       </c>
       <c r="H1759" t="n">
         <v>85839</v>
@@ -51438,7 +51438,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1761" t="n">
-        <v>19.3926582336426</v>
+        <v>19.3926563262939</v>
       </c>
       <c r="H1761" t="n">
         <v>36168</v>
@@ -51496,7 +51496,7 @@
         <v>21</v>
       </c>
       <c r="G1763" t="n">
-        <v>20.7144355773926</v>
+        <v>20.7144374847412</v>
       </c>
       <c r="H1763" t="n">
         <v>79324</v>
@@ -51525,7 +51525,7 @@
         <v>20.75</v>
       </c>
       <c r="G1764" t="n">
-        <v>20.4678344726562</v>
+        <v>20.4678363800049</v>
       </c>
       <c r="H1764" t="n">
         <v>23257</v>
@@ -51583,7 +51583,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1766" t="n">
-        <v>20.6157970428467</v>
+        <v>20.615795135498</v>
       </c>
       <c r="H1766" t="n">
         <v>25212</v>
@@ -51612,7 +51612,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1767" t="n">
-        <v>20.1719169616699</v>
+        <v>20.1719150543213</v>
       </c>
       <c r="H1767" t="n">
         <v>57051</v>
@@ -51641,7 +51641,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1768" t="n">
-        <v>20.6157970428467</v>
+        <v>20.615795135498</v>
       </c>
       <c r="H1768" t="n">
         <v>83439</v>
@@ -51757,7 +51757,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1772" t="n">
-        <v>20.418514251709</v>
+        <v>20.4185161590576</v>
       </c>
       <c r="H1772" t="n">
         <v>112346</v>
@@ -51786,7 +51786,7 @@
         <v>20.75</v>
       </c>
       <c r="G1773" t="n">
-        <v>20.4678344726562</v>
+        <v>20.4678363800049</v>
       </c>
       <c r="H1773" t="n">
         <v>52366</v>
@@ -52105,7 +52105,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1784" t="n">
-        <v>22.2433567047119</v>
+        <v>22.2433586120605</v>
       </c>
       <c r="H1784" t="n">
         <v>46819</v>
@@ -52134,7 +52134,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1785" t="n">
-        <v>22.3419990539551</v>
+        <v>22.3419971466064</v>
       </c>
       <c r="H1785" t="n">
         <v>77558</v>
@@ -61971,6 +61971,35 @@
         <v>72363</v>
       </c>
       <c r="I2124" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2125" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2125" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>26.3500003814697</v>
+      </c>
+      <c r="E2125" t="n">
+        <v>25.6499996185303</v>
+      </c>
+      <c r="F2125" t="n">
+        <v>26.1499996185303</v>
+      </c>
+      <c r="G2125" t="n">
+        <v>26.1499996185303</v>
+      </c>
+      <c r="H2125" t="n">
+        <v>67539</v>
+      </c>
+      <c r="I2125" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G2" t="n">
-        <v>7.53173208236694</v>
+        <v>7.5317325592041</v>
       </c>
       <c r="H2" t="n">
         <v>3452297</v>
@@ -456,7 +456,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G3" t="n">
-        <v>7.8512601852417</v>
+        <v>7.85126066207886</v>
       </c>
       <c r="H3" t="n">
         <v>1125391</v>
@@ -485,7 +485,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G4" t="n">
-        <v>7.75996541976929</v>
+        <v>7.75996589660645</v>
       </c>
       <c r="H4" t="n">
         <v>686773</v>
@@ -514,7 +514,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G5" t="n">
-        <v>7.75996541976929</v>
+        <v>7.75996589660645</v>
       </c>
       <c r="H5" t="n">
         <v>360346</v>
@@ -601,7 +601,7 @@
         <v>8.31955623626709</v>
       </c>
       <c r="G8" t="n">
-        <v>7.82204675674438</v>
+        <v>7.82204627990723</v>
       </c>
       <c r="H8" t="n">
         <v>85887</v>
@@ -630,7 +630,7 @@
         <v>8.41859817504883</v>
       </c>
       <c r="G9" t="n">
-        <v>7.91516494750977</v>
+        <v>7.9151668548584</v>
       </c>
       <c r="H9" t="n">
         <v>85323</v>
@@ -659,7 +659,7 @@
         <v>8.10884761810303</v>
       </c>
       <c r="G10" t="n">
-        <v>7.62393856048584</v>
+        <v>7.623939037323</v>
       </c>
       <c r="H10" t="n">
         <v>23688</v>
@@ -688,7 +688,7 @@
         <v>8.42830753326416</v>
       </c>
       <c r="G11" t="n">
-        <v>7.92429351806641</v>
+        <v>7.92429542541504</v>
       </c>
       <c r="H11" t="n">
         <v>19928</v>
@@ -717,7 +717,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G12" t="n">
-        <v>7.53173208236694</v>
+        <v>7.5317325592041</v>
       </c>
       <c r="H12" t="n">
         <v>75575</v>
@@ -746,7 +746,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G13" t="n">
-        <v>7.53173208236694</v>
+        <v>7.5317325592041</v>
       </c>
       <c r="H13" t="n">
         <v>73138</v>
@@ -891,7 +891,7 @@
         <v>8.00106716156006</v>
       </c>
       <c r="G18" t="n">
-        <v>7.5226035118103</v>
+        <v>7.52260303497314</v>
       </c>
       <c r="H18" t="n">
         <v>83534</v>
@@ -978,7 +978,7 @@
         <v>7.97193717956543</v>
       </c>
       <c r="G21" t="n">
-        <v>7.49521446228027</v>
+        <v>7.49521493911743</v>
       </c>
       <c r="H21" t="n">
         <v>14400</v>
@@ -1036,7 +1036,7 @@
         <v>8.24381828308105</v>
       </c>
       <c r="G23" t="n">
-        <v>7.7508373260498</v>
+        <v>7.75083780288696</v>
       </c>
       <c r="H23" t="n">
         <v>147231</v>
@@ -1094,7 +1094,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G25" t="n">
-        <v>7.80561399459839</v>
+        <v>7.80561447143555</v>
       </c>
       <c r="H25" t="n">
         <v>57598</v>
@@ -1123,7 +1123,7 @@
         <v>8.37101936340332</v>
       </c>
       <c r="G26" t="n">
-        <v>7.87043142318726</v>
+        <v>7.87043237686157</v>
       </c>
       <c r="H26" t="n">
         <v>12597</v>
@@ -1152,7 +1152,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G27" t="n">
-        <v>7.80561399459839</v>
+        <v>7.80561447143555</v>
       </c>
       <c r="H27" t="n">
         <v>7454</v>
@@ -1210,7 +1210,7 @@
         <v>8.31178760528564</v>
       </c>
       <c r="G29" t="n">
-        <v>7.81474256515503</v>
+        <v>7.81474208831787</v>
       </c>
       <c r="H29" t="n">
         <v>129981</v>
@@ -1239,7 +1239,7 @@
         <v>8.47394561767578</v>
       </c>
       <c r="G30" t="n">
-        <v>7.96720361709595</v>
+        <v>7.96720409393311</v>
       </c>
       <c r="H30" t="n">
         <v>238620</v>
@@ -1268,7 +1268,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G31" t="n">
-        <v>7.8512601852417</v>
+        <v>7.85126066207886</v>
       </c>
       <c r="H31" t="n">
         <v>21511</v>
@@ -1297,7 +1297,7 @@
         <v>8.25741195678711</v>
       </c>
       <c r="G32" t="n">
-        <v>7.76361989974976</v>
+        <v>7.76361846923828</v>
       </c>
       <c r="H32" t="n">
         <v>19336</v>
@@ -1326,7 +1326,7 @@
         <v>8.20497798919678</v>
       </c>
       <c r="G33" t="n">
-        <v>7.71431922912598</v>
+        <v>7.71432113647461</v>
       </c>
       <c r="H33" t="n">
         <v>19958</v>
@@ -1355,7 +1355,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G34" t="n">
-        <v>7.80561399459839</v>
+        <v>7.80561447143555</v>
       </c>
       <c r="H34" t="n">
         <v>33613</v>
@@ -1442,7 +1442,7 @@
         <v>8.31178760528564</v>
       </c>
       <c r="G37" t="n">
-        <v>7.81474256515503</v>
+        <v>7.81474208831787</v>
       </c>
       <c r="H37" t="n">
         <v>10519</v>
@@ -1471,7 +1471,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G38" t="n">
-        <v>7.80561399459839</v>
+        <v>7.80561447143555</v>
       </c>
       <c r="H38" t="n">
         <v>50515</v>
@@ -1500,7 +1500,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G39" t="n">
-        <v>7.8512601852417</v>
+        <v>7.85126066207886</v>
       </c>
       <c r="H39" t="n">
         <v>3319</v>
@@ -1558,7 +1558,7 @@
         <v>8.12923908233643</v>
       </c>
       <c r="G41" t="n">
-        <v>7.6431097984314</v>
+        <v>7.64311027526855</v>
       </c>
       <c r="H41" t="n">
         <v>69304</v>
@@ -1587,7 +1587,7 @@
         <v>8.23410797119141</v>
       </c>
       <c r="G42" t="n">
-        <v>7.74170732498169</v>
+        <v>7.74170780181885</v>
       </c>
       <c r="H42" t="n">
         <v>27604</v>
@@ -1616,7 +1616,7 @@
         <v>8.1855583190918</v>
       </c>
       <c r="G43" t="n">
-        <v>7.69606161117554</v>
+        <v>7.69606113433838</v>
       </c>
       <c r="H43" t="n">
         <v>12672</v>
@@ -1674,7 +1674,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G45" t="n">
-        <v>7.8512601852417</v>
+        <v>7.85126066207886</v>
       </c>
       <c r="H45" t="n">
         <v>15675</v>
@@ -1703,7 +1703,7 @@
         <v>8.33606338500977</v>
       </c>
       <c r="G46" t="n">
-        <v>7.83756589889526</v>
+        <v>7.83756542205811</v>
       </c>
       <c r="H46" t="n">
         <v>4029</v>
@@ -1761,7 +1761,7 @@
         <v>8.10787677764893</v>
       </c>
       <c r="G48" t="n">
-        <v>7.62302494049072</v>
+        <v>7.62302446365356</v>
       </c>
       <c r="H48" t="n">
         <v>5413</v>
@@ -1790,7 +1790,7 @@
         <v>8.22634029388428</v>
       </c>
       <c r="G49" t="n">
-        <v>7.73440456390381</v>
+        <v>7.73440504074097</v>
       </c>
       <c r="H49" t="n">
         <v>27912</v>
@@ -1819,7 +1819,7 @@
         <v>8.1875</v>
       </c>
       <c r="G50" t="n">
-        <v>7.6978874206543</v>
+        <v>7.69788646697998</v>
       </c>
       <c r="H50" t="n">
         <v>28126</v>
@@ -1877,7 +1877,7 @@
         <v>8.51667022705078</v>
       </c>
       <c r="G52" t="n">
-        <v>8.00737380981445</v>
+        <v>8.00737190246582</v>
       </c>
       <c r="H52" t="n">
         <v>142170</v>
@@ -1935,7 +1935,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G54" t="n">
-        <v>8.24930191040039</v>
+        <v>8.24930095672607</v>
       </c>
       <c r="H54" t="n">
         <v>56090</v>
@@ -2051,7 +2051,7 @@
         <v>9.46728229522705</v>
       </c>
       <c r="G58" t="n">
-        <v>8.90113735198975</v>
+        <v>8.90113830566406</v>
       </c>
       <c r="H58" t="n">
         <v>74281</v>
@@ -2080,7 +2080,7 @@
         <v>9.08859062194824</v>
       </c>
       <c r="G59" t="n">
-        <v>8.54509353637695</v>
+        <v>8.54509258270264</v>
       </c>
       <c r="H59" t="n">
         <v>57537</v>
@@ -2109,7 +2109,7 @@
         <v>8.75844955444336</v>
       </c>
       <c r="G60" t="n">
-        <v>8.234694480896</v>
+        <v>8.23469352722168</v>
       </c>
       <c r="H60" t="n">
         <v>78366</v>
@@ -2167,7 +2167,7 @@
         <v>8.94973659515381</v>
       </c>
       <c r="G62" t="n">
-        <v>8.41454315185547</v>
+        <v>8.41454219818115</v>
       </c>
       <c r="H62" t="n">
         <v>40240</v>
@@ -2254,7 +2254,7 @@
         <v>9.20511054992676</v>
       </c>
       <c r="G65" t="n">
-        <v>8.65464401245117</v>
+        <v>8.65464496612549</v>
       </c>
       <c r="H65" t="n">
         <v>35765</v>
@@ -2283,7 +2283,7 @@
         <v>9.24395084381104</v>
       </c>
       <c r="G66" t="n">
-        <v>8.69116115570068</v>
+        <v>8.691162109375</v>
       </c>
       <c r="H66" t="n">
         <v>43076</v>
@@ -2370,7 +2370,7 @@
         <v>9.29250144958496</v>
       </c>
       <c r="G69" t="n">
-        <v>8.73680877685547</v>
+        <v>8.73680782318115</v>
       </c>
       <c r="H69" t="n">
         <v>59640</v>
@@ -2457,7 +2457,7 @@
         <v>9.37115287780762</v>
       </c>
       <c r="G72" t="n">
-        <v>8.81075763702393</v>
+        <v>8.81075668334961</v>
       </c>
       <c r="H72" t="n">
         <v>39116</v>
@@ -2515,7 +2515,7 @@
         <v>9.66148281097412</v>
       </c>
       <c r="G74" t="n">
-        <v>9.08372592926025</v>
+        <v>9.08372497558594</v>
       </c>
       <c r="H74" t="n">
         <v>127408</v>
@@ -2544,7 +2544,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G75" t="n">
-        <v>9.27544212341309</v>
+        <v>9.27544116973877</v>
       </c>
       <c r="H75" t="n">
         <v>612811</v>
@@ -2602,7 +2602,7 @@
         <v>9.63332366943359</v>
       </c>
       <c r="G77" t="n">
-        <v>9.05725002288818</v>
+        <v>9.0572509765625</v>
       </c>
       <c r="H77" t="n">
         <v>123734</v>
@@ -2660,7 +2660,7 @@
         <v>9.70614910125732</v>
       </c>
       <c r="G79" t="n">
-        <v>9.1257209777832</v>
+        <v>9.12572193145752</v>
       </c>
       <c r="H79" t="n">
         <v>25765</v>
@@ -2689,7 +2689,7 @@
         <v>9.57506275177002</v>
       </c>
       <c r="G80" t="n">
-        <v>9.00247478485107</v>
+        <v>9.00247383117676</v>
       </c>
       <c r="H80" t="n">
         <v>21310</v>
@@ -2747,7 +2747,7 @@
         <v>9.26239967346191</v>
       </c>
       <c r="G82" t="n">
-        <v>8.7085075378418</v>
+        <v>8.70850658416748</v>
       </c>
       <c r="H82" t="n">
         <v>15137</v>
@@ -2805,7 +2805,7 @@
         <v>9.55467224121094</v>
       </c>
       <c r="G84" t="n">
-        <v>8.98330307006836</v>
+        <v>8.98330402374268</v>
       </c>
       <c r="H84" t="n">
         <v>24808</v>
@@ -2863,7 +2863,7 @@
         <v>9.16238689422607</v>
       </c>
       <c r="G86" t="n">
-        <v>8.61447525024414</v>
+        <v>8.61447620391846</v>
       </c>
       <c r="H86" t="n">
         <v>63090</v>
@@ -2892,7 +2892,7 @@
         <v>8.98954772949219</v>
       </c>
       <c r="G87" t="n">
-        <v>8.45197486877441</v>
+        <v>8.45197200775146</v>
       </c>
       <c r="H87" t="n">
         <v>53966</v>
@@ -2950,7 +2950,7 @@
         <v>8.43413352966309</v>
       </c>
       <c r="G89" t="n">
-        <v>7.92977142333984</v>
+        <v>7.92977046966553</v>
       </c>
       <c r="H89" t="n">
         <v>72833</v>
@@ -2979,7 +2979,7 @@
         <v>8.77689933776855</v>
       </c>
       <c r="G90" t="n">
-        <v>8.25203895568848</v>
+        <v>8.25203990936279</v>
       </c>
       <c r="H90" t="n">
         <v>32211</v>
@@ -3008,7 +3008,7 @@
         <v>8.88467979431152</v>
       </c>
       <c r="G91" t="n">
-        <v>8.3533763885498</v>
+        <v>8.35337448120117</v>
       </c>
       <c r="H91" t="n">
         <v>47197</v>
@@ -3066,7 +3066,7 @@
         <v>9.07888126373291</v>
       </c>
       <c r="G93" t="n">
-        <v>8.53596496582031</v>
+        <v>8.535964012146</v>
       </c>
       <c r="H93" t="n">
         <v>63873</v>
@@ -3124,7 +3124,7 @@
         <v>9.07888126373291</v>
       </c>
       <c r="G95" t="n">
-        <v>8.53596496582031</v>
+        <v>8.535964012146</v>
       </c>
       <c r="H95" t="n">
         <v>54068</v>
@@ -3211,7 +3211,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G98" t="n">
-        <v>7.80561399459839</v>
+        <v>7.80561447143555</v>
       </c>
       <c r="H98" t="n">
         <v>31873</v>
@@ -3240,7 +3240,7 @@
         <v>8.48462677001953</v>
       </c>
       <c r="G99" t="n">
-        <v>7.97724580764771</v>
+        <v>7.97724485397339</v>
       </c>
       <c r="H99" t="n">
         <v>22913</v>
@@ -3269,7 +3269,7 @@
         <v>7.97193717956543</v>
       </c>
       <c r="G100" t="n">
-        <v>7.49521446228027</v>
+        <v>7.49521493911743</v>
       </c>
       <c r="H100" t="n">
         <v>32370</v>
@@ -3298,7 +3298,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G101" t="n">
-        <v>7.75996541976929</v>
+        <v>7.75996589660645</v>
       </c>
       <c r="H101" t="n">
         <v>13973</v>
@@ -3327,7 +3327,7 @@
         <v>8.19041347503662</v>
       </c>
       <c r="G102" t="n">
-        <v>7.70062637329102</v>
+        <v>7.70062685012817</v>
       </c>
       <c r="H102" t="n">
         <v>33890</v>
@@ -3356,7 +3356,7 @@
         <v>8.3700475692749</v>
       </c>
       <c r="G103" t="n">
-        <v>7.86951732635498</v>
+        <v>7.8695182800293</v>
       </c>
       <c r="H103" t="n">
         <v>25306</v>
@@ -3385,7 +3385,7 @@
         <v>8.3700475692749</v>
       </c>
       <c r="G104" t="n">
-        <v>7.86951732635498</v>
+        <v>7.8695182800293</v>
       </c>
       <c r="H104" t="n">
         <v>30512</v>
@@ -3414,7 +3414,7 @@
         <v>8.81476783752441</v>
       </c>
       <c r="G105" t="n">
-        <v>8.2876443862915</v>
+        <v>8.28764343261719</v>
       </c>
       <c r="H105" t="n">
         <v>53875</v>
@@ -3443,7 +3443,7 @@
         <v>9.27210998535156</v>
       </c>
       <c r="G106" t="n">
-        <v>8.71763706207275</v>
+        <v>8.71763801574707</v>
       </c>
       <c r="H106" t="n">
         <v>46620</v>
@@ -3501,7 +3501,7 @@
         <v>9.25074768066406</v>
       </c>
       <c r="G108" t="n">
-        <v>8.69755172729492</v>
+        <v>8.69755077362061</v>
       </c>
       <c r="H108" t="n">
         <v>17543</v>
@@ -3559,7 +3559,7 @@
         <v>9.08664894104004</v>
       </c>
       <c r="G110" t="n">
-        <v>8.54326725006104</v>
+        <v>8.54326820373535</v>
       </c>
       <c r="H110" t="n">
         <v>32067</v>
@@ -3675,7 +3675,7 @@
         <v>8.81379699707031</v>
       </c>
       <c r="G114" t="n">
-        <v>8.28673267364502</v>
+        <v>8.2867317199707</v>
       </c>
       <c r="H114" t="n">
         <v>33903</v>
@@ -3704,7 +3704,7 @@
         <v>9.04586696624756</v>
       </c>
       <c r="G115" t="n">
-        <v>8.50492286682129</v>
+        <v>8.50492477416992</v>
       </c>
       <c r="H115" t="n">
         <v>61099</v>
@@ -3733,7 +3733,7 @@
         <v>9.2138500213623</v>
       </c>
       <c r="G116" t="n">
-        <v>8.66286373138428</v>
+        <v>8.66286182403564</v>
       </c>
       <c r="H116" t="n">
         <v>60391</v>
@@ -3762,7 +3762,7 @@
         <v>8.51084423065186</v>
       </c>
       <c r="G117" t="n">
-        <v>8.0018949508667</v>
+        <v>8.00189590454102</v>
       </c>
       <c r="H117" t="n">
         <v>101226</v>
@@ -3791,7 +3791,7 @@
         <v>8.49724960327148</v>
       </c>
       <c r="G118" t="n">
-        <v>7.98911285400391</v>
+        <v>7.98911333084106</v>
       </c>
       <c r="H118" t="n">
         <v>42084</v>
@@ -3849,7 +3849,7 @@
         <v>8.65260982513428</v>
       </c>
       <c r="G120" t="n">
-        <v>8.13518333435059</v>
+        <v>8.1351842880249</v>
       </c>
       <c r="H120" t="n">
         <v>56877</v>
@@ -3907,7 +3907,7 @@
         <v>8.80700016021729</v>
       </c>
       <c r="G122" t="n">
-        <v>8.28034019470215</v>
+        <v>8.28034210205078</v>
       </c>
       <c r="H122" t="n">
         <v>51549</v>
@@ -3965,7 +3965,7 @@
         <v>8.99149036407471</v>
       </c>
       <c r="G124" t="n">
-        <v>8.45380020141602</v>
+        <v>8.4537992477417</v>
       </c>
       <c r="H124" t="n">
         <v>78582</v>
@@ -4023,7 +4023,7 @@
         <v>9.42650032043457</v>
       </c>
       <c r="G126" t="n">
-        <v>8.86279582977295</v>
+        <v>8.86279392242432</v>
       </c>
       <c r="H126" t="n">
         <v>163957</v>
@@ -4052,7 +4052,7 @@
         <v>9.55078792572021</v>
       </c>
       <c r="G127" t="n">
-        <v>8.97965049743652</v>
+        <v>8.97965145111084</v>
       </c>
       <c r="H127" t="n">
         <v>112485</v>
@@ -4139,7 +4139,7 @@
         <v>9.67119312286377</v>
       </c>
       <c r="G130" t="n">
-        <v>9.09285640716553</v>
+        <v>9.09285449981689</v>
       </c>
       <c r="H130" t="n">
         <v>32320</v>
@@ -4168,7 +4168,7 @@
         <v>9.35076236724854</v>
       </c>
       <c r="G131" t="n">
-        <v>8.79158592224121</v>
+        <v>8.79158687591553</v>
       </c>
       <c r="H131" t="n">
         <v>43129</v>
@@ -4255,7 +4255,7 @@
         <v>9.5935115814209</v>
       </c>
       <c r="G134" t="n">
-        <v>9.01981830596924</v>
+        <v>9.01981925964355</v>
       </c>
       <c r="H134" t="n">
         <v>86092</v>
@@ -4284,7 +4284,7 @@
         <v>9.35755920410156</v>
       </c>
       <c r="G135" t="n">
-        <v>8.79797649383545</v>
+        <v>8.79797744750977</v>
       </c>
       <c r="H135" t="n">
         <v>37188</v>
@@ -4371,7 +4371,7 @@
         <v>8.70018863677979</v>
       </c>
       <c r="G138" t="n">
-        <v>8.17991733551025</v>
+        <v>8.17991828918457</v>
       </c>
       <c r="H138" t="n">
         <v>33830</v>
@@ -4458,7 +4458,7 @@
         <v>8.66523265838623</v>
       </c>
       <c r="G141" t="n">
-        <v>8.14705181121826</v>
+        <v>8.14705276489258</v>
       </c>
       <c r="H141" t="n">
         <v>15104</v>
@@ -4487,7 +4487,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G142" t="n">
-        <v>8.24930191040039</v>
+        <v>8.24930095672607</v>
       </c>
       <c r="H142" t="n">
         <v>40885</v>
@@ -4574,7 +4574,7 @@
         <v>8.76815986633301</v>
       </c>
       <c r="G145" t="n">
-        <v>8.24382400512695</v>
+        <v>8.24382305145264</v>
       </c>
       <c r="H145" t="n">
         <v>27159</v>
@@ -4632,7 +4632,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G147" t="n">
-        <v>8.24930191040039</v>
+        <v>8.24930095672607</v>
       </c>
       <c r="H147" t="n">
         <v>46996</v>
@@ -4661,7 +4661,7 @@
         <v>8.98178005218506</v>
       </c>
       <c r="G148" t="n">
-        <v>8.44466972351074</v>
+        <v>8.44467067718506</v>
       </c>
       <c r="H148" t="n">
         <v>99143</v>
@@ -4748,7 +4748,7 @@
         <v>8.69047927856445</v>
       </c>
       <c r="G151" t="n">
-        <v>8.17078876495361</v>
+        <v>8.1707878112793</v>
       </c>
       <c r="H151" t="n">
         <v>15730</v>
@@ -4835,7 +4835,7 @@
         <v>8.65260982513428</v>
       </c>
       <c r="G154" t="n">
-        <v>8.13518333435059</v>
+        <v>8.1351842880249</v>
       </c>
       <c r="H154" t="n">
         <v>47268</v>
@@ -4893,7 +4893,7 @@
         <v>8.61474132537842</v>
       </c>
       <c r="G156" t="n">
-        <v>8.09958076477051</v>
+        <v>8.09957981109619</v>
       </c>
       <c r="H156" t="n">
         <v>15804</v>
@@ -4951,7 +4951,7 @@
         <v>8.87497043609619</v>
       </c>
       <c r="G158" t="n">
-        <v>8.34424686431885</v>
+        <v>8.34424591064453</v>
       </c>
       <c r="H158" t="n">
         <v>27757</v>
@@ -5038,7 +5038,7 @@
         <v>9.20316886901855</v>
       </c>
       <c r="G161" t="n">
-        <v>8.65281867980957</v>
+        <v>8.65281772613525</v>
       </c>
       <c r="H161" t="n">
         <v>24925</v>
@@ -5067,7 +5067,7 @@
         <v>9.20316886901855</v>
       </c>
       <c r="G162" t="n">
-        <v>8.65281867980957</v>
+        <v>8.65281772613525</v>
       </c>
       <c r="H162" t="n">
         <v>10411</v>
@@ -5154,7 +5154,7 @@
         <v>9.61584568023682</v>
       </c>
       <c r="G165" t="n">
-        <v>9.04081726074219</v>
+        <v>9.04081630706787</v>
       </c>
       <c r="H165" t="n">
         <v>44742</v>
@@ -5212,7 +5212,7 @@
         <v>9.40222454071045</v>
       </c>
       <c r="G167" t="n">
-        <v>8.83997249603271</v>
+        <v>8.8399715423584</v>
       </c>
       <c r="H167" t="n">
         <v>18153</v>
@@ -5270,7 +5270,7 @@
         <v>9.33522605895996</v>
       </c>
       <c r="G169" t="n">
-        <v>8.77697944641113</v>
+        <v>8.7769775390625</v>
       </c>
       <c r="H169" t="n">
         <v>11871</v>
@@ -5328,7 +5328,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G171" t="n">
-        <v>8.99242973327637</v>
+        <v>8.99243068695068</v>
       </c>
       <c r="H171" t="n">
         <v>18448</v>
@@ -5386,7 +5386,7 @@
         <v>9.72751140594482</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14580535888672</v>
+        <v>9.14580631256104</v>
       </c>
       <c r="H173" t="n">
         <v>31014</v>
@@ -5415,7 +5415,7 @@
         <v>9.89258098602295</v>
       </c>
       <c r="G174" t="n">
-        <v>9.30100345611572</v>
+        <v>9.30100440979004</v>
       </c>
       <c r="H174" t="n">
         <v>22663</v>
@@ -5444,7 +5444,7 @@
         <v>9.92753791809082</v>
       </c>
       <c r="G175" t="n">
-        <v>9.33386993408203</v>
+        <v>9.33387088775635</v>
       </c>
       <c r="H175" t="n">
         <v>15678</v>
@@ -5473,7 +5473,7 @@
         <v>10.1547517776489</v>
       </c>
       <c r="G176" t="n">
-        <v>9.54749774932861</v>
+        <v>9.5474967956543</v>
       </c>
       <c r="H176" t="n">
         <v>24722</v>
@@ -5502,7 +5502,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G177" t="n">
-        <v>9.58584213256836</v>
+        <v>9.58584022521973</v>
       </c>
       <c r="H177" t="n">
         <v>18160</v>
@@ -5531,7 +5531,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G178" t="n">
-        <v>9.58584213256836</v>
+        <v>9.58584022521973</v>
       </c>
       <c r="H178" t="n">
         <v>16440</v>
@@ -5560,7 +5560,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G179" t="n">
-        <v>9.58584213256836</v>
+        <v>9.58584022521973</v>
       </c>
       <c r="H179" t="n">
         <v>13022</v>
@@ -5589,7 +5589,7 @@
         <v>10.2440853118896</v>
       </c>
       <c r="G180" t="n">
-        <v>9.63148880004883</v>
+        <v>9.6314868927002</v>
       </c>
       <c r="H180" t="n">
         <v>17545</v>
@@ -5618,7 +5618,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G181" t="n">
-        <v>9.58584213256836</v>
+        <v>9.58584022521973</v>
       </c>
       <c r="H181" t="n">
         <v>12625</v>
@@ -5676,7 +5676,7 @@
         <v>10.1897087097168</v>
       </c>
       <c r="G183" t="n">
-        <v>9.58036518096924</v>
+        <v>9.58036327362061</v>
       </c>
       <c r="H183" t="n">
         <v>13620</v>
@@ -5705,7 +5705,7 @@
         <v>9.84791469573975</v>
       </c>
       <c r="G184" t="n">
-        <v>9.25900840759277</v>
+        <v>9.25900936126709</v>
       </c>
       <c r="H184" t="n">
         <v>45964</v>
@@ -5734,7 +5734,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G185" t="n">
-        <v>9.58584213256836</v>
+        <v>9.58584022521973</v>
       </c>
       <c r="H185" t="n">
         <v>8445</v>
@@ -5821,7 +5821,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G188" t="n">
-        <v>9.58584213256836</v>
+        <v>9.58584022521973</v>
       </c>
       <c r="H188" t="n">
         <v>23356</v>
@@ -5850,7 +5850,7 @@
         <v>10.0498838424683</v>
       </c>
       <c r="G189" t="n">
-        <v>9.44890117645264</v>
+        <v>9.448899269104</v>
       </c>
       <c r="H189" t="n">
         <v>32652</v>
@@ -5937,7 +5937,7 @@
         <v>9.8595666885376</v>
       </c>
       <c r="G192" t="n">
-        <v>9.26996421813965</v>
+        <v>9.26996326446533</v>
       </c>
       <c r="H192" t="n">
         <v>21463</v>
@@ -5995,7 +5995,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G194" t="n">
-        <v>8.99242973327637</v>
+        <v>8.99243068695068</v>
       </c>
       <c r="H194" t="n">
         <v>37882</v>
@@ -6053,7 +6053,7 @@
         <v>9.66148281097412</v>
       </c>
       <c r="G196" t="n">
-        <v>9.08372592926025</v>
+        <v>9.08372497558594</v>
       </c>
       <c r="H196" t="n">
         <v>20981</v>
@@ -6198,7 +6198,7 @@
         <v>8.87497043609619</v>
       </c>
       <c r="G201" t="n">
-        <v>8.34424686431885</v>
+        <v>8.34424591064453</v>
       </c>
       <c r="H201" t="n">
         <v>197330</v>
@@ -6227,7 +6227,7 @@
         <v>8.85263729095459</v>
       </c>
       <c r="G202" t="n">
-        <v>8.32324886322021</v>
+        <v>8.32324981689453</v>
       </c>
       <c r="H202" t="n">
         <v>36498</v>
@@ -6256,7 +6256,7 @@
         <v>9.25657367706299</v>
       </c>
       <c r="G203" t="n">
-        <v>8.70302867889404</v>
+        <v>8.70302963256836</v>
       </c>
       <c r="H203" t="n">
         <v>45319</v>
@@ -6285,7 +6285,7 @@
         <v>9.5935115814209</v>
       </c>
       <c r="G204" t="n">
-        <v>9.01981830596924</v>
+        <v>9.01981925964355</v>
       </c>
       <c r="H204" t="n">
         <v>85559</v>
@@ -6314,7 +6314,7 @@
         <v>9.51680278778076</v>
       </c>
       <c r="G205" t="n">
-        <v>8.94769668579102</v>
+        <v>8.94769859313965</v>
       </c>
       <c r="H205" t="n">
         <v>19012</v>
@@ -6372,7 +6372,7 @@
         <v>9.67119312286377</v>
       </c>
       <c r="G207" t="n">
-        <v>9.09285640716553</v>
+        <v>9.09285449981689</v>
       </c>
       <c r="H207" t="n">
         <v>36508</v>
@@ -6401,7 +6401,7 @@
         <v>9.71003341674805</v>
       </c>
       <c r="G208" t="n">
-        <v>9.12937355041504</v>
+        <v>9.12937450408936</v>
       </c>
       <c r="H208" t="n">
         <v>9796</v>
@@ -6488,7 +6488,7 @@
         <v>9.62264347076416</v>
       </c>
       <c r="G211" t="n">
-        <v>9.04720878601074</v>
+        <v>9.04720973968506</v>
       </c>
       <c r="H211" t="n">
         <v>14681</v>
@@ -6517,7 +6517,7 @@
         <v>9.66148281097412</v>
       </c>
       <c r="G212" t="n">
-        <v>9.08372592926025</v>
+        <v>9.08372497558594</v>
       </c>
       <c r="H212" t="n">
         <v>22204</v>
@@ -6691,7 +6691,7 @@
         <v>10.0790138244629</v>
       </c>
       <c r="G218" t="n">
-        <v>9.47628879547119</v>
+        <v>9.47628974914551</v>
       </c>
       <c r="H218" t="n">
         <v>27030</v>
@@ -6720,7 +6720,7 @@
         <v>10.3120546340942</v>
       </c>
       <c r="G219" t="n">
-        <v>9.69539356231689</v>
+        <v>9.69539260864258</v>
       </c>
       <c r="H219" t="n">
         <v>30483</v>
@@ -6807,7 +6807,7 @@
         <v>10.3120546340942</v>
       </c>
       <c r="G222" t="n">
-        <v>9.69539356231689</v>
+        <v>9.69539260864258</v>
       </c>
       <c r="H222" t="n">
         <v>14768</v>
@@ -6865,7 +6865,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G224" t="n">
-        <v>9.98753452301025</v>
+        <v>9.98753356933594</v>
       </c>
       <c r="H224" t="n">
         <v>8445</v>
@@ -6894,7 +6894,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G225" t="n">
-        <v>9.73190975189209</v>
+        <v>9.73191070556641</v>
       </c>
       <c r="H225" t="n">
         <v>32595</v>
@@ -6923,7 +6923,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G226" t="n">
-        <v>9.98753452301025</v>
+        <v>9.98753356933594</v>
       </c>
       <c r="H226" t="n">
         <v>36732</v>
@@ -6952,7 +6952,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G227" t="n">
-        <v>9.85972213745117</v>
+        <v>9.85972309112549</v>
       </c>
       <c r="H227" t="n">
         <v>13733</v>
@@ -6981,7 +6981,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G228" t="n">
-        <v>9.73190975189209</v>
+        <v>9.73191070556641</v>
       </c>
       <c r="H228" t="n">
         <v>19355</v>
@@ -7039,7 +7039,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G230" t="n">
-        <v>9.73190975189209</v>
+        <v>9.73191070556641</v>
       </c>
       <c r="H230" t="n">
         <v>20369</v>
@@ -7068,7 +7068,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G231" t="n">
-        <v>9.73190975189209</v>
+        <v>9.73191070556641</v>
       </c>
       <c r="H231" t="n">
         <v>21922</v>
@@ -7097,7 +7097,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G232" t="n">
-        <v>9.87798023223877</v>
+        <v>9.8779821395874</v>
       </c>
       <c r="H232" t="n">
         <v>15426</v>
@@ -7126,7 +7126,7 @@
         <v>10.6421957015991</v>
       </c>
       <c r="G233" t="n">
-        <v>10.0057935714722</v>
+        <v>10.0057926177979</v>
       </c>
       <c r="H233" t="n">
         <v>21115</v>
@@ -7242,7 +7242,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G237" t="n">
-        <v>9.76842784881592</v>
+        <v>9.76842880249023</v>
       </c>
       <c r="H237" t="n">
         <v>21826</v>
@@ -7271,7 +7271,7 @@
         <v>10.4285745620728</v>
       </c>
       <c r="G238" t="n">
-        <v>9.80494594573975</v>
+        <v>9.80494403839111</v>
       </c>
       <c r="H238" t="n">
         <v>22184</v>
@@ -7300,7 +7300,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G239" t="n">
-        <v>10.0788278579712</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H239" t="n">
         <v>27320</v>
@@ -7416,7 +7416,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G243" t="n">
-        <v>9.87798023223877</v>
+        <v>9.8779821395874</v>
       </c>
       <c r="H243" t="n">
         <v>23214</v>
@@ -7445,7 +7445,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G244" t="n">
-        <v>10.2431554794312</v>
+        <v>10.2431564331055</v>
       </c>
       <c r="H244" t="n">
         <v>47303</v>
@@ -7474,7 +7474,7 @@
         <v>10.6033563613892</v>
       </c>
       <c r="G245" t="n">
-        <v>9.96927452087402</v>
+        <v>9.96927547454834</v>
       </c>
       <c r="H245" t="n">
         <v>41422</v>
@@ -7503,7 +7503,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G246" t="n">
-        <v>9.85972213745117</v>
+        <v>9.85972309112549</v>
       </c>
       <c r="H246" t="n">
         <v>19835</v>
@@ -7532,7 +7532,7 @@
         <v>10.4285745620728</v>
       </c>
       <c r="G247" t="n">
-        <v>9.80494594573975</v>
+        <v>9.80494403839111</v>
       </c>
       <c r="H247" t="n">
         <v>20516</v>
@@ -7590,7 +7590,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G249" t="n">
-        <v>9.95101642608643</v>
+        <v>9.95101547241211</v>
       </c>
       <c r="H249" t="n">
         <v>9574</v>
@@ -7619,7 +7619,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G250" t="n">
-        <v>10.0605688095093</v>
+        <v>10.060567855835</v>
       </c>
       <c r="H250" t="n">
         <v>11182</v>
@@ -7677,7 +7677,7 @@
         <v>11.2053775787354</v>
       </c>
       <c r="G252" t="n">
-        <v>10.5352964401245</v>
+        <v>10.5352954864502</v>
       </c>
       <c r="H252" t="n">
         <v>17671</v>
@@ -7735,7 +7735,7 @@
         <v>11.3413181304932</v>
       </c>
       <c r="G254" t="n">
-        <v>10.663106918335</v>
+        <v>10.6631059646606</v>
       </c>
       <c r="H254" t="n">
         <v>30537</v>
@@ -7764,7 +7764,7 @@
         <v>11.0111770629883</v>
       </c>
       <c r="G255" t="n">
-        <v>10.352707862854</v>
+        <v>10.3527097702026</v>
       </c>
       <c r="H255" t="n">
         <v>15461</v>
@@ -7793,7 +7793,7 @@
         <v>11.0694379806519</v>
       </c>
       <c r="G256" t="n">
-        <v>10.4074850082397</v>
+        <v>10.4074869155884</v>
       </c>
       <c r="H256" t="n">
         <v>16489</v>
@@ -7822,7 +7822,7 @@
         <v>11.0305967330933</v>
       </c>
       <c r="G257" t="n">
-        <v>10.3709669113159</v>
+        <v>10.3709678649902</v>
       </c>
       <c r="H257" t="n">
         <v>11495</v>
@@ -7851,7 +7851,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G258" t="n">
-        <v>10.2614145278931</v>
+        <v>10.2614154815674</v>
       </c>
       <c r="H258" t="n">
         <v>15387</v>
@@ -7880,7 +7880,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G259" t="n">
-        <v>9.95101642608643</v>
+        <v>9.95101547241211</v>
       </c>
       <c r="H259" t="n">
         <v>25241</v>
@@ -7909,7 +7909,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G260" t="n">
-        <v>9.91449928283691</v>
+        <v>9.91450023651123</v>
       </c>
       <c r="H260" t="n">
         <v>7038</v>
@@ -7967,7 +7967,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G262" t="n">
-        <v>10.0788278579712</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H262" t="n">
         <v>31468</v>
@@ -7996,7 +7996,7 @@
         <v>10.6616163253784</v>
       </c>
       <c r="G263" t="n">
-        <v>10.1156778335571</v>
+        <v>10.1156787872314</v>
       </c>
       <c r="H263" t="n">
         <v>15915</v>
@@ -8025,7 +8025,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G264" t="n">
-        <v>9.87614440917969</v>
+        <v>9.876145362854</v>
       </c>
       <c r="H264" t="n">
         <v>9400</v>
@@ -8083,7 +8083,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G266" t="n">
-        <v>9.8577184677124</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H266" t="n">
         <v>31281</v>
@@ -8112,7 +8112,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G267" t="n">
-        <v>9.8577184677124</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H267" t="n">
         <v>28019</v>
@@ -8141,7 +8141,7 @@
         <v>10.6616163253784</v>
       </c>
       <c r="G268" t="n">
-        <v>10.1156778335571</v>
+        <v>10.1156787872314</v>
       </c>
       <c r="H268" t="n">
         <v>15044</v>
@@ -8170,7 +8170,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G269" t="n">
-        <v>10.0788278579712</v>
+        <v>10.0788259506226</v>
       </c>
       <c r="H269" t="n">
         <v>9058</v>
@@ -8373,7 +8373,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G276" t="n">
-        <v>9.83929252624512</v>
+        <v>9.83929347991943</v>
       </c>
       <c r="H276" t="n">
         <v>16684</v>
@@ -8402,7 +8402,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G277" t="n">
-        <v>9.9867000579834</v>
+        <v>9.98669815063477</v>
       </c>
       <c r="H277" t="n">
         <v>28143</v>
@@ -8547,7 +8547,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G282" t="n">
-        <v>9.67346382141113</v>
+        <v>9.6734619140625</v>
       </c>
       <c r="H282" t="n">
         <v>19151</v>
@@ -8576,7 +8576,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G283" t="n">
-        <v>9.87614440917969</v>
+        <v>9.876145362854</v>
       </c>
       <c r="H283" t="n">
         <v>74802</v>
@@ -8663,7 +8663,7 @@
         <v>10.6421957015991</v>
       </c>
       <c r="G286" t="n">
-        <v>10.0972518920898</v>
+        <v>10.0972528457642</v>
       </c>
       <c r="H286" t="n">
         <v>15436</v>
@@ -8721,7 +8721,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G288" t="n">
-        <v>10.3367872238159</v>
+        <v>10.3367862701416</v>
       </c>
       <c r="H288" t="n">
         <v>11081</v>
@@ -8750,7 +8750,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3552112579346</v>
+        <v>10.3552122116089</v>
       </c>
       <c r="H289" t="n">
         <v>9843</v>
@@ -8779,7 +8779,7 @@
         <v>10.8752374649048</v>
       </c>
       <c r="G290" t="n">
-        <v>10.3183612823486</v>
+        <v>10.318359375</v>
       </c>
       <c r="H290" t="n">
         <v>20080</v>
@@ -8808,7 +8808,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G291" t="n">
-        <v>10.3367872238159</v>
+        <v>10.3367862701416</v>
       </c>
       <c r="H291" t="n">
         <v>11184</v>
@@ -8837,7 +8837,7 @@
         <v>10.8558168411255</v>
       </c>
       <c r="G292" t="n">
-        <v>10.299934387207</v>
+        <v>10.2999353408813</v>
       </c>
       <c r="H292" t="n">
         <v>10827</v>
@@ -8895,7 +8895,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G294" t="n">
-        <v>9.76559162139893</v>
+        <v>9.76559257507324</v>
       </c>
       <c r="H294" t="n">
         <v>19630</v>
@@ -8924,7 +8924,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G295" t="n">
-        <v>10.2446575164795</v>
+        <v>10.2446584701538</v>
       </c>
       <c r="H295" t="n">
         <v>20005</v>
@@ -8953,7 +8953,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G296" t="n">
-        <v>10.3367872238159</v>
+        <v>10.3367862701416</v>
       </c>
       <c r="H296" t="n">
         <v>17062</v>
@@ -8982,7 +8982,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G297" t="n">
-        <v>9.9682731628418</v>
+        <v>9.96827220916748</v>
       </c>
       <c r="H297" t="n">
         <v>9689</v>
@@ -9069,7 +9069,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G300" t="n">
-        <v>9.67346382141113</v>
+        <v>9.6734619140625</v>
       </c>
       <c r="H300" t="n">
         <v>46224</v>
@@ -9127,7 +9127,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G302" t="n">
-        <v>9.83929252624512</v>
+        <v>9.83929347991943</v>
       </c>
       <c r="H302" t="n">
         <v>1056</v>
@@ -9301,7 +9301,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G308" t="n">
-        <v>9.9867000579834</v>
+        <v>9.98669815063477</v>
       </c>
       <c r="H308" t="n">
         <v>5380</v>
@@ -9359,7 +9359,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G310" t="n">
-        <v>10.1893796920776</v>
+        <v>10.1893815994263</v>
       </c>
       <c r="H310" t="n">
         <v>28717</v>
@@ -9388,7 +9388,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G311" t="n">
-        <v>10.1893796920776</v>
+        <v>10.1893815994263</v>
       </c>
       <c r="H311" t="n">
         <v>15871</v>
@@ -9417,7 +9417,7 @@
         <v>10.8752374649048</v>
       </c>
       <c r="G312" t="n">
-        <v>10.3183612823486</v>
+        <v>10.318359375</v>
       </c>
       <c r="H312" t="n">
         <v>7644</v>
@@ -9562,7 +9562,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G317" t="n">
-        <v>11.9766693115234</v>
+        <v>11.9766683578491</v>
       </c>
       <c r="H317" t="n">
         <v>40875</v>
@@ -9591,7 +9591,7 @@
         <v>11.6908798217773</v>
       </c>
       <c r="G318" t="n">
-        <v>11.0922374725342</v>
+        <v>11.0922384262085</v>
       </c>
       <c r="H318" t="n">
         <v>45226</v>
@@ -9707,7 +9707,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G322" t="n">
-        <v>11.4607486724854</v>
+        <v>11.460750579834</v>
       </c>
       <c r="H322" t="n">
         <v>18075</v>
@@ -9881,7 +9881,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G328" t="n">
-        <v>12.0687971115112</v>
+        <v>12.0687952041626</v>
       </c>
       <c r="H328" t="n">
         <v>34385</v>
@@ -9910,7 +9910,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G329" t="n">
-        <v>12.0687971115112</v>
+        <v>12.0687952041626</v>
       </c>
       <c r="H329" t="n">
         <v>28558</v>
@@ -9939,7 +9939,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G330" t="n">
-        <v>12.1609258651733</v>
+        <v>12.160924911499</v>
       </c>
       <c r="H330" t="n">
         <v>146039</v>
@@ -9968,7 +9968,7 @@
         <v>13.0308637619019</v>
       </c>
       <c r="G331" t="n">
-        <v>12.3636064529419</v>
+        <v>12.3636054992676</v>
       </c>
       <c r="H331" t="n">
         <v>18642</v>
@@ -10026,7 +10026,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G333" t="n">
-        <v>12.1056480407715</v>
+        <v>12.1056489944458</v>
       </c>
       <c r="H333" t="n">
         <v>24851</v>
@@ -10258,7 +10258,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G341" t="n">
-        <v>11.4607486724854</v>
+        <v>11.460750579834</v>
       </c>
       <c r="H341" t="n">
         <v>96017</v>
@@ -10374,7 +10374,7 @@
         <v>12.681303024292</v>
       </c>
       <c r="G345" t="n">
-        <v>12.031946182251</v>
+        <v>12.0319452285767</v>
       </c>
       <c r="H345" t="n">
         <v>33851</v>
@@ -10432,7 +10432,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G347" t="n">
-        <v>12.0872201919556</v>
+        <v>12.0872211456299</v>
       </c>
       <c r="H347" t="n">
         <v>17512</v>
@@ -10461,7 +10461,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G348" t="n">
-        <v>12.1609258651733</v>
+        <v>12.160924911499</v>
       </c>
       <c r="H348" t="n">
         <v>164571</v>
@@ -10490,7 +10490,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G349" t="n">
-        <v>11.9766693115234</v>
+        <v>11.9766683578491</v>
       </c>
       <c r="H349" t="n">
         <v>13283</v>
@@ -10519,7 +10519,7 @@
         <v>12.7978229522705</v>
       </c>
       <c r="G350" t="n">
-        <v>12.1424989700317</v>
+        <v>12.1424980163574</v>
       </c>
       <c r="H350" t="n">
         <v>82487</v>
@@ -10548,7 +10548,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G351" t="n">
-        <v>12.4373092651367</v>
+        <v>12.437310218811</v>
       </c>
       <c r="H351" t="n">
         <v>76761</v>
@@ -10577,7 +10577,7 @@
         <v>13.2833251953125</v>
       </c>
       <c r="G352" t="n">
-        <v>12.6031398773193</v>
+        <v>12.6031408309937</v>
       </c>
       <c r="H352" t="n">
         <v>22421</v>
@@ -10606,7 +10606,7 @@
         <v>13.5940456390381</v>
       </c>
       <c r="G353" t="n">
-        <v>12.8979511260986</v>
+        <v>12.8979501724243</v>
       </c>
       <c r="H353" t="n">
         <v>79481</v>
@@ -10664,7 +10664,7 @@
         <v>13.9824476242065</v>
       </c>
       <c r="G355" t="n">
-        <v>13.2664642333984</v>
+        <v>13.2664632797241</v>
       </c>
       <c r="H355" t="n">
         <v>22333</v>
@@ -10693,7 +10693,7 @@
         <v>14.1378078460693</v>
       </c>
       <c r="G356" t="n">
-        <v>13.4138689041138</v>
+        <v>13.4138679504395</v>
       </c>
       <c r="H356" t="n">
         <v>31972</v>
@@ -10722,7 +10722,7 @@
         <v>14.7204103469849</v>
       </c>
       <c r="G357" t="n">
-        <v>13.9666395187378</v>
+        <v>13.9666376113892</v>
       </c>
       <c r="H357" t="n">
         <v>51342</v>
@@ -10751,7 +10751,7 @@
         <v>14.1378078460693</v>
       </c>
       <c r="G358" t="n">
-        <v>13.4138689041138</v>
+        <v>13.4138679504395</v>
       </c>
       <c r="H358" t="n">
         <v>70279</v>
@@ -10838,7 +10838,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G361" t="n">
-        <v>13.0269289016724</v>
+        <v>13.026930809021</v>
       </c>
       <c r="H361" t="n">
         <v>48913</v>
@@ -10867,7 +10867,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G362" t="n">
-        <v>13.0269289016724</v>
+        <v>13.026930809021</v>
       </c>
       <c r="H362" t="n">
         <v>29032</v>
@@ -10925,7 +10925,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G364" t="n">
-        <v>12.2714786529541</v>
+        <v>12.2714796066284</v>
       </c>
       <c r="H364" t="n">
         <v>81687</v>
@@ -10954,7 +10954,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G365" t="n">
-        <v>12.2162008285522</v>
+        <v>12.2162017822266</v>
       </c>
       <c r="H365" t="n">
         <v>190840</v>
@@ -10983,7 +10983,7 @@
         <v>12.9920244216919</v>
       </c>
       <c r="G366" t="n">
-        <v>12.326756477356</v>
+        <v>12.3267545700073</v>
       </c>
       <c r="H366" t="n">
         <v>73862</v>
@@ -11012,7 +11012,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G367" t="n">
-        <v>12.1609258651733</v>
+        <v>12.160924911499</v>
       </c>
       <c r="H367" t="n">
         <v>62783</v>
@@ -11041,7 +11041,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G368" t="n">
-        <v>12.0872201919556</v>
+        <v>12.0872211456299</v>
       </c>
       <c r="H368" t="n">
         <v>34922</v>
@@ -11070,7 +11070,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G369" t="n">
-        <v>12.1056480407715</v>
+        <v>12.1056489944458</v>
       </c>
       <c r="H369" t="n">
         <v>42419</v>
@@ -11128,7 +11128,7 @@
         <v>12.8560838699341</v>
       </c>
       <c r="G371" t="n">
-        <v>12.1977758407593</v>
+        <v>12.1977767944336</v>
       </c>
       <c r="H371" t="n">
         <v>17051</v>
@@ -11157,7 +11157,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G372" t="n">
-        <v>12.4373092651367</v>
+        <v>12.437310218811</v>
       </c>
       <c r="H372" t="n">
         <v>84706</v>
@@ -11215,7 +11215,7 @@
         <v>14.5650501251221</v>
       </c>
       <c r="G374" t="n">
-        <v>13.8192338943481</v>
+        <v>13.8192329406738</v>
       </c>
       <c r="H374" t="n">
         <v>120229</v>
@@ -11244,7 +11244,7 @@
         <v>14.0407075881958</v>
       </c>
       <c r="G375" t="n">
-        <v>13.3217401504517</v>
+        <v>13.321741104126</v>
       </c>
       <c r="H375" t="n">
         <v>115548</v>
@@ -11273,7 +11273,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G376" t="n">
-        <v>13.0822076797485</v>
+        <v>13.0822086334229</v>
       </c>
       <c r="H376" t="n">
         <v>70558</v>
@@ -11360,7 +11360,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G379" t="n">
-        <v>12.4373092651367</v>
+        <v>12.437310218811</v>
       </c>
       <c r="H379" t="n">
         <v>16597</v>
@@ -11389,7 +11389,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G380" t="n">
-        <v>12.4741611480713</v>
+        <v>12.474160194397</v>
       </c>
       <c r="H380" t="n">
         <v>30065</v>
@@ -11418,7 +11418,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G381" t="n">
-        <v>12.2899036407471</v>
+        <v>12.2899055480957</v>
       </c>
       <c r="H381" t="n">
         <v>22165</v>
@@ -11447,7 +11447,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G382" t="n">
-        <v>12.2899036407471</v>
+        <v>12.2899055480957</v>
       </c>
       <c r="H382" t="n">
         <v>16881</v>
@@ -11476,7 +11476,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G383" t="n">
-        <v>12.4373092651367</v>
+        <v>12.437310218811</v>
       </c>
       <c r="H383" t="n">
         <v>19371</v>
@@ -11505,7 +11505,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G384" t="n">
-        <v>12.2162008285522</v>
+        <v>12.2162017822266</v>
       </c>
       <c r="H384" t="n">
         <v>8234</v>
@@ -11563,7 +11563,7 @@
         <v>13.4192657470703</v>
       </c>
       <c r="G386" t="n">
-        <v>12.732120513916</v>
+        <v>12.7321186065674</v>
       </c>
       <c r="H386" t="n">
         <v>34541</v>
@@ -11592,7 +11592,7 @@
         <v>13.4969463348389</v>
       </c>
       <c r="G387" t="n">
-        <v>12.8058233261108</v>
+        <v>12.8058223724365</v>
       </c>
       <c r="H387" t="n">
         <v>42243</v>
@@ -11621,7 +11621,7 @@
         <v>13.7105674743652</v>
       </c>
       <c r="G388" t="n">
-        <v>13.008505821228</v>
+        <v>13.0085067749023</v>
       </c>
       <c r="H388" t="n">
         <v>24282</v>
@@ -11679,7 +11679,7 @@
         <v>13.6911468505859</v>
       </c>
       <c r="G390" t="n">
-        <v>12.9900798797607</v>
+        <v>12.9900789260864</v>
       </c>
       <c r="H390" t="n">
         <v>45738</v>
@@ -11708,7 +11708,7 @@
         <v>13.9630270004272</v>
       </c>
       <c r="G391" t="n">
-        <v>13.2480363845825</v>
+        <v>13.2480373382568</v>
       </c>
       <c r="H391" t="n">
         <v>49918</v>
@@ -11737,7 +11737,7 @@
         <v>13.9630270004272</v>
       </c>
       <c r="G392" t="n">
-        <v>13.2480363845825</v>
+        <v>13.2480373382568</v>
       </c>
       <c r="H392" t="n">
         <v>26496</v>
@@ -11766,7 +11766,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G393" t="n">
-        <v>13.0822076797485</v>
+        <v>13.0822086334229</v>
       </c>
       <c r="H393" t="n">
         <v>14493</v>
@@ -11940,7 +11940,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G399" t="n">
-        <v>12.1056480407715</v>
+        <v>12.1056489944458</v>
       </c>
       <c r="H399" t="n">
         <v>155352</v>
@@ -11969,7 +11969,7 @@
         <v>13.0502843856812</v>
       </c>
       <c r="G400" t="n">
-        <v>12.3820333480835</v>
+        <v>12.3820314407349</v>
       </c>
       <c r="H400" t="n">
         <v>35674</v>
@@ -12056,7 +12056,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G403" t="n">
-        <v>12.4373092651367</v>
+        <v>12.437310218811</v>
       </c>
       <c r="H403" t="n">
         <v>10747</v>
@@ -12114,7 +12114,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G405" t="n">
-        <v>12.1609258651733</v>
+        <v>12.160924911499</v>
       </c>
       <c r="H405" t="n">
         <v>14366</v>
@@ -12143,7 +12143,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G406" t="n">
-        <v>12.0687971115112</v>
+        <v>12.0687952041626</v>
       </c>
       <c r="H406" t="n">
         <v>34716</v>
@@ -12172,7 +12172,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G407" t="n">
-        <v>12.0872201919556</v>
+        <v>12.0872211456299</v>
       </c>
       <c r="H407" t="n">
         <v>16935</v>
@@ -12259,7 +12259,7 @@
         <v>12.4094219207764</v>
       </c>
       <c r="G410" t="n">
-        <v>11.7739868164062</v>
+        <v>11.7739849090576</v>
       </c>
       <c r="H410" t="n">
         <v>15233</v>
@@ -12288,7 +12288,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G411" t="n">
-        <v>11.7002830505371</v>
+        <v>11.7002849578857</v>
       </c>
       <c r="H411" t="n">
         <v>14490</v>
@@ -12317,7 +12317,7 @@
         <v>11.8268203735352</v>
       </c>
       <c r="G412" t="n">
-        <v>11.2212181091309</v>
+        <v>11.2212171554565</v>
       </c>
       <c r="H412" t="n">
         <v>26248</v>
@@ -12346,7 +12346,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G413" t="n">
-        <v>10.9448308944702</v>
+        <v>10.9448318481445</v>
       </c>
       <c r="H413" t="n">
         <v>163465</v>
@@ -12375,7 +12375,7 @@
         <v>11.6131992340088</v>
       </c>
       <c r="G414" t="n">
-        <v>11.0185356140137</v>
+        <v>11.018533706665</v>
       </c>
       <c r="H414" t="n">
         <v>45535</v>
@@ -12404,7 +12404,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G415" t="n">
-        <v>10.9632568359375</v>
+        <v>10.9632587432861</v>
       </c>
       <c r="H415" t="n">
         <v>19309</v>
@@ -12462,7 +12462,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G417" t="n">
-        <v>10.9632568359375</v>
+        <v>10.9632587432861</v>
       </c>
       <c r="H417" t="n">
         <v>37373</v>
@@ -12520,7 +12520,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G419" t="n">
-        <v>10.9448308944702</v>
+        <v>10.9448318481445</v>
       </c>
       <c r="H419" t="n">
         <v>37390</v>
@@ -12607,7 +12607,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G422" t="n">
-        <v>11.0553855895996</v>
+        <v>11.0553874969482</v>
       </c>
       <c r="H422" t="n">
         <v>13462</v>
@@ -12868,7 +12868,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G431" t="n">
-        <v>11.0369606018066</v>
+        <v>11.0369596481323</v>
       </c>
       <c r="H431" t="n">
         <v>33933</v>
@@ -12897,7 +12897,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G432" t="n">
-        <v>10.0788278579712</v>
+        <v>10.0788259506226</v>
       </c>
       <c r="H432" t="n">
         <v>74937</v>
@@ -12984,7 +12984,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G435" t="n">
-        <v>10.2446575164795</v>
+        <v>10.2446584701538</v>
       </c>
       <c r="H435" t="n">
         <v>43976</v>
@@ -13013,7 +13013,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G436" t="n">
-        <v>10.2446575164795</v>
+        <v>10.2446584701538</v>
       </c>
       <c r="H436" t="n">
         <v>63148</v>
@@ -13042,7 +13042,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G437" t="n">
-        <v>9.9867000579834</v>
+        <v>9.98669815063477</v>
       </c>
       <c r="H437" t="n">
         <v>35216</v>
@@ -13071,7 +13071,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G438" t="n">
-        <v>10.3552112579346</v>
+        <v>10.3552122116089</v>
       </c>
       <c r="H438" t="n">
         <v>41072</v>
@@ -13100,7 +13100,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G439" t="n">
-        <v>10.3367872238159</v>
+        <v>10.3367862701416</v>
       </c>
       <c r="H439" t="n">
         <v>50080</v>
@@ -13158,7 +13158,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G441" t="n">
-        <v>10.0788278579712</v>
+        <v>10.0788259506226</v>
       </c>
       <c r="H441" t="n">
         <v>50243</v>
@@ -13187,7 +13187,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G442" t="n">
-        <v>9.67346382141113</v>
+        <v>9.6734619140625</v>
       </c>
       <c r="H442" t="n">
         <v>61109</v>
@@ -13332,7 +13332,7 @@
         <v>9.12743091583252</v>
       </c>
       <c r="G447" t="n">
-        <v>8.66005325317383</v>
+        <v>8.66005420684814</v>
       </c>
       <c r="H447" t="n">
         <v>68799</v>
@@ -13361,7 +13361,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G448" t="n">
-        <v>9.8577184677124</v>
+        <v>9.85772037506104</v>
       </c>
       <c r="H448" t="n">
         <v>42752</v>
@@ -13390,7 +13390,7 @@
         <v>9.22453117370605</v>
       </c>
       <c r="G449" t="n">
-        <v>8.75218105316162</v>
+        <v>8.7521800994873</v>
       </c>
       <c r="H449" t="n">
         <v>29663</v>
@@ -13448,7 +13448,7 @@
         <v>8.6322193145752</v>
       </c>
       <c r="G451" t="n">
-        <v>8.19019985198975</v>
+        <v>8.19019889831543</v>
       </c>
       <c r="H451" t="n">
         <v>140854</v>
@@ -13477,7 +13477,7 @@
         <v>8.58366870880127</v>
       </c>
       <c r="G452" t="n">
-        <v>8.14413261413574</v>
+        <v>8.14413356781006</v>
       </c>
       <c r="H452" t="n">
         <v>27504</v>
@@ -13506,7 +13506,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G453" t="n">
-        <v>8.47579574584961</v>
+        <v>8.47579479217529</v>
       </c>
       <c r="H453" t="n">
         <v>47454</v>
@@ -13564,7 +13564,7 @@
         <v>10.0984344482422</v>
       </c>
       <c r="G455" t="n">
-        <v>9.58133602142334</v>
+        <v>9.58133506774902</v>
       </c>
       <c r="H455" t="n">
         <v>36655</v>
@@ -13593,7 +13593,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G456" t="n">
-        <v>11.7002830505371</v>
+        <v>11.7002849578857</v>
       </c>
       <c r="H456" t="n">
         <v>57587</v>
@@ -13622,7 +13622,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G457" t="n">
-        <v>11.0369606018066</v>
+        <v>11.0369596481323</v>
       </c>
       <c r="H457" t="n">
         <v>57173</v>
@@ -13651,7 +13651,7 @@
         <v>11.2247982025146</v>
       </c>
       <c r="G458" t="n">
-        <v>10.6500215530396</v>
+        <v>10.6500225067139</v>
       </c>
       <c r="H458" t="n">
         <v>48513</v>
@@ -13680,7 +13680,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G459" t="n">
-        <v>10.0788278579712</v>
+        <v>10.0788259506226</v>
       </c>
       <c r="H459" t="n">
         <v>35880</v>
@@ -13738,7 +13738,7 @@
         <v>10.234375</v>
       </c>
       <c r="G461" t="n">
-        <v>9.71031379699707</v>
+        <v>9.71031475067139</v>
       </c>
       <c r="H461" t="n">
         <v>36815</v>
@@ -13796,7 +13796,7 @@
         <v>10.7781372070312</v>
       </c>
       <c r="G463" t="n">
-        <v>10.2262315750122</v>
+        <v>10.2262325286865</v>
       </c>
       <c r="H463" t="n">
         <v>35295</v>
@@ -13854,7 +13854,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G465" t="n">
-        <v>9.76559162139893</v>
+        <v>9.76559257507324</v>
       </c>
       <c r="H465" t="n">
         <v>19814</v>
@@ -13912,7 +13912,7 @@
         <v>10.1761140823364</v>
       </c>
       <c r="G467" t="n">
-        <v>9.65503692626953</v>
+        <v>9.65503597259521</v>
       </c>
       <c r="H467" t="n">
         <v>21752</v>
@@ -13941,7 +13941,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G468" t="n">
-        <v>9.94984817504883</v>
+        <v>9.94984722137451</v>
       </c>
       <c r="H468" t="n">
         <v>26515</v>
@@ -13999,7 +13999,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G470" t="n">
-        <v>11.0553855895996</v>
+        <v>11.0553874969482</v>
       </c>
       <c r="H470" t="n">
         <v>18460</v>
@@ -14028,7 +14028,7 @@
         <v>11.8268203735352</v>
       </c>
       <c r="G471" t="n">
-        <v>11.2212181091309</v>
+        <v>11.2212171554565</v>
       </c>
       <c r="H471" t="n">
         <v>49981</v>
@@ -14057,7 +14057,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G472" t="n">
-        <v>11.0553855895996</v>
+        <v>11.0553874969482</v>
       </c>
       <c r="H472" t="n">
         <v>82131</v>
@@ -14086,7 +14086,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G473" t="n">
-        <v>11.7002830505371</v>
+        <v>11.7002849578857</v>
       </c>
       <c r="H473" t="n">
         <v>33615</v>
@@ -14144,7 +14144,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G475" t="n">
-        <v>11.7924108505249</v>
+        <v>11.7924118041992</v>
       </c>
       <c r="H475" t="n">
         <v>26161</v>
@@ -14202,7 +14202,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G477" t="n">
-        <v>12.4741611480713</v>
+        <v>12.474160194397</v>
       </c>
       <c r="H477" t="n">
         <v>17487</v>
@@ -14231,7 +14231,7 @@
         <v>13.2056446075439</v>
       </c>
       <c r="G478" t="n">
-        <v>12.5294380187988</v>
+        <v>12.5294370651245</v>
       </c>
       <c r="H478" t="n">
         <v>22130</v>
@@ -14289,7 +14289,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G480" t="n">
-        <v>12.2714786529541</v>
+        <v>12.2714796066284</v>
       </c>
       <c r="H480" t="n">
         <v>20669</v>
@@ -14318,7 +14318,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G481" t="n">
-        <v>11.9766693115234</v>
+        <v>11.9766683578491</v>
       </c>
       <c r="H481" t="n">
         <v>21030</v>
@@ -14347,7 +14347,7 @@
         <v>12.3123216629028</v>
       </c>
       <c r="G482" t="n">
-        <v>11.6818571090698</v>
+        <v>11.6818580627441</v>
       </c>
       <c r="H482" t="n">
         <v>22527</v>
@@ -14376,7 +14376,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G483" t="n">
-        <v>11.7924108505249</v>
+        <v>11.7924118041992</v>
       </c>
       <c r="H483" t="n">
         <v>10814</v>
@@ -14434,7 +14434,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G485" t="n">
-        <v>11.7002830505371</v>
+        <v>11.7002849578857</v>
       </c>
       <c r="H485" t="n">
         <v>50887</v>
@@ -14463,7 +14463,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G486" t="n">
-        <v>12.4373092651367</v>
+        <v>12.437310218811</v>
       </c>
       <c r="H486" t="n">
         <v>34820</v>
@@ -14492,7 +14492,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G487" t="n">
-        <v>12.4373092651367</v>
+        <v>12.437310218811</v>
       </c>
       <c r="H487" t="n">
         <v>22322</v>
@@ -14521,7 +14521,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G488" t="n">
-        <v>13.0822076797485</v>
+        <v>13.0822086334229</v>
       </c>
       <c r="H488" t="n">
         <v>24122</v>
@@ -14579,7 +14579,7 @@
         <v>14.1183881759644</v>
       </c>
       <c r="G490" t="n">
-        <v>13.3954439163208</v>
+        <v>13.3954429626465</v>
       </c>
       <c r="H490" t="n">
         <v>42920</v>
@@ -14608,7 +14608,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G491" t="n">
-        <v>13.0269289016724</v>
+        <v>13.026930809021</v>
       </c>
       <c r="H491" t="n">
         <v>30641</v>
@@ -14637,7 +14637,7 @@
         <v>14.2931690216064</v>
       </c>
       <c r="G492" t="n">
-        <v>13.5612735748291</v>
+        <v>13.5612745285034</v>
       </c>
       <c r="H492" t="n">
         <v>30266</v>
@@ -14724,7 +14724,7 @@
         <v>15.633152961731</v>
       </c>
       <c r="G495" t="n">
-        <v>14.8326425552368</v>
+        <v>14.8326435089111</v>
       </c>
       <c r="H495" t="n">
         <v>23740</v>
@@ -14753,7 +14753,7 @@
         <v>14.9146108627319</v>
       </c>
       <c r="G496" t="n">
-        <v>14.1508951187134</v>
+        <v>14.1508941650391</v>
       </c>
       <c r="H496" t="n">
         <v>48940</v>
@@ -14782,7 +14782,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G497" t="n">
-        <v>15.182731628418</v>
+        <v>15.1827297210693</v>
       </c>
       <c r="H497" t="n">
         <v>39377</v>
@@ -14869,7 +14869,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G500" t="n">
-        <v>15.293285369873</v>
+        <v>15.2932844161987</v>
       </c>
       <c r="H500" t="n">
         <v>75736</v>
@@ -14927,7 +14927,7 @@
         <v>15.3030118942261</v>
       </c>
       <c r="G502" t="n">
-        <v>14.5194082260132</v>
+        <v>14.5194072723389</v>
       </c>
       <c r="H502" t="n">
         <v>62720</v>
@@ -15101,7 +15101,7 @@
         <v>14.4679489135742</v>
       </c>
       <c r="G508" t="n">
-        <v>13.7271041870117</v>
+        <v>13.7271032333374</v>
       </c>
       <c r="H508" t="n">
         <v>20871</v>
@@ -15159,7 +15159,7 @@
         <v>14.7398300170898</v>
       </c>
       <c r="G510" t="n">
-        <v>13.9850635528564</v>
+        <v>13.9850625991821</v>
       </c>
       <c r="H510" t="n">
         <v>31610</v>
@@ -15188,7 +15188,7 @@
         <v>14.9922914505005</v>
       </c>
       <c r="G511" t="n">
-        <v>14.2245988845825</v>
+        <v>14.2245979309082</v>
       </c>
       <c r="H511" t="n">
         <v>23708</v>
@@ -15275,7 +15275,7 @@
         <v>15.128231048584</v>
       </c>
       <c r="G514" t="n">
-        <v>14.4609594345093</v>
+        <v>14.460958480835</v>
       </c>
       <c r="H514" t="n">
         <v>34556</v>
@@ -15333,7 +15333,7 @@
         <v>15.4777927398682</v>
       </c>
       <c r="G516" t="n">
-        <v>14.7951011657715</v>
+        <v>14.7951030731201</v>
       </c>
       <c r="H516" t="n">
         <v>13193</v>
@@ -15449,7 +15449,7 @@
         <v>15.8661937713623</v>
       </c>
       <c r="G520" t="n">
-        <v>15.16637134552</v>
+        <v>15.1663722991943</v>
       </c>
       <c r="H520" t="n">
         <v>26150</v>
@@ -15507,7 +15507,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G522" t="n">
-        <v>15.129246711731</v>
+        <v>15.1292457580566</v>
       </c>
       <c r="H522" t="n">
         <v>16871</v>
@@ -15623,7 +15623,7 @@
         <v>15.1864919662476</v>
       </c>
       <c r="G526" t="n">
-        <v>14.5166501998901</v>
+        <v>14.5166511535645</v>
       </c>
       <c r="H526" t="n">
         <v>47887</v>
@@ -15681,7 +15681,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G528" t="n">
-        <v>14.9807357788086</v>
+        <v>14.9807367324829</v>
       </c>
       <c r="H528" t="n">
         <v>11405</v>
@@ -15710,7 +15710,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G529" t="n">
-        <v>14.813666343689</v>
+        <v>14.8136653900146</v>
       </c>
       <c r="H529" t="n">
         <v>6461</v>
@@ -15739,7 +15739,7 @@
         <v>15.2253322601318</v>
       </c>
       <c r="G530" t="n">
-        <v>14.5537776947021</v>
+        <v>14.5537767410278</v>
       </c>
       <c r="H530" t="n">
         <v>10013</v>
@@ -15768,7 +15768,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G531" t="n">
-        <v>15.0364294052124</v>
+        <v>15.0364284515381</v>
       </c>
       <c r="H531" t="n">
         <v>10866</v>
@@ -15797,7 +15797,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G532" t="n">
-        <v>14.8322296142578</v>
+        <v>14.8322286605835</v>
       </c>
       <c r="H532" t="n">
         <v>14290</v>
@@ -15826,7 +15826,7 @@
         <v>15.613733291626</v>
       </c>
       <c r="G533" t="n">
-        <v>14.9250469207764</v>
+        <v>14.9250459671021</v>
       </c>
       <c r="H533" t="n">
         <v>26443</v>
@@ -15855,7 +15855,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G534" t="n">
-        <v>15.129246711731</v>
+        <v>15.1292457580566</v>
       </c>
       <c r="H534" t="n">
         <v>13313</v>
@@ -15884,7 +15884,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G535" t="n">
-        <v>15.129246711731</v>
+        <v>15.1292457580566</v>
       </c>
       <c r="H535" t="n">
         <v>23772</v>
@@ -15971,7 +15971,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G538" t="n">
-        <v>14.813666343689</v>
+        <v>14.8136653900146</v>
       </c>
       <c r="H538" t="n">
         <v>25791</v>
@@ -16145,7 +16145,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G544" t="n">
-        <v>14.8322296142578</v>
+        <v>14.8322286605835</v>
       </c>
       <c r="H544" t="n">
         <v>20980</v>
@@ -16174,7 +16174,7 @@
         <v>16.1769142150879</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4633865356445</v>
+        <v>15.4633855819702</v>
       </c>
       <c r="H545" t="n">
         <v>51347</v>
@@ -16203,7 +16203,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G546" t="n">
-        <v>16.0574169158936</v>
+        <v>16.0574188232422</v>
       </c>
       <c r="H546" t="n">
         <v>61019</v>
@@ -16232,7 +16232,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G547" t="n">
-        <v>16.8556518554688</v>
+        <v>16.8556537628174</v>
       </c>
       <c r="H547" t="n">
         <v>42324</v>
@@ -16377,7 +16377,7 @@
         <v>18.1189212799072</v>
       </c>
       <c r="G552" t="n">
-        <v>17.3197383880615</v>
+        <v>17.3197364807129</v>
       </c>
       <c r="H552" t="n">
         <v>10320</v>
@@ -16464,7 +16464,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G555" t="n">
-        <v>17.6724414825439</v>
+        <v>17.6724452972412</v>
       </c>
       <c r="H555" t="n">
         <v>24199</v>
@@ -16493,7 +16493,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G556" t="n">
-        <v>17.8952045440674</v>
+        <v>17.895206451416</v>
       </c>
       <c r="H556" t="n">
         <v>21308</v>
@@ -16522,7 +16522,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G557" t="n">
-        <v>17.7652606964111</v>
+        <v>17.7652587890625</v>
       </c>
       <c r="H557" t="n">
         <v>17872</v>
@@ -16580,7 +16580,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G559" t="n">
-        <v>18.1922225952148</v>
+        <v>18.1922245025635</v>
       </c>
       <c r="H559" t="n">
         <v>42955</v>
@@ -16638,7 +16638,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G561" t="n">
-        <v>17.4125537872314</v>
+        <v>17.4125556945801</v>
       </c>
       <c r="H561" t="n">
         <v>39089</v>
@@ -16667,7 +16667,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G562" t="n">
-        <v>17.8766422271729</v>
+        <v>17.8766441345215</v>
       </c>
       <c r="H562" t="n">
         <v>12841</v>
@@ -16696,7 +16696,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G563" t="n">
-        <v>18.5634918212891</v>
+        <v>18.5634937286377</v>
       </c>
       <c r="H563" t="n">
         <v>83303</v>
@@ -16754,7 +16754,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G565" t="n">
-        <v>18.2107849121094</v>
+        <v>18.2107830047607</v>
       </c>
       <c r="H565" t="n">
         <v>31275</v>
@@ -16783,7 +16783,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G566" t="n">
-        <v>18.5634918212891</v>
+        <v>18.5634937286377</v>
       </c>
       <c r="H566" t="n">
         <v>84063</v>
@@ -16812,7 +16812,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G567" t="n">
-        <v>17.6724414825439</v>
+        <v>17.6724452972412</v>
       </c>
       <c r="H567" t="n">
         <v>19901</v>
@@ -16870,7 +16870,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G569" t="n">
-        <v>17.9137706756592</v>
+        <v>17.9137725830078</v>
       </c>
       <c r="H569" t="n">
         <v>127033</v>
@@ -16928,7 +16928,7 @@
         <v>18.6626834869385</v>
       </c>
       <c r="G571" t="n">
-        <v>17.8395156860352</v>
+        <v>17.8395137786865</v>
       </c>
       <c r="H571" t="n">
         <v>77837</v>
@@ -16986,7 +16986,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G573" t="n">
-        <v>17.6910057067871</v>
+        <v>17.6910076141357</v>
       </c>
       <c r="H573" t="n">
         <v>109043</v>
@@ -17044,7 +17044,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G575" t="n">
-        <v>16.5586318969727</v>
+        <v>16.5586338043213</v>
       </c>
       <c r="H575" t="n">
         <v>198911</v>
@@ -17073,7 +17073,7 @@
         <v>16.4487953186035</v>
       </c>
       <c r="G576" t="n">
-        <v>15.7232761383057</v>
+        <v>15.72327709198</v>
       </c>
       <c r="H576" t="n">
         <v>46607</v>
@@ -17102,7 +17102,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G577" t="n">
-        <v>16.3544330596924</v>
+        <v>16.354434967041</v>
       </c>
       <c r="H577" t="n">
         <v>50642</v>
@@ -17131,7 +17131,7 @@
         <v>16.5847358703613</v>
       </c>
       <c r="G578" t="n">
-        <v>15.8532209396362</v>
+        <v>15.8532190322876</v>
       </c>
       <c r="H578" t="n">
         <v>124946</v>
@@ -17160,7 +17160,7 @@
         <v>15.9827136993408</v>
       </c>
       <c r="G579" t="n">
-        <v>15.2777519226074</v>
+        <v>15.2777528762817</v>
       </c>
       <c r="H579" t="n">
         <v>42599</v>
@@ -17189,7 +17189,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G580" t="n">
-        <v>15.6675853729248</v>
+        <v>15.6675844192505</v>
       </c>
       <c r="H580" t="n">
         <v>70564</v>
@@ -17247,7 +17247,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G582" t="n">
-        <v>16.4843807220459</v>
+        <v>16.4843826293945</v>
       </c>
       <c r="H582" t="n">
         <v>52124</v>
@@ -17305,7 +17305,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G584" t="n">
-        <v>16.317310333252</v>
+        <v>16.3173122406006</v>
       </c>
       <c r="H584" t="n">
         <v>20341</v>
@@ -17334,7 +17334,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G585" t="n">
-        <v>16.1687984466553</v>
+        <v>16.1688022613525</v>
       </c>
       <c r="H585" t="n">
         <v>23602</v>
@@ -17421,7 +17421,7 @@
         <v>16.9731388092041</v>
       </c>
       <c r="G588" t="n">
-        <v>16.2244930267334</v>
+        <v>16.2244892120361</v>
       </c>
       <c r="H588" t="n">
         <v>17051</v>
@@ -17450,7 +17450,7 @@
         <v>17.1479187011719</v>
       </c>
       <c r="G589" t="n">
-        <v>16.3915615081787</v>
+        <v>16.3915634155273</v>
       </c>
       <c r="H589" t="n">
         <v>20367</v>
@@ -17537,7 +17537,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G592" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H592" t="n">
         <v>9975</v>
@@ -17595,7 +17595,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G594" t="n">
-        <v>16.5586318969727</v>
+        <v>16.5586338043213</v>
       </c>
       <c r="H594" t="n">
         <v>13801</v>
@@ -17653,7 +17653,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G596" t="n">
-        <v>16.521505355835</v>
+        <v>16.5215072631836</v>
       </c>
       <c r="H596" t="n">
         <v>20661</v>
@@ -17682,7 +17682,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G597" t="n">
-        <v>16.5029430389404</v>
+        <v>16.5029449462891</v>
       </c>
       <c r="H597" t="n">
         <v>81026</v>
@@ -17711,7 +17711,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G598" t="n">
-        <v>16.6514549255371</v>
+        <v>16.6514530181885</v>
       </c>
       <c r="H598" t="n">
         <v>15409</v>
@@ -17769,7 +17769,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G600" t="n">
-        <v>16.4843807220459</v>
+        <v>16.4843826293945</v>
       </c>
       <c r="H600" t="n">
         <v>11491</v>
@@ -17798,7 +17798,7 @@
         <v>17.4586391448975</v>
       </c>
       <c r="G601" t="n">
-        <v>16.6885776519775</v>
+        <v>16.6885795593262</v>
       </c>
       <c r="H601" t="n">
         <v>261860</v>
@@ -17943,7 +17943,7 @@
         <v>15.2641716003418</v>
       </c>
       <c r="G606" t="n">
-        <v>14.5909032821655</v>
+        <v>14.5909042358398</v>
       </c>
       <c r="H606" t="n">
         <v>36919</v>
@@ -18059,7 +18059,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G610" t="n">
-        <v>14.9807357788086</v>
+        <v>14.9807367324829</v>
       </c>
       <c r="H610" t="n">
         <v>37926</v>
@@ -18088,7 +18088,7 @@
         <v>15.108811378479</v>
       </c>
       <c r="G611" t="n">
-        <v>14.4423971176147</v>
+        <v>14.4423952102661</v>
       </c>
       <c r="H611" t="n">
         <v>103659</v>
@@ -18117,7 +18117,7 @@
         <v>18.0024013519287</v>
       </c>
       <c r="G612" t="n">
-        <v>17.2083568572998</v>
+        <v>17.2083587646484</v>
       </c>
       <c r="H612" t="n">
         <v>158473</v>
@@ -18146,7 +18146,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G613" t="n">
-        <v>16.4101257324219</v>
+        <v>16.4101276397705</v>
       </c>
       <c r="H613" t="n">
         <v>64161</v>
@@ -18175,7 +18175,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G614" t="n">
-        <v>16.4101257324219</v>
+        <v>16.4101276397705</v>
       </c>
       <c r="H614" t="n">
         <v>66121</v>
@@ -18204,7 +18204,7 @@
         <v>16.5847358703613</v>
       </c>
       <c r="G615" t="n">
-        <v>15.8532209396362</v>
+        <v>15.8532190322876</v>
       </c>
       <c r="H615" t="n">
         <v>42220</v>
@@ -18233,7 +18233,7 @@
         <v>16.2351741790771</v>
       </c>
       <c r="G616" t="n">
-        <v>15.5190773010254</v>
+        <v>15.5190763473511</v>
       </c>
       <c r="H616" t="n">
         <v>54428</v>
@@ -18262,7 +18262,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G617" t="n">
-        <v>16.1687984466553</v>
+        <v>16.1688022613525</v>
       </c>
       <c r="H617" t="n">
         <v>47046</v>
@@ -18291,7 +18291,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G618" t="n">
-        <v>15.7789669036865</v>
+        <v>15.7789659500122</v>
       </c>
       <c r="H618" t="n">
         <v>15816</v>
@@ -18320,7 +18320,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G619" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H619" t="n">
         <v>56147</v>
@@ -18378,7 +18378,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G621" t="n">
-        <v>16.521505355835</v>
+        <v>16.5215072631836</v>
       </c>
       <c r="H621" t="n">
         <v>36994</v>
@@ -18407,7 +18407,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G622" t="n">
-        <v>16.4843807220459</v>
+        <v>16.4843826293945</v>
       </c>
       <c r="H622" t="n">
         <v>47450</v>
@@ -18494,7 +18494,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G625" t="n">
-        <v>16.8556518554688</v>
+        <v>16.8556537628174</v>
       </c>
       <c r="H625" t="n">
         <v>25343</v>
@@ -18552,7 +18552,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G627" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H627" t="n">
         <v>49894</v>
@@ -18581,7 +18581,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G628" t="n">
-        <v>16.5029430389404</v>
+        <v>16.5029449462891</v>
       </c>
       <c r="H628" t="n">
         <v>23660</v>
@@ -18610,7 +18610,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G629" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H629" t="n">
         <v>38483</v>
@@ -18639,7 +18639,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G630" t="n">
-        <v>16.5029430389404</v>
+        <v>16.5029449462891</v>
       </c>
       <c r="H630" t="n">
         <v>20106</v>
@@ -18668,7 +18668,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G631" t="n">
-        <v>16.317310333252</v>
+        <v>16.3173122406006</v>
       </c>
       <c r="H631" t="n">
         <v>40982</v>
@@ -18813,7 +18813,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G636" t="n">
-        <v>16.3544330596924</v>
+        <v>16.354434967041</v>
       </c>
       <c r="H636" t="n">
         <v>28223</v>
@@ -18842,7 +18842,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G637" t="n">
-        <v>16.5400714874268</v>
+        <v>16.5400695800781</v>
       </c>
       <c r="H637" t="n">
         <v>32139</v>
@@ -18871,7 +18871,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G638" t="n">
-        <v>16.7999572753906</v>
+        <v>16.7999591827393</v>
       </c>
       <c r="H638" t="n">
         <v>34698</v>
@@ -18958,7 +18958,7 @@
         <v>17.5557403564453</v>
       </c>
       <c r="G641" t="n">
-        <v>16.7813949584961</v>
+        <v>16.7813968658447</v>
       </c>
       <c r="H641" t="n">
         <v>22369</v>
@@ -18987,7 +18987,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G642" t="n">
-        <v>16.3544330596924</v>
+        <v>16.354434967041</v>
       </c>
       <c r="H642" t="n">
         <v>58190</v>
@@ -19074,7 +19074,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G645" t="n">
-        <v>17.4125537872314</v>
+        <v>17.4125556945801</v>
       </c>
       <c r="H645" t="n">
         <v>65148</v>
@@ -19103,7 +19103,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G646" t="n">
-        <v>17.7838230133057</v>
+        <v>17.7838249206543</v>
       </c>
       <c r="H646" t="n">
         <v>45839</v>
@@ -19161,7 +19161,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G648" t="n">
-        <v>18.414981842041</v>
+        <v>18.4149837493896</v>
       </c>
       <c r="H648" t="n">
         <v>15115</v>
@@ -19219,7 +19219,7 @@
         <v>18.7597846984863</v>
       </c>
       <c r="G650" t="n">
-        <v>17.9323329925537</v>
+        <v>17.9323310852051</v>
       </c>
       <c r="H650" t="n">
         <v>14975</v>
@@ -19248,7 +19248,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G651" t="n">
-        <v>16.7999572753906</v>
+        <v>16.7999591827393</v>
       </c>
       <c r="H651" t="n">
         <v>3928533</v>
@@ -19306,7 +19306,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G653" t="n">
-        <v>16.5400714874268</v>
+        <v>16.5400695800781</v>
       </c>
       <c r="H653" t="n">
         <v>88550</v>
@@ -19393,7 +19393,7 @@
         <v>17.4003791809082</v>
       </c>
       <c r="G656" t="n">
-        <v>16.6328907012939</v>
+        <v>16.6328887939453</v>
       </c>
       <c r="H656" t="n">
         <v>33953</v>
@@ -19509,7 +19509,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G660" t="n">
-        <v>16.5029430389404</v>
+        <v>16.5029449462891</v>
       </c>
       <c r="H660" t="n">
         <v>15595</v>
@@ -19538,7 +19538,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G661" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H661" t="n">
         <v>79956</v>
@@ -19654,7 +19654,7 @@
         <v>16.9731388092041</v>
       </c>
       <c r="G665" t="n">
-        <v>16.2244930267334</v>
+        <v>16.2244892120361</v>
       </c>
       <c r="H665" t="n">
         <v>24961</v>
@@ -19683,7 +19683,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G666" t="n">
-        <v>16.521505355835</v>
+        <v>16.5215072631836</v>
       </c>
       <c r="H666" t="n">
         <v>47042</v>
@@ -19741,7 +19741,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G668" t="n">
-        <v>16.1687984466553</v>
+        <v>16.1688022613525</v>
       </c>
       <c r="H668" t="n">
         <v>98048</v>
@@ -19770,7 +19770,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G669" t="n">
-        <v>15.7789669036865</v>
+        <v>15.7789659500122</v>
       </c>
       <c r="H669" t="n">
         <v>79199</v>
@@ -19857,7 +19857,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G672" t="n">
-        <v>16.7999572753906</v>
+        <v>16.7999591827393</v>
       </c>
       <c r="H672" t="n">
         <v>35437</v>
@@ -19915,7 +19915,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G674" t="n">
-        <v>16.317310333252</v>
+        <v>16.3173122406006</v>
       </c>
       <c r="H674" t="n">
         <v>71685</v>
@@ -19973,7 +19973,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G676" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H676" t="n">
         <v>54594</v>
@@ -20002,7 +20002,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G677" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H677" t="n">
         <v>29454</v>
@@ -20089,7 +20089,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G680" t="n">
-        <v>16.5586318969727</v>
+        <v>16.5586338043213</v>
       </c>
       <c r="H680" t="n">
         <v>73431</v>
@@ -20118,7 +20118,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G681" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H681" t="n">
         <v>28477</v>
@@ -20205,7 +20205,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G684" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H684" t="n">
         <v>45521</v>
@@ -20292,7 +20292,7 @@
         <v>16.2157554626465</v>
       </c>
       <c r="G687" t="n">
-        <v>15.5005149841309</v>
+        <v>15.5005130767822</v>
       </c>
       <c r="H687" t="n">
         <v>34503</v>
@@ -20350,7 +20350,7 @@
         <v>16.6429977416992</v>
       </c>
       <c r="G689" t="n">
-        <v>15.90891456604</v>
+        <v>15.9089136123657</v>
       </c>
       <c r="H689" t="n">
         <v>39172</v>
@@ -20379,7 +20379,7 @@
         <v>16.5264759063721</v>
       </c>
       <c r="G690" t="n">
-        <v>15.7975301742554</v>
+        <v>15.7975311279297</v>
       </c>
       <c r="H690" t="n">
         <v>15685</v>
@@ -20408,7 +20408,7 @@
         <v>16.6041564941406</v>
       </c>
       <c r="G691" t="n">
-        <v>15.8717851638794</v>
+        <v>15.8717842102051</v>
       </c>
       <c r="H691" t="n">
         <v>35414</v>
@@ -20437,7 +20437,7 @@
         <v>15.9632940292358</v>
       </c>
       <c r="G692" t="n">
-        <v>15.2591896057129</v>
+        <v>15.2591886520386</v>
       </c>
       <c r="H692" t="n">
         <v>53417</v>
@@ -20466,7 +20466,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G693" t="n">
-        <v>14.8322296142578</v>
+        <v>14.8322286605835</v>
       </c>
       <c r="H693" t="n">
         <v>74278</v>
@@ -20640,7 +20640,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G699" t="n">
-        <v>14.813666343689</v>
+        <v>14.8136653900146</v>
       </c>
       <c r="H699" t="n">
         <v>36729</v>
@@ -20669,7 +20669,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G700" t="n">
-        <v>15.0364294052124</v>
+        <v>15.0364284515381</v>
       </c>
       <c r="H700" t="n">
         <v>34142</v>
@@ -20756,7 +20756,7 @@
         <v>16.2934341430664</v>
       </c>
       <c r="G703" t="n">
-        <v>15.5747690200806</v>
+        <v>15.5747680664062</v>
       </c>
       <c r="H703" t="n">
         <v>77089</v>
@@ -20785,7 +20785,7 @@
         <v>16.1380748748779</v>
       </c>
       <c r="G704" t="n">
-        <v>15.4262609481812</v>
+        <v>15.4262619018555</v>
       </c>
       <c r="H704" t="n">
         <v>145218</v>
@@ -20814,7 +20814,7 @@
         <v>16.332275390625</v>
       </c>
       <c r="G705" t="n">
-        <v>15.6118974685669</v>
+        <v>15.6118965148926</v>
       </c>
       <c r="H705" t="n">
         <v>37102</v>
@@ -20901,7 +20901,7 @@
         <v>16.0603942871094</v>
       </c>
       <c r="G708" t="n">
-        <v>15.3520069122314</v>
+        <v>15.3520059585571</v>
       </c>
       <c r="H708" t="n">
         <v>913996</v>
@@ -20930,7 +20930,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G709" t="n">
-        <v>15.6675853729248</v>
+        <v>15.6675844192505</v>
       </c>
       <c r="H709" t="n">
         <v>47583</v>
@@ -20959,7 +20959,7 @@
         <v>16.2740154266357</v>
       </c>
       <c r="G710" t="n">
-        <v>15.5562057495117</v>
+        <v>15.5562047958374</v>
       </c>
       <c r="H710" t="n">
         <v>17835</v>
@@ -20988,7 +20988,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G711" t="n">
-        <v>15.7604055404663</v>
+        <v>15.7604036331177</v>
       </c>
       <c r="H711" t="n">
         <v>25713</v>
@@ -21017,7 +21017,7 @@
         <v>16.856616973877</v>
       </c>
       <c r="G712" t="n">
-        <v>16.113109588623</v>
+        <v>16.1131114959717</v>
       </c>
       <c r="H712" t="n">
         <v>96484</v>
@@ -21046,7 +21046,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G713" t="n">
-        <v>16.2430553436279</v>
+        <v>16.2430534362793</v>
       </c>
       <c r="H713" t="n">
         <v>26553</v>
@@ -21104,7 +21104,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G715" t="n">
-        <v>16.985595703125</v>
+        <v>16.9855937957764</v>
       </c>
       <c r="H715" t="n">
         <v>139089</v>
@@ -21162,7 +21162,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G717" t="n">
-        <v>17.8209552764893</v>
+        <v>17.8209533691406</v>
       </c>
       <c r="H717" t="n">
         <v>158059</v>
@@ -21307,7 +21307,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G722" t="n">
-        <v>18.0065841674805</v>
+        <v>18.0065860748291</v>
       </c>
       <c r="H722" t="n">
         <v>30703</v>
@@ -21336,7 +21336,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G723" t="n">
-        <v>17.8209552764893</v>
+        <v>17.8209533691406</v>
       </c>
       <c r="H723" t="n">
         <v>65985</v>
@@ -21394,7 +21394,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G725" t="n">
-        <v>17.8209552764893</v>
+        <v>17.8209533691406</v>
       </c>
       <c r="H725" t="n">
         <v>27519</v>
@@ -21452,7 +21452,7 @@
         <v>18.779203414917</v>
       </c>
       <c r="G727" t="n">
-        <v>17.9508934020996</v>
+        <v>17.9508953094482</v>
       </c>
       <c r="H727" t="n">
         <v>22119</v>
@@ -21481,7 +21481,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G728" t="n">
-        <v>17.7652606964111</v>
+        <v>17.7652587890625</v>
       </c>
       <c r="H728" t="n">
         <v>30824</v>
@@ -21539,7 +21539,7 @@
         <v>17.8470401763916</v>
       </c>
       <c r="G730" t="n">
-        <v>17.0598468780518</v>
+        <v>17.0598487854004</v>
       </c>
       <c r="H730" t="n">
         <v>46352</v>
@@ -21568,7 +21568,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G731" t="n">
-        <v>16.985595703125</v>
+        <v>16.9855937957764</v>
       </c>
       <c r="H731" t="n">
         <v>82850</v>
@@ -21626,7 +21626,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G733" t="n">
-        <v>17.4496803283691</v>
+        <v>17.4496822357178</v>
       </c>
       <c r="H733" t="n">
         <v>16597</v>
@@ -21655,7 +21655,7 @@
         <v>18.293701171875</v>
       </c>
       <c r="G734" t="n">
-        <v>17.4868087768555</v>
+        <v>17.4868068695068</v>
       </c>
       <c r="H734" t="n">
         <v>66103</v>
@@ -21713,7 +21713,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G736" t="n">
-        <v>18.1922225952148</v>
+        <v>18.1922245025635</v>
       </c>
       <c r="H736" t="n">
         <v>69493</v>
@@ -21800,7 +21800,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G739" t="n">
-        <v>19.3060302734375</v>
+        <v>19.3060321807861</v>
       </c>
       <c r="H739" t="n">
         <v>45305</v>
@@ -21829,7 +21829,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G740" t="n">
-        <v>19.3988456726074</v>
+        <v>19.3988475799561</v>
       </c>
       <c r="H740" t="n">
         <v>63358</v>
@@ -21887,7 +21887,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G742" t="n">
-        <v>20.4198417663574</v>
+        <v>20.4198398590088</v>
       </c>
       <c r="H742" t="n">
         <v>47386</v>
@@ -21916,7 +21916,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G743" t="n">
-        <v>20.3270263671875</v>
+        <v>20.3270225524902</v>
       </c>
       <c r="H743" t="n">
         <v>30114</v>
@@ -21945,7 +21945,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G744" t="n">
-        <v>20.1413879394531</v>
+        <v>20.1413898468018</v>
       </c>
       <c r="H744" t="n">
         <v>35528</v>
@@ -22003,7 +22003,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G746" t="n">
-        <v>19.8165283203125</v>
+        <v>19.8165264129639</v>
       </c>
       <c r="H746" t="n">
         <v>36026</v>
@@ -22032,7 +22032,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G747" t="n">
-        <v>20.1413879394531</v>
+        <v>20.1413898468018</v>
       </c>
       <c r="H747" t="n">
         <v>37254</v>
@@ -22061,7 +22061,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G748" t="n">
-        <v>20.0949802398682</v>
+        <v>20.0949783325195</v>
       </c>
       <c r="H748" t="n">
         <v>43044</v>
@@ -22119,7 +22119,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G750" t="n">
-        <v>20.512659072876</v>
+        <v>20.5126571655273</v>
       </c>
       <c r="H750" t="n">
         <v>48520</v>
@@ -22148,7 +22148,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G751" t="n">
-        <v>21.0695648193359</v>
+        <v>21.0695610046387</v>
       </c>
       <c r="H751" t="n">
         <v>190456</v>
@@ -22177,7 +22177,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G752" t="n">
-        <v>21.4408359527588</v>
+        <v>21.4408321380615</v>
       </c>
       <c r="H752" t="n">
         <v>38481</v>
@@ -22206,7 +22206,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G753" t="n">
-        <v>21.8121032714844</v>
+        <v>21.8121013641357</v>
       </c>
       <c r="H753" t="n">
         <v>18138</v>
@@ -22235,7 +22235,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G754" t="n">
-        <v>21.1623821258545</v>
+        <v>21.1623802185059</v>
       </c>
       <c r="H754" t="n">
         <v>35943</v>
@@ -22264,7 +22264,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G755" t="n">
-        <v>20.1413879394531</v>
+        <v>20.1413898468018</v>
       </c>
       <c r="H755" t="n">
         <v>48169</v>
@@ -22322,7 +22322,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G757" t="n">
-        <v>20.4198417663574</v>
+        <v>20.4198398590088</v>
       </c>
       <c r="H757" t="n">
         <v>20797</v>
@@ -22351,7 +22351,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G758" t="n">
-        <v>20.3270263671875</v>
+        <v>20.3270225524902</v>
       </c>
       <c r="H758" t="n">
         <v>23340</v>
@@ -22380,7 +22380,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G759" t="n">
-        <v>20.6982936859131</v>
+        <v>20.6982917785645</v>
       </c>
       <c r="H759" t="n">
         <v>44935</v>
@@ -22409,7 +22409,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G760" t="n">
-        <v>20.0949802398682</v>
+        <v>20.0949783325195</v>
       </c>
       <c r="H760" t="n">
         <v>18398</v>
@@ -22438,7 +22438,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G761" t="n">
-        <v>19.9557514190674</v>
+        <v>19.955753326416</v>
       </c>
       <c r="H761" t="n">
         <v>30499</v>
@@ -22467,7 +22467,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G762" t="n">
-        <v>19.8165283203125</v>
+        <v>19.8165264129639</v>
       </c>
       <c r="H762" t="n">
         <v>62037</v>
@@ -22583,7 +22583,7 @@
         <v>20.245418548584</v>
       </c>
       <c r="G766" t="n">
-        <v>19.3524398803711</v>
+        <v>19.3524379730225</v>
       </c>
       <c r="H766" t="n">
         <v>22875</v>
@@ -22612,7 +22612,7 @@
         <v>19.9541187286377</v>
       </c>
       <c r="G767" t="n">
-        <v>19.0739879608154</v>
+        <v>19.0739860534668</v>
       </c>
       <c r="H767" t="n">
         <v>77644</v>
@@ -22670,7 +22670,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G769" t="n">
-        <v>19.8395595550537</v>
+        <v>19.8395614624023</v>
       </c>
       <c r="H769" t="n">
         <v>15945</v>
@@ -22728,7 +22728,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G771" t="n">
-        <v>19.3260688781738</v>
+        <v>19.3260669708252</v>
       </c>
       <c r="H771" t="n">
         <v>16954</v>
@@ -22786,7 +22786,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G773" t="n">
-        <v>19.3727474212646</v>
+        <v>19.372745513916</v>
       </c>
       <c r="H773" t="n">
         <v>12388</v>
@@ -22815,7 +22815,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G774" t="n">
-        <v>19.5594711303711</v>
+        <v>19.5594730377197</v>
       </c>
       <c r="H774" t="n">
         <v>14470</v>
@@ -22873,7 +22873,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G776" t="n">
-        <v>18.7192077636719</v>
+        <v>18.7192096710205</v>
       </c>
       <c r="H776" t="n">
         <v>25471</v>
@@ -22960,7 +22960,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G779" t="n">
-        <v>18.812572479248</v>
+        <v>18.8125743865967</v>
       </c>
       <c r="H779" t="n">
         <v>10927</v>
@@ -23018,7 +23018,7 @@
         <v>19.6142673492432</v>
       </c>
       <c r="G781" t="n">
-        <v>18.8592529296875</v>
+        <v>18.8592548370361</v>
       </c>
       <c r="H781" t="n">
         <v>24171</v>
@@ -23105,7 +23105,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G784" t="n">
-        <v>19.6995182037354</v>
+        <v>19.6995162963867</v>
       </c>
       <c r="H784" t="n">
         <v>16306</v>
@@ -23250,7 +23250,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G789" t="n">
-        <v>18.5044746398926</v>
+        <v>18.5044765472412</v>
       </c>
       <c r="H789" t="n">
         <v>32253</v>
@@ -23279,7 +23279,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G790" t="n">
-        <v>18.3550968170166</v>
+        <v>18.355094909668</v>
       </c>
       <c r="H790" t="n">
         <v>26414</v>
@@ -23308,7 +23308,7 @@
         <v>19.4006462097168</v>
       </c>
       <c r="G791" t="n">
-        <v>18.6538562774658</v>
+        <v>18.6538543701172</v>
       </c>
       <c r="H791" t="n">
         <v>19831</v>
@@ -23482,7 +23482,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G797" t="n">
-        <v>18.7192077636719</v>
+        <v>18.7192096710205</v>
       </c>
       <c r="H797" t="n">
         <v>22667</v>
@@ -23569,7 +23569,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G800" t="n">
-        <v>19.9329242706299</v>
+        <v>19.9329223632812</v>
       </c>
       <c r="H800" t="n">
         <v>31271</v>
@@ -23685,7 +23685,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G804" t="n">
-        <v>21.146635055542</v>
+        <v>21.1466388702393</v>
       </c>
       <c r="H804" t="n">
         <v>37567</v>
@@ -23714,7 +23714,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G805" t="n">
-        <v>21.9402198791504</v>
+        <v>21.940221786499</v>
       </c>
       <c r="H805" t="n">
         <v>86390</v>
@@ -23743,7 +23743,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G806" t="n">
-        <v>22.3136711120605</v>
+        <v>22.3136692047119</v>
       </c>
       <c r="H806" t="n">
         <v>51200</v>
@@ -23772,7 +23772,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G807" t="n">
-        <v>22.8271656036377</v>
+        <v>22.8271675109863</v>
       </c>
       <c r="H807" t="n">
         <v>71776</v>
@@ -23801,7 +23801,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G808" t="n">
-        <v>23.0605735778809</v>
+        <v>23.0605716705322</v>
       </c>
       <c r="H808" t="n">
         <v>33989</v>
@@ -23830,7 +23830,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G809" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406620025635</v>
       </c>
       <c r="H809" t="n">
         <v>60375</v>
@@ -23859,7 +23859,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G810" t="n">
-        <v>23.0138912200928</v>
+        <v>23.0138893127441</v>
       </c>
       <c r="H810" t="n">
         <v>13899</v>
@@ -23946,7 +23946,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G813" t="n">
-        <v>24.0408782958984</v>
+        <v>24.0408802032471</v>
       </c>
       <c r="H813" t="n">
         <v>26369</v>
@@ -24033,7 +24033,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G816" t="n">
-        <v>23.0138912200928</v>
+        <v>23.0138893127441</v>
       </c>
       <c r="H816" t="n">
         <v>22302</v>
@@ -24062,7 +24062,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G817" t="n">
-        <v>22.8738441467285</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H817" t="n">
         <v>16282</v>
@@ -24091,7 +24091,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G818" t="n">
-        <v>22.6871223449707</v>
+        <v>22.6871204376221</v>
       </c>
       <c r="H818" t="n">
         <v>14320</v>
@@ -24120,7 +24120,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G819" t="n">
-        <v>22.7338008880615</v>
+        <v>22.7338027954102</v>
       </c>
       <c r="H819" t="n">
         <v>35322</v>
@@ -24149,7 +24149,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G820" t="n">
-        <v>23.0138912200928</v>
+        <v>23.0138893127441</v>
       </c>
       <c r="H820" t="n">
         <v>8262</v>
@@ -24207,7 +24207,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G822" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406620025635</v>
       </c>
       <c r="H822" t="n">
         <v>6868</v>
@@ -24265,7 +24265,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G824" t="n">
-        <v>23.3873405456543</v>
+        <v>23.3873424530029</v>
       </c>
       <c r="H824" t="n">
         <v>11942</v>
@@ -24294,7 +24294,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G825" t="n">
-        <v>22.8738441467285</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H825" t="n">
         <v>6260</v>
@@ -24352,7 +24352,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G827" t="n">
-        <v>22.8271656036377</v>
+        <v>22.8271675109863</v>
       </c>
       <c r="H827" t="n">
         <v>7460</v>
@@ -24381,7 +24381,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G828" t="n">
-        <v>23.0605735778809</v>
+        <v>23.0605716705322</v>
       </c>
       <c r="H828" t="n">
         <v>15395</v>
@@ -24410,7 +24410,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G829" t="n">
-        <v>23.1072521209717</v>
+        <v>23.107250213623</v>
       </c>
       <c r="H829" t="n">
         <v>19382</v>
@@ -24439,7 +24439,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G830" t="n">
-        <v>22.8271656036377</v>
+        <v>22.8271675109863</v>
       </c>
       <c r="H830" t="n">
         <v>11430</v>
@@ -24468,7 +24468,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G831" t="n">
-        <v>22.8271656036377</v>
+        <v>22.8271675109863</v>
       </c>
       <c r="H831" t="n">
         <v>6939</v>
@@ -24555,7 +24555,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G834" t="n">
-        <v>23.1072521209717</v>
+        <v>23.107250213623</v>
       </c>
       <c r="H834" t="n">
         <v>13567</v>
@@ -24584,7 +24584,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G835" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406620025635</v>
       </c>
       <c r="H835" t="n">
         <v>15283</v>
@@ -24613,7 +24613,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G836" t="n">
-        <v>24.0408782958984</v>
+        <v>24.0408802032471</v>
       </c>
       <c r="H836" t="n">
         <v>28089</v>
@@ -24671,7 +24671,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G838" t="n">
-        <v>22.8271656036377</v>
+        <v>22.8271675109863</v>
       </c>
       <c r="H838" t="n">
         <v>28752</v>
@@ -24700,7 +24700,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G839" t="n">
-        <v>21.613452911377</v>
+        <v>21.6134510040283</v>
       </c>
       <c r="H839" t="n">
         <v>26813</v>
@@ -24758,7 +24758,7 @@
         <v>22.8671283721924</v>
       </c>
       <c r="G841" t="n">
-        <v>21.9869041442871</v>
+        <v>21.9869022369385</v>
       </c>
       <c r="H841" t="n">
         <v>23080</v>
@@ -24787,7 +24787,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G842" t="n">
-        <v>21.8001747131348</v>
+        <v>21.8001766204834</v>
       </c>
       <c r="H842" t="n">
         <v>13062</v>
@@ -24903,7 +24903,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G846" t="n">
-        <v>20.8198699951172</v>
+        <v>20.8198680877686</v>
       </c>
       <c r="H846" t="n">
         <v>17246</v>
@@ -24990,7 +24990,7 @@
         <v>21.9446754455566</v>
       </c>
       <c r="G849" t="n">
-        <v>21.0999565124512</v>
+        <v>21.0999546051025</v>
       </c>
       <c r="H849" t="n">
         <v>19081</v>
@@ -25048,7 +25048,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G851" t="n">
-        <v>22.8738441467285</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H851" t="n">
         <v>26308</v>
@@ -25077,7 +25077,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G852" t="n">
-        <v>24.6477355957031</v>
+        <v>24.6477336883545</v>
       </c>
       <c r="H852" t="n">
         <v>77188</v>
@@ -25164,7 +25164,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G855" t="n">
-        <v>24.274284362793</v>
+        <v>24.2742862701416</v>
       </c>
       <c r="H855" t="n">
         <v>25954</v>
@@ -25251,7 +25251,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G858" t="n">
-        <v>23.2472972869873</v>
+        <v>23.2472953796387</v>
       </c>
       <c r="H858" t="n">
         <v>50612</v>
@@ -25309,7 +25309,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G860" t="n">
-        <v>23.4807014465332</v>
+        <v>23.4807033538818</v>
       </c>
       <c r="H860" t="n">
         <v>16554</v>
@@ -25338,7 +25338,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G861" t="n">
-        <v>23.2472972869873</v>
+        <v>23.2472953796387</v>
       </c>
       <c r="H861" t="n">
         <v>15469</v>
@@ -25367,7 +25367,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G862" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406620025635</v>
       </c>
       <c r="H862" t="n">
         <v>15813</v>
@@ -25396,7 +25396,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G863" t="n">
-        <v>23.3873405456543</v>
+        <v>23.3873424530029</v>
       </c>
       <c r="H863" t="n">
         <v>16687</v>
@@ -25425,7 +25425,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G864" t="n">
-        <v>23.994197845459</v>
+        <v>23.9941959381104</v>
       </c>
       <c r="H864" t="n">
         <v>26927</v>
@@ -25454,7 +25454,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G865" t="n">
-        <v>23.6674289703369</v>
+        <v>23.6674308776855</v>
       </c>
       <c r="H865" t="n">
         <v>32838</v>
@@ -25483,7 +25483,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G866" t="n">
-        <v>24.134241104126</v>
+        <v>24.1342430114746</v>
       </c>
       <c r="H866" t="n">
         <v>117339</v>
@@ -25512,7 +25512,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G867" t="n">
-        <v>24.134241104126</v>
+        <v>24.1342430114746</v>
       </c>
       <c r="H867" t="n">
         <v>37673</v>
@@ -25541,7 +25541,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G868" t="n">
-        <v>23.8074760437012</v>
+        <v>23.8074722290039</v>
       </c>
       <c r="H868" t="n">
         <v>43603</v>
@@ -25570,7 +25570,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G869" t="n">
-        <v>23.8074760437012</v>
+        <v>23.8074722290039</v>
       </c>
       <c r="H869" t="n">
         <v>33654</v>
@@ -25599,7 +25599,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G870" t="n">
-        <v>24.274284362793</v>
+        <v>24.2742862701416</v>
       </c>
       <c r="H870" t="n">
         <v>28315</v>
@@ -25628,7 +25628,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G871" t="n">
-        <v>24.3209686279297</v>
+        <v>24.3209667205811</v>
       </c>
       <c r="H871" t="n">
         <v>5605</v>
@@ -25686,7 +25686,7 @@
         <v>26.4112892150879</v>
       </c>
       <c r="G873" t="n">
-        <v>25.3946361541748</v>
+        <v>25.3946380615234</v>
       </c>
       <c r="H873" t="n">
         <v>22822</v>
@@ -25744,7 +25744,7 @@
         <v>26.5083904266357</v>
       </c>
       <c r="G875" t="n">
-        <v>25.4879989624023</v>
+        <v>25.488000869751</v>
       </c>
       <c r="H875" t="n">
         <v>23256</v>
@@ -25773,7 +25773,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G876" t="n">
-        <v>25.2079105377197</v>
+        <v>25.2079124450684</v>
       </c>
       <c r="H876" t="n">
         <v>118395</v>
@@ -25802,7 +25802,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G877" t="n">
-        <v>25.1145515441895</v>
+        <v>25.1145496368408</v>
       </c>
       <c r="H877" t="n">
         <v>16708</v>
@@ -25831,7 +25831,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G878" t="n">
-        <v>25.1145515441895</v>
+        <v>25.1145496368408</v>
       </c>
       <c r="H878" t="n">
         <v>12223</v>
@@ -25889,7 +25889,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G880" t="n">
-        <v>23.4807014465332</v>
+        <v>23.4807033538818</v>
       </c>
       <c r="H880" t="n">
         <v>27603</v>
@@ -25918,7 +25918,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G881" t="n">
-        <v>23.1539344787598</v>
+        <v>23.1539325714111</v>
       </c>
       <c r="H881" t="n">
         <v>12809</v>
@@ -25947,7 +25947,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G882" t="n">
-        <v>22.8738441467285</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H882" t="n">
         <v>33759</v>
@@ -25976,7 +25976,7 @@
         <v>23.3040790557861</v>
       </c>
       <c r="G883" t="n">
-        <v>22.4070339202881</v>
+        <v>22.4070320129395</v>
       </c>
       <c r="H883" t="n">
         <v>16536</v>
@@ -26005,7 +26005,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G884" t="n">
-        <v>22.1269474029541</v>
+        <v>22.1269454956055</v>
       </c>
       <c r="H884" t="n">
         <v>44427</v>
@@ -26034,7 +26034,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G885" t="n">
-        <v>22.9672107696533</v>
+        <v>22.967212677002</v>
       </c>
       <c r="H885" t="n">
         <v>41855</v>
@@ -26063,7 +26063,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G886" t="n">
-        <v>22.1269474029541</v>
+        <v>22.1269454956055</v>
       </c>
       <c r="H886" t="n">
         <v>27142</v>
@@ -26092,7 +26092,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G887" t="n">
-        <v>22.8271656036377</v>
+        <v>22.8271675109863</v>
       </c>
       <c r="H887" t="n">
         <v>31840</v>
@@ -26121,7 +26121,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G888" t="n">
-        <v>22.8738441467285</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H888" t="n">
         <v>19991</v>
@@ -26179,7 +26179,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G890" t="n">
-        <v>23.6674289703369</v>
+        <v>23.6674308776855</v>
       </c>
       <c r="H890" t="n">
         <v>36276</v>
@@ -26208,7 +26208,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G891" t="n">
-        <v>24.5543746948242</v>
+        <v>24.5543766021729</v>
       </c>
       <c r="H891" t="n">
         <v>159469</v>
@@ -26266,7 +26266,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G893" t="n">
-        <v>24.3676490783691</v>
+        <v>24.3676509857178</v>
       </c>
       <c r="H893" t="n">
         <v>9165</v>
@@ -26295,7 +26295,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G894" t="n">
-        <v>24.3209686279297</v>
+        <v>24.3209667205811</v>
       </c>
       <c r="H894" t="n">
         <v>89124</v>
@@ -26324,7 +26324,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G895" t="n">
-        <v>24.6010551452637</v>
+        <v>24.601053237915</v>
       </c>
       <c r="H895" t="n">
         <v>11982</v>
@@ -26353,7 +26353,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G896" t="n">
-        <v>24.3676490783691</v>
+        <v>24.3676509857178</v>
       </c>
       <c r="H896" t="n">
         <v>15752</v>
@@ -26382,7 +26382,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G897" t="n">
-        <v>22.8738441467285</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H897" t="n">
         <v>55336</v>
@@ -26411,7 +26411,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G898" t="n">
-        <v>22.8738441467285</v>
+        <v>22.8738479614258</v>
       </c>
       <c r="H898" t="n">
         <v>40638</v>
@@ -26440,7 +26440,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G899" t="n">
-        <v>23.0605735778809</v>
+        <v>23.0605716705322</v>
       </c>
       <c r="H899" t="n">
         <v>20497</v>
@@ -26469,7 +26469,7 @@
         <v>24.7120342254639</v>
       </c>
       <c r="G900" t="n">
-        <v>23.7607898712158</v>
+        <v>23.7607936859131</v>
       </c>
       <c r="H900" t="n">
         <v>11109</v>
@@ -26527,7 +26527,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G902" t="n">
-        <v>23.8541564941406</v>
+        <v>23.8541526794434</v>
       </c>
       <c r="H902" t="n">
         <v>4095</v>
@@ -26556,7 +26556,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G903" t="n">
-        <v>23.8074760437012</v>
+        <v>23.8074722290039</v>
       </c>
       <c r="H903" t="n">
         <v>3761</v>
@@ -26585,7 +26585,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G904" t="n">
-        <v>24.6944198608398</v>
+        <v>24.6944179534912</v>
       </c>
       <c r="H904" t="n">
         <v>9853</v>
@@ -26701,7 +26701,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G908" t="n">
-        <v>23.8541564941406</v>
+        <v>23.8541526794434</v>
       </c>
       <c r="H908" t="n">
         <v>22990</v>
@@ -26730,7 +26730,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G909" t="n">
-        <v>23.8074760437012</v>
+        <v>23.8074722290039</v>
       </c>
       <c r="H909" t="n">
         <v>30538</v>
@@ -26788,7 +26788,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G911" t="n">
-        <v>23.4807014465332</v>
+        <v>23.4807033538818</v>
       </c>
       <c r="H911" t="n">
         <v>50279</v>
@@ -26817,7 +26817,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G912" t="n">
-        <v>24.3209686279297</v>
+        <v>24.3209667205811</v>
       </c>
       <c r="H912" t="n">
         <v>54129</v>
@@ -26875,7 +26875,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G914" t="n">
-        <v>24.9745082855225</v>
+        <v>24.9745063781738</v>
       </c>
       <c r="H914" t="n">
         <v>27980</v>
@@ -26933,7 +26933,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G916" t="n">
-        <v>23.4807014465332</v>
+        <v>23.4807033538818</v>
       </c>
       <c r="H916" t="n">
         <v>38891</v>
@@ -26962,7 +26962,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G917" t="n">
-        <v>22.7338008880615</v>
+        <v>22.7338027954102</v>
       </c>
       <c r="H917" t="n">
         <v>35692</v>
@@ -26991,7 +26991,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G918" t="n">
-        <v>23.3406600952148</v>
+        <v>23.3406620025635</v>
       </c>
       <c r="H918" t="n">
         <v>22305</v>
@@ -27078,7 +27078,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G921" t="n">
-        <v>21.3800449371338</v>
+        <v>21.3800430297852</v>
       </c>
       <c r="H921" t="n">
         <v>28013</v>
@@ -27223,7 +27223,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G926" t="n">
-        <v>19.8395595550537</v>
+        <v>19.8395614624023</v>
       </c>
       <c r="H926" t="n">
         <v>42284</v>
@@ -27252,7 +27252,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G927" t="n">
-        <v>21.146635055542</v>
+        <v>21.1466388702393</v>
       </c>
       <c r="H927" t="n">
         <v>93245</v>
@@ -27281,7 +27281,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G928" t="n">
-        <v>21.6601333618164</v>
+        <v>21.6601314544678</v>
       </c>
       <c r="H928" t="n">
         <v>33637</v>
@@ -27310,7 +27310,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G929" t="n">
-        <v>21.146635055542</v>
+        <v>21.1466388702393</v>
       </c>
       <c r="H929" t="n">
         <v>29524</v>
@@ -27368,7 +27368,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G931" t="n">
-        <v>20.7265071868896</v>
+        <v>20.726505279541</v>
       </c>
       <c r="H931" t="n">
         <v>16494</v>
@@ -27455,7 +27455,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G934" t="n">
-        <v>21.4734058380127</v>
+        <v>21.4734077453613</v>
       </c>
       <c r="H934" t="n">
         <v>71464</v>
@@ -27484,7 +27484,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G935" t="n">
-        <v>21.3800449371338</v>
+        <v>21.3800430297852</v>
       </c>
       <c r="H935" t="n">
         <v>77704</v>
@@ -27513,7 +27513,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G936" t="n">
-        <v>21.2399997711182</v>
+        <v>21.2400016784668</v>
       </c>
       <c r="H936" t="n">
         <v>51511</v>
@@ -27571,7 +27571,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G938" t="n">
-        <v>21.146635055542</v>
+        <v>21.1466388702393</v>
       </c>
       <c r="H938" t="n">
         <v>20938</v>
@@ -27774,7 +27774,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G945" t="n">
-        <v>19.7461967468262</v>
+        <v>19.7462005615234</v>
       </c>
       <c r="H945" t="n">
         <v>44866</v>
@@ -27803,7 +27803,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G946" t="n">
-        <v>20.5397796630859</v>
+        <v>20.5397834777832</v>
       </c>
       <c r="H946" t="n">
         <v>99259</v>
@@ -27832,7 +27832,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G947" t="n">
-        <v>19.3260688781738</v>
+        <v>19.3260669708252</v>
       </c>
       <c r="H947" t="n">
         <v>31704</v>
@@ -27861,7 +27861,7 @@
         <v>20.0026683807373</v>
       </c>
       <c r="G948" t="n">
-        <v>19.232702255249</v>
+        <v>19.2327041625977</v>
       </c>
       <c r="H948" t="n">
         <v>67870</v>
@@ -27890,7 +27890,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G949" t="n">
-        <v>18.0936794281006</v>
+        <v>18.0936813354492</v>
       </c>
       <c r="H949" t="n">
         <v>53865</v>
@@ -27948,7 +27948,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G951" t="n">
-        <v>16.9359817504883</v>
+        <v>16.9359836578369</v>
       </c>
       <c r="H951" t="n">
         <v>122448</v>
@@ -27977,7 +27977,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G952" t="n">
-        <v>16.7119121551514</v>
+        <v>16.7119102478027</v>
       </c>
       <c r="H952" t="n">
         <v>87288</v>
@@ -28006,7 +28006,7 @@
         <v>18.9151439666748</v>
       </c>
       <c r="G953" t="n">
-        <v>18.1870441436768</v>
+        <v>18.1870422363281</v>
       </c>
       <c r="H953" t="n">
         <v>72558</v>
@@ -28064,7 +28064,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G955" t="n">
-        <v>18.5418224334717</v>
+        <v>18.541820526123</v>
       </c>
       <c r="H955" t="n">
         <v>25102</v>
@@ -28093,7 +28093,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G956" t="n">
-        <v>19.7928810119629</v>
+        <v>19.7928791046143</v>
       </c>
       <c r="H956" t="n">
         <v>33741</v>
@@ -28209,7 +28209,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G960" t="n">
-        <v>20.5397796630859</v>
+        <v>20.5397834777832</v>
       </c>
       <c r="H960" t="n">
         <v>59869</v>
@@ -28267,7 +28267,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G962" t="n">
-        <v>21.6601333618164</v>
+        <v>21.6601314544678</v>
       </c>
       <c r="H962" t="n">
         <v>33840</v>
@@ -28354,7 +28354,7 @@
         <v>22.7214775085449</v>
       </c>
       <c r="G965" t="n">
-        <v>21.8468589782715</v>
+        <v>21.8468570709229</v>
       </c>
       <c r="H965" t="n">
         <v>94239</v>
@@ -28383,7 +28383,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G966" t="n">
-        <v>21.6601333618164</v>
+        <v>21.6601314544678</v>
       </c>
       <c r="H966" t="n">
         <v>24672</v>
@@ -28441,7 +28441,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G968" t="n">
-        <v>23.0138912200928</v>
+        <v>23.0138893127441</v>
       </c>
       <c r="H968" t="n">
         <v>48550</v>
@@ -28499,7 +28499,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G970" t="n">
-        <v>21.3333625793457</v>
+        <v>21.3333644866943</v>
       </c>
       <c r="H970" t="n">
         <v>58150</v>
@@ -28528,7 +28528,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G971" t="n">
-        <v>20.3530521392822</v>
+        <v>20.3530540466309</v>
       </c>
       <c r="H971" t="n">
         <v>40643</v>
@@ -28557,7 +28557,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G972" t="n">
-        <v>20.166332244873</v>
+        <v>20.1663303375244</v>
       </c>
       <c r="H972" t="n">
         <v>49476</v>
@@ -28673,7 +28673,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G976" t="n">
-        <v>20.3530521392822</v>
+        <v>20.3530540466309</v>
       </c>
       <c r="H976" t="n">
         <v>48544</v>
@@ -28702,7 +28702,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G977" t="n">
-        <v>20.166332244873</v>
+        <v>20.1663303375244</v>
       </c>
       <c r="H977" t="n">
         <v>28457</v>
@@ -28760,7 +28760,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G979" t="n">
-        <v>20.3530521392822</v>
+        <v>20.3530540466309</v>
       </c>
       <c r="H979" t="n">
         <v>22991</v>
@@ -28847,7 +28847,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G982" t="n">
-        <v>21.6601333618164</v>
+        <v>21.6601314544678</v>
       </c>
       <c r="H982" t="n">
         <v>44876</v>
@@ -28934,7 +28934,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G985" t="n">
-        <v>21.4734058380127</v>
+        <v>21.4734077453613</v>
       </c>
       <c r="H985" t="n">
         <v>81020</v>
@@ -28963,7 +28963,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G986" t="n">
-        <v>21.3800449371338</v>
+        <v>21.3800430297852</v>
       </c>
       <c r="H986" t="n">
         <v>29463</v>
@@ -29079,7 +29079,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G990" t="n">
-        <v>21.8001747131348</v>
+        <v>21.8001766204834</v>
       </c>
       <c r="H990" t="n">
         <v>24793</v>
@@ -29137,7 +29137,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G992" t="n">
-        <v>21.3333625793457</v>
+        <v>21.3333644866943</v>
       </c>
       <c r="H992" t="n">
         <v>333685</v>
@@ -29340,7 +29340,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G999" t="n">
-        <v>20.8198699951172</v>
+        <v>20.8198680877686</v>
       </c>
       <c r="H999" t="n">
         <v>26674</v>
@@ -29369,7 +29369,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1000" t="n">
-        <v>20.5397796630859</v>
+        <v>20.5397834777832</v>
       </c>
       <c r="H1000" t="n">
         <v>33541</v>
@@ -29427,7 +29427,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1002" t="n">
-        <v>20.3530521392822</v>
+        <v>20.3530540466309</v>
       </c>
       <c r="H1002" t="n">
         <v>38321</v>
@@ -29514,7 +29514,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1005" t="n">
-        <v>19.9329242706299</v>
+        <v>19.9329223632812</v>
       </c>
       <c r="H1005" t="n">
         <v>21452</v>
@@ -29543,7 +29543,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G1006" t="n">
-        <v>19.7461967468262</v>
+        <v>19.7462005615234</v>
       </c>
       <c r="H1006" t="n">
         <v>18894</v>
@@ -29659,7 +29659,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1010" t="n">
-        <v>20.8198699951172</v>
+        <v>20.8198680877686</v>
       </c>
       <c r="H1010" t="n">
         <v>174076</v>
@@ -29688,7 +29688,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1011" t="n">
-        <v>20.8198699951172</v>
+        <v>20.8198680877686</v>
       </c>
       <c r="H1011" t="n">
         <v>37844</v>
@@ -29717,7 +29717,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1012" t="n">
-        <v>20.5397796630859</v>
+        <v>20.5397834777832</v>
       </c>
       <c r="H1012" t="n">
         <v>31028</v>
@@ -29804,7 +29804,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1015" t="n">
-        <v>20.5397796630859</v>
+        <v>20.5397834777832</v>
       </c>
       <c r="H1015" t="n">
         <v>22236</v>
@@ -29891,7 +29891,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1018" t="n">
-        <v>18.812572479248</v>
+        <v>18.8125743865967</v>
       </c>
       <c r="H1018" t="n">
         <v>17176</v>
@@ -29920,7 +29920,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1019" t="n">
-        <v>18.2057132720947</v>
+        <v>18.2057113647461</v>
       </c>
       <c r="H1019" t="n">
         <v>43373</v>
@@ -29978,7 +29978,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G1021" t="n">
-        <v>17.7762451171875</v>
+        <v>17.7762470245361</v>
       </c>
       <c r="H1021" t="n">
         <v>16938</v>
@@ -30007,7 +30007,7 @@
         <v>17.7887802124023</v>
       </c>
       <c r="G1022" t="n">
-        <v>17.1040344238281</v>
+        <v>17.1040363311768</v>
       </c>
       <c r="H1022" t="n">
         <v>20900</v>
@@ -30065,7 +30065,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G1024" t="n">
-        <v>16.6617622375488</v>
+        <v>16.6617603302002</v>
       </c>
       <c r="H1024" t="n">
         <v>24826</v>
@@ -30123,7 +30123,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G1026" t="n">
-        <v>16.7935447692871</v>
+        <v>16.7935466766357</v>
       </c>
       <c r="H1026" t="n">
         <v>20196</v>
@@ -30326,7 +30326,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G1033" t="n">
-        <v>17.6972370147705</v>
+        <v>17.6972351074219</v>
       </c>
       <c r="H1033" t="n">
         <v>21958</v>
@@ -30355,7 +30355,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1034" t="n">
-        <v>18.1490802764893</v>
+        <v>18.1490821838379</v>
       </c>
       <c r="H1034" t="n">
         <v>19382</v>
@@ -30442,7 +30442,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G1037" t="n">
-        <v>18.8268489837646</v>
+        <v>18.826847076416</v>
       </c>
       <c r="H1037" t="n">
         <v>15503</v>
@@ -30500,7 +30500,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G1039" t="n">
-        <v>18.4503116607666</v>
+        <v>18.450309753418</v>
       </c>
       <c r="H1039" t="n">
         <v>24812</v>
@@ -30529,7 +30529,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G1040" t="n">
-        <v>18.6574058532715</v>
+        <v>18.6574077606201</v>
       </c>
       <c r="H1040" t="n">
         <v>12934</v>
@@ -30587,7 +30587,7 @@
         <v>18.3908023834229</v>
       </c>
       <c r="G1042" t="n">
-        <v>17.8290214538574</v>
+        <v>17.8290233612061</v>
       </c>
       <c r="H1042" t="n">
         <v>14439</v>
@@ -30674,7 +30674,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G1045" t="n">
-        <v>18.4691371917725</v>
+        <v>18.4691352844238</v>
       </c>
       <c r="H1045" t="n">
         <v>12329</v>
@@ -30703,7 +30703,7 @@
         <v>19.225866317749</v>
       </c>
       <c r="G1046" t="n">
-        <v>18.638578414917</v>
+        <v>18.6385803222656</v>
       </c>
       <c r="H1046" t="n">
         <v>13909</v>
@@ -30819,7 +30819,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1050" t="n">
-        <v>20.7095336914062</v>
+        <v>20.7095317840576</v>
       </c>
       <c r="H1050" t="n">
         <v>19089</v>
@@ -30848,7 +30848,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1051" t="n">
-        <v>20.8036670684814</v>
+        <v>20.8036651611328</v>
       </c>
       <c r="H1051" t="n">
         <v>13490</v>
@@ -30877,7 +30877,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G1052" t="n">
-        <v>20.7566013336182</v>
+        <v>20.7565994262695</v>
       </c>
       <c r="H1052" t="n">
         <v>32793</v>
@@ -30906,7 +30906,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G1053" t="n">
-        <v>20.8978004455566</v>
+        <v>20.897798538208</v>
       </c>
       <c r="H1053" t="n">
         <v>38937</v>
@@ -30935,7 +30935,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1054" t="n">
-        <v>20.8036670684814</v>
+        <v>20.8036651611328</v>
       </c>
       <c r="H1054" t="n">
         <v>30458</v>
@@ -30993,7 +30993,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1056" t="n">
-        <v>20.1447238922119</v>
+        <v>20.1447257995605</v>
       </c>
       <c r="H1056" t="n">
         <v>20364</v>
@@ -31051,7 +31051,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1058" t="n">
-        <v>22.5451507568359</v>
+        <v>22.5451488494873</v>
       </c>
       <c r="H1058" t="n">
         <v>114287</v>
@@ -31080,7 +31080,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1059" t="n">
-        <v>22.5451507568359</v>
+        <v>22.5451488494873</v>
       </c>
       <c r="H1059" t="n">
         <v>13110</v>
@@ -31109,7 +31109,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1060" t="n">
-        <v>22.121545791626</v>
+        <v>22.1215438842773</v>
       </c>
       <c r="H1060" t="n">
         <v>11974</v>
@@ -31167,7 +31167,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1062" t="n">
-        <v>22.4510135650635</v>
+        <v>22.4510154724121</v>
       </c>
       <c r="H1062" t="n">
         <v>5796</v>
@@ -31196,7 +31196,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1063" t="n">
-        <v>22.121545791626</v>
+        <v>22.1215438842773</v>
       </c>
       <c r="H1063" t="n">
         <v>8499</v>
@@ -31254,7 +31254,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G1065" t="n">
-        <v>21.3214015960693</v>
+        <v>21.321403503418</v>
       </c>
       <c r="H1065" t="n">
         <v>16460</v>
@@ -31341,7 +31341,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1068" t="n">
-        <v>20.7095336914062</v>
+        <v>20.7095317840576</v>
       </c>
       <c r="H1068" t="n">
         <v>62150</v>
@@ -31399,7 +31399,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1070" t="n">
-        <v>20.8036670684814</v>
+        <v>20.8036651611328</v>
       </c>
       <c r="H1070" t="n">
         <v>24078</v>
@@ -31486,7 +31486,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1073" t="n">
-        <v>20.1447238922119</v>
+        <v>20.1447257995605</v>
       </c>
       <c r="H1073" t="n">
         <v>6725</v>
@@ -31515,7 +31515,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1074" t="n">
-        <v>20.1447238922119</v>
+        <v>20.1447257995605</v>
       </c>
       <c r="H1074" t="n">
         <v>6921</v>
@@ -31544,7 +31544,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1075" t="n">
-        <v>20.1447238922119</v>
+        <v>20.1447257995605</v>
       </c>
       <c r="H1075" t="n">
         <v>16126</v>
@@ -31573,7 +31573,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G1076" t="n">
-        <v>19.5328540802002</v>
+        <v>19.5328521728516</v>
       </c>
       <c r="H1076" t="n">
         <v>7123</v>
@@ -31689,7 +31689,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G1080" t="n">
-        <v>19.1092491149902</v>
+        <v>19.1092472076416</v>
       </c>
       <c r="H1080" t="n">
         <v>7826</v>
@@ -31718,7 +31718,7 @@
         <v>20.0512180328369</v>
       </c>
       <c r="G1081" t="n">
-        <v>19.4387187957764</v>
+        <v>19.438720703125</v>
       </c>
       <c r="H1081" t="n">
         <v>37815</v>
@@ -31921,7 +31921,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G1088" t="n">
-        <v>18.2432155609131</v>
+        <v>18.2432136535645</v>
       </c>
       <c r="H1088" t="n">
         <v>13941</v>
@@ -31979,7 +31979,7 @@
         <v>18.6821041107178</v>
       </c>
       <c r="G1090" t="n">
-        <v>18.1114273071289</v>
+        <v>18.1114253997803</v>
       </c>
       <c r="H1090" t="n">
         <v>14002</v>
@@ -32037,7 +32037,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G1092" t="n">
-        <v>18.2620391845703</v>
+        <v>18.2620410919189</v>
       </c>
       <c r="H1092" t="n">
         <v>39880</v>
@@ -32124,7 +32124,7 @@
         <v>18.2354412078857</v>
       </c>
       <c r="G1095" t="n">
-        <v>17.6784076690674</v>
+        <v>17.6784057617188</v>
       </c>
       <c r="H1095" t="n">
         <v>40255</v>
@@ -32182,7 +32182,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G1097" t="n">
-        <v>18.0172920227051</v>
+        <v>18.0172901153564</v>
       </c>
       <c r="H1097" t="n">
         <v>18857</v>
@@ -32211,7 +32211,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1098" t="n">
-        <v>18.9680480957031</v>
+        <v>18.9680500030518</v>
       </c>
       <c r="H1098" t="n">
         <v>57714</v>
@@ -32269,7 +32269,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1100" t="n">
-        <v>18.9680480957031</v>
+        <v>18.9680500030518</v>
       </c>
       <c r="H1100" t="n">
         <v>38979</v>
@@ -32298,7 +32298,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G1101" t="n">
-        <v>18.676233291626</v>
+        <v>18.6762313842773</v>
       </c>
       <c r="H1101" t="n">
         <v>15144</v>
@@ -32356,7 +32356,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G1103" t="n">
-        <v>18.1679077148438</v>
+        <v>18.1679096221924</v>
       </c>
       <c r="H1103" t="n">
         <v>14703</v>
@@ -32501,7 +32501,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1108" t="n">
-        <v>18.1490802764893</v>
+        <v>18.1490821838379</v>
       </c>
       <c r="H1108" t="n">
         <v>23220</v>
@@ -32530,7 +32530,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G1109" t="n">
-        <v>18.2432155609131</v>
+        <v>18.2432136535645</v>
       </c>
       <c r="H1109" t="n">
         <v>23271</v>
@@ -32559,7 +32559,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1110" t="n">
-        <v>18.1490802764893</v>
+        <v>18.1490821838379</v>
       </c>
       <c r="H1110" t="n">
         <v>7289</v>
@@ -32617,7 +32617,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1112" t="n">
-        <v>18.3561763763428</v>
+        <v>18.3561744689941</v>
       </c>
       <c r="H1112" t="n">
         <v>9961</v>
@@ -32675,7 +32675,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1114" t="n">
-        <v>20.52126121521</v>
+        <v>20.5212631225586</v>
       </c>
       <c r="H1114" t="n">
         <v>25708</v>
@@ -32704,7 +32704,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1115" t="n">
-        <v>20.4741954803467</v>
+        <v>20.4741973876953</v>
       </c>
       <c r="H1115" t="n">
         <v>82382</v>
@@ -32733,7 +32733,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1116" t="n">
-        <v>20.8036670684814</v>
+        <v>20.8036651611328</v>
       </c>
       <c r="H1116" t="n">
         <v>39044</v>
@@ -32762,7 +32762,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1117" t="n">
-        <v>20.8036670684814</v>
+        <v>20.8036651611328</v>
       </c>
       <c r="H1117" t="n">
         <v>9756</v>
@@ -32791,7 +32791,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G1118" t="n">
-        <v>20.7566013336182</v>
+        <v>20.7565994262695</v>
       </c>
       <c r="H1118" t="n">
         <v>17929</v>
@@ -32849,7 +32849,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1120" t="n">
-        <v>20.52126121521</v>
+        <v>20.5212631225586</v>
       </c>
       <c r="H1120" t="n">
         <v>13548</v>
@@ -32907,7 +32907,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1122" t="n">
-        <v>20.4741954803467</v>
+        <v>20.4741973876953</v>
       </c>
       <c r="H1122" t="n">
         <v>11738</v>
@@ -32965,7 +32965,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1124" t="n">
-        <v>20.7095336914062</v>
+        <v>20.7095317840576</v>
       </c>
       <c r="H1124" t="n">
         <v>20743</v>
@@ -33023,7 +33023,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1126" t="n">
-        <v>22.3568801879883</v>
+        <v>22.3568820953369</v>
       </c>
       <c r="H1126" t="n">
         <v>38618</v>
@@ -33052,7 +33052,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1127" t="n">
-        <v>23.1570224761963</v>
+        <v>23.1570243835449</v>
       </c>
       <c r="H1127" t="n">
         <v>91749</v>
@@ -33284,7 +33284,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1135" t="n">
-        <v>23.5335597991943</v>
+        <v>23.533561706543</v>
       </c>
       <c r="H1135" t="n">
         <v>37839</v>
@@ -33313,7 +33313,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1136" t="n">
-        <v>23.1570224761963</v>
+        <v>23.1570243835449</v>
       </c>
       <c r="H1136" t="n">
         <v>28758</v>
@@ -33371,7 +33371,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1138" t="n">
-        <v>22.5451507568359</v>
+        <v>22.5451488494873</v>
       </c>
       <c r="H1138" t="n">
         <v>20349</v>
@@ -33429,7 +33429,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1140" t="n">
-        <v>22.3568801879883</v>
+        <v>22.3568820953369</v>
       </c>
       <c r="H1140" t="n">
         <v>41434</v>
@@ -33458,7 +33458,7 @@
         <v>23.4497299194336</v>
       </c>
       <c r="G1141" t="n">
-        <v>22.733419418335</v>
+        <v>22.7334175109863</v>
       </c>
       <c r="H1141" t="n">
         <v>21340</v>
@@ -33516,7 +33516,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1143" t="n">
-        <v>22.8746204376221</v>
+        <v>22.8746185302734</v>
       </c>
       <c r="H1143" t="n">
         <v>19066</v>
@@ -33632,7 +33632,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1147" t="n">
-        <v>23.5335597991943</v>
+        <v>23.533561706543</v>
       </c>
       <c r="H1147" t="n">
         <v>124040</v>
@@ -33690,7 +33690,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1149" t="n">
-        <v>24.192497253418</v>
+        <v>24.1924991607666</v>
       </c>
       <c r="H1149" t="n">
         <v>89817</v>
@@ -33806,7 +33806,7 @@
         <v>22.9642276763916</v>
       </c>
       <c r="G1153" t="n">
-        <v>22.2627449035645</v>
+        <v>22.2627468109131</v>
       </c>
       <c r="H1153" t="n">
         <v>25466</v>
@@ -33835,7 +33835,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G1154" t="n">
-        <v>21.8391437530518</v>
+        <v>21.8391418457031</v>
       </c>
       <c r="H1154" t="n">
         <v>31463</v>
@@ -33922,7 +33922,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1157" t="n">
-        <v>22.3568801879883</v>
+        <v>22.3568820953369</v>
       </c>
       <c r="H1157" t="n">
         <v>6702</v>
@@ -33951,7 +33951,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1158" t="n">
-        <v>22.3568801879883</v>
+        <v>22.3568820953369</v>
       </c>
       <c r="H1158" t="n">
         <v>11254</v>
@@ -34009,7 +34009,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1160" t="n">
-        <v>22.3568801879883</v>
+        <v>22.3568820953369</v>
       </c>
       <c r="H1160" t="n">
         <v>4782</v>
@@ -34038,7 +34038,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1161" t="n">
-        <v>22.121545791626</v>
+        <v>22.1215438842773</v>
       </c>
       <c r="H1161" t="n">
         <v>5817</v>
@@ -34067,7 +34067,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1162" t="n">
-        <v>22.121545791626</v>
+        <v>22.1215438842773</v>
       </c>
       <c r="H1162" t="n">
         <v>2813</v>
@@ -34154,7 +34154,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G1165" t="n">
-        <v>21.4626064300537</v>
+        <v>21.4626045227051</v>
       </c>
       <c r="H1165" t="n">
         <v>13718</v>
@@ -34183,7 +34183,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1166" t="n">
-        <v>21.6508731842041</v>
+        <v>21.6508750915527</v>
       </c>
       <c r="H1166" t="n">
         <v>13219</v>
@@ -34241,7 +34241,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G1168" t="n">
-        <v>21.5567398071289</v>
+        <v>21.5567417144775</v>
       </c>
       <c r="H1168" t="n">
         <v>20696</v>
@@ -34270,7 +34270,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G1169" t="n">
-        <v>21.4155387878418</v>
+        <v>21.4155368804932</v>
       </c>
       <c r="H1169" t="n">
         <v>29907</v>
@@ -34299,7 +34299,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G1170" t="n">
-        <v>21.2272701263428</v>
+        <v>21.2272720336914</v>
       </c>
       <c r="H1170" t="n">
         <v>32052</v>
@@ -34357,7 +34357,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G1172" t="n">
-        <v>21.7920780181885</v>
+        <v>21.7920761108398</v>
       </c>
       <c r="H1172" t="n">
         <v>51171</v>
@@ -34386,7 +34386,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1173" t="n">
-        <v>21.6508731842041</v>
+        <v>21.6508750915527</v>
       </c>
       <c r="H1173" t="n">
         <v>24793</v>
@@ -34415,7 +34415,7 @@
         <v>22.9642276763916</v>
       </c>
       <c r="G1174" t="n">
-        <v>22.2627449035645</v>
+        <v>22.2627468109131</v>
       </c>
       <c r="H1174" t="n">
         <v>55108</v>
@@ -34444,7 +34444,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1175" t="n">
-        <v>21.6508731842041</v>
+        <v>21.6508750915527</v>
       </c>
       <c r="H1175" t="n">
         <v>29488</v>
@@ -34473,7 +34473,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1176" t="n">
-        <v>22.121545791626</v>
+        <v>22.1215438842773</v>
       </c>
       <c r="H1176" t="n">
         <v>36657</v>
@@ -34531,7 +34531,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1178" t="n">
-        <v>22.8746204376221</v>
+        <v>22.8746185302734</v>
       </c>
       <c r="H1178" t="n">
         <v>20291</v>
@@ -34560,7 +34560,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1179" t="n">
-        <v>22.5451507568359</v>
+        <v>22.5451488494873</v>
       </c>
       <c r="H1179" t="n">
         <v>10229</v>
@@ -34589,7 +34589,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1180" t="n">
-        <v>22.3568801879883</v>
+        <v>22.3568820953369</v>
       </c>
       <c r="H1180" t="n">
         <v>9877</v>
@@ -34647,7 +34647,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G1182" t="n">
-        <v>21.7920780181885</v>
+        <v>21.7920761108398</v>
       </c>
       <c r="H1182" t="n">
         <v>17354</v>
@@ -34676,7 +34676,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G1183" t="n">
-        <v>21.3684730529785</v>
+        <v>21.3684711456299</v>
       </c>
       <c r="H1183" t="n">
         <v>24503</v>
@@ -34705,7 +34705,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1184" t="n">
-        <v>22.3568801879883</v>
+        <v>22.3568820953369</v>
       </c>
       <c r="H1184" t="n">
         <v>21995</v>
@@ -34792,7 +34792,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G1187" t="n">
-        <v>24.5219688415527</v>
+        <v>24.5219669342041</v>
       </c>
       <c r="H1187" t="n">
         <v>20612</v>
@@ -34821,7 +34821,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G1188" t="n">
-        <v>23.8159618377686</v>
+        <v>23.8159599304199</v>
       </c>
       <c r="H1188" t="n">
         <v>26776</v>
@@ -34908,7 +34908,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1191" t="n">
-        <v>23.9100952148438</v>
+        <v>23.9100933074951</v>
       </c>
       <c r="H1191" t="n">
         <v>18246</v>
@@ -34995,7 +34995,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1194" t="n">
-        <v>24.6631679534912</v>
+        <v>24.6631698608398</v>
       </c>
       <c r="H1194" t="n">
         <v>10597</v>
@@ -35053,7 +35053,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1196" t="n">
-        <v>24.2395648956299</v>
+        <v>24.2395668029785</v>
       </c>
       <c r="H1196" t="n">
         <v>7570</v>
@@ -35140,7 +35140,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1199" t="n">
-        <v>24.3336982727051</v>
+        <v>24.3337001800537</v>
       </c>
       <c r="H1199" t="n">
         <v>31535</v>
@@ -35169,7 +35169,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1200" t="n">
-        <v>24.8514385223389</v>
+        <v>24.8514366149902</v>
       </c>
       <c r="H1200" t="n">
         <v>15649</v>
@@ -35198,7 +35198,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1201" t="n">
-        <v>25.557445526123</v>
+        <v>25.5574436187744</v>
       </c>
       <c r="H1201" t="n">
         <v>47925</v>
@@ -35227,7 +35227,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G1202" t="n">
-        <v>24.4749011993408</v>
+        <v>24.4748992919922</v>
       </c>
       <c r="H1202" t="n">
         <v>47505</v>
@@ -35256,7 +35256,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1203" t="n">
-        <v>24.8514385223389</v>
+        <v>24.8514366149902</v>
       </c>
       <c r="H1203" t="n">
         <v>47889</v>
@@ -35285,7 +35285,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1204" t="n">
-        <v>24.3336982727051</v>
+        <v>24.3337001800537</v>
       </c>
       <c r="H1204" t="n">
         <v>35811</v>
@@ -35314,7 +35314,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1205" t="n">
-        <v>24.192497253418</v>
+        <v>24.1924991607666</v>
       </c>
       <c r="H1205" t="n">
         <v>30448</v>
@@ -35343,7 +35343,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1206" t="n">
-        <v>24.8514385223389</v>
+        <v>24.8514366149902</v>
       </c>
       <c r="H1206" t="n">
         <v>51167</v>
@@ -35401,7 +35401,7 @@
         <v>26.1685390472412</v>
       </c>
       <c r="G1208" t="n">
-        <v>25.3691749572754</v>
+        <v>25.369176864624</v>
       </c>
       <c r="H1208" t="n">
         <v>93294</v>
@@ -35488,7 +35488,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1211" t="n">
-        <v>23.9100952148438</v>
+        <v>23.9100933074951</v>
       </c>
       <c r="H1211" t="n">
         <v>145585</v>
@@ -35546,7 +35546,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1213" t="n">
-        <v>23.9100952148438</v>
+        <v>23.9100933074951</v>
       </c>
       <c r="H1213" t="n">
         <v>55602</v>
@@ -35720,7 +35720,7 @@
         <v>23.5468292236328</v>
       </c>
       <c r="G1219" t="n">
-        <v>22.8275508880615</v>
+        <v>22.8275527954102</v>
       </c>
       <c r="H1219" t="n">
         <v>18907</v>
@@ -35778,7 +35778,7 @@
         <v>23.5468292236328</v>
       </c>
       <c r="G1221" t="n">
-        <v>22.8275508880615</v>
+        <v>22.8275527954102</v>
       </c>
       <c r="H1221" t="n">
         <v>39792</v>
@@ -35865,7 +35865,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G1224" t="n">
-        <v>23.4864921569824</v>
+        <v>23.4864940643311</v>
       </c>
       <c r="H1224" t="n">
         <v>14439</v>
@@ -35923,7 +35923,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1226" t="n">
-        <v>23.7218284606934</v>
+        <v>23.7218265533447</v>
       </c>
       <c r="H1226" t="n">
         <v>13707</v>
@@ -35952,7 +35952,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1227" t="n">
-        <v>24.2395648956299</v>
+        <v>24.2395668029785</v>
       </c>
       <c r="H1227" t="n">
         <v>14100</v>
@@ -36097,7 +36097,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1232" t="n">
-        <v>22.8746204376221</v>
+        <v>22.8746185302734</v>
       </c>
       <c r="H1232" t="n">
         <v>16581</v>
@@ -36213,7 +36213,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1236" t="n">
-        <v>22.4510135650635</v>
+        <v>22.4510154724121</v>
       </c>
       <c r="H1236" t="n">
         <v>19108</v>
@@ -36242,7 +36242,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1237" t="n">
-        <v>22.3568801879883</v>
+        <v>22.3568820953369</v>
       </c>
       <c r="H1237" t="n">
         <v>15807</v>
@@ -36358,7 +36358,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G1241" t="n">
-        <v>21.3214015960693</v>
+        <v>21.321403503418</v>
       </c>
       <c r="H1241" t="n">
         <v>24454</v>
@@ -36387,7 +36387,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G1242" t="n">
-        <v>21.1802024841309</v>
+        <v>21.1802043914795</v>
       </c>
       <c r="H1242" t="n">
         <v>13607</v>
@@ -36416,7 +36416,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G1243" t="n">
-        <v>22.498083114624</v>
+        <v>22.4980812072754</v>
       </c>
       <c r="H1243" t="n">
         <v>32241</v>
@@ -36503,7 +36503,7 @@
         <v>22.915678024292</v>
       </c>
       <c r="G1246" t="n">
-        <v>22.2156791687012</v>
+        <v>22.2156810760498</v>
       </c>
       <c r="H1246" t="n">
         <v>6773</v>
@@ -36532,7 +36532,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1247" t="n">
-        <v>22.4510135650635</v>
+        <v>22.4510154724121</v>
       </c>
       <c r="H1247" t="n">
         <v>19850</v>
@@ -36561,7 +36561,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G1248" t="n">
-        <v>22.498083114624</v>
+        <v>22.4980812072754</v>
       </c>
       <c r="H1248" t="n">
         <v>10244</v>
@@ -36619,7 +36619,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1250" t="n">
-        <v>23.5335597991943</v>
+        <v>23.533561706543</v>
       </c>
       <c r="H1250" t="n">
         <v>46385</v>
@@ -36648,7 +36648,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G1251" t="n">
-        <v>23.4864921569824</v>
+        <v>23.4864940643311</v>
       </c>
       <c r="H1251" t="n">
         <v>65266</v>
@@ -36764,7 +36764,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1255" t="n">
-        <v>22.8746204376221</v>
+        <v>22.8746185302734</v>
       </c>
       <c r="H1255" t="n">
         <v>9052</v>
@@ -36793,7 +36793,7 @@
         <v>23.5468292236328</v>
       </c>
       <c r="G1256" t="n">
-        <v>22.8275508880615</v>
+        <v>22.8275527954102</v>
       </c>
       <c r="H1256" t="n">
         <v>31209</v>
@@ -36909,7 +36909,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1260" t="n">
-        <v>23.1570224761963</v>
+        <v>23.1570243835449</v>
       </c>
       <c r="H1260" t="n">
         <v>25058</v>
@@ -36938,7 +36938,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1261" t="n">
-        <v>22.4510135650635</v>
+        <v>22.4510154724121</v>
       </c>
       <c r="H1261" t="n">
         <v>25184</v>
@@ -36996,7 +36996,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1263" t="n">
-        <v>23.7218284606934</v>
+        <v>23.7218265533447</v>
       </c>
       <c r="H1263" t="n">
         <v>72638</v>
@@ -37431,7 +37431,7 @@
         <v>27.3337421417236</v>
       </c>
       <c r="G1278" t="n">
-        <v>26.4987850189209</v>
+        <v>26.4987869262695</v>
       </c>
       <c r="H1278" t="n">
         <v>95765</v>
@@ -37489,7 +37489,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1280" t="n">
-        <v>25.5798091888428</v>
+        <v>25.5798110961914</v>
       </c>
       <c r="H1280" t="n">
         <v>70356</v>
@@ -37518,7 +37518,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G1281" t="n">
-        <v>25.4850692749023</v>
+        <v>25.485071182251</v>
       </c>
       <c r="H1281" t="n">
         <v>54364</v>
@@ -37547,7 +37547,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1282" t="n">
-        <v>25.5798091888428</v>
+        <v>25.5798110961914</v>
       </c>
       <c r="H1282" t="n">
         <v>23120</v>
@@ -37576,7 +37576,7 @@
         <v>26.3141899108887</v>
       </c>
       <c r="G1283" t="n">
-        <v>25.6745491027832</v>
+        <v>25.6745471954346</v>
       </c>
       <c r="H1283" t="n">
         <v>4950</v>
@@ -37605,7 +37605,7 @@
         <v>26.071439743042</v>
       </c>
       <c r="G1284" t="n">
-        <v>25.4376983642578</v>
+        <v>25.4377002716064</v>
       </c>
       <c r="H1284" t="n">
         <v>30025</v>
@@ -37634,7 +37634,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1285" t="n">
-        <v>25.5798091888428</v>
+        <v>25.5798110961914</v>
       </c>
       <c r="H1285" t="n">
         <v>11480</v>
@@ -37750,7 +37750,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G1289" t="n">
-        <v>25.3429584503174</v>
+        <v>25.342960357666</v>
       </c>
       <c r="H1289" t="n">
         <v>23089</v>
@@ -37779,7 +37779,7 @@
         <v>26.6054916381836</v>
       </c>
       <c r="G1290" t="n">
-        <v>25.9587688446045</v>
+        <v>25.9587707519531</v>
       </c>
       <c r="H1290" t="n">
         <v>20344</v>
@@ -37895,7 +37895,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G1294" t="n">
-        <v>25.4850692749023</v>
+        <v>25.485071182251</v>
       </c>
       <c r="H1294" t="n">
         <v>35111</v>
@@ -37924,7 +37924,7 @@
         <v>26.2656402587891</v>
       </c>
       <c r="G1295" t="n">
-        <v>25.6271800994873</v>
+        <v>25.6271820068359</v>
       </c>
       <c r="H1295" t="n">
         <v>26453</v>
@@ -37982,7 +37982,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G1297" t="n">
-        <v>25.0587406158447</v>
+        <v>25.0587387084961</v>
       </c>
       <c r="H1297" t="n">
         <v>13083</v>
@@ -38098,7 +38098,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1301" t="n">
-        <v>25.0113697052002</v>
+        <v>25.0113677978516</v>
       </c>
       <c r="H1301" t="n">
         <v>13511</v>
@@ -38214,7 +38214,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1305" t="n">
-        <v>23.7797470092773</v>
+        <v>23.779748916626</v>
       </c>
       <c r="H1305" t="n">
         <v>297008</v>
@@ -38272,7 +38272,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1307" t="n">
-        <v>24.7745208740234</v>
+        <v>24.7745189666748</v>
       </c>
       <c r="H1307" t="n">
         <v>97414</v>
@@ -38417,7 +38417,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1312" t="n">
-        <v>24.3481884002686</v>
+        <v>24.3481864929199</v>
       </c>
       <c r="H1312" t="n">
         <v>20106</v>
@@ -38475,7 +38475,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1314" t="n">
-        <v>23.7797470092773</v>
+        <v>23.779748916626</v>
       </c>
       <c r="H1314" t="n">
         <v>19054</v>
@@ -38533,7 +38533,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1316" t="n">
-        <v>23.7797470092773</v>
+        <v>23.779748916626</v>
       </c>
       <c r="H1316" t="n">
         <v>27645</v>
@@ -38562,7 +38562,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1317" t="n">
-        <v>24.0639686584473</v>
+        <v>24.0639705657959</v>
       </c>
       <c r="H1317" t="n">
         <v>18064</v>
@@ -38591,7 +38591,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1318" t="n">
-        <v>23.5428981781006</v>
+        <v>23.542896270752</v>
       </c>
       <c r="H1318" t="n">
         <v>20396</v>
@@ -38620,7 +38620,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1319" t="n">
-        <v>23.6850090026855</v>
+        <v>23.6850070953369</v>
       </c>
       <c r="H1319" t="n">
         <v>4144</v>
@@ -38678,7 +38678,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1321" t="n">
-        <v>24.1587085723877</v>
+        <v>24.1587104797363</v>
       </c>
       <c r="H1321" t="n">
         <v>52546</v>
@@ -38736,7 +38736,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G1323" t="n">
-        <v>23.9218578338623</v>
+        <v>23.9218597412109</v>
       </c>
       <c r="H1323" t="n">
         <v>29989</v>
@@ -38794,7 +38794,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1325" t="n">
-        <v>23.7797470092773</v>
+        <v>23.779748916626</v>
       </c>
       <c r="H1325" t="n">
         <v>49423</v>
@@ -38823,7 +38823,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1326" t="n">
-        <v>23.5428981781006</v>
+        <v>23.542896270752</v>
       </c>
       <c r="H1326" t="n">
         <v>20003</v>
@@ -38968,7 +38968,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1331" t="n">
-        <v>24.5850391387939</v>
+        <v>24.5850410461426</v>
       </c>
       <c r="H1331" t="n">
         <v>98175</v>
@@ -39026,7 +39026,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1333" t="n">
-        <v>24.7745208740234</v>
+        <v>24.7745189666748</v>
       </c>
       <c r="H1333" t="n">
         <v>11347</v>
@@ -39055,7 +39055,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1334" t="n">
-        <v>25.5798091888428</v>
+        <v>25.5798110961914</v>
       </c>
       <c r="H1334" t="n">
         <v>94863</v>
@@ -39316,7 +39316,7 @@
         <v>23.3040790557861</v>
       </c>
       <c r="G1343" t="n">
-        <v>22.737606048584</v>
+        <v>22.7376098632812</v>
       </c>
       <c r="H1343" t="n">
         <v>17057</v>
@@ -39403,7 +39403,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G1346" t="n">
-        <v>21.0322875976562</v>
+        <v>21.0322895050049</v>
       </c>
       <c r="H1346" t="n">
         <v>61721</v>
@@ -39461,7 +39461,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1348" t="n">
-        <v>20.7954368591309</v>
+        <v>20.7954349517822</v>
       </c>
       <c r="H1348" t="n">
         <v>35094</v>
@@ -39519,7 +39519,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1350" t="n">
-        <v>21.1743965148926</v>
+        <v>21.1743984222412</v>
       </c>
       <c r="H1350" t="n">
         <v>34561</v>
@@ -39548,7 +39548,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1351" t="n">
-        <v>21.1743965148926</v>
+        <v>21.1743984222412</v>
       </c>
       <c r="H1351" t="n">
         <v>18138</v>
@@ -39664,7 +39664,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1355" t="n">
-        <v>20.7954368591309</v>
+        <v>20.7954349517822</v>
       </c>
       <c r="H1355" t="n">
         <v>40880</v>
@@ -39751,7 +39751,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G1358" t="n">
-        <v>19.9427757263184</v>
+        <v>19.942777633667</v>
       </c>
       <c r="H1358" t="n">
         <v>25115</v>
@@ -39838,7 +39838,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1361" t="n">
-        <v>21.1743965148926</v>
+        <v>21.1743984222412</v>
       </c>
       <c r="H1361" t="n">
         <v>15624</v>
@@ -39925,7 +39925,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1364" t="n">
-        <v>20.7954368591309</v>
+        <v>20.7954349517822</v>
       </c>
       <c r="H1364" t="n">
         <v>24196</v>
@@ -39954,7 +39954,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G1365" t="n">
-        <v>18.815372467041</v>
+        <v>18.8153705596924</v>
       </c>
       <c r="H1365" t="n">
         <v>116416</v>
@@ -39983,7 +39983,7 @@
         <v>19.759916305542</v>
       </c>
       <c r="G1366" t="n">
-        <v>19.279598236084</v>
+        <v>19.2795963287354</v>
       </c>
       <c r="H1366" t="n">
         <v>65681</v>
@@ -40041,7 +40041,7 @@
         <v>18.8763046264648</v>
       </c>
       <c r="G1368" t="n">
-        <v>18.4174613952637</v>
+        <v>18.4174633026123</v>
       </c>
       <c r="H1368" t="n">
         <v>26162</v>
@@ -40070,7 +40070,7 @@
         <v>18.8568840026855</v>
       </c>
       <c r="G1369" t="n">
-        <v>18.3985157012939</v>
+        <v>18.3985137939453</v>
       </c>
       <c r="H1369" t="n">
         <v>19594</v>
@@ -40186,7 +40186,7 @@
         <v>18.1966018676758</v>
       </c>
       <c r="G1373" t="n">
-        <v>17.7542819976807</v>
+        <v>17.7542839050293</v>
       </c>
       <c r="H1373" t="n">
         <v>16473</v>
@@ -40215,7 +40215,7 @@
         <v>19.1093444824219</v>
       </c>
       <c r="G1374" t="n">
-        <v>18.6448364257812</v>
+        <v>18.6448383331299</v>
       </c>
       <c r="H1374" t="n">
         <v>91119</v>
@@ -40273,7 +40273,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G1376" t="n">
-        <v>19.8006649017334</v>
+        <v>19.800666809082</v>
       </c>
       <c r="H1376" t="n">
         <v>91478</v>
@@ -40708,7 +40708,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1391" t="n">
-        <v>19.6601963043213</v>
+        <v>19.6601982116699</v>
       </c>
       <c r="H1391" t="n">
         <v>113261</v>
@@ -40853,7 +40853,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1396" t="n">
-        <v>22.7336254119873</v>
+        <v>22.7336273193359</v>
       </c>
       <c r="H1396" t="n">
         <v>118906</v>
@@ -40882,7 +40882,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1397" t="n">
-        <v>22.636058807373</v>
+        <v>22.6360607147217</v>
       </c>
       <c r="H1397" t="n">
         <v>109229</v>
@@ -40969,7 +40969,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1400" t="n">
         <v>108927</v>
@@ -40998,7 +40998,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1401" t="n">
-        <v>22.001859664917</v>
+        <v>22.0018577575684</v>
       </c>
       <c r="H1401" t="n">
         <v>65659</v>
@@ -41027,7 +41027,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1402" t="n">
-        <v>21.6603679656982</v>
+        <v>21.6603660583496</v>
       </c>
       <c r="H1402" t="n">
         <v>36928</v>
@@ -41143,7 +41143,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1406" t="n">
-        <v>23.0751190185547</v>
+        <v>23.0751209259033</v>
       </c>
       <c r="H1406" t="n">
         <v>96786</v>
@@ -41172,7 +41172,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1407" t="n">
-        <v>23.8556728363037</v>
+        <v>23.8556747436523</v>
       </c>
       <c r="H1407" t="n">
         <v>98631</v>
@@ -41201,7 +41201,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1408" t="n">
-        <v>23.0751190185547</v>
+        <v>23.0751209259033</v>
       </c>
       <c r="H1408" t="n">
         <v>52454</v>
@@ -41230,7 +41230,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1409" t="n">
-        <v>23.3678302764893</v>
+        <v>23.3678283691406</v>
       </c>
       <c r="H1409" t="n">
         <v>55523</v>
@@ -41259,7 +41259,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1410" t="n">
-        <v>24.2459506988525</v>
+        <v>24.2459526062012</v>
       </c>
       <c r="H1410" t="n">
         <v>44095</v>
@@ -41346,7 +41346,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G1413" t="n">
-        <v>24.5386581420898</v>
+        <v>24.5386562347412</v>
       </c>
       <c r="H1413" t="n">
         <v>60428</v>
@@ -41433,7 +41433,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1416" t="n">
-        <v>23.3678302764893</v>
+        <v>23.3678283691406</v>
       </c>
       <c r="H1416" t="n">
         <v>48294</v>
@@ -41462,7 +41462,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1417" t="n">
-        <v>22.7336254119873</v>
+        <v>22.7336273193359</v>
       </c>
       <c r="H1417" t="n">
         <v>78463</v>
@@ -41491,7 +41491,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1418" t="n">
-        <v>22.7336254119873</v>
+        <v>22.7336273193359</v>
       </c>
       <c r="H1418" t="n">
         <v>37481</v>
@@ -41607,7 +41607,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1422" t="n">
-        <v>22.3921356201172</v>
+        <v>22.3921375274658</v>
       </c>
       <c r="H1422" t="n">
         <v>18812</v>
@@ -41636,7 +41636,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>22.0506458282471</v>
+        <v>22.0506420135498</v>
       </c>
       <c r="H1423" t="n">
         <v>55220</v>
@@ -41694,7 +41694,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1425" t="n">
-        <v>22.3433494567871</v>
+        <v>22.3433513641357</v>
       </c>
       <c r="H1425" t="n">
         <v>23340</v>
@@ -41810,7 +41810,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1429" t="n">
-        <v>21.6603679656982</v>
+        <v>21.6603660583496</v>
       </c>
       <c r="H1429" t="n">
         <v>27223</v>
@@ -41839,7 +41839,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1430" t="n">
-        <v>21.5627975463867</v>
+        <v>21.5627994537354</v>
       </c>
       <c r="H1430" t="n">
         <v>69939</v>
@@ -41897,7 +41897,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1432" t="n">
-        <v>22.1482124328613</v>
+        <v>22.14821434021</v>
       </c>
       <c r="H1432" t="n">
         <v>49306</v>
@@ -41926,7 +41926,7 @@
         <v>22.25</v>
       </c>
       <c r="G1433" t="n">
-        <v>21.7091522216797</v>
+        <v>21.7091503143311</v>
       </c>
       <c r="H1433" t="n">
         <v>48514</v>
@@ -41955,7 +41955,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1434" t="n">
-        <v>22.0994262695312</v>
+        <v>22.0994281768799</v>
       </c>
       <c r="H1434" t="n">
         <v>38190</v>
@@ -42129,7 +42129,7 @@
         <v>22.25</v>
       </c>
       <c r="G1440" t="n">
-        <v>21.7091522216797</v>
+        <v>21.7091503143311</v>
       </c>
       <c r="H1440" t="n">
         <v>34966</v>
@@ -42158,7 +42158,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1441" t="n">
-        <v>21.5627975463867</v>
+        <v>21.5627994537354</v>
       </c>
       <c r="H1441" t="n">
         <v>74371</v>
@@ -42187,7 +42187,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1442" t="n">
-        <v>22.3433494567871</v>
+        <v>22.3433513641357</v>
       </c>
       <c r="H1442" t="n">
         <v>67943</v>
@@ -42216,7 +42216,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1443" t="n">
-        <v>22.0994262695312</v>
+        <v>22.0994281768799</v>
       </c>
       <c r="H1443" t="n">
         <v>31822</v>
@@ -42303,7 +42303,7 @@
         <v>22.25</v>
       </c>
       <c r="G1446" t="n">
-        <v>21.7091522216797</v>
+        <v>21.7091503143311</v>
       </c>
       <c r="H1446" t="n">
         <v>34680</v>
@@ -42332,7 +42332,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1447" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1447" t="n">
         <v>18969</v>
@@ -42361,7 +42361,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1448" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1448" t="n">
         <v>21948</v>
@@ -42448,7 +42448,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1451" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1451" t="n">
         <v>28545</v>
@@ -42477,7 +42477,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1452" t="n">
-        <v>21.6603679656982</v>
+        <v>21.6603660583496</v>
       </c>
       <c r="H1452" t="n">
         <v>32703</v>
@@ -42506,7 +42506,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1453" t="n">
-        <v>21.9042911529541</v>
+        <v>21.9042892456055</v>
       </c>
       <c r="H1453" t="n">
         <v>72050</v>
@@ -42535,7 +42535,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1454" t="n">
-        <v>21.6603679656982</v>
+        <v>21.6603660583496</v>
       </c>
       <c r="H1454" t="n">
         <v>52275</v>
@@ -42593,7 +42593,7 @@
         <v>22</v>
       </c>
       <c r="G1456" t="n">
-        <v>21.4652290344238</v>
+        <v>21.4652271270752</v>
       </c>
       <c r="H1456" t="n">
         <v>54384</v>
@@ -42622,7 +42622,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1457" t="n">
-        <v>21.074951171875</v>
+        <v>21.0749530792236</v>
       </c>
       <c r="H1457" t="n">
         <v>40203</v>
@@ -42651,7 +42651,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1458" t="n">
-        <v>20.8798122406006</v>
+        <v>20.879810333252</v>
       </c>
       <c r="H1458" t="n">
         <v>192758</v>
@@ -42680,7 +42680,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1459" t="n">
-        <v>21.3188743591309</v>
+        <v>21.3188762664795</v>
       </c>
       <c r="H1459" t="n">
         <v>56874</v>
@@ -42738,7 +42738,7 @@
         <v>21.5</v>
       </c>
       <c r="G1461" t="n">
-        <v>20.9773807525635</v>
+        <v>20.9773826599121</v>
       </c>
       <c r="H1461" t="n">
         <v>42275</v>
@@ -42767,7 +42767,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1462" t="n">
-        <v>21.2700901031494</v>
+        <v>21.2700881958008</v>
       </c>
       <c r="H1462" t="n">
         <v>52249</v>
@@ -42825,7 +42825,7 @@
         <v>20</v>
       </c>
       <c r="G1464" t="n">
-        <v>19.5138416290283</v>
+        <v>19.513843536377</v>
       </c>
       <c r="H1464" t="n">
         <v>140532</v>
@@ -42941,7 +42941,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1468" t="n">
-        <v>18.8308601379395</v>
+        <v>18.8308582305908</v>
       </c>
       <c r="H1468" t="n">
         <v>119630</v>
@@ -42970,7 +42970,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1469" t="n">
-        <v>19.0845375061035</v>
+        <v>19.0845394134521</v>
       </c>
       <c r="H1469" t="n">
         <v>77237</v>
@@ -42999,7 +42999,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1470" t="n">
-        <v>19.0650253295898</v>
+        <v>19.0650272369385</v>
       </c>
       <c r="H1470" t="n">
         <v>53735</v>
@@ -43057,7 +43057,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1472" t="n">
-        <v>18.9869709014893</v>
+        <v>18.9869689941406</v>
       </c>
       <c r="H1472" t="n">
         <v>57045</v>
@@ -43086,7 +43086,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1473" t="n">
-        <v>19.6601963043213</v>
+        <v>19.6601982116699</v>
       </c>
       <c r="H1473" t="n">
         <v>74930</v>
@@ -43202,7 +43202,7 @@
         <v>21</v>
       </c>
       <c r="G1477" t="n">
-        <v>20.489538192749</v>
+        <v>20.4895362854004</v>
       </c>
       <c r="H1477" t="n">
         <v>53759</v>
@@ -43492,7 +43492,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1487" t="n">
-        <v>18.8308601379395</v>
+        <v>18.8308582305908</v>
       </c>
       <c r="H1487" t="n">
         <v>43098</v>
@@ -43521,7 +43521,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1488" t="n">
-        <v>18.6162071228027</v>
+        <v>18.6162052154541</v>
       </c>
       <c r="H1488" t="n">
         <v>59185</v>
@@ -43579,7 +43579,7 @@
         <v>18.5</v>
       </c>
       <c r="G1490" t="n">
-        <v>18.0503063201904</v>
+        <v>18.0503044128418</v>
       </c>
       <c r="H1490" t="n">
         <v>82372</v>
@@ -43608,7 +43608,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1491" t="n">
-        <v>18.1088466644287</v>
+        <v>18.1088447570801</v>
       </c>
       <c r="H1491" t="n">
         <v>98046</v>
@@ -43695,7 +43695,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1494" t="n">
-        <v>18.1088466644287</v>
+        <v>18.1088447570801</v>
       </c>
       <c r="H1494" t="n">
         <v>122278</v>
@@ -43753,7 +43753,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1496" t="n">
-        <v>17.6014881134033</v>
+        <v>17.6014862060547</v>
       </c>
       <c r="H1496" t="n">
         <v>58459</v>
@@ -43898,7 +43898,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1501" t="n">
-        <v>18.3820419311523</v>
+        <v>18.3820400238037</v>
       </c>
       <c r="H1501" t="n">
         <v>36525</v>
@@ -43956,7 +43956,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1503" t="n">
-        <v>18.7528038024902</v>
+        <v>18.7528018951416</v>
       </c>
       <c r="H1503" t="n">
         <v>48675</v>
@@ -43985,7 +43985,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1504" t="n">
-        <v>18.6162071228027</v>
+        <v>18.6162052154541</v>
       </c>
       <c r="H1504" t="n">
         <v>64995</v>
@@ -44014,7 +44014,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1505" t="n">
-        <v>17.3087787628174</v>
+        <v>17.308780670166</v>
       </c>
       <c r="H1505" t="n">
         <v>125347</v>
@@ -44043,7 +44043,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1506" t="n">
-        <v>18.1673889160156</v>
+        <v>18.1673908233643</v>
       </c>
       <c r="H1506" t="n">
         <v>142776</v>
@@ -44072,7 +44072,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1507" t="n">
-        <v>18.128360748291</v>
+        <v>18.1283588409424</v>
       </c>
       <c r="H1507" t="n">
         <v>63388</v>
@@ -44101,7 +44101,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1508" t="n">
-        <v>16.6453075408936</v>
+        <v>16.6453094482422</v>
       </c>
       <c r="H1508" t="n">
         <v>280958</v>
@@ -44246,7 +44246,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1513" t="n">
-        <v>17.4063510894775</v>
+        <v>17.4063491821289</v>
       </c>
       <c r="H1513" t="n">
         <v>54000</v>
@@ -44275,7 +44275,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1514" t="n">
-        <v>17.1526679992676</v>
+        <v>17.1526699066162</v>
       </c>
       <c r="H1514" t="n">
         <v>59133</v>
@@ -44304,7 +44304,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1515" t="n">
-        <v>17.2112102508545</v>
+        <v>17.2112083435059</v>
       </c>
       <c r="H1515" t="n">
         <v>56490</v>
@@ -44391,7 +44391,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1518" t="n">
-        <v>17.5234298706055</v>
+        <v>17.5234317779541</v>
       </c>
       <c r="H1518" t="n">
         <v>61417</v>
@@ -44449,7 +44449,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1520" t="n">
-        <v>17.1136417388916</v>
+        <v>17.113639831543</v>
       </c>
       <c r="H1520" t="n">
         <v>47227</v>
@@ -44507,7 +44507,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1522" t="n">
-        <v>17.3478088378906</v>
+        <v>17.347806930542</v>
       </c>
       <c r="H1522" t="n">
         <v>58345</v>
@@ -44536,7 +44536,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1523" t="n">
-        <v>16.9965591430664</v>
+        <v>16.9965572357178</v>
       </c>
       <c r="H1523" t="n">
         <v>137407</v>
@@ -44565,7 +44565,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1524" t="n">
-        <v>17.1331558227539</v>
+        <v>17.1331539154053</v>
       </c>
       <c r="H1524" t="n">
         <v>33260</v>
@@ -44594,7 +44594,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1525" t="n">
-        <v>16.6648216247559</v>
+        <v>16.6648235321045</v>
       </c>
       <c r="H1525" t="n">
         <v>51768</v>
@@ -44710,7 +44710,7 @@
         <v>18</v>
       </c>
       <c r="G1529" t="n">
-        <v>17.5624580383301</v>
+        <v>17.5624599456787</v>
       </c>
       <c r="H1529" t="n">
         <v>58987</v>
@@ -44826,7 +44826,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1533" t="n">
-        <v>16.8209342956543</v>
+        <v>16.8209323883057</v>
       </c>
       <c r="H1533" t="n">
         <v>22910</v>
@@ -44855,7 +44855,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1534" t="n">
-        <v>16.5087108612061</v>
+        <v>16.5087127685547</v>
       </c>
       <c r="H1534" t="n">
         <v>104928</v>
@@ -44884,7 +44884,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1535" t="n">
-        <v>17.3087787628174</v>
+        <v>17.308780670166</v>
       </c>
       <c r="H1535" t="n">
         <v>67122</v>
@@ -62000,6 +62000,35 @@
         <v>67539</v>
       </c>
       <c r="I2125" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2126" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2126" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>26.4500007629395</v>
+      </c>
+      <c r="E2126" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F2126" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G2126" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H2126" t="n">
+        <v>47878</v>
+      </c>
+      <c r="I2126" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G2" t="n">
-        <v>7.5317325592041</v>
+        <v>7.53173303604126</v>
       </c>
       <c r="H2" t="n">
         <v>3452297</v>
@@ -456,7 +456,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G3" t="n">
-        <v>7.85126066207886</v>
+        <v>7.85125923156738</v>
       </c>
       <c r="H3" t="n">
         <v>1125391</v>
@@ -485,7 +485,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G4" t="n">
-        <v>7.75996589660645</v>
+        <v>7.7599663734436</v>
       </c>
       <c r="H4" t="n">
         <v>686773</v>
@@ -514,7 +514,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G5" t="n">
-        <v>7.75996589660645</v>
+        <v>7.7599663734436</v>
       </c>
       <c r="H5" t="n">
         <v>360346</v>
@@ -543,7 +543,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G6" t="n">
-        <v>7.66867399215698</v>
+        <v>7.66867351531982</v>
       </c>
       <c r="H6" t="n">
         <v>211023</v>
@@ -572,7 +572,7 @@
         <v>8.1253547668457</v>
       </c>
       <c r="G7" t="n">
-        <v>7.63945770263672</v>
+        <v>7.63945817947388</v>
       </c>
       <c r="H7" t="n">
         <v>72296</v>
@@ -601,7 +601,7 @@
         <v>8.31955623626709</v>
       </c>
       <c r="G8" t="n">
-        <v>7.82204627990723</v>
+        <v>7.82204532623291</v>
       </c>
       <c r="H8" t="n">
         <v>85887</v>
@@ -630,7 +630,7 @@
         <v>8.41859817504883</v>
       </c>
       <c r="G9" t="n">
-        <v>7.9151668548584</v>
+        <v>7.91516494750977</v>
       </c>
       <c r="H9" t="n">
         <v>85323</v>
@@ -659,7 +659,7 @@
         <v>8.10884761810303</v>
       </c>
       <c r="G10" t="n">
-        <v>7.623939037323</v>
+        <v>7.62393808364868</v>
       </c>
       <c r="H10" t="n">
         <v>23688</v>
@@ -688,7 +688,7 @@
         <v>8.42830753326416</v>
       </c>
       <c r="G11" t="n">
-        <v>7.92429542541504</v>
+        <v>7.92429399490356</v>
       </c>
       <c r="H11" t="n">
         <v>19928</v>
@@ -717,7 +717,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G12" t="n">
-        <v>7.5317325592041</v>
+        <v>7.53173303604126</v>
       </c>
       <c r="H12" t="n">
         <v>75575</v>
@@ -746,7 +746,7 @@
         <v>8.01077747344971</v>
       </c>
       <c r="G13" t="n">
-        <v>7.5317325592041</v>
+        <v>7.53173303604126</v>
       </c>
       <c r="H13" t="n">
         <v>73138</v>
@@ -775,7 +775,7 @@
         <v>7.86609792709351</v>
       </c>
       <c r="G14" t="n">
-        <v>7.3957052230835</v>
+        <v>7.39570569992065</v>
       </c>
       <c r="H14" t="n">
         <v>22352</v>
@@ -804,7 +804,7 @@
         <v>7.71656322479248</v>
       </c>
       <c r="G15" t="n">
-        <v>7.2551121711731</v>
+        <v>7.25511169433594</v>
       </c>
       <c r="H15" t="n">
         <v>329290</v>
@@ -891,7 +891,7 @@
         <v>8.00106716156006</v>
       </c>
       <c r="G18" t="n">
-        <v>7.52260303497314</v>
+        <v>7.5226035118103</v>
       </c>
       <c r="H18" t="n">
         <v>83534</v>
@@ -920,7 +920,7 @@
         <v>7.8651270866394</v>
       </c>
       <c r="G19" t="n">
-        <v>7.3947925567627</v>
+        <v>7.39479207992554</v>
       </c>
       <c r="H19" t="n">
         <v>36988</v>
@@ -978,7 +978,7 @@
         <v>7.97193717956543</v>
       </c>
       <c r="G21" t="n">
-        <v>7.49521493911743</v>
+        <v>7.49521446228027</v>
       </c>
       <c r="H21" t="n">
         <v>14400</v>
@@ -1007,7 +1007,7 @@
         <v>8.08068943023682</v>
       </c>
       <c r="G22" t="n">
-        <v>7.59746313095093</v>
+        <v>7.59746360778809</v>
       </c>
       <c r="H22" t="n">
         <v>16520</v>
@@ -1065,7 +1065,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G24" t="n">
-        <v>7.66867399215698</v>
+        <v>7.66867351531982</v>
       </c>
       <c r="H24" t="n">
         <v>80661</v>
@@ -1094,7 +1094,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G25" t="n">
-        <v>7.80561447143555</v>
+        <v>7.80561399459839</v>
       </c>
       <c r="H25" t="n">
         <v>57598</v>
@@ -1123,7 +1123,7 @@
         <v>8.37101936340332</v>
       </c>
       <c r="G26" t="n">
-        <v>7.87043237686157</v>
+        <v>7.87043285369873</v>
       </c>
       <c r="H26" t="n">
         <v>12597</v>
@@ -1152,7 +1152,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G27" t="n">
-        <v>7.80561447143555</v>
+        <v>7.80561399459839</v>
       </c>
       <c r="H27" t="n">
         <v>7454</v>
@@ -1239,7 +1239,7 @@
         <v>8.47394561767578</v>
       </c>
       <c r="G30" t="n">
-        <v>7.96720409393311</v>
+        <v>7.96720314025879</v>
       </c>
       <c r="H30" t="n">
         <v>238620</v>
@@ -1268,7 +1268,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G31" t="n">
-        <v>7.85126066207886</v>
+        <v>7.85125923156738</v>
       </c>
       <c r="H31" t="n">
         <v>21511</v>
@@ -1326,7 +1326,7 @@
         <v>8.20497798919678</v>
       </c>
       <c r="G33" t="n">
-        <v>7.71432113647461</v>
+        <v>7.71432065963745</v>
       </c>
       <c r="H33" t="n">
         <v>19958</v>
@@ -1355,7 +1355,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G34" t="n">
-        <v>7.80561447143555</v>
+        <v>7.80561399459839</v>
       </c>
       <c r="H34" t="n">
         <v>33613</v>
@@ -1384,7 +1384,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G35" t="n">
-        <v>7.66867399215698</v>
+        <v>7.66867351531982</v>
       </c>
       <c r="H35" t="n">
         <v>126429</v>
@@ -1413,7 +1413,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G36" t="n">
-        <v>7.66867399215698</v>
+        <v>7.66867351531982</v>
       </c>
       <c r="H36" t="n">
         <v>13515</v>
@@ -1471,7 +1471,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G38" t="n">
-        <v>7.80561447143555</v>
+        <v>7.80561399459839</v>
       </c>
       <c r="H38" t="n">
         <v>50515</v>
@@ -1500,7 +1500,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G39" t="n">
-        <v>7.85126066207886</v>
+        <v>7.85125923156738</v>
       </c>
       <c r="H39" t="n">
         <v>3319</v>
@@ -1529,7 +1529,7 @@
         <v>8.29625225067139</v>
       </c>
       <c r="G40" t="n">
-        <v>7.80013608932495</v>
+        <v>7.80013561248779</v>
       </c>
       <c r="H40" t="n">
         <v>43895</v>
@@ -1558,7 +1558,7 @@
         <v>8.12923908233643</v>
       </c>
       <c r="G41" t="n">
-        <v>7.64311027526855</v>
+        <v>7.64311075210571</v>
       </c>
       <c r="H41" t="n">
         <v>69304</v>
@@ -1587,7 +1587,7 @@
         <v>8.23410797119141</v>
       </c>
       <c r="G42" t="n">
-        <v>7.74170780181885</v>
+        <v>7.74170732498169</v>
       </c>
       <c r="H42" t="n">
         <v>27604</v>
@@ -1645,7 +1645,7 @@
         <v>8.15642833709717</v>
       </c>
       <c r="G44" t="n">
-        <v>7.66867399215698</v>
+        <v>7.66867351531982</v>
       </c>
       <c r="H44" t="n">
         <v>23162</v>
@@ -1674,7 +1674,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G45" t="n">
-        <v>7.85126066207886</v>
+        <v>7.85125923156738</v>
       </c>
       <c r="H45" t="n">
         <v>15675</v>
@@ -1703,7 +1703,7 @@
         <v>8.33606338500977</v>
       </c>
       <c r="G46" t="n">
-        <v>7.83756542205811</v>
+        <v>7.83756685256958</v>
       </c>
       <c r="H46" t="n">
         <v>4029</v>
@@ -1732,7 +1732,7 @@
         <v>7.99232816696167</v>
       </c>
       <c r="G47" t="n">
-        <v>7.51438665390015</v>
+        <v>7.5143871307373</v>
       </c>
       <c r="H47" t="n">
         <v>96901</v>
@@ -1761,7 +1761,7 @@
         <v>8.10787677764893</v>
       </c>
       <c r="G48" t="n">
-        <v>7.62302446365356</v>
+        <v>7.62302589416504</v>
       </c>
       <c r="H48" t="n">
         <v>5413</v>
@@ -1819,7 +1819,7 @@
         <v>8.1875</v>
       </c>
       <c r="G50" t="n">
-        <v>7.69788646697998</v>
+        <v>7.69788694381714</v>
       </c>
       <c r="H50" t="n">
         <v>28126</v>
@@ -1848,7 +1848,7 @@
         <v>8.44772911071777</v>
       </c>
       <c r="G51" t="n">
-        <v>7.94255542755127</v>
+        <v>7.94255399703979</v>
       </c>
       <c r="H51" t="n">
         <v>78995</v>
@@ -1877,7 +1877,7 @@
         <v>8.51667022705078</v>
       </c>
       <c r="G52" t="n">
-        <v>8.00737190246582</v>
+        <v>8.00737380981445</v>
       </c>
       <c r="H52" t="n">
         <v>142170</v>
@@ -1906,7 +1906,7 @@
         <v>8.57395935058594</v>
       </c>
       <c r="G53" t="n">
-        <v>8.06123638153076</v>
+        <v>8.06123542785645</v>
       </c>
       <c r="H53" t="n">
         <v>11925</v>
@@ -1935,7 +1935,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G54" t="n">
-        <v>8.24930095672607</v>
+        <v>8.24930191040039</v>
       </c>
       <c r="H54" t="n">
         <v>56090</v>
@@ -1993,7 +1993,7 @@
         <v>8.96721458435059</v>
       </c>
       <c r="G56" t="n">
-        <v>8.43097400665283</v>
+        <v>8.43097496032715</v>
       </c>
       <c r="H56" t="n">
         <v>37346</v>
@@ -2051,7 +2051,7 @@
         <v>9.46728229522705</v>
       </c>
       <c r="G58" t="n">
-        <v>8.90113830566406</v>
+        <v>8.90113639831543</v>
       </c>
       <c r="H58" t="n">
         <v>74281</v>
@@ -2080,7 +2080,7 @@
         <v>9.08859062194824</v>
       </c>
       <c r="G59" t="n">
-        <v>8.54509258270264</v>
+        <v>8.54509162902832</v>
       </c>
       <c r="H59" t="n">
         <v>57537</v>
@@ -2109,7 +2109,7 @@
         <v>8.75844955444336</v>
       </c>
       <c r="G60" t="n">
-        <v>8.23469352722168</v>
+        <v>8.234694480896</v>
       </c>
       <c r="H60" t="n">
         <v>78366</v>
@@ -2138,7 +2138,7 @@
         <v>8.71960926055908</v>
       </c>
       <c r="G61" t="n">
-        <v>8.19817638397217</v>
+        <v>8.19817543029785</v>
       </c>
       <c r="H61" t="n">
         <v>19712</v>
@@ -2167,7 +2167,7 @@
         <v>8.94973659515381</v>
       </c>
       <c r="G62" t="n">
-        <v>8.41454219818115</v>
+        <v>8.41454124450684</v>
       </c>
       <c r="H62" t="n">
         <v>40240</v>
@@ -2196,7 +2196,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G63" t="n">
-        <v>8.30772876739502</v>
+        <v>8.30772972106934</v>
       </c>
       <c r="H63" t="n">
         <v>12792</v>
@@ -2254,7 +2254,7 @@
         <v>9.20511054992676</v>
       </c>
       <c r="G65" t="n">
-        <v>8.65464496612549</v>
+        <v>8.65464401245117</v>
       </c>
       <c r="H65" t="n">
         <v>35765</v>
@@ -2283,7 +2283,7 @@
         <v>9.24395084381104</v>
       </c>
       <c r="G66" t="n">
-        <v>8.691162109375</v>
+        <v>8.69116306304932</v>
       </c>
       <c r="H66" t="n">
         <v>43076</v>
@@ -2341,7 +2341,7 @@
         <v>9.15656089782715</v>
       </c>
       <c r="G68" t="n">
-        <v>8.60899925231934</v>
+        <v>8.60899829864502</v>
       </c>
       <c r="H68" t="n">
         <v>39006</v>
@@ -2370,7 +2370,7 @@
         <v>9.29250144958496</v>
       </c>
       <c r="G69" t="n">
-        <v>8.73680782318115</v>
+        <v>8.73680877685547</v>
       </c>
       <c r="H69" t="n">
         <v>59640</v>
@@ -2399,7 +2399,7 @@
         <v>9.51583194732666</v>
       </c>
       <c r="G70" t="n">
-        <v>8.94678592681885</v>
+        <v>8.94678497314453</v>
       </c>
       <c r="H70" t="n">
         <v>51034</v>
@@ -2428,7 +2428,7 @@
         <v>9.51583194732666</v>
       </c>
       <c r="G71" t="n">
-        <v>8.94678592681885</v>
+        <v>8.94678497314453</v>
       </c>
       <c r="H71" t="n">
         <v>33820</v>
@@ -2457,7 +2457,7 @@
         <v>9.37115287780762</v>
       </c>
       <c r="G72" t="n">
-        <v>8.81075668334961</v>
+        <v>8.81075572967529</v>
       </c>
       <c r="H72" t="n">
         <v>39116</v>
@@ -2486,7 +2486,7 @@
         <v>9.63235282897949</v>
       </c>
       <c r="G73" t="n">
-        <v>9.0563383102417</v>
+        <v>9.05633926391602</v>
       </c>
       <c r="H73" t="n">
         <v>79933</v>
@@ -2515,7 +2515,7 @@
         <v>9.66148281097412</v>
       </c>
       <c r="G74" t="n">
-        <v>9.08372497558594</v>
+        <v>9.08372592926025</v>
       </c>
       <c r="H74" t="n">
         <v>127408</v>
@@ -2573,7 +2573,7 @@
         <v>9.61293315887451</v>
       </c>
       <c r="G76" t="n">
-        <v>9.03807926177979</v>
+        <v>9.03807830810547</v>
       </c>
       <c r="H76" t="n">
         <v>25372</v>
@@ -2602,7 +2602,7 @@
         <v>9.63332366943359</v>
       </c>
       <c r="G77" t="n">
-        <v>9.0572509765625</v>
+        <v>9.05725002288818</v>
       </c>
       <c r="H77" t="n">
         <v>123734</v>
@@ -2660,7 +2660,7 @@
         <v>9.70614910125732</v>
       </c>
       <c r="G79" t="n">
-        <v>9.12572193145752</v>
+        <v>9.12572288513184</v>
       </c>
       <c r="H79" t="n">
         <v>25765</v>
@@ -2718,7 +2718,7 @@
         <v>9.53525161743164</v>
       </c>
       <c r="G81" t="n">
-        <v>8.96504402160645</v>
+        <v>8.96504497528076</v>
       </c>
       <c r="H81" t="n">
         <v>14579</v>
@@ -2747,7 +2747,7 @@
         <v>9.26239967346191</v>
       </c>
       <c r="G82" t="n">
-        <v>8.70850658416748</v>
+        <v>8.7085075378418</v>
       </c>
       <c r="H82" t="n">
         <v>15137</v>
@@ -2805,7 +2805,7 @@
         <v>9.55467224121094</v>
       </c>
       <c r="G84" t="n">
-        <v>8.98330402374268</v>
+        <v>8.98330307006836</v>
       </c>
       <c r="H84" t="n">
         <v>24808</v>
@@ -2892,7 +2892,7 @@
         <v>8.98954772949219</v>
       </c>
       <c r="G87" t="n">
-        <v>8.45197200775146</v>
+        <v>8.45197296142578</v>
       </c>
       <c r="H87" t="n">
         <v>53966</v>
@@ -2921,7 +2921,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G88" t="n">
-        <v>8.30772876739502</v>
+        <v>8.30772972106934</v>
       </c>
       <c r="H88" t="n">
         <v>54203</v>
@@ -2950,7 +2950,7 @@
         <v>8.43413352966309</v>
       </c>
       <c r="G89" t="n">
-        <v>7.92977046966553</v>
+        <v>7.92977142333984</v>
       </c>
       <c r="H89" t="n">
         <v>72833</v>
@@ -2979,7 +2979,7 @@
         <v>8.77689933776855</v>
       </c>
       <c r="G90" t="n">
-        <v>8.25203990936279</v>
+        <v>8.25204086303711</v>
       </c>
       <c r="H90" t="n">
         <v>32211</v>
@@ -3008,7 +3008,7 @@
         <v>8.88467979431152</v>
       </c>
       <c r="G91" t="n">
-        <v>8.35337448120117</v>
+        <v>8.35337543487549</v>
       </c>
       <c r="H91" t="n">
         <v>47197</v>
@@ -3066,7 +3066,7 @@
         <v>9.07888126373291</v>
       </c>
       <c r="G93" t="n">
-        <v>8.535964012146</v>
+        <v>8.53596305847168</v>
       </c>
       <c r="H93" t="n">
         <v>63873</v>
@@ -3095,7 +3095,7 @@
         <v>9.12743091583252</v>
       </c>
       <c r="G94" t="n">
-        <v>8.58161067962646</v>
+        <v>8.58160972595215</v>
       </c>
       <c r="H94" t="n">
         <v>29067</v>
@@ -3124,7 +3124,7 @@
         <v>9.07888126373291</v>
       </c>
       <c r="G95" t="n">
-        <v>8.535964012146</v>
+        <v>8.53596305847168</v>
       </c>
       <c r="H95" t="n">
         <v>54068</v>
@@ -3153,7 +3153,7 @@
         <v>9.30706596374512</v>
       </c>
       <c r="G96" t="n">
-        <v>8.75050449371338</v>
+        <v>8.75050163269043</v>
       </c>
       <c r="H96" t="n">
         <v>28672</v>
@@ -3182,7 +3182,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G97" t="n">
-        <v>8.30772876739502</v>
+        <v>8.30772972106934</v>
       </c>
       <c r="H97" t="n">
         <v>82302</v>
@@ -3211,7 +3211,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G98" t="n">
-        <v>7.80561447143555</v>
+        <v>7.80561399459839</v>
       </c>
       <c r="H98" t="n">
         <v>31873</v>
@@ -3240,7 +3240,7 @@
         <v>8.48462677001953</v>
       </c>
       <c r="G99" t="n">
-        <v>7.97724485397339</v>
+        <v>7.97724580764771</v>
       </c>
       <c r="H99" t="n">
         <v>22913</v>
@@ -3269,7 +3269,7 @@
         <v>7.97193717956543</v>
       </c>
       <c r="G100" t="n">
-        <v>7.49521493911743</v>
+        <v>7.49521446228027</v>
       </c>
       <c r="H100" t="n">
         <v>32370</v>
@@ -3298,7 +3298,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G101" t="n">
-        <v>7.75996589660645</v>
+        <v>7.7599663734436</v>
       </c>
       <c r="H101" t="n">
         <v>13973</v>
@@ -3414,7 +3414,7 @@
         <v>8.81476783752441</v>
       </c>
       <c r="G105" t="n">
-        <v>8.28764343261719</v>
+        <v>8.28764533996582</v>
       </c>
       <c r="H105" t="n">
         <v>53875</v>
@@ -3472,7 +3472,7 @@
         <v>9.27502346038818</v>
       </c>
       <c r="G107" t="n">
-        <v>8.72037792205811</v>
+        <v>8.72037601470947</v>
       </c>
       <c r="H107" t="n">
         <v>77271</v>
@@ -3501,7 +3501,7 @@
         <v>9.25074768066406</v>
       </c>
       <c r="G108" t="n">
-        <v>8.69755077362061</v>
+        <v>8.69755172729492</v>
       </c>
       <c r="H108" t="n">
         <v>17543</v>
@@ -3559,7 +3559,7 @@
         <v>9.08664894104004</v>
       </c>
       <c r="G110" t="n">
-        <v>8.54326820373535</v>
+        <v>8.54326725006104</v>
       </c>
       <c r="H110" t="n">
         <v>32067</v>
@@ -3588,7 +3588,7 @@
         <v>9.19443035125732</v>
       </c>
       <c r="G111" t="n">
-        <v>8.64460277557373</v>
+        <v>8.64460468292236</v>
       </c>
       <c r="H111" t="n">
         <v>53266</v>
@@ -3704,7 +3704,7 @@
         <v>9.04586696624756</v>
       </c>
       <c r="G115" t="n">
-        <v>8.50492477416992</v>
+        <v>8.50492382049561</v>
       </c>
       <c r="H115" t="n">
         <v>61099</v>
@@ -3733,7 +3733,7 @@
         <v>9.2138500213623</v>
       </c>
       <c r="G116" t="n">
-        <v>8.66286182403564</v>
+        <v>8.66285991668701</v>
       </c>
       <c r="H116" t="n">
         <v>60391</v>
@@ -3762,7 +3762,7 @@
         <v>8.51084423065186</v>
       </c>
       <c r="G117" t="n">
-        <v>8.00189590454102</v>
+        <v>8.0018949508667</v>
       </c>
       <c r="H117" t="n">
         <v>101226</v>
@@ -3791,7 +3791,7 @@
         <v>8.49724960327148</v>
       </c>
       <c r="G118" t="n">
-        <v>7.98911333084106</v>
+        <v>7.98911428451538</v>
       </c>
       <c r="H118" t="n">
         <v>42084</v>
@@ -3820,7 +3820,7 @@
         <v>8.54482936859131</v>
       </c>
       <c r="G119" t="n">
-        <v>8.03384780883789</v>
+        <v>8.03384876251221</v>
       </c>
       <c r="H119" t="n">
         <v>132514</v>
@@ -3849,7 +3849,7 @@
         <v>8.65260982513428</v>
       </c>
       <c r="G120" t="n">
-        <v>8.1351842880249</v>
+        <v>8.13518333435059</v>
       </c>
       <c r="H120" t="n">
         <v>56877</v>
@@ -3965,7 +3965,7 @@
         <v>8.99149036407471</v>
       </c>
       <c r="G124" t="n">
-        <v>8.4537992477417</v>
+        <v>8.45379829406738</v>
       </c>
       <c r="H124" t="n">
         <v>78582</v>
@@ -4023,7 +4023,7 @@
         <v>9.42650032043457</v>
       </c>
       <c r="G126" t="n">
-        <v>8.86279392242432</v>
+        <v>8.86279487609863</v>
       </c>
       <c r="H126" t="n">
         <v>163957</v>
@@ -4052,7 +4052,7 @@
         <v>9.55078792572021</v>
       </c>
       <c r="G127" t="n">
-        <v>8.97965145111084</v>
+        <v>8.97964954376221</v>
       </c>
       <c r="H127" t="n">
         <v>112485</v>
@@ -4081,7 +4081,7 @@
         <v>9.48281764984131</v>
       </c>
       <c r="G128" t="n">
-        <v>8.91574478149414</v>
+        <v>8.91574573516846</v>
       </c>
       <c r="H128" t="n">
         <v>65394</v>
@@ -4139,7 +4139,7 @@
         <v>9.67119312286377</v>
       </c>
       <c r="G130" t="n">
-        <v>9.09285449981689</v>
+        <v>9.09285545349121</v>
       </c>
       <c r="H130" t="n">
         <v>32320</v>
@@ -4168,7 +4168,7 @@
         <v>9.35076236724854</v>
       </c>
       <c r="G131" t="n">
-        <v>8.79158687591553</v>
+        <v>8.79158592224121</v>
       </c>
       <c r="H131" t="n">
         <v>43129</v>
@@ -4226,7 +4226,7 @@
         <v>9.53525161743164</v>
       </c>
       <c r="G133" t="n">
-        <v>8.96504402160645</v>
+        <v>8.96504497528076</v>
       </c>
       <c r="H133" t="n">
         <v>44153</v>
@@ -4255,7 +4255,7 @@
         <v>9.5935115814209</v>
       </c>
       <c r="G134" t="n">
-        <v>9.01981925964355</v>
+        <v>9.01981735229492</v>
       </c>
       <c r="H134" t="n">
         <v>86092</v>
@@ -4284,7 +4284,7 @@
         <v>9.35755920410156</v>
       </c>
       <c r="G135" t="n">
-        <v>8.79797744750977</v>
+        <v>8.79797649383545</v>
       </c>
       <c r="H135" t="n">
         <v>37188</v>
@@ -4313,7 +4313,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G136" t="n">
-        <v>8.30772876739502</v>
+        <v>8.30772972106934</v>
       </c>
       <c r="H136" t="n">
         <v>90963</v>
@@ -4342,7 +4342,7 @@
         <v>8.77495670318604</v>
       </c>
       <c r="G137" t="n">
-        <v>8.25021266937256</v>
+        <v>8.25021457672119</v>
       </c>
       <c r="H137" t="n">
         <v>49854</v>
@@ -4371,7 +4371,7 @@
         <v>8.70018863677979</v>
       </c>
       <c r="G138" t="n">
-        <v>8.17991828918457</v>
+        <v>8.17991733551025</v>
       </c>
       <c r="H138" t="n">
         <v>33830</v>
@@ -4429,7 +4429,7 @@
         <v>8.80991268157959</v>
       </c>
       <c r="G140" t="n">
-        <v>8.28308010101318</v>
+        <v>8.28307914733887</v>
       </c>
       <c r="H140" t="n">
         <v>1874557</v>
@@ -4458,7 +4458,7 @@
         <v>8.66523265838623</v>
       </c>
       <c r="G141" t="n">
-        <v>8.14705276489258</v>
+        <v>8.14705181121826</v>
       </c>
       <c r="H141" t="n">
         <v>15104</v>
@@ -4487,7 +4487,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G142" t="n">
-        <v>8.24930095672607</v>
+        <v>8.24930191040039</v>
       </c>
       <c r="H142" t="n">
         <v>40885</v>
@@ -4516,7 +4516,7 @@
         <v>8.8798246383667</v>
       </c>
       <c r="G143" t="n">
-        <v>8.34881114959717</v>
+        <v>8.34881019592285</v>
       </c>
       <c r="H143" t="n">
         <v>25023</v>
@@ -4574,7 +4574,7 @@
         <v>8.76815986633301</v>
       </c>
       <c r="G145" t="n">
-        <v>8.24382305145264</v>
+        <v>8.24382400512695</v>
       </c>
       <c r="H145" t="n">
         <v>27159</v>
@@ -4603,7 +4603,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G146" t="n">
-        <v>8.30772876739502</v>
+        <v>8.30772972106934</v>
       </c>
       <c r="H146" t="n">
         <v>74791</v>
@@ -4632,7 +4632,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G147" t="n">
-        <v>8.24930095672607</v>
+        <v>8.24930191040039</v>
       </c>
       <c r="H147" t="n">
         <v>46996</v>
@@ -4661,7 +4661,7 @@
         <v>8.98178005218506</v>
       </c>
       <c r="G148" t="n">
-        <v>8.44467067718506</v>
+        <v>8.44466972351074</v>
       </c>
       <c r="H148" t="n">
         <v>99143</v>
@@ -4719,7 +4719,7 @@
         <v>8.91380977630615</v>
       </c>
       <c r="G150" t="n">
-        <v>8.38076210021973</v>
+        <v>8.38076305389404</v>
       </c>
       <c r="H150" t="n">
         <v>37840</v>
@@ -4835,7 +4835,7 @@
         <v>8.65260982513428</v>
       </c>
       <c r="G154" t="n">
-        <v>8.1351842880249</v>
+        <v>8.13518333435059</v>
       </c>
       <c r="H154" t="n">
         <v>47268</v>
@@ -4864,7 +4864,7 @@
         <v>8.68659496307373</v>
       </c>
       <c r="G155" t="n">
-        <v>8.16713523864746</v>
+        <v>8.16713714599609</v>
       </c>
       <c r="H155" t="n">
         <v>67644</v>
@@ -4893,7 +4893,7 @@
         <v>8.61474132537842</v>
       </c>
       <c r="G156" t="n">
-        <v>8.09957981109619</v>
+        <v>8.09957885742188</v>
       </c>
       <c r="H156" t="n">
         <v>15804</v>
@@ -4951,7 +4951,7 @@
         <v>8.87497043609619</v>
       </c>
       <c r="G158" t="n">
-        <v>8.34424591064453</v>
+        <v>8.34424781799316</v>
       </c>
       <c r="H158" t="n">
         <v>27757</v>
@@ -4980,7 +4980,7 @@
         <v>8.90410041809082</v>
       </c>
       <c r="G159" t="n">
-        <v>8.3716344833374</v>
+        <v>8.37163543701172</v>
       </c>
       <c r="H159" t="n">
         <v>31397</v>
@@ -5009,7 +5009,7 @@
         <v>8.96430206298828</v>
       </c>
       <c r="G160" t="n">
-        <v>8.42823600769043</v>
+        <v>8.42823696136475</v>
       </c>
       <c r="H160" t="n">
         <v>66416</v>
@@ -5038,7 +5038,7 @@
         <v>9.20316886901855</v>
       </c>
       <c r="G161" t="n">
-        <v>8.65281772613525</v>
+        <v>8.65281867980957</v>
       </c>
       <c r="H161" t="n">
         <v>24925</v>
@@ -5067,7 +5067,7 @@
         <v>9.20316886901855</v>
       </c>
       <c r="G162" t="n">
-        <v>8.65281772613525</v>
+        <v>8.65281867980957</v>
       </c>
       <c r="H162" t="n">
         <v>10411</v>
@@ -5125,7 +5125,7 @@
         <v>9.21482086181641</v>
       </c>
       <c r="G164" t="n">
-        <v>8.66377353668213</v>
+        <v>8.66377544403076</v>
       </c>
       <c r="H164" t="n">
         <v>26339</v>
@@ -5154,7 +5154,7 @@
         <v>9.61584568023682</v>
       </c>
       <c r="G165" t="n">
-        <v>9.04081630706787</v>
+        <v>9.04081726074219</v>
       </c>
       <c r="H165" t="n">
         <v>44742</v>
@@ -5212,7 +5212,7 @@
         <v>9.40222454071045</v>
       </c>
       <c r="G167" t="n">
-        <v>8.8399715423584</v>
+        <v>8.83997058868408</v>
       </c>
       <c r="H167" t="n">
         <v>18153</v>
@@ -5241,7 +5241,7 @@
         <v>9.51583194732666</v>
       </c>
       <c r="G168" t="n">
-        <v>8.94678592681885</v>
+        <v>8.94678497314453</v>
       </c>
       <c r="H168" t="n">
         <v>11146</v>
@@ -5270,7 +5270,7 @@
         <v>9.33522605895996</v>
       </c>
       <c r="G169" t="n">
-        <v>8.7769775390625</v>
+        <v>8.77697849273682</v>
       </c>
       <c r="H169" t="n">
         <v>11871</v>
@@ -5328,7 +5328,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G171" t="n">
-        <v>8.99243068695068</v>
+        <v>8.992431640625</v>
       </c>
       <c r="H171" t="n">
         <v>18448</v>
@@ -5386,7 +5386,7 @@
         <v>9.72751140594482</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14580631256104</v>
+        <v>9.14580535888672</v>
       </c>
       <c r="H173" t="n">
         <v>31014</v>
@@ -5415,7 +5415,7 @@
         <v>9.89258098602295</v>
       </c>
       <c r="G174" t="n">
-        <v>9.30100440979004</v>
+        <v>9.30100345611572</v>
       </c>
       <c r="H174" t="n">
         <v>22663</v>
@@ -5502,7 +5502,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G177" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H177" t="n">
         <v>18160</v>
@@ -5531,7 +5531,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G178" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H178" t="n">
         <v>16440</v>
@@ -5560,7 +5560,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G179" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H179" t="n">
         <v>13022</v>
@@ -5589,7 +5589,7 @@
         <v>10.2440853118896</v>
       </c>
       <c r="G180" t="n">
-        <v>9.6314868927002</v>
+        <v>9.63148784637451</v>
       </c>
       <c r="H180" t="n">
         <v>17545</v>
@@ -5618,7 +5618,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G181" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H181" t="n">
         <v>12625</v>
@@ -5647,7 +5647,7 @@
         <v>10.1372737884521</v>
       </c>
       <c r="G182" t="n">
-        <v>9.5310640335083</v>
+        <v>9.53106498718262</v>
       </c>
       <c r="H182" t="n">
         <v>36436</v>
@@ -5734,7 +5734,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G185" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H185" t="n">
         <v>8445</v>
@@ -5792,7 +5792,7 @@
         <v>10.0304641723633</v>
       </c>
       <c r="G187" t="n">
-        <v>9.43064212799072</v>
+        <v>9.43064117431641</v>
       </c>
       <c r="H187" t="n">
         <v>7232</v>
@@ -5821,7 +5821,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G188" t="n">
-        <v>9.58584022521973</v>
+        <v>9.58584117889404</v>
       </c>
       <c r="H188" t="n">
         <v>23356</v>
@@ -5908,7 +5908,7 @@
         <v>9.99939155578613</v>
       </c>
       <c r="G191" t="n">
-        <v>9.40142822265625</v>
+        <v>9.40142631530762</v>
       </c>
       <c r="H191" t="n">
         <v>15472</v>
@@ -5937,7 +5937,7 @@
         <v>9.8595666885376</v>
       </c>
       <c r="G192" t="n">
-        <v>9.26996326446533</v>
+        <v>9.26996421813965</v>
       </c>
       <c r="H192" t="n">
         <v>21463</v>
@@ -5995,7 +5995,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G194" t="n">
-        <v>8.99243068695068</v>
+        <v>8.992431640625</v>
       </c>
       <c r="H194" t="n">
         <v>37882</v>
@@ -6053,7 +6053,7 @@
         <v>9.66148281097412</v>
       </c>
       <c r="G196" t="n">
-        <v>9.08372497558594</v>
+        <v>9.08372592926025</v>
       </c>
       <c r="H196" t="n">
         <v>20981</v>
@@ -6082,7 +6082,7 @@
         <v>9.66536712646484</v>
       </c>
       <c r="G197" t="n">
-        <v>9.08737659454346</v>
+        <v>9.08737850189209</v>
       </c>
       <c r="H197" t="n">
         <v>16116</v>
@@ -6198,7 +6198,7 @@
         <v>8.87497043609619</v>
       </c>
       <c r="G201" t="n">
-        <v>8.34424591064453</v>
+        <v>8.34424781799316</v>
       </c>
       <c r="H201" t="n">
         <v>197330</v>
@@ -6256,7 +6256,7 @@
         <v>9.25657367706299</v>
       </c>
       <c r="G203" t="n">
-        <v>8.70302963256836</v>
+        <v>8.70302867889404</v>
       </c>
       <c r="H203" t="n">
         <v>45319</v>
@@ -6285,7 +6285,7 @@
         <v>9.5935115814209</v>
       </c>
       <c r="G204" t="n">
-        <v>9.01981925964355</v>
+        <v>9.01981735229492</v>
       </c>
       <c r="H204" t="n">
         <v>85559</v>
@@ -6343,7 +6343,7 @@
         <v>9.61293315887451</v>
       </c>
       <c r="G206" t="n">
-        <v>9.03807926177979</v>
+        <v>9.03807830810547</v>
       </c>
       <c r="H206" t="n">
         <v>13515</v>
@@ -6372,7 +6372,7 @@
         <v>9.67119312286377</v>
       </c>
       <c r="G207" t="n">
-        <v>9.09285449981689</v>
+        <v>9.09285545349121</v>
       </c>
       <c r="H207" t="n">
         <v>36508</v>
@@ -6401,7 +6401,7 @@
         <v>9.71003341674805</v>
       </c>
       <c r="G208" t="n">
-        <v>9.12937450408936</v>
+        <v>9.12937355041504</v>
       </c>
       <c r="H208" t="n">
         <v>9796</v>
@@ -6430,7 +6430,7 @@
         <v>9.47699165344238</v>
       </c>
       <c r="G209" t="n">
-        <v>8.91026592254639</v>
+        <v>8.91026782989502</v>
       </c>
       <c r="H209" t="n">
         <v>16863</v>
@@ -6459,7 +6459,7 @@
         <v>9.47699165344238</v>
       </c>
       <c r="G210" t="n">
-        <v>8.91026592254639</v>
+        <v>8.91026782989502</v>
       </c>
       <c r="H210" t="n">
         <v>24429</v>
@@ -6488,7 +6488,7 @@
         <v>9.62264347076416</v>
       </c>
       <c r="G211" t="n">
-        <v>9.04720973968506</v>
+        <v>9.04720878601074</v>
       </c>
       <c r="H211" t="n">
         <v>14681</v>
@@ -6517,7 +6517,7 @@
         <v>9.66148281097412</v>
       </c>
       <c r="G212" t="n">
-        <v>9.08372497558594</v>
+        <v>9.08372592926025</v>
       </c>
       <c r="H212" t="n">
         <v>22204</v>
@@ -6575,7 +6575,7 @@
         <v>9.98191356658936</v>
       </c>
       <c r="G214" t="n">
-        <v>9.38499450683594</v>
+        <v>9.38499355316162</v>
       </c>
       <c r="H214" t="n">
         <v>18233</v>
@@ -6662,7 +6662,7 @@
         <v>10.0013341903687</v>
       </c>
       <c r="G217" t="n">
-        <v>9.40325355529785</v>
+        <v>9.40325450897217</v>
       </c>
       <c r="H217" t="n">
         <v>50349</v>
@@ -6691,7 +6691,7 @@
         <v>10.0790138244629</v>
       </c>
       <c r="G218" t="n">
-        <v>9.47628974914551</v>
+        <v>9.47628784179688</v>
       </c>
       <c r="H218" t="n">
         <v>27030</v>
@@ -6836,7 +6836,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G223" t="n">
-        <v>9.93275737762451</v>
+        <v>9.93275833129883</v>
       </c>
       <c r="H223" t="n">
         <v>12586</v>
@@ -6865,7 +6865,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G224" t="n">
-        <v>9.98753356933594</v>
+        <v>9.98753452301025</v>
       </c>
       <c r="H224" t="n">
         <v>8445</v>
@@ -6894,7 +6894,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G225" t="n">
-        <v>9.73191070556641</v>
+        <v>9.73191165924072</v>
       </c>
       <c r="H225" t="n">
         <v>32595</v>
@@ -6923,7 +6923,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G226" t="n">
-        <v>9.98753356933594</v>
+        <v>9.98753452301025</v>
       </c>
       <c r="H226" t="n">
         <v>36732</v>
@@ -6981,7 +6981,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G228" t="n">
-        <v>9.73191070556641</v>
+        <v>9.73191165924072</v>
       </c>
       <c r="H228" t="n">
         <v>19355</v>
@@ -7039,7 +7039,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G230" t="n">
-        <v>9.73191070556641</v>
+        <v>9.73191165924072</v>
       </c>
       <c r="H230" t="n">
         <v>20369</v>
@@ -7068,7 +7068,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G231" t="n">
-        <v>9.73191070556641</v>
+        <v>9.73191165924072</v>
       </c>
       <c r="H231" t="n">
         <v>21922</v>
@@ -7097,7 +7097,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G232" t="n">
-        <v>9.8779821395874</v>
+        <v>9.87798118591309</v>
       </c>
       <c r="H232" t="n">
         <v>15426</v>
@@ -7184,7 +7184,7 @@
         <v>10.214955329895</v>
       </c>
       <c r="G235" t="n">
-        <v>9.60410022735596</v>
+        <v>9.60410118103027</v>
       </c>
       <c r="H235" t="n">
         <v>164121</v>
@@ -7213,7 +7213,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G236" t="n">
-        <v>9.71365165710449</v>
+        <v>9.71365261077881</v>
       </c>
       <c r="H236" t="n">
         <v>14595</v>
@@ -7242,7 +7242,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G237" t="n">
-        <v>9.76842880249023</v>
+        <v>9.76842784881592</v>
       </c>
       <c r="H237" t="n">
         <v>21826</v>
@@ -7271,7 +7271,7 @@
         <v>10.4285745620728</v>
       </c>
       <c r="G238" t="n">
-        <v>9.80494403839111</v>
+        <v>9.80494594573975</v>
       </c>
       <c r="H238" t="n">
         <v>22184</v>
@@ -7416,7 +7416,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G243" t="n">
-        <v>9.8779821395874</v>
+        <v>9.87798118591309</v>
       </c>
       <c r="H243" t="n">
         <v>23214</v>
@@ -7474,7 +7474,7 @@
         <v>10.6033563613892</v>
       </c>
       <c r="G245" t="n">
-        <v>9.96927547454834</v>
+        <v>9.96927452087402</v>
       </c>
       <c r="H245" t="n">
         <v>41422</v>
@@ -7532,7 +7532,7 @@
         <v>10.4285745620728</v>
       </c>
       <c r="G247" t="n">
-        <v>9.80494403839111</v>
+        <v>9.80494594573975</v>
       </c>
       <c r="H247" t="n">
         <v>20516</v>
@@ -7561,7 +7561,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G248" t="n">
-        <v>9.93275737762451</v>
+        <v>9.93275833129883</v>
       </c>
       <c r="H248" t="n">
         <v>13400</v>
@@ -7590,7 +7590,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G249" t="n">
-        <v>9.95101547241211</v>
+        <v>9.95101451873779</v>
       </c>
       <c r="H249" t="n">
         <v>9574</v>
@@ -7648,7 +7648,7 @@
         <v>11.1082782745361</v>
       </c>
       <c r="G251" t="n">
-        <v>10.4440021514893</v>
+        <v>10.4440031051636</v>
       </c>
       <c r="H251" t="n">
         <v>24083</v>
@@ -7706,7 +7706,7 @@
         <v>11.2636375427246</v>
       </c>
       <c r="G253" t="n">
-        <v>10.5900716781616</v>
+        <v>10.5900726318359</v>
       </c>
       <c r="H253" t="n">
         <v>6565</v>
@@ -7735,7 +7735,7 @@
         <v>11.3413181304932</v>
       </c>
       <c r="G254" t="n">
-        <v>10.6631059646606</v>
+        <v>10.663106918335</v>
       </c>
       <c r="H254" t="n">
         <v>30537</v>
@@ -7793,7 +7793,7 @@
         <v>11.0694379806519</v>
       </c>
       <c r="G256" t="n">
-        <v>10.4074869155884</v>
+        <v>10.4074859619141</v>
       </c>
       <c r="H256" t="n">
         <v>16489</v>
@@ -7822,7 +7822,7 @@
         <v>11.0305967330933</v>
       </c>
       <c r="G257" t="n">
-        <v>10.3709678649902</v>
+        <v>10.3709659576416</v>
       </c>
       <c r="H257" t="n">
         <v>11495</v>
@@ -7851,7 +7851,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G258" t="n">
-        <v>10.2614154815674</v>
+        <v>10.2614135742188</v>
       </c>
       <c r="H258" t="n">
         <v>15387</v>
@@ -7880,7 +7880,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G259" t="n">
-        <v>9.95101547241211</v>
+        <v>9.95101451873779</v>
       </c>
       <c r="H259" t="n">
         <v>25241</v>
@@ -7909,7 +7909,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G260" t="n">
-        <v>9.91450023651123</v>
+        <v>9.9144983291626</v>
       </c>
       <c r="H260" t="n">
         <v>7038</v>
@@ -7938,7 +7938,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G261" t="n">
-        <v>9.78668689727783</v>
+        <v>9.78668594360352</v>
       </c>
       <c r="H261" t="n">
         <v>10557</v>
@@ -8025,7 +8025,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G264" t="n">
-        <v>9.876145362854</v>
+        <v>9.87614440917969</v>
       </c>
       <c r="H264" t="n">
         <v>9400</v>
@@ -8083,7 +8083,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G266" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H266" t="n">
         <v>31281</v>
@@ -8112,7 +8112,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G267" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H267" t="n">
         <v>28019</v>
@@ -8170,7 +8170,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G269" t="n">
-        <v>10.0788259506226</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H269" t="n">
         <v>9058</v>
@@ -8199,7 +8199,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G270" t="n">
-        <v>9.93142127990723</v>
+        <v>9.93142223358154</v>
       </c>
       <c r="H270" t="n">
         <v>4825</v>
@@ -8228,7 +8228,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G271" t="n">
-        <v>10.1341028213501</v>
+        <v>10.1341037750244</v>
       </c>
       <c r="H271" t="n">
         <v>105178</v>
@@ -8286,7 +8286,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G273" t="n">
-        <v>10.1341028213501</v>
+        <v>10.1341037750244</v>
       </c>
       <c r="H273" t="n">
         <v>6761</v>
@@ -8373,7 +8373,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G276" t="n">
-        <v>9.83929347991943</v>
+        <v>9.83929443359375</v>
       </c>
       <c r="H276" t="n">
         <v>16684</v>
@@ -8431,7 +8431,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G278" t="n">
-        <v>9.93142127990723</v>
+        <v>9.93142223358154</v>
       </c>
       <c r="H278" t="n">
         <v>68449</v>
@@ -8460,7 +8460,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G279" t="n">
-        <v>10.1341028213501</v>
+        <v>10.1341037750244</v>
       </c>
       <c r="H279" t="n">
         <v>63120</v>
@@ -8576,7 +8576,7 @@
         <v>10.4091548919678</v>
       </c>
       <c r="G283" t="n">
-        <v>9.876145362854</v>
+        <v>9.87614440917969</v>
       </c>
       <c r="H283" t="n">
         <v>74802</v>
@@ -8663,7 +8663,7 @@
         <v>10.6421957015991</v>
       </c>
       <c r="G286" t="n">
-        <v>10.0972528457642</v>
+        <v>10.0972518920898</v>
       </c>
       <c r="H286" t="n">
         <v>15436</v>
@@ -8721,7 +8721,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G288" t="n">
-        <v>10.3367862701416</v>
+        <v>10.3367853164673</v>
       </c>
       <c r="H288" t="n">
         <v>11081</v>
@@ -8750,7 +8750,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G289" t="n">
-        <v>10.3552122116089</v>
+        <v>10.3552112579346</v>
       </c>
       <c r="H289" t="n">
         <v>9843</v>
@@ -8779,7 +8779,7 @@
         <v>10.8752374649048</v>
       </c>
       <c r="G290" t="n">
-        <v>10.318359375</v>
+        <v>10.3183603286743</v>
       </c>
       <c r="H290" t="n">
         <v>20080</v>
@@ -8808,7 +8808,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G291" t="n">
-        <v>10.3367862701416</v>
+        <v>10.3367853164673</v>
       </c>
       <c r="H291" t="n">
         <v>11184</v>
@@ -8837,7 +8837,7 @@
         <v>10.8558168411255</v>
       </c>
       <c r="G292" t="n">
-        <v>10.2999353408813</v>
+        <v>10.299934387207</v>
       </c>
       <c r="H292" t="n">
         <v>10827</v>
@@ -8866,7 +8866,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G293" t="n">
-        <v>9.93142127990723</v>
+        <v>9.93142223358154</v>
       </c>
       <c r="H293" t="n">
         <v>15397</v>
@@ -8895,7 +8895,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G294" t="n">
-        <v>9.76559257507324</v>
+        <v>9.76559162139893</v>
       </c>
       <c r="H294" t="n">
         <v>19630</v>
@@ -8924,7 +8924,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G295" t="n">
-        <v>10.2446584701538</v>
+        <v>10.2446594238281</v>
       </c>
       <c r="H295" t="n">
         <v>20005</v>
@@ -8953,7 +8953,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G296" t="n">
-        <v>10.3367862701416</v>
+        <v>10.3367853164673</v>
       </c>
       <c r="H296" t="n">
         <v>17062</v>
@@ -9011,7 +9011,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G298" t="n">
-        <v>9.93142127990723</v>
+        <v>9.93142223358154</v>
       </c>
       <c r="H298" t="n">
         <v>15459</v>
@@ -9127,7 +9127,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G302" t="n">
-        <v>9.83929347991943</v>
+        <v>9.83929443359375</v>
       </c>
       <c r="H302" t="n">
         <v>1056</v>
@@ -9156,7 +9156,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G303" t="n">
-        <v>10.0051259994507</v>
+        <v>10.0051240921021</v>
       </c>
       <c r="H303" t="n">
         <v>22348</v>
@@ -9185,7 +9185,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G304" t="n">
-        <v>10.0419750213623</v>
+        <v>10.0419759750366</v>
       </c>
       <c r="H304" t="n">
         <v>9296</v>
@@ -9214,7 +9214,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G305" t="n">
-        <v>10.1341028213501</v>
+        <v>10.1341037750244</v>
       </c>
       <c r="H305" t="n">
         <v>4341</v>
@@ -9243,7 +9243,7 @@
         <v>10.253794670105</v>
       </c>
       <c r="G306" t="n">
-        <v>9.72873973846436</v>
+        <v>9.72873878479004</v>
       </c>
       <c r="H306" t="n">
         <v>15350</v>
@@ -9272,7 +9272,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G307" t="n">
-        <v>9.93142127990723</v>
+        <v>9.93142223358154</v>
       </c>
       <c r="H307" t="n">
         <v>5672</v>
@@ -9330,7 +9330,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G309" t="n">
-        <v>9.93142127990723</v>
+        <v>9.93142223358154</v>
       </c>
       <c r="H309" t="n">
         <v>10750</v>
@@ -9359,7 +9359,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G310" t="n">
-        <v>10.1893815994263</v>
+        <v>10.189380645752</v>
       </c>
       <c r="H310" t="n">
         <v>28717</v>
@@ -9388,7 +9388,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G311" t="n">
-        <v>10.1893815994263</v>
+        <v>10.189380645752</v>
       </c>
       <c r="H311" t="n">
         <v>15871</v>
@@ -9417,7 +9417,7 @@
         <v>10.8752374649048</v>
       </c>
       <c r="G312" t="n">
-        <v>10.318359375</v>
+        <v>10.3183603286743</v>
       </c>
       <c r="H312" t="n">
         <v>7644</v>
@@ -9504,7 +9504,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G315" t="n">
-        <v>10.4104881286621</v>
+        <v>10.4104890823364</v>
       </c>
       <c r="H315" t="n">
         <v>51796</v>
@@ -9562,7 +9562,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G317" t="n">
-        <v>11.9766683578491</v>
+        <v>11.9766674041748</v>
       </c>
       <c r="H317" t="n">
         <v>40875</v>
@@ -9591,7 +9591,7 @@
         <v>11.6908798217773</v>
       </c>
       <c r="G318" t="n">
-        <v>11.0922384262085</v>
+        <v>11.0922365188599</v>
       </c>
       <c r="H318" t="n">
         <v>45226</v>
@@ -9649,7 +9649,7 @@
         <v>11.943341255188</v>
       </c>
       <c r="G320" t="n">
-        <v>11.3317718505859</v>
+        <v>11.3317708969116</v>
       </c>
       <c r="H320" t="n">
         <v>26477</v>
@@ -9678,7 +9678,7 @@
         <v>11.943341255188</v>
       </c>
       <c r="G321" t="n">
-        <v>11.3317718505859</v>
+        <v>11.3317708969116</v>
       </c>
       <c r="H321" t="n">
         <v>65085</v>
@@ -9707,7 +9707,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G322" t="n">
-        <v>11.460750579834</v>
+        <v>11.4607515335083</v>
       </c>
       <c r="H322" t="n">
         <v>18075</v>
@@ -9765,7 +9765,7 @@
         <v>12.0598611831665</v>
       </c>
       <c r="G324" t="n">
-        <v>11.4423246383667</v>
+        <v>11.442325592041</v>
       </c>
       <c r="H324" t="n">
         <v>55912</v>
@@ -9852,7 +9852,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G327" t="n">
-        <v>11.884539604187</v>
+        <v>11.8845405578613</v>
       </c>
       <c r="H327" t="n">
         <v>38628</v>
@@ -9881,7 +9881,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G328" t="n">
-        <v>12.0687952041626</v>
+        <v>12.0687961578369</v>
       </c>
       <c r="H328" t="n">
         <v>34385</v>
@@ -9910,7 +9910,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G329" t="n">
-        <v>12.0687952041626</v>
+        <v>12.0687961578369</v>
       </c>
       <c r="H329" t="n">
         <v>28558</v>
@@ -9939,7 +9939,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G330" t="n">
-        <v>12.160924911499</v>
+        <v>12.1609239578247</v>
       </c>
       <c r="H330" t="n">
         <v>146039</v>
@@ -9968,7 +9968,7 @@
         <v>13.0308637619019</v>
       </c>
       <c r="G331" t="n">
-        <v>12.3636054992676</v>
+        <v>12.3636045455933</v>
       </c>
       <c r="H331" t="n">
         <v>18642</v>
@@ -9997,7 +9997,7 @@
         <v>13.186224937439</v>
       </c>
       <c r="G332" t="n">
-        <v>12.5110120773315</v>
+        <v>12.5110130310059</v>
       </c>
       <c r="H332" t="n">
         <v>22060</v>
@@ -10026,7 +10026,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G333" t="n">
-        <v>12.1056489944458</v>
+        <v>12.1056480407715</v>
       </c>
       <c r="H333" t="n">
         <v>24851</v>
@@ -10055,7 +10055,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G334" t="n">
-        <v>11.4976024627686</v>
+        <v>11.4976005554199</v>
       </c>
       <c r="H334" t="n">
         <v>51985</v>
@@ -10171,7 +10171,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G338" t="n">
-        <v>11.4976024627686</v>
+        <v>11.4976005554199</v>
       </c>
       <c r="H338" t="n">
         <v>37042</v>
@@ -10200,7 +10200,7 @@
         <v>12.0210208892822</v>
       </c>
       <c r="G339" t="n">
-        <v>11.4054737091064</v>
+        <v>11.4054727554321</v>
       </c>
       <c r="H339" t="n">
         <v>16302</v>
@@ -10258,7 +10258,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G341" t="n">
-        <v>11.460750579834</v>
+        <v>11.4607515335083</v>
       </c>
       <c r="H341" t="n">
         <v>96017</v>
@@ -10316,7 +10316,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G343" t="n">
-        <v>11.4976024627686</v>
+        <v>11.4976005554199</v>
       </c>
       <c r="H343" t="n">
         <v>44961</v>
@@ -10403,7 +10403,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G346" t="n">
-        <v>11.884539604187</v>
+        <v>11.8845405578613</v>
       </c>
       <c r="H346" t="n">
         <v>25063</v>
@@ -10432,7 +10432,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G347" t="n">
-        <v>12.0872211456299</v>
+        <v>12.0872220993042</v>
       </c>
       <c r="H347" t="n">
         <v>17512</v>
@@ -10461,7 +10461,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G348" t="n">
-        <v>12.160924911499</v>
+        <v>12.1609239578247</v>
       </c>
       <c r="H348" t="n">
         <v>164571</v>
@@ -10490,7 +10490,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G349" t="n">
-        <v>11.9766683578491</v>
+        <v>11.9766674041748</v>
       </c>
       <c r="H349" t="n">
         <v>13283</v>
@@ -10577,7 +10577,7 @@
         <v>13.2833251953125</v>
       </c>
       <c r="G352" t="n">
-        <v>12.6031408309937</v>
+        <v>12.6031398773193</v>
       </c>
       <c r="H352" t="n">
         <v>22421</v>
@@ -10635,7 +10635,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G354" t="n">
-        <v>13.1743354797363</v>
+        <v>13.1743335723877</v>
       </c>
       <c r="H354" t="n">
         <v>49028</v>
@@ -10664,7 +10664,7 @@
         <v>13.9824476242065</v>
       </c>
       <c r="G355" t="n">
-        <v>13.2664632797241</v>
+        <v>13.2664623260498</v>
       </c>
       <c r="H355" t="n">
         <v>22333</v>
@@ -10780,7 +10780,7 @@
         <v>14.0989675521851</v>
       </c>
       <c r="G359" t="n">
-        <v>13.3770160675049</v>
+        <v>13.3770179748535</v>
       </c>
       <c r="H359" t="n">
         <v>62383</v>
@@ -10809,7 +10809,7 @@
         <v>13.8270874023438</v>
       </c>
       <c r="G360" t="n">
-        <v>13.1190576553345</v>
+        <v>13.1190586090088</v>
       </c>
       <c r="H360" t="n">
         <v>43385</v>
@@ -10838,7 +10838,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G361" t="n">
-        <v>13.026930809021</v>
+        <v>13.0269298553467</v>
       </c>
       <c r="H361" t="n">
         <v>48913</v>
@@ -10867,7 +10867,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G362" t="n">
-        <v>13.026930809021</v>
+        <v>13.0269298553467</v>
       </c>
       <c r="H362" t="n">
         <v>29032</v>
@@ -10925,7 +10925,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G364" t="n">
-        <v>12.2714796066284</v>
+        <v>12.2714786529541</v>
       </c>
       <c r="H364" t="n">
         <v>81687</v>
@@ -10954,7 +10954,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G365" t="n">
-        <v>12.2162017822266</v>
+        <v>12.2162008285522</v>
       </c>
       <c r="H365" t="n">
         <v>190840</v>
@@ -10983,7 +10983,7 @@
         <v>12.9920244216919</v>
       </c>
       <c r="G366" t="n">
-        <v>12.3267545700073</v>
+        <v>12.3267555236816</v>
       </c>
       <c r="H366" t="n">
         <v>73862</v>
@@ -11012,7 +11012,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G367" t="n">
-        <v>12.160924911499</v>
+        <v>12.1609239578247</v>
       </c>
       <c r="H367" t="n">
         <v>62783</v>
@@ -11041,7 +11041,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G368" t="n">
-        <v>12.0872211456299</v>
+        <v>12.0872220993042</v>
       </c>
       <c r="H368" t="n">
         <v>34922</v>
@@ -11070,7 +11070,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G369" t="n">
-        <v>12.1056489944458</v>
+        <v>12.1056480407715</v>
       </c>
       <c r="H369" t="n">
         <v>42419</v>
@@ -11099,7 +11099,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G370" t="n">
-        <v>12.1240739822388</v>
+        <v>12.1240720748901</v>
       </c>
       <c r="H370" t="n">
         <v>23953</v>
@@ -11128,7 +11128,7 @@
         <v>12.8560838699341</v>
       </c>
       <c r="G371" t="n">
-        <v>12.1977767944336</v>
+        <v>12.1977777481079</v>
       </c>
       <c r="H371" t="n">
         <v>17051</v>
@@ -11215,7 +11215,7 @@
         <v>14.5650501251221</v>
       </c>
       <c r="G374" t="n">
-        <v>13.8192329406738</v>
+        <v>13.8192338943481</v>
       </c>
       <c r="H374" t="n">
         <v>120229</v>
@@ -11244,7 +11244,7 @@
         <v>14.0407075881958</v>
       </c>
       <c r="G375" t="n">
-        <v>13.321741104126</v>
+        <v>13.3217401504517</v>
       </c>
       <c r="H375" t="n">
         <v>115548</v>
@@ -11273,7 +11273,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G376" t="n">
-        <v>13.0822086334229</v>
+        <v>13.0822076797485</v>
       </c>
       <c r="H376" t="n">
         <v>70558</v>
@@ -11331,7 +11331,7 @@
         <v>13.3027448654175</v>
       </c>
       <c r="G378" t="n">
-        <v>12.6215648651123</v>
+        <v>12.6215658187866</v>
       </c>
       <c r="H378" t="n">
         <v>479797</v>
@@ -11389,7 +11389,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G380" t="n">
-        <v>12.474160194397</v>
+        <v>12.4741611480713</v>
       </c>
       <c r="H380" t="n">
         <v>30065</v>
@@ -11505,7 +11505,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G384" t="n">
-        <v>12.2162017822266</v>
+        <v>12.2162008285522</v>
       </c>
       <c r="H384" t="n">
         <v>8234</v>
@@ -11534,7 +11534,7 @@
         <v>13.380425453186</v>
       </c>
       <c r="G385" t="n">
-        <v>12.6952695846558</v>
+        <v>12.6952676773071</v>
       </c>
       <c r="H385" t="n">
         <v>15276</v>
@@ -11563,7 +11563,7 @@
         <v>13.4192657470703</v>
       </c>
       <c r="G386" t="n">
-        <v>12.7321186065674</v>
+        <v>12.732120513916</v>
       </c>
       <c r="H386" t="n">
         <v>34541</v>
@@ -11621,7 +11621,7 @@
         <v>13.7105674743652</v>
       </c>
       <c r="G388" t="n">
-        <v>13.0085067749023</v>
+        <v>13.0085048675537</v>
       </c>
       <c r="H388" t="n">
         <v>24282</v>
@@ -11650,7 +11650,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G389" t="n">
-        <v>13.1743354797363</v>
+        <v>13.1743335723877</v>
       </c>
       <c r="H389" t="n">
         <v>30802</v>
@@ -11679,7 +11679,7 @@
         <v>13.6911468505859</v>
       </c>
       <c r="G390" t="n">
-        <v>12.9900789260864</v>
+        <v>12.9900779724121</v>
       </c>
       <c r="H390" t="n">
         <v>45738</v>
@@ -11766,7 +11766,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G393" t="n">
-        <v>13.0822086334229</v>
+        <v>13.0822076797485</v>
       </c>
       <c r="H393" t="n">
         <v>14493</v>
@@ -11824,7 +11824,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G395" t="n">
-        <v>13.1743354797363</v>
+        <v>13.1743335723877</v>
       </c>
       <c r="H395" t="n">
         <v>43095</v>
@@ -11911,7 +11911,7 @@
         <v>12.8949241638184</v>
       </c>
       <c r="G398" t="n">
-        <v>12.2346267700195</v>
+        <v>12.2346277236938</v>
       </c>
       <c r="H398" t="n">
         <v>34385</v>
@@ -11940,7 +11940,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G399" t="n">
-        <v>12.1056489944458</v>
+        <v>12.1056480407715</v>
       </c>
       <c r="H399" t="n">
         <v>155352</v>
@@ -11998,7 +11998,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G401" t="n">
-        <v>12.3451814651489</v>
+        <v>12.3451805114746</v>
       </c>
       <c r="H401" t="n">
         <v>20963</v>
@@ -12027,7 +12027,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G402" t="n">
-        <v>12.3451814651489</v>
+        <v>12.3451805114746</v>
       </c>
       <c r="H402" t="n">
         <v>17932</v>
@@ -12085,7 +12085,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G404" t="n">
-        <v>12.3451814651489</v>
+        <v>12.3451805114746</v>
       </c>
       <c r="H404" t="n">
         <v>20738</v>
@@ -12114,7 +12114,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G405" t="n">
-        <v>12.160924911499</v>
+        <v>12.1609239578247</v>
       </c>
       <c r="H405" t="n">
         <v>14366</v>
@@ -12143,7 +12143,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G406" t="n">
-        <v>12.0687952041626</v>
+        <v>12.0687961578369</v>
       </c>
       <c r="H406" t="n">
         <v>34716</v>
@@ -12172,7 +12172,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G407" t="n">
-        <v>12.0872211456299</v>
+        <v>12.0872220993042</v>
       </c>
       <c r="H407" t="n">
         <v>16935</v>
@@ -12201,7 +12201,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G408" t="n">
-        <v>11.884539604187</v>
+        <v>11.8845405578613</v>
       </c>
       <c r="H408" t="n">
         <v>21960</v>
@@ -12259,7 +12259,7 @@
         <v>12.4094219207764</v>
       </c>
       <c r="G410" t="n">
-        <v>11.7739849090576</v>
+        <v>11.7739858627319</v>
       </c>
       <c r="H410" t="n">
         <v>15233</v>
@@ -12288,7 +12288,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G411" t="n">
-        <v>11.7002849578857</v>
+        <v>11.7002840042114</v>
       </c>
       <c r="H411" t="n">
         <v>14490</v>
@@ -12375,7 +12375,7 @@
         <v>11.6131992340088</v>
       </c>
       <c r="G414" t="n">
-        <v>11.018533706665</v>
+        <v>11.0185346603394</v>
       </c>
       <c r="H414" t="n">
         <v>45535</v>
@@ -12404,7 +12404,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G415" t="n">
-        <v>10.9632587432861</v>
+        <v>10.9632577896118</v>
       </c>
       <c r="H415" t="n">
         <v>19309</v>
@@ -12462,7 +12462,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G417" t="n">
-        <v>10.9632587432861</v>
+        <v>10.9632577896118</v>
       </c>
       <c r="H417" t="n">
         <v>37373</v>
@@ -12607,7 +12607,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G422" t="n">
-        <v>11.0553874969482</v>
+        <v>11.0553865432739</v>
       </c>
       <c r="H422" t="n">
         <v>13462</v>
@@ -12636,7 +12636,7 @@
         <v>11.8073997497559</v>
       </c>
       <c r="G423" t="n">
-        <v>11.2027912139893</v>
+        <v>11.2027902603149</v>
       </c>
       <c r="H423" t="n">
         <v>14119</v>
@@ -12810,7 +12810,7 @@
         <v>11.8073997497559</v>
       </c>
       <c r="G429" t="n">
-        <v>11.2027912139893</v>
+        <v>11.2027902603149</v>
       </c>
       <c r="H429" t="n">
         <v>10547</v>
@@ -12868,7 +12868,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G431" t="n">
-        <v>11.0369596481323</v>
+        <v>11.0369606018066</v>
       </c>
       <c r="H431" t="n">
         <v>33933</v>
@@ -12897,7 +12897,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G432" t="n">
-        <v>10.0788259506226</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H432" t="n">
         <v>74937</v>
@@ -12926,7 +12926,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G433" t="n">
-        <v>10.4104881286621</v>
+        <v>10.4104890823364</v>
       </c>
       <c r="H433" t="n">
         <v>46588</v>
@@ -12984,7 +12984,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G435" t="n">
-        <v>10.2446584701538</v>
+        <v>10.2446594238281</v>
       </c>
       <c r="H435" t="n">
         <v>43976</v>
@@ -13013,7 +13013,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G436" t="n">
-        <v>10.2446584701538</v>
+        <v>10.2446594238281</v>
       </c>
       <c r="H436" t="n">
         <v>63148</v>
@@ -13071,7 +13071,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G438" t="n">
-        <v>10.3552122116089</v>
+        <v>10.3552112579346</v>
       </c>
       <c r="H438" t="n">
         <v>41072</v>
@@ -13100,7 +13100,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G439" t="n">
-        <v>10.3367862701416</v>
+        <v>10.3367853164673</v>
       </c>
       <c r="H439" t="n">
         <v>50080</v>
@@ -13158,7 +13158,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G441" t="n">
-        <v>10.0788259506226</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H441" t="n">
         <v>50243</v>
@@ -13216,7 +13216,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G443" t="n">
-        <v>9.36022567749023</v>
+        <v>9.36022663116455</v>
       </c>
       <c r="H443" t="n">
         <v>58787</v>
@@ -13274,7 +13274,7 @@
         <v>9.30221080780029</v>
       </c>
       <c r="G445" t="n">
-        <v>8.82588195800781</v>
+        <v>8.8258810043335</v>
       </c>
       <c r="H445" t="n">
         <v>198608</v>
@@ -13303,7 +13303,7 @@
         <v>10.0013341903687</v>
       </c>
       <c r="G446" t="n">
-        <v>9.48920726776123</v>
+        <v>9.48920631408691</v>
       </c>
       <c r="H446" t="n">
         <v>50177</v>
@@ -13332,7 +13332,7 @@
         <v>9.12743091583252</v>
       </c>
       <c r="G447" t="n">
-        <v>8.66005420684814</v>
+        <v>8.66005325317383</v>
       </c>
       <c r="H447" t="n">
         <v>68799</v>
@@ -13361,7 +13361,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G448" t="n">
-        <v>9.85772037506104</v>
+        <v>9.85771942138672</v>
       </c>
       <c r="H448" t="n">
         <v>42752</v>
@@ -13390,7 +13390,7 @@
         <v>9.22453117370605</v>
       </c>
       <c r="G449" t="n">
-        <v>8.7521800994873</v>
+        <v>8.75218200683594</v>
       </c>
       <c r="H449" t="n">
         <v>29663</v>
@@ -13419,7 +13419,7 @@
         <v>8.59337902069092</v>
       </c>
       <c r="G450" t="n">
-        <v>8.15334701538086</v>
+        <v>8.15334796905518</v>
       </c>
       <c r="H450" t="n">
         <v>148767</v>
@@ -13477,7 +13477,7 @@
         <v>8.58366870880127</v>
       </c>
       <c r="G452" t="n">
-        <v>8.14413356781006</v>
+        <v>8.14413452148438</v>
       </c>
       <c r="H452" t="n">
         <v>27504</v>
@@ -13506,7 +13506,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G453" t="n">
-        <v>8.47579479217529</v>
+        <v>8.47579574584961</v>
       </c>
       <c r="H453" t="n">
         <v>47454</v>
@@ -13535,7 +13535,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G454" t="n">
-        <v>8.3836669921875</v>
+        <v>8.38366794586182</v>
       </c>
       <c r="H454" t="n">
         <v>58292</v>
@@ -13564,7 +13564,7 @@
         <v>10.0984344482422</v>
       </c>
       <c r="G455" t="n">
-        <v>9.58133506774902</v>
+        <v>9.58133411407471</v>
       </c>
       <c r="H455" t="n">
         <v>36655</v>
@@ -13593,7 +13593,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G456" t="n">
-        <v>11.7002849578857</v>
+        <v>11.7002840042114</v>
       </c>
       <c r="H456" t="n">
         <v>57587</v>
@@ -13622,7 +13622,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G457" t="n">
-        <v>11.0369596481323</v>
+        <v>11.0369606018066</v>
       </c>
       <c r="H457" t="n">
         <v>57173</v>
@@ -13651,7 +13651,7 @@
         <v>11.2247982025146</v>
       </c>
       <c r="G458" t="n">
-        <v>10.6500225067139</v>
+        <v>10.6500234603882</v>
       </c>
       <c r="H458" t="n">
         <v>48513</v>
@@ -13680,7 +13680,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G459" t="n">
-        <v>10.0788259506226</v>
+        <v>10.0788269042969</v>
       </c>
       <c r="H459" t="n">
         <v>35880</v>
@@ -13709,7 +13709,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G460" t="n">
-        <v>10.1341028213501</v>
+        <v>10.1341037750244</v>
       </c>
       <c r="H460" t="n">
         <v>72969</v>
@@ -13767,7 +13767,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G462" t="n">
-        <v>10.1341028213501</v>
+        <v>10.1341037750244</v>
       </c>
       <c r="H462" t="n">
         <v>20192</v>
@@ -13796,7 +13796,7 @@
         <v>10.7781372070312</v>
       </c>
       <c r="G463" t="n">
-        <v>10.2262325286865</v>
+        <v>10.2262334823608</v>
       </c>
       <c r="H463" t="n">
         <v>35295</v>
@@ -13854,7 +13854,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G465" t="n">
-        <v>9.76559257507324</v>
+        <v>9.76559162139893</v>
       </c>
       <c r="H465" t="n">
         <v>19814</v>
@@ -13912,7 +13912,7 @@
         <v>10.1761140823364</v>
       </c>
       <c r="G467" t="n">
-        <v>9.65503597259521</v>
+        <v>9.65503692626953</v>
       </c>
       <c r="H467" t="n">
         <v>21752</v>
@@ -13941,7 +13941,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G468" t="n">
-        <v>9.94984722137451</v>
+        <v>9.94984912872314</v>
       </c>
       <c r="H468" t="n">
         <v>26515</v>
@@ -13999,7 +13999,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G470" t="n">
-        <v>11.0553874969482</v>
+        <v>11.0553865432739</v>
       </c>
       <c r="H470" t="n">
         <v>18460</v>
@@ -14057,7 +14057,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G472" t="n">
-        <v>11.0553874969482</v>
+        <v>11.0553865432739</v>
       </c>
       <c r="H472" t="n">
         <v>82131</v>
@@ -14086,7 +14086,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G473" t="n">
-        <v>11.7002849578857</v>
+        <v>11.7002840042114</v>
       </c>
       <c r="H473" t="n">
         <v>33615</v>
@@ -14115,7 +14115,7 @@
         <v>12.2346420288086</v>
       </c>
       <c r="G474" t="n">
-        <v>11.6081552505493</v>
+        <v>11.6081562042236</v>
       </c>
       <c r="H474" t="n">
         <v>33682</v>
@@ -14144,7 +14144,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G475" t="n">
-        <v>11.7924118041992</v>
+        <v>11.7924108505249</v>
       </c>
       <c r="H475" t="n">
         <v>26161</v>
@@ -14202,7 +14202,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G477" t="n">
-        <v>12.474160194397</v>
+        <v>12.4741611480713</v>
       </c>
       <c r="H477" t="n">
         <v>17487</v>
@@ -14260,7 +14260,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G479" t="n">
-        <v>12.3451814651489</v>
+        <v>12.3451805114746</v>
       </c>
       <c r="H479" t="n">
         <v>43601</v>
@@ -14289,7 +14289,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G480" t="n">
-        <v>12.2714796066284</v>
+        <v>12.2714786529541</v>
       </c>
       <c r="H480" t="n">
         <v>20669</v>
@@ -14318,7 +14318,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G481" t="n">
-        <v>11.9766683578491</v>
+        <v>11.9766674041748</v>
       </c>
       <c r="H481" t="n">
         <v>21030</v>
@@ -14376,7 +14376,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G483" t="n">
-        <v>11.7924118041992</v>
+        <v>11.7924108505249</v>
       </c>
       <c r="H483" t="n">
         <v>10814</v>
@@ -14405,7 +14405,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G484" t="n">
-        <v>12.1240739822388</v>
+        <v>12.1240720748901</v>
       </c>
       <c r="H484" t="n">
         <v>26687</v>
@@ -14434,7 +14434,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G485" t="n">
-        <v>11.7002849578857</v>
+        <v>11.7002840042114</v>
       </c>
       <c r="H485" t="n">
         <v>50887</v>
@@ -14521,7 +14521,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G488" t="n">
-        <v>13.0822086334229</v>
+        <v>13.0822076797485</v>
       </c>
       <c r="H488" t="n">
         <v>24122</v>
@@ -14579,7 +14579,7 @@
         <v>14.1183881759644</v>
       </c>
       <c r="G490" t="n">
-        <v>13.3954429626465</v>
+        <v>13.3954439163208</v>
       </c>
       <c r="H490" t="n">
         <v>42920</v>
@@ -14608,7 +14608,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G491" t="n">
-        <v>13.026930809021</v>
+        <v>13.0269298553467</v>
       </c>
       <c r="H491" t="n">
         <v>30641</v>
@@ -14724,7 +14724,7 @@
         <v>15.633152961731</v>
       </c>
       <c r="G495" t="n">
-        <v>14.8326435089111</v>
+        <v>14.8326425552368</v>
       </c>
       <c r="H495" t="n">
         <v>23740</v>
@@ -14753,7 +14753,7 @@
         <v>14.9146108627319</v>
       </c>
       <c r="G496" t="n">
-        <v>14.1508941650391</v>
+        <v>14.1508951187134</v>
       </c>
       <c r="H496" t="n">
         <v>48940</v>
@@ -14782,7 +14782,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G497" t="n">
-        <v>15.1827297210693</v>
+        <v>15.1827306747437</v>
       </c>
       <c r="H497" t="n">
         <v>39377</v>
@@ -14811,7 +14811,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G498" t="n">
-        <v>15.6433715820312</v>
+        <v>15.6433725357056</v>
       </c>
       <c r="H498" t="n">
         <v>302386</v>
@@ -14840,7 +14840,7 @@
         <v>16.7206764221191</v>
       </c>
       <c r="G499" t="n">
-        <v>15.8644781112671</v>
+        <v>15.8644771575928</v>
       </c>
       <c r="H499" t="n">
         <v>78961</v>
@@ -14927,7 +14927,7 @@
         <v>15.3030118942261</v>
       </c>
       <c r="G502" t="n">
-        <v>14.5194072723389</v>
+        <v>14.5194063186646</v>
       </c>
       <c r="H502" t="n">
         <v>62720</v>
@@ -14985,7 +14985,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G504" t="n">
-        <v>13.9482126235962</v>
+        <v>13.9482116699219</v>
       </c>
       <c r="H504" t="n">
         <v>30184</v>
@@ -15014,7 +15014,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G505" t="n">
-        <v>13.9482126235962</v>
+        <v>13.9482116699219</v>
       </c>
       <c r="H505" t="n">
         <v>46105</v>
@@ -15043,7 +15043,7 @@
         <v>14.7980899810791</v>
       </c>
       <c r="G506" t="n">
-        <v>14.040340423584</v>
+        <v>14.0403394699097</v>
       </c>
       <c r="H506" t="n">
         <v>43424</v>
@@ -15101,7 +15101,7 @@
         <v>14.4679489135742</v>
       </c>
       <c r="G508" t="n">
-        <v>13.7271032333374</v>
+        <v>13.7271041870117</v>
       </c>
       <c r="H508" t="n">
         <v>20871</v>
@@ -15159,7 +15159,7 @@
         <v>14.7398300170898</v>
       </c>
       <c r="G510" t="n">
-        <v>13.9850625991821</v>
+        <v>13.9850616455078</v>
       </c>
       <c r="H510" t="n">
         <v>31610</v>
@@ -15188,7 +15188,7 @@
         <v>14.9922914505005</v>
       </c>
       <c r="G511" t="n">
-        <v>14.2245979309082</v>
+        <v>14.2245969772339</v>
       </c>
       <c r="H511" t="n">
         <v>23708</v>
@@ -15275,7 +15275,7 @@
         <v>15.128231048584</v>
       </c>
       <c r="G514" t="n">
-        <v>14.460958480835</v>
+        <v>14.4609594345093</v>
       </c>
       <c r="H514" t="n">
         <v>34556</v>
@@ -15304,7 +15304,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G515" t="n">
-        <v>14.7022829055786</v>
+        <v>14.7022838592529</v>
       </c>
       <c r="H515" t="n">
         <v>22064</v>
@@ -15333,7 +15333,7 @@
         <v>15.4777927398682</v>
       </c>
       <c r="G516" t="n">
-        <v>14.7951030731201</v>
+        <v>14.7951021194458</v>
       </c>
       <c r="H516" t="n">
         <v>13193</v>
@@ -15420,7 +15420,7 @@
         <v>15.5748929977417</v>
       </c>
       <c r="G519" t="n">
-        <v>14.8879194259644</v>
+        <v>14.8879203796387</v>
       </c>
       <c r="H519" t="n">
         <v>10780</v>
@@ -15449,7 +15449,7 @@
         <v>15.8661937713623</v>
       </c>
       <c r="G520" t="n">
-        <v>15.1663722991943</v>
+        <v>15.16637134552</v>
       </c>
       <c r="H520" t="n">
         <v>26150</v>
@@ -15478,7 +15478,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G521" t="n">
-        <v>14.7022829055786</v>
+        <v>14.7022838592529</v>
       </c>
       <c r="H521" t="n">
         <v>20529</v>
@@ -15507,7 +15507,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G522" t="n">
-        <v>15.1292457580566</v>
+        <v>15.1292448043823</v>
       </c>
       <c r="H522" t="n">
         <v>16871</v>
@@ -15536,7 +15536,7 @@
         <v>16.0215549468994</v>
       </c>
       <c r="G523" t="n">
-        <v>15.3148794174194</v>
+        <v>15.3148813247681</v>
       </c>
       <c r="H523" t="n">
         <v>26072</v>
@@ -15565,7 +15565,7 @@
         <v>15.9244537353516</v>
       </c>
       <c r="G524" t="n">
-        <v>15.2220630645752</v>
+        <v>15.2220621109009</v>
       </c>
       <c r="H524" t="n">
         <v>14203</v>
@@ -15594,7 +15594,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G525" t="n">
-        <v>14.9064826965332</v>
+        <v>14.9064836502075</v>
       </c>
       <c r="H525" t="n">
         <v>16186</v>
@@ -15623,7 +15623,7 @@
         <v>15.1864919662476</v>
       </c>
       <c r="G526" t="n">
-        <v>14.5166511535645</v>
+        <v>14.5166501998901</v>
       </c>
       <c r="H526" t="n">
         <v>47887</v>
@@ -15652,7 +15652,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G527" t="n">
-        <v>14.9064826965332</v>
+        <v>14.9064836502075</v>
       </c>
       <c r="H527" t="n">
         <v>40650</v>
@@ -15681,7 +15681,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G528" t="n">
-        <v>14.9807367324829</v>
+        <v>14.9807376861572</v>
       </c>
       <c r="H528" t="n">
         <v>11405</v>
@@ -15768,7 +15768,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G531" t="n">
-        <v>15.0364284515381</v>
+        <v>15.0364274978638</v>
       </c>
       <c r="H531" t="n">
         <v>10866</v>
@@ -15797,7 +15797,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G532" t="n">
-        <v>14.8322286605835</v>
+        <v>14.8322296142578</v>
       </c>
       <c r="H532" t="n">
         <v>14290</v>
@@ -15826,7 +15826,7 @@
         <v>15.613733291626</v>
       </c>
       <c r="G533" t="n">
-        <v>14.9250459671021</v>
+        <v>14.9250469207764</v>
       </c>
       <c r="H533" t="n">
         <v>26443</v>
@@ -15855,7 +15855,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G534" t="n">
-        <v>15.1292457580566</v>
+        <v>15.1292448043823</v>
       </c>
       <c r="H534" t="n">
         <v>13313</v>
@@ -15884,7 +15884,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G535" t="n">
-        <v>15.1292457580566</v>
+        <v>15.1292448043823</v>
       </c>
       <c r="H535" t="n">
         <v>23772</v>
@@ -15913,7 +15913,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G536" t="n">
-        <v>14.9064826965332</v>
+        <v>14.9064836502075</v>
       </c>
       <c r="H536" t="n">
         <v>7951</v>
@@ -15942,7 +15942,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G537" t="n">
-        <v>15.2963161468506</v>
+        <v>15.2963171005249</v>
       </c>
       <c r="H537" t="n">
         <v>21472</v>
@@ -16145,7 +16145,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G544" t="n">
-        <v>14.8322286605835</v>
+        <v>14.8322296142578</v>
       </c>
       <c r="H544" t="n">
         <v>20980</v>
@@ -16174,7 +16174,7 @@
         <v>16.1769142150879</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4633855819702</v>
+        <v>15.4633846282959</v>
       </c>
       <c r="H545" t="n">
         <v>51347</v>
@@ -16232,7 +16232,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G547" t="n">
-        <v>16.8556537628174</v>
+        <v>16.8556499481201</v>
       </c>
       <c r="H547" t="n">
         <v>42324</v>
@@ -16319,7 +16319,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G550" t="n">
-        <v>16.6143245697021</v>
+        <v>16.6143264770508</v>
       </c>
       <c r="H550" t="n">
         <v>37074</v>
@@ -16348,7 +16348,7 @@
         <v>17.536319732666</v>
       </c>
       <c r="G551" t="n">
-        <v>16.7628326416016</v>
+        <v>16.7628307342529</v>
       </c>
       <c r="H551" t="n">
         <v>13202</v>
@@ -16493,7 +16493,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G556" t="n">
-        <v>17.895206451416</v>
+        <v>17.8952045440674</v>
       </c>
       <c r="H556" t="n">
         <v>21308</v>
@@ -16522,7 +16522,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G557" t="n">
-        <v>17.7652587890625</v>
+        <v>17.7652626037598</v>
       </c>
       <c r="H557" t="n">
         <v>17872</v>
@@ -16580,7 +16580,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G559" t="n">
-        <v>18.1922245025635</v>
+        <v>18.1922206878662</v>
       </c>
       <c r="H559" t="n">
         <v>42955</v>
@@ -16609,7 +16609,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G560" t="n">
-        <v>17.542501449585</v>
+        <v>17.5424995422363</v>
       </c>
       <c r="H560" t="n">
         <v>23181</v>
@@ -16638,7 +16638,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G561" t="n">
-        <v>17.4125556945801</v>
+        <v>17.4125537872314</v>
       </c>
       <c r="H561" t="n">
         <v>39089</v>
@@ -16725,7 +16725,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G564" t="n">
-        <v>19.0275764465332</v>
+        <v>19.0275783538818</v>
       </c>
       <c r="H564" t="n">
         <v>81569</v>
@@ -16754,7 +16754,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G565" t="n">
-        <v>18.2107830047607</v>
+        <v>18.2107849121094</v>
       </c>
       <c r="H565" t="n">
         <v>31275</v>
@@ -16928,7 +16928,7 @@
         <v>18.6626834869385</v>
       </c>
       <c r="G571" t="n">
-        <v>17.8395137786865</v>
+        <v>17.8395156860352</v>
       </c>
       <c r="H571" t="n">
         <v>77837</v>
@@ -16957,7 +16957,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G572" t="n">
-        <v>17.3568668365479</v>
+        <v>17.3568649291992</v>
       </c>
       <c r="H572" t="n">
         <v>123917</v>
@@ -16986,7 +16986,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G573" t="n">
-        <v>17.6910076141357</v>
+        <v>17.6910057067871</v>
       </c>
       <c r="H573" t="n">
         <v>109043</v>
@@ -17073,7 +17073,7 @@
         <v>16.4487953186035</v>
       </c>
       <c r="G576" t="n">
-        <v>15.72327709198</v>
+        <v>15.7232761383057</v>
       </c>
       <c r="H576" t="n">
         <v>46607</v>
@@ -17131,7 +17131,7 @@
         <v>16.5847358703613</v>
       </c>
       <c r="G578" t="n">
-        <v>15.8532190322876</v>
+        <v>15.8532209396362</v>
       </c>
       <c r="H578" t="n">
         <v>124946</v>
@@ -17160,7 +17160,7 @@
         <v>15.9827136993408</v>
       </c>
       <c r="G579" t="n">
-        <v>15.2777528762817</v>
+        <v>15.2777519226074</v>
       </c>
       <c r="H579" t="n">
         <v>42599</v>
@@ -17247,7 +17247,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G582" t="n">
-        <v>16.4843826293945</v>
+        <v>16.4843788146973</v>
       </c>
       <c r="H582" t="n">
         <v>52124</v>
@@ -17305,7 +17305,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G584" t="n">
-        <v>16.3173122406006</v>
+        <v>16.3173084259033</v>
       </c>
       <c r="H584" t="n">
         <v>20341</v>
@@ -17334,7 +17334,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G585" t="n">
-        <v>16.1688022613525</v>
+        <v>16.1688041687012</v>
       </c>
       <c r="H585" t="n">
         <v>23602</v>
@@ -17363,7 +17363,7 @@
         <v>17.5168991088867</v>
       </c>
       <c r="G586" t="n">
-        <v>16.7442684173584</v>
+        <v>16.744270324707</v>
       </c>
       <c r="H586" t="n">
         <v>151028</v>
@@ -17392,7 +17392,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G587" t="n">
-        <v>16.5957622528076</v>
+        <v>16.595760345459</v>
       </c>
       <c r="H587" t="n">
         <v>34827</v>
@@ -17421,7 +17421,7 @@
         <v>16.9731388092041</v>
       </c>
       <c r="G588" t="n">
-        <v>16.2244892120361</v>
+        <v>16.2244930267334</v>
       </c>
       <c r="H588" t="n">
         <v>17051</v>
@@ -17479,7 +17479,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G590" t="n">
-        <v>16.2616176605225</v>
+        <v>16.2616195678711</v>
       </c>
       <c r="H590" t="n">
         <v>13011</v>
@@ -17508,7 +17508,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G591" t="n">
-        <v>16.2616176605225</v>
+        <v>16.2616195678711</v>
       </c>
       <c r="H591" t="n">
         <v>99956</v>
@@ -17537,7 +17537,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G592" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H592" t="n">
         <v>9975</v>
@@ -17566,7 +17566,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G593" t="n">
-        <v>16.5957622528076</v>
+        <v>16.595760345459</v>
       </c>
       <c r="H593" t="n">
         <v>14891</v>
@@ -17682,7 +17682,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G597" t="n">
-        <v>16.5029449462891</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H597" t="n">
         <v>81026</v>
@@ -17740,7 +17740,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G599" t="n">
-        <v>16.7071418762207</v>
+        <v>16.7071437835693</v>
       </c>
       <c r="H599" t="n">
         <v>91536</v>
@@ -17769,7 +17769,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G600" t="n">
-        <v>16.4843826293945</v>
+        <v>16.4843788146973</v>
       </c>
       <c r="H600" t="n">
         <v>11491</v>
@@ -17827,7 +17827,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G602" t="n">
-        <v>16.6143245697021</v>
+        <v>16.6143264770508</v>
       </c>
       <c r="H602" t="n">
         <v>70209</v>
@@ -17856,7 +17856,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G603" t="n">
-        <v>15.686149597168</v>
+        <v>15.6861486434937</v>
       </c>
       <c r="H603" t="n">
         <v>79485</v>
@@ -17885,7 +17885,7 @@
         <v>16.0409755706787</v>
       </c>
       <c r="G604" t="n">
-        <v>15.3334436416626</v>
+        <v>15.3334455490112</v>
       </c>
       <c r="H604" t="n">
         <v>40930</v>
@@ -17943,7 +17943,7 @@
         <v>15.2641716003418</v>
       </c>
       <c r="G606" t="n">
-        <v>14.5909042358398</v>
+        <v>14.5909032821655</v>
       </c>
       <c r="H606" t="n">
         <v>36919</v>
@@ -18030,7 +18030,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G609" t="n">
-        <v>15.686149597168</v>
+        <v>15.6861486434937</v>
       </c>
       <c r="H609" t="n">
         <v>29121</v>
@@ -18059,7 +18059,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G610" t="n">
-        <v>14.9807367324829</v>
+        <v>14.9807376861572</v>
       </c>
       <c r="H610" t="n">
         <v>37926</v>
@@ -18088,7 +18088,7 @@
         <v>15.108811378479</v>
       </c>
       <c r="G611" t="n">
-        <v>14.4423952102661</v>
+        <v>14.4423961639404</v>
       </c>
       <c r="H611" t="n">
         <v>103659</v>
@@ -18117,7 +18117,7 @@
         <v>18.0024013519287</v>
       </c>
       <c r="G612" t="n">
-        <v>17.2083587646484</v>
+        <v>17.2083568572998</v>
       </c>
       <c r="H612" t="n">
         <v>158473</v>
@@ -18146,7 +18146,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G613" t="n">
-        <v>16.4101276397705</v>
+        <v>16.4101257324219</v>
       </c>
       <c r="H613" t="n">
         <v>64161</v>
@@ -18175,7 +18175,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G614" t="n">
-        <v>16.4101276397705</v>
+        <v>16.4101257324219</v>
       </c>
       <c r="H614" t="n">
         <v>66121</v>
@@ -18204,7 +18204,7 @@
         <v>16.5847358703613</v>
       </c>
       <c r="G615" t="n">
-        <v>15.8532190322876</v>
+        <v>15.8532209396362</v>
       </c>
       <c r="H615" t="n">
         <v>42220</v>
@@ -18233,7 +18233,7 @@
         <v>16.2351741790771</v>
       </c>
       <c r="G616" t="n">
-        <v>15.5190763473511</v>
+        <v>15.5190773010254</v>
       </c>
       <c r="H616" t="n">
         <v>54428</v>
@@ -18262,7 +18262,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G617" t="n">
-        <v>16.1688022613525</v>
+        <v>16.1688041687012</v>
       </c>
       <c r="H617" t="n">
         <v>47046</v>
@@ -18291,7 +18291,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G618" t="n">
-        <v>15.7789659500122</v>
+        <v>15.7789640426636</v>
       </c>
       <c r="H618" t="n">
         <v>15816</v>
@@ -18320,7 +18320,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G619" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H619" t="n">
         <v>56147</v>
@@ -18349,7 +18349,7 @@
         <v>16.8760375976562</v>
       </c>
       <c r="G620" t="n">
-        <v>16.1316738128662</v>
+        <v>16.1316757202148</v>
       </c>
       <c r="H620" t="n">
         <v>12213</v>
@@ -18407,7 +18407,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G622" t="n">
-        <v>16.4843826293945</v>
+        <v>16.4843788146973</v>
       </c>
       <c r="H622" t="n">
         <v>47450</v>
@@ -18436,7 +18436,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G623" t="n">
-        <v>16.5957622528076</v>
+        <v>16.595760345459</v>
       </c>
       <c r="H623" t="n">
         <v>26365</v>
@@ -18465,7 +18465,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G624" t="n">
-        <v>16.3729991912842</v>
+        <v>16.3730010986328</v>
       </c>
       <c r="H624" t="n">
         <v>31241</v>
@@ -18494,7 +18494,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G625" t="n">
-        <v>16.8556537628174</v>
+        <v>16.8556499481201</v>
       </c>
       <c r="H625" t="n">
         <v>25343</v>
@@ -18523,7 +18523,7 @@
         <v>17.4974803924561</v>
       </c>
       <c r="G626" t="n">
-        <v>16.7257061004639</v>
+        <v>16.7257041931152</v>
       </c>
       <c r="H626" t="n">
         <v>33551</v>
@@ -18552,7 +18552,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G627" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H627" t="n">
         <v>49894</v>
@@ -18581,7 +18581,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G628" t="n">
-        <v>16.5029449462891</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H628" t="n">
         <v>23660</v>
@@ -18610,7 +18610,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G629" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H629" t="n">
         <v>38483</v>
@@ -18639,7 +18639,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G630" t="n">
-        <v>16.5029449462891</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H630" t="n">
         <v>20106</v>
@@ -18668,7 +18668,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G631" t="n">
-        <v>16.3173122406006</v>
+        <v>16.3173084259033</v>
       </c>
       <c r="H631" t="n">
         <v>40982</v>
@@ -18697,7 +18697,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G632" t="n">
-        <v>16.3358707427979</v>
+        <v>16.3358745574951</v>
       </c>
       <c r="H632" t="n">
         <v>30546</v>
@@ -18726,7 +18726,7 @@
         <v>17.4974803924561</v>
       </c>
       <c r="G633" t="n">
-        <v>16.7257061004639</v>
+        <v>16.7257041931152</v>
       </c>
       <c r="H633" t="n">
         <v>30295</v>
@@ -18842,7 +18842,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G637" t="n">
-        <v>16.5400695800781</v>
+        <v>16.5400714874268</v>
       </c>
       <c r="H637" t="n">
         <v>32139</v>
@@ -18900,7 +18900,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G639" t="n">
-        <v>16.3729991912842</v>
+        <v>16.3730010986328</v>
       </c>
       <c r="H639" t="n">
         <v>73109</v>
@@ -18929,7 +18929,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G640" t="n">
-        <v>16.7071418762207</v>
+        <v>16.7071437835693</v>
       </c>
       <c r="H640" t="n">
         <v>38853</v>
@@ -18958,7 +18958,7 @@
         <v>17.5557403564453</v>
       </c>
       <c r="G641" t="n">
-        <v>16.7813968658447</v>
+        <v>16.7813987731934</v>
       </c>
       <c r="H641" t="n">
         <v>22369</v>
@@ -19016,7 +19016,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G643" t="n">
-        <v>16.7071418762207</v>
+        <v>16.7071437835693</v>
       </c>
       <c r="H643" t="n">
         <v>69682</v>
@@ -19074,7 +19074,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G645" t="n">
-        <v>17.4125556945801</v>
+        <v>17.4125537872314</v>
       </c>
       <c r="H645" t="n">
         <v>65148</v>
@@ -19103,7 +19103,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G646" t="n">
-        <v>17.7838249206543</v>
+        <v>17.7838230133057</v>
       </c>
       <c r="H646" t="n">
         <v>45839</v>
@@ -19132,7 +19132,7 @@
         <v>18.7986240386963</v>
       </c>
       <c r="G647" t="n">
-        <v>17.9694576263428</v>
+        <v>17.9694595336914</v>
       </c>
       <c r="H647" t="n">
         <v>7183</v>
@@ -19219,7 +19219,7 @@
         <v>18.7597846984863</v>
       </c>
       <c r="G650" t="n">
-        <v>17.9323310852051</v>
+        <v>17.9323329925537</v>
       </c>
       <c r="H650" t="n">
         <v>14975</v>
@@ -19306,7 +19306,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G653" t="n">
-        <v>16.5400695800781</v>
+        <v>16.5400714874268</v>
       </c>
       <c r="H653" t="n">
         <v>88550</v>
@@ -19335,7 +19335,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G654" t="n">
-        <v>16.3358707427979</v>
+        <v>16.3358745574951</v>
       </c>
       <c r="H654" t="n">
         <v>83206</v>
@@ -19393,7 +19393,7 @@
         <v>17.4003791809082</v>
       </c>
       <c r="G656" t="n">
-        <v>16.6328887939453</v>
+        <v>16.6328868865967</v>
       </c>
       <c r="H656" t="n">
         <v>33953</v>
@@ -19422,7 +19422,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G657" t="n">
-        <v>16.7071418762207</v>
+        <v>16.7071437835693</v>
       </c>
       <c r="H657" t="n">
         <v>18230</v>
@@ -19480,7 +19480,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G659" t="n">
-        <v>16.5957622528076</v>
+        <v>16.595760345459</v>
       </c>
       <c r="H659" t="n">
         <v>86369</v>
@@ -19509,7 +19509,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G660" t="n">
-        <v>16.5029449462891</v>
+        <v>16.5029430389404</v>
       </c>
       <c r="H660" t="n">
         <v>15595</v>
@@ -19538,7 +19538,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G661" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H661" t="n">
         <v>79956</v>
@@ -19567,7 +19567,7 @@
         <v>17.2061786651611</v>
       </c>
       <c r="G662" t="n">
-        <v>16.4472541809082</v>
+        <v>16.4472522735596</v>
       </c>
       <c r="H662" t="n">
         <v>36381</v>
@@ -19596,7 +19596,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G663" t="n">
-        <v>16.3729991912842</v>
+        <v>16.3730010986328</v>
       </c>
       <c r="H663" t="n">
         <v>19638</v>
@@ -19625,7 +19625,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G664" t="n">
-        <v>16.3729991912842</v>
+        <v>16.3730010986328</v>
       </c>
       <c r="H664" t="n">
         <v>18813</v>
@@ -19654,7 +19654,7 @@
         <v>16.9731388092041</v>
       </c>
       <c r="G665" t="n">
-        <v>16.2244892120361</v>
+        <v>16.2244930267334</v>
       </c>
       <c r="H665" t="n">
         <v>24961</v>
@@ -19712,7 +19712,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G667" t="n">
-        <v>16.3358707427979</v>
+        <v>16.3358745574951</v>
       </c>
       <c r="H667" t="n">
         <v>69209</v>
@@ -19741,7 +19741,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G668" t="n">
-        <v>16.1688022613525</v>
+        <v>16.1688041687012</v>
       </c>
       <c r="H668" t="n">
         <v>98048</v>
@@ -19770,7 +19770,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G669" t="n">
-        <v>15.7789659500122</v>
+        <v>15.7789640426636</v>
       </c>
       <c r="H669" t="n">
         <v>79199</v>
@@ -19799,7 +19799,7 @@
         <v>16.9537181854248</v>
       </c>
       <c r="G670" t="n">
-        <v>16.2059307098389</v>
+        <v>16.2059288024902</v>
       </c>
       <c r="H670" t="n">
         <v>39708</v>
@@ -19828,7 +19828,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G671" t="n">
-        <v>16.2616176605225</v>
+        <v>16.2616195678711</v>
       </c>
       <c r="H671" t="n">
         <v>26089</v>
@@ -19886,7 +19886,7 @@
         <v>17.6916809082031</v>
       </c>
       <c r="G673" t="n">
-        <v>16.911340713501</v>
+        <v>16.9113426208496</v>
       </c>
       <c r="H673" t="n">
         <v>54149</v>
@@ -19915,7 +19915,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G674" t="n">
-        <v>16.3173122406006</v>
+        <v>16.3173084259033</v>
       </c>
       <c r="H674" t="n">
         <v>71685</v>
@@ -19973,7 +19973,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G676" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H676" t="n">
         <v>54594</v>
@@ -20002,7 +20002,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G677" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H677" t="n">
         <v>29454</v>
@@ -20031,7 +20031,7 @@
         <v>16.9537181854248</v>
       </c>
       <c r="G678" t="n">
-        <v>16.2059307098389</v>
+        <v>16.2059288024902</v>
       </c>
       <c r="H678" t="n">
         <v>12610</v>
@@ -20060,7 +20060,7 @@
         <v>17.2061786651611</v>
       </c>
       <c r="G679" t="n">
-        <v>16.4472541809082</v>
+        <v>16.4472522735596</v>
       </c>
       <c r="H679" t="n">
         <v>75304</v>
@@ -20118,7 +20118,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G681" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H681" t="n">
         <v>28477</v>
@@ -20147,7 +20147,7 @@
         <v>16.7012577056885</v>
       </c>
       <c r="G682" t="n">
-        <v>15.9646043777466</v>
+        <v>15.9646024703979</v>
       </c>
       <c r="H682" t="n">
         <v>13217</v>
@@ -20176,7 +20176,7 @@
         <v>16.4682159423828</v>
       </c>
       <c r="G683" t="n">
-        <v>15.7418403625488</v>
+        <v>15.7418384552002</v>
       </c>
       <c r="H683" t="n">
         <v>37888</v>
@@ -20205,7 +20205,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G684" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H684" t="n">
         <v>45521</v>
@@ -20234,7 +20234,7 @@
         <v>16.8760375976562</v>
       </c>
       <c r="G685" t="n">
-        <v>16.1316738128662</v>
+        <v>16.1316757202148</v>
       </c>
       <c r="H685" t="n">
         <v>33702</v>
@@ -20292,7 +20292,7 @@
         <v>16.2157554626465</v>
       </c>
       <c r="G687" t="n">
-        <v>15.5005130767822</v>
+        <v>15.5005140304565</v>
       </c>
       <c r="H687" t="n">
         <v>34503</v>
@@ -20350,7 +20350,7 @@
         <v>16.6429977416992</v>
       </c>
       <c r="G689" t="n">
-        <v>15.9089136123657</v>
+        <v>15.9089117050171</v>
       </c>
       <c r="H689" t="n">
         <v>39172</v>
@@ -20379,7 +20379,7 @@
         <v>16.5264759063721</v>
       </c>
       <c r="G690" t="n">
-        <v>15.7975311279297</v>
+        <v>15.7975301742554</v>
       </c>
       <c r="H690" t="n">
         <v>15685</v>
@@ -20408,7 +20408,7 @@
         <v>16.6041564941406</v>
       </c>
       <c r="G691" t="n">
-        <v>15.8717842102051</v>
+        <v>15.8717813491821</v>
       </c>
       <c r="H691" t="n">
         <v>35414</v>
@@ -20466,7 +20466,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G693" t="n">
-        <v>14.8322286605835</v>
+        <v>14.8322296142578</v>
       </c>
       <c r="H693" t="n">
         <v>74278</v>
@@ -20669,7 +20669,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G700" t="n">
-        <v>15.0364284515381</v>
+        <v>15.0364274978638</v>
       </c>
       <c r="H700" t="n">
         <v>34142</v>
@@ -20727,7 +20727,7 @@
         <v>16.2545948028564</v>
       </c>
       <c r="G702" t="n">
-        <v>15.5376415252686</v>
+        <v>15.5376405715942</v>
       </c>
       <c r="H702" t="n">
         <v>40534</v>
@@ -20756,7 +20756,7 @@
         <v>16.2934341430664</v>
       </c>
       <c r="G703" t="n">
-        <v>15.5747680664062</v>
+        <v>15.5747671127319</v>
       </c>
       <c r="H703" t="n">
         <v>77089</v>
@@ -20785,7 +20785,7 @@
         <v>16.1380748748779</v>
       </c>
       <c r="G704" t="n">
-        <v>15.4262619018555</v>
+        <v>15.4262609481812</v>
       </c>
       <c r="H704" t="n">
         <v>145218</v>
@@ -20814,7 +20814,7 @@
         <v>16.332275390625</v>
       </c>
       <c r="G705" t="n">
-        <v>15.6118965148926</v>
+        <v>15.6118955612183</v>
       </c>
       <c r="H705" t="n">
         <v>37102</v>
@@ -20872,7 +20872,7 @@
         <v>16.0798149108887</v>
       </c>
       <c r="G707" t="n">
-        <v>15.3705711364746</v>
+        <v>15.3705701828003</v>
       </c>
       <c r="H707" t="n">
         <v>58366</v>
@@ -20959,7 +20959,7 @@
         <v>16.2740154266357</v>
       </c>
       <c r="G710" t="n">
-        <v>15.5562047958374</v>
+        <v>15.5562057495117</v>
       </c>
       <c r="H710" t="n">
         <v>17835</v>
@@ -20988,7 +20988,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G711" t="n">
-        <v>15.7604036331177</v>
+        <v>15.760404586792</v>
       </c>
       <c r="H711" t="n">
         <v>25713</v>
@@ -21017,7 +21017,7 @@
         <v>16.856616973877</v>
       </c>
       <c r="G712" t="n">
-        <v>16.1131114959717</v>
+        <v>16.113109588623</v>
       </c>
       <c r="H712" t="n">
         <v>96484</v>
@@ -21046,7 +21046,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G713" t="n">
-        <v>16.2430534362793</v>
+        <v>16.2430553436279</v>
       </c>
       <c r="H713" t="n">
         <v>26553</v>
@@ -21104,7 +21104,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G715" t="n">
-        <v>16.9855937957764</v>
+        <v>16.9855976104736</v>
       </c>
       <c r="H715" t="n">
         <v>139089</v>
@@ -21133,7 +21133,7 @@
         <v>17.8082008361816</v>
       </c>
       <c r="G716" t="n">
-        <v>17.0227222442627</v>
+        <v>17.0227241516113</v>
       </c>
       <c r="H716" t="n">
         <v>35076</v>
@@ -21191,7 +21191,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G718" t="n">
-        <v>17.542501449585</v>
+        <v>17.5424995422363</v>
       </c>
       <c r="H718" t="n">
         <v>38062</v>
@@ -21220,7 +21220,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G719" t="n">
-        <v>17.542501449585</v>
+        <v>17.5424995422363</v>
       </c>
       <c r="H719" t="n">
         <v>75597</v>
@@ -21249,7 +21249,7 @@
         <v>18.2742824554443</v>
       </c>
       <c r="G720" t="n">
-        <v>17.4682445526123</v>
+        <v>17.4682464599609</v>
       </c>
       <c r="H720" t="n">
         <v>21727</v>
@@ -21307,7 +21307,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G722" t="n">
-        <v>18.0065860748291</v>
+        <v>18.0065879821777</v>
       </c>
       <c r="H722" t="n">
         <v>30703</v>
@@ -21423,7 +21423,7 @@
         <v>19.2064456939697</v>
       </c>
       <c r="G726" t="n">
-        <v>18.3592929840088</v>
+        <v>18.3592948913574</v>
       </c>
       <c r="H726" t="n">
         <v>25988</v>
@@ -21481,7 +21481,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G728" t="n">
-        <v>17.7652587890625</v>
+        <v>17.7652626037598</v>
       </c>
       <c r="H728" t="n">
         <v>30824</v>
@@ -21539,7 +21539,7 @@
         <v>17.8470401763916</v>
       </c>
       <c r="G730" t="n">
-        <v>17.0598487854004</v>
+        <v>17.059850692749</v>
       </c>
       <c r="H730" t="n">
         <v>46352</v>
@@ -21568,7 +21568,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G731" t="n">
-        <v>16.9855937957764</v>
+        <v>16.9855976104736</v>
       </c>
       <c r="H731" t="n">
         <v>82850</v>
@@ -21684,7 +21684,7 @@
         <v>18.4490623474121</v>
       </c>
       <c r="G735" t="n">
-        <v>17.6353168487549</v>
+        <v>17.6353187561035</v>
       </c>
       <c r="H735" t="n">
         <v>39308</v>
@@ -21713,7 +21713,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G736" t="n">
-        <v>18.1922245025635</v>
+        <v>18.1922206878662</v>
       </c>
       <c r="H736" t="n">
         <v>69493</v>
@@ -21742,7 +21742,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G737" t="n">
-        <v>19.5844841003418</v>
+        <v>19.5844860076904</v>
       </c>
       <c r="H737" t="n">
         <v>99755</v>
@@ -21771,7 +21771,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G738" t="n">
-        <v>19.6773014068604</v>
+        <v>19.6772994995117</v>
       </c>
       <c r="H738" t="n">
         <v>55073</v>
@@ -21887,7 +21887,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G742" t="n">
-        <v>20.4198398590088</v>
+        <v>20.4198417663574</v>
       </c>
       <c r="H742" t="n">
         <v>47386</v>
@@ -21916,7 +21916,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G743" t="n">
-        <v>20.3270225524902</v>
+        <v>20.3270244598389</v>
       </c>
       <c r="H743" t="n">
         <v>30114</v>
@@ -21945,7 +21945,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G744" t="n">
-        <v>20.1413898468018</v>
+        <v>20.1413879394531</v>
       </c>
       <c r="H744" t="n">
         <v>35528</v>
@@ -22032,7 +22032,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G747" t="n">
-        <v>20.1413898468018</v>
+        <v>20.1413879394531</v>
       </c>
       <c r="H747" t="n">
         <v>37254</v>
@@ -22061,7 +22061,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G748" t="n">
-        <v>20.0949783325195</v>
+        <v>20.0949802398682</v>
       </c>
       <c r="H748" t="n">
         <v>43044</v>
@@ -22090,7 +22090,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G749" t="n">
-        <v>20.466251373291</v>
+        <v>20.4662475585938</v>
       </c>
       <c r="H749" t="n">
         <v>34125</v>
@@ -22206,7 +22206,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G753" t="n">
-        <v>21.8121013641357</v>
+        <v>21.8121032714844</v>
       </c>
       <c r="H753" t="n">
         <v>18138</v>
@@ -22264,7 +22264,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G755" t="n">
-        <v>20.1413898468018</v>
+        <v>20.1413879394531</v>
       </c>
       <c r="H755" t="n">
         <v>48169</v>
@@ -22293,7 +22293,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G756" t="n">
-        <v>20.466251373291</v>
+        <v>20.4662475585938</v>
       </c>
       <c r="H756" t="n">
         <v>70825</v>
@@ -22322,7 +22322,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G757" t="n">
-        <v>20.4198398590088</v>
+        <v>20.4198417663574</v>
       </c>
       <c r="H757" t="n">
         <v>20797</v>
@@ -22351,7 +22351,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G758" t="n">
-        <v>20.3270225524902</v>
+        <v>20.3270244598389</v>
       </c>
       <c r="H758" t="n">
         <v>23340</v>
@@ -22409,7 +22409,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G760" t="n">
-        <v>20.0949783325195</v>
+        <v>20.0949802398682</v>
       </c>
       <c r="H760" t="n">
         <v>18398</v>
@@ -22525,7 +22525,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G764" t="n">
-        <v>19.6308917999268</v>
+        <v>19.6308937072754</v>
       </c>
       <c r="H764" t="n">
         <v>34886</v>
@@ -22554,7 +22554,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G765" t="n">
-        <v>19.5844841003418</v>
+        <v>19.5844860076904</v>
       </c>
       <c r="H765" t="n">
         <v>35652</v>
@@ -22612,7 +22612,7 @@
         <v>19.9541187286377</v>
       </c>
       <c r="G767" t="n">
-        <v>19.0739860534668</v>
+        <v>19.0739879608154</v>
       </c>
       <c r="H767" t="n">
         <v>77644</v>
@@ -22670,7 +22670,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G769" t="n">
-        <v>19.8395614624023</v>
+        <v>19.8395595550537</v>
       </c>
       <c r="H769" t="n">
         <v>15945</v>
@@ -22786,7 +22786,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G773" t="n">
-        <v>19.372745513916</v>
+        <v>19.3727474212646</v>
       </c>
       <c r="H773" t="n">
         <v>12388</v>
@@ -22815,7 +22815,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G774" t="n">
-        <v>19.5594730377197</v>
+        <v>19.5594749450684</v>
       </c>
       <c r="H774" t="n">
         <v>14470</v>
@@ -22844,7 +22844,7 @@
         <v>19.6628170013428</v>
       </c>
       <c r="G775" t="n">
-        <v>18.905933380127</v>
+        <v>18.9059352874756</v>
       </c>
       <c r="H775" t="n">
         <v>26959</v>
@@ -22960,7 +22960,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G779" t="n">
-        <v>18.8125743865967</v>
+        <v>18.812572479248</v>
       </c>
       <c r="H779" t="n">
         <v>10927</v>
@@ -23105,7 +23105,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G784" t="n">
-        <v>19.6995162963867</v>
+        <v>19.6995182037354</v>
       </c>
       <c r="H784" t="n">
         <v>16306</v>
@@ -23134,7 +23134,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G785" t="n">
-        <v>19.1393394470215</v>
+        <v>19.1393413543701</v>
       </c>
       <c r="H785" t="n">
         <v>17581</v>
@@ -23250,7 +23250,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G789" t="n">
-        <v>18.5044765472412</v>
+        <v>18.5044746398926</v>
       </c>
       <c r="H789" t="n">
         <v>32253</v>
@@ -23279,7 +23279,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G790" t="n">
-        <v>18.355094909668</v>
+        <v>18.3550930023193</v>
       </c>
       <c r="H790" t="n">
         <v>26414</v>
@@ -23337,7 +23337,7 @@
         <v>19.1287651062012</v>
       </c>
       <c r="G792" t="n">
-        <v>18.3924388885498</v>
+        <v>18.3924407958984</v>
       </c>
       <c r="H792" t="n">
         <v>27508</v>
@@ -23366,7 +23366,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G793" t="n">
-        <v>18.6725273132324</v>
+        <v>18.6725292205811</v>
       </c>
       <c r="H793" t="n">
         <v>38165</v>
@@ -23395,7 +23395,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G794" t="n">
-        <v>18.6725273132324</v>
+        <v>18.6725292205811</v>
       </c>
       <c r="H794" t="n">
         <v>26327</v>
@@ -23453,7 +23453,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G796" t="n">
-        <v>18.6725273132324</v>
+        <v>18.6725292205811</v>
       </c>
       <c r="H796" t="n">
         <v>16839</v>
@@ -23511,7 +23511,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G798" t="n">
-        <v>18.6725273132324</v>
+        <v>18.6725292205811</v>
       </c>
       <c r="H798" t="n">
         <v>43372</v>
@@ -23569,7 +23569,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G800" t="n">
-        <v>19.9329223632812</v>
+        <v>19.9329242706299</v>
       </c>
       <c r="H800" t="n">
         <v>31271</v>
@@ -23772,7 +23772,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G807" t="n">
-        <v>22.8271675109863</v>
+        <v>22.8271656036377</v>
       </c>
       <c r="H807" t="n">
         <v>71776</v>
@@ -23830,7 +23830,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G809" t="n">
-        <v>23.3406620025635</v>
+        <v>23.3406600952148</v>
       </c>
       <c r="H809" t="n">
         <v>60375</v>
@@ -23888,7 +23888,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G811" t="n">
-        <v>22.9205265045166</v>
+        <v>22.9205284118652</v>
       </c>
       <c r="H811" t="n">
         <v>38908</v>
@@ -24207,7 +24207,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G822" t="n">
-        <v>23.3406620025635</v>
+        <v>23.3406600952148</v>
       </c>
       <c r="H822" t="n">
         <v>6868</v>
@@ -24352,7 +24352,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G827" t="n">
-        <v>22.8271675109863</v>
+        <v>22.8271656036377</v>
       </c>
       <c r="H827" t="n">
         <v>7460</v>
@@ -24439,7 +24439,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G830" t="n">
-        <v>22.8271675109863</v>
+        <v>22.8271656036377</v>
       </c>
       <c r="H830" t="n">
         <v>11430</v>
@@ -24468,7 +24468,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G831" t="n">
-        <v>22.8271675109863</v>
+        <v>22.8271656036377</v>
       </c>
       <c r="H831" t="n">
         <v>6939</v>
@@ -24584,7 +24584,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G835" t="n">
-        <v>23.3406620025635</v>
+        <v>23.3406600952148</v>
       </c>
       <c r="H835" t="n">
         <v>15283</v>
@@ -24642,7 +24642,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G837" t="n">
-        <v>23.7141094207764</v>
+        <v>23.714111328125</v>
       </c>
       <c r="H837" t="n">
         <v>18520</v>
@@ -24671,7 +24671,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G838" t="n">
-        <v>22.8271675109863</v>
+        <v>22.8271656036377</v>
       </c>
       <c r="H838" t="n">
         <v>28752</v>
@@ -24729,7 +24729,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G840" t="n">
-        <v>21.5667724609375</v>
+        <v>21.5667705535889</v>
       </c>
       <c r="H840" t="n">
         <v>38817</v>
@@ -24787,7 +24787,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G842" t="n">
-        <v>21.8001766204834</v>
+        <v>21.8001747131348</v>
       </c>
       <c r="H842" t="n">
         <v>13062</v>
@@ -24845,7 +24845,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G844" t="n">
-        <v>21.0065937042236</v>
+        <v>21.006591796875</v>
       </c>
       <c r="H844" t="n">
         <v>14580</v>
@@ -24990,7 +24990,7 @@
         <v>21.9446754455566</v>
       </c>
       <c r="G849" t="n">
-        <v>21.0999546051025</v>
+        <v>21.0999565124512</v>
       </c>
       <c r="H849" t="n">
         <v>19081</v>
@@ -25367,7 +25367,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G862" t="n">
-        <v>23.3406620025635</v>
+        <v>23.3406600952148</v>
       </c>
       <c r="H862" t="n">
         <v>15813</v>
@@ -25425,7 +25425,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G864" t="n">
-        <v>23.9941959381104</v>
+        <v>23.9941940307617</v>
       </c>
       <c r="H864" t="n">
         <v>26927</v>
@@ -25483,7 +25483,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G866" t="n">
-        <v>24.1342430114746</v>
+        <v>24.134241104126</v>
       </c>
       <c r="H866" t="n">
         <v>117339</v>
@@ -25512,7 +25512,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G867" t="n">
-        <v>24.1342430114746</v>
+        <v>24.134241104126</v>
       </c>
       <c r="H867" t="n">
         <v>37673</v>
@@ -26005,7 +26005,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G884" t="n">
-        <v>22.1269454956055</v>
+        <v>22.1269474029541</v>
       </c>
       <c r="H884" t="n">
         <v>44427</v>
@@ -26034,7 +26034,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G885" t="n">
-        <v>22.967212677002</v>
+        <v>22.9672107696533</v>
       </c>
       <c r="H885" t="n">
         <v>41855</v>
@@ -26063,7 +26063,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G886" t="n">
-        <v>22.1269454956055</v>
+        <v>22.1269474029541</v>
       </c>
       <c r="H886" t="n">
         <v>27142</v>
@@ -26092,7 +26092,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G887" t="n">
-        <v>22.8271675109863</v>
+        <v>22.8271656036377</v>
       </c>
       <c r="H887" t="n">
         <v>31840</v>
@@ -26150,7 +26150,7 @@
         <v>25.0518856048584</v>
       </c>
       <c r="G889" t="n">
-        <v>24.0875606536865</v>
+        <v>24.0875625610352</v>
       </c>
       <c r="H889" t="n">
         <v>14318</v>
@@ -26208,7 +26208,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G891" t="n">
-        <v>24.5543766021729</v>
+        <v>24.5543746948242</v>
       </c>
       <c r="H891" t="n">
         <v>159469</v>
@@ -26266,7 +26266,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G893" t="n">
-        <v>24.3676509857178</v>
+        <v>24.3676490783691</v>
       </c>
       <c r="H893" t="n">
         <v>9165</v>
@@ -26353,7 +26353,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G896" t="n">
-        <v>24.3676509857178</v>
+        <v>24.3676490783691</v>
       </c>
       <c r="H896" t="n">
         <v>15752</v>
@@ -26469,7 +26469,7 @@
         <v>24.7120342254639</v>
       </c>
       <c r="G900" t="n">
-        <v>23.7607936859131</v>
+        <v>23.7607917785645</v>
       </c>
       <c r="H900" t="n">
         <v>11109</v>
@@ -26759,7 +26759,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G910" t="n">
-        <v>23.7141094207764</v>
+        <v>23.714111328125</v>
       </c>
       <c r="H910" t="n">
         <v>15535</v>
@@ -26846,7 +26846,7 @@
         <v>26.0228881835938</v>
       </c>
       <c r="G913" t="n">
-        <v>25.0211868286133</v>
+        <v>25.0211849212646</v>
       </c>
       <c r="H913" t="n">
         <v>29943</v>
@@ -26904,7 +26904,7 @@
         <v>25.0518856048584</v>
       </c>
       <c r="G915" t="n">
-        <v>24.0875606536865</v>
+        <v>24.0875625610352</v>
       </c>
       <c r="H915" t="n">
         <v>27160</v>
@@ -26991,7 +26991,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G918" t="n">
-        <v>23.3406620025635</v>
+        <v>23.3406600952148</v>
       </c>
       <c r="H918" t="n">
         <v>22305</v>
@@ -27223,7 +27223,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G926" t="n">
-        <v>19.8395614624023</v>
+        <v>19.8395595550537</v>
       </c>
       <c r="H926" t="n">
         <v>42284</v>
@@ -27339,7 +27339,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G930" t="n">
-        <v>21.0065937042236</v>
+        <v>21.006591796875</v>
       </c>
       <c r="H930" t="n">
         <v>21059</v>
@@ -27368,7 +27368,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G931" t="n">
-        <v>20.726505279541</v>
+        <v>20.7265071868896</v>
       </c>
       <c r="H931" t="n">
         <v>16494</v>
@@ -27629,7 +27629,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G940" t="n">
-        <v>21.0065937042236</v>
+        <v>21.006591796875</v>
       </c>
       <c r="H940" t="n">
         <v>14225</v>
@@ -27977,7 +27977,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G952" t="n">
-        <v>16.7119102478027</v>
+        <v>16.7119121551514</v>
       </c>
       <c r="H952" t="n">
         <v>87288</v>
@@ -28064,7 +28064,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G955" t="n">
-        <v>18.541820526123</v>
+        <v>18.5418186187744</v>
       </c>
       <c r="H955" t="n">
         <v>25102</v>
@@ -28412,7 +28412,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G967" t="n">
-        <v>22.1736278533936</v>
+        <v>22.1736259460449</v>
       </c>
       <c r="H967" t="n">
         <v>17485</v>
@@ -28528,7 +28528,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G971" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530559539795</v>
       </c>
       <c r="H971" t="n">
         <v>40643</v>
@@ -28557,7 +28557,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G972" t="n">
-        <v>20.1663303375244</v>
+        <v>20.166332244873</v>
       </c>
       <c r="H972" t="n">
         <v>49476</v>
@@ -28673,7 +28673,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G976" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530559539795</v>
       </c>
       <c r="H976" t="n">
         <v>48544</v>
@@ -28702,7 +28702,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G977" t="n">
-        <v>20.1663303375244</v>
+        <v>20.166332244873</v>
       </c>
       <c r="H977" t="n">
         <v>28457</v>
@@ -28760,7 +28760,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G979" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530559539795</v>
       </c>
       <c r="H979" t="n">
         <v>22991</v>
@@ -28876,7 +28876,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G983" t="n">
-        <v>21.5667724609375</v>
+        <v>21.5667705535889</v>
       </c>
       <c r="H983" t="n">
         <v>57275</v>
@@ -29050,7 +29050,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G989" t="n">
-        <v>22.1736278533936</v>
+        <v>22.1736259460449</v>
       </c>
       <c r="H989" t="n">
         <v>51340</v>
@@ -29079,7 +29079,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G990" t="n">
-        <v>21.8001766204834</v>
+        <v>21.8001747131348</v>
       </c>
       <c r="H990" t="n">
         <v>24793</v>
@@ -29108,7 +29108,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G991" t="n">
-        <v>21.5667724609375</v>
+        <v>21.5667705535889</v>
       </c>
       <c r="H991" t="n">
         <v>11542</v>
@@ -29282,7 +29282,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G997" t="n">
-        <v>19.1393394470215</v>
+        <v>19.1393413543701</v>
       </c>
       <c r="H997" t="n">
         <v>23859</v>
@@ -29311,7 +29311,7 @@
         <v>22.6243762969971</v>
       </c>
       <c r="G998" t="n">
-        <v>21.7534923553467</v>
+        <v>21.7534942626953</v>
       </c>
       <c r="H998" t="n">
         <v>76098</v>
@@ -29427,7 +29427,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1002" t="n">
-        <v>20.3530540466309</v>
+        <v>20.3530559539795</v>
       </c>
       <c r="H1002" t="n">
         <v>38321</v>
@@ -29514,7 +29514,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1005" t="n">
-        <v>19.9329223632812</v>
+        <v>19.9329242706299</v>
       </c>
       <c r="H1005" t="n">
         <v>21452</v>
@@ -29601,7 +29601,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G1008" t="n">
-        <v>21.0065937042236</v>
+        <v>21.006591796875</v>
       </c>
       <c r="H1008" t="n">
         <v>36921</v>
@@ -29630,7 +29630,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G1009" t="n">
-        <v>21.5667724609375</v>
+        <v>21.5667705535889</v>
       </c>
       <c r="H1009" t="n">
         <v>42728</v>
@@ -29891,7 +29891,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1018" t="n">
-        <v>18.8125743865967</v>
+        <v>18.812572479248</v>
       </c>
       <c r="H1018" t="n">
         <v>17176</v>
@@ -29920,7 +29920,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1019" t="n">
-        <v>18.2057113647461</v>
+        <v>18.2057132720947</v>
       </c>
       <c r="H1019" t="n">
         <v>43373</v>
@@ -30007,7 +30007,7 @@
         <v>17.7887802124023</v>
       </c>
       <c r="G1022" t="n">
-        <v>17.1040363311768</v>
+        <v>17.1040344238281</v>
       </c>
       <c r="H1022" t="n">
         <v>20900</v>
@@ -30065,7 +30065,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G1024" t="n">
-        <v>16.6617603302002</v>
+        <v>16.6617584228516</v>
       </c>
       <c r="H1024" t="n">
         <v>24826</v>
@@ -30210,7 +30210,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G1029" t="n">
-        <v>16.7182426452637</v>
+        <v>16.718240737915</v>
       </c>
       <c r="H1029" t="n">
         <v>93254</v>
@@ -30355,7 +30355,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1034" t="n">
-        <v>18.1490821838379</v>
+        <v>18.1490802764893</v>
       </c>
       <c r="H1034" t="n">
         <v>19382</v>
@@ -30442,7 +30442,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G1037" t="n">
-        <v>18.826847076416</v>
+        <v>18.8268489837646</v>
       </c>
       <c r="H1037" t="n">
         <v>15503</v>
@@ -30471,7 +30471,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G1038" t="n">
-        <v>18.5067920684814</v>
+        <v>18.5067901611328</v>
       </c>
       <c r="H1038" t="n">
         <v>30888</v>
@@ -30529,7 +30529,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G1040" t="n">
-        <v>18.6574077606201</v>
+        <v>18.6574058532715</v>
       </c>
       <c r="H1040" t="n">
         <v>12934</v>
@@ -30645,7 +30645,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G1044" t="n">
-        <v>18.5067920684814</v>
+        <v>18.5067901611328</v>
       </c>
       <c r="H1044" t="n">
         <v>17310</v>
@@ -30906,7 +30906,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G1053" t="n">
-        <v>20.897798538208</v>
+        <v>20.8978004455566</v>
       </c>
       <c r="H1053" t="n">
         <v>38937</v>
@@ -31022,7 +31022,7 @@
         <v>22.6243762969971</v>
       </c>
       <c r="G1057" t="n">
-        <v>21.9332752227783</v>
+        <v>21.933277130127</v>
       </c>
       <c r="H1057" t="n">
         <v>45506</v>
@@ -31138,7 +31138,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G1061" t="n">
-        <v>22.3098125457764</v>
+        <v>22.309814453125</v>
       </c>
       <c r="H1061" t="n">
         <v>27117</v>
@@ -31312,7 +31312,7 @@
         <v>21.9446754455566</v>
       </c>
       <c r="G1067" t="n">
-        <v>21.2743358612061</v>
+        <v>21.2743377685547</v>
       </c>
       <c r="H1067" t="n">
         <v>8354</v>
@@ -31573,7 +31573,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G1076" t="n">
-        <v>19.5328521728516</v>
+        <v>19.5328540802002</v>
       </c>
       <c r="H1076" t="n">
         <v>7123</v>
@@ -31602,7 +31602,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1077" t="n">
-        <v>20.0976581573486</v>
+        <v>20.0976600646973</v>
       </c>
       <c r="H1077" t="n">
         <v>57729</v>
@@ -31805,7 +31805,7 @@
         <v>19.6628170013428</v>
       </c>
       <c r="G1084" t="n">
-        <v>19.0621814727783</v>
+        <v>19.062183380127</v>
       </c>
       <c r="H1084" t="n">
         <v>12861</v>
@@ -31863,7 +31863,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1086" t="n">
-        <v>18.9209804534912</v>
+        <v>18.9209823608398</v>
       </c>
       <c r="H1086" t="n">
         <v>15251</v>
@@ -31950,7 +31950,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G1089" t="n">
-        <v>17.8101997375488</v>
+        <v>17.8101978302002</v>
       </c>
       <c r="H1089" t="n">
         <v>11701</v>
@@ -32124,7 +32124,7 @@
         <v>18.2354412078857</v>
       </c>
       <c r="G1095" t="n">
-        <v>17.6784057617188</v>
+        <v>17.6784076690674</v>
       </c>
       <c r="H1095" t="n">
         <v>40255</v>
@@ -32182,7 +32182,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G1097" t="n">
-        <v>18.0172901153564</v>
+        <v>18.0172920227051</v>
       </c>
       <c r="H1097" t="n">
         <v>18857</v>
@@ -32211,7 +32211,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1098" t="n">
-        <v>18.9680500030518</v>
+        <v>18.9680480957031</v>
       </c>
       <c r="H1098" t="n">
         <v>57714</v>
@@ -32269,7 +32269,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1100" t="n">
-        <v>18.9680500030518</v>
+        <v>18.9680480957031</v>
       </c>
       <c r="H1100" t="n">
         <v>38979</v>
@@ -32327,7 +32327,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G1102" t="n">
-        <v>18.0361194610596</v>
+        <v>18.0361175537109</v>
       </c>
       <c r="H1102" t="n">
         <v>10913</v>
@@ -32472,7 +32472,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G1107" t="n">
-        <v>17.9419860839844</v>
+        <v>17.9419841766357</v>
       </c>
       <c r="H1107" t="n">
         <v>14867</v>
@@ -32501,7 +32501,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1108" t="n">
-        <v>18.1490821838379</v>
+        <v>18.1490802764893</v>
       </c>
       <c r="H1108" t="n">
         <v>23220</v>
@@ -32559,7 +32559,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1110" t="n">
-        <v>18.1490821838379</v>
+        <v>18.1490802764893</v>
       </c>
       <c r="H1110" t="n">
         <v>7289</v>
@@ -32617,7 +32617,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1112" t="n">
-        <v>18.3561744689941</v>
+        <v>18.3561763763428</v>
       </c>
       <c r="H1112" t="n">
         <v>9961</v>
@@ -32646,7 +32646,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1113" t="n">
-        <v>18.9209804534912</v>
+        <v>18.9209823608398</v>
       </c>
       <c r="H1113" t="n">
         <v>34948</v>
@@ -32675,7 +32675,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1114" t="n">
-        <v>20.5212631225586</v>
+        <v>20.5212650299072</v>
       </c>
       <c r="H1114" t="n">
         <v>25708</v>
@@ -32849,7 +32849,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1120" t="n">
-        <v>20.5212631225586</v>
+        <v>20.5212650299072</v>
       </c>
       <c r="H1120" t="n">
         <v>13548</v>
@@ -33023,7 +33023,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1126" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1126" t="n">
         <v>38618</v>
@@ -33052,7 +33052,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1127" t="n">
-        <v>23.1570243835449</v>
+        <v>23.1570224761963</v>
       </c>
       <c r="H1127" t="n">
         <v>91749</v>
@@ -33284,7 +33284,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1135" t="n">
-        <v>23.533561706543</v>
+        <v>23.5335597991943</v>
       </c>
       <c r="H1135" t="n">
         <v>37839</v>
@@ -33313,7 +33313,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1136" t="n">
-        <v>23.1570243835449</v>
+        <v>23.1570224761963</v>
       </c>
       <c r="H1136" t="n">
         <v>28758</v>
@@ -33400,7 +33400,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1139" t="n">
-        <v>21.9803447723389</v>
+        <v>21.9803428649902</v>
       </c>
       <c r="H1139" t="n">
         <v>23896</v>
@@ -33429,7 +33429,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1140" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1140" t="n">
         <v>41434</v>
@@ -33545,7 +33545,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1144" t="n">
-        <v>21.9803447723389</v>
+        <v>21.9803428649902</v>
       </c>
       <c r="H1144" t="n">
         <v>17518</v>
@@ -33632,7 +33632,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1147" t="n">
-        <v>23.533561706543</v>
+        <v>23.5335597991943</v>
       </c>
       <c r="H1147" t="n">
         <v>124040</v>
@@ -33690,7 +33690,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1149" t="n">
-        <v>24.1924991607666</v>
+        <v>24.192497253418</v>
       </c>
       <c r="H1149" t="n">
         <v>89817</v>
@@ -33777,7 +33777,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G1152" t="n">
-        <v>23.0158214569092</v>
+        <v>23.0158195495605</v>
       </c>
       <c r="H1152" t="n">
         <v>35010</v>
@@ -33922,7 +33922,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1157" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1157" t="n">
         <v>6702</v>
@@ -33951,7 +33951,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1158" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1158" t="n">
         <v>11254</v>
@@ -33980,7 +33980,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1159" t="n">
-        <v>21.9803447723389</v>
+        <v>21.9803428649902</v>
       </c>
       <c r="H1159" t="n">
         <v>8931</v>
@@ -34009,7 +34009,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1160" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1160" t="n">
         <v>4782</v>
@@ -34096,7 +34096,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1163" t="n">
-        <v>21.9803447723389</v>
+        <v>21.9803428649902</v>
       </c>
       <c r="H1163" t="n">
         <v>7133</v>
@@ -34589,7 +34589,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1180" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1180" t="n">
         <v>9877</v>
@@ -34618,7 +34618,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1181" t="n">
-        <v>21.9803447723389</v>
+        <v>21.9803428649902</v>
       </c>
       <c r="H1181" t="n">
         <v>20567</v>
@@ -34705,7 +34705,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1184" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1184" t="n">
         <v>21995</v>
@@ -34908,7 +34908,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1191" t="n">
-        <v>23.9100933074951</v>
+        <v>23.9100952148438</v>
       </c>
       <c r="H1191" t="n">
         <v>18246</v>
@@ -34937,7 +34937,7 @@
         <v>25.9257888793945</v>
       </c>
       <c r="G1192" t="n">
-        <v>25.1338424682617</v>
+        <v>25.1338405609131</v>
       </c>
       <c r="H1192" t="n">
         <v>68922</v>
@@ -34966,7 +34966,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.7573070526123</v>
+        <v>24.7573051452637</v>
       </c>
       <c r="H1193" t="n">
         <v>10170</v>
@@ -35024,7 +35024,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G1195" t="n">
-        <v>24.5690364837646</v>
+        <v>24.569034576416</v>
       </c>
       <c r="H1195" t="n">
         <v>22609</v>
@@ -35140,7 +35140,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1199" t="n">
-        <v>24.3337001800537</v>
+        <v>24.3336982727051</v>
       </c>
       <c r="H1199" t="n">
         <v>31535</v>
@@ -35285,7 +35285,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1204" t="n">
-        <v>24.3337001800537</v>
+        <v>24.3336982727051</v>
       </c>
       <c r="H1204" t="n">
         <v>35811</v>
@@ -35314,7 +35314,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1205" t="n">
-        <v>24.1924991607666</v>
+        <v>24.192497253418</v>
       </c>
       <c r="H1205" t="n">
         <v>30448</v>
@@ -35372,7 +35372,7 @@
         <v>25.9257888793945</v>
       </c>
       <c r="G1207" t="n">
-        <v>25.1338424682617</v>
+        <v>25.1338405609131</v>
       </c>
       <c r="H1207" t="n">
         <v>44723</v>
@@ -35401,7 +35401,7 @@
         <v>26.1685390472412</v>
       </c>
       <c r="G1208" t="n">
-        <v>25.369176864624</v>
+        <v>25.3691749572754</v>
       </c>
       <c r="H1208" t="n">
         <v>93294</v>
@@ -35488,7 +35488,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1211" t="n">
-        <v>23.9100933074951</v>
+        <v>23.9100952148438</v>
       </c>
       <c r="H1211" t="n">
         <v>145585</v>
@@ -35546,7 +35546,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1213" t="n">
-        <v>23.9100933074951</v>
+        <v>23.9100952148438</v>
       </c>
       <c r="H1213" t="n">
         <v>55602</v>
@@ -35604,7 +35604,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1215" t="n">
-        <v>23.3923587799072</v>
+        <v>23.3923568725586</v>
       </c>
       <c r="H1215" t="n">
         <v>30211</v>
@@ -35691,7 +35691,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1218" t="n">
-        <v>23.1099529266357</v>
+        <v>23.1099548339844</v>
       </c>
       <c r="H1218" t="n">
         <v>44072</v>
@@ -36010,7 +36010,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1229" t="n">
-        <v>23.1099529266357</v>
+        <v>23.1099548339844</v>
       </c>
       <c r="H1229" t="n">
         <v>11949</v>
@@ -36126,7 +36126,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1233" t="n">
-        <v>23.1099529266357</v>
+        <v>23.1099548339844</v>
       </c>
       <c r="H1233" t="n">
         <v>59785</v>
@@ -36242,7 +36242,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1237" t="n">
-        <v>22.3568820953369</v>
+        <v>22.3568801879883</v>
       </c>
       <c r="H1237" t="n">
         <v>15807</v>
@@ -36300,7 +36300,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G1239" t="n">
-        <v>22.3098125457764</v>
+        <v>22.309814453125</v>
       </c>
       <c r="H1239" t="n">
         <v>22787</v>
@@ -36329,7 +36329,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1240" t="n">
-        <v>21.9803447723389</v>
+        <v>21.9803428649902</v>
       </c>
       <c r="H1240" t="n">
         <v>23706</v>
@@ -36387,7 +36387,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G1242" t="n">
-        <v>21.1802043914795</v>
+        <v>21.1802024841309</v>
       </c>
       <c r="H1242" t="n">
         <v>13607</v>
@@ -36619,7 +36619,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1250" t="n">
-        <v>23.533561706543</v>
+        <v>23.5335597991943</v>
       </c>
       <c r="H1250" t="n">
         <v>46385</v>
@@ -36677,7 +36677,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1252" t="n">
-        <v>23.3923587799072</v>
+        <v>23.3923568725586</v>
       </c>
       <c r="H1252" t="n">
         <v>59927</v>
@@ -36909,7 +36909,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1260" t="n">
-        <v>23.1570243835449</v>
+        <v>23.1570224761963</v>
       </c>
       <c r="H1260" t="n">
         <v>25058</v>
@@ -37170,7 +37170,7 @@
         <v>27.1395435333252</v>
       </c>
       <c r="G1269" t="n">
-        <v>26.3105201721191</v>
+        <v>26.3105182647705</v>
       </c>
       <c r="H1269" t="n">
         <v>72054</v>
@@ -62014,7 +62014,7 @@
         <v>25.5</v>
       </c>
       <c r="D2126" t="n">
-        <v>26.4500007629395</v>
+        <v>26.5</v>
       </c>
       <c r="E2126" t="n">
         <v>25.5</v>
@@ -62029,6 +62029,35 @@
         <v>47878</v>
       </c>
       <c r="I2126" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2127" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2127" t="n">
+        <v>25.5499992370605</v>
+      </c>
+      <c r="D2127" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E2127" t="n">
+        <v>25.4500007629395</v>
+      </c>
+      <c r="F2127" t="n">
+        <v>25.4500007629395</v>
+      </c>
+      <c r="G2127" t="n">
+        <v>25.4500007629395</v>
+      </c>
+      <c r="H2127" t="n">
+        <v>53007</v>
+      </c>
+      <c r="I2127" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -456,7 +456,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G3" t="n">
-        <v>7.85125923156738</v>
+        <v>7.8512601852417</v>
       </c>
       <c r="H3" t="n">
         <v>1125391</v>
@@ -485,7 +485,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G4" t="n">
-        <v>7.7599663734436</v>
+        <v>7.75996732711792</v>
       </c>
       <c r="H4" t="n">
         <v>686773</v>
@@ -514,7 +514,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G5" t="n">
-        <v>7.7599663734436</v>
+        <v>7.75996732711792</v>
       </c>
       <c r="H5" t="n">
         <v>360346</v>
@@ -572,7 +572,7 @@
         <v>8.1253547668457</v>
       </c>
       <c r="G7" t="n">
-        <v>7.63945817947388</v>
+        <v>7.63945913314819</v>
       </c>
       <c r="H7" t="n">
         <v>72296</v>
@@ -601,7 +601,7 @@
         <v>8.31955623626709</v>
       </c>
       <c r="G8" t="n">
-        <v>7.82204532623291</v>
+        <v>7.82204580307007</v>
       </c>
       <c r="H8" t="n">
         <v>85887</v>
@@ -630,7 +630,7 @@
         <v>8.41859817504883</v>
       </c>
       <c r="G9" t="n">
-        <v>7.91516494750977</v>
+        <v>7.91516637802124</v>
       </c>
       <c r="H9" t="n">
         <v>85323</v>
@@ -659,7 +659,7 @@
         <v>8.10884761810303</v>
       </c>
       <c r="G10" t="n">
-        <v>7.62393808364868</v>
+        <v>7.623939037323</v>
       </c>
       <c r="H10" t="n">
         <v>23688</v>
@@ -688,7 +688,7 @@
         <v>8.42830753326416</v>
       </c>
       <c r="G11" t="n">
-        <v>7.92429399490356</v>
+        <v>7.92429494857788</v>
       </c>
       <c r="H11" t="n">
         <v>19928</v>
@@ -804,7 +804,7 @@
         <v>7.71656322479248</v>
       </c>
       <c r="G15" t="n">
-        <v>7.25511169433594</v>
+        <v>7.25511312484741</v>
       </c>
       <c r="H15" t="n">
         <v>329290</v>
@@ -833,7 +833,7 @@
         <v>7.95154619216919</v>
       </c>
       <c r="G16" t="n">
-        <v>7.47604370117188</v>
+        <v>7.47604322433472</v>
       </c>
       <c r="H16" t="n">
         <v>61150</v>
@@ -920,7 +920,7 @@
         <v>7.8651270866394</v>
       </c>
       <c r="G19" t="n">
-        <v>7.39479207992554</v>
+        <v>7.39479160308838</v>
       </c>
       <c r="H19" t="n">
         <v>36988</v>
@@ -949,7 +949,7 @@
         <v>7.95251703262329</v>
       </c>
       <c r="G20" t="n">
-        <v>7.47695636749268</v>
+        <v>7.47695541381836</v>
       </c>
       <c r="H20" t="n">
         <v>51465</v>
@@ -978,7 +978,7 @@
         <v>7.97193717956543</v>
       </c>
       <c r="G21" t="n">
-        <v>7.49521446228027</v>
+        <v>7.49521493911743</v>
       </c>
       <c r="H21" t="n">
         <v>14400</v>
@@ -1007,7 +1007,7 @@
         <v>8.08068943023682</v>
       </c>
       <c r="G22" t="n">
-        <v>7.59746360778809</v>
+        <v>7.59746408462524</v>
       </c>
       <c r="H22" t="n">
         <v>16520</v>
@@ -1036,7 +1036,7 @@
         <v>8.24381828308105</v>
       </c>
       <c r="G23" t="n">
-        <v>7.75083780288696</v>
+        <v>7.75083827972412</v>
       </c>
       <c r="H23" t="n">
         <v>147231</v>
@@ -1094,7 +1094,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G25" t="n">
-        <v>7.80561399459839</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H25" t="n">
         <v>57598</v>
@@ -1123,7 +1123,7 @@
         <v>8.37101936340332</v>
       </c>
       <c r="G26" t="n">
-        <v>7.87043285369873</v>
+        <v>7.87043237686157</v>
       </c>
       <c r="H26" t="n">
         <v>12597</v>
@@ -1152,7 +1152,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G27" t="n">
-        <v>7.80561399459839</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H27" t="n">
         <v>7454</v>
@@ -1181,7 +1181,7 @@
         <v>8.45743942260742</v>
       </c>
       <c r="G28" t="n">
-        <v>7.95168399810791</v>
+        <v>7.95168542861938</v>
       </c>
       <c r="H28" t="n">
         <v>134473</v>
@@ -1239,7 +1239,7 @@
         <v>8.47394561767578</v>
       </c>
       <c r="G30" t="n">
-        <v>7.96720314025879</v>
+        <v>7.96720409393311</v>
       </c>
       <c r="H30" t="n">
         <v>238620</v>
@@ -1268,7 +1268,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G31" t="n">
-        <v>7.85125923156738</v>
+        <v>7.8512601852417</v>
       </c>
       <c r="H31" t="n">
         <v>21511</v>
@@ -1297,7 +1297,7 @@
         <v>8.25741195678711</v>
       </c>
       <c r="G32" t="n">
-        <v>7.76361846923828</v>
+        <v>7.76361799240112</v>
       </c>
       <c r="H32" t="n">
         <v>19336</v>
@@ -1326,7 +1326,7 @@
         <v>8.20497798919678</v>
       </c>
       <c r="G33" t="n">
-        <v>7.71432065963745</v>
+        <v>7.71432018280029</v>
       </c>
       <c r="H33" t="n">
         <v>19958</v>
@@ -1355,7 +1355,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G34" t="n">
-        <v>7.80561399459839</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H34" t="n">
         <v>33613</v>
@@ -1471,7 +1471,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G38" t="n">
-        <v>7.80561399459839</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H38" t="n">
         <v>50515</v>
@@ -1500,7 +1500,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G39" t="n">
-        <v>7.85125923156738</v>
+        <v>7.8512601852417</v>
       </c>
       <c r="H39" t="n">
         <v>3319</v>
@@ -1529,7 +1529,7 @@
         <v>8.29625225067139</v>
       </c>
       <c r="G40" t="n">
-        <v>7.80013561248779</v>
+        <v>7.80013608932495</v>
       </c>
       <c r="H40" t="n">
         <v>43895</v>
@@ -1558,7 +1558,7 @@
         <v>8.12923908233643</v>
       </c>
       <c r="G41" t="n">
-        <v>7.64311075210571</v>
+        <v>7.6431097984314</v>
       </c>
       <c r="H41" t="n">
         <v>69304</v>
@@ -1616,7 +1616,7 @@
         <v>8.1855583190918</v>
       </c>
       <c r="G43" t="n">
-        <v>7.69606113433838</v>
+        <v>7.69606161117554</v>
       </c>
       <c r="H43" t="n">
         <v>12672</v>
@@ -1674,7 +1674,7 @@
         <v>8.35062789916992</v>
       </c>
       <c r="G45" t="n">
-        <v>7.85125923156738</v>
+        <v>7.8512601852417</v>
       </c>
       <c r="H45" t="n">
         <v>15675</v>
@@ -1703,7 +1703,7 @@
         <v>8.33606338500977</v>
       </c>
       <c r="G46" t="n">
-        <v>7.83756685256958</v>
+        <v>7.83756637573242</v>
       </c>
       <c r="H46" t="n">
         <v>4029</v>
@@ -1761,7 +1761,7 @@
         <v>8.10787677764893</v>
       </c>
       <c r="G48" t="n">
-        <v>7.62302589416504</v>
+        <v>7.62302541732788</v>
       </c>
       <c r="H48" t="n">
         <v>5413</v>
@@ -1848,7 +1848,7 @@
         <v>8.44772911071777</v>
       </c>
       <c r="G51" t="n">
-        <v>7.94255399703979</v>
+        <v>7.94255352020264</v>
       </c>
       <c r="H51" t="n">
         <v>78995</v>
@@ -1877,7 +1877,7 @@
         <v>8.51667022705078</v>
       </c>
       <c r="G52" t="n">
-        <v>8.00737380981445</v>
+        <v>8.00737285614014</v>
       </c>
       <c r="H52" t="n">
         <v>142170</v>
@@ -1935,7 +1935,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G54" t="n">
-        <v>8.24930191040039</v>
+        <v>8.24930095672607</v>
       </c>
       <c r="H54" t="n">
         <v>56090</v>
@@ -1964,7 +1964,7 @@
         <v>8.94293975830078</v>
       </c>
       <c r="G55" t="n">
-        <v>8.40815162658691</v>
+        <v>8.40815353393555</v>
       </c>
       <c r="H55" t="n">
         <v>93447</v>
@@ -2022,7 +2022,7 @@
         <v>9.24977684020996</v>
       </c>
       <c r="G57" t="n">
-        <v>8.69663906097412</v>
+        <v>8.69664001464844</v>
       </c>
       <c r="H57" t="n">
         <v>80805</v>
@@ -2051,7 +2051,7 @@
         <v>9.46728229522705</v>
       </c>
       <c r="G58" t="n">
-        <v>8.90113639831543</v>
+        <v>8.90113830566406</v>
       </c>
       <c r="H58" t="n">
         <v>74281</v>
@@ -2080,7 +2080,7 @@
         <v>9.08859062194824</v>
       </c>
       <c r="G59" t="n">
-        <v>8.54509162902832</v>
+        <v>8.54509258270264</v>
       </c>
       <c r="H59" t="n">
         <v>57537</v>
@@ -2109,7 +2109,7 @@
         <v>8.75844955444336</v>
       </c>
       <c r="G60" t="n">
-        <v>8.234694480896</v>
+        <v>8.23469352722168</v>
       </c>
       <c r="H60" t="n">
         <v>78366</v>
@@ -2138,7 +2138,7 @@
         <v>8.71960926055908</v>
       </c>
       <c r="G61" t="n">
-        <v>8.19817543029785</v>
+        <v>8.19817638397217</v>
       </c>
       <c r="H61" t="n">
         <v>19712</v>
@@ -2167,7 +2167,7 @@
         <v>8.94973659515381</v>
       </c>
       <c r="G62" t="n">
-        <v>8.41454124450684</v>
+        <v>8.41454219818115</v>
       </c>
       <c r="H62" t="n">
         <v>40240</v>
@@ -2196,7 +2196,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G63" t="n">
-        <v>8.30772972106934</v>
+        <v>8.30772876739502</v>
       </c>
       <c r="H63" t="n">
         <v>12792</v>
@@ -2225,7 +2225,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G64" t="n">
-        <v>8.39902114868164</v>
+        <v>8.39902210235596</v>
       </c>
       <c r="H64" t="n">
         <v>50571</v>
@@ -2254,7 +2254,7 @@
         <v>9.20511054992676</v>
       </c>
       <c r="G65" t="n">
-        <v>8.65464401245117</v>
+        <v>8.65464305877686</v>
       </c>
       <c r="H65" t="n">
         <v>35765</v>
@@ -2457,7 +2457,7 @@
         <v>9.37115287780762</v>
       </c>
       <c r="G72" t="n">
-        <v>8.81075572967529</v>
+        <v>8.81075763702393</v>
       </c>
       <c r="H72" t="n">
         <v>39116</v>
@@ -2486,7 +2486,7 @@
         <v>9.63235282897949</v>
       </c>
       <c r="G73" t="n">
-        <v>9.05633926391602</v>
+        <v>9.05633735656738</v>
       </c>
       <c r="H73" t="n">
         <v>79933</v>
@@ -2544,7 +2544,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G75" t="n">
-        <v>9.27544116973877</v>
+        <v>9.2754430770874</v>
       </c>
       <c r="H75" t="n">
         <v>612811</v>
@@ -2573,7 +2573,7 @@
         <v>9.61293315887451</v>
       </c>
       <c r="G76" t="n">
-        <v>9.03807830810547</v>
+        <v>9.03807926177979</v>
       </c>
       <c r="H76" t="n">
         <v>25372</v>
@@ -2602,7 +2602,7 @@
         <v>9.63332366943359</v>
       </c>
       <c r="G77" t="n">
-        <v>9.05725002288818</v>
+        <v>9.0572509765625</v>
       </c>
       <c r="H77" t="n">
         <v>123734</v>
@@ -2660,7 +2660,7 @@
         <v>9.70614910125732</v>
       </c>
       <c r="G79" t="n">
-        <v>9.12572288513184</v>
+        <v>9.12572193145752</v>
       </c>
       <c r="H79" t="n">
         <v>25765</v>
@@ -2718,7 +2718,7 @@
         <v>9.53525161743164</v>
       </c>
       <c r="G81" t="n">
-        <v>8.96504497528076</v>
+        <v>8.96504402160645</v>
       </c>
       <c r="H81" t="n">
         <v>14579</v>
@@ -2776,7 +2776,7 @@
         <v>9.50320911407471</v>
       </c>
       <c r="G83" t="n">
-        <v>8.93491649627686</v>
+        <v>8.93491554260254</v>
       </c>
       <c r="H83" t="n">
         <v>21357</v>
@@ -2834,7 +2834,7 @@
         <v>9.40610885620117</v>
       </c>
       <c r="G85" t="n">
-        <v>8.84362316131592</v>
+        <v>8.84362411499023</v>
       </c>
       <c r="H85" t="n">
         <v>64744</v>
@@ -2863,7 +2863,7 @@
         <v>9.16238689422607</v>
       </c>
       <c r="G86" t="n">
-        <v>8.61447620391846</v>
+        <v>8.61447525024414</v>
       </c>
       <c r="H86" t="n">
         <v>63090</v>
@@ -2892,7 +2892,7 @@
         <v>8.98954772949219</v>
       </c>
       <c r="G87" t="n">
-        <v>8.45197296142578</v>
+        <v>8.45197200775146</v>
       </c>
       <c r="H87" t="n">
         <v>53966</v>
@@ -2921,7 +2921,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G88" t="n">
-        <v>8.30772972106934</v>
+        <v>8.30772876739502</v>
       </c>
       <c r="H88" t="n">
         <v>54203</v>
@@ -2950,7 +2950,7 @@
         <v>8.43413352966309</v>
       </c>
       <c r="G89" t="n">
-        <v>7.92977142333984</v>
+        <v>7.929771900177</v>
       </c>
       <c r="H89" t="n">
         <v>72833</v>
@@ -2979,7 +2979,7 @@
         <v>8.77689933776855</v>
       </c>
       <c r="G90" t="n">
-        <v>8.25204086303711</v>
+        <v>8.25203990936279</v>
       </c>
       <c r="H90" t="n">
         <v>32211</v>
@@ -3153,7 +3153,7 @@
         <v>9.30706596374512</v>
       </c>
       <c r="G96" t="n">
-        <v>8.75050163269043</v>
+        <v>8.75050449371338</v>
       </c>
       <c r="H96" t="n">
         <v>28672</v>
@@ -3182,7 +3182,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G97" t="n">
-        <v>8.30772972106934</v>
+        <v>8.30772876739502</v>
       </c>
       <c r="H97" t="n">
         <v>82302</v>
@@ -3211,7 +3211,7 @@
         <v>8.30207824707031</v>
       </c>
       <c r="G98" t="n">
-        <v>7.80561399459839</v>
+        <v>7.80561351776123</v>
       </c>
       <c r="H98" t="n">
         <v>31873</v>
@@ -3240,7 +3240,7 @@
         <v>8.48462677001953</v>
       </c>
       <c r="G99" t="n">
-        <v>7.97724580764771</v>
+        <v>7.97724628448486</v>
       </c>
       <c r="H99" t="n">
         <v>22913</v>
@@ -3269,7 +3269,7 @@
         <v>7.97193717956543</v>
       </c>
       <c r="G100" t="n">
-        <v>7.49521446228027</v>
+        <v>7.49521493911743</v>
       </c>
       <c r="H100" t="n">
         <v>32370</v>
@@ -3298,7 +3298,7 @@
         <v>8.25352764129639</v>
       </c>
       <c r="G101" t="n">
-        <v>7.7599663734436</v>
+        <v>7.75996732711792</v>
       </c>
       <c r="H101" t="n">
         <v>13973</v>
@@ -3327,7 +3327,7 @@
         <v>8.19041347503662</v>
       </c>
       <c r="G102" t="n">
-        <v>7.70062685012817</v>
+        <v>7.70062637329102</v>
       </c>
       <c r="H102" t="n">
         <v>33890</v>
@@ -3356,7 +3356,7 @@
         <v>8.3700475692749</v>
       </c>
       <c r="G103" t="n">
-        <v>7.8695182800293</v>
+        <v>7.86951923370361</v>
       </c>
       <c r="H103" t="n">
         <v>25306</v>
@@ -3385,7 +3385,7 @@
         <v>8.3700475692749</v>
       </c>
       <c r="G104" t="n">
-        <v>7.8695182800293</v>
+        <v>7.86951923370361</v>
       </c>
       <c r="H104" t="n">
         <v>30512</v>
@@ -3443,7 +3443,7 @@
         <v>9.27210998535156</v>
       </c>
       <c r="G106" t="n">
-        <v>8.71763801574707</v>
+        <v>8.71763706207275</v>
       </c>
       <c r="H106" t="n">
         <v>46620</v>
@@ -3530,7 +3530,7 @@
         <v>8.98760604858398</v>
       </c>
       <c r="G109" t="n">
-        <v>8.45014762878418</v>
+        <v>8.45014667510986</v>
       </c>
       <c r="H109" t="n">
         <v>17509</v>
@@ -3588,7 +3588,7 @@
         <v>9.19443035125732</v>
       </c>
       <c r="G111" t="n">
-        <v>8.64460468292236</v>
+        <v>8.64460372924805</v>
       </c>
       <c r="H111" t="n">
         <v>53266</v>
@@ -3617,7 +3617,7 @@
         <v>9.06334495544434</v>
       </c>
       <c r="G112" t="n">
-        <v>8.5213565826416</v>
+        <v>8.52135562896729</v>
       </c>
       <c r="H112" t="n">
         <v>56861</v>
@@ -3704,7 +3704,7 @@
         <v>9.04586696624756</v>
       </c>
       <c r="G115" t="n">
-        <v>8.50492382049561</v>
+        <v>8.50492477416992</v>
       </c>
       <c r="H115" t="n">
         <v>61099</v>
@@ -3733,7 +3733,7 @@
         <v>9.2138500213623</v>
       </c>
       <c r="G116" t="n">
-        <v>8.66285991668701</v>
+        <v>8.66286182403564</v>
       </c>
       <c r="H116" t="n">
         <v>60391</v>
@@ -3762,7 +3762,7 @@
         <v>8.51084423065186</v>
       </c>
       <c r="G117" t="n">
-        <v>8.0018949508667</v>
+        <v>8.00189590454102</v>
       </c>
       <c r="H117" t="n">
         <v>101226</v>
@@ -3791,7 +3791,7 @@
         <v>8.49724960327148</v>
       </c>
       <c r="G118" t="n">
-        <v>7.98911428451538</v>
+        <v>7.98911476135254</v>
       </c>
       <c r="H118" t="n">
         <v>42084</v>
@@ -3878,7 +3878,7 @@
         <v>9.03324413299561</v>
       </c>
       <c r="G121" t="n">
-        <v>8.49305629730225</v>
+        <v>8.49305725097656</v>
       </c>
       <c r="H121" t="n">
         <v>102634</v>
@@ -3907,7 +3907,7 @@
         <v>8.80700016021729</v>
       </c>
       <c r="G122" t="n">
-        <v>8.28034210205078</v>
+        <v>8.28034114837646</v>
       </c>
       <c r="H122" t="n">
         <v>51549</v>
@@ -3936,7 +3936,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G123" t="n">
-        <v>8.39902114868164</v>
+        <v>8.39902210235596</v>
       </c>
       <c r="H123" t="n">
         <v>89881</v>
@@ -3965,7 +3965,7 @@
         <v>8.99149036407471</v>
       </c>
       <c r="G124" t="n">
-        <v>8.45379829406738</v>
+        <v>8.4537992477417</v>
       </c>
       <c r="H124" t="n">
         <v>78582</v>
@@ -3994,7 +3994,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G125" t="n">
-        <v>8.39902114868164</v>
+        <v>8.39902210235596</v>
       </c>
       <c r="H125" t="n">
         <v>508178</v>
@@ -4052,7 +4052,7 @@
         <v>9.55078792572021</v>
       </c>
       <c r="G127" t="n">
-        <v>8.97964954376221</v>
+        <v>8.97965049743652</v>
       </c>
       <c r="H127" t="n">
         <v>112485</v>
@@ -4081,7 +4081,7 @@
         <v>9.48281764984131</v>
       </c>
       <c r="G128" t="n">
-        <v>8.91574573516846</v>
+        <v>8.91574478149414</v>
       </c>
       <c r="H128" t="n">
         <v>65394</v>
@@ -4110,7 +4110,7 @@
         <v>9.52748394012451</v>
       </c>
       <c r="G129" t="n">
-        <v>8.95773983001709</v>
+        <v>8.95774078369141</v>
       </c>
       <c r="H129" t="n">
         <v>150488</v>
@@ -4139,7 +4139,7 @@
         <v>9.67119312286377</v>
       </c>
       <c r="G130" t="n">
-        <v>9.09285545349121</v>
+        <v>9.09285449981689</v>
       </c>
       <c r="H130" t="n">
         <v>32320</v>
@@ -4226,7 +4226,7 @@
         <v>9.53525161743164</v>
       </c>
       <c r="G133" t="n">
-        <v>8.96504497528076</v>
+        <v>8.96504402160645</v>
       </c>
       <c r="H133" t="n">
         <v>44153</v>
@@ -4255,7 +4255,7 @@
         <v>9.5935115814209</v>
       </c>
       <c r="G134" t="n">
-        <v>9.01981735229492</v>
+        <v>9.01981830596924</v>
       </c>
       <c r="H134" t="n">
         <v>86092</v>
@@ -4284,7 +4284,7 @@
         <v>9.35755920410156</v>
       </c>
       <c r="G135" t="n">
-        <v>8.79797649383545</v>
+        <v>8.79797744750977</v>
       </c>
       <c r="H135" t="n">
         <v>37188</v>
@@ -4313,7 +4313,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G136" t="n">
-        <v>8.30772972106934</v>
+        <v>8.30772876739502</v>
       </c>
       <c r="H136" t="n">
         <v>90963</v>
@@ -4371,7 +4371,7 @@
         <v>8.70018863677979</v>
       </c>
       <c r="G138" t="n">
-        <v>8.17991733551025</v>
+        <v>8.17991638183594</v>
       </c>
       <c r="H138" t="n">
         <v>33830</v>
@@ -4458,7 +4458,7 @@
         <v>8.66523265838623</v>
       </c>
       <c r="G141" t="n">
-        <v>8.14705181121826</v>
+        <v>8.14705085754395</v>
       </c>
       <c r="H141" t="n">
         <v>15104</v>
@@ -4487,7 +4487,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G142" t="n">
-        <v>8.24930191040039</v>
+        <v>8.24930095672607</v>
       </c>
       <c r="H142" t="n">
         <v>40885</v>
@@ -4516,7 +4516,7 @@
         <v>8.8798246383667</v>
       </c>
       <c r="G143" t="n">
-        <v>8.34881019592285</v>
+        <v>8.34881114959717</v>
       </c>
       <c r="H143" t="n">
         <v>25023</v>
@@ -4574,7 +4574,7 @@
         <v>8.76815986633301</v>
       </c>
       <c r="G145" t="n">
-        <v>8.24382400512695</v>
+        <v>8.24382495880127</v>
       </c>
       <c r="H145" t="n">
         <v>27159</v>
@@ -4603,7 +4603,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G146" t="n">
-        <v>8.30772972106934</v>
+        <v>8.30772876739502</v>
       </c>
       <c r="H146" t="n">
         <v>74791</v>
@@ -4632,7 +4632,7 @@
         <v>8.77398586273193</v>
       </c>
       <c r="G147" t="n">
-        <v>8.24930191040039</v>
+        <v>8.24930095672607</v>
       </c>
       <c r="H147" t="n">
         <v>46996</v>
@@ -4661,7 +4661,7 @@
         <v>8.98178005218506</v>
       </c>
       <c r="G148" t="n">
-        <v>8.44466972351074</v>
+        <v>8.44467067718506</v>
       </c>
       <c r="H148" t="n">
         <v>99143</v>
@@ -4690,7 +4690,7 @@
         <v>8.94293975830078</v>
       </c>
       <c r="G149" t="n">
-        <v>8.40815162658691</v>
+        <v>8.40815353393555</v>
       </c>
       <c r="H149" t="n">
         <v>78033</v>
@@ -4748,7 +4748,7 @@
         <v>8.69047927856445</v>
       </c>
       <c r="G151" t="n">
-        <v>8.1707878112793</v>
+        <v>8.17078876495361</v>
       </c>
       <c r="H151" t="n">
         <v>15730</v>
@@ -4806,7 +4806,7 @@
         <v>8.82739067077637</v>
       </c>
       <c r="G153" t="n">
-        <v>8.29951286315918</v>
+        <v>8.29951190948486</v>
       </c>
       <c r="H153" t="n">
         <v>35901</v>
@@ -4864,7 +4864,7 @@
         <v>8.68659496307373</v>
       </c>
       <c r="G155" t="n">
-        <v>8.16713714599609</v>
+        <v>8.16713428497314</v>
       </c>
       <c r="H155" t="n">
         <v>67644</v>
@@ -4980,7 +4980,7 @@
         <v>8.90410041809082</v>
       </c>
       <c r="G159" t="n">
-        <v>8.37163543701172</v>
+        <v>8.37163352966309</v>
       </c>
       <c r="H159" t="n">
         <v>31397</v>
@@ -5038,7 +5038,7 @@
         <v>9.20316886901855</v>
       </c>
       <c r="G161" t="n">
-        <v>8.65281867980957</v>
+        <v>8.65281772613525</v>
       </c>
       <c r="H161" t="n">
         <v>24925</v>
@@ -5067,7 +5067,7 @@
         <v>9.20316886901855</v>
       </c>
       <c r="G162" t="n">
-        <v>8.65281867980957</v>
+        <v>8.65281772613525</v>
       </c>
       <c r="H162" t="n">
         <v>10411</v>
@@ -5096,7 +5096,7 @@
         <v>9.26822566986084</v>
       </c>
       <c r="G163" t="n">
-        <v>8.71398544311523</v>
+        <v>8.71398448944092</v>
       </c>
       <c r="H163" t="n">
         <v>14598</v>
@@ -5125,7 +5125,7 @@
         <v>9.21482086181641</v>
       </c>
       <c r="G164" t="n">
-        <v>8.66377544403076</v>
+        <v>8.66377449035645</v>
       </c>
       <c r="H164" t="n">
         <v>26339</v>
@@ -5183,7 +5183,7 @@
         <v>9.57894706726074</v>
       </c>
       <c r="G166" t="n">
-        <v>9.00612545013428</v>
+        <v>9.00612640380859</v>
       </c>
       <c r="H166" t="n">
         <v>21729</v>
@@ -5270,7 +5270,7 @@
         <v>9.33522605895996</v>
       </c>
       <c r="G169" t="n">
-        <v>8.77697849273682</v>
+        <v>8.77698040008545</v>
       </c>
       <c r="H169" t="n">
         <v>11871</v>
@@ -5299,7 +5299,7 @@
         <v>9.48573112487793</v>
       </c>
       <c r="G170" t="n">
-        <v>8.91848468780518</v>
+        <v>8.91848373413086</v>
       </c>
       <c r="H170" t="n">
         <v>9464</v>
@@ -5328,7 +5328,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G171" t="n">
-        <v>8.992431640625</v>
+        <v>8.99243068695068</v>
       </c>
       <c r="H171" t="n">
         <v>18448</v>
@@ -5357,7 +5357,7 @@
         <v>9.75858306884766</v>
       </c>
       <c r="G172" t="n">
-        <v>9.17501926422119</v>
+        <v>9.17502021789551</v>
       </c>
       <c r="H172" t="n">
         <v>58649</v>
@@ -5386,7 +5386,7 @@
         <v>9.72751140594482</v>
       </c>
       <c r="G173" t="n">
-        <v>9.14580535888672</v>
+        <v>9.14580631256104</v>
       </c>
       <c r="H173" t="n">
         <v>31014</v>
@@ -5444,7 +5444,7 @@
         <v>9.92753791809082</v>
       </c>
       <c r="G175" t="n">
-        <v>9.33387088775635</v>
+        <v>9.33387184143066</v>
       </c>
       <c r="H175" t="n">
         <v>15678</v>
@@ -5473,7 +5473,7 @@
         <v>10.1547517776489</v>
       </c>
       <c r="G176" t="n">
-        <v>9.5474967956543</v>
+        <v>9.54749774932861</v>
       </c>
       <c r="H176" t="n">
         <v>24722</v>
@@ -5589,7 +5589,7 @@
         <v>10.2440853118896</v>
       </c>
       <c r="G180" t="n">
-        <v>9.63148784637451</v>
+        <v>9.63148880004883</v>
       </c>
       <c r="H180" t="n">
         <v>17545</v>
@@ -5676,7 +5676,7 @@
         <v>10.1897087097168</v>
       </c>
       <c r="G183" t="n">
-        <v>9.58036327362061</v>
+        <v>9.58036422729492</v>
       </c>
       <c r="H183" t="n">
         <v>13620</v>
@@ -5792,7 +5792,7 @@
         <v>10.0304641723633</v>
       </c>
       <c r="G187" t="n">
-        <v>9.43064117431641</v>
+        <v>9.43064212799072</v>
       </c>
       <c r="H187" t="n">
         <v>7232</v>
@@ -5995,7 +5995,7 @@
         <v>9.56438159942627</v>
       </c>
       <c r="G194" t="n">
-        <v>8.992431640625</v>
+        <v>8.99243068695068</v>
       </c>
       <c r="H194" t="n">
         <v>37882</v>
@@ -6082,7 +6082,7 @@
         <v>9.66536712646484</v>
       </c>
       <c r="G197" t="n">
-        <v>9.08737850189209</v>
+        <v>9.08737659454346</v>
       </c>
       <c r="H197" t="n">
         <v>16116</v>
@@ -6111,7 +6111,7 @@
         <v>9.57409191131592</v>
       </c>
       <c r="G198" t="n">
-        <v>9.00156021118164</v>
+        <v>9.00156211853027</v>
       </c>
       <c r="H198" t="n">
         <v>26236</v>
@@ -6140,7 +6140,7 @@
         <v>9.44786167144775</v>
       </c>
       <c r="G199" t="n">
-        <v>8.88287925720215</v>
+        <v>8.88288021087646</v>
       </c>
       <c r="H199" t="n">
         <v>57242</v>
@@ -6227,7 +6227,7 @@
         <v>8.85263729095459</v>
       </c>
       <c r="G202" t="n">
-        <v>8.32324981689453</v>
+        <v>8.32324886322021</v>
       </c>
       <c r="H202" t="n">
         <v>36498</v>
@@ -6256,7 +6256,7 @@
         <v>9.25657367706299</v>
       </c>
       <c r="G203" t="n">
-        <v>8.70302867889404</v>
+        <v>8.70302963256836</v>
       </c>
       <c r="H203" t="n">
         <v>45319</v>
@@ -6285,7 +6285,7 @@
         <v>9.5935115814209</v>
       </c>
       <c r="G204" t="n">
-        <v>9.01981735229492</v>
+        <v>9.01981830596924</v>
       </c>
       <c r="H204" t="n">
         <v>85559</v>
@@ -6314,7 +6314,7 @@
         <v>9.51680278778076</v>
       </c>
       <c r="G205" t="n">
-        <v>8.94769859313965</v>
+        <v>8.94769763946533</v>
       </c>
       <c r="H205" t="n">
         <v>19012</v>
@@ -6343,7 +6343,7 @@
         <v>9.61293315887451</v>
       </c>
       <c r="G206" t="n">
-        <v>9.03807830810547</v>
+        <v>9.03807926177979</v>
       </c>
       <c r="H206" t="n">
         <v>13515</v>
@@ -6372,7 +6372,7 @@
         <v>9.67119312286377</v>
       </c>
       <c r="G207" t="n">
-        <v>9.09285545349121</v>
+        <v>9.09285449981689</v>
       </c>
       <c r="H207" t="n">
         <v>36508</v>
@@ -6488,7 +6488,7 @@
         <v>9.62264347076416</v>
       </c>
       <c r="G211" t="n">
-        <v>9.04720878601074</v>
+        <v>9.04720973968506</v>
       </c>
       <c r="H211" t="n">
         <v>14681</v>
@@ -6575,7 +6575,7 @@
         <v>9.98191356658936</v>
       </c>
       <c r="G214" t="n">
-        <v>9.38499355316162</v>
+        <v>9.38499450683594</v>
       </c>
       <c r="H214" t="n">
         <v>18233</v>
@@ -6604,7 +6604,7 @@
         <v>9.9236536026001</v>
       </c>
       <c r="G215" t="n">
-        <v>9.33021926879883</v>
+        <v>9.33021831512451</v>
       </c>
       <c r="H215" t="n">
         <v>38169</v>
@@ -6633,7 +6633,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G216" t="n">
-        <v>9.6771354675293</v>
+        <v>9.67713451385498</v>
       </c>
       <c r="H216" t="n">
         <v>41846</v>
@@ -6662,7 +6662,7 @@
         <v>10.0013341903687</v>
       </c>
       <c r="G217" t="n">
-        <v>9.40325450897217</v>
+        <v>9.40325355529785</v>
       </c>
       <c r="H217" t="n">
         <v>50349</v>
@@ -6691,7 +6691,7 @@
         <v>10.0790138244629</v>
       </c>
       <c r="G218" t="n">
-        <v>9.47628784179688</v>
+        <v>9.47628879547119</v>
       </c>
       <c r="H218" t="n">
         <v>27030</v>
@@ -6720,7 +6720,7 @@
         <v>10.3120546340942</v>
       </c>
       <c r="G219" t="n">
-        <v>9.69539260864258</v>
+        <v>9.69539356231689</v>
       </c>
       <c r="H219" t="n">
         <v>30483</v>
@@ -6749,7 +6749,7 @@
         <v>10.234375</v>
       </c>
       <c r="G220" t="n">
-        <v>9.62235832214355</v>
+        <v>9.62235927581787</v>
       </c>
       <c r="H220" t="n">
         <v>76922</v>
@@ -6778,7 +6778,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G221" t="n">
-        <v>9.84146308898926</v>
+        <v>9.84146213531494</v>
       </c>
       <c r="H221" t="n">
         <v>36359</v>
@@ -6807,7 +6807,7 @@
         <v>10.3120546340942</v>
       </c>
       <c r="G222" t="n">
-        <v>9.69539260864258</v>
+        <v>9.69539356231689</v>
       </c>
       <c r="H222" t="n">
         <v>14768</v>
@@ -6836,7 +6836,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G223" t="n">
-        <v>9.93275833129883</v>
+        <v>9.93275928497314</v>
       </c>
       <c r="H223" t="n">
         <v>12586</v>
@@ -6894,7 +6894,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G225" t="n">
-        <v>9.73191165924072</v>
+        <v>9.73191070556641</v>
       </c>
       <c r="H225" t="n">
         <v>32595</v>
@@ -6981,7 +6981,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G228" t="n">
-        <v>9.73191165924072</v>
+        <v>9.73191070556641</v>
       </c>
       <c r="H228" t="n">
         <v>19355</v>
@@ -7010,7 +7010,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G229" t="n">
-        <v>9.750168800354</v>
+        <v>9.75016975402832</v>
       </c>
       <c r="H229" t="n">
         <v>11125</v>
@@ -7039,7 +7039,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G230" t="n">
-        <v>9.73191165924072</v>
+        <v>9.73191070556641</v>
       </c>
       <c r="H230" t="n">
         <v>20369</v>
@@ -7068,7 +7068,7 @@
         <v>10.3508949279785</v>
       </c>
       <c r="G231" t="n">
-        <v>9.73191165924072</v>
+        <v>9.73191070556641</v>
       </c>
       <c r="H231" t="n">
         <v>21922</v>
@@ -7097,7 +7097,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G232" t="n">
-        <v>9.87798118591309</v>
+        <v>9.87797927856445</v>
       </c>
       <c r="H232" t="n">
         <v>15426</v>
@@ -7126,7 +7126,7 @@
         <v>10.6421957015991</v>
       </c>
       <c r="G233" t="n">
-        <v>10.0057926177979</v>
+        <v>10.0057916641235</v>
       </c>
       <c r="H233" t="n">
         <v>21115</v>
@@ -7155,7 +7155,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G234" t="n">
-        <v>10.0423097610474</v>
+        <v>10.042308807373</v>
       </c>
       <c r="H234" t="n">
         <v>13286</v>
@@ -7184,7 +7184,7 @@
         <v>10.214955329895</v>
       </c>
       <c r="G235" t="n">
-        <v>9.60410118103027</v>
+        <v>9.60410213470459</v>
       </c>
       <c r="H235" t="n">
         <v>164121</v>
@@ -7213,7 +7213,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G236" t="n">
-        <v>9.71365261077881</v>
+        <v>9.71365165710449</v>
       </c>
       <c r="H236" t="n">
         <v>14595</v>
@@ -7242,7 +7242,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G237" t="n">
-        <v>9.76842784881592</v>
+        <v>9.76842975616455</v>
       </c>
       <c r="H237" t="n">
         <v>21826</v>
@@ -7329,7 +7329,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G240" t="n">
-        <v>10.0423097610474</v>
+        <v>10.042308807373</v>
       </c>
       <c r="H240" t="n">
         <v>30544</v>
@@ -7358,7 +7358,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G241" t="n">
-        <v>10.0423097610474</v>
+        <v>10.042308807373</v>
       </c>
       <c r="H241" t="n">
         <v>35869</v>
@@ -7387,7 +7387,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G242" t="n">
-        <v>10.0970859527588</v>
+        <v>10.0970849990845</v>
       </c>
       <c r="H242" t="n">
         <v>43166</v>
@@ -7416,7 +7416,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G243" t="n">
-        <v>9.87798118591309</v>
+        <v>9.87797927856445</v>
       </c>
       <c r="H243" t="n">
         <v>23214</v>
@@ -7445,7 +7445,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G244" t="n">
-        <v>10.2431564331055</v>
+        <v>10.2431573867798</v>
       </c>
       <c r="H244" t="n">
         <v>47303</v>
@@ -7474,7 +7474,7 @@
         <v>10.6033563613892</v>
       </c>
       <c r="G245" t="n">
-        <v>9.96927452087402</v>
+        <v>9.96927547454834</v>
       </c>
       <c r="H245" t="n">
         <v>41422</v>
@@ -7561,7 +7561,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G248" t="n">
-        <v>9.93275833129883</v>
+        <v>9.93275928497314</v>
       </c>
       <c r="H248" t="n">
         <v>13400</v>
@@ -7590,7 +7590,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G249" t="n">
-        <v>9.95101451873779</v>
+        <v>9.95101547241211</v>
       </c>
       <c r="H249" t="n">
         <v>9574</v>
@@ -7648,7 +7648,7 @@
         <v>11.1082782745361</v>
       </c>
       <c r="G251" t="n">
-        <v>10.4440031051636</v>
+        <v>10.4440021514893</v>
       </c>
       <c r="H251" t="n">
         <v>24083</v>
@@ -7677,7 +7677,7 @@
         <v>11.2053775787354</v>
       </c>
       <c r="G252" t="n">
-        <v>10.5352954864502</v>
+        <v>10.5352945327759</v>
       </c>
       <c r="H252" t="n">
         <v>17671</v>
@@ -7764,7 +7764,7 @@
         <v>11.0111770629883</v>
       </c>
       <c r="G255" t="n">
-        <v>10.3527097702026</v>
+        <v>10.352707862854</v>
       </c>
       <c r="H255" t="n">
         <v>15461</v>
@@ -7851,7 +7851,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G258" t="n">
-        <v>10.2614135742188</v>
+        <v>10.2614145278931</v>
       </c>
       <c r="H258" t="n">
         <v>15387</v>
@@ -7880,7 +7880,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G259" t="n">
-        <v>9.95101451873779</v>
+        <v>9.95101547241211</v>
       </c>
       <c r="H259" t="n">
         <v>25241</v>
@@ -7909,7 +7909,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G260" t="n">
-        <v>9.9144983291626</v>
+        <v>9.91449928283691</v>
       </c>
       <c r="H260" t="n">
         <v>7038</v>
@@ -8083,7 +8083,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G266" t="n">
-        <v>9.85771942138672</v>
+        <v>9.8577184677124</v>
       </c>
       <c r="H266" t="n">
         <v>31281</v>
@@ -8112,7 +8112,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G267" t="n">
-        <v>9.85771942138672</v>
+        <v>9.8577184677124</v>
       </c>
       <c r="H267" t="n">
         <v>28019</v>
@@ -8199,7 +8199,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G270" t="n">
-        <v>9.93142223358154</v>
+        <v>9.93142032623291</v>
       </c>
       <c r="H270" t="n">
         <v>4825</v>
@@ -8228,7 +8228,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G271" t="n">
-        <v>10.1341037750244</v>
+        <v>10.1341028213501</v>
       </c>
       <c r="H271" t="n">
         <v>105178</v>
@@ -8286,7 +8286,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G273" t="n">
-        <v>10.1341037750244</v>
+        <v>10.1341028213501</v>
       </c>
       <c r="H273" t="n">
         <v>6761</v>
@@ -8373,7 +8373,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G276" t="n">
-        <v>9.83929443359375</v>
+        <v>9.83929347991943</v>
       </c>
       <c r="H276" t="n">
         <v>16684</v>
@@ -8431,7 +8431,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G278" t="n">
-        <v>9.93142223358154</v>
+        <v>9.93142032623291</v>
       </c>
       <c r="H278" t="n">
         <v>68449</v>
@@ -8460,7 +8460,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G279" t="n">
-        <v>10.1341037750244</v>
+        <v>10.1341028213501</v>
       </c>
       <c r="H279" t="n">
         <v>63120</v>
@@ -8547,7 +8547,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G282" t="n">
-        <v>9.6734619140625</v>
+        <v>9.67346382141113</v>
       </c>
       <c r="H282" t="n">
         <v>19151</v>
@@ -8663,7 +8663,7 @@
         <v>10.6421957015991</v>
       </c>
       <c r="G286" t="n">
-        <v>10.0972518920898</v>
+        <v>10.0972528457642</v>
       </c>
       <c r="H286" t="n">
         <v>15436</v>
@@ -8692,7 +8692,7 @@
         <v>11.0500173568726</v>
       </c>
       <c r="G287" t="n">
-        <v>10.4841909408569</v>
+        <v>10.4841918945312</v>
       </c>
       <c r="H287" t="n">
         <v>48301</v>
@@ -8779,7 +8779,7 @@
         <v>10.8752374649048</v>
       </c>
       <c r="G290" t="n">
-        <v>10.3183603286743</v>
+        <v>10.3183612823486</v>
       </c>
       <c r="H290" t="n">
         <v>20080</v>
@@ -8866,7 +8866,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G293" t="n">
-        <v>9.93142223358154</v>
+        <v>9.93142032623291</v>
       </c>
       <c r="H293" t="n">
         <v>15397</v>
@@ -8895,7 +8895,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G294" t="n">
-        <v>9.76559162139893</v>
+        <v>9.76559066772461</v>
       </c>
       <c r="H294" t="n">
         <v>19630</v>
@@ -8924,7 +8924,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G295" t="n">
-        <v>10.2446594238281</v>
+        <v>10.2446584701538</v>
       </c>
       <c r="H295" t="n">
         <v>20005</v>
@@ -8982,7 +8982,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G297" t="n">
-        <v>9.96827220916748</v>
+        <v>9.9682731628418</v>
       </c>
       <c r="H297" t="n">
         <v>9689</v>
@@ -9011,7 +9011,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G298" t="n">
-        <v>9.93142223358154</v>
+        <v>9.93142032623291</v>
       </c>
       <c r="H298" t="n">
         <v>15459</v>
@@ -9069,7 +9069,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G300" t="n">
-        <v>9.6734619140625</v>
+        <v>9.67346382141113</v>
       </c>
       <c r="H300" t="n">
         <v>46224</v>
@@ -9098,7 +9098,7 @@
         <v>10.2732152938843</v>
       </c>
       <c r="G301" t="n">
-        <v>9.74716663360596</v>
+        <v>9.74716567993164</v>
       </c>
       <c r="H301" t="n">
         <v>8278</v>
@@ -9127,7 +9127,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G302" t="n">
-        <v>9.83929443359375</v>
+        <v>9.83929347991943</v>
       </c>
       <c r="H302" t="n">
         <v>1056</v>
@@ -9156,7 +9156,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G303" t="n">
-        <v>10.0051240921021</v>
+        <v>10.0051259994507</v>
       </c>
       <c r="H303" t="n">
         <v>22348</v>
@@ -9185,7 +9185,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G304" t="n">
-        <v>10.0419759750366</v>
+        <v>10.0419769287109</v>
       </c>
       <c r="H304" t="n">
         <v>9296</v>
@@ -9214,7 +9214,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G305" t="n">
-        <v>10.1341037750244</v>
+        <v>10.1341028213501</v>
       </c>
       <c r="H305" t="n">
         <v>4341</v>
@@ -9272,7 +9272,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G307" t="n">
-        <v>9.93142223358154</v>
+        <v>9.93142032623291</v>
       </c>
       <c r="H307" t="n">
         <v>5672</v>
@@ -9330,7 +9330,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G309" t="n">
-        <v>9.93142223358154</v>
+        <v>9.93142032623291</v>
       </c>
       <c r="H309" t="n">
         <v>10750</v>
@@ -9359,7 +9359,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G310" t="n">
-        <v>10.189380645752</v>
+        <v>10.1893796920776</v>
       </c>
       <c r="H310" t="n">
         <v>28717</v>
@@ -9388,7 +9388,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G311" t="n">
-        <v>10.189380645752</v>
+        <v>10.1893796920776</v>
       </c>
       <c r="H311" t="n">
         <v>15871</v>
@@ -9417,7 +9417,7 @@
         <v>10.8752374649048</v>
       </c>
       <c r="G312" t="n">
-        <v>10.3183603286743</v>
+        <v>10.3183612823486</v>
       </c>
       <c r="H312" t="n">
         <v>7644</v>
@@ -9446,7 +9446,7 @@
         <v>11.0500173568726</v>
       </c>
       <c r="G313" t="n">
-        <v>10.4841909408569</v>
+        <v>10.4841918945312</v>
       </c>
       <c r="H313" t="n">
         <v>16890</v>
@@ -9504,7 +9504,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G315" t="n">
-        <v>10.4104890823364</v>
+        <v>10.4104881286621</v>
       </c>
       <c r="H315" t="n">
         <v>51796</v>
@@ -9562,7 +9562,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G317" t="n">
-        <v>11.9766674041748</v>
+        <v>11.9766693115234</v>
       </c>
       <c r="H317" t="n">
         <v>40875</v>
@@ -9649,7 +9649,7 @@
         <v>11.943341255188</v>
       </c>
       <c r="G320" t="n">
-        <v>11.3317708969116</v>
+        <v>11.3317718505859</v>
       </c>
       <c r="H320" t="n">
         <v>26477</v>
@@ -9678,7 +9678,7 @@
         <v>11.943341255188</v>
       </c>
       <c r="G321" t="n">
-        <v>11.3317708969116</v>
+        <v>11.3317718505859</v>
       </c>
       <c r="H321" t="n">
         <v>65085</v>
@@ -9707,7 +9707,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G322" t="n">
-        <v>11.4607515335083</v>
+        <v>11.4607496261597</v>
       </c>
       <c r="H322" t="n">
         <v>18075</v>
@@ -9765,7 +9765,7 @@
         <v>12.0598611831665</v>
       </c>
       <c r="G324" t="n">
-        <v>11.442325592041</v>
+        <v>11.4423246383667</v>
       </c>
       <c r="H324" t="n">
         <v>55912</v>
@@ -9881,7 +9881,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G328" t="n">
-        <v>12.0687961578369</v>
+        <v>12.0687971115112</v>
       </c>
       <c r="H328" t="n">
         <v>34385</v>
@@ -9910,7 +9910,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G329" t="n">
-        <v>12.0687961578369</v>
+        <v>12.0687971115112</v>
       </c>
       <c r="H329" t="n">
         <v>28558</v>
@@ -9939,7 +9939,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G330" t="n">
-        <v>12.1609239578247</v>
+        <v>12.160924911499</v>
       </c>
       <c r="H330" t="n">
         <v>146039</v>
@@ -9968,7 +9968,7 @@
         <v>13.0308637619019</v>
       </c>
       <c r="G331" t="n">
-        <v>12.3636045455933</v>
+        <v>12.3636054992676</v>
       </c>
       <c r="H331" t="n">
         <v>18642</v>
@@ -10055,7 +10055,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G334" t="n">
-        <v>11.4976005554199</v>
+        <v>11.4976015090942</v>
       </c>
       <c r="H334" t="n">
         <v>51985</v>
@@ -10084,7 +10084,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G335" t="n">
-        <v>11.5160264968872</v>
+        <v>11.5160255432129</v>
       </c>
       <c r="H335" t="n">
         <v>357943</v>
@@ -10113,7 +10113,7 @@
         <v>12.2929019927979</v>
       </c>
       <c r="G336" t="n">
-        <v>11.6634330749512</v>
+        <v>11.6634321212769</v>
       </c>
       <c r="H336" t="n">
         <v>43056</v>
@@ -10142,7 +10142,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G337" t="n">
-        <v>11.5160264968872</v>
+        <v>11.5160255432129</v>
       </c>
       <c r="H337" t="n">
         <v>43441</v>
@@ -10171,7 +10171,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G338" t="n">
-        <v>11.4976005554199</v>
+        <v>11.4976015090942</v>
       </c>
       <c r="H338" t="n">
         <v>37042</v>
@@ -10229,7 +10229,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G340" t="n">
-        <v>11.5160264968872</v>
+        <v>11.5160255432129</v>
       </c>
       <c r="H340" t="n">
         <v>33301</v>
@@ -10258,7 +10258,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G341" t="n">
-        <v>11.4607515335083</v>
+        <v>11.4607496261597</v>
       </c>
       <c r="H341" t="n">
         <v>96017</v>
@@ -10287,7 +10287,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G342" t="n">
-        <v>11.5160264968872</v>
+        <v>11.5160255432129</v>
       </c>
       <c r="H342" t="n">
         <v>101629</v>
@@ -10316,7 +10316,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G343" t="n">
-        <v>11.4976005554199</v>
+        <v>11.4976015090942</v>
       </c>
       <c r="H343" t="n">
         <v>44961</v>
@@ -10461,7 +10461,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G348" t="n">
-        <v>12.1609239578247</v>
+        <v>12.160924911499</v>
       </c>
       <c r="H348" t="n">
         <v>164571</v>
@@ -10490,7 +10490,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G349" t="n">
-        <v>11.9766674041748</v>
+        <v>11.9766693115234</v>
       </c>
       <c r="H349" t="n">
         <v>13283</v>
@@ -10519,7 +10519,7 @@
         <v>12.7978229522705</v>
       </c>
       <c r="G350" t="n">
-        <v>12.1424980163574</v>
+        <v>12.1424989700317</v>
       </c>
       <c r="H350" t="n">
         <v>82487</v>
@@ -10577,7 +10577,7 @@
         <v>13.2833251953125</v>
       </c>
       <c r="G352" t="n">
-        <v>12.6031398773193</v>
+        <v>12.6031408309937</v>
       </c>
       <c r="H352" t="n">
         <v>22421</v>
@@ -10606,7 +10606,7 @@
         <v>13.5940456390381</v>
       </c>
       <c r="G353" t="n">
-        <v>12.8979501724243</v>
+        <v>12.8979511260986</v>
       </c>
       <c r="H353" t="n">
         <v>79481</v>
@@ -10635,7 +10635,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G354" t="n">
-        <v>13.1743335723877</v>
+        <v>13.174334526062</v>
       </c>
       <c r="H354" t="n">
         <v>49028</v>
@@ -10664,7 +10664,7 @@
         <v>13.9824476242065</v>
       </c>
       <c r="G355" t="n">
-        <v>13.2664623260498</v>
+        <v>13.2664632797241</v>
       </c>
       <c r="H355" t="n">
         <v>22333</v>
@@ -10722,7 +10722,7 @@
         <v>14.7204103469849</v>
       </c>
       <c r="G357" t="n">
-        <v>13.9666376113892</v>
+        <v>13.9666385650635</v>
       </c>
       <c r="H357" t="n">
         <v>51342</v>
@@ -10780,7 +10780,7 @@
         <v>14.0989675521851</v>
       </c>
       <c r="G359" t="n">
-        <v>13.3770179748535</v>
+        <v>13.3770160675049</v>
       </c>
       <c r="H359" t="n">
         <v>62383</v>
@@ -10838,7 +10838,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G361" t="n">
-        <v>13.0269298553467</v>
+        <v>13.0269317626953</v>
       </c>
       <c r="H361" t="n">
         <v>48913</v>
@@ -10867,7 +10867,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G362" t="n">
-        <v>13.0269298553467</v>
+        <v>13.0269317626953</v>
       </c>
       <c r="H362" t="n">
         <v>29032</v>
@@ -10896,7 +10896,7 @@
         <v>12.9726037979126</v>
       </c>
       <c r="G363" t="n">
-        <v>12.3083305358887</v>
+        <v>12.3083295822144</v>
       </c>
       <c r="H363" t="n">
         <v>328227</v>
@@ -10925,7 +10925,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G364" t="n">
-        <v>12.2714786529541</v>
+        <v>12.2714796066284</v>
       </c>
       <c r="H364" t="n">
         <v>81687</v>
@@ -11012,7 +11012,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G367" t="n">
-        <v>12.1609239578247</v>
+        <v>12.160924911499</v>
       </c>
       <c r="H367" t="n">
         <v>62783</v>
@@ -11099,7 +11099,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G370" t="n">
-        <v>12.1240720748901</v>
+        <v>12.1240739822388</v>
       </c>
       <c r="H370" t="n">
         <v>23953</v>
@@ -11128,7 +11128,7 @@
         <v>12.8560838699341</v>
       </c>
       <c r="G371" t="n">
-        <v>12.1977777481079</v>
+        <v>12.1977758407593</v>
       </c>
       <c r="H371" t="n">
         <v>17051</v>
@@ -11273,7 +11273,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G376" t="n">
-        <v>13.0822076797485</v>
+        <v>13.0822067260742</v>
       </c>
       <c r="H376" t="n">
         <v>70558</v>
@@ -11302,7 +11302,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G377" t="n">
-        <v>12.768970489502</v>
+        <v>12.7689714431763</v>
       </c>
       <c r="H377" t="n">
         <v>105631</v>
@@ -11534,7 +11534,7 @@
         <v>13.380425453186</v>
       </c>
       <c r="G385" t="n">
-        <v>12.6952676773071</v>
+        <v>12.6952686309814</v>
       </c>
       <c r="H385" t="n">
         <v>15276</v>
@@ -11563,7 +11563,7 @@
         <v>13.4192657470703</v>
       </c>
       <c r="G386" t="n">
-        <v>12.732120513916</v>
+        <v>12.7321195602417</v>
       </c>
       <c r="H386" t="n">
         <v>34541</v>
@@ -11592,7 +11592,7 @@
         <v>13.4969463348389</v>
       </c>
       <c r="G387" t="n">
-        <v>12.8058223724365</v>
+        <v>12.8058233261108</v>
       </c>
       <c r="H387" t="n">
         <v>42243</v>
@@ -11621,7 +11621,7 @@
         <v>13.7105674743652</v>
       </c>
       <c r="G388" t="n">
-        <v>13.0085048675537</v>
+        <v>13.008505821228</v>
       </c>
       <c r="H388" t="n">
         <v>24282</v>
@@ -11650,7 +11650,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G389" t="n">
-        <v>13.1743335723877</v>
+        <v>13.174334526062</v>
       </c>
       <c r="H389" t="n">
         <v>30802</v>
@@ -11679,7 +11679,7 @@
         <v>13.6911468505859</v>
       </c>
       <c r="G390" t="n">
-        <v>12.9900779724121</v>
+        <v>12.9900789260864</v>
       </c>
       <c r="H390" t="n">
         <v>45738</v>
@@ -11766,7 +11766,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G393" t="n">
-        <v>13.0822076797485</v>
+        <v>13.0822067260742</v>
       </c>
       <c r="H393" t="n">
         <v>14493</v>
@@ -11795,7 +11795,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G394" t="n">
-        <v>12.768970489502</v>
+        <v>12.7689714431763</v>
       </c>
       <c r="H394" t="n">
         <v>27023</v>
@@ -11824,7 +11824,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G395" t="n">
-        <v>13.1743335723877</v>
+        <v>13.174334526062</v>
       </c>
       <c r="H395" t="n">
         <v>43095</v>
@@ -11853,7 +11853,7 @@
         <v>13.6717262268066</v>
       </c>
       <c r="G396" t="n">
-        <v>12.9716520309448</v>
+        <v>12.9716529846191</v>
       </c>
       <c r="H396" t="n">
         <v>33477</v>
@@ -11969,7 +11969,7 @@
         <v>13.0502843856812</v>
       </c>
       <c r="G400" t="n">
-        <v>12.3820314407349</v>
+        <v>12.3820333480835</v>
       </c>
       <c r="H400" t="n">
         <v>35674</v>
@@ -11998,7 +11998,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G401" t="n">
-        <v>12.3451805114746</v>
+        <v>12.3451814651489</v>
       </c>
       <c r="H401" t="n">
         <v>20963</v>
@@ -12027,7 +12027,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G402" t="n">
-        <v>12.3451805114746</v>
+        <v>12.3451814651489</v>
       </c>
       <c r="H402" t="n">
         <v>17932</v>
@@ -12085,7 +12085,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G404" t="n">
-        <v>12.3451805114746</v>
+        <v>12.3451814651489</v>
       </c>
       <c r="H404" t="n">
         <v>20738</v>
@@ -12114,7 +12114,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G405" t="n">
-        <v>12.1609239578247</v>
+        <v>12.160924911499</v>
       </c>
       <c r="H405" t="n">
         <v>14366</v>
@@ -12143,7 +12143,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G406" t="n">
-        <v>12.0687961578369</v>
+        <v>12.0687971115112</v>
       </c>
       <c r="H406" t="n">
         <v>34716</v>
@@ -12259,7 +12259,7 @@
         <v>12.4094219207764</v>
       </c>
       <c r="G410" t="n">
-        <v>11.7739858627319</v>
+        <v>11.7739868164062</v>
       </c>
       <c r="H410" t="n">
         <v>15233</v>
@@ -12288,7 +12288,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G411" t="n">
-        <v>11.7002840042114</v>
+        <v>11.7002849578857</v>
       </c>
       <c r="H411" t="n">
         <v>14490</v>
@@ -12404,7 +12404,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G415" t="n">
-        <v>10.9632577896118</v>
+        <v>10.9632587432861</v>
       </c>
       <c r="H415" t="n">
         <v>19309</v>
@@ -12462,7 +12462,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G417" t="n">
-        <v>10.9632577896118</v>
+        <v>10.9632587432861</v>
       </c>
       <c r="H417" t="n">
         <v>37373</v>
@@ -12549,7 +12549,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G420" t="n">
-        <v>11.2396430969238</v>
+        <v>11.2396411895752</v>
       </c>
       <c r="H420" t="n">
         <v>84619</v>
@@ -12578,7 +12578,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G421" t="n">
-        <v>11.2396430969238</v>
+        <v>11.2396411895752</v>
       </c>
       <c r="H421" t="n">
         <v>94440</v>
@@ -12607,7 +12607,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G422" t="n">
-        <v>11.0553865432739</v>
+        <v>11.0553855895996</v>
       </c>
       <c r="H422" t="n">
         <v>13462</v>
@@ -12665,7 +12665,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G424" t="n">
-        <v>11.1475143432617</v>
+        <v>11.1475133895874</v>
       </c>
       <c r="H424" t="n">
         <v>53206</v>
@@ -12694,7 +12694,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G425" t="n">
-        <v>11.2396430969238</v>
+        <v>11.2396411895752</v>
       </c>
       <c r="H425" t="n">
         <v>21806</v>
@@ -12723,7 +12723,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G426" t="n">
-        <v>11.2396430969238</v>
+        <v>11.2396411895752</v>
       </c>
       <c r="H426" t="n">
         <v>44690</v>
@@ -12752,7 +12752,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G427" t="n">
-        <v>11.2396430969238</v>
+        <v>11.2396411895752</v>
       </c>
       <c r="H427" t="n">
         <v>35187</v>
@@ -12781,7 +12781,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G428" t="n">
-        <v>11.1475143432617</v>
+        <v>11.1475133895874</v>
       </c>
       <c r="H428" t="n">
         <v>6846</v>
@@ -12839,7 +12839,7 @@
         <v>11.9045000076294</v>
       </c>
       <c r="G430" t="n">
-        <v>11.2949190139771</v>
+        <v>11.2949180603027</v>
       </c>
       <c r="H430" t="n">
         <v>24294</v>
@@ -12868,7 +12868,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G431" t="n">
-        <v>11.0369606018066</v>
+        <v>11.036958694458</v>
       </c>
       <c r="H431" t="n">
         <v>33933</v>
@@ -12926,7 +12926,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G433" t="n">
-        <v>10.4104890823364</v>
+        <v>10.4104881286621</v>
       </c>
       <c r="H433" t="n">
         <v>46588</v>
@@ -12984,7 +12984,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G435" t="n">
-        <v>10.2446594238281</v>
+        <v>10.2446584701538</v>
       </c>
       <c r="H435" t="n">
         <v>43976</v>
@@ -13013,7 +13013,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G436" t="n">
-        <v>10.2446594238281</v>
+        <v>10.2446584701538</v>
       </c>
       <c r="H436" t="n">
         <v>63148</v>
@@ -13187,7 +13187,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G442" t="n">
-        <v>9.6734619140625</v>
+        <v>9.67346382141113</v>
       </c>
       <c r="H442" t="n">
         <v>61109</v>
@@ -13216,7 +13216,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G443" t="n">
-        <v>9.36022663116455</v>
+        <v>9.36022567749023</v>
       </c>
       <c r="H443" t="n">
         <v>58787</v>
@@ -13245,7 +13245,7 @@
         <v>9.84597301483154</v>
       </c>
       <c r="G444" t="n">
-        <v>9.34180068969727</v>
+        <v>9.34179973602295</v>
       </c>
       <c r="H444" t="n">
         <v>33783</v>
@@ -13274,7 +13274,7 @@
         <v>9.30221080780029</v>
       </c>
       <c r="G445" t="n">
-        <v>8.8258810043335</v>
+        <v>8.82588291168213</v>
       </c>
       <c r="H445" t="n">
         <v>198608</v>
@@ -13303,7 +13303,7 @@
         <v>10.0013341903687</v>
       </c>
       <c r="G446" t="n">
-        <v>9.48920631408691</v>
+        <v>9.4892053604126</v>
       </c>
       <c r="H446" t="n">
         <v>50177</v>
@@ -13332,7 +13332,7 @@
         <v>9.12743091583252</v>
       </c>
       <c r="G447" t="n">
-        <v>8.66005325317383</v>
+        <v>8.66005229949951</v>
       </c>
       <c r="H447" t="n">
         <v>68799</v>
@@ -13361,7 +13361,7 @@
         <v>10.3897352218628</v>
       </c>
       <c r="G448" t="n">
-        <v>9.85771942138672</v>
+        <v>9.8577184677124</v>
       </c>
       <c r="H448" t="n">
         <v>42752</v>
@@ -13390,7 +13390,7 @@
         <v>9.22453117370605</v>
       </c>
       <c r="G449" t="n">
-        <v>8.75218200683594</v>
+        <v>8.75218105316162</v>
       </c>
       <c r="H449" t="n">
         <v>29663</v>
@@ -13419,7 +13419,7 @@
         <v>8.59337902069092</v>
       </c>
       <c r="G450" t="n">
-        <v>8.15334796905518</v>
+        <v>8.15334701538086</v>
       </c>
       <c r="H450" t="n">
         <v>148767</v>
@@ -13448,7 +13448,7 @@
         <v>8.6322193145752</v>
       </c>
       <c r="G451" t="n">
-        <v>8.19019889831543</v>
+        <v>8.19019794464111</v>
       </c>
       <c r="H451" t="n">
         <v>140854</v>
@@ -13535,7 +13535,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G454" t="n">
-        <v>8.38366794586182</v>
+        <v>8.38366889953613</v>
       </c>
       <c r="H454" t="n">
         <v>58292</v>
@@ -13564,7 +13564,7 @@
         <v>10.0984344482422</v>
       </c>
       <c r="G455" t="n">
-        <v>9.58133411407471</v>
+        <v>9.58133506774902</v>
       </c>
       <c r="H455" t="n">
         <v>36655</v>
@@ -13593,7 +13593,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G456" t="n">
-        <v>11.7002840042114</v>
+        <v>11.7002849578857</v>
       </c>
       <c r="H456" t="n">
         <v>57587</v>
@@ -13622,7 +13622,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G457" t="n">
-        <v>11.0369606018066</v>
+        <v>11.036958694458</v>
       </c>
       <c r="H457" t="n">
         <v>57173</v>
@@ -13651,7 +13651,7 @@
         <v>11.2247982025146</v>
       </c>
       <c r="G458" t="n">
-        <v>10.6500234603882</v>
+        <v>10.6500225067139</v>
       </c>
       <c r="H458" t="n">
         <v>48513</v>
@@ -13709,7 +13709,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G460" t="n">
-        <v>10.1341037750244</v>
+        <v>10.1341028213501</v>
       </c>
       <c r="H460" t="n">
         <v>72969</v>
@@ -13767,7 +13767,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G462" t="n">
-        <v>10.1341037750244</v>
+        <v>10.1341028213501</v>
       </c>
       <c r="H462" t="n">
         <v>20192</v>
@@ -13796,7 +13796,7 @@
         <v>10.7781372070312</v>
       </c>
       <c r="G463" t="n">
-        <v>10.2262334823608</v>
+        <v>10.2262315750122</v>
       </c>
       <c r="H463" t="n">
         <v>35295</v>
@@ -13825,7 +13825,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G464" t="n">
-        <v>10.170955657959</v>
+        <v>10.1709547042847</v>
       </c>
       <c r="H464" t="n">
         <v>21536</v>
@@ -13854,7 +13854,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G465" t="n">
-        <v>9.76559162139893</v>
+        <v>9.76559066772461</v>
       </c>
       <c r="H465" t="n">
         <v>19814</v>
@@ -13883,7 +13883,7 @@
         <v>10.2732152938843</v>
       </c>
       <c r="G466" t="n">
-        <v>9.74716663360596</v>
+        <v>9.74716567993164</v>
       </c>
       <c r="H466" t="n">
         <v>17649</v>
@@ -13999,7 +13999,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G470" t="n">
-        <v>11.0553865432739</v>
+        <v>11.0553855895996</v>
       </c>
       <c r="H470" t="n">
         <v>18460</v>
@@ -14057,7 +14057,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G472" t="n">
-        <v>11.0553865432739</v>
+        <v>11.0553855895996</v>
       </c>
       <c r="H472" t="n">
         <v>82131</v>
@@ -14086,7 +14086,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G473" t="n">
-        <v>11.7002840042114</v>
+        <v>11.7002849578857</v>
       </c>
       <c r="H473" t="n">
         <v>33615</v>
@@ -14115,7 +14115,7 @@
         <v>12.2346420288086</v>
       </c>
       <c r="G474" t="n">
-        <v>11.6081562042236</v>
+        <v>11.6081552505493</v>
       </c>
       <c r="H474" t="n">
         <v>33682</v>
@@ -14144,7 +14144,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G475" t="n">
-        <v>11.7924108505249</v>
+        <v>11.7924118041992</v>
       </c>
       <c r="H475" t="n">
         <v>26161</v>
@@ -14173,7 +14173,7 @@
         <v>13.0697040557861</v>
       </c>
       <c r="G476" t="n">
-        <v>12.4004573822021</v>
+        <v>12.4004583358765</v>
       </c>
       <c r="H476" t="n">
         <v>23109</v>
@@ -14231,7 +14231,7 @@
         <v>13.2056446075439</v>
       </c>
       <c r="G478" t="n">
-        <v>12.5294370651245</v>
+        <v>12.5294380187988</v>
       </c>
       <c r="H478" t="n">
         <v>22130</v>
@@ -14260,7 +14260,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G479" t="n">
-        <v>12.3451805114746</v>
+        <v>12.3451814651489</v>
       </c>
       <c r="H479" t="n">
         <v>43601</v>
@@ -14289,7 +14289,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G480" t="n">
-        <v>12.2714786529541</v>
+        <v>12.2714796066284</v>
       </c>
       <c r="H480" t="n">
         <v>20669</v>
@@ -14318,7 +14318,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G481" t="n">
-        <v>11.9766674041748</v>
+        <v>11.9766693115234</v>
       </c>
       <c r="H481" t="n">
         <v>21030</v>
@@ -14347,7 +14347,7 @@
         <v>12.3123216629028</v>
       </c>
       <c r="G482" t="n">
-        <v>11.6818580627441</v>
+        <v>11.6818571090698</v>
       </c>
       <c r="H482" t="n">
         <v>22527</v>
@@ -14376,7 +14376,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G483" t="n">
-        <v>11.7924108505249</v>
+        <v>11.7924118041992</v>
       </c>
       <c r="H483" t="n">
         <v>10814</v>
@@ -14405,7 +14405,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G484" t="n">
-        <v>12.1240720748901</v>
+        <v>12.1240739822388</v>
       </c>
       <c r="H484" t="n">
         <v>26687</v>
@@ -14434,7 +14434,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G485" t="n">
-        <v>11.7002840042114</v>
+        <v>11.7002849578857</v>
       </c>
       <c r="H485" t="n">
         <v>50887</v>
@@ -14521,7 +14521,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G488" t="n">
-        <v>13.0822076797485</v>
+        <v>13.0822067260742</v>
       </c>
       <c r="H488" t="n">
         <v>24122</v>
@@ -14608,7 +14608,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G491" t="n">
-        <v>13.0269298553467</v>
+        <v>13.0269317626953</v>
       </c>
       <c r="H491" t="n">
         <v>30641</v>
@@ -14666,7 +14666,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G493" t="n">
-        <v>14.7957906723022</v>
+        <v>14.7957916259766</v>
       </c>
       <c r="H493" t="n">
         <v>75829</v>
@@ -14695,7 +14695,7 @@
         <v>15.7496738433838</v>
       </c>
       <c r="G494" t="n">
-        <v>14.9431962966919</v>
+        <v>14.9431972503662</v>
       </c>
       <c r="H494" t="n">
         <v>32674</v>
@@ -14724,7 +14724,7 @@
         <v>15.633152961731</v>
       </c>
       <c r="G495" t="n">
-        <v>14.8326425552368</v>
+        <v>14.8326435089111</v>
       </c>
       <c r="H495" t="n">
         <v>23740</v>
@@ -14782,7 +14782,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G497" t="n">
-        <v>15.1827306747437</v>
+        <v>15.1827297210693</v>
       </c>
       <c r="H497" t="n">
         <v>39377</v>
@@ -14840,7 +14840,7 @@
         <v>16.7206764221191</v>
       </c>
       <c r="G499" t="n">
-        <v>15.8644771575928</v>
+        <v>15.8644781112671</v>
       </c>
       <c r="H499" t="n">
         <v>78961</v>
@@ -14869,7 +14869,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G500" t="n">
-        <v>15.2932844161987</v>
+        <v>15.2932834625244</v>
       </c>
       <c r="H500" t="n">
         <v>75736</v>
@@ -14927,7 +14927,7 @@
         <v>15.3030118942261</v>
       </c>
       <c r="G502" t="n">
-        <v>14.5194063186646</v>
+        <v>14.5194072723389</v>
       </c>
       <c r="H502" t="n">
         <v>62720</v>
@@ -15043,7 +15043,7 @@
         <v>14.7980899810791</v>
       </c>
       <c r="G506" t="n">
-        <v>14.0403394699097</v>
+        <v>14.040340423584</v>
       </c>
       <c r="H506" t="n">
         <v>43424</v>
@@ -15101,7 +15101,7 @@
         <v>14.4679489135742</v>
       </c>
       <c r="G508" t="n">
-        <v>13.7271041870117</v>
+        <v>13.727105140686</v>
       </c>
       <c r="H508" t="n">
         <v>20871</v>
@@ -15159,7 +15159,7 @@
         <v>14.7398300170898</v>
       </c>
       <c r="G510" t="n">
-        <v>13.9850616455078</v>
+        <v>13.9850635528564</v>
       </c>
       <c r="H510" t="n">
         <v>31610</v>
@@ -15217,7 +15217,7 @@
         <v>15.4001121520996</v>
       </c>
       <c r="G512" t="n">
-        <v>14.6115341186523</v>
+        <v>14.6115350723267</v>
       </c>
       <c r="H512" t="n">
         <v>22649</v>
@@ -15246,7 +15246,7 @@
         <v>15.6914129257202</v>
       </c>
       <c r="G513" t="n">
-        <v>14.8879194259644</v>
+        <v>14.8879203796387</v>
       </c>
       <c r="H513" t="n">
         <v>54549</v>
@@ -15304,7 +15304,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G515" t="n">
-        <v>14.7022838592529</v>
+        <v>14.7022848129272</v>
       </c>
       <c r="H515" t="n">
         <v>22064</v>
@@ -15333,7 +15333,7 @@
         <v>15.4777927398682</v>
       </c>
       <c r="G516" t="n">
-        <v>14.7951021194458</v>
+        <v>14.7951030731201</v>
       </c>
       <c r="H516" t="n">
         <v>13193</v>
@@ -15420,7 +15420,7 @@
         <v>15.5748929977417</v>
       </c>
       <c r="G519" t="n">
-        <v>14.8879203796387</v>
+        <v>14.8879194259644</v>
       </c>
       <c r="H519" t="n">
         <v>10780</v>
@@ -15449,7 +15449,7 @@
         <v>15.8661937713623</v>
       </c>
       <c r="G520" t="n">
-        <v>15.16637134552</v>
+        <v>15.1663722991943</v>
       </c>
       <c r="H520" t="n">
         <v>26150</v>
@@ -15478,7 +15478,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G521" t="n">
-        <v>14.7022838592529</v>
+        <v>14.7022848129272</v>
       </c>
       <c r="H521" t="n">
         <v>20529</v>
@@ -15536,7 +15536,7 @@
         <v>16.0215549468994</v>
       </c>
       <c r="G523" t="n">
-        <v>15.3148813247681</v>
+        <v>15.3148803710938</v>
       </c>
       <c r="H523" t="n">
         <v>26072</v>
@@ -15594,7 +15594,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G525" t="n">
-        <v>14.9064836502075</v>
+        <v>14.9064826965332</v>
       </c>
       <c r="H525" t="n">
         <v>16186</v>
@@ -15652,7 +15652,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G527" t="n">
-        <v>14.9064836502075</v>
+        <v>14.9064826965332</v>
       </c>
       <c r="H527" t="n">
         <v>40650</v>
@@ -15681,7 +15681,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G528" t="n">
-        <v>14.9807376861572</v>
+        <v>14.9807367324829</v>
       </c>
       <c r="H528" t="n">
         <v>11405</v>
@@ -15739,7 +15739,7 @@
         <v>15.2253322601318</v>
       </c>
       <c r="G530" t="n">
-        <v>14.5537767410278</v>
+        <v>14.5537776947021</v>
       </c>
       <c r="H530" t="n">
         <v>10013</v>
@@ -15797,7 +15797,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G532" t="n">
-        <v>14.8322296142578</v>
+        <v>14.8322286605835</v>
       </c>
       <c r="H532" t="n">
         <v>14290</v>
@@ -15826,7 +15826,7 @@
         <v>15.613733291626</v>
       </c>
       <c r="G533" t="n">
-        <v>14.9250469207764</v>
+        <v>14.9250459671021</v>
       </c>
       <c r="H533" t="n">
         <v>26443</v>
@@ -15913,7 +15913,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G536" t="n">
-        <v>14.9064836502075</v>
+        <v>14.9064826965332</v>
       </c>
       <c r="H536" t="n">
         <v>7951</v>
@@ -15942,7 +15942,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G537" t="n">
-        <v>15.2963171005249</v>
+        <v>15.2963161468506</v>
       </c>
       <c r="H537" t="n">
         <v>21472</v>
@@ -16145,7 +16145,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G544" t="n">
-        <v>14.8322296142578</v>
+        <v>14.8322286605835</v>
       </c>
       <c r="H544" t="n">
         <v>20980</v>
@@ -16174,7 +16174,7 @@
         <v>16.1769142150879</v>
       </c>
       <c r="G545" t="n">
-        <v>15.4633846282959</v>
+        <v>15.4633855819702</v>
       </c>
       <c r="H545" t="n">
         <v>51347</v>
@@ -16203,7 +16203,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G546" t="n">
-        <v>16.0574188232422</v>
+        <v>16.0574207305908</v>
       </c>
       <c r="H546" t="n">
         <v>61019</v>
@@ -16232,7 +16232,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G547" t="n">
-        <v>16.8556499481201</v>
+        <v>16.8556537628174</v>
       </c>
       <c r="H547" t="n">
         <v>42324</v>
@@ -16319,7 +16319,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G550" t="n">
-        <v>16.6143264770508</v>
+        <v>16.6143245697021</v>
       </c>
       <c r="H550" t="n">
         <v>37074</v>
@@ -16348,7 +16348,7 @@
         <v>17.536319732666</v>
       <